--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="228">
   <si>
     <t>📊  PANDUAN PENGGUNAAN — DATA PENCAPAIAN 2026</t>
   </si>
@@ -909,7 +909,7 @@
     <t>RONALD</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL —  12 SEPTEMBER 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL —  14 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>
@@ -2556,33 +2556,6 @@
     <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2613,6 +2586,33 @@
     <xf numFmtId="0" fontId="48" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2626,15 +2626,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2656,6 +2647,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4299,11 +4299,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>219</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -4623,33 +4623,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -4658,49 +4658,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -4725,13 +4725,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="172" t="s">
         <v>216</v>
       </c>
@@ -5847,21 +5847,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
-      <c r="F67" s="285"/>
-      <c r="G67" s="269" t="s">
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
+      <c r="F67" s="292"/>
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -6180,10 +6180,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -6495,6 +6495,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -6509,12 +6515,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="C3" s="75">
         <f ca="1">IF($J$5&lt;&gt;"",$J$5,MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),9,1)),EOMONTH(DATE(YEAR(TODAY()),9,1),0),11)-MAX(0,$J$3-$J$4)))</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="76" t="s">
         <v>104</v>
@@ -6718,19 +6718,19 @@
         <v>112</v>
       </c>
       <c r="C10" s="234">
-        <v>90465097.389457002</v>
+        <v>94300637.951456994</v>
       </c>
       <c r="D10" s="234">
         <v>20944050.82</v>
       </c>
       <c r="E10" s="234">
-        <v>83709000.253910005</v>
+        <v>99411702.953909993</v>
       </c>
       <c r="F10" s="234">
-        <v>70576712.069966003</v>
+        <v>76315833.649960995</v>
       </c>
       <c r="G10" s="234">
-        <v>265694860.533333</v>
+        <v>290972225.375328</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="111"/>
@@ -6749,13 +6749,13 @@
         <v>8173668</v>
       </c>
       <c r="E11" s="234">
-        <v>124887387.99950001</v>
-      </c>
-      <c r="F11" s="234" t="s">
-        <v>165</v>
+        <v>148761261.99939999</v>
+      </c>
+      <c r="F11" s="234">
+        <v>0</v>
       </c>
       <c r="G11" s="234">
-        <v>136811055.99950001</v>
+        <v>160684929.99939999</v>
       </c>
       <c r="H11" s="111"/>
       <c r="I11" s="111"/>
@@ -6768,19 +6768,19 @@
         <v>70</v>
       </c>
       <c r="C12" s="234">
-        <v>87927404.296865001</v>
+        <v>90457134.376817003</v>
       </c>
       <c r="D12" s="234">
-        <v>46810267.45149</v>
+        <v>47804580.981486998</v>
       </c>
       <c r="E12" s="234">
-        <v>64584785.079810999</v>
+        <v>75155055.669801995</v>
       </c>
       <c r="F12" s="234">
         <v>34989283.75</v>
       </c>
       <c r="G12" s="234">
-        <v>234311740.57816601</v>
+        <v>248406054.778106</v>
       </c>
       <c r="H12" s="111"/>
       <c r="I12" s="111"/>
@@ -6793,19 +6793,19 @@
         <v>114</v>
       </c>
       <c r="C13" s="234">
-        <v>16816680.42481</v>
+        <v>17858099.384810001</v>
       </c>
       <c r="D13" s="234">
-        <v>10857800.079988001</v>
+        <v>11385728.009987</v>
       </c>
       <c r="E13" s="234">
-        <v>96492433.349796996</v>
+        <v>105548694.69976901</v>
       </c>
       <c r="F13" s="234">
         <v>23539329.489999998</v>
       </c>
       <c r="G13" s="234">
-        <v>147706243.34459499</v>
+        <v>158331851.584566</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="111"/>
@@ -6818,19 +6818,19 @@
         <v>115</v>
       </c>
       <c r="C14" s="234">
-        <v>216211066.54874799</v>
+        <v>217006066.54874799</v>
       </c>
       <c r="D14" s="234">
         <v>21781667.005913999</v>
       </c>
       <c r="E14" s="234">
-        <v>80153855.929943994</v>
+        <v>80743855.929943994</v>
       </c>
       <c r="F14" s="234">
-        <v>174709642.90987501</v>
+        <v>178712210.57987499</v>
       </c>
       <c r="G14" s="234">
-        <v>492856232.394481</v>
+        <v>498243800.06448102</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="111"/>
@@ -6843,10 +6843,10 @@
         <v>118</v>
       </c>
       <c r="C15" s="234">
-        <v>492038424.70114303</v>
+        <v>512902821.09112298</v>
       </c>
       <c r="D15" s="234">
-        <v>3060767.4569959999</v>
+        <v>3499064.7569960002</v>
       </c>
       <c r="E15" s="234">
         <v>30690917.85997</v>
@@ -6855,7 +6855,7 @@
         <v>11200000.32</v>
       </c>
       <c r="G15" s="234">
-        <v>536990110.33810902</v>
+        <v>558292804.02808905</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="111"/>
@@ -6868,19 +6868,19 @@
         <v>120</v>
       </c>
       <c r="C16" s="234">
-        <v>202909288.52531099</v>
+        <v>225357040.79817799</v>
       </c>
       <c r="D16" s="234">
-        <v>22161819.63998</v>
+        <v>22434819.63998</v>
       </c>
       <c r="E16" s="234">
-        <v>153219279.709703</v>
+        <v>156468829.24970099</v>
       </c>
       <c r="F16" s="234">
-        <v>446419095.06998199</v>
+        <v>526669634.76998198</v>
       </c>
       <c r="G16" s="234">
-        <v>824709482.94497597</v>
+        <v>930930324.45784104</v>
       </c>
       <c r="H16" s="111"/>
       <c r="I16" s="111"/>
@@ -6893,19 +6893,19 @@
         <v>122</v>
       </c>
       <c r="C17" s="234">
-        <v>57296138.647610001</v>
+        <v>60141278.285573997</v>
       </c>
       <c r="D17" s="234">
         <v>9978337.7908999994</v>
       </c>
       <c r="E17" s="234">
-        <v>43291371.869258001</v>
+        <v>52967051.869258001</v>
       </c>
       <c r="F17" s="234">
         <v>23000000.5</v>
       </c>
       <c r="G17" s="234">
-        <v>133565848.807768</v>
+        <v>146086668.445732</v>
       </c>
       <c r="H17" s="111"/>
       <c r="I17" s="111"/>
@@ -6919,19 +6919,19 @@
         <v>123</v>
       </c>
       <c r="C18" s="234">
-        <v>8335580</v>
+        <v>8495810</v>
       </c>
       <c r="D18" s="234">
         <v>88602544.295750007</v>
       </c>
       <c r="E18" s="234">
-        <v>34074001.5</v>
+        <v>35293741.5</v>
       </c>
       <c r="F18" s="234">
-        <v>54670271.420000002</v>
+        <v>59881082.359999999</v>
       </c>
       <c r="G18" s="234">
-        <v>185682397.21575001</v>
+        <v>192273178.15575001</v>
       </c>
       <c r="H18" s="111"/>
       <c r="I18" s="111"/>
@@ -6945,19 +6945,19 @@
         <v>169</v>
       </c>
       <c r="C19" s="234">
-        <v>7128958.96</v>
-      </c>
-      <c r="D19" s="234" t="s">
-        <v>165</v>
-      </c>
-      <c r="E19" s="234" t="s">
-        <v>165</v>
+        <v>37937447.460000001</v>
+      </c>
+      <c r="D19" s="234">
+        <v>0</v>
+      </c>
+      <c r="E19" s="234">
+        <v>0</v>
       </c>
       <c r="F19" s="234">
-        <v>2198198.14</v>
+        <v>4684684.5599999996</v>
       </c>
       <c r="G19" s="234">
-        <v>9327157.0999999996</v>
+        <v>42622132.020000003</v>
       </c>
       <c r="H19" s="111"/>
       <c r="I19" s="111"/>
@@ -6971,19 +6971,19 @@
         <v>170</v>
       </c>
       <c r="C20" s="234">
-        <v>74419869.560000002</v>
-      </c>
-      <c r="D20" s="234" t="s">
-        <v>165</v>
-      </c>
-      <c r="E20" s="234" t="s">
-        <v>165</v>
+        <v>101915659.56</v>
+      </c>
+      <c r="D20" s="234">
+        <v>0</v>
+      </c>
+      <c r="E20" s="234">
+        <v>0</v>
       </c>
       <c r="F20" s="234">
         <v>5723693.54</v>
       </c>
       <c r="G20" s="234">
-        <v>80143563.099999994</v>
+        <v>107639353.09999999</v>
       </c>
       <c r="H20" s="111"/>
       <c r="I20" s="111"/>
@@ -7001,26 +7001,26 @@
         <v>124</v>
       </c>
       <c r="C21" s="234">
-        <v>131955015.304013</v>
+        <v>138779411.85907</v>
       </c>
       <c r="D21" s="234">
-        <v>27491961.544973999</v>
+        <v>27897366.944974001</v>
       </c>
       <c r="E21" s="234">
-        <v>73171648.789895996</v>
+        <v>78549937.029896006</v>
       </c>
       <c r="F21" s="234">
-        <v>195859849.49992001</v>
+        <v>205798588.24992001</v>
       </c>
       <c r="G21" s="234">
-        <v>428478475.13880301</v>
+        <v>451025304.08385998</v>
       </c>
       <c r="H21" s="111"/>
       <c r="I21" s="111"/>
       <c r="J21" s="111"/>
       <c r="M21" s="14">
         <f>SUM(C33,C34)+M20</f>
-        <v>264937331.65099001</v>
+        <v>331139383.81018001</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>224</v>
@@ -7031,19 +7031,19 @@
         <v>125</v>
       </c>
       <c r="C22" s="234">
-        <v>112429542.756111</v>
+        <v>122963699.481111</v>
       </c>
       <c r="D22" s="234">
-        <v>36086093.799973004</v>
+        <v>36359093.799973004</v>
       </c>
       <c r="E22" s="234">
-        <v>91954325.497528002</v>
+        <v>99646577.797502995</v>
       </c>
       <c r="F22" s="234">
-        <v>146008228.63973001</v>
+        <v>160386697.35973001</v>
       </c>
       <c r="G22" s="234">
-        <v>386478190.69334197</v>
+        <v>419356068.438317</v>
       </c>
       <c r="H22" s="111"/>
       <c r="I22" s="111"/>
@@ -7054,19 +7054,19 @@
         <v>126</v>
       </c>
       <c r="C23" s="234">
-        <v>230276351.96849599</v>
+        <v>246152018.821336</v>
       </c>
       <c r="D23" s="234">
-        <v>31105916.244963001</v>
+        <v>31651916.244963001</v>
       </c>
       <c r="E23" s="234">
-        <v>103293334.36991701</v>
+        <v>107975721.769917</v>
       </c>
       <c r="F23" s="234">
-        <v>270778557.89970303</v>
+        <v>299201801.53968298</v>
       </c>
       <c r="G23" s="234">
-        <v>635454160.48307896</v>
+        <v>684981458.37589896</v>
       </c>
       <c r="H23" s="111"/>
       <c r="I23" s="111"/>
@@ -7077,19 +7077,19 @@
         <v>225</v>
       </c>
       <c r="C24" s="234">
-        <v>105250806.02646799</v>
+        <v>112131143.770466</v>
       </c>
       <c r="D24" s="234">
-        <v>24274459.509978998</v>
+        <v>26436621.659975</v>
       </c>
       <c r="E24" s="234">
-        <v>84552008.768277004</v>
+        <v>91731288.128275007</v>
       </c>
       <c r="F24" s="234">
-        <v>27923423.170000002</v>
+        <v>28644143.870000001</v>
       </c>
       <c r="G24" s="234">
-        <v>242000697.47472399</v>
+        <v>258943197.428716</v>
       </c>
       <c r="H24" s="111"/>
       <c r="I24" s="111"/>
@@ -7100,19 +7100,19 @@
         <v>220</v>
       </c>
       <c r="C25" s="234">
-        <v>132173249.01884601</v>
+        <v>138186464.73536199</v>
       </c>
       <c r="D25" s="234">
-        <v>46302273.721727997</v>
+        <v>49441138.601727001</v>
       </c>
       <c r="E25" s="234">
-        <v>49505757.005854003</v>
+        <v>54299554.287846997</v>
       </c>
       <c r="F25" s="234">
         <v>20000000.43</v>
       </c>
       <c r="G25" s="234">
-        <v>247981280.17642799</v>
+        <v>261927158.05493599</v>
       </c>
       <c r="H25" s="111"/>
       <c r="I25" s="111"/>
@@ -7123,19 +7123,19 @@
         <v>127</v>
       </c>
       <c r="C26" s="234">
-        <v>236825245.38513801</v>
+        <v>252837877.07610399</v>
       </c>
       <c r="D26" s="234">
         <v>150942202.70816001</v>
       </c>
       <c r="E26" s="234">
-        <v>126208925.25759999</v>
+        <v>166101717.34703001</v>
       </c>
       <c r="F26" s="234">
         <v>7660216.3833999997</v>
       </c>
       <c r="G26" s="234">
-        <v>521636589.73429799</v>
+        <v>577542013.51469398</v>
       </c>
       <c r="H26" s="111"/>
       <c r="I26" s="111"/>
@@ -7178,7 +7178,7 @@
         <v>131</v>
       </c>
       <c r="C31" s="234">
-        <v>103000858.655599</v>
+        <v>106473741.715563</v>
       </c>
       <c r="G31" s="111"/>
       <c r="H31" s="111"/>
@@ -7189,7 +7189,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="234">
-        <v>73731814.289717004</v>
+        <v>84600229.289704993</v>
       </c>
       <c r="G32" s="111"/>
       <c r="H32" s="111"/>
@@ -7200,7 +7200,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="234">
-        <v>64693415.257090002</v>
+        <v>67261415.257090002</v>
       </c>
       <c r="G33" s="111"/>
       <c r="H33" s="111"/>
@@ -7211,7 +7211,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="234">
-        <v>200243916.39390001</v>
+        <v>263877968.55309001</v>
       </c>
       <c r="G34" s="111"/>
       <c r="H34" s="111"/>
@@ -7256,17 +7256,17 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
       <c r="F40" s="174">
         <f ca="1">IF(MONTH(TODAY())=9,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;9,1,0))</f>
-        <v>0.4</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="G40" s="192" t="s">
         <v>187</v>
@@ -7353,35 +7353,35 @@
       </c>
       <c r="E42" s="46">
         <f>H65</f>
-        <v>1714170294.8118732</v>
+        <v>1868269790.1090329</v>
       </c>
       <c r="F42" s="176">
         <f>IFERROR(E42/D42,0)</f>
-        <v>0.37993164613933511</v>
+        <v>0.41408652275497265</v>
       </c>
       <c r="G42" s="184">
         <f>D42*$H$40-E42</f>
-        <v>2797615738.8875227</v>
+        <v>2643516243.5903635</v>
       </c>
       <c r="H42" s="184">
         <f ca="1">IFERROR(G42/$C$3,0)</f>
-        <v>174850983.68047017</v>
+        <v>176234416.23935756</v>
       </c>
       <c r="I42" s="204">
         <f>D42*$J$40-E42</f>
-        <v>2797615738.8875227</v>
+        <v>2643516243.5903635</v>
       </c>
       <c r="J42" s="204">
         <f ca="1">IFERROR(I42/$C$3,0)</f>
-        <v>174850983.68047017</v>
+        <v>176234416.23935756</v>
       </c>
       <c r="K42" s="185">
         <f>D42*$L$40-E42</f>
-        <v>2797615738.8875227</v>
+        <v>2643516243.5903635</v>
       </c>
       <c r="L42" s="185">
         <f ca="1">IFERROR(K42/$C$3,0)</f>
-        <v>174850983.68047017</v>
+        <v>176234416.23935756</v>
       </c>
       <c r="S42" s="173">
         <v>0.8</v>
@@ -7400,35 +7400,35 @@
       </c>
       <c r="E43" s="46">
         <f>I65</f>
-        <v>545513062.61379898</v>
+        <v>553833736.50379002</v>
       </c>
       <c r="F43" s="176">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.38927256049542291</v>
+        <v>0.39521010856198002</v>
       </c>
       <c r="G43" s="184">
         <f>D43*$H$40-E43</f>
-        <v>855852247.90161598</v>
+        <v>847531574.01162493</v>
       </c>
       <c r="H43" s="184">
         <f ca="1">IFERROR(G43/$C$3,0)</f>
-        <v>53490765.493850999</v>
+        <v>56502104.934108332</v>
       </c>
       <c r="I43" s="204">
         <f>D43*$J$40-E43</f>
-        <v>855852247.90161598</v>
+        <v>847531574.01162493</v>
       </c>
       <c r="J43" s="204">
         <f ca="1">IFERROR(I43/$C$3,0)</f>
-        <v>53490765.493850999</v>
+        <v>56502104.934108332</v>
       </c>
       <c r="K43" s="185">
         <f>D43*$L$40-E43</f>
-        <v>855852247.90161598</v>
+        <v>847531574.01162493</v>
       </c>
       <c r="L43" s="185">
         <f ca="1">IFERROR(K43/$C$3,0)</f>
-        <v>53490765.493850999</v>
+        <v>56502104.934108332</v>
       </c>
       <c r="S43" s="173">
         <v>0.85</v>
@@ -7447,35 +7447,35 @@
       </c>
       <c r="E44" s="46">
         <f>J65</f>
-        <v>1209098115.380995</v>
+        <v>1352654990.2322519</v>
       </c>
       <c r="F44" s="176">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.41058553605466308</v>
+        <v>0.45933457938317929</v>
       </c>
       <c r="G44" s="184">
         <f>IF(D44=0,0,D44*$H$40-E44)</f>
-        <v>1735716080.9476902</v>
+        <v>1592159206.0964334</v>
       </c>
       <c r="H44" s="184">
         <f ca="1">IFERROR(G44/$C$3,0)</f>
-        <v>108482255.05923064</v>
+        <v>106143947.07309556</v>
       </c>
       <c r="I44" s="204">
         <f>IF(D44=0,0,D44*$J$40-E44)</f>
-        <v>1735716080.9476902</v>
+        <v>1592159206.0964334</v>
       </c>
       <c r="J44" s="204">
         <f ca="1">IFERROR(I44/$C$3,0)</f>
-        <v>108482255.05923064</v>
+        <v>106143947.07309556</v>
       </c>
       <c r="K44" s="185">
         <f>IF(D44=0,0,D44*$L$40-E44)</f>
-        <v>1735716080.9476902</v>
+        <v>1592159206.0964334</v>
       </c>
       <c r="L44" s="185">
         <f ca="1">IFERROR(K44/$C$3,0)</f>
-        <v>108482255.05923064</v>
+        <v>106143947.07309556</v>
       </c>
       <c r="S44" s="173">
         <v>0.9</v>
@@ -7494,35 +7494,35 @@
       </c>
       <c r="E45" s="46">
         <f>E74</f>
-        <v>441670004.59630603</v>
+        <v>522213354.81544799</v>
       </c>
       <c r="F45" s="176">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.25377127403455235</v>
+        <v>0.30004923809689554</v>
       </c>
       <c r="G45" s="184">
         <f>D45*$H$40-E45</f>
-        <v>1298755527.3185875</v>
+        <v>1218212177.0994456</v>
       </c>
       <c r="H45" s="184">
         <f ca="1">IFERROR(G45/$C$3,0)</f>
-        <v>81172220.457411721</v>
+        <v>81214145.139963046</v>
       </c>
       <c r="I45" s="204">
         <f>D45*$J$40-E45</f>
-        <v>1298755527.3185875</v>
+        <v>1218212177.0994456</v>
       </c>
       <c r="J45" s="204">
         <f ca="1">IFERROR(I45/$C$3,0)</f>
-        <v>81172220.457411721</v>
+        <v>81214145.139963046</v>
       </c>
       <c r="K45" s="185">
         <f>D45*$L$40-E45</f>
-        <v>1298755527.3185875</v>
+        <v>1218212177.0994456</v>
       </c>
       <c r="L45" s="185">
         <f ca="1">IFERROR(K45/$C$3,0)</f>
-        <v>81172220.457411721</v>
+        <v>81214145.139963046</v>
       </c>
       <c r="S45" s="173">
         <v>0.95</v>
@@ -7539,35 +7539,35 @@
       </c>
       <c r="E46" s="47">
         <f>SUM(E42:E45)</f>
-        <v>3910451477.4029732</v>
+        <v>4296971871.6605225</v>
       </c>
       <c r="F46" s="177">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.36896652054715218</v>
+        <v>0.4054362442641779</v>
       </c>
       <c r="G46" s="181">
         <f>SUM(G42:G45)</f>
-        <v>6687939595.0554161</v>
+        <v>6301419200.7978668</v>
       </c>
       <c r="H46" s="181">
         <f ca="1">IFERROR(G46/$C$3,0)</f>
-        <v>417996224.69096351</v>
+        <v>420094613.38652444</v>
       </c>
       <c r="I46" s="186">
         <f>SUM(I42:I45)</f>
-        <v>6687939595.0554161</v>
+        <v>6301419200.7978668</v>
       </c>
       <c r="J46" s="186">
         <f ca="1">IFERROR(I46/$C$3,0)</f>
-        <v>417996224.69096351</v>
+        <v>420094613.38652444</v>
       </c>
       <c r="K46" s="186">
         <f>SUM(K42:K45)</f>
-        <v>6687939595.0554161</v>
+        <v>6301419200.7978668</v>
       </c>
       <c r="L46" s="186">
         <f ca="1">IFERROR(K46/$C$3,0)</f>
-        <v>417996224.69096351</v>
+        <v>420094613.38652444</v>
       </c>
       <c r="S46" s="173">
         <v>1</v>
@@ -7580,33 +7580,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -7615,49 +7615,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -7682,13 +7682,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -7721,47 +7721,47 @@
       </c>
       <c r="H51" s="114">
         <f>SUMIF($B$10:$B$26,$T51,C$10:C$26)+SUMIF($B$10:$B$26,$U51,C$10:C$26)</f>
-        <v>131955015.304013</v>
+        <v>138779411.85907</v>
       </c>
       <c r="I51" s="114">
         <f t="shared" ref="I51:I64" si="1">SUMIF($B$10:$B$26,$T51,D$10:D$26)+SUMIF($B$10:$B$26,$U51,D$10:D$26)</f>
-        <v>27491961.544973999</v>
+        <v>27897366.944974001</v>
       </c>
       <c r="J51" s="114">
         <f t="shared" ref="J51:J64" si="2">SUMIF($B$10:$B$26,$T51,E$10:E$26)+SUMIF($B$10:$B$26,$U51,E$10:E$26)</f>
-        <v>73171648.789895996</v>
+        <v>78549937.029896006</v>
       </c>
       <c r="K51" s="114">
         <f t="shared" ref="K51:K64" si="3">SUM(H51:J51)</f>
-        <v>232618625.63888299</v>
+        <v>245226715.83394003</v>
       </c>
       <c r="L51" s="187">
         <f t="shared" ref="L51:L65" si="4">IFERROR(K51/G51,0)</f>
-        <v>0.45224205776070425</v>
+        <v>0.47675388968553384</v>
       </c>
       <c r="M51" s="184">
         <f t="shared" ref="M51:M64" si="5">G51*$H$40-K51</f>
-        <v>281748894.2479316</v>
+        <v>269140804.05287457</v>
       </c>
       <c r="N51" s="184">
         <f t="shared" ref="N51:N65" ca="1" si="6">IFERROR(M51/$C$3,0)</f>
-        <v>17609305.890495725</v>
+        <v>17942720.270191636</v>
       </c>
       <c r="O51" s="180">
         <f t="shared" ref="O51:O64" si="7">G51*$J$40-K51</f>
-        <v>281748894.2479316</v>
+        <v>269140804.05287457</v>
       </c>
       <c r="P51" s="180">
         <f t="shared" ref="P51:P65" ca="1" si="8">IFERROR(O51/$C$3,0)</f>
-        <v>17609305.890495725</v>
+        <v>17942720.270191636</v>
       </c>
       <c r="Q51" s="185">
         <f t="shared" ref="Q51:Q64" si="9">G51*$L$40-K51</f>
-        <v>281748894.2479316</v>
+        <v>269140804.05287457</v>
       </c>
       <c r="R51" s="185">
         <f t="shared" ref="R51:R65" ca="1" si="10">IFERROR(Q51/$C$3,0)</f>
-        <v>17609305.890495725</v>
+        <v>17942720.270191636</v>
       </c>
       <c r="T51" t="s">
         <v>124</v>
@@ -7795,47 +7795,47 @@
       </c>
       <c r="H52" s="114">
         <f t="shared" ref="H52:H64" si="11">SUMIF($B$10:$B$26,$T52,C$10:C$26)+SUMIF($B$10:$B$26,$U52,C$10:C$26)</f>
-        <v>104744084.72167501</v>
+        <v>108315233.761627</v>
       </c>
       <c r="I52" s="114">
         <f t="shared" si="1"/>
-        <v>57668067.531478003</v>
+        <v>59190308.991474003</v>
       </c>
       <c r="J52" s="114">
         <f t="shared" si="2"/>
-        <v>161077218.42960799</v>
+        <v>180703750.369571</v>
       </c>
       <c r="K52" s="114">
         <f t="shared" si="3"/>
-        <v>323489370.68276101</v>
+        <v>348209293.12267196</v>
       </c>
       <c r="L52" s="187">
         <f t="shared" si="4"/>
-        <v>0.41181354040812546</v>
+        <v>0.44328288592976639</v>
       </c>
       <c r="M52" s="184">
         <f t="shared" si="5"/>
-        <v>462034510.73738056</v>
+        <v>437314588.29746962</v>
       </c>
       <c r="N52" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>28877156.921086285</v>
+        <v>29154305.886497974</v>
       </c>
       <c r="O52" s="180">
         <f t="shared" si="7"/>
-        <v>462034510.73738056</v>
+        <v>437314588.29746962</v>
       </c>
       <c r="P52" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>28877156.921086285</v>
+        <v>29154305.886497974</v>
       </c>
       <c r="Q52" s="185">
         <f t="shared" si="9"/>
-        <v>462034510.73738056</v>
+        <v>437314588.29746962</v>
       </c>
       <c r="R52" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>28877156.921086285</v>
+        <v>29154305.886497974</v>
       </c>
       <c r="T52" t="s">
         <v>70</v>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H53" s="114">
         <f t="shared" si="11"/>
-        <v>7128958.96</v>
+        <v>37937447.460000001</v>
       </c>
       <c r="I53" s="114">
         <f t="shared" si="1"/>
@@ -7881,35 +7881,35 @@
       </c>
       <c r="K53" s="114">
         <f t="shared" si="3"/>
-        <v>7128958.96</v>
+        <v>37937447.460000001</v>
       </c>
       <c r="L53" s="187">
         <f t="shared" si="4"/>
-        <v>2.7111141959292349E-2</v>
+        <v>0.14427457493194137</v>
       </c>
       <c r="M53" s="184">
         <f t="shared" si="5"/>
-        <v>255824146.10301074</v>
+        <v>225015657.60301074</v>
       </c>
       <c r="N53" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>15989009.131438171</v>
+        <v>15001043.840200717</v>
       </c>
       <c r="O53" s="180">
         <f t="shared" si="7"/>
-        <v>255824146.10301074</v>
+        <v>225015657.60301074</v>
       </c>
       <c r="P53" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>15989009.131438171</v>
+        <v>15001043.840200717</v>
       </c>
       <c r="Q53" s="185">
         <f t="shared" si="9"/>
-        <v>255824146.10301074</v>
+        <v>225015657.60301074</v>
       </c>
       <c r="R53" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>15989009.131438171</v>
+        <v>15001043.840200717</v>
       </c>
       <c r="T53" t="s">
         <v>169</v>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="H54" s="114">
         <f t="shared" si="11"/>
-        <v>216211066.54874799</v>
+        <v>217006066.54874799</v>
       </c>
       <c r="I54" s="114">
         <f t="shared" si="1"/>
@@ -7951,39 +7951,39 @@
       </c>
       <c r="J54" s="114">
         <f t="shared" si="2"/>
-        <v>80153855.929943994</v>
+        <v>80743855.929943994</v>
       </c>
       <c r="K54" s="114">
         <f t="shared" si="3"/>
-        <v>318146589.48460597</v>
+        <v>319531589.48460597</v>
       </c>
       <c r="L54" s="187">
         <f t="shared" si="4"/>
-        <v>0.43781330944456232</v>
+        <v>0.43971925926022132</v>
       </c>
       <c r="M54" s="184">
         <f t="shared" si="5"/>
-        <v>408525219.30125958</v>
+        <v>407140219.30125958</v>
       </c>
       <c r="N54" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>25532826.206328724</v>
+        <v>27142681.286750637</v>
       </c>
       <c r="O54" s="180">
         <f t="shared" si="7"/>
-        <v>408525219.30125958</v>
+        <v>407140219.30125958</v>
       </c>
       <c r="P54" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>25532826.206328724</v>
+        <v>27142681.286750637</v>
       </c>
       <c r="Q54" s="185">
         <f t="shared" si="9"/>
-        <v>408525219.30125958</v>
+        <v>407140219.30125958</v>
       </c>
       <c r="R54" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>25532826.206328724</v>
+        <v>27142681.286750637</v>
       </c>
       <c r="T54" t="s">
         <v>115</v>
@@ -8025,39 +8025,39 @@
       </c>
       <c r="J55" s="114">
         <f t="shared" si="2"/>
-        <v>124887387.99950001</v>
+        <v>148761261.99939999</v>
       </c>
       <c r="K55" s="114">
         <f t="shared" si="3"/>
-        <v>136811055.99950001</v>
+        <v>160684929.99939999</v>
       </c>
       <c r="L55" s="187">
         <f t="shared" si="4"/>
-        <v>0.25467386715370066</v>
+        <v>0.29911509868338743</v>
       </c>
       <c r="M55" s="184">
         <f t="shared" si="5"/>
-        <v>400389943.57118559</v>
+        <v>376516069.57128561</v>
       </c>
       <c r="N55" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>25024371.473199099</v>
+        <v>25101071.304752372</v>
       </c>
       <c r="O55" s="180">
         <f t="shared" si="7"/>
-        <v>400389943.57118559</v>
+        <v>376516069.57128561</v>
       </c>
       <c r="P55" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>25024371.473199099</v>
+        <v>25101071.304752372</v>
       </c>
       <c r="Q55" s="185">
         <f t="shared" si="9"/>
-        <v>400389943.57118559</v>
+        <v>376516069.57128561</v>
       </c>
       <c r="R55" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>25024371.473199099</v>
+        <v>25101071.304752372</v>
       </c>
       <c r="T55" t="s">
         <v>182</v>
@@ -8091,47 +8091,47 @@
       </c>
       <c r="H56" s="114">
         <f t="shared" si="11"/>
-        <v>105250806.02646799</v>
+        <v>112131143.770466</v>
       </c>
       <c r="I56" s="114">
         <f t="shared" si="1"/>
-        <v>24274459.509978998</v>
+        <v>26436621.659975</v>
       </c>
       <c r="J56" s="114">
         <f t="shared" si="2"/>
-        <v>84552008.768277004</v>
+        <v>91731288.128275007</v>
       </c>
       <c r="K56" s="114">
         <f t="shared" si="3"/>
-        <v>214077274.30472398</v>
+        <v>230299053.558716</v>
       </c>
       <c r="L56" s="187">
         <f t="shared" si="4"/>
-        <v>0.37234327847587489</v>
+        <v>0.40055771875105189</v>
       </c>
       <c r="M56" s="184">
         <f t="shared" si="5"/>
-        <v>360868714.19549441</v>
+        <v>344646934.94150239</v>
       </c>
       <c r="N56" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>22554294.637218401</v>
+        <v>22976462.329433493</v>
       </c>
       <c r="O56" s="180">
         <f t="shared" si="7"/>
-        <v>360868714.19549441</v>
+        <v>344646934.94150239</v>
       </c>
       <c r="P56" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>22554294.637218401</v>
+        <v>22976462.329433493</v>
       </c>
       <c r="Q56" s="185">
         <f t="shared" si="9"/>
-        <v>360868714.19549441</v>
+        <v>344646934.94150239</v>
       </c>
       <c r="R56" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>22554294.637218401</v>
+        <v>22976462.329433493</v>
       </c>
       <c r="T56" t="s">
         <v>225</v>
@@ -8165,47 +8165,47 @@
       </c>
       <c r="H57" s="114">
         <f t="shared" si="11"/>
-        <v>202909288.52531099</v>
+        <v>225357040.79817799</v>
       </c>
       <c r="I57" s="114">
         <f t="shared" si="1"/>
-        <v>22161819.63998</v>
+        <v>22434819.63998</v>
       </c>
       <c r="J57" s="114">
         <f t="shared" si="2"/>
-        <v>153219279.709703</v>
+        <v>156468829.24970099</v>
       </c>
       <c r="K57" s="114">
         <f t="shared" si="3"/>
-        <v>378290387.87499398</v>
+        <v>404260689.68785894</v>
       </c>
       <c r="L57" s="187">
         <f t="shared" si="4"/>
-        <v>0.34105285103967631</v>
+        <v>0.36446673032271359</v>
       </c>
       <c r="M57" s="184">
         <f t="shared" si="5"/>
-        <v>730893677.64975262</v>
+        <v>704923375.83688772</v>
       </c>
       <c r="N57" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>45680854.853109539</v>
+        <v>46994891.722459182</v>
       </c>
       <c r="O57" s="180">
         <f t="shared" si="7"/>
-        <v>730893677.64975262</v>
+        <v>704923375.83688772</v>
       </c>
       <c r="P57" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>45680854.853109539</v>
+        <v>46994891.722459182</v>
       </c>
       <c r="Q57" s="185">
         <f t="shared" si="9"/>
-        <v>730893677.64975262</v>
+        <v>704923375.83688772</v>
       </c>
       <c r="R57" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>45680854.853109539</v>
+        <v>46994891.722459182</v>
       </c>
       <c r="T57" t="s">
         <v>120</v>
@@ -8239,47 +8239,47 @@
       </c>
       <c r="H58" s="114">
         <f t="shared" si="11"/>
-        <v>112429542.756111</v>
+        <v>122963699.481111</v>
       </c>
       <c r="I58" s="114">
         <f t="shared" si="1"/>
-        <v>36086093.799973004</v>
+        <v>36359093.799973004</v>
       </c>
       <c r="J58" s="114">
         <f t="shared" si="2"/>
-        <v>91954325.497528002</v>
+        <v>99646577.797502995</v>
       </c>
       <c r="K58" s="114">
         <f t="shared" si="3"/>
-        <v>240469962.05361199</v>
+        <v>258969371.078587</v>
       </c>
       <c r="L58" s="187">
         <f t="shared" si="4"/>
-        <v>0.39127472676516123</v>
+        <v>0.42137558073356779</v>
       </c>
       <c r="M58" s="184">
         <f t="shared" si="5"/>
-        <v>374110908.1234169</v>
+        <v>355611499.0984419</v>
       </c>
       <c r="N58" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>23381931.757713556</v>
+        <v>23707433.273229461</v>
       </c>
       <c r="O58" s="180">
         <f t="shared" si="7"/>
-        <v>374110908.1234169</v>
+        <v>355611499.0984419</v>
       </c>
       <c r="P58" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>23381931.757713556</v>
+        <v>23707433.273229461</v>
       </c>
       <c r="Q58" s="185">
         <f t="shared" si="9"/>
-        <v>374110908.1234169</v>
+        <v>355611499.0984419</v>
       </c>
       <c r="R58" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>23381931.757713556</v>
+        <v>23707433.273229461</v>
       </c>
       <c r="T58" t="s">
         <v>125</v>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="H59" s="114">
         <f t="shared" si="11"/>
-        <v>74419869.560000002</v>
+        <v>101915659.56</v>
       </c>
       <c r="I59" s="114">
         <f t="shared" si="1"/>
@@ -8325,35 +8325,35 @@
       </c>
       <c r="K59" s="114">
         <f t="shared" si="3"/>
-        <v>74419869.560000002</v>
+        <v>101915659.56</v>
       </c>
       <c r="L59" s="187">
         <f t="shared" si="4"/>
-        <v>0.16767020448343645</v>
+        <v>0.22961904635847757</v>
       </c>
       <c r="M59" s="184">
         <f t="shared" si="5"/>
-        <v>369426846.01642001</v>
+        <v>341931056.01642001</v>
       </c>
       <c r="N59" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>23089177.87602625</v>
+        <v>22795403.734428</v>
       </c>
       <c r="O59" s="180">
         <f t="shared" si="7"/>
-        <v>369426846.01642001</v>
+        <v>341931056.01642001</v>
       </c>
       <c r="P59" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>23089177.87602625</v>
+        <v>22795403.734428</v>
       </c>
       <c r="Q59" s="185">
         <f t="shared" si="9"/>
-        <v>369426846.01642001</v>
+        <v>341931056.01642001</v>
       </c>
       <c r="R59" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>23089177.87602625</v>
+        <v>22795403.734428</v>
       </c>
       <c r="T59" t="s">
         <v>170</v>
@@ -8387,47 +8387,47 @@
       </c>
       <c r="H60" s="114">
         <f t="shared" si="11"/>
-        <v>132173249.01884601</v>
+        <v>138186464.73536199</v>
       </c>
       <c r="I60" s="114">
         <f t="shared" si="1"/>
-        <v>46302273.721727997</v>
+        <v>49441138.601727001</v>
       </c>
       <c r="J60" s="114">
         <f t="shared" si="2"/>
-        <v>49505757.005854003</v>
+        <v>54299554.287846997</v>
       </c>
       <c r="K60" s="114">
         <f t="shared" si="3"/>
-        <v>227981279.74642801</v>
+        <v>241927157.62493598</v>
       </c>
       <c r="L60" s="187">
         <f t="shared" si="4"/>
-        <v>0.3936234608492728</v>
+        <v>0.41770186202863818</v>
       </c>
       <c r="M60" s="184">
         <f t="shared" si="5"/>
-        <v>351204928.4499557</v>
+        <v>337259050.57144773</v>
       </c>
       <c r="N60" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>21950308.028122231</v>
+        <v>22483936.704763182</v>
       </c>
       <c r="O60" s="180">
         <f t="shared" si="7"/>
-        <v>351204928.4499557</v>
+        <v>337259050.57144773</v>
       </c>
       <c r="P60" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>21950308.028122231</v>
+        <v>22483936.704763182</v>
       </c>
       <c r="Q60" s="185">
         <f t="shared" si="9"/>
-        <v>351204928.4499557</v>
+        <v>337259050.57144773</v>
       </c>
       <c r="R60" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>21950308.028122231</v>
+        <v>22483936.704763182</v>
       </c>
       <c r="T60" t="s">
         <v>220</v>
@@ -8461,47 +8461,47 @@
       </c>
       <c r="H61" s="114">
         <f t="shared" si="11"/>
-        <v>230276351.96849599</v>
+        <v>246152018.821336</v>
       </c>
       <c r="I61" s="114">
         <f t="shared" si="1"/>
-        <v>31105916.244963001</v>
+        <v>31651916.244963001</v>
       </c>
       <c r="J61" s="114">
         <f t="shared" si="2"/>
-        <v>103293334.36991701</v>
+        <v>107975721.769917</v>
       </c>
       <c r="K61" s="114">
         <f t="shared" si="3"/>
-        <v>364675602.58337599</v>
+        <v>385779656.83621603</v>
       </c>
       <c r="L61" s="187">
         <f t="shared" si="4"/>
-        <v>0.50890212934452961</v>
+        <v>0.53835268230445044</v>
       </c>
       <c r="M61" s="184">
         <f t="shared" si="5"/>
-        <v>351917198.96980554</v>
+        <v>330813144.7169655</v>
       </c>
       <c r="N61" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>21994824.935612846</v>
+        <v>22054209.6477977</v>
       </c>
       <c r="O61" s="180">
         <f t="shared" si="7"/>
-        <v>351917198.96980554</v>
+        <v>330813144.7169655</v>
       </c>
       <c r="P61" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>21994824.935612846</v>
+        <v>22054209.6477977</v>
       </c>
       <c r="Q61" s="185">
         <f t="shared" si="9"/>
-        <v>351917198.96980554</v>
+        <v>330813144.7169655</v>
       </c>
       <c r="R61" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>21994824.935612846</v>
+        <v>22054209.6477977</v>
       </c>
       <c r="T61" t="s">
         <v>126</v>
@@ -8535,7 +8535,7 @@
       </c>
       <c r="H62" s="114">
         <f t="shared" si="11"/>
-        <v>90465097.389457002</v>
+        <v>94300637.951456994</v>
       </c>
       <c r="I62" s="114">
         <f t="shared" si="1"/>
@@ -8543,39 +8543,39 @@
       </c>
       <c r="J62" s="114">
         <f t="shared" si="2"/>
-        <v>83709000.253910005</v>
+        <v>99411702.953909993</v>
       </c>
       <c r="K62" s="114">
         <f t="shared" si="3"/>
-        <v>195118148.46336702</v>
+        <v>214656391.72536698</v>
       </c>
       <c r="L62" s="187">
         <f t="shared" si="4"/>
-        <v>0.40903277852966574</v>
+        <v>0.44999145916487482</v>
       </c>
       <c r="M62" s="184">
         <f t="shared" si="5"/>
-        <v>281905109.09743452</v>
+        <v>262366865.83543453</v>
       </c>
       <c r="N62" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>17619069.318589658</v>
+        <v>17491124.38902897</v>
       </c>
       <c r="O62" s="180">
         <f t="shared" si="7"/>
-        <v>281905109.09743452</v>
+        <v>262366865.83543453</v>
       </c>
       <c r="P62" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>17619069.318589658</v>
+        <v>17491124.38902897</v>
       </c>
       <c r="Q62" s="185">
         <f t="shared" si="9"/>
-        <v>281905109.09743452</v>
+        <v>262366865.83543453</v>
       </c>
       <c r="R62" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>17619069.318589658</v>
+        <v>17491124.38902897</v>
       </c>
       <c r="T62" t="s">
         <v>112</v>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="H63" s="114">
         <f t="shared" si="11"/>
-        <v>236825245.38513801</v>
+        <v>252837877.07610399</v>
       </c>
       <c r="I63" s="114">
         <f t="shared" si="1"/>
@@ -8617,39 +8617,39 @@
       </c>
       <c r="J63" s="114">
         <f t="shared" si="2"/>
-        <v>126208925.25759999</v>
+        <v>166101717.34703001</v>
       </c>
       <c r="K63" s="114">
         <f t="shared" si="3"/>
-        <v>513976373.35089803</v>
+        <v>569881797.13129401</v>
       </c>
       <c r="L63" s="187">
         <f t="shared" si="4"/>
-        <v>0.52501534746754375</v>
+        <v>0.58212148505131633</v>
       </c>
       <c r="M63" s="184">
         <f t="shared" si="5"/>
-        <v>464997623.94290853</v>
+        <v>409092200.16251254</v>
       </c>
       <c r="N63" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>29062351.496431783</v>
+        <v>27272813.344167504</v>
       </c>
       <c r="O63" s="180">
         <f t="shared" si="7"/>
-        <v>464997623.94290853</v>
+        <v>409092200.16251254</v>
       </c>
       <c r="P63" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>29062351.496431783</v>
+        <v>27272813.344167504</v>
       </c>
       <c r="Q63" s="185">
         <f t="shared" si="9"/>
-        <v>464997623.94290853</v>
+        <v>409092200.16251254</v>
       </c>
       <c r="R63" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>29062351.496431783</v>
+        <v>27272813.344167504</v>
       </c>
       <c r="T63" t="s">
         <v>127</v>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="H64" s="114">
         <f t="shared" si="11"/>
-        <v>65631718.647610001</v>
+        <v>68637088.285573989</v>
       </c>
       <c r="I64" s="114">
         <f t="shared" si="1"/>
@@ -8691,39 +8691,39 @@
       </c>
       <c r="J64" s="114">
         <f t="shared" si="2"/>
-        <v>77365373.369258001</v>
+        <v>88260793.369258001</v>
       </c>
       <c r="K64" s="114">
         <f t="shared" si="3"/>
-        <v>241577974.10351801</v>
+        <v>255478763.74148202</v>
       </c>
       <c r="L64" s="187">
         <f t="shared" si="4"/>
-        <v>0.44993766129786139</v>
+        <v>0.47582780630428895</v>
       </c>
       <c r="M64" s="184">
         <f t="shared" si="5"/>
-        <v>295336347.33087277</v>
+        <v>281435557.69290876</v>
       </c>
       <c r="N64" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>18458521.708179548</v>
+        <v>18762370.512860585</v>
       </c>
       <c r="O64" s="180">
         <f t="shared" si="7"/>
-        <v>295336347.33087277</v>
+        <v>281435557.69290876</v>
       </c>
       <c r="P64" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>18458521.708179548</v>
+        <v>18762370.512860585</v>
       </c>
       <c r="Q64" s="185">
         <f t="shared" si="9"/>
-        <v>295336347.33087277</v>
+        <v>281435557.69290876</v>
       </c>
       <c r="R64" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>18458521.708179548</v>
+        <v>18762370.512860585</v>
       </c>
       <c r="T64" t="s">
         <v>122</v>
@@ -8755,47 +8755,47 @@
       </c>
       <c r="H65" s="135">
         <f t="shared" si="12"/>
-        <v>1714170294.8118732</v>
+        <v>1868269790.1090329</v>
       </c>
       <c r="I65" s="135">
         <f t="shared" si="12"/>
-        <v>545513062.61379898</v>
+        <v>553833736.50379002</v>
       </c>
       <c r="J65" s="135">
         <f t="shared" si="12"/>
-        <v>1209098115.380995</v>
+        <v>1352654990.2322519</v>
       </c>
       <c r="K65" s="135">
         <f t="shared" si="12"/>
-        <v>3468781472.8066669</v>
+        <v>3774758516.8450747</v>
       </c>
       <c r="L65" s="189">
         <f t="shared" si="4"/>
-        <v>0.39160024465322474</v>
+        <v>0.42614283150772658</v>
       </c>
       <c r="M65" s="181">
         <f>SUM(M51:M64)</f>
-        <v>5389184067.7368279</v>
+        <v>5083207023.6984215</v>
       </c>
       <c r="N65" s="181">
         <f t="shared" ca="1" si="6"/>
-        <v>336824004.23355174</v>
+        <v>338880468.24656141</v>
       </c>
       <c r="O65" s="181">
         <f>SUM(O51:O64)</f>
-        <v>5389184067.7368279</v>
+        <v>5083207023.6984215</v>
       </c>
       <c r="P65" s="181">
         <f t="shared" ca="1" si="8"/>
-        <v>336824004.23355174</v>
+        <v>338880468.24656141</v>
       </c>
       <c r="Q65" s="186">
         <f>SUM(Q51:Q64)</f>
-        <v>5389184067.7368279</v>
+        <v>5083207023.6984215</v>
       </c>
       <c r="R65" s="186">
         <f t="shared" ca="1" si="10"/>
-        <v>336824004.23355174</v>
+        <v>338880468.24656141</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8804,21 +8804,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="269" t="s">
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -8880,35 +8880,35 @@
       </c>
       <c r="E69" s="114">
         <f>IFERROR($C$31,0)</f>
-        <v>103000858.655599</v>
+        <v>106473741.715563</v>
       </c>
       <c r="F69" s="187">
         <f t="shared" ref="F69:F74" si="13">IFERROR(E69/D69,0)</f>
-        <v>0.40194280099974539</v>
+        <v>0.41549511855210608</v>
       </c>
       <c r="G69" s="184">
         <f>D69*$H$40-E69</f>
-        <v>153256644.64936563</v>
+        <v>149783761.58940163</v>
       </c>
       <c r="H69" s="184">
         <f t="shared" ref="H69:H74" ca="1" si="14">IFERROR(G69/$C$3,0)</f>
-        <v>9578540.2905853521</v>
+        <v>9985584.1059601083</v>
       </c>
       <c r="I69" s="204">
         <f>D69*$J$40-E69</f>
-        <v>153256644.64936563</v>
+        <v>149783761.58940163</v>
       </c>
       <c r="J69" s="204">
         <f t="shared" ref="J69:J74" ca="1" si="15">IFERROR(I69/$C$3,0)</f>
-        <v>9578540.2905853521</v>
+        <v>9985584.1059601083</v>
       </c>
       <c r="K69" s="185">
         <f>D69*$L$40-E69</f>
-        <v>153256644.64936563</v>
+        <v>149783761.58940163</v>
       </c>
       <c r="L69" s="185">
         <f t="shared" ref="L69:L74" ca="1" si="16">IFERROR(K69/$C$3,0)</f>
-        <v>9578540.2905853521</v>
+        <v>9985584.1059601083</v>
       </c>
     </row>
     <row r="70" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8924,35 +8924,35 @@
       </c>
       <c r="E70" s="114">
         <f>IFERROR($C$32,0)</f>
-        <v>73731814.289717004</v>
+        <v>84600229.289704993</v>
       </c>
       <c r="F70" s="187">
         <f t="shared" si="13"/>
-        <v>0.18453325476086058</v>
+        <v>0.21173432140163156</v>
       </c>
       <c r="G70" s="184">
         <f>D70*$H$40-E70</f>
-        <v>325826598.01524758</v>
+        <v>314958183.01525962</v>
       </c>
       <c r="H70" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>20364162.375952974</v>
+        <v>20997212.201017309</v>
       </c>
       <c r="I70" s="204">
         <f>D70*$J$40-E70</f>
-        <v>325826598.01524758</v>
+        <v>314958183.01525962</v>
       </c>
       <c r="J70" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>20364162.375952974</v>
+        <v>20997212.201017309</v>
       </c>
       <c r="K70" s="185">
         <f>D70*$L$40-E70</f>
-        <v>325826598.01524758</v>
+        <v>314958183.01525962</v>
       </c>
       <c r="L70" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>20364162.375952974</v>
+        <v>20997212.201017309</v>
       </c>
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.25">
@@ -8968,35 +8968,35 @@
       </c>
       <c r="E71" s="114">
         <f>M21</f>
-        <v>264937331.65099001</v>
+        <v>331139383.81018001</v>
       </c>
       <c r="F71" s="187">
         <f t="shared" si="13"/>
-        <v>0.24426976090584135</v>
+        <v>0.30530743857711851</v>
       </c>
       <c r="G71" s="184">
         <f>D71*$H$40-E71</f>
-        <v>819672284.65397453</v>
+        <v>753470232.49478459</v>
       </c>
       <c r="H71" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>51229517.790873408</v>
+        <v>50231348.83298564</v>
       </c>
       <c r="I71" s="204">
         <f>D71*$J$40-E71</f>
-        <v>819672284.65397453</v>
+        <v>753470232.49478459</v>
       </c>
       <c r="J71" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>51229517.790873408</v>
+        <v>50231348.83298564</v>
       </c>
       <c r="K71" s="185">
         <f>D71*$L$40-E71</f>
-        <v>819672284.65397453</v>
+        <v>753470232.49478459</v>
       </c>
       <c r="L71" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>51229517.790873408</v>
+        <v>50231348.83298564</v>
       </c>
     </row>
     <row r="72" spans="2:21" hidden="1" x14ac:dyDescent="0.25">
@@ -9098,35 +9098,35 @@
       </c>
       <c r="E74" s="115">
         <f>SUM(E69:E73)</f>
-        <v>441670004.59630603</v>
+        <v>522213354.81544799</v>
       </c>
       <c r="F74" s="177">
         <f t="shared" si="13"/>
-        <v>0.25377127403455235</v>
+        <v>0.30004923809689554</v>
       </c>
       <c r="G74" s="181">
         <f>SUM(G69:G73)</f>
-        <v>1298755527.3185878</v>
+        <v>1218212177.0994458</v>
       </c>
       <c r="H74" s="181">
         <f t="shared" ca="1" si="14"/>
-        <v>81172220.457411736</v>
+        <v>81214145.139963061</v>
       </c>
       <c r="I74" s="186">
         <f>SUM(I69:I73)</f>
-        <v>1298755527.3185878</v>
+        <v>1218212177.0994458</v>
       </c>
       <c r="J74" s="186">
         <f t="shared" ca="1" si="15"/>
-        <v>81172220.457411736</v>
+        <v>81214145.139963061</v>
       </c>
       <c r="K74" s="186">
         <f>SUM(K69:K73)</f>
-        <v>1298755527.3185878</v>
+        <v>1218212177.0994458</v>
       </c>
       <c r="L74" s="186">
         <f t="shared" ca="1" si="16"/>
-        <v>81172220.457411736</v>
+        <v>81214145.139963061</v>
       </c>
     </row>
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9139,10 +9139,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="D80" s="131">
         <f>SUMIF($B$10:$B$26,$T80,$F$10:$F$26)+SUMIF($B$10:$B$26,$U80,$F$10:$F$26)</f>
-        <v>195859849.49992001</v>
+        <v>205798588.24992001</v>
       </c>
       <c r="T80" t="str">
         <f t="shared" ref="T80:U93" si="17">T51</f>
@@ -9211,7 +9211,7 @@
       </c>
       <c r="D82" s="132">
         <f t="shared" si="18"/>
-        <v>2198198.14</v>
+        <v>4684684.5599999996</v>
       </c>
       <c r="T82" t="str">
         <f t="shared" si="17"/>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="D83" s="131">
         <f t="shared" si="18"/>
-        <v>174709642.90987501</v>
+        <v>178712210.57987499</v>
       </c>
       <c r="T83" t="str">
         <f t="shared" si="17"/>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="D85" s="131">
         <f t="shared" si="18"/>
-        <v>27923423.170000002</v>
+        <v>28644143.870000001</v>
       </c>
       <c r="T85" t="str">
         <f t="shared" si="17"/>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="D86" s="132">
         <f t="shared" si="18"/>
-        <v>446419095.06998199</v>
+        <v>526669634.76998198</v>
       </c>
       <c r="T86" t="str">
         <f t="shared" si="17"/>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="D87" s="131">
         <f t="shared" si="18"/>
-        <v>146008228.63973001</v>
+        <v>160386697.35973001</v>
       </c>
       <c r="T87" t="str">
         <f t="shared" si="17"/>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="D90" s="131">
         <f t="shared" si="18"/>
-        <v>270778557.89970303</v>
+        <v>299201801.53968298</v>
       </c>
       <c r="T90" t="str">
         <f t="shared" si="17"/>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="D91" s="132">
         <f t="shared" si="18"/>
-        <v>70576712.069966003</v>
+        <v>76315833.649960995</v>
       </c>
       <c r="T91" t="str">
         <f t="shared" si="17"/>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="D93" s="132">
         <f t="shared" si="18"/>
-        <v>77670271.920000002</v>
+        <v>82881082.859999999</v>
       </c>
       <c r="T93" t="str">
         <f t="shared" si="17"/>
@@ -9449,12 +9449,18 @@
       <c r="C94" s="58"/>
       <c r="D94" s="120">
         <f>SUM(D80:D93)</f>
-        <v>1504056502.9125762</v>
+        <v>1655207201.0325511</v>
       </c>
     </row>
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -9469,12 +9475,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -10102,11 +10102,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>163</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -10426,33 +10426,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -10461,49 +10461,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -10528,13 +10528,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -11650,21 +11650,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="269" t="s">
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -11985,10 +11985,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -12301,6 +12301,12 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -12315,12 +12321,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -12948,11 +12948,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>175</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -13272,33 +13272,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -13307,49 +13307,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -13374,13 +13374,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -14496,21 +14496,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="269" t="s">
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -14831,10 +14831,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -15147,6 +15147,12 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -15161,12 +15167,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -15794,11 +15794,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>177</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -16118,33 +16118,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -16153,49 +16153,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -16220,13 +16220,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -17328,21 +17328,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="269" t="s">
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -17663,10 +17663,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -17979,6 +17979,12 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -17993,12 +17999,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -25778,11 +25778,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="259" t="s">
+      <c r="B41" s="269" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="260"/>
-      <c r="D41" s="261"/>
+      <c r="C41" s="270"/>
+      <c r="D41" s="271"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -26053,59 +26053,59 @@
       </c>
     </row>
     <row r="48" spans="2:19" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="270"/>
-      <c r="M48" s="270"/>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="271"/>
+      <c r="L48" s="261"/>
+      <c r="M48" s="261"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
       <c r="Q48"/>
       <c r="R48"/>
     </row>
     <row r="49" spans="2:18" s="139" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="267" t="s">
+      <c r="B49" s="277" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="267" t="s">
+      <c r="C49" s="277" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="264" t="s">
+      <c r="D49" s="274" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="265"/>
-      <c r="F49" s="266"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
       <c r="G49" s="140" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="140"/>
       <c r="I49" s="140"/>
-      <c r="J49" s="264" t="s">
+      <c r="J49" s="274" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="272" t="str">
+      <c r="K49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="272" t="str">
+      <c r="L49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
@@ -26120,7 +26120,7 @@
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="276" t="str">
+      <c r="P49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -26129,8 +26129,8 @@
       <c r="R49"/>
     </row>
     <row r="50" spans="2:18" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="267"/>
-      <c r="C50" s="267"/>
+      <c r="B50" s="277"/>
+      <c r="C50" s="277"/>
       <c r="D50" s="141" t="s">
         <v>149</v>
       </c>
@@ -26149,13 +26149,13 @@
       <c r="I50" s="142" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="264"/>
-      <c r="K50" s="273"/>
-      <c r="L50" s="273"/>
-      <c r="M50" s="275"/>
+      <c r="J50" s="274"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="266"/>
       <c r="N50" s="188"/>
       <c r="O50" s="183"/>
-      <c r="P50" s="277"/>
+      <c r="P50" s="268"/>
       <c r="Q50"/>
       <c r="R50"/>
     </row>
@@ -27496,10 +27496,10 @@
       <c r="I77"/>
     </row>
     <row r="78" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -27698,6 +27698,13 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="J49:J50"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
     <mergeCell ref="K48:P48"/>
@@ -27707,13 +27714,6 @@
     <mergeCell ref="P49:P50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="J49:J50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="26" priority="8">
@@ -28753,25 +28753,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="270"/>
-      <c r="M48" s="270"/>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="271"/>
+      <c r="L48" s="261"/>
+      <c r="M48" s="261"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -28793,32 +28793,32 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="272" t="str">
+      <c r="K49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="272" t="str">
+      <c r="L49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="274" t="str">
+      <c r="N49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="276" t="str">
+      <c r="O49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="276" t="str">
+      <c r="P49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -28846,12 +28846,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="273"/>
-      <c r="L50" s="273"/>
-      <c r="M50" s="275"/>
-      <c r="N50" s="275"/>
-      <c r="O50" s="277"/>
-      <c r="P50" s="277"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="266"/>
+      <c r="N50" s="266"/>
+      <c r="O50" s="268"/>
+      <c r="P50" s="268"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="167" t="s">
@@ -30088,10 +30088,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -30285,6 +30285,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -30292,17 +30303,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -31060,11 +31060,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="259" t="s">
+      <c r="B41" s="269" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="260"/>
-      <c r="D41" s="261"/>
+      <c r="C41" s="270"/>
+      <c r="D41" s="271"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -31339,25 +31339,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="270"/>
-      <c r="M48" s="270"/>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="271"/>
+      <c r="L48" s="261"/>
+      <c r="M48" s="261"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -31379,32 +31379,32 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="272" t="str">
+      <c r="K49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="272" t="str">
+      <c r="L49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="274" t="str">
+      <c r="N49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="276" t="str">
+      <c r="O49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="276" t="str">
+      <c r="P49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -31432,12 +31432,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="273"/>
-      <c r="L50" s="273"/>
-      <c r="M50" s="275"/>
-      <c r="N50" s="275"/>
-      <c r="O50" s="277"/>
-      <c r="P50" s="277"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="266"/>
+      <c r="N50" s="266"/>
+      <c r="O50" s="268"/>
+      <c r="P50" s="268"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -32674,10 +32674,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -32858,6 +32858,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -32865,17 +32876,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -33654,11 +33654,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" s="191" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="259" t="s">
+      <c r="B41" s="269" t="s">
         <v>189</v>
       </c>
-      <c r="C41" s="260"/>
-      <c r="D41" s="261"/>
+      <c r="C41" s="270"/>
+      <c r="D41" s="271"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -33933,25 +33933,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="270"/>
-      <c r="M48" s="270"/>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="271"/>
+      <c r="L48" s="261"/>
+      <c r="M48" s="261"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
     </row>
     <row r="49" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -33973,22 +33973,22 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="272" t="str">
+      <c r="K49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="272" t="str">
+      <c r="L49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="274" t="str">
+      <c r="N49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
@@ -34026,10 +34026,10 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="273"/>
-      <c r="L50" s="273"/>
-      <c r="M50" s="275"/>
-      <c r="N50" s="275"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="266"/>
+      <c r="N50" s="266"/>
       <c r="O50" s="282"/>
       <c r="P50" s="282"/>
     </row>
@@ -35268,10 +35268,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -35465,6 +35465,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
@@ -35478,11 +35483,6 @@
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="228">
   <si>
     <t>📊  PANDUAN PENGGUNAAN — DATA PENCAPAIAN 2026</t>
   </si>
@@ -909,7 +909,7 @@
     <t>RONALD</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL —  14 SEPTEMBER 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL —  15 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>
@@ -2556,6 +2556,33 @@
     <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2586,33 +2613,6 @@
     <xf numFmtId="0" fontId="48" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2626,6 +2626,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2647,15 +2656,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4299,11 +4299,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="259" t="s">
         <v>219</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="260"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -4623,33 +4623,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="263"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="270"/>
+      <c r="Q48" s="270"/>
+      <c r="R48" s="271"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -4658,49 +4658,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="268"/>
+      <c r="C50" s="268"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -4725,13 +4725,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="273"/>
+      <c r="N50" s="273"/>
+      <c r="O50" s="275"/>
+      <c r="P50" s="275"/>
+      <c r="Q50" s="277"/>
+      <c r="R50" s="277"/>
       <c r="T50" s="172" t="s">
         <v>216</v>
       </c>
@@ -5847,21 +5847,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="283" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
-      <c r="F67" s="292"/>
-      <c r="G67" s="260" t="s">
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
+      <c r="F67" s="285"/>
+      <c r="G67" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="270"/>
+      <c r="I67" s="270"/>
+      <c r="J67" s="270"/>
+      <c r="K67" s="270"/>
+      <c r="L67" s="271"/>
     </row>
     <row r="68" spans="2:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -6180,10 +6180,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -6495,12 +6495,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -6515,6 +6509,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="C3" s="75">
         <f ca="1">IF($J$5&lt;&gt;"",$J$5,MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),9,1)),EOMONTH(DATE(YEAR(TODAY()),9,1),0),11)-MAX(0,$J$3-$J$4)))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" s="76" t="s">
         <v>104</v>
@@ -6718,19 +6718,19 @@
         <v>112</v>
       </c>
       <c r="C10" s="234">
-        <v>94300637.951456994</v>
+        <v>97216448.761456996</v>
       </c>
       <c r="D10" s="234">
-        <v>20944050.82</v>
+        <v>23128050.82</v>
       </c>
       <c r="E10" s="234">
-        <v>99411702.953909993</v>
+        <v>115369270.523895</v>
       </c>
       <c r="F10" s="234">
-        <v>76315833.649960995</v>
+        <v>87616734.749956995</v>
       </c>
       <c r="G10" s="234">
-        <v>290972225.375328</v>
+        <v>323330504.85530901</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="111"/>
@@ -6743,19 +6743,19 @@
         <v>182</v>
       </c>
       <c r="C11" s="234">
-        <v>3750000</v>
+        <v>4173423.4199979999</v>
       </c>
       <c r="D11" s="234">
         <v>8173668</v>
       </c>
       <c r="E11" s="234">
-        <v>148761261.99939999</v>
-      </c>
-      <c r="F11" s="234">
-        <v>0</v>
+        <v>172635135.9993</v>
+      </c>
+      <c r="F11" s="234" t="s">
+        <v>165</v>
       </c>
       <c r="G11" s="234">
-        <v>160684929.99939999</v>
+        <v>184982227.41929799</v>
       </c>
       <c r="H11" s="111"/>
       <c r="I11" s="111"/>
@@ -6768,19 +6768,19 @@
         <v>70</v>
       </c>
       <c r="C12" s="234">
-        <v>90457134.376817003</v>
+        <v>91706728.976816997</v>
       </c>
       <c r="D12" s="234">
-        <v>47804580.981486998</v>
+        <v>50114229.631486997</v>
       </c>
       <c r="E12" s="234">
-        <v>75155055.669801995</v>
+        <v>91828840.309686005</v>
       </c>
       <c r="F12" s="234">
-        <v>34989283.75</v>
+        <v>36339283.75</v>
       </c>
       <c r="G12" s="234">
-        <v>248406054.778106</v>
+        <v>269989082.66799003</v>
       </c>
       <c r="H12" s="111"/>
       <c r="I12" s="111"/>
@@ -6793,19 +6793,19 @@
         <v>114</v>
       </c>
       <c r="C13" s="234">
-        <v>17858099.384810001</v>
+        <v>20451403.544785999</v>
       </c>
       <c r="D13" s="234">
         <v>11385728.009987</v>
       </c>
       <c r="E13" s="234">
-        <v>105548694.69976901</v>
+        <v>110224370.349769</v>
       </c>
       <c r="F13" s="234">
-        <v>23539329.489999998</v>
+        <v>48944735.640000001</v>
       </c>
       <c r="G13" s="234">
-        <v>158331851.584566</v>
+        <v>191006237.54454201</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="111"/>
@@ -6818,19 +6818,19 @@
         <v>115</v>
       </c>
       <c r="C14" s="234">
-        <v>217006066.54874799</v>
+        <v>243299179.44867501</v>
       </c>
       <c r="D14" s="234">
-        <v>21781667.005913999</v>
+        <v>22641180.565914001</v>
       </c>
       <c r="E14" s="234">
-        <v>80743855.929943994</v>
+        <v>89583383.009923995</v>
       </c>
       <c r="F14" s="234">
-        <v>178712210.57987499</v>
+        <v>217414914.14984</v>
       </c>
       <c r="G14" s="234">
-        <v>498243800.06448102</v>
+        <v>572938657.174353</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="111"/>
@@ -6843,19 +6843,19 @@
         <v>118</v>
       </c>
       <c r="C15" s="234">
-        <v>512902821.09112298</v>
+        <v>513300118.391123</v>
       </c>
       <c r="D15" s="234">
-        <v>3499064.7569960002</v>
+        <v>7952668.2969239997</v>
       </c>
       <c r="E15" s="234">
         <v>30690917.85997</v>
       </c>
       <c r="F15" s="234">
-        <v>11200000.32</v>
+        <v>12048648.960000001</v>
       </c>
       <c r="G15" s="234">
-        <v>558292804.02808905</v>
+        <v>563992353.50801694</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="111"/>
@@ -6868,19 +6868,19 @@
         <v>120</v>
       </c>
       <c r="C16" s="234">
-        <v>225357040.79817799</v>
+        <v>239332510.527154</v>
       </c>
       <c r="D16" s="234">
-        <v>22434819.63998</v>
+        <v>24932116.839954998</v>
       </c>
       <c r="E16" s="234">
-        <v>156468829.24970099</v>
+        <v>173790360.81968999</v>
       </c>
       <c r="F16" s="234">
-        <v>526669634.76998198</v>
+        <v>512576661.13998199</v>
       </c>
       <c r="G16" s="234">
-        <v>930930324.45784104</v>
+        <v>950631649.32678103</v>
       </c>
       <c r="H16" s="111"/>
       <c r="I16" s="111"/>
@@ -6893,19 +6893,19 @@
         <v>122</v>
       </c>
       <c r="C17" s="234">
-        <v>60141278.285573997</v>
+        <v>65500918.065573998</v>
       </c>
       <c r="D17" s="234">
-        <v>9978337.7908999994</v>
+        <v>10163923.380899999</v>
       </c>
       <c r="E17" s="234">
-        <v>52967051.869258001</v>
+        <v>53129214.029257998</v>
       </c>
       <c r="F17" s="234">
         <v>23000000.5</v>
       </c>
       <c r="G17" s="234">
-        <v>146086668.445732</v>
+        <v>151794055.975732</v>
       </c>
       <c r="H17" s="111"/>
       <c r="I17" s="111"/>
@@ -6919,19 +6919,19 @@
         <v>123</v>
       </c>
       <c r="C18" s="234">
-        <v>8495810</v>
+        <v>8816270</v>
       </c>
       <c r="D18" s="234">
-        <v>88602544.295750007</v>
+        <v>89597138.855749995</v>
       </c>
       <c r="E18" s="234">
-        <v>35293741.5</v>
+        <v>38334282</v>
       </c>
       <c r="F18" s="234">
-        <v>59881082.359999999</v>
+        <v>61232433.740000002</v>
       </c>
       <c r="G18" s="234">
-        <v>192273178.15575001</v>
+        <v>197980124.59575</v>
       </c>
       <c r="H18" s="111"/>
       <c r="I18" s="111"/>
@@ -6945,19 +6945,19 @@
         <v>169</v>
       </c>
       <c r="C19" s="234">
-        <v>37937447.460000001</v>
-      </c>
-      <c r="D19" s="234">
-        <v>0</v>
-      </c>
-      <c r="E19" s="234">
-        <v>0</v>
+        <v>60472267.460000001</v>
+      </c>
+      <c r="D19" s="234" t="s">
+        <v>165</v>
+      </c>
+      <c r="E19" s="234" t="s">
+        <v>165</v>
       </c>
       <c r="F19" s="234">
         <v>4684684.5599999996</v>
       </c>
       <c r="G19" s="234">
-        <v>42622132.020000003</v>
+        <v>65156952.020000003</v>
       </c>
       <c r="H19" s="111"/>
       <c r="I19" s="111"/>
@@ -6973,11 +6973,11 @@
       <c r="C20" s="234">
         <v>101915659.56</v>
       </c>
-      <c r="D20" s="234">
-        <v>0</v>
-      </c>
-      <c r="E20" s="234">
-        <v>0</v>
+      <c r="D20" s="234" t="s">
+        <v>165</v>
+      </c>
+      <c r="E20" s="234" t="s">
+        <v>165</v>
       </c>
       <c r="F20" s="234">
         <v>5723693.54</v>
@@ -7001,26 +7001,26 @@
         <v>124</v>
       </c>
       <c r="C21" s="234">
-        <v>138779411.85907</v>
+        <v>149619192.339046</v>
       </c>
       <c r="D21" s="234">
-        <v>27897366.944974001</v>
+        <v>31844096.684974</v>
       </c>
       <c r="E21" s="234">
-        <v>78549937.029896006</v>
+        <v>88558585.899890006</v>
       </c>
       <c r="F21" s="234">
-        <v>205798588.24992001</v>
+        <v>223826336.25990999</v>
       </c>
       <c r="G21" s="234">
-        <v>451025304.08385998</v>
+        <v>493848211.18382001</v>
       </c>
       <c r="H21" s="111"/>
       <c r="I21" s="111"/>
       <c r="J21" s="111"/>
       <c r="M21" s="14">
         <f>SUM(C33,C34)+M20</f>
-        <v>331139383.81018001</v>
+        <v>367847681.28290999</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>224</v>
@@ -7031,19 +7031,19 @@
         <v>125</v>
       </c>
       <c r="C22" s="234">
-        <v>122963699.481111</v>
+        <v>134205157.25907899</v>
       </c>
       <c r="D22" s="234">
-        <v>36359093.799973004</v>
+        <v>37451093.799973004</v>
       </c>
       <c r="E22" s="234">
-        <v>99646577.797502995</v>
+        <v>106501082.50749999</v>
       </c>
       <c r="F22" s="234">
-        <v>160386697.35973001</v>
+        <v>185945256.43967</v>
       </c>
       <c r="G22" s="234">
-        <v>419356068.438317</v>
+        <v>464102590.00622201</v>
       </c>
       <c r="H22" s="111"/>
       <c r="I22" s="111"/>
@@ -7054,19 +7054,19 @@
         <v>126</v>
       </c>
       <c r="C23" s="234">
-        <v>246152018.821336</v>
+        <v>266345676.026207</v>
       </c>
       <c r="D23" s="234">
-        <v>31651916.244963001</v>
+        <v>33822227.054963</v>
       </c>
       <c r="E23" s="234">
-        <v>107975721.769917</v>
+        <v>117236487.58991501</v>
       </c>
       <c r="F23" s="234">
-        <v>299201801.53968298</v>
+        <v>329431621.62963599</v>
       </c>
       <c r="G23" s="234">
-        <v>684981458.37589896</v>
+        <v>746836012.30072105</v>
       </c>
       <c r="H23" s="111"/>
       <c r="I23" s="111"/>
@@ -7077,19 +7077,19 @@
         <v>225</v>
       </c>
       <c r="C24" s="234">
-        <v>112131143.770466</v>
+        <v>113441089.730461</v>
       </c>
       <c r="D24" s="234">
-        <v>26436621.659975</v>
+        <v>27162265.819968998</v>
       </c>
       <c r="E24" s="234">
-        <v>91731288.128275007</v>
+        <v>93079035.878275007</v>
       </c>
       <c r="F24" s="234">
         <v>28644143.870000001</v>
       </c>
       <c r="G24" s="234">
-        <v>258943197.428716</v>
+        <v>262326535.29870501</v>
       </c>
       <c r="H24" s="111"/>
       <c r="I24" s="111"/>
@@ -7100,19 +7100,19 @@
         <v>220</v>
       </c>
       <c r="C25" s="234">
-        <v>138186464.73536199</v>
+        <v>148994604.18081501</v>
       </c>
       <c r="D25" s="234">
-        <v>49441138.601727001</v>
+        <v>58721904.781634003</v>
       </c>
       <c r="E25" s="234">
-        <v>54299554.287846997</v>
+        <v>59769779.527842999</v>
       </c>
       <c r="F25" s="234">
         <v>20000000.43</v>
       </c>
       <c r="G25" s="234">
-        <v>261927158.05493599</v>
+        <v>287486288.92029202</v>
       </c>
       <c r="H25" s="111"/>
       <c r="I25" s="111"/>
@@ -7123,19 +7123,19 @@
         <v>127</v>
       </c>
       <c r="C26" s="234">
-        <v>252837877.07610399</v>
+        <v>256023408.716097</v>
       </c>
       <c r="D26" s="234">
-        <v>150942202.70816001</v>
+        <v>162504689.06803399</v>
       </c>
       <c r="E26" s="234">
-        <v>166101717.34703001</v>
+        <v>174759375.72681299</v>
       </c>
       <c r="F26" s="234">
-        <v>7660216.3833999997</v>
+        <v>9343459.6473999992</v>
       </c>
       <c r="G26" s="234">
-        <v>577542013.51469398</v>
+        <v>602630933.15834403</v>
       </c>
       <c r="H26" s="111"/>
       <c r="I26" s="111"/>
@@ -7178,7 +7178,7 @@
         <v>131</v>
       </c>
       <c r="C31" s="234">
-        <v>106473741.715563</v>
+        <v>110102138.155559</v>
       </c>
       <c r="G31" s="111"/>
       <c r="H31" s="111"/>
@@ -7189,7 +7189,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="234">
-        <v>84600229.289704993</v>
+        <v>85308067.049704999</v>
       </c>
       <c r="G32" s="111"/>
       <c r="H32" s="111"/>
@@ -7200,7 +7200,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="234">
-        <v>67261415.257090002</v>
+        <v>82096451.309998006</v>
       </c>
       <c r="G33" s="111"/>
       <c r="H33" s="111"/>
@@ -7211,7 +7211,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="234">
-        <v>263877968.55309001</v>
+        <v>285751229.97291201</v>
       </c>
       <c r="G34" s="111"/>
       <c r="H34" s="111"/>
@@ -7256,17 +7256,17 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="259" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="260"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
       <c r="F40" s="174">
         <f ca="1">IF(MONTH(TODAY())=9,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;9,1,0))</f>
-        <v>0.46666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="G40" s="192" t="s">
         <v>187</v>
@@ -7353,35 +7353,35 @@
       </c>
       <c r="E42" s="46">
         <f>H65</f>
-        <v>1868269790.1090329</v>
+        <v>2001513938.016166</v>
       </c>
       <c r="F42" s="176">
         <f>IFERROR(E42/D42,0)</f>
-        <v>0.41408652275497265</v>
+        <v>0.44361898438145647</v>
       </c>
       <c r="G42" s="184">
         <f>D42*$H$40-E42</f>
-        <v>2643516243.5903635</v>
+        <v>2510272095.6832304</v>
       </c>
       <c r="H42" s="184">
         <f ca="1">IFERROR(G42/$C$3,0)</f>
-        <v>176234416.23935756</v>
+        <v>179305149.6916593</v>
       </c>
       <c r="I42" s="204">
         <f>D42*$J$40-E42</f>
-        <v>2643516243.5903635</v>
+        <v>2510272095.6832304</v>
       </c>
       <c r="J42" s="204">
         <f ca="1">IFERROR(I42/$C$3,0)</f>
-        <v>176234416.23935756</v>
+        <v>179305149.6916593</v>
       </c>
       <c r="K42" s="185">
         <f>D42*$L$40-E42</f>
-        <v>2643516243.5903635</v>
+        <v>2510272095.6832304</v>
       </c>
       <c r="L42" s="185">
         <f ca="1">IFERROR(K42/$C$3,0)</f>
-        <v>176234416.23935756</v>
+        <v>179305149.6916593</v>
       </c>
       <c r="S42" s="173">
         <v>0.8</v>
@@ -7400,35 +7400,35 @@
       </c>
       <c r="E43" s="46">
         <f>I65</f>
-        <v>553833736.50379002</v>
+        <v>591642313.31353998</v>
       </c>
       <c r="F43" s="176">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.39521010856198002</v>
+        <v>0.4221899235510097</v>
       </c>
       <c r="G43" s="184">
         <f>D43*$H$40-E43</f>
-        <v>847531574.01162493</v>
+        <v>809722997.20187497</v>
       </c>
       <c r="H43" s="184">
         <f ca="1">IFERROR(G43/$C$3,0)</f>
-        <v>56502104.934108332</v>
+        <v>57837356.94299107</v>
       </c>
       <c r="I43" s="204">
         <f>D43*$J$40-E43</f>
-        <v>847531574.01162493</v>
+        <v>809722997.20187497</v>
       </c>
       <c r="J43" s="204">
         <f ca="1">IFERROR(I43/$C$3,0)</f>
-        <v>56502104.934108332</v>
+        <v>57837356.94299107</v>
       </c>
       <c r="K43" s="185">
         <f>D43*$L$40-E43</f>
-        <v>847531574.01162493</v>
+        <v>809722997.20187497</v>
       </c>
       <c r="L43" s="185">
         <f ca="1">IFERROR(K43/$C$3,0)</f>
-        <v>56502104.934108332</v>
+        <v>57837356.94299107</v>
       </c>
       <c r="S43" s="173">
         <v>0.85</v>
@@ -7447,35 +7447,35 @@
       </c>
       <c r="E44" s="46">
         <f>J65</f>
-        <v>1352654990.2322519</v>
+        <v>1484799204.1717582</v>
       </c>
       <c r="F44" s="176">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.45933457938317929</v>
+        <v>0.50420811133784427</v>
       </c>
       <c r="G44" s="184">
         <f>IF(D44=0,0,D44*$H$40-E44)</f>
-        <v>1592159206.0964334</v>
+        <v>1460014992.1569271</v>
       </c>
       <c r="H44" s="184">
         <f ca="1">IFERROR(G44/$C$3,0)</f>
-        <v>106143947.07309556</v>
+        <v>104286785.15406622</v>
       </c>
       <c r="I44" s="204">
         <f>IF(D44=0,0,D44*$J$40-E44)</f>
-        <v>1592159206.0964334</v>
+        <v>1460014992.1569271</v>
       </c>
       <c r="J44" s="204">
         <f ca="1">IFERROR(I44/$C$3,0)</f>
-        <v>106143947.07309556</v>
+        <v>104286785.15406622</v>
       </c>
       <c r="K44" s="185">
         <f>IF(D44=0,0,D44*$L$40-E44)</f>
-        <v>1592159206.0964334</v>
+        <v>1460014992.1569271</v>
       </c>
       <c r="L44" s="185">
         <f ca="1">IFERROR(K44/$C$3,0)</f>
-        <v>106143947.07309556</v>
+        <v>104286785.15406622</v>
       </c>
       <c r="S44" s="173">
         <v>0.9</v>
@@ -7494,35 +7494,35 @@
       </c>
       <c r="E45" s="46">
         <f>E74</f>
-        <v>522213354.81544799</v>
+        <v>563257886.48817396</v>
       </c>
       <c r="F45" s="176">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.30004923809689554</v>
+        <v>0.32363228196753269</v>
       </c>
       <c r="G45" s="184">
         <f>D45*$H$40-E45</f>
-        <v>1218212177.0994456</v>
+        <v>1177167645.4267197</v>
       </c>
       <c r="H45" s="184">
         <f ca="1">IFERROR(G45/$C$3,0)</f>
-        <v>81214145.139963046</v>
+        <v>84083403.244765684</v>
       </c>
       <c r="I45" s="204">
         <f>D45*$J$40-E45</f>
-        <v>1218212177.0994456</v>
+        <v>1177167645.4267197</v>
       </c>
       <c r="J45" s="204">
         <f ca="1">IFERROR(I45/$C$3,0)</f>
-        <v>81214145.139963046</v>
+        <v>84083403.244765684</v>
       </c>
       <c r="K45" s="185">
         <f>D45*$L$40-E45</f>
-        <v>1218212177.0994456</v>
+        <v>1177167645.4267197</v>
       </c>
       <c r="L45" s="185">
         <f ca="1">IFERROR(K45/$C$3,0)</f>
-        <v>81214145.139963046</v>
+        <v>84083403.244765684</v>
       </c>
       <c r="S45" s="173">
         <v>0.95</v>
@@ -7539,35 +7539,35 @@
       </c>
       <c r="E46" s="47">
         <f>SUM(E42:E45)</f>
-        <v>4296971871.6605225</v>
+        <v>4641213341.9896383</v>
       </c>
       <c r="F46" s="177">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.4054362442641779</v>
+        <v>0.43791678475146772</v>
       </c>
       <c r="G46" s="181">
         <f>SUM(G42:G45)</f>
-        <v>6301419200.7978668</v>
+        <v>5957177730.4687519</v>
       </c>
       <c r="H46" s="181">
         <f ca="1">IFERROR(G46/$C$3,0)</f>
-        <v>420094613.38652444</v>
+        <v>425512695.03348225</v>
       </c>
       <c r="I46" s="186">
         <f>SUM(I42:I45)</f>
-        <v>6301419200.7978668</v>
+        <v>5957177730.4687519</v>
       </c>
       <c r="J46" s="186">
         <f ca="1">IFERROR(I46/$C$3,0)</f>
-        <v>420094613.38652444</v>
+        <v>425512695.03348225</v>
       </c>
       <c r="K46" s="186">
         <f>SUM(K42:K45)</f>
-        <v>6301419200.7978668</v>
+        <v>5957177730.4687519</v>
       </c>
       <c r="L46" s="186">
         <f ca="1">IFERROR(K46/$C$3,0)</f>
-        <v>420094613.38652444</v>
+        <v>425512695.03348225</v>
       </c>
       <c r="S46" s="173">
         <v>1</v>
@@ -7580,33 +7580,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="263"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="270"/>
+      <c r="Q48" s="270"/>
+      <c r="R48" s="271"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -7615,49 +7615,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="268"/>
+      <c r="C50" s="268"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -7682,13 +7682,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="273"/>
+      <c r="N50" s="273"/>
+      <c r="O50" s="275"/>
+      <c r="P50" s="275"/>
+      <c r="Q50" s="277"/>
+      <c r="R50" s="277"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -7721,47 +7721,47 @@
       </c>
       <c r="H51" s="114">
         <f>SUMIF($B$10:$B$26,$T51,C$10:C$26)+SUMIF($B$10:$B$26,$U51,C$10:C$26)</f>
-        <v>138779411.85907</v>
+        <v>149619192.339046</v>
       </c>
       <c r="I51" s="114">
         <f t="shared" ref="I51:I64" si="1">SUMIF($B$10:$B$26,$T51,D$10:D$26)+SUMIF($B$10:$B$26,$U51,D$10:D$26)</f>
-        <v>27897366.944974001</v>
+        <v>31844096.684974</v>
       </c>
       <c r="J51" s="114">
         <f t="shared" ref="J51:J64" si="2">SUMIF($B$10:$B$26,$T51,E$10:E$26)+SUMIF($B$10:$B$26,$U51,E$10:E$26)</f>
-        <v>78549937.029896006</v>
+        <v>88558585.899890006</v>
       </c>
       <c r="K51" s="114">
         <f t="shared" ref="K51:K64" si="3">SUM(H51:J51)</f>
-        <v>245226715.83394003</v>
+        <v>270021874.92391002</v>
       </c>
       <c r="L51" s="187">
         <f t="shared" ref="L51:L65" si="4">IFERROR(K51/G51,0)</f>
-        <v>0.47675388968553384</v>
+        <v>0.52495903120657328</v>
       </c>
       <c r="M51" s="184">
         <f t="shared" ref="M51:M64" si="5">G51*$H$40-K51</f>
-        <v>269140804.05287457</v>
+        <v>244345644.96290457</v>
       </c>
       <c r="N51" s="184">
         <f t="shared" ref="N51:N65" ca="1" si="6">IFERROR(M51/$C$3,0)</f>
-        <v>17942720.270191636</v>
+        <v>17453260.354493182</v>
       </c>
       <c r="O51" s="180">
         <f t="shared" ref="O51:O64" si="7">G51*$J$40-K51</f>
-        <v>269140804.05287457</v>
+        <v>244345644.96290457</v>
       </c>
       <c r="P51" s="180">
         <f t="shared" ref="P51:P65" ca="1" si="8">IFERROR(O51/$C$3,0)</f>
-        <v>17942720.270191636</v>
+        <v>17453260.354493182</v>
       </c>
       <c r="Q51" s="185">
         <f t="shared" ref="Q51:Q64" si="9">G51*$L$40-K51</f>
-        <v>269140804.05287457</v>
+        <v>244345644.96290457</v>
       </c>
       <c r="R51" s="185">
         <f t="shared" ref="R51:R65" ca="1" si="10">IFERROR(Q51/$C$3,0)</f>
-        <v>17942720.270191636</v>
+        <v>17453260.354493182</v>
       </c>
       <c r="T51" t="s">
         <v>124</v>
@@ -7795,47 +7795,47 @@
       </c>
       <c r="H52" s="114">
         <f t="shared" ref="H52:H64" si="11">SUMIF($B$10:$B$26,$T52,C$10:C$26)+SUMIF($B$10:$B$26,$U52,C$10:C$26)</f>
-        <v>108315233.761627</v>
+        <v>112158132.52160299</v>
       </c>
       <c r="I52" s="114">
         <f t="shared" si="1"/>
-        <v>59190308.991474003</v>
+        <v>61499957.641473994</v>
       </c>
       <c r="J52" s="114">
         <f t="shared" si="2"/>
-        <v>180703750.369571</v>
+        <v>202053210.659455</v>
       </c>
       <c r="K52" s="114">
         <f t="shared" si="3"/>
-        <v>348209293.12267196</v>
+        <v>375711300.822532</v>
       </c>
       <c r="L52" s="187">
         <f t="shared" si="4"/>
-        <v>0.44328288592976639</v>
+        <v>0.47829392550521432</v>
       </c>
       <c r="M52" s="184">
         <f t="shared" si="5"/>
-        <v>437314588.29746962</v>
+        <v>409812580.59760958</v>
       </c>
       <c r="N52" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>29154305.886497974</v>
+        <v>29272327.185543541</v>
       </c>
       <c r="O52" s="180">
         <f t="shared" si="7"/>
-        <v>437314588.29746962</v>
+        <v>409812580.59760958</v>
       </c>
       <c r="P52" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>29154305.886497974</v>
+        <v>29272327.185543541</v>
       </c>
       <c r="Q52" s="185">
         <f t="shared" si="9"/>
-        <v>437314588.29746962</v>
+        <v>409812580.59760958</v>
       </c>
       <c r="R52" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>29154305.886497974</v>
+        <v>29272327.185543541</v>
       </c>
       <c r="T52" t="s">
         <v>70</v>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H53" s="114">
         <f t="shared" si="11"/>
-        <v>37937447.460000001</v>
+        <v>60472267.460000001</v>
       </c>
       <c r="I53" s="114">
         <f t="shared" si="1"/>
@@ -7881,35 +7881,35 @@
       </c>
       <c r="K53" s="114">
         <f t="shared" si="3"/>
-        <v>37937447.460000001</v>
+        <v>60472267.460000001</v>
       </c>
       <c r="L53" s="187">
         <f t="shared" si="4"/>
-        <v>0.14427457493194137</v>
+        <v>0.22997358196439321</v>
       </c>
       <c r="M53" s="184">
         <f t="shared" si="5"/>
-        <v>225015657.60301074</v>
+        <v>202480837.60301074</v>
       </c>
       <c r="N53" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>15001043.840200717</v>
+        <v>14462916.971643625</v>
       </c>
       <c r="O53" s="180">
         <f t="shared" si="7"/>
-        <v>225015657.60301074</v>
+        <v>202480837.60301074</v>
       </c>
       <c r="P53" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>15001043.840200717</v>
+        <v>14462916.971643625</v>
       </c>
       <c r="Q53" s="185">
         <f t="shared" si="9"/>
-        <v>225015657.60301074</v>
+        <v>202480837.60301074</v>
       </c>
       <c r="R53" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>15001043.840200717</v>
+        <v>14462916.971643625</v>
       </c>
       <c r="T53" t="s">
         <v>169</v>
@@ -7943,47 +7943,47 @@
       </c>
       <c r="H54" s="114">
         <f t="shared" si="11"/>
-        <v>217006066.54874799</v>
+        <v>243299179.44867501</v>
       </c>
       <c r="I54" s="114">
         <f t="shared" si="1"/>
-        <v>21781667.005913999</v>
+        <v>22641180.565914001</v>
       </c>
       <c r="J54" s="114">
         <f t="shared" si="2"/>
-        <v>80743855.929943994</v>
+        <v>89583383.009923995</v>
       </c>
       <c r="K54" s="114">
         <f t="shared" si="3"/>
-        <v>319531589.48460597</v>
+        <v>355523743.02451301</v>
       </c>
       <c r="L54" s="187">
         <f t="shared" si="4"/>
-        <v>0.43971925926022132</v>
+        <v>0.48924939529239142</v>
       </c>
       <c r="M54" s="184">
         <f t="shared" si="5"/>
-        <v>407140219.30125958</v>
+        <v>371148065.76135254</v>
       </c>
       <c r="N54" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>27142681.286750637</v>
+        <v>26510576.125810895</v>
       </c>
       <c r="O54" s="180">
         <f t="shared" si="7"/>
-        <v>407140219.30125958</v>
+        <v>371148065.76135254</v>
       </c>
       <c r="P54" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>27142681.286750637</v>
+        <v>26510576.125810895</v>
       </c>
       <c r="Q54" s="185">
         <f t="shared" si="9"/>
-        <v>407140219.30125958</v>
+        <v>371148065.76135254</v>
       </c>
       <c r="R54" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>27142681.286750637</v>
+        <v>26510576.125810895</v>
       </c>
       <c r="T54" t="s">
         <v>115</v>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="H55" s="114">
         <f t="shared" si="11"/>
-        <v>3750000</v>
+        <v>4173423.4199979999</v>
       </c>
       <c r="I55" s="114">
         <f t="shared" si="1"/>
@@ -8025,39 +8025,39 @@
       </c>
       <c r="J55" s="114">
         <f t="shared" si="2"/>
-        <v>148761261.99939999</v>
+        <v>172635135.9993</v>
       </c>
       <c r="K55" s="114">
         <f t="shared" si="3"/>
-        <v>160684929.99939999</v>
+        <v>184982227.41929799</v>
       </c>
       <c r="L55" s="187">
         <f t="shared" si="4"/>
-        <v>0.29911509868338743</v>
+        <v>0.34434453317683705</v>
       </c>
       <c r="M55" s="184">
         <f t="shared" si="5"/>
-        <v>376516069.57128561</v>
+        <v>352218772.15138763</v>
       </c>
       <c r="N55" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>25101071.304752372</v>
+        <v>25158483.725099117</v>
       </c>
       <c r="O55" s="180">
         <f t="shared" si="7"/>
-        <v>376516069.57128561</v>
+        <v>352218772.15138763</v>
       </c>
       <c r="P55" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>25101071.304752372</v>
+        <v>25158483.725099117</v>
       </c>
       <c r="Q55" s="185">
         <f t="shared" si="9"/>
-        <v>376516069.57128561</v>
+        <v>352218772.15138763</v>
       </c>
       <c r="R55" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>25101071.304752372</v>
+        <v>25158483.725099117</v>
       </c>
       <c r="T55" t="s">
         <v>182</v>
@@ -8091,47 +8091,47 @@
       </c>
       <c r="H56" s="114">
         <f t="shared" si="11"/>
-        <v>112131143.770466</v>
+        <v>113441089.730461</v>
       </c>
       <c r="I56" s="114">
         <f t="shared" si="1"/>
-        <v>26436621.659975</v>
+        <v>27162265.819968998</v>
       </c>
       <c r="J56" s="114">
         <f t="shared" si="2"/>
-        <v>91731288.128275007</v>
+        <v>93079035.878275007</v>
       </c>
       <c r="K56" s="114">
         <f t="shared" si="3"/>
-        <v>230299053.558716</v>
+        <v>233682391.42870501</v>
       </c>
       <c r="L56" s="187">
         <f t="shared" si="4"/>
-        <v>0.40055771875105189</v>
+        <v>0.40644233737203689</v>
       </c>
       <c r="M56" s="184">
         <f t="shared" si="5"/>
-        <v>344646934.94150239</v>
+        <v>341263597.07151341</v>
       </c>
       <c r="N56" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>22976462.329433493</v>
+        <v>24375971.219393816</v>
       </c>
       <c r="O56" s="180">
         <f t="shared" si="7"/>
-        <v>344646934.94150239</v>
+        <v>341263597.07151341</v>
       </c>
       <c r="P56" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>22976462.329433493</v>
+        <v>24375971.219393816</v>
       </c>
       <c r="Q56" s="185">
         <f t="shared" si="9"/>
-        <v>344646934.94150239</v>
+        <v>341263597.07151341</v>
       </c>
       <c r="R56" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>22976462.329433493</v>
+        <v>24375971.219393816</v>
       </c>
       <c r="T56" t="s">
         <v>225</v>
@@ -8165,47 +8165,47 @@
       </c>
       <c r="H57" s="114">
         <f t="shared" si="11"/>
-        <v>225357040.79817799</v>
+        <v>239332510.527154</v>
       </c>
       <c r="I57" s="114">
         <f t="shared" si="1"/>
-        <v>22434819.63998</v>
+        <v>24932116.839954998</v>
       </c>
       <c r="J57" s="114">
         <f t="shared" si="2"/>
-        <v>156468829.24970099</v>
+        <v>173790360.81968999</v>
       </c>
       <c r="K57" s="114">
         <f t="shared" si="3"/>
-        <v>404260689.68785894</v>
+        <v>438054988.18679899</v>
       </c>
       <c r="L57" s="187">
         <f t="shared" si="4"/>
-        <v>0.36446673032271359</v>
+        <v>0.39493444037131786</v>
       </c>
       <c r="M57" s="184">
         <f t="shared" si="5"/>
-        <v>704923375.83688772</v>
+        <v>671129077.33794761</v>
       </c>
       <c r="N57" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>46994891.722459182</v>
+        <v>47937791.23842483</v>
       </c>
       <c r="O57" s="180">
         <f t="shared" si="7"/>
-        <v>704923375.83688772</v>
+        <v>671129077.33794761</v>
       </c>
       <c r="P57" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>46994891.722459182</v>
+        <v>47937791.23842483</v>
       </c>
       <c r="Q57" s="185">
         <f t="shared" si="9"/>
-        <v>704923375.83688772</v>
+        <v>671129077.33794761</v>
       </c>
       <c r="R57" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>46994891.722459182</v>
+        <v>47937791.23842483</v>
       </c>
       <c r="T57" t="s">
         <v>120</v>
@@ -8239,47 +8239,47 @@
       </c>
       <c r="H58" s="114">
         <f t="shared" si="11"/>
-        <v>122963699.481111</v>
+        <v>134205157.25907899</v>
       </c>
       <c r="I58" s="114">
         <f t="shared" si="1"/>
-        <v>36359093.799973004</v>
+        <v>37451093.799973004</v>
       </c>
       <c r="J58" s="114">
         <f t="shared" si="2"/>
-        <v>99646577.797502995</v>
+        <v>106501082.50749999</v>
       </c>
       <c r="K58" s="114">
         <f t="shared" si="3"/>
-        <v>258969371.078587</v>
+        <v>278157333.56655198</v>
       </c>
       <c r="L58" s="187">
         <f t="shared" si="4"/>
-        <v>0.42137558073356779</v>
+        <v>0.45259679736928565</v>
       </c>
       <c r="M58" s="184">
         <f t="shared" si="5"/>
-        <v>355611499.0984419</v>
+        <v>336423536.61047691</v>
       </c>
       <c r="N58" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>23707433.273229461</v>
+        <v>24030252.615034066</v>
       </c>
       <c r="O58" s="180">
         <f t="shared" si="7"/>
-        <v>355611499.0984419</v>
+        <v>336423536.61047691</v>
       </c>
       <c r="P58" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>23707433.273229461</v>
+        <v>24030252.615034066</v>
       </c>
       <c r="Q58" s="185">
         <f t="shared" si="9"/>
-        <v>355611499.0984419</v>
+        <v>336423536.61047691</v>
       </c>
       <c r="R58" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>23707433.273229461</v>
+        <v>24030252.615034066</v>
       </c>
       <c r="T58" t="s">
         <v>125</v>
@@ -8337,7 +8337,7 @@
       </c>
       <c r="N59" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>22795403.734428</v>
+        <v>24423646.858315714</v>
       </c>
       <c r="O59" s="180">
         <f t="shared" si="7"/>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="P59" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>22795403.734428</v>
+        <v>24423646.858315714</v>
       </c>
       <c r="Q59" s="185">
         <f t="shared" si="9"/>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="R59" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>22795403.734428</v>
+        <v>24423646.858315714</v>
       </c>
       <c r="T59" t="s">
         <v>170</v>
@@ -8387,47 +8387,47 @@
       </c>
       <c r="H60" s="114">
         <f t="shared" si="11"/>
-        <v>138186464.73536199</v>
+        <v>148994604.18081501</v>
       </c>
       <c r="I60" s="114">
         <f t="shared" si="1"/>
-        <v>49441138.601727001</v>
+        <v>58721904.781634003</v>
       </c>
       <c r="J60" s="114">
         <f t="shared" si="2"/>
-        <v>54299554.287846997</v>
+        <v>59769779.527842999</v>
       </c>
       <c r="K60" s="114">
         <f t="shared" si="3"/>
-        <v>241927157.62493598</v>
+        <v>267486288.49029201</v>
       </c>
       <c r="L60" s="187">
         <f t="shared" si="4"/>
-        <v>0.41770186202863818</v>
+        <v>0.46183124650577984</v>
       </c>
       <c r="M60" s="184">
         <f t="shared" si="5"/>
-        <v>337259050.57144773</v>
+        <v>311699919.7060917</v>
       </c>
       <c r="N60" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>22483936.704763182</v>
+        <v>22264279.979006551</v>
       </c>
       <c r="O60" s="180">
         <f t="shared" si="7"/>
-        <v>337259050.57144773</v>
+        <v>311699919.7060917</v>
       </c>
       <c r="P60" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>22483936.704763182</v>
+        <v>22264279.979006551</v>
       </c>
       <c r="Q60" s="185">
         <f t="shared" si="9"/>
-        <v>337259050.57144773</v>
+        <v>311699919.7060917</v>
       </c>
       <c r="R60" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>22483936.704763182</v>
+        <v>22264279.979006551</v>
       </c>
       <c r="T60" t="s">
         <v>220</v>
@@ -8461,47 +8461,47 @@
       </c>
       <c r="H61" s="114">
         <f t="shared" si="11"/>
-        <v>246152018.821336</v>
+        <v>266345676.026207</v>
       </c>
       <c r="I61" s="114">
         <f t="shared" si="1"/>
-        <v>31651916.244963001</v>
+        <v>33822227.054963</v>
       </c>
       <c r="J61" s="114">
         <f t="shared" si="2"/>
-        <v>107975721.769917</v>
+        <v>117236487.58991501</v>
       </c>
       <c r="K61" s="114">
         <f t="shared" si="3"/>
-        <v>385779656.83621603</v>
+        <v>417404390.671085</v>
       </c>
       <c r="L61" s="187">
         <f t="shared" si="4"/>
-        <v>0.53835268230445044</v>
+        <v>0.58248476647599645</v>
       </c>
       <c r="M61" s="184">
         <f t="shared" si="5"/>
-        <v>330813144.7169655</v>
+        <v>299188410.88209653</v>
       </c>
       <c r="N61" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>22054209.6477977</v>
+        <v>21370600.777292609</v>
       </c>
       <c r="O61" s="180">
         <f t="shared" si="7"/>
-        <v>330813144.7169655</v>
+        <v>299188410.88209653</v>
       </c>
       <c r="P61" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>22054209.6477977</v>
+        <v>21370600.777292609</v>
       </c>
       <c r="Q61" s="185">
         <f t="shared" si="9"/>
-        <v>330813144.7169655</v>
+        <v>299188410.88209653</v>
       </c>
       <c r="R61" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>22054209.6477977</v>
+        <v>21370600.777292609</v>
       </c>
       <c r="T61" t="s">
         <v>126</v>
@@ -8535,47 +8535,47 @@
       </c>
       <c r="H62" s="114">
         <f t="shared" si="11"/>
-        <v>94300637.951456994</v>
+        <v>97216448.761456996</v>
       </c>
       <c r="I62" s="114">
         <f t="shared" si="1"/>
-        <v>20944050.82</v>
+        <v>23128050.82</v>
       </c>
       <c r="J62" s="114">
         <f t="shared" si="2"/>
-        <v>99411702.953909993</v>
+        <v>115369270.523895</v>
       </c>
       <c r="K62" s="114">
         <f t="shared" si="3"/>
-        <v>214656391.72536698</v>
+        <v>235713770.10535198</v>
       </c>
       <c r="L62" s="187">
         <f t="shared" si="4"/>
-        <v>0.44999145916487482</v>
+        <v>0.4941347541640731</v>
       </c>
       <c r="M62" s="184">
         <f t="shared" si="5"/>
-        <v>262366865.83543453</v>
+        <v>241309487.45544952</v>
       </c>
       <c r="N62" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>17491124.38902897</v>
+        <v>17236391.961103536</v>
       </c>
       <c r="O62" s="180">
         <f t="shared" si="7"/>
-        <v>262366865.83543453</v>
+        <v>241309487.45544952</v>
       </c>
       <c r="P62" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>17491124.38902897</v>
+        <v>17236391.961103536</v>
       </c>
       <c r="Q62" s="185">
         <f t="shared" si="9"/>
-        <v>262366865.83543453</v>
+        <v>241309487.45544952</v>
       </c>
       <c r="R62" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>17491124.38902897</v>
+        <v>17236391.961103536</v>
       </c>
       <c r="T62" t="s">
         <v>112</v>
@@ -8609,47 +8609,47 @@
       </c>
       <c r="H63" s="114">
         <f t="shared" si="11"/>
-        <v>252837877.07610399</v>
+        <v>256023408.716097</v>
       </c>
       <c r="I63" s="114">
         <f t="shared" si="1"/>
-        <v>150942202.70816001</v>
+        <v>162504689.06803399</v>
       </c>
       <c r="J63" s="114">
         <f t="shared" si="2"/>
-        <v>166101717.34703001</v>
+        <v>174759375.72681299</v>
       </c>
       <c r="K63" s="114">
         <f t="shared" si="3"/>
-        <v>569881797.13129401</v>
+        <v>593287473.51094401</v>
       </c>
       <c r="L63" s="187">
         <f t="shared" si="4"/>
-        <v>0.58212148505131633</v>
+        <v>0.60602985896558847</v>
       </c>
       <c r="M63" s="184">
         <f t="shared" si="5"/>
-        <v>409092200.16251254</v>
+        <v>385686523.78286254</v>
       </c>
       <c r="N63" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>27272813.344167504</v>
+        <v>27549037.413061611</v>
       </c>
       <c r="O63" s="180">
         <f t="shared" si="7"/>
-        <v>409092200.16251254</v>
+        <v>385686523.78286254</v>
       </c>
       <c r="P63" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>27272813.344167504</v>
+        <v>27549037.413061611</v>
       </c>
       <c r="Q63" s="185">
         <f t="shared" si="9"/>
-        <v>409092200.16251254</v>
+        <v>385686523.78286254</v>
       </c>
       <c r="R63" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>27272813.344167504</v>
+        <v>27549037.413061611</v>
       </c>
       <c r="T63" t="s">
         <v>127</v>
@@ -8683,47 +8683,47 @@
       </c>
       <c r="H64" s="114">
         <f t="shared" si="11"/>
-        <v>68637088.285573989</v>
+        <v>74317188.06557399</v>
       </c>
       <c r="I64" s="114">
         <f t="shared" si="1"/>
-        <v>98580882.086650014</v>
+        <v>99761062.23664999</v>
       </c>
       <c r="J64" s="114">
         <f t="shared" si="2"/>
-        <v>88260793.369258001</v>
+        <v>91463496.029257998</v>
       </c>
       <c r="K64" s="114">
         <f t="shared" si="3"/>
-        <v>255478763.74148202</v>
+        <v>265541746.33148199</v>
       </c>
       <c r="L64" s="187">
         <f t="shared" si="4"/>
-        <v>0.47582780630428895</v>
+        <v>0.49457005658197989</v>
       </c>
       <c r="M64" s="184">
         <f t="shared" si="5"/>
-        <v>281435557.69290876</v>
+        <v>271372575.10290879</v>
       </c>
       <c r="N64" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>18762370.512860585</v>
+        <v>19383755.364493486</v>
       </c>
       <c r="O64" s="180">
         <f t="shared" si="7"/>
-        <v>281435557.69290876</v>
+        <v>271372575.10290879</v>
       </c>
       <c r="P64" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>18762370.512860585</v>
+        <v>19383755.364493486</v>
       </c>
       <c r="Q64" s="185">
         <f t="shared" si="9"/>
-        <v>281435557.69290876</v>
+        <v>271372575.10290879</v>
       </c>
       <c r="R64" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>18762370.512860585</v>
+        <v>19383755.364493486</v>
       </c>
       <c r="T64" t="s">
         <v>122</v>
@@ -8755,47 +8755,47 @@
       </c>
       <c r="H65" s="135">
         <f t="shared" si="12"/>
-        <v>1868269790.1090329</v>
+        <v>2001513938.016166</v>
       </c>
       <c r="I65" s="135">
         <f t="shared" si="12"/>
-        <v>553833736.50379002</v>
+        <v>591642313.31353998</v>
       </c>
       <c r="J65" s="135">
         <f t="shared" si="12"/>
-        <v>1352654990.2322519</v>
+        <v>1484799204.1717582</v>
       </c>
       <c r="K65" s="135">
         <f t="shared" si="12"/>
-        <v>3774758516.8450747</v>
+        <v>4077955455.5014639</v>
       </c>
       <c r="L65" s="189">
         <f t="shared" si="4"/>
-        <v>0.42614283150772658</v>
+        <v>0.46037156464838247</v>
       </c>
       <c r="M65" s="181">
         <f>SUM(M51:M64)</f>
-        <v>5083207023.6984215</v>
+        <v>4780010085.0420322</v>
       </c>
       <c r="N65" s="181">
         <f t="shared" ca="1" si="6"/>
-        <v>338880468.24656141</v>
+        <v>341429291.78871661</v>
       </c>
       <c r="O65" s="181">
         <f>SUM(O51:O64)</f>
-        <v>5083207023.6984215</v>
+        <v>4780010085.0420322</v>
       </c>
       <c r="P65" s="181">
         <f t="shared" ca="1" si="8"/>
-        <v>338880468.24656141</v>
+        <v>341429291.78871661</v>
       </c>
       <c r="Q65" s="186">
         <f>SUM(Q51:Q64)</f>
-        <v>5083207023.6984215</v>
+        <v>4780010085.0420322</v>
       </c>
       <c r="R65" s="186">
         <f t="shared" ca="1" si="10"/>
-        <v>338880468.24656141</v>
+        <v>341429291.78871661</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8804,21 +8804,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="283" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="260" t="s">
+      <c r="G67" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="270"/>
+      <c r="I67" s="270"/>
+      <c r="J67" s="270"/>
+      <c r="K67" s="270"/>
+      <c r="L67" s="271"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -8880,35 +8880,35 @@
       </c>
       <c r="E69" s="114">
         <f>IFERROR($C$31,0)</f>
-        <v>106473741.715563</v>
+        <v>110102138.155559</v>
       </c>
       <c r="F69" s="187">
         <f t="shared" ref="F69:F74" si="13">IFERROR(E69/D69,0)</f>
-        <v>0.41549511855210608</v>
+        <v>0.42965429981782677</v>
       </c>
       <c r="G69" s="184">
         <f>D69*$H$40-E69</f>
-        <v>149783761.58940163</v>
+        <v>146155365.14940563</v>
       </c>
       <c r="H69" s="184">
         <f t="shared" ref="H69:H74" ca="1" si="14">IFERROR(G69/$C$3,0)</f>
-        <v>9985584.1059601083</v>
+        <v>10439668.939243259</v>
       </c>
       <c r="I69" s="204">
         <f>D69*$J$40-E69</f>
-        <v>149783761.58940163</v>
+        <v>146155365.14940563</v>
       </c>
       <c r="J69" s="204">
         <f t="shared" ref="J69:J74" ca="1" si="15">IFERROR(I69/$C$3,0)</f>
-        <v>9985584.1059601083</v>
+        <v>10439668.939243259</v>
       </c>
       <c r="K69" s="185">
         <f>D69*$L$40-E69</f>
-        <v>149783761.58940163</v>
+        <v>146155365.14940563</v>
       </c>
       <c r="L69" s="185">
         <f t="shared" ref="L69:L74" ca="1" si="16">IFERROR(K69/$C$3,0)</f>
-        <v>9985584.1059601083</v>
+        <v>10439668.939243259</v>
       </c>
     </row>
     <row r="70" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8924,35 +8924,35 @@
       </c>
       <c r="E70" s="114">
         <f>IFERROR($C$32,0)</f>
-        <v>84600229.289704993</v>
+        <v>85308067.049704999</v>
       </c>
       <c r="F70" s="187">
         <f t="shared" si="13"/>
-        <v>0.21173432140163156</v>
+        <v>0.21350587153848549</v>
       </c>
       <c r="G70" s="184">
         <f>D70*$H$40-E70</f>
-        <v>314958183.01525962</v>
+        <v>314250345.25525963</v>
       </c>
       <c r="H70" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>20997212.201017309</v>
+        <v>22446453.232518546</v>
       </c>
       <c r="I70" s="204">
         <f>D70*$J$40-E70</f>
-        <v>314958183.01525962</v>
+        <v>314250345.25525963</v>
       </c>
       <c r="J70" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>20997212.201017309</v>
+        <v>22446453.232518546</v>
       </c>
       <c r="K70" s="185">
         <f>D70*$L$40-E70</f>
-        <v>314958183.01525962</v>
+        <v>314250345.25525963</v>
       </c>
       <c r="L70" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>20997212.201017309</v>
+        <v>22446453.232518546</v>
       </c>
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.25">
@@ -8968,35 +8968,35 @@
       </c>
       <c r="E71" s="114">
         <f>M21</f>
-        <v>331139383.81018001</v>
+        <v>367847681.28290999</v>
       </c>
       <c r="F71" s="187">
         <f t="shared" si="13"/>
-        <v>0.30530743857711851</v>
+        <v>0.33915214815823708</v>
       </c>
       <c r="G71" s="184">
         <f>D71*$H$40-E71</f>
-        <v>753470232.49478459</v>
+        <v>716761935.02205455</v>
       </c>
       <c r="H71" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>50231348.83298564</v>
+        <v>51197281.073003896</v>
       </c>
       <c r="I71" s="204">
         <f>D71*$J$40-E71</f>
-        <v>753470232.49478459</v>
+        <v>716761935.02205455</v>
       </c>
       <c r="J71" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>50231348.83298564</v>
+        <v>51197281.073003896</v>
       </c>
       <c r="K71" s="185">
         <f>D71*$L$40-E71</f>
-        <v>753470232.49478459</v>
+        <v>716761935.02205455</v>
       </c>
       <c r="L71" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>50231348.83298564</v>
+        <v>51197281.073003896</v>
       </c>
     </row>
     <row r="72" spans="2:21" hidden="1" x14ac:dyDescent="0.25">
@@ -9098,35 +9098,35 @@
       </c>
       <c r="E74" s="115">
         <f>SUM(E69:E73)</f>
-        <v>522213354.81544799</v>
+        <v>563257886.48817396</v>
       </c>
       <c r="F74" s="177">
         <f t="shared" si="13"/>
-        <v>0.30004923809689554</v>
+        <v>0.32363228196753269</v>
       </c>
       <c r="G74" s="181">
         <f>SUM(G69:G73)</f>
-        <v>1218212177.0994458</v>
+        <v>1177167645.4267197</v>
       </c>
       <c r="H74" s="181">
         <f t="shared" ca="1" si="14"/>
-        <v>81214145.139963061</v>
+        <v>84083403.244765684</v>
       </c>
       <c r="I74" s="186">
         <f>SUM(I69:I73)</f>
-        <v>1218212177.0994458</v>
+        <v>1177167645.4267197</v>
       </c>
       <c r="J74" s="186">
         <f t="shared" ca="1" si="15"/>
-        <v>81214145.139963061</v>
+        <v>84083403.244765684</v>
       </c>
       <c r="K74" s="186">
         <f>SUM(K69:K73)</f>
-        <v>1218212177.0994458</v>
+        <v>1177167645.4267197</v>
       </c>
       <c r="L74" s="186">
         <f t="shared" ca="1" si="16"/>
-        <v>81214145.139963061</v>
+        <v>84083403.244765684</v>
       </c>
     </row>
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9139,10 +9139,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="D80" s="131">
         <f>SUMIF($B$10:$B$26,$T80,$F$10:$F$26)+SUMIF($B$10:$B$26,$U80,$F$10:$F$26)</f>
-        <v>205798588.24992001</v>
+        <v>223826336.25990999</v>
       </c>
       <c r="T80" t="str">
         <f t="shared" ref="T80:U93" si="17">T51</f>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="D81" s="132">
         <f t="shared" ref="D81:D93" si="18">SUMIF($B$10:$B$26,$T81,$F$10:$F$26)+SUMIF($B$10:$B$26,$U81,$F$10:$F$26)</f>
-        <v>58528613.239999995</v>
+        <v>85284019.390000001</v>
       </c>
       <c r="T81" t="str">
         <f t="shared" si="17"/>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="D83" s="131">
         <f t="shared" si="18"/>
-        <v>178712210.57987499</v>
+        <v>217414914.14984</v>
       </c>
       <c r="T83" t="str">
         <f t="shared" si="17"/>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="D86" s="132">
         <f t="shared" si="18"/>
-        <v>526669634.76998198</v>
+        <v>512576661.13998199</v>
       </c>
       <c r="T86" t="str">
         <f t="shared" si="17"/>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="D87" s="131">
         <f t="shared" si="18"/>
-        <v>160386697.35973001</v>
+        <v>185945256.43967</v>
       </c>
       <c r="T87" t="str">
         <f t="shared" si="17"/>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="D90" s="131">
         <f t="shared" si="18"/>
-        <v>299201801.53968298</v>
+        <v>329431621.62963599</v>
       </c>
       <c r="T90" t="str">
         <f t="shared" si="17"/>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="D91" s="132">
         <f t="shared" si="18"/>
-        <v>76315833.649960995</v>
+        <v>87616734.749956995</v>
       </c>
       <c r="T91" t="str">
         <f t="shared" si="17"/>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="D92" s="131">
         <f t="shared" si="18"/>
-        <v>7660216.3833999997</v>
+        <v>9343459.6473999992</v>
       </c>
       <c r="T92" t="str">
         <f t="shared" si="17"/>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="D93" s="132">
         <f t="shared" si="18"/>
-        <v>82881082.859999999</v>
+        <v>84232434.24000001</v>
       </c>
       <c r="T93" t="str">
         <f t="shared" si="17"/>
@@ -9449,18 +9449,12 @@
       <c r="C94" s="58"/>
       <c r="D94" s="120">
         <f>SUM(D80:D93)</f>
-        <v>1655207201.0325511</v>
+        <v>1794723960.0463951</v>
       </c>
     </row>
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -9475,6 +9469,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -10102,11 +10102,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="259" t="s">
         <v>163</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="260"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -10426,33 +10426,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="263"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="270"/>
+      <c r="Q48" s="270"/>
+      <c r="R48" s="271"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -10461,49 +10461,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="268"/>
+      <c r="C50" s="268"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -10528,13 +10528,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="273"/>
+      <c r="N50" s="273"/>
+      <c r="O50" s="275"/>
+      <c r="P50" s="275"/>
+      <c r="Q50" s="277"/>
+      <c r="R50" s="277"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -11650,21 +11650,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="283" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="260" t="s">
+      <c r="G67" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="270"/>
+      <c r="I67" s="270"/>
+      <c r="J67" s="270"/>
+      <c r="K67" s="270"/>
+      <c r="L67" s="271"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -11985,10 +11985,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -12301,12 +12301,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -12321,6 +12315,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -12948,11 +12948,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="259" t="s">
         <v>175</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="260"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -13272,33 +13272,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="263"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="270"/>
+      <c r="Q48" s="270"/>
+      <c r="R48" s="271"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -13307,49 +13307,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="268"/>
+      <c r="C50" s="268"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -13374,13 +13374,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="273"/>
+      <c r="N50" s="273"/>
+      <c r="O50" s="275"/>
+      <c r="P50" s="275"/>
+      <c r="Q50" s="277"/>
+      <c r="R50" s="277"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -14496,21 +14496,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="283" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="260" t="s">
+      <c r="G67" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="270"/>
+      <c r="I67" s="270"/>
+      <c r="J67" s="270"/>
+      <c r="K67" s="270"/>
+      <c r="L67" s="271"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -14831,10 +14831,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -15147,12 +15147,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -15167,6 +15161,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -15794,11 +15794,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="259" t="s">
         <v>177</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="260"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -16118,33 +16118,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="263"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="270"/>
+      <c r="Q48" s="270"/>
+      <c r="R48" s="271"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -16153,49 +16153,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="268"/>
+      <c r="C50" s="268"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -16220,13 +16220,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="273"/>
+      <c r="N50" s="273"/>
+      <c r="O50" s="275"/>
+      <c r="P50" s="275"/>
+      <c r="Q50" s="277"/>
+      <c r="R50" s="277"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -17328,21 +17328,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="283" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="260" t="s">
+      <c r="G67" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="270"/>
+      <c r="I67" s="270"/>
+      <c r="J67" s="270"/>
+      <c r="K67" s="270"/>
+      <c r="L67" s="271"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -17663,10 +17663,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -17979,12 +17979,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -17999,6 +17993,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -25778,11 +25778,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="269" t="s">
+      <c r="B41" s="259" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="270"/>
-      <c r="D41" s="271"/>
+      <c r="C41" s="260"/>
+      <c r="D41" s="261"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -26053,59 +26053,59 @@
       </c>
     </row>
     <row r="48" spans="2:19" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="261"/>
-      <c r="M48" s="261"/>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
+      <c r="L48" s="270"/>
+      <c r="M48" s="270"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="271"/>
       <c r="Q48"/>
       <c r="R48"/>
     </row>
     <row r="49" spans="2:18" s="139" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="277" t="s">
+      <c r="B49" s="267" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="277" t="s">
+      <c r="C49" s="267" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="274" t="s">
+      <c r="D49" s="264" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
+      <c r="E49" s="265"/>
+      <c r="F49" s="266"/>
       <c r="G49" s="140" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="140"/>
       <c r="I49" s="140"/>
-      <c r="J49" s="274" t="s">
+      <c r="J49" s="264" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="263" t="str">
+      <c r="K49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="263" t="str">
+      <c r="L49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
@@ -26120,7 +26120,7 @@
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="267" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -26129,8 +26129,8 @@
       <c r="R49"/>
     </row>
     <row r="50" spans="2:18" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="277"/>
-      <c r="C50" s="277"/>
+      <c r="B50" s="267"/>
+      <c r="C50" s="267"/>
       <c r="D50" s="141" t="s">
         <v>149</v>
       </c>
@@ -26149,13 +26149,13 @@
       <c r="I50" s="142" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="274"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="266"/>
+      <c r="J50" s="264"/>
+      <c r="K50" s="273"/>
+      <c r="L50" s="273"/>
+      <c r="M50" s="275"/>
       <c r="N50" s="188"/>
       <c r="O50" s="183"/>
-      <c r="P50" s="268"/>
+      <c r="P50" s="277"/>
       <c r="Q50"/>
       <c r="R50"/>
     </row>
@@ -27496,10 +27496,10 @@
       <c r="I77"/>
     </row>
     <row r="78" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -27698,13 +27698,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="J49:J50"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
     <mergeCell ref="K48:P48"/>
@@ -27714,6 +27707,13 @@
     <mergeCell ref="P49:P50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="J49:J50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="26" priority="8">
@@ -28753,25 +28753,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="261"/>
-      <c r="M48" s="261"/>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
+      <c r="L48" s="270"/>
+      <c r="M48" s="270"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="271"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -28793,32 +28793,32 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="263" t="str">
+      <c r="K49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="263" t="str">
+      <c r="L49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="265" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="267" t="str">
+      <c r="O49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="267" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -28846,12 +28846,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="266"/>
-      <c r="N50" s="266"/>
-      <c r="O50" s="268"/>
-      <c r="P50" s="268"/>
+      <c r="K50" s="273"/>
+      <c r="L50" s="273"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
+      <c r="O50" s="277"/>
+      <c r="P50" s="277"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="167" t="s">
@@ -30088,10 +30088,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -30285,17 +30285,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -30303,6 +30292,17 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -31060,11 +31060,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="269" t="s">
+      <c r="B41" s="259" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="270"/>
-      <c r="D41" s="271"/>
+      <c r="C41" s="260"/>
+      <c r="D41" s="261"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -31339,25 +31339,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="261"/>
-      <c r="M48" s="261"/>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
+      <c r="L48" s="270"/>
+      <c r="M48" s="270"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="271"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -31379,32 +31379,32 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="263" t="str">
+      <c r="K49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="263" t="str">
+      <c r="L49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="265" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="267" t="str">
+      <c r="O49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="267" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -31432,12 +31432,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="266"/>
-      <c r="N50" s="266"/>
-      <c r="O50" s="268"/>
-      <c r="P50" s="268"/>
+      <c r="K50" s="273"/>
+      <c r="L50" s="273"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
+      <c r="O50" s="277"/>
+      <c r="P50" s="277"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -32674,10 +32674,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -32858,17 +32858,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -32876,6 +32865,17 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -33654,11 +33654,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" s="191" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="269" t="s">
+      <c r="B41" s="259" t="s">
         <v>189</v>
       </c>
-      <c r="C41" s="270"/>
-      <c r="D41" s="271"/>
+      <c r="C41" s="260"/>
+      <c r="D41" s="261"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -33933,25 +33933,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="261"/>
-      <c r="M48" s="261"/>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
+      <c r="L48" s="270"/>
+      <c r="M48" s="270"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="271"/>
     </row>
     <row r="49" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -33973,22 +33973,22 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="263" t="str">
+      <c r="K49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="263" t="str">
+      <c r="L49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="265" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
@@ -34026,10 +34026,10 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="266"/>
-      <c r="N50" s="266"/>
+      <c r="K50" s="273"/>
+      <c r="L50" s="273"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
       <c r="O50" s="282"/>
       <c r="P50" s="282"/>
     </row>
@@ -35268,10 +35268,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -35465,11 +35465,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
@@ -35483,6 +35478,11 @@
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="229">
   <si>
     <t>📊  PANDUAN PENGGUNAAN — DATA PENCAPAIAN 2026</t>
   </si>
@@ -909,7 +909,10 @@
     <t>RONALD</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL —  15 SEPTEMBER 2026</t>
+    <t>WIDI</t>
+  </si>
+  <si>
+    <t>DATA PENCAPAIAN — GLOBAL —  16 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>
@@ -2556,33 +2559,6 @@
     <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2613,6 +2589,33 @@
     <xf numFmtId="0" fontId="48" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2626,15 +2629,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2656,6 +2650,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4299,11 +4302,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>219</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -4623,33 +4626,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -4658,49 +4661,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -4725,13 +4728,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="172" t="s">
         <v>216</v>
       </c>
@@ -5847,21 +5850,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
-      <c r="F67" s="285"/>
-      <c r="G67" s="269" t="s">
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
+      <c r="F67" s="292"/>
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -6180,10 +6183,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -6495,6 +6498,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -6509,12 +6518,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -6590,7 +6593,7 @@
       </c>
       <c r="C3" s="75">
         <f ca="1">IF($J$5&lt;&gt;"",$J$5,MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),9,1)),EOMONTH(DATE(YEAR(TODAY()),9,1),0),11)-MAX(0,$J$3-$J$4)))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" s="76" t="s">
         <v>104</v>
@@ -6718,19 +6721,19 @@
         <v>112</v>
       </c>
       <c r="C10" s="234">
-        <v>97216448.761456996</v>
+        <v>97687948.761456996</v>
       </c>
       <c r="D10" s="234">
-        <v>23128050.82</v>
+        <v>25690735.559999999</v>
       </c>
       <c r="E10" s="234">
-        <v>115369270.523895</v>
+        <v>126561892.173888</v>
       </c>
       <c r="F10" s="234">
-        <v>87616734.749956995</v>
+        <v>89910108.649957001</v>
       </c>
       <c r="G10" s="234">
-        <v>323330504.85530901</v>
+        <v>339850685.145302</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="111"/>
@@ -6746,7 +6749,7 @@
         <v>4173423.4199979999</v>
       </c>
       <c r="D11" s="234">
-        <v>8173668</v>
+        <v>16503315.6</v>
       </c>
       <c r="E11" s="234">
         <v>172635135.9993</v>
@@ -6755,7 +6758,7 @@
         <v>165</v>
       </c>
       <c r="G11" s="234">
-        <v>184982227.41929799</v>
+        <v>193311875.01929799</v>
       </c>
       <c r="H11" s="111"/>
       <c r="I11" s="111"/>
@@ -6768,19 +6771,19 @@
         <v>70</v>
       </c>
       <c r="C12" s="234">
-        <v>91706728.976816997</v>
+        <v>101270591.616817</v>
       </c>
       <c r="D12" s="234">
-        <v>50114229.631486997</v>
+        <v>52222436.801475003</v>
       </c>
       <c r="E12" s="234">
-        <v>91828840.309686005</v>
+        <v>93153164.649685994</v>
       </c>
       <c r="F12" s="234">
-        <v>36339283.75</v>
+        <v>37670094.600000001</v>
       </c>
       <c r="G12" s="234">
-        <v>269989082.66799003</v>
+        <v>284316287.66797799</v>
       </c>
       <c r="H12" s="111"/>
       <c r="I12" s="111"/>
@@ -6796,16 +6799,16 @@
         <v>20451403.544785999</v>
       </c>
       <c r="D13" s="234">
-        <v>11385728.009987</v>
+        <v>15163511.849981001</v>
       </c>
       <c r="E13" s="234">
-        <v>110224370.349769</v>
+        <v>126255902.09974401</v>
       </c>
       <c r="F13" s="234">
-        <v>48944735.640000001</v>
+        <v>51539330.359999999</v>
       </c>
       <c r="G13" s="234">
-        <v>191006237.54454201</v>
+        <v>213410147.85451099</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="111"/>
@@ -6818,19 +6821,19 @@
         <v>115</v>
       </c>
       <c r="C14" s="234">
-        <v>243299179.44867501</v>
+        <v>266514368.66966501</v>
       </c>
       <c r="D14" s="234">
-        <v>22641180.565914001</v>
+        <v>23592531.925912</v>
       </c>
       <c r="E14" s="234">
-        <v>89583383.009923995</v>
+        <v>92544959.589921996</v>
       </c>
       <c r="F14" s="234">
-        <v>217414914.14984</v>
+        <v>221318157.41984001</v>
       </c>
       <c r="G14" s="234">
-        <v>572938657.174353</v>
+        <v>603970017.60533905</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="111"/>
@@ -6843,19 +6846,19 @@
         <v>118</v>
       </c>
       <c r="C15" s="234">
-        <v>513300118.391123</v>
+        <v>908915548.22112203</v>
       </c>
       <c r="D15" s="234">
-        <v>7952668.2969239997</v>
+        <v>8227443.0769239999</v>
       </c>
       <c r="E15" s="234">
-        <v>30690917.85997</v>
+        <v>30703980.92997</v>
       </c>
       <c r="F15" s="234">
         <v>12048648.960000001</v>
       </c>
       <c r="G15" s="234">
-        <v>563992353.50801694</v>
+        <v>959895621.18801606</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="111"/>
@@ -6868,19 +6871,19 @@
         <v>120</v>
       </c>
       <c r="C16" s="234">
-        <v>239332510.527154</v>
+        <v>265775234.204144</v>
       </c>
       <c r="D16" s="234">
-        <v>24932116.839954998</v>
+        <v>25660116.839954998</v>
       </c>
       <c r="E16" s="234">
-        <v>173790360.81968999</v>
+        <v>196011307.52963001</v>
       </c>
       <c r="F16" s="234">
-        <v>512576661.13998199</v>
+        <v>607080263.83997297</v>
       </c>
       <c r="G16" s="234">
-        <v>950631649.32678103</v>
+        <v>1094526922.413702</v>
       </c>
       <c r="H16" s="111"/>
       <c r="I16" s="111"/>
@@ -6893,19 +6896,19 @@
         <v>122</v>
       </c>
       <c r="C17" s="234">
-        <v>65500918.065573998</v>
+        <v>69762134.505548999</v>
       </c>
       <c r="D17" s="234">
         <v>10163923.380899999</v>
       </c>
       <c r="E17" s="234">
-        <v>53129214.029257998</v>
+        <v>57507816.839057997</v>
       </c>
       <c r="F17" s="234">
         <v>23000000.5</v>
       </c>
       <c r="G17" s="234">
-        <v>151794055.975732</v>
+        <v>160433875.22550699</v>
       </c>
       <c r="H17" s="111"/>
       <c r="I17" s="111"/>
@@ -6919,19 +6922,19 @@
         <v>123</v>
       </c>
       <c r="C18" s="234">
-        <v>8816270</v>
+        <v>8992270</v>
       </c>
       <c r="D18" s="234">
-        <v>89597138.855749995</v>
+        <v>101908649.17565399</v>
       </c>
       <c r="E18" s="234">
-        <v>38334282</v>
+        <v>45427362</v>
       </c>
       <c r="F18" s="234">
-        <v>61232433.740000002</v>
+        <v>78205407.060000002</v>
       </c>
       <c r="G18" s="234">
-        <v>197980124.59575</v>
+        <v>234533688.235654</v>
       </c>
       <c r="H18" s="111"/>
       <c r="I18" s="111"/>
@@ -6945,7 +6948,7 @@
         <v>169</v>
       </c>
       <c r="C19" s="234">
-        <v>60472267.460000001</v>
+        <v>61062267.460000001</v>
       </c>
       <c r="D19" s="234" t="s">
         <v>165</v>
@@ -6957,7 +6960,7 @@
         <v>4684684.5599999996</v>
       </c>
       <c r="G19" s="234">
-        <v>65156952.020000003</v>
+        <v>65746952.020000003</v>
       </c>
       <c r="H19" s="111"/>
       <c r="I19" s="111"/>
@@ -6971,7 +6974,7 @@
         <v>170</v>
       </c>
       <c r="C20" s="234">
-        <v>101915659.56</v>
+        <v>103678947.86</v>
       </c>
       <c r="D20" s="234" t="s">
         <v>165</v>
@@ -6980,10 +6983,10 @@
         <v>165</v>
       </c>
       <c r="F20" s="234">
-        <v>5723693.54</v>
+        <v>7921891.6799999997</v>
       </c>
       <c r="G20" s="234">
-        <v>107639353.09999999</v>
+        <v>111600839.54000001</v>
       </c>
       <c r="H20" s="111"/>
       <c r="I20" s="111"/>
@@ -7001,26 +7004,26 @@
         <v>124</v>
       </c>
       <c r="C21" s="234">
-        <v>149619192.339046</v>
+        <v>152742305.07272601</v>
       </c>
       <c r="D21" s="234">
-        <v>31844096.684974</v>
+        <v>32800972.803474002</v>
       </c>
       <c r="E21" s="234">
-        <v>88558585.899890006</v>
+        <v>97627392.209875003</v>
       </c>
       <c r="F21" s="234">
-        <v>223826336.25990999</v>
+        <v>244186872.36991</v>
       </c>
       <c r="G21" s="234">
-        <v>493848211.18382001</v>
+        <v>527357542.45598501</v>
       </c>
       <c r="H21" s="111"/>
       <c r="I21" s="111"/>
       <c r="J21" s="111"/>
       <c r="M21" s="14">
         <f>SUM(C33,C34)+M20</f>
-        <v>367847681.28290999</v>
+        <v>376485717.10283202</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>224</v>
@@ -7031,19 +7034,19 @@
         <v>125</v>
       </c>
       <c r="C22" s="234">
-        <v>134205157.25907899</v>
+        <v>143453221.699076</v>
       </c>
       <c r="D22" s="234">
-        <v>37451093.799973004</v>
+        <v>41749093.869970001</v>
       </c>
       <c r="E22" s="234">
-        <v>106501082.50749999</v>
+        <v>109082163.58750001</v>
       </c>
       <c r="F22" s="234">
-        <v>185945256.43967</v>
+        <v>189300211.47966999</v>
       </c>
       <c r="G22" s="234">
-        <v>464102590.00622201</v>
+        <v>483584690.63621598</v>
       </c>
       <c r="H22" s="111"/>
       <c r="I22" s="111"/>
@@ -7054,19 +7057,19 @@
         <v>126</v>
       </c>
       <c r="C23" s="234">
-        <v>266345676.026207</v>
+        <v>276762050.17882401</v>
       </c>
       <c r="D23" s="234">
-        <v>33822227.054963</v>
+        <v>35346659.494962998</v>
       </c>
       <c r="E23" s="234">
-        <v>117236487.58991501</v>
+        <v>123659802.999915</v>
       </c>
       <c r="F23" s="234">
-        <v>329431621.62963599</v>
+        <v>346886126.43963599</v>
       </c>
       <c r="G23" s="234">
-        <v>746836012.30072105</v>
+        <v>782654639.11333799</v>
       </c>
       <c r="H23" s="111"/>
       <c r="I23" s="111"/>
@@ -7077,19 +7080,19 @@
         <v>225</v>
       </c>
       <c r="C24" s="234">
-        <v>113441089.730461</v>
+        <v>115644192.418262</v>
       </c>
       <c r="D24" s="234">
-        <v>27162265.819968998</v>
+        <v>29527747.859962001</v>
       </c>
       <c r="E24" s="234">
-        <v>93079035.878275007</v>
+        <v>96494351.178264007</v>
       </c>
       <c r="F24" s="234">
         <v>28644143.870000001</v>
       </c>
       <c r="G24" s="234">
-        <v>262326535.29870501</v>
+        <v>270310435.32648802</v>
       </c>
       <c r="H24" s="111"/>
       <c r="I24" s="111"/>
@@ -7100,19 +7103,19 @@
         <v>220</v>
       </c>
       <c r="C25" s="234">
-        <v>148994604.18081501</v>
+        <v>177146201.091674</v>
       </c>
       <c r="D25" s="234">
-        <v>58721904.781634003</v>
+        <v>59546904.781634003</v>
       </c>
       <c r="E25" s="234">
-        <v>59769779.527842999</v>
+        <v>63015076.846628003</v>
       </c>
       <c r="F25" s="234">
         <v>20000000.43</v>
       </c>
       <c r="G25" s="234">
-        <v>287486288.92029202</v>
+        <v>319708183.14993602</v>
       </c>
       <c r="H25" s="111"/>
       <c r="I25" s="111"/>
@@ -7123,19 +7126,19 @@
         <v>127</v>
       </c>
       <c r="C26" s="234">
-        <v>256023408.716097</v>
+        <v>279359725.396097</v>
       </c>
       <c r="D26" s="234">
-        <v>162504689.06803399</v>
+        <v>163050689.06803399</v>
       </c>
       <c r="E26" s="234">
-        <v>174759375.72681299</v>
+        <v>197107299.82678801</v>
       </c>
       <c r="F26" s="234">
         <v>9343459.6473999992</v>
       </c>
       <c r="G26" s="234">
-        <v>602630933.15834403</v>
+        <v>648861173.93831897</v>
       </c>
       <c r="H26" s="111"/>
       <c r="I26" s="111"/>
@@ -7178,7 +7181,7 @@
         <v>131</v>
       </c>
       <c r="C31" s="234">
-        <v>110102138.155559</v>
+        <v>114868579.59551699</v>
       </c>
       <c r="G31" s="111"/>
       <c r="H31" s="111"/>
@@ -7189,7 +7192,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="234">
-        <v>85308067.049704999</v>
+        <v>95938067.129668996</v>
       </c>
       <c r="G32" s="111"/>
       <c r="H32" s="111"/>
@@ -7200,7 +7203,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="234">
-        <v>82096451.309998006</v>
+        <v>89213406.129920006</v>
       </c>
       <c r="G33" s="111"/>
       <c r="H33" s="111"/>
@@ -7211,7 +7214,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="234">
-        <v>285751229.97291201</v>
+        <v>287272310.97291201</v>
       </c>
       <c r="G34" s="111"/>
       <c r="H34" s="111"/>
@@ -7256,17 +7259,17 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
-        <v>227</v>
-      </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="B40" s="269" t="s">
+        <v>228</v>
+      </c>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
       <c r="F40" s="174">
         <f ca="1">IF(MONTH(TODAY())=9,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;9,1,0))</f>
-        <v>0.5</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="G40" s="192" t="s">
         <v>187</v>
@@ -7353,35 +7356,35 @@
       </c>
       <c r="E42" s="46">
         <f>H65</f>
-        <v>2001513938.016166</v>
+        <v>2144476285.8990748</v>
       </c>
       <c r="F42" s="176">
         <f>IFERROR(E42/D42,0)</f>
-        <v>0.44361898438145647</v>
+        <v>0.47530540452972941</v>
       </c>
       <c r="G42" s="184">
         <f>D42*$H$40-E42</f>
-        <v>2510272095.6832304</v>
+        <v>2367309747.8003216</v>
       </c>
       <c r="H42" s="184">
         <f ca="1">IFERROR(G42/$C$3,0)</f>
-        <v>179305149.6916593</v>
+        <v>182100749.83079398</v>
       </c>
       <c r="I42" s="204">
         <f>D42*$J$40-E42</f>
-        <v>2510272095.6832304</v>
+        <v>2367309747.8003216</v>
       </c>
       <c r="J42" s="204">
         <f ca="1">IFERROR(I42/$C$3,0)</f>
-        <v>179305149.6916593</v>
+        <v>182100749.83079398</v>
       </c>
       <c r="K42" s="185">
         <f>D42*$L$40-E42</f>
-        <v>2510272095.6832304</v>
+        <v>2367309747.8003216</v>
       </c>
       <c r="L42" s="185">
         <f ca="1">IFERROR(K42/$C$3,0)</f>
-        <v>179305149.6916593</v>
+        <v>182100749.83079398</v>
       </c>
       <c r="S42" s="173">
         <v>0.8</v>
@@ -7400,35 +7403,35 @@
       </c>
       <c r="E43" s="46">
         <f>I65</f>
-        <v>591642313.31353998</v>
+        <v>632927289.01191401</v>
       </c>
       <c r="F43" s="176">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.4221899235510097</v>
+        <v>0.45165046134838788</v>
       </c>
       <c r="G43" s="184">
         <f>D43*$H$40-E43</f>
-        <v>809722997.20187497</v>
+        <v>768438021.50350094</v>
       </c>
       <c r="H43" s="184">
         <f ca="1">IFERROR(G43/$C$3,0)</f>
-        <v>57837356.94299107</v>
+        <v>59110617.038730845</v>
       </c>
       <c r="I43" s="204">
         <f>D43*$J$40-E43</f>
-        <v>809722997.20187497</v>
+        <v>768438021.50350094</v>
       </c>
       <c r="J43" s="204">
         <f ca="1">IFERROR(I43/$C$3,0)</f>
-        <v>57837356.94299107</v>
+        <v>59110617.038730845</v>
       </c>
       <c r="K43" s="185">
         <f>D43*$L$40-E43</f>
-        <v>809722997.20187497</v>
+        <v>768438021.50350094</v>
       </c>
       <c r="L43" s="185">
         <f ca="1">IFERROR(K43/$C$3,0)</f>
-        <v>57837356.94299107</v>
+        <v>59110617.038730845</v>
       </c>
       <c r="S43" s="173">
         <v>0.85</v>
@@ -7447,35 +7450,35 @@
       </c>
       <c r="E44" s="46">
         <f>J65</f>
-        <v>1484799204.1717582</v>
+        <v>1597083627.5301979</v>
       </c>
       <c r="F44" s="176">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.50420811133784427</v>
+        <v>0.5423376556392896</v>
       </c>
       <c r="G44" s="184">
         <f>IF(D44=0,0,D44*$H$40-E44)</f>
-        <v>1460014992.1569271</v>
+        <v>1347730568.7984874</v>
       </c>
       <c r="H44" s="184">
         <f ca="1">IFERROR(G44/$C$3,0)</f>
-        <v>104286785.15406622</v>
+        <v>103671582.21526827</v>
       </c>
       <c r="I44" s="204">
         <f>IF(D44=0,0,D44*$J$40-E44)</f>
-        <v>1460014992.1569271</v>
+        <v>1347730568.7984874</v>
       </c>
       <c r="J44" s="204">
         <f ca="1">IFERROR(I44/$C$3,0)</f>
-        <v>104286785.15406622</v>
+        <v>103671582.21526827</v>
       </c>
       <c r="K44" s="185">
         <f>IF(D44=0,0,D44*$L$40-E44)</f>
-        <v>1460014992.1569271</v>
+        <v>1347730568.7984874</v>
       </c>
       <c r="L44" s="185">
         <f ca="1">IFERROR(K44/$C$3,0)</f>
-        <v>104286785.15406622</v>
+        <v>103671582.21526827</v>
       </c>
       <c r="S44" s="173">
         <v>0.9</v>
@@ -7494,35 +7497,35 @@
       </c>
       <c r="E45" s="46">
         <f>E74</f>
-        <v>563257886.48817396</v>
+        <v>587292363.82801795</v>
       </c>
       <c r="F45" s="176">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.32363228196753269</v>
+        <v>0.33744182273736972</v>
       </c>
       <c r="G45" s="184">
         <f>D45*$H$40-E45</f>
-        <v>1177167645.4267197</v>
+        <v>1153133168.0868757</v>
       </c>
       <c r="H45" s="184">
         <f ca="1">IFERROR(G45/$C$3,0)</f>
-        <v>84083403.244765684</v>
+        <v>88702551.39129813</v>
       </c>
       <c r="I45" s="204">
         <f>D45*$J$40-E45</f>
-        <v>1177167645.4267197</v>
+        <v>1153133168.0868757</v>
       </c>
       <c r="J45" s="204">
         <f ca="1">IFERROR(I45/$C$3,0)</f>
-        <v>84083403.244765684</v>
+        <v>88702551.39129813</v>
       </c>
       <c r="K45" s="185">
         <f>D45*$L$40-E45</f>
-        <v>1177167645.4267197</v>
+        <v>1153133168.0868757</v>
       </c>
       <c r="L45" s="185">
         <f ca="1">IFERROR(K45/$C$3,0)</f>
-        <v>84083403.244765684</v>
+        <v>88702551.39129813</v>
       </c>
       <c r="S45" s="173">
         <v>0.95</v>
@@ -7539,35 +7542,35 @@
       </c>
       <c r="E46" s="47">
         <f>SUM(E42:E45)</f>
-        <v>4641213341.9896383</v>
+        <v>4961779566.2692051</v>
       </c>
       <c r="F46" s="177">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.43791678475146772</v>
+        <v>0.46816347239376555</v>
       </c>
       <c r="G46" s="181">
         <f>SUM(G42:G45)</f>
-        <v>5957177730.4687519</v>
+        <v>5636611506.1891861</v>
       </c>
       <c r="H46" s="181">
         <f ca="1">IFERROR(G46/$C$3,0)</f>
-        <v>425512695.03348225</v>
+        <v>433585500.47609127</v>
       </c>
       <c r="I46" s="186">
         <f>SUM(I42:I45)</f>
-        <v>5957177730.4687519</v>
+        <v>5636611506.1891861</v>
       </c>
       <c r="J46" s="186">
         <f ca="1">IFERROR(I46/$C$3,0)</f>
-        <v>425512695.03348225</v>
+        <v>433585500.47609127</v>
       </c>
       <c r="K46" s="186">
         <f>SUM(K42:K45)</f>
-        <v>5957177730.4687519</v>
+        <v>5636611506.1891861</v>
       </c>
       <c r="L46" s="186">
         <f ca="1">IFERROR(K46/$C$3,0)</f>
-        <v>425512695.03348225</v>
+        <v>433585500.47609127</v>
       </c>
       <c r="S46" s="173">
         <v>1</v>
@@ -7580,33 +7583,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -7615,49 +7618,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -7682,13 +7685,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -7721,47 +7724,47 @@
       </c>
       <c r="H51" s="114">
         <f>SUMIF($B$10:$B$26,$T51,C$10:C$26)+SUMIF($B$10:$B$26,$U51,C$10:C$26)</f>
-        <v>149619192.339046</v>
+        <v>152742305.07272601</v>
       </c>
       <c r="I51" s="114">
         <f t="shared" ref="I51:I64" si="1">SUMIF($B$10:$B$26,$T51,D$10:D$26)+SUMIF($B$10:$B$26,$U51,D$10:D$26)</f>
-        <v>31844096.684974</v>
+        <v>32800972.803474002</v>
       </c>
       <c r="J51" s="114">
         <f t="shared" ref="J51:J64" si="2">SUMIF($B$10:$B$26,$T51,E$10:E$26)+SUMIF($B$10:$B$26,$U51,E$10:E$26)</f>
-        <v>88558585.899890006</v>
+        <v>97627392.209875003</v>
       </c>
       <c r="K51" s="114">
         <f t="shared" ref="K51:K64" si="3">SUM(H51:J51)</f>
-        <v>270021874.92391002</v>
+        <v>283170670.08607501</v>
       </c>
       <c r="L51" s="187">
         <f t="shared" ref="L51:L65" si="4">IFERROR(K51/G51,0)</f>
-        <v>0.52495903120657328</v>
+        <v>0.55052206668956483</v>
       </c>
       <c r="M51" s="184">
         <f t="shared" ref="M51:M64" si="5">G51*$H$40-K51</f>
-        <v>244345644.96290457</v>
+        <v>231196849.80073959</v>
       </c>
       <c r="N51" s="184">
         <f t="shared" ref="N51:N65" ca="1" si="6">IFERROR(M51/$C$3,0)</f>
-        <v>17453260.354493182</v>
+        <v>17784373.061595354</v>
       </c>
       <c r="O51" s="180">
         <f t="shared" ref="O51:O64" si="7">G51*$J$40-K51</f>
-        <v>244345644.96290457</v>
+        <v>231196849.80073959</v>
       </c>
       <c r="P51" s="180">
         <f t="shared" ref="P51:P65" ca="1" si="8">IFERROR(O51/$C$3,0)</f>
-        <v>17453260.354493182</v>
+        <v>17784373.061595354</v>
       </c>
       <c r="Q51" s="185">
         <f t="shared" ref="Q51:Q64" si="9">G51*$L$40-K51</f>
-        <v>244345644.96290457</v>
+        <v>231196849.80073959</v>
       </c>
       <c r="R51" s="185">
         <f t="shared" ref="R51:R65" ca="1" si="10">IFERROR(Q51/$C$3,0)</f>
-        <v>17453260.354493182</v>
+        <v>17784373.061595354</v>
       </c>
       <c r="T51" t="s">
         <v>124</v>
@@ -7795,47 +7798,47 @@
       </c>
       <c r="H52" s="114">
         <f t="shared" ref="H52:H64" si="11">SUMIF($B$10:$B$26,$T52,C$10:C$26)+SUMIF($B$10:$B$26,$U52,C$10:C$26)</f>
-        <v>112158132.52160299</v>
+        <v>121721995.161603</v>
       </c>
       <c r="I52" s="114">
         <f t="shared" si="1"/>
-        <v>61499957.641473994</v>
+        <v>67385948.651455998</v>
       </c>
       <c r="J52" s="114">
         <f t="shared" si="2"/>
-        <v>202053210.659455</v>
+        <v>219409066.74943</v>
       </c>
       <c r="K52" s="114">
         <f t="shared" si="3"/>
-        <v>375711300.822532</v>
+        <v>408517010.56248903</v>
       </c>
       <c r="L52" s="187">
         <f t="shared" si="4"/>
-        <v>0.47829392550521432</v>
+        <v>0.52005676749627883</v>
       </c>
       <c r="M52" s="184">
         <f t="shared" si="5"/>
-        <v>409812580.59760958</v>
+        <v>377006870.85765254</v>
       </c>
       <c r="N52" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>29272327.185543541</v>
+        <v>29000528.527511735</v>
       </c>
       <c r="O52" s="180">
         <f t="shared" si="7"/>
-        <v>409812580.59760958</v>
+        <v>377006870.85765254</v>
       </c>
       <c r="P52" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>29272327.185543541</v>
+        <v>29000528.527511735</v>
       </c>
       <c r="Q52" s="185">
         <f t="shared" si="9"/>
-        <v>409812580.59760958</v>
+        <v>377006870.85765254</v>
       </c>
       <c r="R52" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>29272327.185543541</v>
+        <v>29000528.527511735</v>
       </c>
       <c r="T52" t="s">
         <v>70</v>
@@ -7869,7 +7872,7 @@
       </c>
       <c r="H53" s="114">
         <f t="shared" si="11"/>
-        <v>60472267.460000001</v>
+        <v>61062267.460000001</v>
       </c>
       <c r="I53" s="114">
         <f t="shared" si="1"/>
@@ -7881,35 +7884,35 @@
       </c>
       <c r="K53" s="114">
         <f t="shared" si="3"/>
-        <v>60472267.460000001</v>
+        <v>61062267.460000001</v>
       </c>
       <c r="L53" s="187">
         <f t="shared" si="4"/>
-        <v>0.22997358196439321</v>
+        <v>0.23221732804930298</v>
       </c>
       <c r="M53" s="184">
         <f t="shared" si="5"/>
-        <v>202480837.60301074</v>
+        <v>201890837.60301074</v>
       </c>
       <c r="N53" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>14462916.971643625</v>
+        <v>15530064.431000827</v>
       </c>
       <c r="O53" s="180">
         <f t="shared" si="7"/>
-        <v>202480837.60301074</v>
+        <v>201890837.60301074</v>
       </c>
       <c r="P53" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>14462916.971643625</v>
+        <v>15530064.431000827</v>
       </c>
       <c r="Q53" s="185">
         <f t="shared" si="9"/>
-        <v>202480837.60301074</v>
+        <v>201890837.60301074</v>
       </c>
       <c r="R53" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>14462916.971643625</v>
+        <v>15530064.431000827</v>
       </c>
       <c r="T53" t="s">
         <v>169</v>
@@ -7943,47 +7946,47 @@
       </c>
       <c r="H54" s="114">
         <f t="shared" si="11"/>
-        <v>243299179.44867501</v>
+        <v>266514368.66966501</v>
       </c>
       <c r="I54" s="114">
         <f t="shared" si="1"/>
-        <v>22641180.565914001</v>
+        <v>23592531.925912</v>
       </c>
       <c r="J54" s="114">
         <f t="shared" si="2"/>
-        <v>89583383.009923995</v>
+        <v>92544959.589921996</v>
       </c>
       <c r="K54" s="114">
         <f t="shared" si="3"/>
-        <v>355523743.02451301</v>
+        <v>382651860.18549901</v>
       </c>
       <c r="L54" s="187">
         <f t="shared" si="4"/>
-        <v>0.48924939529239142</v>
+        <v>0.52658140244196294</v>
       </c>
       <c r="M54" s="184">
         <f t="shared" si="5"/>
-        <v>371148065.76135254</v>
+        <v>344019948.60036653</v>
       </c>
       <c r="N54" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>26510576.125810895</v>
+        <v>26463072.969258964</v>
       </c>
       <c r="O54" s="180">
         <f t="shared" si="7"/>
-        <v>371148065.76135254</v>
+        <v>344019948.60036653</v>
       </c>
       <c r="P54" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>26510576.125810895</v>
+        <v>26463072.969258964</v>
       </c>
       <c r="Q54" s="185">
         <f t="shared" si="9"/>
-        <v>371148065.76135254</v>
+        <v>344019948.60036653</v>
       </c>
       <c r="R54" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>26510576.125810895</v>
+        <v>26463072.969258964</v>
       </c>
       <c r="T54" t="s">
         <v>115</v>
@@ -8021,7 +8024,7 @@
       </c>
       <c r="I55" s="114">
         <f t="shared" si="1"/>
-        <v>8173668</v>
+        <v>16503315.6</v>
       </c>
       <c r="J55" s="114">
         <f t="shared" si="2"/>
@@ -8029,35 +8032,35 @@
       </c>
       <c r="K55" s="114">
         <f t="shared" si="3"/>
-        <v>184982227.41929799</v>
+        <v>193311875.01929802</v>
       </c>
       <c r="L55" s="187">
         <f t="shared" si="4"/>
-        <v>0.34434453317683705</v>
+        <v>0.3598501774452893</v>
       </c>
       <c r="M55" s="184">
         <f t="shared" si="5"/>
-        <v>352218772.15138763</v>
+        <v>343889124.55138761</v>
       </c>
       <c r="N55" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>25158483.725099117</v>
+        <v>26453009.58087597</v>
       </c>
       <c r="O55" s="180">
         <f t="shared" si="7"/>
-        <v>352218772.15138763</v>
+        <v>343889124.55138761</v>
       </c>
       <c r="P55" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>25158483.725099117</v>
+        <v>26453009.58087597</v>
       </c>
       <c r="Q55" s="185">
         <f t="shared" si="9"/>
-        <v>352218772.15138763</v>
+        <v>343889124.55138761</v>
       </c>
       <c r="R55" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>25158483.725099117</v>
+        <v>26453009.58087597</v>
       </c>
       <c r="T55" t="s">
         <v>182</v>
@@ -8091,47 +8094,47 @@
       </c>
       <c r="H56" s="114">
         <f t="shared" si="11"/>
-        <v>113441089.730461</v>
+        <v>115644192.418262</v>
       </c>
       <c r="I56" s="114">
         <f t="shared" si="1"/>
-        <v>27162265.819968998</v>
+        <v>29527747.859962001</v>
       </c>
       <c r="J56" s="114">
         <f t="shared" si="2"/>
-        <v>93079035.878275007</v>
+        <v>96494351.178264007</v>
       </c>
       <c r="K56" s="114">
         <f t="shared" si="3"/>
-        <v>233682391.42870501</v>
+        <v>241666291.45648801</v>
       </c>
       <c r="L56" s="187">
         <f t="shared" si="4"/>
-        <v>0.40644233737203689</v>
+        <v>0.42032868528553308</v>
       </c>
       <c r="M56" s="184">
         <f t="shared" si="5"/>
-        <v>341263597.07151341</v>
+        <v>333279697.04373038</v>
       </c>
       <c r="N56" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>24375971.219393816</v>
+        <v>25636899.772594646</v>
       </c>
       <c r="O56" s="180">
         <f t="shared" si="7"/>
-        <v>341263597.07151341</v>
+        <v>333279697.04373038</v>
       </c>
       <c r="P56" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>24375971.219393816</v>
+        <v>25636899.772594646</v>
       </c>
       <c r="Q56" s="185">
         <f t="shared" si="9"/>
-        <v>341263597.07151341</v>
+        <v>333279697.04373038</v>
       </c>
       <c r="R56" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>24375971.219393816</v>
+        <v>25636899.772594646</v>
       </c>
       <c r="T56" t="s">
         <v>225</v>
@@ -8165,47 +8168,47 @@
       </c>
       <c r="H57" s="114">
         <f t="shared" si="11"/>
-        <v>239332510.527154</v>
+        <v>265775234.204144</v>
       </c>
       <c r="I57" s="114">
         <f t="shared" si="1"/>
-        <v>24932116.839954998</v>
+        <v>25660116.839954998</v>
       </c>
       <c r="J57" s="114">
         <f t="shared" si="2"/>
-        <v>173790360.81968999</v>
+        <v>196011307.52963001</v>
       </c>
       <c r="K57" s="114">
         <f t="shared" si="3"/>
-        <v>438054988.18679899</v>
+        <v>487446658.57372898</v>
       </c>
       <c r="L57" s="187">
         <f t="shared" si="4"/>
-        <v>0.39493444037131786</v>
+        <v>0.43946417346260885</v>
       </c>
       <c r="M57" s="184">
         <f t="shared" si="5"/>
-        <v>671129077.33794761</v>
+        <v>621737406.95101762</v>
       </c>
       <c r="N57" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>47937791.23842483</v>
+        <v>47825954.380847506</v>
       </c>
       <c r="O57" s="180">
         <f t="shared" si="7"/>
-        <v>671129077.33794761</v>
+        <v>621737406.95101762</v>
       </c>
       <c r="P57" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>47937791.23842483</v>
+        <v>47825954.380847506</v>
       </c>
       <c r="Q57" s="185">
         <f t="shared" si="9"/>
-        <v>671129077.33794761</v>
+        <v>621737406.95101762</v>
       </c>
       <c r="R57" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>47937791.23842483</v>
+        <v>47825954.380847506</v>
       </c>
       <c r="T57" t="s">
         <v>120</v>
@@ -8239,47 +8242,47 @@
       </c>
       <c r="H58" s="114">
         <f t="shared" si="11"/>
-        <v>134205157.25907899</v>
+        <v>143453221.699076</v>
       </c>
       <c r="I58" s="114">
         <f t="shared" si="1"/>
-        <v>37451093.799973004</v>
+        <v>41749093.869970001</v>
       </c>
       <c r="J58" s="114">
         <f t="shared" si="2"/>
-        <v>106501082.50749999</v>
+        <v>109082163.58750001</v>
       </c>
       <c r="K58" s="114">
         <f t="shared" si="3"/>
-        <v>278157333.56655198</v>
+        <v>294284479.156546</v>
       </c>
       <c r="L58" s="187">
         <f t="shared" si="4"/>
-        <v>0.45259679736928565</v>
+        <v>0.47883768180382491</v>
       </c>
       <c r="M58" s="184">
         <f t="shared" si="5"/>
-        <v>336423536.61047691</v>
+        <v>320296391.0204829</v>
       </c>
       <c r="N58" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>24030252.615034066</v>
+        <v>24638183.924652532</v>
       </c>
       <c r="O58" s="180">
         <f t="shared" si="7"/>
-        <v>336423536.61047691</v>
+        <v>320296391.0204829</v>
       </c>
       <c r="P58" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>24030252.615034066</v>
+        <v>24638183.924652532</v>
       </c>
       <c r="Q58" s="185">
         <f t="shared" si="9"/>
-        <v>336423536.61047691</v>
+        <v>320296391.0204829</v>
       </c>
       <c r="R58" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>24030252.615034066</v>
+        <v>24638183.924652532</v>
       </c>
       <c r="T58" t="s">
         <v>125</v>
@@ -8313,7 +8316,7 @@
       </c>
       <c r="H59" s="114">
         <f t="shared" si="11"/>
-        <v>101915659.56</v>
+        <v>103678947.86</v>
       </c>
       <c r="I59" s="114">
         <f t="shared" si="1"/>
@@ -8325,35 +8328,35 @@
       </c>
       <c r="K59" s="114">
         <f t="shared" si="3"/>
-        <v>101915659.56</v>
+        <v>103678947.86</v>
       </c>
       <c r="L59" s="187">
         <f t="shared" si="4"/>
-        <v>0.22961904635847757</v>
+        <v>0.23359178793370819</v>
       </c>
       <c r="M59" s="184">
         <f t="shared" si="5"/>
-        <v>341931056.01642001</v>
+        <v>340167767.71641999</v>
       </c>
       <c r="N59" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>24423646.858315714</v>
+        <v>26166751.362801537</v>
       </c>
       <c r="O59" s="180">
         <f t="shared" si="7"/>
-        <v>341931056.01642001</v>
+        <v>340167767.71641999</v>
       </c>
       <c r="P59" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>24423646.858315714</v>
+        <v>26166751.362801537</v>
       </c>
       <c r="Q59" s="185">
         <f t="shared" si="9"/>
-        <v>341931056.01642001</v>
+        <v>340167767.71641999</v>
       </c>
       <c r="R59" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>24423646.858315714</v>
+        <v>26166751.362801537</v>
       </c>
       <c r="T59" t="s">
         <v>170</v>
@@ -8387,47 +8390,47 @@
       </c>
       <c r="H60" s="114">
         <f t="shared" si="11"/>
-        <v>148994604.18081501</v>
+        <v>177146201.091674</v>
       </c>
       <c r="I60" s="114">
         <f t="shared" si="1"/>
-        <v>58721904.781634003</v>
+        <v>59546904.781634003</v>
       </c>
       <c r="J60" s="114">
         <f t="shared" si="2"/>
-        <v>59769779.527842999</v>
+        <v>63015076.846628003</v>
       </c>
       <c r="K60" s="114">
         <f t="shared" si="3"/>
-        <v>267486288.49029201</v>
+        <v>299708182.71993601</v>
       </c>
       <c r="L60" s="187">
         <f t="shared" si="4"/>
-        <v>0.46183124650577984</v>
+        <v>0.5174642946924497</v>
       </c>
       <c r="M60" s="184">
         <f t="shared" si="5"/>
-        <v>311699919.7060917</v>
+        <v>279478025.4764477</v>
       </c>
       <c r="N60" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>22264279.979006551</v>
+        <v>21498309.652034439</v>
       </c>
       <c r="O60" s="180">
         <f t="shared" si="7"/>
-        <v>311699919.7060917</v>
+        <v>279478025.4764477</v>
       </c>
       <c r="P60" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>22264279.979006551</v>
+        <v>21498309.652034439</v>
       </c>
       <c r="Q60" s="185">
         <f t="shared" si="9"/>
-        <v>311699919.7060917</v>
+        <v>279478025.4764477</v>
       </c>
       <c r="R60" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>22264279.979006551</v>
+        <v>21498309.652034439</v>
       </c>
       <c r="T60" t="s">
         <v>220</v>
@@ -8461,47 +8464,47 @@
       </c>
       <c r="H61" s="114">
         <f t="shared" si="11"/>
-        <v>266345676.026207</v>
+        <v>276762050.17882401</v>
       </c>
       <c r="I61" s="114">
         <f t="shared" si="1"/>
-        <v>33822227.054963</v>
+        <v>35346659.494962998</v>
       </c>
       <c r="J61" s="114">
         <f t="shared" si="2"/>
-        <v>117236487.58991501</v>
+        <v>123659802.999915</v>
       </c>
       <c r="K61" s="114">
         <f t="shared" si="3"/>
-        <v>417404390.671085</v>
+        <v>435768512.673702</v>
       </c>
       <c r="L61" s="187">
         <f t="shared" si="4"/>
-        <v>0.58248476647599645</v>
+        <v>0.60811176407186063</v>
       </c>
       <c r="M61" s="184">
         <f t="shared" si="5"/>
-        <v>299188410.88209653</v>
+        <v>280824288.87947953</v>
       </c>
       <c r="N61" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>21370600.777292609</v>
+        <v>21601868.375344578</v>
       </c>
       <c r="O61" s="180">
         <f t="shared" si="7"/>
-        <v>299188410.88209653</v>
+        <v>280824288.87947953</v>
       </c>
       <c r="P61" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>21370600.777292609</v>
+        <v>21601868.375344578</v>
       </c>
       <c r="Q61" s="185">
         <f t="shared" si="9"/>
-        <v>299188410.88209653</v>
+        <v>280824288.87947953</v>
       </c>
       <c r="R61" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>21370600.777292609</v>
+        <v>21601868.375344578</v>
       </c>
       <c r="T61" t="s">
         <v>126</v>
@@ -8535,47 +8538,47 @@
       </c>
       <c r="H62" s="114">
         <f t="shared" si="11"/>
-        <v>97216448.761456996</v>
+        <v>97687948.761456996</v>
       </c>
       <c r="I62" s="114">
         <f t="shared" si="1"/>
-        <v>23128050.82</v>
+        <v>25690735.559999999</v>
       </c>
       <c r="J62" s="114">
         <f t="shared" si="2"/>
-        <v>115369270.523895</v>
+        <v>126561892.173888</v>
       </c>
       <c r="K62" s="114">
         <f t="shared" si="3"/>
-        <v>235713770.10535198</v>
+        <v>249940576.495345</v>
       </c>
       <c r="L62" s="187">
         <f t="shared" si="4"/>
-        <v>0.4941347541640731</v>
+        <v>0.52395888991531514</v>
       </c>
       <c r="M62" s="184">
         <f t="shared" si="5"/>
-        <v>241309487.45544952</v>
+        <v>227082681.06545651</v>
       </c>
       <c r="N62" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>17236391.961103536</v>
+        <v>17467898.543496653</v>
       </c>
       <c r="O62" s="180">
         <f t="shared" si="7"/>
-        <v>241309487.45544952</v>
+        <v>227082681.06545651</v>
       </c>
       <c r="P62" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>17236391.961103536</v>
+        <v>17467898.543496653</v>
       </c>
       <c r="Q62" s="185">
         <f t="shared" si="9"/>
-        <v>241309487.45544952</v>
+        <v>227082681.06545651</v>
       </c>
       <c r="R62" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>17236391.961103536</v>
+        <v>17467898.543496653</v>
       </c>
       <c r="T62" t="s">
         <v>112</v>
@@ -8609,47 +8612,47 @@
       </c>
       <c r="H63" s="114">
         <f t="shared" si="11"/>
-        <v>256023408.716097</v>
+        <v>279359725.396097</v>
       </c>
       <c r="I63" s="114">
         <f t="shared" si="1"/>
-        <v>162504689.06803399</v>
+        <v>163050689.06803399</v>
       </c>
       <c r="J63" s="114">
         <f t="shared" si="2"/>
-        <v>174759375.72681299</v>
+        <v>197107299.82678801</v>
       </c>
       <c r="K63" s="114">
         <f t="shared" si="3"/>
-        <v>593287473.51094401</v>
+        <v>639517714.29091907</v>
       </c>
       <c r="L63" s="187">
         <f t="shared" si="4"/>
-        <v>0.60602985896558847</v>
+        <v>0.65325301392963253</v>
       </c>
       <c r="M63" s="184">
         <f t="shared" si="5"/>
-        <v>385686523.78286254</v>
+        <v>339456283.00288749</v>
       </c>
       <c r="N63" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>27549037.413061611</v>
+        <v>26112021.769452885</v>
       </c>
       <c r="O63" s="180">
         <f t="shared" si="7"/>
-        <v>385686523.78286254</v>
+        <v>339456283.00288749</v>
       </c>
       <c r="P63" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>27549037.413061611</v>
+        <v>26112021.769452885</v>
       </c>
       <c r="Q63" s="185">
         <f t="shared" si="9"/>
-        <v>385686523.78286254</v>
+        <v>339456283.00288749</v>
       </c>
       <c r="R63" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>27549037.413061611</v>
+        <v>26112021.769452885</v>
       </c>
       <c r="T63" t="s">
         <v>127</v>
@@ -8683,47 +8686,47 @@
       </c>
       <c r="H64" s="114">
         <f t="shared" si="11"/>
-        <v>74317188.06557399</v>
+        <v>78754404.505548999</v>
       </c>
       <c r="I64" s="114">
         <f t="shared" si="1"/>
-        <v>99761062.23664999</v>
+        <v>112072572.55655399</v>
       </c>
       <c r="J64" s="114">
         <f t="shared" si="2"/>
-        <v>91463496.029257998</v>
+        <v>102935178.839058</v>
       </c>
       <c r="K64" s="114">
         <f t="shared" si="3"/>
-        <v>265541746.33148199</v>
+        <v>293762155.90116096</v>
       </c>
       <c r="L64" s="187">
         <f t="shared" si="4"/>
-        <v>0.49457005658197989</v>
+        <v>0.54713041573628007</v>
       </c>
       <c r="M64" s="184">
         <f t="shared" si="5"/>
-        <v>271372575.10290879</v>
+        <v>243152165.53322983</v>
       </c>
       <c r="N64" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>19383755.364493486</v>
+        <v>18704012.73332537</v>
       </c>
       <c r="O64" s="180">
         <f t="shared" si="7"/>
-        <v>271372575.10290879</v>
+        <v>243152165.53322983</v>
       </c>
       <c r="P64" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>19383755.364493486</v>
+        <v>18704012.73332537</v>
       </c>
       <c r="Q64" s="185">
         <f t="shared" si="9"/>
-        <v>271372575.10290879</v>
+        <v>243152165.53322983</v>
       </c>
       <c r="R64" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>19383755.364493486</v>
+        <v>18704012.73332537</v>
       </c>
       <c r="T64" t="s">
         <v>122</v>
@@ -8755,47 +8758,47 @@
       </c>
       <c r="H65" s="135">
         <f t="shared" si="12"/>
-        <v>2001513938.016166</v>
+        <v>2144476285.8990748</v>
       </c>
       <c r="I65" s="135">
         <f t="shared" si="12"/>
-        <v>591642313.31353998</v>
+        <v>632927289.01191401</v>
       </c>
       <c r="J65" s="135">
         <f t="shared" si="12"/>
-        <v>1484799204.1717582</v>
+        <v>1597083627.5301979</v>
       </c>
       <c r="K65" s="135">
         <f t="shared" si="12"/>
-        <v>4077955455.5014639</v>
+        <v>4374487202.4411879</v>
       </c>
       <c r="L65" s="189">
         <f t="shared" si="4"/>
-        <v>0.46037156464838247</v>
+        <v>0.49384784603404358</v>
       </c>
       <c r="M65" s="181">
         <f>SUM(M51:M64)</f>
-        <v>4780010085.0420322</v>
+        <v>4483478338.1023083</v>
       </c>
       <c r="N65" s="181">
         <f t="shared" ca="1" si="6"/>
-        <v>341429291.78871661</v>
+        <v>344882949.08479297</v>
       </c>
       <c r="O65" s="181">
         <f>SUM(O51:O64)</f>
-        <v>4780010085.0420322</v>
+        <v>4483478338.1023083</v>
       </c>
       <c r="P65" s="181">
         <f t="shared" ca="1" si="8"/>
-        <v>341429291.78871661</v>
+        <v>344882949.08479297</v>
       </c>
       <c r="Q65" s="186">
         <f>SUM(Q51:Q64)</f>
-        <v>4780010085.0420322</v>
+        <v>4483478338.1023083</v>
       </c>
       <c r="R65" s="186">
         <f t="shared" ca="1" si="10"/>
-        <v>341429291.78871661</v>
+        <v>344882949.08479297</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8804,21 +8807,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="269" t="s">
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -8880,35 +8883,35 @@
       </c>
       <c r="E69" s="114">
         <f>IFERROR($C$31,0)</f>
-        <v>110102138.155559</v>
+        <v>114868579.59551699</v>
       </c>
       <c r="F69" s="187">
         <f t="shared" ref="F69:F74" si="13">IFERROR(E69/D69,0)</f>
-        <v>0.42965429981782677</v>
+        <v>0.44825450226452579</v>
       </c>
       <c r="G69" s="184">
         <f>D69*$H$40-E69</f>
-        <v>146155365.14940563</v>
+        <v>141388923.70944762</v>
       </c>
       <c r="H69" s="184">
         <f t="shared" ref="H69:H74" ca="1" si="14">IFERROR(G69/$C$3,0)</f>
-        <v>10439668.939243259</v>
+        <v>10876071.054572893</v>
       </c>
       <c r="I69" s="204">
         <f>D69*$J$40-E69</f>
-        <v>146155365.14940563</v>
+        <v>141388923.70944762</v>
       </c>
       <c r="J69" s="204">
         <f t="shared" ref="J69:J74" ca="1" si="15">IFERROR(I69/$C$3,0)</f>
-        <v>10439668.939243259</v>
+        <v>10876071.054572893</v>
       </c>
       <c r="K69" s="185">
         <f>D69*$L$40-E69</f>
-        <v>146155365.14940563</v>
+        <v>141388923.70944762</v>
       </c>
       <c r="L69" s="185">
         <f t="shared" ref="L69:L74" ca="1" si="16">IFERROR(K69/$C$3,0)</f>
-        <v>10439668.939243259</v>
+        <v>10876071.054572893</v>
       </c>
     </row>
     <row r="70" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8916,7 +8919,7 @@
         <v>94</v>
       </c>
       <c r="C70" s="56" t="s">
-        <v>99</v>
+        <v>227</v>
       </c>
       <c r="D70" s="117">
         <f>TARGETS!L23</f>
@@ -8924,35 +8927,35 @@
       </c>
       <c r="E70" s="114">
         <f>IFERROR($C$32,0)</f>
-        <v>85308067.049704999</v>
+        <v>95938067.129668996</v>
       </c>
       <c r="F70" s="187">
         <f t="shared" si="13"/>
-        <v>0.21350587153848549</v>
+        <v>0.24011024214513063</v>
       </c>
       <c r="G70" s="184">
         <f>D70*$H$40-E70</f>
-        <v>314250345.25525963</v>
+        <v>303620345.17529559</v>
       </c>
       <c r="H70" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>22446453.232518546</v>
+        <v>23355411.167330429</v>
       </c>
       <c r="I70" s="204">
         <f>D70*$J$40-E70</f>
-        <v>314250345.25525963</v>
+        <v>303620345.17529559</v>
       </c>
       <c r="J70" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>22446453.232518546</v>
+        <v>23355411.167330429</v>
       </c>
       <c r="K70" s="185">
         <f>D70*$L$40-E70</f>
-        <v>314250345.25525963</v>
+        <v>303620345.17529559</v>
       </c>
       <c r="L70" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>22446453.232518546</v>
+        <v>23355411.167330429</v>
       </c>
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.25">
@@ -8968,35 +8971,35 @@
       </c>
       <c r="E71" s="114">
         <f>M21</f>
-        <v>367847681.28290999</v>
+        <v>376485717.10283202</v>
       </c>
       <c r="F71" s="187">
         <f t="shared" si="13"/>
-        <v>0.33915214815823708</v>
+        <v>0.34711633701482308</v>
       </c>
       <c r="G71" s="184">
         <f>D71*$H$40-E71</f>
-        <v>716761935.02205455</v>
+        <v>708123899.20213246</v>
       </c>
       <c r="H71" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>51197281.073003896</v>
+        <v>54471069.169394806</v>
       </c>
       <c r="I71" s="204">
         <f>D71*$J$40-E71</f>
-        <v>716761935.02205455</v>
+        <v>708123899.20213246</v>
       </c>
       <c r="J71" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>51197281.073003896</v>
+        <v>54471069.169394806</v>
       </c>
       <c r="K71" s="185">
         <f>D71*$L$40-E71</f>
-        <v>716761935.02205455</v>
+        <v>708123899.20213246</v>
       </c>
       <c r="L71" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>51197281.073003896</v>
+        <v>54471069.169394806</v>
       </c>
     </row>
     <row r="72" spans="2:21" hidden="1" x14ac:dyDescent="0.25">
@@ -9098,35 +9101,35 @@
       </c>
       <c r="E74" s="115">
         <f>SUM(E69:E73)</f>
-        <v>563257886.48817396</v>
+        <v>587292363.82801795</v>
       </c>
       <c r="F74" s="177">
         <f t="shared" si="13"/>
-        <v>0.32363228196753269</v>
+        <v>0.33744182273736972</v>
       </c>
       <c r="G74" s="181">
         <f>SUM(G69:G73)</f>
-        <v>1177167645.4267197</v>
+        <v>1153133168.0868757</v>
       </c>
       <c r="H74" s="181">
         <f t="shared" ca="1" si="14"/>
-        <v>84083403.244765684</v>
+        <v>88702551.39129813</v>
       </c>
       <c r="I74" s="186">
         <f>SUM(I69:I73)</f>
-        <v>1177167645.4267197</v>
+        <v>1153133168.0868757</v>
       </c>
       <c r="J74" s="186">
         <f t="shared" ca="1" si="15"/>
-        <v>84083403.244765684</v>
+        <v>88702551.39129813</v>
       </c>
       <c r="K74" s="186">
         <f>SUM(K69:K73)</f>
-        <v>1177167645.4267197</v>
+        <v>1153133168.0868757</v>
       </c>
       <c r="L74" s="186">
         <f t="shared" ca="1" si="16"/>
-        <v>84083403.244765684</v>
+        <v>88702551.39129813</v>
       </c>
     </row>
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9139,10 +9142,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -9171,7 +9174,7 @@
       </c>
       <c r="D80" s="131">
         <f>SUMIF($B$10:$B$26,$T80,$F$10:$F$26)+SUMIF($B$10:$B$26,$U80,$F$10:$F$26)</f>
-        <v>223826336.25990999</v>
+        <v>244186872.36991</v>
       </c>
       <c r="T80" t="str">
         <f t="shared" ref="T80:U93" si="17">T51</f>
@@ -9191,7 +9194,7 @@
       </c>
       <c r="D81" s="132">
         <f t="shared" ref="D81:D93" si="18">SUMIF($B$10:$B$26,$T81,$F$10:$F$26)+SUMIF($B$10:$B$26,$U81,$F$10:$F$26)</f>
-        <v>85284019.390000001</v>
+        <v>89209424.960000008</v>
       </c>
       <c r="T81" t="str">
         <f t="shared" si="17"/>
@@ -9231,7 +9234,7 @@
       </c>
       <c r="D83" s="131">
         <f t="shared" si="18"/>
-        <v>217414914.14984</v>
+        <v>221318157.41984001</v>
       </c>
       <c r="T83" t="str">
         <f t="shared" si="17"/>
@@ -9291,7 +9294,7 @@
       </c>
       <c r="D86" s="132">
         <f t="shared" si="18"/>
-        <v>512576661.13998199</v>
+        <v>607080263.83997297</v>
       </c>
       <c r="T86" t="str">
         <f t="shared" si="17"/>
@@ -9311,7 +9314,7 @@
       </c>
       <c r="D87" s="131">
         <f t="shared" si="18"/>
-        <v>185945256.43967</v>
+        <v>189300211.47966999</v>
       </c>
       <c r="T87" t="str">
         <f t="shared" si="17"/>
@@ -9331,7 +9334,7 @@
       </c>
       <c r="D88" s="132">
         <f t="shared" si="18"/>
-        <v>5723693.54</v>
+        <v>7921891.6799999997</v>
       </c>
       <c r="T88" t="str">
         <f t="shared" si="17"/>
@@ -9371,7 +9374,7 @@
       </c>
       <c r="D90" s="131">
         <f t="shared" si="18"/>
-        <v>329431621.62963599</v>
+        <v>346886126.43963599</v>
       </c>
       <c r="T90" t="str">
         <f t="shared" si="17"/>
@@ -9391,7 +9394,7 @@
       </c>
       <c r="D91" s="132">
         <f t="shared" si="18"/>
-        <v>87616734.749956995</v>
+        <v>89910108.649957001</v>
       </c>
       <c r="T91" t="str">
         <f t="shared" si="17"/>
@@ -9431,7 +9434,7 @@
       </c>
       <c r="D93" s="132">
         <f t="shared" si="18"/>
-        <v>84232434.24000001</v>
+        <v>101205407.56</v>
       </c>
       <c r="T93" t="str">
         <f t="shared" si="17"/>
@@ -9449,12 +9452,18 @@
       <c r="C94" s="58"/>
       <c r="D94" s="120">
         <f>SUM(D80:D93)</f>
-        <v>1794723960.0463951</v>
+        <v>1959690752.9063859</v>
       </c>
     </row>
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -9469,12 +9478,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -10102,11 +10105,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>163</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -10426,33 +10429,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -10461,49 +10464,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -10528,13 +10531,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -11650,21 +11653,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="269" t="s">
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -11985,10 +11988,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -12301,6 +12304,12 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -12315,12 +12324,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -12948,11 +12951,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>175</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -13272,33 +13275,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -13307,49 +13310,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -13374,13 +13377,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -14496,21 +14499,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="269" t="s">
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -14831,10 +14834,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -15147,6 +15150,12 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -15161,12 +15170,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -15794,11 +15797,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>177</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -16118,33 +16121,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -16153,49 +16156,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -16220,13 +16223,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -17328,21 +17331,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="269" t="s">
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -17663,10 +17666,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -17979,6 +17982,12 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -17993,12 +18002,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -25778,11 +25781,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="259" t="s">
+      <c r="B41" s="269" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="260"/>
-      <c r="D41" s="261"/>
+      <c r="C41" s="270"/>
+      <c r="D41" s="271"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -26053,59 +26056,59 @@
       </c>
     </row>
     <row r="48" spans="2:19" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="270"/>
-      <c r="M48" s="270"/>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="271"/>
+      <c r="L48" s="261"/>
+      <c r="M48" s="261"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
       <c r="Q48"/>
       <c r="R48"/>
     </row>
     <row r="49" spans="2:18" s="139" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="267" t="s">
+      <c r="B49" s="277" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="267" t="s">
+      <c r="C49" s="277" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="264" t="s">
+      <c r="D49" s="274" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="265"/>
-      <c r="F49" s="266"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
       <c r="G49" s="140" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="140"/>
       <c r="I49" s="140"/>
-      <c r="J49" s="264" t="s">
+      <c r="J49" s="274" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="272" t="str">
+      <c r="K49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="272" t="str">
+      <c r="L49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
@@ -26120,7 +26123,7 @@
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="276" t="str">
+      <c r="P49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -26129,8 +26132,8 @@
       <c r="R49"/>
     </row>
     <row r="50" spans="2:18" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="267"/>
-      <c r="C50" s="267"/>
+      <c r="B50" s="277"/>
+      <c r="C50" s="277"/>
       <c r="D50" s="141" t="s">
         <v>149</v>
       </c>
@@ -26149,13 +26152,13 @@
       <c r="I50" s="142" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="264"/>
-      <c r="K50" s="273"/>
-      <c r="L50" s="273"/>
-      <c r="M50" s="275"/>
+      <c r="J50" s="274"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="266"/>
       <c r="N50" s="188"/>
       <c r="O50" s="183"/>
-      <c r="P50" s="277"/>
+      <c r="P50" s="268"/>
       <c r="Q50"/>
       <c r="R50"/>
     </row>
@@ -27496,10 +27499,10 @@
       <c r="I77"/>
     </row>
     <row r="78" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -27698,6 +27701,13 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="J49:J50"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
     <mergeCell ref="K48:P48"/>
@@ -27707,13 +27717,6 @@
     <mergeCell ref="P49:P50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="J49:J50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="26" priority="8">
@@ -28753,25 +28756,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="270"/>
-      <c r="M48" s="270"/>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="271"/>
+      <c r="L48" s="261"/>
+      <c r="M48" s="261"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -28793,32 +28796,32 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="272" t="str">
+      <c r="K49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="272" t="str">
+      <c r="L49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="274" t="str">
+      <c r="N49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="276" t="str">
+      <c r="O49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="276" t="str">
+      <c r="P49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -28846,12 +28849,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="273"/>
-      <c r="L50" s="273"/>
-      <c r="M50" s="275"/>
-      <c r="N50" s="275"/>
-      <c r="O50" s="277"/>
-      <c r="P50" s="277"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="266"/>
+      <c r="N50" s="266"/>
+      <c r="O50" s="268"/>
+      <c r="P50" s="268"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="167" t="s">
@@ -30088,10 +30091,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -30285,6 +30288,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -30292,17 +30306,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -31060,11 +31063,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="259" t="s">
+      <c r="B41" s="269" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="260"/>
-      <c r="D41" s="261"/>
+      <c r="C41" s="270"/>
+      <c r="D41" s="271"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -31339,25 +31342,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="270"/>
-      <c r="M48" s="270"/>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="271"/>
+      <c r="L48" s="261"/>
+      <c r="M48" s="261"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -31379,32 +31382,32 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="272" t="str">
+      <c r="K49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="272" t="str">
+      <c r="L49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="274" t="str">
+      <c r="N49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="276" t="str">
+      <c r="O49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="276" t="str">
+      <c r="P49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -31432,12 +31435,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="273"/>
-      <c r="L50" s="273"/>
-      <c r="M50" s="275"/>
-      <c r="N50" s="275"/>
-      <c r="O50" s="277"/>
-      <c r="P50" s="277"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="266"/>
+      <c r="N50" s="266"/>
+      <c r="O50" s="268"/>
+      <c r="P50" s="268"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -32674,10 +32677,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -32858,6 +32861,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -32865,17 +32879,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -33654,11 +33657,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" s="191" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="259" t="s">
+      <c r="B41" s="269" t="s">
         <v>189</v>
       </c>
-      <c r="C41" s="260"/>
-      <c r="D41" s="261"/>
+      <c r="C41" s="270"/>
+      <c r="D41" s="271"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -33933,25 +33936,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="270"/>
-      <c r="M48" s="270"/>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="271"/>
+      <c r="L48" s="261"/>
+      <c r="M48" s="261"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
     </row>
     <row r="49" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -33973,22 +33976,22 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="272" t="str">
+      <c r="K49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="272" t="str">
+      <c r="L49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="274" t="str">
+      <c r="N49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
@@ -34026,10 +34029,10 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="273"/>
-      <c r="L50" s="273"/>
-      <c r="M50" s="275"/>
-      <c r="N50" s="275"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="266"/>
+      <c r="N50" s="266"/>
       <c r="O50" s="282"/>
       <c r="P50" s="282"/>
     </row>
@@ -35268,10 +35271,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -35465,6 +35468,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
@@ -35478,11 +35486,6 @@
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -912,7 +912,7 @@
     <t>WIDI</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL —  16 SEPTEMBER 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL —  17 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>
@@ -2559,6 +2559,33 @@
     <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2589,33 +2616,6 @@
     <xf numFmtId="0" fontId="48" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2629,6 +2629,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2650,15 +2659,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4302,11 +4302,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="259" t="s">
         <v>219</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="260"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -4626,33 +4626,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="263"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="270"/>
+      <c r="Q48" s="270"/>
+      <c r="R48" s="271"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -4661,49 +4661,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="268"/>
+      <c r="C50" s="268"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -4728,13 +4728,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="273"/>
+      <c r="N50" s="273"/>
+      <c r="O50" s="275"/>
+      <c r="P50" s="275"/>
+      <c r="Q50" s="277"/>
+      <c r="R50" s="277"/>
       <c r="T50" s="172" t="s">
         <v>216</v>
       </c>
@@ -5850,21 +5850,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="283" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
-      <c r="F67" s="292"/>
-      <c r="G67" s="260" t="s">
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
+      <c r="F67" s="285"/>
+      <c r="G67" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="270"/>
+      <c r="I67" s="270"/>
+      <c r="J67" s="270"/>
+      <c r="K67" s="270"/>
+      <c r="L67" s="271"/>
     </row>
     <row r="68" spans="2:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -6183,10 +6183,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -6498,12 +6498,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -6518,6 +6512,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -6551,8 +6551,10 @@
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="37.42578125" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" customWidth="1"/>
-    <col min="4" max="10" width="16.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="16.42578125" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
+    <col min="8" max="10" width="16.42578125" customWidth="1"/>
     <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="18" width="16.42578125" customWidth="1"/>
   </cols>
@@ -6593,7 +6595,7 @@
       </c>
       <c r="C3" s="75">
         <f ca="1">IF($J$5&lt;&gt;"",$J$5,MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),9,1)),EOMONTH(DATE(YEAR(TODAY()),9,1),0),11)-MAX(0,$J$3-$J$4)))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" s="76" t="s">
         <v>104</v>
@@ -6721,19 +6723,19 @@
         <v>112</v>
       </c>
       <c r="C10" s="234">
-        <v>97687948.761456996</v>
+        <v>94059448.761456996</v>
       </c>
       <c r="D10" s="234">
-        <v>25690735.559999999</v>
+        <v>28420735.559999999</v>
       </c>
       <c r="E10" s="234">
-        <v>126561892.173888</v>
+        <v>127169369.653888</v>
       </c>
       <c r="F10" s="234">
-        <v>89910108.649957001</v>
+        <v>97531730.539957002</v>
       </c>
       <c r="G10" s="234">
-        <v>339850685.145302</v>
+        <v>347181284.515302</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="111"/>
@@ -6771,19 +6773,19 @@
         <v>70</v>
       </c>
       <c r="C12" s="234">
-        <v>101270591.616817</v>
+        <v>114479651.836816</v>
       </c>
       <c r="D12" s="234">
-        <v>52222436.801475003</v>
+        <v>52195418.771476999</v>
       </c>
       <c r="E12" s="234">
-        <v>93153164.649685994</v>
+        <v>93048570.049695998</v>
       </c>
       <c r="F12" s="234">
         <v>37670094.600000001</v>
       </c>
       <c r="G12" s="234">
-        <v>284316287.66797799</v>
+        <v>297393735.25798899</v>
       </c>
       <c r="H12" s="111"/>
       <c r="I12" s="111"/>
@@ -6802,13 +6804,13 @@
         <v>15163511.849981001</v>
       </c>
       <c r="E13" s="234">
-        <v>126255902.09974401</v>
+        <v>126765181.37974399</v>
       </c>
       <c r="F13" s="234">
-        <v>51539330.359999999</v>
+        <v>51377168.189999998</v>
       </c>
       <c r="G13" s="234">
-        <v>213410147.85451099</v>
+        <v>213757264.96451101</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="111"/>
@@ -6821,19 +6823,19 @@
         <v>115</v>
       </c>
       <c r="C14" s="234">
-        <v>266514368.66966501</v>
+        <v>292379540.899665</v>
       </c>
       <c r="D14" s="234">
-        <v>23592531.925912</v>
+        <v>24047531.925912</v>
       </c>
       <c r="E14" s="234">
-        <v>92544959.589921996</v>
+        <v>96084216.349922001</v>
       </c>
       <c r="F14" s="234">
-        <v>221318157.41984001</v>
+        <v>247825364.82984</v>
       </c>
       <c r="G14" s="234">
-        <v>603970017.60533905</v>
+        <v>660336654.00533903</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="111"/>
@@ -6846,19 +6848,19 @@
         <v>118</v>
       </c>
       <c r="C15" s="234">
-        <v>908915548.22112203</v>
+        <v>1049053078.841123</v>
       </c>
       <c r="D15" s="234">
         <v>8227443.0769239999</v>
       </c>
       <c r="E15" s="234">
-        <v>30703980.92997</v>
+        <v>55748125.069968</v>
       </c>
       <c r="F15" s="234">
-        <v>12048648.960000001</v>
+        <v>10913513.77</v>
       </c>
       <c r="G15" s="234">
-        <v>959895621.18801606</v>
+        <v>1123942160.7580149</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="111"/>
@@ -6871,19 +6873,19 @@
         <v>120</v>
       </c>
       <c r="C16" s="234">
-        <v>265775234.204144</v>
+        <v>278713205.39376199</v>
       </c>
       <c r="D16" s="234">
-        <v>25660116.839954998</v>
+        <v>27681738.359931</v>
       </c>
       <c r="E16" s="234">
-        <v>196011307.52963001</v>
+        <v>198283694.90963</v>
       </c>
       <c r="F16" s="234">
-        <v>607080263.83997297</v>
+        <v>645336660.99997306</v>
       </c>
       <c r="G16" s="234">
-        <v>1094526922.413702</v>
+        <v>1150015299.663296</v>
       </c>
       <c r="H16" s="111"/>
       <c r="I16" s="111"/>
@@ -6896,19 +6898,19 @@
         <v>122</v>
       </c>
       <c r="C17" s="234">
-        <v>69762134.505548999</v>
+        <v>71065918.306536004</v>
       </c>
       <c r="D17" s="234">
-        <v>10163923.380899999</v>
+        <v>11277436.9209</v>
       </c>
       <c r="E17" s="234">
-        <v>57507816.839057997</v>
+        <v>60965924.859052002</v>
       </c>
       <c r="F17" s="234">
         <v>23000000.5</v>
       </c>
       <c r="G17" s="234">
-        <v>160433875.22550699</v>
+        <v>166309280.58648801</v>
       </c>
       <c r="H17" s="111"/>
       <c r="I17" s="111"/>
@@ -6925,16 +6927,16 @@
         <v>8992270</v>
       </c>
       <c r="D18" s="234">
-        <v>101908649.17565399</v>
+        <v>103233876.372637</v>
       </c>
       <c r="E18" s="234">
-        <v>45427362</v>
+        <v>46059402</v>
       </c>
       <c r="F18" s="234">
-        <v>78205407.060000002</v>
+        <v>83394596.359999999</v>
       </c>
       <c r="G18" s="234">
-        <v>234533688.235654</v>
+        <v>241680144.73263699</v>
       </c>
       <c r="H18" s="111"/>
       <c r="I18" s="111"/>
@@ -6948,7 +6950,7 @@
         <v>169</v>
       </c>
       <c r="C19" s="234">
-        <v>61062267.460000001</v>
+        <v>30253778.960000001</v>
       </c>
       <c r="D19" s="234" t="s">
         <v>165</v>
@@ -6960,7 +6962,7 @@
         <v>4684684.5599999996</v>
       </c>
       <c r="G19" s="234">
-        <v>65746952.020000003</v>
+        <v>34938463.520000003</v>
       </c>
       <c r="H19" s="111"/>
       <c r="I19" s="111"/>
@@ -6974,7 +6976,7 @@
         <v>170</v>
       </c>
       <c r="C20" s="234">
-        <v>103678947.86</v>
+        <v>94308937.159999996</v>
       </c>
       <c r="D20" s="234" t="s">
         <v>165</v>
@@ -6986,7 +6988,7 @@
         <v>7921891.6799999997</v>
       </c>
       <c r="G20" s="234">
-        <v>111600839.54000001</v>
+        <v>102230828.84</v>
       </c>
       <c r="H20" s="111"/>
       <c r="I20" s="111"/>
@@ -7004,26 +7006,26 @@
         <v>124</v>
       </c>
       <c r="C21" s="234">
-        <v>152742305.07272601</v>
+        <v>158274692.538654</v>
       </c>
       <c r="D21" s="234">
-        <v>32800972.803474002</v>
+        <v>34764395.343473002</v>
       </c>
       <c r="E21" s="234">
-        <v>97627392.209875003</v>
+        <v>99808923.749874994</v>
       </c>
       <c r="F21" s="234">
-        <v>244186872.36991</v>
+        <v>252305457.80991</v>
       </c>
       <c r="G21" s="234">
-        <v>527357542.45598501</v>
+        <v>545153469.44191206</v>
       </c>
       <c r="H21" s="111"/>
       <c r="I21" s="111"/>
       <c r="J21" s="111"/>
       <c r="M21" s="14">
         <f>SUM(C33,C34)+M20</f>
-        <v>376485717.10283202</v>
+        <v>392950330.36262703</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>224</v>
@@ -7034,19 +7036,19 @@
         <v>125</v>
       </c>
       <c r="C22" s="234">
-        <v>143453221.699076</v>
+        <v>149448636.296076</v>
       </c>
       <c r="D22" s="234">
-        <v>41749093.869970001</v>
+        <v>42335012.789970003</v>
       </c>
       <c r="E22" s="234">
-        <v>109082163.58750001</v>
+        <v>118795902.36748999</v>
       </c>
       <c r="F22" s="234">
-        <v>189300211.47966999</v>
+        <v>201444355.70966101</v>
       </c>
       <c r="G22" s="234">
-        <v>483584690.63621598</v>
+        <v>512023907.16319698</v>
       </c>
       <c r="H22" s="111"/>
       <c r="I22" s="111"/>
@@ -7057,19 +7059,19 @@
         <v>126</v>
       </c>
       <c r="C23" s="234">
-        <v>276762050.17882401</v>
+        <v>293741906.22570401</v>
       </c>
       <c r="D23" s="234">
-        <v>35346659.494962998</v>
+        <v>36987838.754964001</v>
       </c>
       <c r="E23" s="234">
-        <v>123659802.999915</v>
+        <v>131777731.029908</v>
       </c>
       <c r="F23" s="234">
-        <v>346886126.43963599</v>
+        <v>360216667.15961599</v>
       </c>
       <c r="G23" s="234">
-        <v>782654639.11333799</v>
+        <v>822724143.170192</v>
       </c>
       <c r="H23" s="111"/>
       <c r="I23" s="111"/>
@@ -7080,19 +7082,19 @@
         <v>225</v>
       </c>
       <c r="C24" s="234">
-        <v>115644192.418262</v>
+        <v>136777627.932459</v>
       </c>
       <c r="D24" s="234">
-        <v>29527747.859962001</v>
+        <v>30034247.859962001</v>
       </c>
       <c r="E24" s="234">
-        <v>96494351.178264007</v>
+        <v>111081018.17824399</v>
       </c>
       <c r="F24" s="234">
-        <v>28644143.870000001</v>
+        <v>28674143.870000001</v>
       </c>
       <c r="G24" s="234">
-        <v>270310435.32648802</v>
+        <v>306567037.84066498</v>
       </c>
       <c r="H24" s="111"/>
       <c r="I24" s="111"/>
@@ -7103,19 +7105,19 @@
         <v>220</v>
       </c>
       <c r="C25" s="234">
-        <v>177146201.091674</v>
+        <v>189050468.946652</v>
       </c>
       <c r="D25" s="234">
-        <v>59546904.781634003</v>
+        <v>60319548.956625998</v>
       </c>
       <c r="E25" s="234">
-        <v>63015076.846628003</v>
+        <v>65683779.564621001</v>
       </c>
       <c r="F25" s="234">
         <v>20000000.43</v>
       </c>
       <c r="G25" s="234">
-        <v>319708183.14993602</v>
+        <v>335053797.89789897</v>
       </c>
       <c r="H25" s="111"/>
       <c r="I25" s="111"/>
@@ -7126,19 +7128,19 @@
         <v>127</v>
       </c>
       <c r="C26" s="234">
-        <v>279359725.396097</v>
+        <v>299809425.396097</v>
       </c>
       <c r="D26" s="234">
-        <v>163050689.06803399</v>
+        <v>167667121.467994</v>
       </c>
       <c r="E26" s="234">
-        <v>197107299.82678801</v>
+        <v>207404010.08629799</v>
       </c>
       <c r="F26" s="234">
-        <v>9343459.6473999992</v>
+        <v>14154270.5474</v>
       </c>
       <c r="G26" s="234">
-        <v>648861173.93831897</v>
+        <v>689034827.49778903</v>
       </c>
       <c r="H26" s="111"/>
       <c r="I26" s="111"/>
@@ -7181,7 +7183,7 @@
         <v>131</v>
       </c>
       <c r="C31" s="234">
-        <v>114868579.59551699</v>
+        <v>131326817.995389</v>
       </c>
       <c r="G31" s="111"/>
       <c r="H31" s="111"/>
@@ -7192,7 +7194,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="234">
-        <v>95938067.129668996</v>
+        <v>97328112.229664996</v>
       </c>
       <c r="G32" s="111"/>
       <c r="H32" s="111"/>
@@ -7203,7 +7205,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="234">
-        <v>89213406.129920006</v>
+        <v>92572379.469917998</v>
       </c>
       <c r="G33" s="111"/>
       <c r="H33" s="111"/>
@@ -7214,7 +7216,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="234">
-        <v>287272310.97291201</v>
+        <v>300377950.89270902</v>
       </c>
       <c r="G34" s="111"/>
       <c r="H34" s="111"/>
@@ -7259,17 +7261,17 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="259" t="s">
         <v>228</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="260"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
       <c r="F40" s="174">
         <f ca="1">IF(MONTH(TODAY())=9,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;9,1,0))</f>
-        <v>0.53333333333333333</v>
+        <v>0.56666666666666665</v>
       </c>
       <c r="G40" s="192" t="s">
         <v>187</v>
@@ -7356,35 +7358,35 @@
       </c>
       <c r="E42" s="46">
         <f>H65</f>
-        <v>2144476285.8990748</v>
+        <v>2235980335.6186624</v>
       </c>
       <c r="F42" s="176">
         <f>IFERROR(E42/D42,0)</f>
-        <v>0.47530540452972941</v>
+        <v>0.49558651915620466</v>
       </c>
       <c r="G42" s="184">
         <f>D42*$H$40-E42</f>
-        <v>2367309747.8003216</v>
+        <v>2275805698.0807338</v>
       </c>
       <c r="H42" s="184">
         <f ca="1">IFERROR(G42/$C$3,0)</f>
-        <v>182100749.83079398</v>
+        <v>189650474.84006116</v>
       </c>
       <c r="I42" s="204">
         <f>D42*$J$40-E42</f>
-        <v>2367309747.8003216</v>
+        <v>2275805698.0807338</v>
       </c>
       <c r="J42" s="204">
         <f ca="1">IFERROR(I42/$C$3,0)</f>
-        <v>182100749.83079398</v>
+        <v>189650474.84006116</v>
       </c>
       <c r="K42" s="185">
         <f>D42*$L$40-E42</f>
-        <v>2367309747.8003216</v>
+        <v>2275805698.0807338</v>
       </c>
       <c r="L42" s="185">
         <f ca="1">IFERROR(K42/$C$3,0)</f>
-        <v>182100749.83079398</v>
+        <v>189650474.84006116</v>
       </c>
       <c r="S42" s="173">
         <v>0.8</v>
@@ -7403,35 +7405,35 @@
       </c>
       <c r="E43" s="46">
         <f>I65</f>
-        <v>632927289.01191401</v>
+        <v>650631730.53382707</v>
       </c>
       <c r="F43" s="176">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.45165046134838788</v>
+        <v>0.46428417033851654</v>
       </c>
       <c r="G43" s="184">
         <f>D43*$H$40-E43</f>
-        <v>768438021.50350094</v>
+        <v>750733579.98158789</v>
       </c>
       <c r="H43" s="184">
         <f ca="1">IFERROR(G43/$C$3,0)</f>
-        <v>59110617.038730845</v>
+        <v>62561131.665132321</v>
       </c>
       <c r="I43" s="204">
         <f>D43*$J$40-E43</f>
-        <v>768438021.50350094</v>
+        <v>750733579.98158789</v>
       </c>
       <c r="J43" s="204">
         <f ca="1">IFERROR(I43/$C$3,0)</f>
-        <v>59110617.038730845</v>
+        <v>62561131.665132321</v>
       </c>
       <c r="K43" s="185">
         <f>D43*$L$40-E43</f>
-        <v>768438021.50350094</v>
+        <v>750733579.98158789</v>
       </c>
       <c r="L43" s="185">
         <f ca="1">IFERROR(K43/$C$3,0)</f>
-        <v>59110617.038730845</v>
+        <v>62561131.665132321</v>
       </c>
       <c r="S43" s="173">
         <v>0.85</v>
@@ -7450,35 +7452,35 @@
       </c>
       <c r="E44" s="46">
         <f>J65</f>
-        <v>1597083627.5301979</v>
+        <v>1655562860.1776679</v>
       </c>
       <c r="F44" s="176">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.5423376556392896</v>
+        <v>0.56219603336660984</v>
       </c>
       <c r="G44" s="184">
         <f>IF(D44=0,0,D44*$H$40-E44)</f>
-        <v>1347730568.7984874</v>
+        <v>1289251336.1510174</v>
       </c>
       <c r="H44" s="184">
         <f ca="1">IFERROR(G44/$C$3,0)</f>
-        <v>103671582.21526827</v>
+        <v>107437611.34591812</v>
       </c>
       <c r="I44" s="204">
         <f>IF(D44=0,0,D44*$J$40-E44)</f>
-        <v>1347730568.7984874</v>
+        <v>1289251336.1510174</v>
       </c>
       <c r="J44" s="204">
         <f ca="1">IFERROR(I44/$C$3,0)</f>
-        <v>103671582.21526827</v>
+        <v>107437611.34591812</v>
       </c>
       <c r="K44" s="185">
         <f>IF(D44=0,0,D44*$L$40-E44)</f>
-        <v>1347730568.7984874</v>
+        <v>1289251336.1510174</v>
       </c>
       <c r="L44" s="185">
         <f ca="1">IFERROR(K44/$C$3,0)</f>
-        <v>103671582.21526827</v>
+        <v>107437611.34591812</v>
       </c>
       <c r="S44" s="173">
         <v>0.9</v>
@@ -7497,35 +7499,35 @@
       </c>
       <c r="E45" s="46">
         <f>E74</f>
-        <v>587292363.82801795</v>
+        <v>621605260.58768106</v>
       </c>
       <c r="F45" s="176">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.33744182273736972</v>
+        <v>0.35715705681688276</v>
       </c>
       <c r="G45" s="184">
         <f>D45*$H$40-E45</f>
-        <v>1153133168.0868757</v>
+        <v>1118820271.3272126</v>
       </c>
       <c r="H45" s="184">
         <f ca="1">IFERROR(G45/$C$3,0)</f>
-        <v>88702551.39129813</v>
+        <v>93235022.610601053</v>
       </c>
       <c r="I45" s="204">
         <f>D45*$J$40-E45</f>
-        <v>1153133168.0868757</v>
+        <v>1118820271.3272126</v>
       </c>
       <c r="J45" s="204">
         <f ca="1">IFERROR(I45/$C$3,0)</f>
-        <v>88702551.39129813</v>
+        <v>93235022.610601053</v>
       </c>
       <c r="K45" s="185">
         <f>D45*$L$40-E45</f>
-        <v>1153133168.0868757</v>
+        <v>1118820271.3272126</v>
       </c>
       <c r="L45" s="185">
         <f ca="1">IFERROR(K45/$C$3,0)</f>
-        <v>88702551.39129813</v>
+        <v>93235022.610601053</v>
       </c>
       <c r="S45" s="173">
         <v>0.95</v>
@@ -7542,35 +7544,35 @@
       </c>
       <c r="E46" s="47">
         <f>SUM(E42:E45)</f>
-        <v>4961779566.2692051</v>
+        <v>5163780186.9178381</v>
       </c>
       <c r="F46" s="177">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.46816347239376555</v>
+        <v>0.48722302768547049</v>
       </c>
       <c r="G46" s="181">
         <f>SUM(G42:G45)</f>
-        <v>5636611506.1891861</v>
+        <v>5434610885.5405512</v>
       </c>
       <c r="H46" s="181">
         <f ca="1">IFERROR(G46/$C$3,0)</f>
-        <v>433585500.47609127</v>
+        <v>452884240.4617126</v>
       </c>
       <c r="I46" s="186">
         <f>SUM(I42:I45)</f>
-        <v>5636611506.1891861</v>
+        <v>5434610885.5405512</v>
       </c>
       <c r="J46" s="186">
         <f ca="1">IFERROR(I46/$C$3,0)</f>
-        <v>433585500.47609127</v>
+        <v>452884240.4617126</v>
       </c>
       <c r="K46" s="186">
         <f>SUM(K42:K45)</f>
-        <v>5636611506.1891861</v>
+        <v>5434610885.5405512</v>
       </c>
       <c r="L46" s="186">
         <f ca="1">IFERROR(K46/$C$3,0)</f>
-        <v>433585500.47609127</v>
+        <v>452884240.4617126</v>
       </c>
       <c r="S46" s="173">
         <v>1</v>
@@ -7583,33 +7585,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="263"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="270"/>
+      <c r="Q48" s="270"/>
+      <c r="R48" s="271"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -7618,49 +7620,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="268"/>
+      <c r="C50" s="268"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -7685,13 +7687,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="273"/>
+      <c r="N50" s="273"/>
+      <c r="O50" s="275"/>
+      <c r="P50" s="275"/>
+      <c r="Q50" s="277"/>
+      <c r="R50" s="277"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -7724,47 +7726,47 @@
       </c>
       <c r="H51" s="114">
         <f>SUMIF($B$10:$B$26,$T51,C$10:C$26)+SUMIF($B$10:$B$26,$U51,C$10:C$26)</f>
-        <v>152742305.07272601</v>
+        <v>158274692.538654</v>
       </c>
       <c r="I51" s="114">
         <f t="shared" ref="I51:I64" si="1">SUMIF($B$10:$B$26,$T51,D$10:D$26)+SUMIF($B$10:$B$26,$U51,D$10:D$26)</f>
-        <v>32800972.803474002</v>
+        <v>34764395.343473002</v>
       </c>
       <c r="J51" s="114">
         <f t="shared" ref="J51:J64" si="2">SUMIF($B$10:$B$26,$T51,E$10:E$26)+SUMIF($B$10:$B$26,$U51,E$10:E$26)</f>
-        <v>97627392.209875003</v>
+        <v>99808923.749874994</v>
       </c>
       <c r="K51" s="114">
         <f t="shared" ref="K51:K64" si="3">SUM(H51:J51)</f>
-        <v>283170670.08607501</v>
+        <v>292848011.632002</v>
       </c>
       <c r="L51" s="187">
         <f t="shared" ref="L51:L65" si="4">IFERROR(K51/G51,0)</f>
-        <v>0.55052206668956483</v>
+        <v>0.56933612700981306</v>
       </c>
       <c r="M51" s="184">
         <f t="shared" ref="M51:M64" si="5">G51*$H$40-K51</f>
-        <v>231196849.80073959</v>
+        <v>221519508.2548126</v>
       </c>
       <c r="N51" s="184">
         <f t="shared" ref="N51:N65" ca="1" si="6">IFERROR(M51/$C$3,0)</f>
-        <v>17784373.061595354</v>
+        <v>18459959.021234382</v>
       </c>
       <c r="O51" s="180">
         <f t="shared" ref="O51:O64" si="7">G51*$J$40-K51</f>
-        <v>231196849.80073959</v>
+        <v>221519508.2548126</v>
       </c>
       <c r="P51" s="180">
         <f t="shared" ref="P51:P65" ca="1" si="8">IFERROR(O51/$C$3,0)</f>
-        <v>17784373.061595354</v>
+        <v>18459959.021234382</v>
       </c>
       <c r="Q51" s="185">
         <f t="shared" ref="Q51:Q64" si="9">G51*$L$40-K51</f>
-        <v>231196849.80073959</v>
+        <v>221519508.2548126</v>
       </c>
       <c r="R51" s="185">
         <f t="shared" ref="R51:R65" ca="1" si="10">IFERROR(Q51/$C$3,0)</f>
-        <v>17784373.061595354</v>
+        <v>18459959.021234382</v>
       </c>
       <c r="T51" t="s">
         <v>124</v>
@@ -7798,47 +7800,47 @@
       </c>
       <c r="H52" s="114">
         <f t="shared" ref="H52:H64" si="11">SUMIF($B$10:$B$26,$T52,C$10:C$26)+SUMIF($B$10:$B$26,$U52,C$10:C$26)</f>
-        <v>121721995.161603</v>
+        <v>134931055.38160199</v>
       </c>
       <c r="I52" s="114">
         <f t="shared" si="1"/>
-        <v>67385948.651455998</v>
+        <v>67358930.621457994</v>
       </c>
       <c r="J52" s="114">
         <f t="shared" si="2"/>
-        <v>219409066.74943</v>
+        <v>219813751.42943999</v>
       </c>
       <c r="K52" s="114">
         <f t="shared" si="3"/>
-        <v>408517010.56248903</v>
+        <v>422103737.4325</v>
       </c>
       <c r="L52" s="187">
         <f t="shared" si="4"/>
-        <v>0.52005676749627883</v>
+        <v>0.53735315681221862</v>
       </c>
       <c r="M52" s="184">
         <f t="shared" si="5"/>
-        <v>377006870.85765254</v>
+        <v>363420143.98764157</v>
       </c>
       <c r="N52" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>29000528.527511735</v>
+        <v>30285011.998970132</v>
       </c>
       <c r="O52" s="180">
         <f t="shared" si="7"/>
-        <v>377006870.85765254</v>
+        <v>363420143.98764157</v>
       </c>
       <c r="P52" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>29000528.527511735</v>
+        <v>30285011.998970132</v>
       </c>
       <c r="Q52" s="185">
         <f t="shared" si="9"/>
-        <v>377006870.85765254</v>
+        <v>363420143.98764157</v>
       </c>
       <c r="R52" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>29000528.527511735</v>
+        <v>30285011.998970132</v>
       </c>
       <c r="T52" t="s">
         <v>70</v>
@@ -7872,7 +7874,7 @@
       </c>
       <c r="H53" s="114">
         <f t="shared" si="11"/>
-        <v>61062267.460000001</v>
+        <v>30253778.960000001</v>
       </c>
       <c r="I53" s="114">
         <f t="shared" si="1"/>
@@ -7884,35 +7886,35 @@
       </c>
       <c r="K53" s="114">
         <f t="shared" si="3"/>
-        <v>61062267.460000001</v>
+        <v>30253778.960000001</v>
       </c>
       <c r="L53" s="187">
         <f t="shared" si="4"/>
-        <v>0.23221732804930298</v>
+        <v>0.11505389507665395</v>
       </c>
       <c r="M53" s="184">
         <f t="shared" si="5"/>
-        <v>201890837.60301074</v>
+        <v>232699326.10301074</v>
       </c>
       <c r="N53" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>15530064.431000827</v>
+        <v>19391610.508584227</v>
       </c>
       <c r="O53" s="180">
         <f t="shared" si="7"/>
-        <v>201890837.60301074</v>
+        <v>232699326.10301074</v>
       </c>
       <c r="P53" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>15530064.431000827</v>
+        <v>19391610.508584227</v>
       </c>
       <c r="Q53" s="185">
         <f t="shared" si="9"/>
-        <v>201890837.60301074</v>
+        <v>232699326.10301074</v>
       </c>
       <c r="R53" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>15530064.431000827</v>
+        <v>19391610.508584227</v>
       </c>
       <c r="T53" t="s">
         <v>169</v>
@@ -7946,47 +7948,47 @@
       </c>
       <c r="H54" s="114">
         <f t="shared" si="11"/>
-        <v>266514368.66966501</v>
+        <v>292379540.899665</v>
       </c>
       <c r="I54" s="114">
         <f t="shared" si="1"/>
-        <v>23592531.925912</v>
+        <v>24047531.925912</v>
       </c>
       <c r="J54" s="114">
         <f t="shared" si="2"/>
-        <v>92544959.589921996</v>
+        <v>96084216.349922001</v>
       </c>
       <c r="K54" s="114">
         <f t="shared" si="3"/>
-        <v>382651860.18549901</v>
+        <v>412511289.17549902</v>
       </c>
       <c r="L54" s="187">
         <f t="shared" si="4"/>
-        <v>0.52658140244196294</v>
+        <v>0.56767206899732248</v>
       </c>
       <c r="M54" s="184">
         <f t="shared" si="5"/>
-        <v>344019948.60036653</v>
+        <v>314160519.61036652</v>
       </c>
       <c r="N54" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>26463072.969258964</v>
+        <v>26180043.300863877</v>
       </c>
       <c r="O54" s="180">
         <f t="shared" si="7"/>
-        <v>344019948.60036653</v>
+        <v>314160519.61036652</v>
       </c>
       <c r="P54" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>26463072.969258964</v>
+        <v>26180043.300863877</v>
       </c>
       <c r="Q54" s="185">
         <f t="shared" si="9"/>
-        <v>344019948.60036653</v>
+        <v>314160519.61036652</v>
       </c>
       <c r="R54" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>26463072.969258964</v>
+        <v>26180043.300863877</v>
       </c>
       <c r="T54" t="s">
         <v>115</v>
@@ -8044,7 +8046,7 @@
       </c>
       <c r="N55" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>26453009.58087597</v>
+        <v>28657427.045948967</v>
       </c>
       <c r="O55" s="180">
         <f t="shared" si="7"/>
@@ -8052,7 +8054,7 @@
       </c>
       <c r="P55" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>26453009.58087597</v>
+        <v>28657427.045948967</v>
       </c>
       <c r="Q55" s="185">
         <f t="shared" si="9"/>
@@ -8060,7 +8062,7 @@
       </c>
       <c r="R55" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>26453009.58087597</v>
+        <v>28657427.045948967</v>
       </c>
       <c r="T55" t="s">
         <v>182</v>
@@ -8094,47 +8096,47 @@
       </c>
       <c r="H56" s="114">
         <f t="shared" si="11"/>
-        <v>115644192.418262</v>
+        <v>136777627.932459</v>
       </c>
       <c r="I56" s="114">
         <f t="shared" si="1"/>
-        <v>29527747.859962001</v>
+        <v>30034247.859962001</v>
       </c>
       <c r="J56" s="114">
         <f t="shared" si="2"/>
-        <v>96494351.178264007</v>
+        <v>111081018.17824399</v>
       </c>
       <c r="K56" s="114">
         <f t="shared" si="3"/>
-        <v>241666291.45648801</v>
+        <v>277892893.97066498</v>
       </c>
       <c r="L56" s="187">
         <f t="shared" si="4"/>
-        <v>0.42032868528553308</v>
+        <v>0.48333739086616728</v>
       </c>
       <c r="M56" s="184">
         <f t="shared" si="5"/>
-        <v>333279697.04373038</v>
+        <v>297053094.52955341</v>
       </c>
       <c r="N56" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>25636899.772594646</v>
+        <v>24754424.54412945</v>
       </c>
       <c r="O56" s="180">
         <f t="shared" si="7"/>
-        <v>333279697.04373038</v>
+        <v>297053094.52955341</v>
       </c>
       <c r="P56" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>25636899.772594646</v>
+        <v>24754424.54412945</v>
       </c>
       <c r="Q56" s="185">
         <f t="shared" si="9"/>
-        <v>333279697.04373038</v>
+        <v>297053094.52955341</v>
       </c>
       <c r="R56" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>25636899.772594646</v>
+        <v>24754424.54412945</v>
       </c>
       <c r="T56" t="s">
         <v>225</v>
@@ -8168,47 +8170,47 @@
       </c>
       <c r="H57" s="114">
         <f t="shared" si="11"/>
-        <v>265775234.204144</v>
+        <v>278713205.39376199</v>
       </c>
       <c r="I57" s="114">
         <f t="shared" si="1"/>
-        <v>25660116.839954998</v>
+        <v>27681738.359931</v>
       </c>
       <c r="J57" s="114">
         <f t="shared" si="2"/>
-        <v>196011307.52963001</v>
+        <v>198283694.90963</v>
       </c>
       <c r="K57" s="114">
         <f t="shared" si="3"/>
-        <v>487446658.57372898</v>
+        <v>504678638.66332299</v>
       </c>
       <c r="L57" s="187">
         <f t="shared" si="4"/>
-        <v>0.43946417346260885</v>
+        <v>0.45499989979081001</v>
       </c>
       <c r="M57" s="184">
         <f t="shared" si="5"/>
-        <v>621737406.95101762</v>
+        <v>604505426.86142373</v>
       </c>
       <c r="N57" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>47825954.380847506</v>
+        <v>50375452.23845198</v>
       </c>
       <c r="O57" s="180">
         <f t="shared" si="7"/>
-        <v>621737406.95101762</v>
+        <v>604505426.86142373</v>
       </c>
       <c r="P57" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>47825954.380847506</v>
+        <v>50375452.23845198</v>
       </c>
       <c r="Q57" s="185">
         <f t="shared" si="9"/>
-        <v>621737406.95101762</v>
+        <v>604505426.86142373</v>
       </c>
       <c r="R57" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>47825954.380847506</v>
+        <v>50375452.23845198</v>
       </c>
       <c r="T57" t="s">
         <v>120</v>
@@ -8242,47 +8244,47 @@
       </c>
       <c r="H58" s="114">
         <f t="shared" si="11"/>
-        <v>143453221.699076</v>
+        <v>149448636.296076</v>
       </c>
       <c r="I58" s="114">
         <f t="shared" si="1"/>
-        <v>41749093.869970001</v>
+        <v>42335012.789970003</v>
       </c>
       <c r="J58" s="114">
         <f t="shared" si="2"/>
-        <v>109082163.58750001</v>
+        <v>118795902.36748999</v>
       </c>
       <c r="K58" s="114">
         <f t="shared" si="3"/>
-        <v>294284479.156546</v>
+        <v>310579551.45353603</v>
       </c>
       <c r="L58" s="187">
         <f t="shared" si="4"/>
-        <v>0.47883768180382491</v>
+        <v>0.50535180400924973</v>
       </c>
       <c r="M58" s="184">
         <f t="shared" si="5"/>
-        <v>320296391.0204829</v>
+        <v>304001318.72349286</v>
       </c>
       <c r="N58" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>24638183.924652532</v>
+        <v>25333443.226957738</v>
       </c>
       <c r="O58" s="180">
         <f t="shared" si="7"/>
-        <v>320296391.0204829</v>
+        <v>304001318.72349286</v>
       </c>
       <c r="P58" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>24638183.924652532</v>
+        <v>25333443.226957738</v>
       </c>
       <c r="Q58" s="185">
         <f t="shared" si="9"/>
-        <v>320296391.0204829</v>
+        <v>304001318.72349286</v>
       </c>
       <c r="R58" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>24638183.924652532</v>
+        <v>25333443.226957738</v>
       </c>
       <c r="T58" t="s">
         <v>125</v>
@@ -8316,7 +8318,7 @@
       </c>
       <c r="H59" s="114">
         <f t="shared" si="11"/>
-        <v>103678947.86</v>
+        <v>94308937.159999996</v>
       </c>
       <c r="I59" s="114">
         <f t="shared" si="1"/>
@@ -8328,35 +8330,35 @@
       </c>
       <c r="K59" s="114">
         <f t="shared" si="3"/>
-        <v>103678947.86</v>
+        <v>94308937.159999996</v>
       </c>
       <c r="L59" s="187">
         <f t="shared" si="4"/>
-        <v>0.23359178793370819</v>
+        <v>0.21248087199996912</v>
       </c>
       <c r="M59" s="184">
         <f t="shared" si="5"/>
-        <v>340167767.71641999</v>
+        <v>349537778.41641998</v>
       </c>
       <c r="N59" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>26166751.362801537</v>
+        <v>29128148.201368332</v>
       </c>
       <c r="O59" s="180">
         <f t="shared" si="7"/>
-        <v>340167767.71641999</v>
+        <v>349537778.41641998</v>
       </c>
       <c r="P59" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>26166751.362801537</v>
+        <v>29128148.201368332</v>
       </c>
       <c r="Q59" s="185">
         <f t="shared" si="9"/>
-        <v>340167767.71641999</v>
+        <v>349537778.41641998</v>
       </c>
       <c r="R59" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>26166751.362801537</v>
+        <v>29128148.201368332</v>
       </c>
       <c r="T59" t="s">
         <v>170</v>
@@ -8390,47 +8392,47 @@
       </c>
       <c r="H60" s="114">
         <f t="shared" si="11"/>
-        <v>177146201.091674</v>
+        <v>189050468.946652</v>
       </c>
       <c r="I60" s="114">
         <f t="shared" si="1"/>
-        <v>59546904.781634003</v>
+        <v>60319548.956625998</v>
       </c>
       <c r="J60" s="114">
         <f t="shared" si="2"/>
-        <v>63015076.846628003</v>
+        <v>65683779.564621001</v>
       </c>
       <c r="K60" s="114">
         <f t="shared" si="3"/>
-        <v>299708182.71993601</v>
+        <v>315053797.46789896</v>
       </c>
       <c r="L60" s="187">
         <f t="shared" si="4"/>
-        <v>0.5174642946924497</v>
+        <v>0.54395942619040094</v>
       </c>
       <c r="M60" s="184">
         <f t="shared" si="5"/>
-        <v>279478025.4764477</v>
+        <v>264132410.72848475</v>
       </c>
       <c r="N60" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>21498309.652034439</v>
+        <v>22011034.22737373</v>
       </c>
       <c r="O60" s="180">
         <f t="shared" si="7"/>
-        <v>279478025.4764477</v>
+        <v>264132410.72848475</v>
       </c>
       <c r="P60" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>21498309.652034439</v>
+        <v>22011034.22737373</v>
       </c>
       <c r="Q60" s="185">
         <f t="shared" si="9"/>
-        <v>279478025.4764477</v>
+        <v>264132410.72848475</v>
       </c>
       <c r="R60" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>21498309.652034439</v>
+        <v>22011034.22737373</v>
       </c>
       <c r="T60" t="s">
         <v>220</v>
@@ -8464,47 +8466,47 @@
       </c>
       <c r="H61" s="114">
         <f t="shared" si="11"/>
-        <v>276762050.17882401</v>
+        <v>293741906.22570401</v>
       </c>
       <c r="I61" s="114">
         <f t="shared" si="1"/>
-        <v>35346659.494962998</v>
+        <v>36987838.754964001</v>
       </c>
       <c r="J61" s="114">
         <f t="shared" si="2"/>
-        <v>123659802.999915</v>
+        <v>131777731.029908</v>
       </c>
       <c r="K61" s="114">
         <f t="shared" si="3"/>
-        <v>435768512.673702</v>
+        <v>462507476.01057601</v>
       </c>
       <c r="L61" s="187">
         <f t="shared" si="4"/>
-        <v>0.60811176407186063</v>
+        <v>0.64542579133939471</v>
       </c>
       <c r="M61" s="184">
         <f t="shared" si="5"/>
-        <v>280824288.87947953</v>
+        <v>254085325.54260552</v>
       </c>
       <c r="N61" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>21601868.375344578</v>
+        <v>21173777.128550459</v>
       </c>
       <c r="O61" s="180">
         <f t="shared" si="7"/>
-        <v>280824288.87947953</v>
+        <v>254085325.54260552</v>
       </c>
       <c r="P61" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>21601868.375344578</v>
+        <v>21173777.128550459</v>
       </c>
       <c r="Q61" s="185">
         <f t="shared" si="9"/>
-        <v>280824288.87947953</v>
+        <v>254085325.54260552</v>
       </c>
       <c r="R61" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>21601868.375344578</v>
+        <v>21173777.128550459</v>
       </c>
       <c r="T61" t="s">
         <v>126</v>
@@ -8538,47 +8540,47 @@
       </c>
       <c r="H62" s="114">
         <f t="shared" si="11"/>
-        <v>97687948.761456996</v>
+        <v>94059448.761456996</v>
       </c>
       <c r="I62" s="114">
         <f t="shared" si="1"/>
-        <v>25690735.559999999</v>
+        <v>28420735.559999999</v>
       </c>
       <c r="J62" s="114">
         <f t="shared" si="2"/>
-        <v>126561892.173888</v>
+        <v>127169369.653888</v>
       </c>
       <c r="K62" s="114">
         <f t="shared" si="3"/>
-        <v>249940576.495345</v>
+        <v>249649553.97534502</v>
       </c>
       <c r="L62" s="187">
         <f t="shared" si="4"/>
-        <v>0.52395888991531514</v>
+        <v>0.52334880955678476</v>
       </c>
       <c r="M62" s="184">
         <f t="shared" si="5"/>
-        <v>227082681.06545651</v>
+        <v>227373703.58545649</v>
       </c>
       <c r="N62" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>17467898.543496653</v>
+        <v>18947808.632121373</v>
       </c>
       <c r="O62" s="180">
         <f t="shared" si="7"/>
-        <v>227082681.06545651</v>
+        <v>227373703.58545649</v>
       </c>
       <c r="P62" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>17467898.543496653</v>
+        <v>18947808.632121373</v>
       </c>
       <c r="Q62" s="185">
         <f t="shared" si="9"/>
-        <v>227082681.06545651</v>
+        <v>227373703.58545649</v>
       </c>
       <c r="R62" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>17467898.543496653</v>
+        <v>18947808.632121373</v>
       </c>
       <c r="T62" t="s">
         <v>112</v>
@@ -8612,47 +8614,47 @@
       </c>
       <c r="H63" s="114">
         <f t="shared" si="11"/>
-        <v>279359725.396097</v>
+        <v>299809425.396097</v>
       </c>
       <c r="I63" s="114">
         <f t="shared" si="1"/>
-        <v>163050689.06803399</v>
+        <v>167667121.467994</v>
       </c>
       <c r="J63" s="114">
         <f t="shared" si="2"/>
-        <v>197107299.82678801</v>
+        <v>207404010.08629799</v>
       </c>
       <c r="K63" s="114">
         <f t="shared" si="3"/>
-        <v>639517714.29091907</v>
+        <v>674880556.95038903</v>
       </c>
       <c r="L63" s="187">
         <f t="shared" si="4"/>
-        <v>0.65325301392963253</v>
+        <v>0.6893753652456267</v>
       </c>
       <c r="M63" s="184">
         <f t="shared" si="5"/>
-        <v>339456283.00288749</v>
+        <v>304093440.34341753</v>
       </c>
       <c r="N63" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>26112021.769452885</v>
+        <v>25341120.028618127</v>
       </c>
       <c r="O63" s="180">
         <f t="shared" si="7"/>
-        <v>339456283.00288749</v>
+        <v>304093440.34341753</v>
       </c>
       <c r="P63" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>26112021.769452885</v>
+        <v>25341120.028618127</v>
       </c>
       <c r="Q63" s="185">
         <f t="shared" si="9"/>
-        <v>339456283.00288749</v>
+        <v>304093440.34341753</v>
       </c>
       <c r="R63" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>26112021.769452885</v>
+        <v>25341120.028618127</v>
       </c>
       <c r="T63" t="s">
         <v>127</v>
@@ -8686,47 +8688,47 @@
       </c>
       <c r="H64" s="114">
         <f t="shared" si="11"/>
-        <v>78754404.505548999</v>
+        <v>80058188.306536004</v>
       </c>
       <c r="I64" s="114">
         <f t="shared" si="1"/>
-        <v>112072572.55655399</v>
+        <v>114511313.29353701</v>
       </c>
       <c r="J64" s="114">
         <f t="shared" si="2"/>
-        <v>102935178.839058</v>
+        <v>107025326.859052</v>
       </c>
       <c r="K64" s="114">
         <f t="shared" si="3"/>
-        <v>293762155.90116096</v>
+        <v>301594828.45912504</v>
       </c>
       <c r="L64" s="187">
         <f t="shared" si="4"/>
-        <v>0.54713041573628007</v>
+        <v>0.56171872572406134</v>
       </c>
       <c r="M64" s="184">
         <f t="shared" si="5"/>
-        <v>243152165.53322983</v>
+        <v>235319492.97526574</v>
       </c>
       <c r="N64" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>18704012.73332537</v>
+        <v>19609957.747938812</v>
       </c>
       <c r="O64" s="180">
         <f t="shared" si="7"/>
-        <v>243152165.53322983</v>
+        <v>235319492.97526574</v>
       </c>
       <c r="P64" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>18704012.73332537</v>
+        <v>19609957.747938812</v>
       </c>
       <c r="Q64" s="185">
         <f t="shared" si="9"/>
-        <v>243152165.53322983</v>
+        <v>235319492.97526574</v>
       </c>
       <c r="R64" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>18704012.73332537</v>
+        <v>19609957.747938812</v>
       </c>
       <c r="T64" t="s">
         <v>122</v>
@@ -8758,47 +8760,47 @@
       </c>
       <c r="H65" s="135">
         <f t="shared" si="12"/>
-        <v>2144476285.8990748</v>
+        <v>2235980335.6186624</v>
       </c>
       <c r="I65" s="135">
         <f t="shared" si="12"/>
-        <v>632927289.01191401</v>
+        <v>650631730.53382707</v>
       </c>
       <c r="J65" s="135">
         <f t="shared" si="12"/>
-        <v>1597083627.5301979</v>
+        <v>1655562860.1776679</v>
       </c>
       <c r="K65" s="135">
         <f t="shared" si="12"/>
-        <v>4374487202.4411879</v>
+        <v>4542174926.3301563</v>
       </c>
       <c r="L65" s="189">
         <f t="shared" si="4"/>
-        <v>0.49384784603404358</v>
+        <v>0.5127785726350278</v>
       </c>
       <c r="M65" s="181">
         <f>SUM(M51:M64)</f>
-        <v>4483478338.1023083</v>
+        <v>4315790614.2133389</v>
       </c>
       <c r="N65" s="181">
         <f t="shared" ca="1" si="6"/>
-        <v>344882949.08479297</v>
+        <v>359649217.85111159</v>
       </c>
       <c r="O65" s="181">
         <f>SUM(O51:O64)</f>
-        <v>4483478338.1023083</v>
+        <v>4315790614.2133389</v>
       </c>
       <c r="P65" s="181">
         <f t="shared" ca="1" si="8"/>
-        <v>344882949.08479297</v>
+        <v>359649217.85111159</v>
       </c>
       <c r="Q65" s="186">
         <f>SUM(Q51:Q64)</f>
-        <v>4483478338.1023083</v>
+        <v>4315790614.2133389</v>
       </c>
       <c r="R65" s="186">
         <f t="shared" ca="1" si="10"/>
-        <v>344882949.08479297</v>
+        <v>359649217.85111159</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8807,21 +8809,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="283" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="260" t="s">
+      <c r="G67" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="270"/>
+      <c r="I67" s="270"/>
+      <c r="J67" s="270"/>
+      <c r="K67" s="270"/>
+      <c r="L67" s="271"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -8883,35 +8885,35 @@
       </c>
       <c r="E69" s="114">
         <f>IFERROR($C$31,0)</f>
-        <v>114868579.59551699</v>
+        <v>131326817.995389</v>
       </c>
       <c r="F69" s="187">
         <f t="shared" ref="F69:F74" si="13">IFERROR(E69/D69,0)</f>
-        <v>0.44825450226452579</v>
+        <v>0.5124798934730147</v>
       </c>
       <c r="G69" s="184">
         <f>D69*$H$40-E69</f>
-        <v>141388923.70944762</v>
+        <v>124930685.30957563</v>
       </c>
       <c r="H69" s="184">
         <f t="shared" ref="H69:H74" ca="1" si="14">IFERROR(G69/$C$3,0)</f>
-        <v>10876071.054572893</v>
+        <v>10410890.442464637</v>
       </c>
       <c r="I69" s="204">
         <f>D69*$J$40-E69</f>
-        <v>141388923.70944762</v>
+        <v>124930685.30957563</v>
       </c>
       <c r="J69" s="204">
         <f t="shared" ref="J69:J74" ca="1" si="15">IFERROR(I69/$C$3,0)</f>
-        <v>10876071.054572893</v>
+        <v>10410890.442464637</v>
       </c>
       <c r="K69" s="185">
         <f>D69*$L$40-E69</f>
-        <v>141388923.70944762</v>
+        <v>124930685.30957563</v>
       </c>
       <c r="L69" s="185">
         <f t="shared" ref="L69:L74" ca="1" si="16">IFERROR(K69/$C$3,0)</f>
-        <v>10876071.054572893</v>
+        <v>10410890.442464637</v>
       </c>
     </row>
     <row r="70" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8927,35 +8929,35 @@
       </c>
       <c r="E70" s="114">
         <f>IFERROR($C$32,0)</f>
-        <v>95938067.129668996</v>
+        <v>97328112.229664996</v>
       </c>
       <c r="F70" s="187">
         <f t="shared" si="13"/>
-        <v>0.24011024214513063</v>
+        <v>0.24358919555266156</v>
       </c>
       <c r="G70" s="184">
         <f>D70*$H$40-E70</f>
-        <v>303620345.17529559</v>
+        <v>302230300.07529962</v>
       </c>
       <c r="H70" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>23355411.167330429</v>
+        <v>25185858.3396083</v>
       </c>
       <c r="I70" s="204">
         <f>D70*$J$40-E70</f>
-        <v>303620345.17529559</v>
+        <v>302230300.07529962</v>
       </c>
       <c r="J70" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>23355411.167330429</v>
+        <v>25185858.3396083</v>
       </c>
       <c r="K70" s="185">
         <f>D70*$L$40-E70</f>
-        <v>303620345.17529559</v>
+        <v>302230300.07529962</v>
       </c>
       <c r="L70" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>23355411.167330429</v>
+        <v>25185858.3396083</v>
       </c>
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.25">
@@ -8971,35 +8973,35 @@
       </c>
       <c r="E71" s="114">
         <f>M21</f>
-        <v>376485717.10283202</v>
+        <v>392950330.36262703</v>
       </c>
       <c r="F71" s="187">
         <f t="shared" si="13"/>
-        <v>0.34711633701482308</v>
+        <v>0.36229655763271368</v>
       </c>
       <c r="G71" s="184">
         <f>D71*$H$40-E71</f>
-        <v>708123899.20213246</v>
+        <v>691659285.94233751</v>
       </c>
       <c r="H71" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>54471069.169394806</v>
+        <v>57638273.828528129</v>
       </c>
       <c r="I71" s="204">
         <f>D71*$J$40-E71</f>
-        <v>708123899.20213246</v>
+        <v>691659285.94233751</v>
       </c>
       <c r="J71" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>54471069.169394806</v>
+        <v>57638273.828528129</v>
       </c>
       <c r="K71" s="185">
         <f>D71*$L$40-E71</f>
-        <v>708123899.20213246</v>
+        <v>691659285.94233751</v>
       </c>
       <c r="L71" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>54471069.169394806</v>
+        <v>57638273.828528129</v>
       </c>
     </row>
     <row r="72" spans="2:21" hidden="1" x14ac:dyDescent="0.25">
@@ -9101,35 +9103,35 @@
       </c>
       <c r="E74" s="115">
         <f>SUM(E69:E73)</f>
-        <v>587292363.82801795</v>
+        <v>621605260.58768106</v>
       </c>
       <c r="F74" s="177">
         <f t="shared" si="13"/>
-        <v>0.33744182273736972</v>
+        <v>0.35715705681688276</v>
       </c>
       <c r="G74" s="181">
         <f>SUM(G69:G73)</f>
-        <v>1153133168.0868757</v>
+        <v>1118820271.3272128</v>
       </c>
       <c r="H74" s="181">
         <f t="shared" ca="1" si="14"/>
-        <v>88702551.39129813</v>
+        <v>93235022.610601068</v>
       </c>
       <c r="I74" s="186">
         <f>SUM(I69:I73)</f>
-        <v>1153133168.0868757</v>
+        <v>1118820271.3272128</v>
       </c>
       <c r="J74" s="186">
         <f t="shared" ca="1" si="15"/>
-        <v>88702551.39129813</v>
+        <v>93235022.610601068</v>
       </c>
       <c r="K74" s="186">
         <f>SUM(K69:K73)</f>
-        <v>1153133168.0868757</v>
+        <v>1118820271.3272128</v>
       </c>
       <c r="L74" s="186">
         <f t="shared" ca="1" si="16"/>
-        <v>88702551.39129813</v>
+        <v>93235022.610601068</v>
       </c>
     </row>
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9142,10 +9144,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -9174,7 +9176,7 @@
       </c>
       <c r="D80" s="131">
         <f>SUMIF($B$10:$B$26,$T80,$F$10:$F$26)+SUMIF($B$10:$B$26,$U80,$F$10:$F$26)</f>
-        <v>244186872.36991</v>
+        <v>252305457.80991</v>
       </c>
       <c r="T80" t="str">
         <f t="shared" ref="T80:U93" si="17">T51</f>
@@ -9194,7 +9196,7 @@
       </c>
       <c r="D81" s="132">
         <f t="shared" ref="D81:D93" si="18">SUMIF($B$10:$B$26,$T81,$F$10:$F$26)+SUMIF($B$10:$B$26,$U81,$F$10:$F$26)</f>
-        <v>89209424.960000008</v>
+        <v>89047262.789999992</v>
       </c>
       <c r="T81" t="str">
         <f t="shared" si="17"/>
@@ -9234,7 +9236,7 @@
       </c>
       <c r="D83" s="131">
         <f t="shared" si="18"/>
-        <v>221318157.41984001</v>
+        <v>247825364.82984</v>
       </c>
       <c r="T83" t="str">
         <f t="shared" si="17"/>
@@ -9274,7 +9276,7 @@
       </c>
       <c r="D85" s="131">
         <f t="shared" si="18"/>
-        <v>28644143.870000001</v>
+        <v>28674143.870000001</v>
       </c>
       <c r="T85" t="str">
         <f t="shared" si="17"/>
@@ -9294,7 +9296,7 @@
       </c>
       <c r="D86" s="132">
         <f t="shared" si="18"/>
-        <v>607080263.83997297</v>
+        <v>645336660.99997306</v>
       </c>
       <c r="T86" t="str">
         <f t="shared" si="17"/>
@@ -9314,7 +9316,7 @@
       </c>
       <c r="D87" s="131">
         <f t="shared" si="18"/>
-        <v>189300211.47966999</v>
+        <v>201444355.70966101</v>
       </c>
       <c r="T87" t="str">
         <f t="shared" si="17"/>
@@ -9374,7 +9376,7 @@
       </c>
       <c r="D90" s="131">
         <f t="shared" si="18"/>
-        <v>346886126.43963599</v>
+        <v>360216667.15961599</v>
       </c>
       <c r="T90" t="str">
         <f t="shared" si="17"/>
@@ -9394,7 +9396,7 @@
       </c>
       <c r="D91" s="132">
         <f t="shared" si="18"/>
-        <v>89910108.649957001</v>
+        <v>97531730.539957002</v>
       </c>
       <c r="T91" t="str">
         <f t="shared" si="17"/>
@@ -9414,7 +9416,7 @@
       </c>
       <c r="D92" s="131">
         <f t="shared" si="18"/>
-        <v>9343459.6473999992</v>
+        <v>14154270.5474</v>
       </c>
       <c r="T92" t="str">
         <f t="shared" si="17"/>
@@ -9434,7 +9436,7 @@
       </c>
       <c r="D93" s="132">
         <f t="shared" si="18"/>
-        <v>101205407.56</v>
+        <v>106394596.86</v>
       </c>
       <c r="T93" t="str">
         <f t="shared" si="17"/>
@@ -9452,18 +9454,12 @@
       <c r="C94" s="58"/>
       <c r="D94" s="120">
         <f>SUM(D80:D93)</f>
-        <v>1959690752.9063859</v>
+        <v>2075537087.7863572</v>
       </c>
     </row>
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -9478,6 +9474,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -10105,11 +10107,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="259" t="s">
         <v>163</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="260"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -10429,33 +10431,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="263"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="270"/>
+      <c r="Q48" s="270"/>
+      <c r="R48" s="271"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -10464,49 +10466,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="268"/>
+      <c r="C50" s="268"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -10531,13 +10533,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="273"/>
+      <c r="N50" s="273"/>
+      <c r="O50" s="275"/>
+      <c r="P50" s="275"/>
+      <c r="Q50" s="277"/>
+      <c r="R50" s="277"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -11653,21 +11655,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="283" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="260" t="s">
+      <c r="G67" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="270"/>
+      <c r="I67" s="270"/>
+      <c r="J67" s="270"/>
+      <c r="K67" s="270"/>
+      <c r="L67" s="271"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -11988,10 +11990,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -12304,12 +12306,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -12324,6 +12320,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -12951,11 +12953,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="259" t="s">
         <v>175</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="260"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -13275,33 +13277,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="263"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="270"/>
+      <c r="Q48" s="270"/>
+      <c r="R48" s="271"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -13310,49 +13312,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="268"/>
+      <c r="C50" s="268"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -13377,13 +13379,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="273"/>
+      <c r="N50" s="273"/>
+      <c r="O50" s="275"/>
+      <c r="P50" s="275"/>
+      <c r="Q50" s="277"/>
+      <c r="R50" s="277"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -14499,21 +14501,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="283" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="260" t="s">
+      <c r="G67" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="270"/>
+      <c r="I67" s="270"/>
+      <c r="J67" s="270"/>
+      <c r="K67" s="270"/>
+      <c r="L67" s="271"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -14834,10 +14836,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -15150,12 +15152,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -15170,6 +15166,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -15797,11 +15799,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="259" t="s">
         <v>177</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="260"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -16121,33 +16123,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="263"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="270"/>
+      <c r="Q48" s="270"/>
+      <c r="R48" s="271"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -16156,49 +16158,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="268"/>
+      <c r="C50" s="268"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -16223,13 +16225,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="273"/>
+      <c r="N50" s="273"/>
+      <c r="O50" s="275"/>
+      <c r="P50" s="275"/>
+      <c r="Q50" s="277"/>
+      <c r="R50" s="277"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -17331,21 +17333,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="283" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="260" t="s">
+      <c r="G67" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="270"/>
+      <c r="I67" s="270"/>
+      <c r="J67" s="270"/>
+      <c r="K67" s="270"/>
+      <c r="L67" s="271"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -17666,10 +17668,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -17982,12 +17984,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -18002,6 +17998,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -25781,11 +25783,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="269" t="s">
+      <c r="B41" s="259" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="270"/>
-      <c r="D41" s="271"/>
+      <c r="C41" s="260"/>
+      <c r="D41" s="261"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -26056,59 +26058,59 @@
       </c>
     </row>
     <row r="48" spans="2:19" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="261"/>
-      <c r="M48" s="261"/>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
+      <c r="L48" s="270"/>
+      <c r="M48" s="270"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="271"/>
       <c r="Q48"/>
       <c r="R48"/>
     </row>
     <row r="49" spans="2:18" s="139" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="277" t="s">
+      <c r="B49" s="267" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="277" t="s">
+      <c r="C49" s="267" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="274" t="s">
+      <c r="D49" s="264" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
+      <c r="E49" s="265"/>
+      <c r="F49" s="266"/>
       <c r="G49" s="140" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="140"/>
       <c r="I49" s="140"/>
-      <c r="J49" s="274" t="s">
+      <c r="J49" s="264" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="263" t="str">
+      <c r="K49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="263" t="str">
+      <c r="L49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
@@ -26123,7 +26125,7 @@
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="267" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -26132,8 +26134,8 @@
       <c r="R49"/>
     </row>
     <row r="50" spans="2:18" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="277"/>
-      <c r="C50" s="277"/>
+      <c r="B50" s="267"/>
+      <c r="C50" s="267"/>
       <c r="D50" s="141" t="s">
         <v>149</v>
       </c>
@@ -26152,13 +26154,13 @@
       <c r="I50" s="142" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="274"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="266"/>
+      <c r="J50" s="264"/>
+      <c r="K50" s="273"/>
+      <c r="L50" s="273"/>
+      <c r="M50" s="275"/>
       <c r="N50" s="188"/>
       <c r="O50" s="183"/>
-      <c r="P50" s="268"/>
+      <c r="P50" s="277"/>
       <c r="Q50"/>
       <c r="R50"/>
     </row>
@@ -27499,10 +27501,10 @@
       <c r="I77"/>
     </row>
     <row r="78" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -27701,13 +27703,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="J49:J50"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
     <mergeCell ref="K48:P48"/>
@@ -27717,6 +27712,13 @@
     <mergeCell ref="P49:P50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="J49:J50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="26" priority="8">
@@ -28756,25 +28758,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="261"/>
-      <c r="M48" s="261"/>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
+      <c r="L48" s="270"/>
+      <c r="M48" s="270"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="271"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -28796,32 +28798,32 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="263" t="str">
+      <c r="K49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="263" t="str">
+      <c r="L49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="265" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="267" t="str">
+      <c r="O49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="267" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -28849,12 +28851,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="266"/>
-      <c r="N50" s="266"/>
-      <c r="O50" s="268"/>
-      <c r="P50" s="268"/>
+      <c r="K50" s="273"/>
+      <c r="L50" s="273"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
+      <c r="O50" s="277"/>
+      <c r="P50" s="277"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="167" t="s">
@@ -30091,10 +30093,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -30288,17 +30290,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -30306,6 +30297,17 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -31063,11 +31065,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="269" t="s">
+      <c r="B41" s="259" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="270"/>
-      <c r="D41" s="271"/>
+      <c r="C41" s="260"/>
+      <c r="D41" s="261"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -31342,25 +31344,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="261"/>
-      <c r="M48" s="261"/>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
+      <c r="L48" s="270"/>
+      <c r="M48" s="270"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="271"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -31382,32 +31384,32 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="263" t="str">
+      <c r="K49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="263" t="str">
+      <c r="L49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="265" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="267" t="str">
+      <c r="O49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="267" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -31435,12 +31437,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="266"/>
-      <c r="N50" s="266"/>
-      <c r="O50" s="268"/>
-      <c r="P50" s="268"/>
+      <c r="K50" s="273"/>
+      <c r="L50" s="273"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
+      <c r="O50" s="277"/>
+      <c r="P50" s="277"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -32677,10 +32679,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -32861,17 +32863,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -32879,6 +32870,17 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -33657,11 +33659,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" s="191" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="269" t="s">
+      <c r="B41" s="259" t="s">
         <v>189</v>
       </c>
-      <c r="C41" s="270"/>
-      <c r="D41" s="271"/>
+      <c r="C41" s="260"/>
+      <c r="D41" s="261"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -33936,25 +33938,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="261"/>
-      <c r="M48" s="261"/>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
+      <c r="L48" s="270"/>
+      <c r="M48" s="270"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="271"/>
     </row>
     <row r="49" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -33976,22 +33978,22 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="263" t="str">
+      <c r="K49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="263" t="str">
+      <c r="L49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="265" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
@@ -34029,10 +34031,10 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="266"/>
-      <c r="N50" s="266"/>
+      <c r="K50" s="273"/>
+      <c r="L50" s="273"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
       <c r="O50" s="282"/>
       <c r="P50" s="282"/>
     </row>
@@ -35271,10 +35273,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -35468,11 +35470,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
@@ -35486,6 +35483,11 @@
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -912,7 +912,7 @@
     <t>WIDI</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL —  17 SEPTEMBER 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL —  18 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>
@@ -2559,33 +2559,6 @@
     <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2616,6 +2589,33 @@
     <xf numFmtId="0" fontId="48" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2629,15 +2629,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2659,6 +2650,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4302,11 +4302,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>219</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -4626,33 +4626,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -4661,49 +4661,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -4728,13 +4728,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="172" t="s">
         <v>216</v>
       </c>
@@ -5850,21 +5850,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
-      <c r="F67" s="285"/>
-      <c r="G67" s="269" t="s">
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
+      <c r="F67" s="292"/>
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -6183,10 +6183,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -6498,6 +6498,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -6512,12 +6518,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="C3" s="75">
         <f ca="1">IF($J$5&lt;&gt;"",$J$5,MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),9,1)),EOMONTH(DATE(YEAR(TODAY()),9,1),0),11)-MAX(0,$J$3-$J$4)))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="76" t="s">
         <v>104</v>
@@ -6723,19 +6723,19 @@
         <v>112</v>
       </c>
       <c r="C10" s="234">
-        <v>94059448.761456996</v>
+        <v>96917521.722049996</v>
       </c>
       <c r="D10" s="234">
-        <v>28420735.559999999</v>
+        <v>29107735.559999999</v>
       </c>
       <c r="E10" s="234">
-        <v>127169369.653888</v>
+        <v>136252883.21706399</v>
       </c>
       <c r="F10" s="234">
-        <v>97531730.539957002</v>
+        <v>100110649.099953</v>
       </c>
       <c r="G10" s="234">
-        <v>347181284.515302</v>
+        <v>362388789.59906697</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="111"/>
@@ -6773,19 +6773,19 @@
         <v>70</v>
       </c>
       <c r="C12" s="234">
-        <v>114479651.836816</v>
+        <v>116147651.836816</v>
       </c>
       <c r="D12" s="234">
-        <v>52195418.771476999</v>
+        <v>54534837.701471999</v>
       </c>
       <c r="E12" s="234">
-        <v>93048570.049695998</v>
+        <v>95450687.169696003</v>
       </c>
       <c r="F12" s="234">
         <v>37670094.600000001</v>
       </c>
       <c r="G12" s="234">
-        <v>297393735.25798899</v>
+        <v>303803271.30798399</v>
       </c>
       <c r="H12" s="111"/>
       <c r="I12" s="111"/>
@@ -6798,19 +6798,19 @@
         <v>114</v>
       </c>
       <c r="C13" s="234">
-        <v>20451403.544785999</v>
+        <v>21583616.169985998</v>
       </c>
       <c r="D13" s="234">
-        <v>15163511.849981001</v>
+        <v>16536638.039975001</v>
       </c>
       <c r="E13" s="234">
-        <v>126765181.37974399</v>
+        <v>138116532.959694</v>
       </c>
       <c r="F13" s="234">
-        <v>51377168.189999998</v>
+        <v>51507668.189999998</v>
       </c>
       <c r="G13" s="234">
-        <v>213757264.96451101</v>
+        <v>227744455.35965499</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="111"/>
@@ -6823,19 +6823,19 @@
         <v>115</v>
       </c>
       <c r="C14" s="234">
-        <v>292379540.899665</v>
+        <v>313943352.84965998</v>
       </c>
       <c r="D14" s="234">
-        <v>24047531.925912</v>
+        <v>30269657.985479001</v>
       </c>
       <c r="E14" s="234">
-        <v>96084216.349922001</v>
+        <v>101974162.349902</v>
       </c>
       <c r="F14" s="234">
-        <v>247825364.82984</v>
+        <v>250228878.32984</v>
       </c>
       <c r="G14" s="234">
-        <v>660336654.00533903</v>
+        <v>696416051.51488101</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="111"/>
@@ -6848,19 +6848,19 @@
         <v>118</v>
       </c>
       <c r="C15" s="234">
-        <v>1049053078.841123</v>
+        <v>1067496483.041103</v>
       </c>
       <c r="D15" s="234">
-        <v>8227443.0769239999</v>
+        <v>8138253.8869240005</v>
       </c>
       <c r="E15" s="234">
-        <v>55748125.069968</v>
+        <v>58176052.949942999</v>
       </c>
       <c r="F15" s="234">
         <v>10913513.77</v>
       </c>
       <c r="G15" s="234">
-        <v>1123942160.7580149</v>
+        <v>1144724303.64797</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="111"/>
@@ -6873,19 +6873,19 @@
         <v>120</v>
       </c>
       <c r="C16" s="234">
-        <v>278713205.39376199</v>
+        <v>312494152.79274601</v>
       </c>
       <c r="D16" s="234">
-        <v>27681738.359931</v>
+        <v>29437089.039930999</v>
       </c>
       <c r="E16" s="234">
-        <v>198283694.90963</v>
+        <v>210140451.63960499</v>
       </c>
       <c r="F16" s="234">
-        <v>645336660.99997306</v>
+        <v>668372515.47996902</v>
       </c>
       <c r="G16" s="234">
-        <v>1150015299.663296</v>
+        <v>1220444208.952251</v>
       </c>
       <c r="H16" s="111"/>
       <c r="I16" s="111"/>
@@ -6898,19 +6898,19 @@
         <v>122</v>
       </c>
       <c r="C17" s="234">
-        <v>71065918.306536004</v>
+        <v>72865918.306536004</v>
       </c>
       <c r="D17" s="234">
         <v>11277436.9209</v>
       </c>
       <c r="E17" s="234">
-        <v>60965924.859052002</v>
+        <v>66284032.579031996</v>
       </c>
       <c r="F17" s="234">
         <v>23000000.5</v>
       </c>
       <c r="G17" s="234">
-        <v>166309280.58648801</v>
+        <v>173427388.30646801</v>
       </c>
       <c r="H17" s="111"/>
       <c r="I17" s="111"/>
@@ -6927,16 +6927,16 @@
         <v>8992270</v>
       </c>
       <c r="D18" s="234">
-        <v>103233876.372637</v>
+        <v>107181678.62261599</v>
       </c>
       <c r="E18" s="234">
-        <v>46059402</v>
+        <v>46461402</v>
       </c>
       <c r="F18" s="234">
-        <v>83394596.359999999</v>
+        <v>83978380.159999996</v>
       </c>
       <c r="G18" s="234">
-        <v>241680144.73263699</v>
+        <v>246613730.78261599</v>
       </c>
       <c r="H18" s="111"/>
       <c r="I18" s="111"/>
@@ -6976,7 +6976,7 @@
         <v>170</v>
       </c>
       <c r="C20" s="234">
-        <v>94308937.159999996</v>
+        <v>127135467.16</v>
       </c>
       <c r="D20" s="234" t="s">
         <v>165</v>
@@ -6988,7 +6988,7 @@
         <v>7921891.6799999997</v>
       </c>
       <c r="G20" s="234">
-        <v>102230828.84</v>
+        <v>135057358.84</v>
       </c>
       <c r="H20" s="111"/>
       <c r="I20" s="111"/>
@@ -7006,26 +7006,26 @@
         <v>124</v>
       </c>
       <c r="C21" s="234">
-        <v>158274692.538654</v>
+        <v>177164270.058642</v>
       </c>
       <c r="D21" s="234">
-        <v>34764395.343473002</v>
+        <v>35900827.783471003</v>
       </c>
       <c r="E21" s="234">
-        <v>99808923.749874994</v>
+        <v>111568653.35986499</v>
       </c>
       <c r="F21" s="234">
-        <v>252305457.80991</v>
+        <v>290454016.77988499</v>
       </c>
       <c r="G21" s="234">
-        <v>545153469.44191206</v>
+        <v>615087767.98186302</v>
       </c>
       <c r="H21" s="111"/>
       <c r="I21" s="111"/>
       <c r="J21" s="111"/>
       <c r="M21" s="14">
         <f>SUM(C33,C34)+M20</f>
-        <v>392950330.36262703</v>
+        <v>454997313.98041403</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>224</v>
@@ -7036,19 +7036,19 @@
         <v>125</v>
       </c>
       <c r="C22" s="234">
-        <v>149448636.296076</v>
+        <v>172201414.51065901</v>
       </c>
       <c r="D22" s="234">
-        <v>42335012.789970003</v>
+        <v>49903023.629965</v>
       </c>
       <c r="E22" s="234">
-        <v>118795902.36748999</v>
+        <v>126746353.23747499</v>
       </c>
       <c r="F22" s="234">
-        <v>201444355.70966101</v>
+        <v>210355166.919631</v>
       </c>
       <c r="G22" s="234">
-        <v>512023907.16319698</v>
+        <v>559205958.29772997</v>
       </c>
       <c r="H22" s="111"/>
       <c r="I22" s="111"/>
@@ -7059,19 +7059,19 @@
         <v>126</v>
       </c>
       <c r="C23" s="234">
-        <v>293741906.22570401</v>
+        <v>323500640.14265001</v>
       </c>
       <c r="D23" s="234">
-        <v>36987838.754964001</v>
+        <v>39057838.754964001</v>
       </c>
       <c r="E23" s="234">
-        <v>131777731.029908</v>
+        <v>139958091.469908</v>
       </c>
       <c r="F23" s="234">
-        <v>360216667.15961599</v>
+        <v>390890270.92961597</v>
       </c>
       <c r="G23" s="234">
-        <v>822724143.170192</v>
+        <v>893406841.29713798</v>
       </c>
       <c r="H23" s="111"/>
       <c r="I23" s="111"/>
@@ -7082,19 +7082,19 @@
         <v>225</v>
       </c>
       <c r="C24" s="234">
-        <v>136777627.932459</v>
+        <v>138586461.24244899</v>
       </c>
       <c r="D24" s="234">
-        <v>30034247.859962001</v>
+        <v>34780160.220744997</v>
       </c>
       <c r="E24" s="234">
-        <v>111081018.17824399</v>
+        <v>116499752.948219</v>
       </c>
       <c r="F24" s="234">
-        <v>28674143.870000001</v>
+        <v>36782251.869999997</v>
       </c>
       <c r="G24" s="234">
-        <v>306567037.84066498</v>
+        <v>326648626.28141302</v>
       </c>
       <c r="H24" s="111"/>
       <c r="I24" s="111"/>
@@ -7105,19 +7105,19 @@
         <v>220</v>
       </c>
       <c r="C25" s="234">
-        <v>189050468.946652</v>
+        <v>199516529.892643</v>
       </c>
       <c r="D25" s="234">
-        <v>60319548.956625998</v>
+        <v>62512341.996574</v>
       </c>
       <c r="E25" s="234">
-        <v>65683779.564621001</v>
+        <v>72789644.420606002</v>
       </c>
       <c r="F25" s="234">
-        <v>20000000.43</v>
+        <v>29729730.43</v>
       </c>
       <c r="G25" s="234">
-        <v>335053797.89789897</v>
+        <v>364548246.73982298</v>
       </c>
       <c r="H25" s="111"/>
       <c r="I25" s="111"/>
@@ -7128,19 +7128,19 @@
         <v>127</v>
       </c>
       <c r="C26" s="234">
-        <v>299809425.396097</v>
+        <v>321648535.34862697</v>
       </c>
       <c r="D26" s="234">
-        <v>167667121.467994</v>
+        <v>173348011.65299401</v>
       </c>
       <c r="E26" s="234">
-        <v>207404010.08629799</v>
+        <v>223413017.625983</v>
       </c>
       <c r="F26" s="234">
-        <v>14154270.5474</v>
+        <v>15098054.3574</v>
       </c>
       <c r="G26" s="234">
-        <v>689034827.49778903</v>
+        <v>733507618.98500395</v>
       </c>
       <c r="H26" s="111"/>
       <c r="I26" s="111"/>
@@ -7182,8 +7182,8 @@
       <c r="B31" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="C31" s="234">
-        <v>131326817.995389</v>
+      <c r="C31" s="171">
+        <v>167182405.05536899</v>
       </c>
       <c r="G31" s="111"/>
       <c r="H31" s="111"/>
@@ -7194,7 +7194,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="234">
-        <v>97328112.229664996</v>
+        <v>351088868.38575</v>
       </c>
       <c r="G32" s="111"/>
       <c r="H32" s="111"/>
@@ -7205,7 +7205,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="234">
-        <v>92572379.469917998</v>
+        <v>95000987.568413004</v>
       </c>
       <c r="G33" s="111"/>
       <c r="H33" s="111"/>
@@ -7216,7 +7216,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="234">
-        <v>300377950.89270902</v>
+        <v>359996326.41200101</v>
       </c>
       <c r="G34" s="111"/>
       <c r="H34" s="111"/>
@@ -7261,17 +7261,17 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>228</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
       <c r="F40" s="174">
         <f ca="1">IF(MONTH(TODAY())=9,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;9,1,0))</f>
-        <v>0.56666666666666665</v>
+        <v>0.6</v>
       </c>
       <c r="G40" s="192" t="s">
         <v>187</v>
@@ -7358,35 +7358,35 @@
       </c>
       <c r="E42" s="46">
         <f>H65</f>
-        <v>2235980335.6186624</v>
+        <v>2437125004.4134622</v>
       </c>
       <c r="F42" s="176">
         <f>IFERROR(E42/D42,0)</f>
-        <v>0.49558651915620466</v>
+        <v>0.54016856876857799</v>
       </c>
       <c r="G42" s="184">
         <f>D42*$H$40-E42</f>
-        <v>2275805698.0807338</v>
+        <v>2074661029.285934</v>
       </c>
       <c r="H42" s="184">
         <f ca="1">IFERROR(G42/$C$3,0)</f>
-        <v>189650474.84006116</v>
+        <v>188605548.1169031</v>
       </c>
       <c r="I42" s="204">
         <f>D42*$J$40-E42</f>
-        <v>2275805698.0807338</v>
+        <v>2074661029.285934</v>
       </c>
       <c r="J42" s="204">
         <f ca="1">IFERROR(I42/$C$3,0)</f>
-        <v>189650474.84006116</v>
+        <v>188605548.1169031</v>
       </c>
       <c r="K42" s="185">
         <f>D42*$L$40-E42</f>
-        <v>2275805698.0807338</v>
+        <v>2074661029.285934</v>
       </c>
       <c r="L42" s="185">
         <f ca="1">IFERROR(K42/$C$3,0)</f>
-        <v>189650474.84006116</v>
+        <v>188605548.1169031</v>
       </c>
       <c r="S42" s="173">
         <v>0.8</v>
@@ -7405,35 +7405,35 @@
       </c>
       <c r="E43" s="46">
         <f>I65</f>
-        <v>650631730.53382707</v>
+        <v>690350593.50908601</v>
       </c>
       <c r="F43" s="176">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.46428417033851654</v>
+        <v>0.49262714606170649</v>
       </c>
       <c r="G43" s="184">
         <f>D43*$H$40-E43</f>
-        <v>750733579.98158789</v>
+        <v>711014717.00632894</v>
       </c>
       <c r="H43" s="184">
         <f ca="1">IFERROR(G43/$C$3,0)</f>
-        <v>62561131.665132321</v>
+        <v>64637701.546029903</v>
       </c>
       <c r="I43" s="204">
         <f>D43*$J$40-E43</f>
-        <v>750733579.98158789</v>
+        <v>711014717.00632894</v>
       </c>
       <c r="J43" s="204">
         <f ca="1">IFERROR(I43/$C$3,0)</f>
-        <v>62561131.665132321</v>
+        <v>64637701.546029903</v>
       </c>
       <c r="K43" s="185">
         <f>D43*$L$40-E43</f>
-        <v>750733579.98158789</v>
+        <v>711014717.00632894</v>
       </c>
       <c r="L43" s="185">
         <f ca="1">IFERROR(K43/$C$3,0)</f>
-        <v>62561131.665132321</v>
+        <v>64637701.546029903</v>
       </c>
       <c r="S43" s="173">
         <v>0.85</v>
@@ -7452,35 +7452,35 @@
       </c>
       <c r="E44" s="46">
         <f>J65</f>
-        <v>1655562860.1776679</v>
+        <v>1758290800.9763489</v>
       </c>
       <c r="F44" s="176">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.56219603336660984</v>
+        <v>0.59708038733595448</v>
       </c>
       <c r="G44" s="184">
         <f>IF(D44=0,0,D44*$H$40-E44)</f>
-        <v>1289251336.1510174</v>
+        <v>1186523395.3523364</v>
       </c>
       <c r="H44" s="184">
         <f ca="1">IFERROR(G44/$C$3,0)</f>
-        <v>107437611.34591812</v>
+        <v>107865763.21384877</v>
       </c>
       <c r="I44" s="204">
         <f>IF(D44=0,0,D44*$J$40-E44)</f>
-        <v>1289251336.1510174</v>
+        <v>1186523395.3523364</v>
       </c>
       <c r="J44" s="204">
         <f ca="1">IFERROR(I44/$C$3,0)</f>
-        <v>107437611.34591812</v>
+        <v>107865763.21384877</v>
       </c>
       <c r="K44" s="185">
         <f>IF(D44=0,0,D44*$L$40-E44)</f>
-        <v>1289251336.1510174</v>
+        <v>1186523395.3523364</v>
       </c>
       <c r="L44" s="185">
         <f ca="1">IFERROR(K44/$C$3,0)</f>
-        <v>107437611.34591812</v>
+        <v>107865763.21384877</v>
       </c>
       <c r="S44" s="173">
         <v>0.9</v>
@@ -7499,35 +7499,35 @@
       </c>
       <c r="E45" s="46">
         <f>E74</f>
-        <v>621605260.58768106</v>
+        <v>973268587.42153299</v>
       </c>
       <c r="F45" s="176">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.35715705681688276</v>
+        <v>0.55921300255271456</v>
       </c>
       <c r="G45" s="184">
         <f>D45*$H$40-E45</f>
-        <v>1118820271.3272126</v>
+        <v>767156944.49336064</v>
       </c>
       <c r="H45" s="184">
         <f ca="1">IFERROR(G45/$C$3,0)</f>
-        <v>93235022.610601053</v>
+        <v>69741540.408487335</v>
       </c>
       <c r="I45" s="204">
         <f>D45*$J$40-E45</f>
-        <v>1118820271.3272126</v>
+        <v>767156944.49336064</v>
       </c>
       <c r="J45" s="204">
         <f ca="1">IFERROR(I45/$C$3,0)</f>
-        <v>93235022.610601053</v>
+        <v>69741540.408487335</v>
       </c>
       <c r="K45" s="185">
         <f>D45*$L$40-E45</f>
-        <v>1118820271.3272126</v>
+        <v>767156944.49336064</v>
       </c>
       <c r="L45" s="185">
         <f ca="1">IFERROR(K45/$C$3,0)</f>
-        <v>93235022.610601053</v>
+        <v>69741540.408487335</v>
       </c>
       <c r="S45" s="173">
         <v>0.95</v>
@@ -7544,35 +7544,35 @@
       </c>
       <c r="E46" s="47">
         <f>SUM(E42:E45)</f>
-        <v>5163780186.9178381</v>
+        <v>5859034986.3204298</v>
       </c>
       <c r="F46" s="177">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.48722302768547049</v>
+        <v>0.55282306024223493</v>
       </c>
       <c r="G46" s="181">
         <f>SUM(G42:G45)</f>
-        <v>5434610885.5405512</v>
+        <v>4739356086.1379604</v>
       </c>
       <c r="H46" s="181">
         <f ca="1">IFERROR(G46/$C$3,0)</f>
-        <v>452884240.4617126</v>
+        <v>430850553.28526914</v>
       </c>
       <c r="I46" s="186">
         <f>SUM(I42:I45)</f>
-        <v>5434610885.5405512</v>
+        <v>4739356086.1379604</v>
       </c>
       <c r="J46" s="186">
         <f ca="1">IFERROR(I46/$C$3,0)</f>
-        <v>452884240.4617126</v>
+        <v>430850553.28526914</v>
       </c>
       <c r="K46" s="186">
         <f>SUM(K42:K45)</f>
-        <v>5434610885.5405512</v>
+        <v>4739356086.1379604</v>
       </c>
       <c r="L46" s="186">
         <f ca="1">IFERROR(K46/$C$3,0)</f>
-        <v>452884240.4617126</v>
+        <v>430850553.28526914</v>
       </c>
       <c r="S46" s="173">
         <v>1</v>
@@ -7585,33 +7585,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -7620,49 +7620,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -7687,13 +7687,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -7726,47 +7726,47 @@
       </c>
       <c r="H51" s="114">
         <f>SUMIF($B$10:$B$26,$T51,C$10:C$26)+SUMIF($B$10:$B$26,$U51,C$10:C$26)</f>
-        <v>158274692.538654</v>
+        <v>177164270.058642</v>
       </c>
       <c r="I51" s="114">
         <f t="shared" ref="I51:I64" si="1">SUMIF($B$10:$B$26,$T51,D$10:D$26)+SUMIF($B$10:$B$26,$U51,D$10:D$26)</f>
-        <v>34764395.343473002</v>
+        <v>35900827.783471003</v>
       </c>
       <c r="J51" s="114">
         <f t="shared" ref="J51:J64" si="2">SUMIF($B$10:$B$26,$T51,E$10:E$26)+SUMIF($B$10:$B$26,$U51,E$10:E$26)</f>
-        <v>99808923.749874994</v>
+        <v>111568653.35986499</v>
       </c>
       <c r="K51" s="114">
         <f t="shared" ref="K51:K64" si="3">SUM(H51:J51)</f>
-        <v>292848011.632002</v>
+        <v>324633751.20197803</v>
       </c>
       <c r="L51" s="187">
         <f t="shared" ref="L51:L65" si="4">IFERROR(K51/G51,0)</f>
-        <v>0.56933612700981306</v>
+        <v>0.63113190209485415</v>
       </c>
       <c r="M51" s="184">
         <f t="shared" ref="M51:M64" si="5">G51*$H$40-K51</f>
-        <v>221519508.2548126</v>
+        <v>189733768.68483657</v>
       </c>
       <c r="N51" s="184">
         <f t="shared" ref="N51:N65" ca="1" si="6">IFERROR(M51/$C$3,0)</f>
-        <v>18459959.021234382</v>
+        <v>17248524.425894234</v>
       </c>
       <c r="O51" s="180">
         <f t="shared" ref="O51:O64" si="7">G51*$J$40-K51</f>
-        <v>221519508.2548126</v>
+        <v>189733768.68483657</v>
       </c>
       <c r="P51" s="180">
         <f t="shared" ref="P51:P65" ca="1" si="8">IFERROR(O51/$C$3,0)</f>
-        <v>18459959.021234382</v>
+        <v>17248524.425894234</v>
       </c>
       <c r="Q51" s="185">
         <f t="shared" ref="Q51:Q64" si="9">G51*$L$40-K51</f>
-        <v>221519508.2548126</v>
+        <v>189733768.68483657</v>
       </c>
       <c r="R51" s="185">
         <f t="shared" ref="R51:R65" ca="1" si="10">IFERROR(Q51/$C$3,0)</f>
-        <v>18459959.021234382</v>
+        <v>17248524.425894234</v>
       </c>
       <c r="T51" t="s">
         <v>124</v>
@@ -7800,47 +7800,47 @@
       </c>
       <c r="H52" s="114">
         <f t="shared" ref="H52:H64" si="11">SUMIF($B$10:$B$26,$T52,C$10:C$26)+SUMIF($B$10:$B$26,$U52,C$10:C$26)</f>
-        <v>134931055.38160199</v>
+        <v>137731268.00680199</v>
       </c>
       <c r="I52" s="114">
         <f t="shared" si="1"/>
-        <v>67358930.621457994</v>
+        <v>71071475.741447002</v>
       </c>
       <c r="J52" s="114">
         <f t="shared" si="2"/>
-        <v>219813751.42943999</v>
+        <v>233567220.12939</v>
       </c>
       <c r="K52" s="114">
         <f t="shared" si="3"/>
-        <v>422103737.4325</v>
+        <v>442369963.877639</v>
       </c>
       <c r="L52" s="187">
         <f t="shared" si="4"/>
-        <v>0.53735315681221862</v>
+        <v>0.56315278801948365</v>
       </c>
       <c r="M52" s="184">
         <f t="shared" si="5"/>
-        <v>363420143.98764157</v>
+        <v>343153917.54250258</v>
       </c>
       <c r="N52" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>30285011.998970132</v>
+        <v>31195810.685682055</v>
       </c>
       <c r="O52" s="180">
         <f t="shared" si="7"/>
-        <v>363420143.98764157</v>
+        <v>343153917.54250258</v>
       </c>
       <c r="P52" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>30285011.998970132</v>
+        <v>31195810.685682055</v>
       </c>
       <c r="Q52" s="185">
         <f t="shared" si="9"/>
-        <v>363420143.98764157</v>
+        <v>343153917.54250258</v>
       </c>
       <c r="R52" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>30285011.998970132</v>
+        <v>31195810.685682055</v>
       </c>
       <c r="T52" t="s">
         <v>70</v>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="N53" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>19391610.508584227</v>
+        <v>21154484.191182796</v>
       </c>
       <c r="O53" s="180">
         <f t="shared" si="7"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P53" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>19391610.508584227</v>
+        <v>21154484.191182796</v>
       </c>
       <c r="Q53" s="185">
         <f t="shared" si="9"/>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="R53" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>19391610.508584227</v>
+        <v>21154484.191182796</v>
       </c>
       <c r="T53" t="s">
         <v>169</v>
@@ -7948,47 +7948,47 @@
       </c>
       <c r="H54" s="114">
         <f t="shared" si="11"/>
-        <v>292379540.899665</v>
+        <v>313943352.84965998</v>
       </c>
       <c r="I54" s="114">
         <f t="shared" si="1"/>
-        <v>24047531.925912</v>
+        <v>30269657.985479001</v>
       </c>
       <c r="J54" s="114">
         <f t="shared" si="2"/>
-        <v>96084216.349922001</v>
+        <v>101974162.349902</v>
       </c>
       <c r="K54" s="114">
         <f t="shared" si="3"/>
-        <v>412511289.17549902</v>
+        <v>446187173.18504095</v>
       </c>
       <c r="L54" s="187">
         <f t="shared" si="4"/>
-        <v>0.56767206899732248</v>
+        <v>0.61401470070861475</v>
       </c>
       <c r="M54" s="184">
         <f t="shared" si="5"/>
-        <v>314160519.61036652</v>
+        <v>280484635.60082459</v>
       </c>
       <c r="N54" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>26180043.300863877</v>
+        <v>25498603.236438598</v>
       </c>
       <c r="O54" s="180">
         <f t="shared" si="7"/>
-        <v>314160519.61036652</v>
+        <v>280484635.60082459</v>
       </c>
       <c r="P54" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>26180043.300863877</v>
+        <v>25498603.236438598</v>
       </c>
       <c r="Q54" s="185">
         <f t="shared" si="9"/>
-        <v>314160519.61036652</v>
+        <v>280484635.60082459</v>
       </c>
       <c r="R54" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>26180043.300863877</v>
+        <v>25498603.236438598</v>
       </c>
       <c r="T54" t="s">
         <v>115</v>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="N55" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>28657427.045948967</v>
+        <v>31262647.686489783</v>
       </c>
       <c r="O55" s="180">
         <f t="shared" si="7"/>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="P55" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>28657427.045948967</v>
+        <v>31262647.686489783</v>
       </c>
       <c r="Q55" s="185">
         <f t="shared" si="9"/>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="R55" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>28657427.045948967</v>
+        <v>31262647.686489783</v>
       </c>
       <c r="T55" t="s">
         <v>182</v>
@@ -8096,47 +8096,47 @@
       </c>
       <c r="H56" s="114">
         <f t="shared" si="11"/>
-        <v>136777627.932459</v>
+        <v>138586461.24244899</v>
       </c>
       <c r="I56" s="114">
         <f t="shared" si="1"/>
-        <v>30034247.859962001</v>
+        <v>34780160.220744997</v>
       </c>
       <c r="J56" s="114">
         <f t="shared" si="2"/>
-        <v>111081018.17824399</v>
+        <v>116499752.948219</v>
       </c>
       <c r="K56" s="114">
         <f t="shared" si="3"/>
-        <v>277892893.97066498</v>
+        <v>289866374.41141295</v>
       </c>
       <c r="L56" s="187">
         <f t="shared" si="4"/>
-        <v>0.48333739086616728</v>
+        <v>0.50416279130418329</v>
       </c>
       <c r="M56" s="184">
         <f t="shared" si="5"/>
-        <v>297053094.52955341</v>
+        <v>285079614.08880544</v>
       </c>
       <c r="N56" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>24754424.54412945</v>
+        <v>25916328.553527769</v>
       </c>
       <c r="O56" s="180">
         <f t="shared" si="7"/>
-        <v>297053094.52955341</v>
+        <v>285079614.08880544</v>
       </c>
       <c r="P56" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>24754424.54412945</v>
+        <v>25916328.553527769</v>
       </c>
       <c r="Q56" s="185">
         <f t="shared" si="9"/>
-        <v>297053094.52955341</v>
+        <v>285079614.08880544</v>
       </c>
       <c r="R56" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>24754424.54412945</v>
+        <v>25916328.553527769</v>
       </c>
       <c r="T56" t="s">
         <v>225</v>
@@ -8170,47 +8170,47 @@
       </c>
       <c r="H57" s="114">
         <f t="shared" si="11"/>
-        <v>278713205.39376199</v>
+        <v>312494152.79274601</v>
       </c>
       <c r="I57" s="114">
         <f t="shared" si="1"/>
-        <v>27681738.359931</v>
+        <v>29437089.039930999</v>
       </c>
       <c r="J57" s="114">
         <f t="shared" si="2"/>
-        <v>198283694.90963</v>
+        <v>210140451.63960499</v>
       </c>
       <c r="K57" s="114">
         <f t="shared" si="3"/>
-        <v>504678638.66332299</v>
+        <v>552071693.47228193</v>
       </c>
       <c r="L57" s="187">
         <f t="shared" si="4"/>
-        <v>0.45499989979081001</v>
+        <v>0.49772775378908907</v>
       </c>
       <c r="M57" s="184">
         <f t="shared" si="5"/>
-        <v>604505426.86142373</v>
+        <v>557112372.05246472</v>
       </c>
       <c r="N57" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>50375452.23845198</v>
+        <v>50646579.277496792</v>
       </c>
       <c r="O57" s="180">
         <f t="shared" si="7"/>
-        <v>604505426.86142373</v>
+        <v>557112372.05246472</v>
       </c>
       <c r="P57" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>50375452.23845198</v>
+        <v>50646579.277496792</v>
       </c>
       <c r="Q57" s="185">
         <f t="shared" si="9"/>
-        <v>604505426.86142373</v>
+        <v>557112372.05246472</v>
       </c>
       <c r="R57" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>50375452.23845198</v>
+        <v>50646579.277496792</v>
       </c>
       <c r="T57" t="s">
         <v>120</v>
@@ -8244,47 +8244,47 @@
       </c>
       <c r="H58" s="114">
         <f t="shared" si="11"/>
-        <v>149448636.296076</v>
+        <v>172201414.51065901</v>
       </c>
       <c r="I58" s="114">
         <f t="shared" si="1"/>
-        <v>42335012.789970003</v>
+        <v>49903023.629965</v>
       </c>
       <c r="J58" s="114">
         <f t="shared" si="2"/>
-        <v>118795902.36748999</v>
+        <v>126746353.23747499</v>
       </c>
       <c r="K58" s="114">
         <f t="shared" si="3"/>
-        <v>310579551.45353603</v>
+        <v>348850791.37809902</v>
       </c>
       <c r="L58" s="187">
         <f t="shared" si="4"/>
-        <v>0.50535180400924973</v>
+        <v>0.56762390159917142</v>
       </c>
       <c r="M58" s="184">
         <f t="shared" si="5"/>
-        <v>304001318.72349286</v>
+        <v>265730078.79892987</v>
       </c>
       <c r="N58" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>25333443.226957738</v>
+        <v>24157279.890811805</v>
       </c>
       <c r="O58" s="180">
         <f t="shared" si="7"/>
-        <v>304001318.72349286</v>
+        <v>265730078.79892987</v>
       </c>
       <c r="P58" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>25333443.226957738</v>
+        <v>24157279.890811805</v>
       </c>
       <c r="Q58" s="185">
         <f t="shared" si="9"/>
-        <v>304001318.72349286</v>
+        <v>265730078.79892987</v>
       </c>
       <c r="R58" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>25333443.226957738</v>
+        <v>24157279.890811805</v>
       </c>
       <c r="T58" t="s">
         <v>125</v>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="H59" s="114">
         <f t="shared" si="11"/>
-        <v>94308937.159999996</v>
+        <v>127135467.16</v>
       </c>
       <c r="I59" s="114">
         <f t="shared" si="1"/>
@@ -8330,35 +8330,35 @@
       </c>
       <c r="K59" s="114">
         <f t="shared" si="3"/>
-        <v>94308937.159999996</v>
+        <v>127135467.16</v>
       </c>
       <c r="L59" s="187">
         <f t="shared" si="4"/>
-        <v>0.21248087199996912</v>
+        <v>0.28644003143042351</v>
       </c>
       <c r="M59" s="184">
         <f t="shared" si="5"/>
-        <v>349537778.41641998</v>
+        <v>316711248.41641998</v>
       </c>
       <c r="N59" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>29128148.201368332</v>
+        <v>28791931.674219999</v>
       </c>
       <c r="O59" s="180">
         <f t="shared" si="7"/>
-        <v>349537778.41641998</v>
+        <v>316711248.41641998</v>
       </c>
       <c r="P59" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>29128148.201368332</v>
+        <v>28791931.674219999</v>
       </c>
       <c r="Q59" s="185">
         <f t="shared" si="9"/>
-        <v>349537778.41641998</v>
+        <v>316711248.41641998</v>
       </c>
       <c r="R59" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>29128148.201368332</v>
+        <v>28791931.674219999</v>
       </c>
       <c r="T59" t="s">
         <v>170</v>
@@ -8392,47 +8392,47 @@
       </c>
       <c r="H60" s="114">
         <f t="shared" si="11"/>
-        <v>189050468.946652</v>
+        <v>199516529.892643</v>
       </c>
       <c r="I60" s="114">
         <f t="shared" si="1"/>
-        <v>60319548.956625998</v>
+        <v>62512341.996574</v>
       </c>
       <c r="J60" s="114">
         <f t="shared" si="2"/>
-        <v>65683779.564621001</v>
+        <v>72789644.420606002</v>
       </c>
       <c r="K60" s="114">
         <f t="shared" si="3"/>
-        <v>315053797.46789896</v>
+        <v>334818516.30982304</v>
       </c>
       <c r="L60" s="187">
         <f t="shared" si="4"/>
-        <v>0.54395942619040094</v>
+        <v>0.57808440803945504</v>
       </c>
       <c r="M60" s="184">
         <f t="shared" si="5"/>
-        <v>264132410.72848475</v>
+        <v>244367691.88656068</v>
       </c>
       <c r="N60" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>22011034.22737373</v>
+        <v>22215244.716960061</v>
       </c>
       <c r="O60" s="180">
         <f t="shared" si="7"/>
-        <v>264132410.72848475</v>
+        <v>244367691.88656068</v>
       </c>
       <c r="P60" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>22011034.22737373</v>
+        <v>22215244.716960061</v>
       </c>
       <c r="Q60" s="185">
         <f t="shared" si="9"/>
-        <v>264132410.72848475</v>
+        <v>244367691.88656068</v>
       </c>
       <c r="R60" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>22011034.22737373</v>
+        <v>22215244.716960061</v>
       </c>
       <c r="T60" t="s">
         <v>220</v>
@@ -8466,47 +8466,47 @@
       </c>
       <c r="H61" s="114">
         <f t="shared" si="11"/>
-        <v>293741906.22570401</v>
+        <v>323500640.14265001</v>
       </c>
       <c r="I61" s="114">
         <f t="shared" si="1"/>
-        <v>36987838.754964001</v>
+        <v>39057838.754964001</v>
       </c>
       <c r="J61" s="114">
         <f t="shared" si="2"/>
-        <v>131777731.029908</v>
+        <v>139958091.469908</v>
       </c>
       <c r="K61" s="114">
         <f t="shared" si="3"/>
-        <v>462507476.01057601</v>
+        <v>502516570.367522</v>
       </c>
       <c r="L61" s="187">
         <f t="shared" si="4"/>
-        <v>0.64542579133939471</v>
+        <v>0.70125818913941185</v>
       </c>
       <c r="M61" s="184">
         <f t="shared" si="5"/>
-        <v>254085325.54260552</v>
+        <v>214076231.18565953</v>
       </c>
       <c r="N61" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>21173777.128550459</v>
+        <v>19461475.562332686</v>
       </c>
       <c r="O61" s="180">
         <f t="shared" si="7"/>
-        <v>254085325.54260552</v>
+        <v>214076231.18565953</v>
       </c>
       <c r="P61" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>21173777.128550459</v>
+        <v>19461475.562332686</v>
       </c>
       <c r="Q61" s="185">
         <f t="shared" si="9"/>
-        <v>254085325.54260552</v>
+        <v>214076231.18565953</v>
       </c>
       <c r="R61" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>21173777.128550459</v>
+        <v>19461475.562332686</v>
       </c>
       <c r="T61" t="s">
         <v>126</v>
@@ -8540,47 +8540,47 @@
       </c>
       <c r="H62" s="114">
         <f t="shared" si="11"/>
-        <v>94059448.761456996</v>
+        <v>96917521.722049996</v>
       </c>
       <c r="I62" s="114">
         <f t="shared" si="1"/>
-        <v>28420735.559999999</v>
+        <v>29107735.559999999</v>
       </c>
       <c r="J62" s="114">
         <f t="shared" si="2"/>
-        <v>127169369.653888</v>
+        <v>136252883.21706399</v>
       </c>
       <c r="K62" s="114">
         <f t="shared" si="3"/>
-        <v>249649553.97534502</v>
+        <v>262278140.49911398</v>
       </c>
       <c r="L62" s="187">
         <f t="shared" si="4"/>
-        <v>0.52334880955678476</v>
+        <v>0.54982254290962729</v>
       </c>
       <c r="M62" s="184">
         <f t="shared" si="5"/>
-        <v>227373703.58545649</v>
+        <v>214745117.06168753</v>
       </c>
       <c r="N62" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>18947808.632121373</v>
+        <v>19522283.369244322</v>
       </c>
       <c r="O62" s="180">
         <f t="shared" si="7"/>
-        <v>227373703.58545649</v>
+        <v>214745117.06168753</v>
       </c>
       <c r="P62" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>18947808.632121373</v>
+        <v>19522283.369244322</v>
       </c>
       <c r="Q62" s="185">
         <f t="shared" si="9"/>
-        <v>227373703.58545649</v>
+        <v>214745117.06168753</v>
       </c>
       <c r="R62" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>18947808.632121373</v>
+        <v>19522283.369244322</v>
       </c>
       <c r="T62" t="s">
         <v>112</v>
@@ -8614,47 +8614,47 @@
       </c>
       <c r="H63" s="114">
         <f t="shared" si="11"/>
-        <v>299809425.396097</v>
+        <v>321648535.34862697</v>
       </c>
       <c r="I63" s="114">
         <f t="shared" si="1"/>
-        <v>167667121.467994</v>
+        <v>173348011.65299401</v>
       </c>
       <c r="J63" s="114">
         <f t="shared" si="2"/>
-        <v>207404010.08629799</v>
+        <v>223413017.625983</v>
       </c>
       <c r="K63" s="114">
         <f t="shared" si="3"/>
-        <v>674880556.95038903</v>
+        <v>718409564.62760401</v>
       </c>
       <c r="L63" s="187">
         <f t="shared" si="4"/>
-        <v>0.6893753652456267</v>
+        <v>0.73383927112825775</v>
       </c>
       <c r="M63" s="184">
         <f t="shared" si="5"/>
-        <v>304093440.34341753</v>
+        <v>260564432.66620255</v>
       </c>
       <c r="N63" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>25341120.028618127</v>
+        <v>23687675.696927503</v>
       </c>
       <c r="O63" s="180">
         <f t="shared" si="7"/>
-        <v>304093440.34341753</v>
+        <v>260564432.66620255</v>
       </c>
       <c r="P63" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>25341120.028618127</v>
+        <v>23687675.696927503</v>
       </c>
       <c r="Q63" s="185">
         <f t="shared" si="9"/>
-        <v>304093440.34341753</v>
+        <v>260564432.66620255</v>
       </c>
       <c r="R63" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>25341120.028618127</v>
+        <v>23687675.696927503</v>
       </c>
       <c r="T63" t="s">
         <v>127</v>
@@ -8688,47 +8688,47 @@
       </c>
       <c r="H64" s="114">
         <f t="shared" si="11"/>
-        <v>80058188.306536004</v>
+        <v>81858188.306536004</v>
       </c>
       <c r="I64" s="114">
         <f t="shared" si="1"/>
-        <v>114511313.29353701</v>
+        <v>118459115.543516</v>
       </c>
       <c r="J64" s="114">
         <f t="shared" si="2"/>
-        <v>107025326.859052</v>
+        <v>112745434.579032</v>
       </c>
       <c r="K64" s="114">
         <f t="shared" si="3"/>
-        <v>301594828.45912504</v>
+        <v>313062738.429084</v>
       </c>
       <c r="L64" s="187">
         <f t="shared" si="4"/>
-        <v>0.56171872572406134</v>
+        <v>0.58307764559664343</v>
       </c>
       <c r="M64" s="184">
         <f t="shared" si="5"/>
-        <v>235319492.97526574</v>
+        <v>223851583.00530678</v>
       </c>
       <c r="N64" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>19609957.747938812</v>
+        <v>20350143.909573343</v>
       </c>
       <c r="O64" s="180">
         <f t="shared" si="7"/>
-        <v>235319492.97526574</v>
+        <v>223851583.00530678</v>
       </c>
       <c r="P64" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>19609957.747938812</v>
+        <v>20350143.909573343</v>
       </c>
       <c r="Q64" s="185">
         <f t="shared" si="9"/>
-        <v>235319492.97526574</v>
+        <v>223851583.00530678</v>
       </c>
       <c r="R64" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>19609957.747938812</v>
+        <v>20350143.909573343</v>
       </c>
       <c r="T64" t="s">
         <v>122</v>
@@ -8760,47 +8760,47 @@
       </c>
       <c r="H65" s="135">
         <f t="shared" si="12"/>
-        <v>2235980335.6186624</v>
+        <v>2437125004.4134622</v>
       </c>
       <c r="I65" s="135">
         <f t="shared" si="12"/>
-        <v>650631730.53382707</v>
+        <v>690350593.50908601</v>
       </c>
       <c r="J65" s="135">
         <f t="shared" si="12"/>
-        <v>1655562860.1776679</v>
+        <v>1758290800.9763489</v>
       </c>
       <c r="K65" s="135">
         <f t="shared" si="12"/>
-        <v>4542174926.3301563</v>
+        <v>4885766398.8988962</v>
       </c>
       <c r="L65" s="189">
         <f t="shared" si="4"/>
-        <v>0.5127785726350278</v>
+        <v>0.55156755538689106</v>
       </c>
       <c r="M65" s="181">
         <f>SUM(M51:M64)</f>
-        <v>4315790614.2133389</v>
+        <v>3972199141.6445985</v>
       </c>
       <c r="N65" s="181">
         <f t="shared" ca="1" si="6"/>
-        <v>359649217.85111159</v>
+        <v>361109012.8767817</v>
       </c>
       <c r="O65" s="181">
         <f>SUM(O51:O64)</f>
-        <v>4315790614.2133389</v>
+        <v>3972199141.6445985</v>
       </c>
       <c r="P65" s="181">
         <f t="shared" ca="1" si="8"/>
-        <v>359649217.85111159</v>
+        <v>361109012.8767817</v>
       </c>
       <c r="Q65" s="186">
         <f>SUM(Q51:Q64)</f>
-        <v>4315790614.2133389</v>
+        <v>3972199141.6445985</v>
       </c>
       <c r="R65" s="186">
         <f t="shared" ca="1" si="10"/>
-        <v>359649217.85111159</v>
+        <v>361109012.8767817</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8809,21 +8809,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="269" t="s">
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -8885,35 +8885,35 @@
       </c>
       <c r="E69" s="114">
         <f>IFERROR($C$31,0)</f>
-        <v>131326817.995389</v>
+        <v>167182405.05536899</v>
       </c>
       <c r="F69" s="187">
         <f t="shared" ref="F69:F74" si="13">IFERROR(E69/D69,0)</f>
-        <v>0.5124798934730147</v>
+        <v>0.65240003862993257</v>
       </c>
       <c r="G69" s="184">
         <f>D69*$H$40-E69</f>
-        <v>124930685.30957563</v>
+        <v>89075098.249595642</v>
       </c>
       <c r="H69" s="184">
         <f t="shared" ref="H69:H74" ca="1" si="14">IFERROR(G69/$C$3,0)</f>
-        <v>10410890.442464637</v>
+        <v>8097736.2045086948</v>
       </c>
       <c r="I69" s="204">
         <f>D69*$J$40-E69</f>
-        <v>124930685.30957563</v>
+        <v>89075098.249595642</v>
       </c>
       <c r="J69" s="204">
         <f t="shared" ref="J69:J74" ca="1" si="15">IFERROR(I69/$C$3,0)</f>
-        <v>10410890.442464637</v>
+        <v>8097736.2045086948</v>
       </c>
       <c r="K69" s="185">
         <f>D69*$L$40-E69</f>
-        <v>124930685.30957563</v>
+        <v>89075098.249595642</v>
       </c>
       <c r="L69" s="185">
         <f t="shared" ref="L69:L74" ca="1" si="16">IFERROR(K69/$C$3,0)</f>
-        <v>10410890.442464637</v>
+        <v>8097736.2045086948</v>
       </c>
     </row>
     <row r="70" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8929,35 +8929,35 @@
       </c>
       <c r="E70" s="114">
         <f>IFERROR($C$32,0)</f>
-        <v>97328112.229664996</v>
+        <v>351088868.38575</v>
       </c>
       <c r="F70" s="187">
         <f t="shared" si="13"/>
-        <v>0.24358919555266156</v>
+        <v>0.87869222014472315</v>
       </c>
       <c r="G70" s="184">
         <f>D70*$H$40-E70</f>
-        <v>302230300.07529962</v>
+        <v>48469543.919214606</v>
       </c>
       <c r="H70" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>25185858.3396083</v>
+        <v>4406322.1744740549</v>
       </c>
       <c r="I70" s="204">
         <f>D70*$J$40-E70</f>
-        <v>302230300.07529962</v>
+        <v>48469543.919214606</v>
       </c>
       <c r="J70" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>25185858.3396083</v>
+        <v>4406322.1744740549</v>
       </c>
       <c r="K70" s="185">
         <f>D70*$L$40-E70</f>
-        <v>302230300.07529962</v>
+        <v>48469543.919214606</v>
       </c>
       <c r="L70" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>25185858.3396083</v>
+        <v>4406322.1744740549</v>
       </c>
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.25">
@@ -8973,35 +8973,35 @@
       </c>
       <c r="E71" s="114">
         <f>M21</f>
-        <v>392950330.36262703</v>
+        <v>454997313.98041403</v>
       </c>
       <c r="F71" s="187">
         <f t="shared" si="13"/>
-        <v>0.36229655763271368</v>
+        <v>0.4195033006718985</v>
       </c>
       <c r="G71" s="184">
         <f>D71*$H$40-E71</f>
-        <v>691659285.94233751</v>
+        <v>629612302.32455051</v>
       </c>
       <c r="H71" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>57638273.828528129</v>
+        <v>57237482.02950459</v>
       </c>
       <c r="I71" s="204">
         <f>D71*$J$40-E71</f>
-        <v>691659285.94233751</v>
+        <v>629612302.32455051</v>
       </c>
       <c r="J71" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>57638273.828528129</v>
+        <v>57237482.02950459</v>
       </c>
       <c r="K71" s="185">
         <f>D71*$L$40-E71</f>
-        <v>691659285.94233751</v>
+        <v>629612302.32455051</v>
       </c>
       <c r="L71" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>57638273.828528129</v>
+        <v>57237482.02950459</v>
       </c>
     </row>
     <row r="72" spans="2:21" hidden="1" x14ac:dyDescent="0.25">
@@ -9103,35 +9103,35 @@
       </c>
       <c r="E74" s="115">
         <f>SUM(E69:E73)</f>
-        <v>621605260.58768106</v>
+        <v>973268587.42153299</v>
       </c>
       <c r="F74" s="177">
         <f t="shared" si="13"/>
-        <v>0.35715705681688276</v>
+        <v>0.55921300255271456</v>
       </c>
       <c r="G74" s="181">
         <f>SUM(G69:G73)</f>
-        <v>1118820271.3272128</v>
+        <v>767156944.49336076</v>
       </c>
       <c r="H74" s="181">
         <f t="shared" ca="1" si="14"/>
-        <v>93235022.610601068</v>
+        <v>69741540.408487335</v>
       </c>
       <c r="I74" s="186">
         <f>SUM(I69:I73)</f>
-        <v>1118820271.3272128</v>
+        <v>767156944.49336076</v>
       </c>
       <c r="J74" s="186">
         <f t="shared" ca="1" si="15"/>
-        <v>93235022.610601068</v>
+        <v>69741540.408487335</v>
       </c>
       <c r="K74" s="186">
         <f>SUM(K69:K73)</f>
-        <v>1118820271.3272128</v>
+        <v>767156944.49336076</v>
       </c>
       <c r="L74" s="186">
         <f t="shared" ca="1" si="16"/>
-        <v>93235022.610601068</v>
+        <v>69741540.408487335</v>
       </c>
     </row>
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9144,10 +9144,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="D80" s="131">
         <f>SUMIF($B$10:$B$26,$T80,$F$10:$F$26)+SUMIF($B$10:$B$26,$U80,$F$10:$F$26)</f>
-        <v>252305457.80991</v>
+        <v>290454016.77988499</v>
       </c>
       <c r="T80" t="str">
         <f t="shared" ref="T80:U93" si="17">T51</f>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="D81" s="132">
         <f t="shared" ref="D81:D93" si="18">SUMIF($B$10:$B$26,$T81,$F$10:$F$26)+SUMIF($B$10:$B$26,$U81,$F$10:$F$26)</f>
-        <v>89047262.789999992</v>
+        <v>89177762.789999992</v>
       </c>
       <c r="T81" t="str">
         <f t="shared" si="17"/>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="D83" s="131">
         <f t="shared" si="18"/>
-        <v>247825364.82984</v>
+        <v>250228878.32984</v>
       </c>
       <c r="T83" t="str">
         <f t="shared" si="17"/>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="D85" s="131">
         <f t="shared" si="18"/>
-        <v>28674143.870000001</v>
+        <v>36782251.869999997</v>
       </c>
       <c r="T85" t="str">
         <f t="shared" si="17"/>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="D86" s="132">
         <f t="shared" si="18"/>
-        <v>645336660.99997306</v>
+        <v>668372515.47996902</v>
       </c>
       <c r="T86" t="str">
         <f t="shared" si="17"/>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="D87" s="131">
         <f t="shared" si="18"/>
-        <v>201444355.70966101</v>
+        <v>210355166.919631</v>
       </c>
       <c r="T87" t="str">
         <f t="shared" si="17"/>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D89" s="132">
         <f t="shared" si="18"/>
-        <v>20000000.43</v>
+        <v>29729730.43</v>
       </c>
       <c r="T89" t="str">
         <f t="shared" si="17"/>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="D90" s="131">
         <f t="shared" si="18"/>
-        <v>360216667.15961599</v>
+        <v>390890270.92961597</v>
       </c>
       <c r="T90" t="str">
         <f t="shared" si="17"/>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="D91" s="132">
         <f t="shared" si="18"/>
-        <v>97531730.539957002</v>
+        <v>100110649.099953</v>
       </c>
       <c r="T91" t="str">
         <f t="shared" si="17"/>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="D92" s="131">
         <f t="shared" si="18"/>
-        <v>14154270.5474</v>
+        <v>15098054.3574</v>
       </c>
       <c r="T92" t="str">
         <f t="shared" si="17"/>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="D93" s="132">
         <f t="shared" si="18"/>
-        <v>106394596.86</v>
+        <v>106978380.66</v>
       </c>
       <c r="T93" t="str">
         <f t="shared" si="17"/>
@@ -9454,12 +9454,18 @@
       <c r="C94" s="58"/>
       <c r="D94" s="120">
         <f>SUM(D80:D93)</f>
-        <v>2075537087.7863572</v>
+        <v>2200784253.8862939</v>
       </c>
     </row>
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -9474,12 +9480,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -10107,11 +10107,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>163</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -10431,33 +10431,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -10466,49 +10466,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -10533,13 +10533,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -11655,21 +11655,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="269" t="s">
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -11990,10 +11990,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -12306,6 +12306,12 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -12320,12 +12326,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -12953,11 +12953,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>175</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -13277,33 +13277,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -13312,49 +13312,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -13379,13 +13379,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -14501,21 +14501,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="269" t="s">
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -14836,10 +14836,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -15152,6 +15152,12 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -15166,12 +15172,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -15799,11 +15799,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>177</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -16123,33 +16123,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -16158,49 +16158,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -16225,13 +16225,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -17333,21 +17333,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="269" t="s">
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -17668,10 +17668,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -17984,6 +17984,12 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -17998,12 +18004,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -25783,11 +25783,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="259" t="s">
+      <c r="B41" s="269" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="260"/>
-      <c r="D41" s="261"/>
+      <c r="C41" s="270"/>
+      <c r="D41" s="271"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -26058,59 +26058,59 @@
       </c>
     </row>
     <row r="48" spans="2:19" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="270"/>
-      <c r="M48" s="270"/>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="271"/>
+      <c r="L48" s="261"/>
+      <c r="M48" s="261"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
       <c r="Q48"/>
       <c r="R48"/>
     </row>
     <row r="49" spans="2:18" s="139" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="267" t="s">
+      <c r="B49" s="277" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="267" t="s">
+      <c r="C49" s="277" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="264" t="s">
+      <c r="D49" s="274" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="265"/>
-      <c r="F49" s="266"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
       <c r="G49" s="140" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="140"/>
       <c r="I49" s="140"/>
-      <c r="J49" s="264" t="s">
+      <c r="J49" s="274" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="272" t="str">
+      <c r="K49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="272" t="str">
+      <c r="L49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
@@ -26125,7 +26125,7 @@
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="276" t="str">
+      <c r="P49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -26134,8 +26134,8 @@
       <c r="R49"/>
     </row>
     <row r="50" spans="2:18" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="267"/>
-      <c r="C50" s="267"/>
+      <c r="B50" s="277"/>
+      <c r="C50" s="277"/>
       <c r="D50" s="141" t="s">
         <v>149</v>
       </c>
@@ -26154,13 +26154,13 @@
       <c r="I50" s="142" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="264"/>
-      <c r="K50" s="273"/>
-      <c r="L50" s="273"/>
-      <c r="M50" s="275"/>
+      <c r="J50" s="274"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="266"/>
       <c r="N50" s="188"/>
       <c r="O50" s="183"/>
-      <c r="P50" s="277"/>
+      <c r="P50" s="268"/>
       <c r="Q50"/>
       <c r="R50"/>
     </row>
@@ -27501,10 +27501,10 @@
       <c r="I77"/>
     </row>
     <row r="78" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -27703,6 +27703,13 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="J49:J50"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
     <mergeCell ref="K48:P48"/>
@@ -27712,13 +27719,6 @@
     <mergeCell ref="P49:P50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="J49:J50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="26" priority="8">
@@ -28758,25 +28758,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="270"/>
-      <c r="M48" s="270"/>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="271"/>
+      <c r="L48" s="261"/>
+      <c r="M48" s="261"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -28798,32 +28798,32 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="272" t="str">
+      <c r="K49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="272" t="str">
+      <c r="L49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="274" t="str">
+      <c r="N49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="276" t="str">
+      <c r="O49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="276" t="str">
+      <c r="P49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -28851,12 +28851,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="273"/>
-      <c r="L50" s="273"/>
-      <c r="M50" s="275"/>
-      <c r="N50" s="275"/>
-      <c r="O50" s="277"/>
-      <c r="P50" s="277"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="266"/>
+      <c r="N50" s="266"/>
+      <c r="O50" s="268"/>
+      <c r="P50" s="268"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="167" t="s">
@@ -30093,10 +30093,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -30290,6 +30290,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -30297,17 +30308,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -31065,11 +31065,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="259" t="s">
+      <c r="B41" s="269" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="260"/>
-      <c r="D41" s="261"/>
+      <c r="C41" s="270"/>
+      <c r="D41" s="271"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -31344,25 +31344,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="270"/>
-      <c r="M48" s="270"/>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="271"/>
+      <c r="L48" s="261"/>
+      <c r="M48" s="261"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -31384,32 +31384,32 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="272" t="str">
+      <c r="K49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="272" t="str">
+      <c r="L49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="274" t="str">
+      <c r="N49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="276" t="str">
+      <c r="O49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="276" t="str">
+      <c r="P49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -31437,12 +31437,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="273"/>
-      <c r="L50" s="273"/>
-      <c r="M50" s="275"/>
-      <c r="N50" s="275"/>
-      <c r="O50" s="277"/>
-      <c r="P50" s="277"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="266"/>
+      <c r="N50" s="266"/>
+      <c r="O50" s="268"/>
+      <c r="P50" s="268"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -32679,10 +32679,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -32863,6 +32863,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -32870,17 +32881,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -33659,11 +33659,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" s="191" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="259" t="s">
+      <c r="B41" s="269" t="s">
         <v>189</v>
       </c>
-      <c r="C41" s="260"/>
-      <c r="D41" s="261"/>
+      <c r="C41" s="270"/>
+      <c r="D41" s="271"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -33938,25 +33938,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="270"/>
-      <c r="M48" s="270"/>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="271"/>
+      <c r="L48" s="261"/>
+      <c r="M48" s="261"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
     </row>
     <row r="49" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -33978,22 +33978,22 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="272" t="str">
+      <c r="K49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="272" t="str">
+      <c r="L49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="274" t="str">
+      <c r="N49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
@@ -34031,10 +34031,10 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="273"/>
-      <c r="L50" s="273"/>
-      <c r="M50" s="275"/>
-      <c r="N50" s="275"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="266"/>
+      <c r="N50" s="266"/>
       <c r="O50" s="282"/>
       <c r="P50" s="282"/>
     </row>
@@ -35273,10 +35273,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -35470,6 +35470,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
@@ -35483,11 +35488,6 @@
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -912,7 +912,7 @@
     <t>WIDI</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL —  18 SEPTEMBER 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL —  19 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="C3" s="75">
         <f ca="1">IF($J$5&lt;&gt;"",$J$5,MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),9,1)),EOMONTH(DATE(YEAR(TODAY()),9,1),0),11)-MAX(0,$J$3-$J$4)))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" s="76" t="s">
         <v>104</v>
@@ -6723,19 +6723,19 @@
         <v>112</v>
       </c>
       <c r="C10" s="234">
-        <v>96917521.722049996</v>
+        <v>100376981.08205</v>
       </c>
       <c r="D10" s="234">
         <v>29107735.559999999</v>
       </c>
       <c r="E10" s="234">
-        <v>136252883.21706399</v>
+        <v>139127171.50706401</v>
       </c>
       <c r="F10" s="234">
-        <v>100110649.099953</v>
+        <v>106507045.649948</v>
       </c>
       <c r="G10" s="234">
-        <v>362388789.59906697</v>
+        <v>375118933.79906201</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="111"/>
@@ -6754,13 +6754,13 @@
         <v>16503315.6</v>
       </c>
       <c r="E11" s="234">
-        <v>172635135.9993</v>
+        <v>199157658.6392</v>
       </c>
       <c r="F11" s="234" t="s">
         <v>165</v>
       </c>
       <c r="G11" s="234">
-        <v>193311875.01929799</v>
+        <v>219834397.65919799</v>
       </c>
       <c r="H11" s="111"/>
       <c r="I11" s="111"/>
@@ -6773,19 +6773,19 @@
         <v>70</v>
       </c>
       <c r="C12" s="234">
-        <v>116147651.836816</v>
+        <v>117345624.50743701</v>
       </c>
       <c r="D12" s="234">
-        <v>54534837.701471999</v>
+        <v>55173988.001571998</v>
       </c>
       <c r="E12" s="234">
-        <v>95450687.169696003</v>
+        <v>102973209.969696</v>
       </c>
       <c r="F12" s="234">
-        <v>37670094.600000001</v>
+        <v>41739148.850000001</v>
       </c>
       <c r="G12" s="234">
-        <v>303803271.30798399</v>
+        <v>317231971.32870501</v>
       </c>
       <c r="H12" s="111"/>
       <c r="I12" s="111"/>
@@ -6798,19 +6798,19 @@
         <v>114</v>
       </c>
       <c r="C13" s="234">
-        <v>21583616.169985998</v>
+        <v>24334967.469985999</v>
       </c>
       <c r="D13" s="234">
         <v>16536638.039975001</v>
       </c>
       <c r="E13" s="234">
-        <v>138116532.959694</v>
+        <v>139693109.55969399</v>
       </c>
       <c r="F13" s="234">
-        <v>51507668.189999998</v>
+        <v>52480641.210000001</v>
       </c>
       <c r="G13" s="234">
-        <v>227744455.35965499</v>
+        <v>233045356.27965501</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="111"/>
@@ -6823,19 +6823,19 @@
         <v>115</v>
       </c>
       <c r="C14" s="234">
-        <v>313943352.84965998</v>
+        <v>347582298.36464101</v>
       </c>
       <c r="D14" s="234">
         <v>30269657.985479001</v>
       </c>
       <c r="E14" s="234">
-        <v>101974162.349902</v>
+        <v>108883833.48989999</v>
       </c>
       <c r="F14" s="234">
-        <v>250228878.32984</v>
+        <v>279248599.70980501</v>
       </c>
       <c r="G14" s="234">
-        <v>696416051.51488101</v>
+        <v>765984389.54982495</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="111"/>
@@ -6848,19 +6848,19 @@
         <v>118</v>
       </c>
       <c r="C15" s="234">
-        <v>1067496483.041103</v>
+        <v>1080265998.3800981</v>
       </c>
       <c r="D15" s="234">
-        <v>8138253.8869240005</v>
+        <v>8214253.8869240005</v>
       </c>
       <c r="E15" s="234">
         <v>58176052.949942999</v>
       </c>
       <c r="F15" s="234">
-        <v>10913513.77</v>
+        <v>12372973.210000001</v>
       </c>
       <c r="G15" s="234">
-        <v>1144724303.64797</v>
+        <v>1159029278.426965</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="111"/>
@@ -6873,19 +6873,19 @@
         <v>120</v>
       </c>
       <c r="C16" s="234">
-        <v>312494152.79274601</v>
+        <v>316453700.88274598</v>
       </c>
       <c r="D16" s="234">
         <v>29437089.039930999</v>
       </c>
       <c r="E16" s="234">
-        <v>210140451.63960499</v>
+        <v>214955766.96959001</v>
       </c>
       <c r="F16" s="234">
-        <v>668372515.47996902</v>
+        <v>653436569.67996895</v>
       </c>
       <c r="G16" s="234">
-        <v>1220444208.952251</v>
+        <v>1214283126.5722361</v>
       </c>
       <c r="H16" s="111"/>
       <c r="I16" s="111"/>
@@ -6898,19 +6898,19 @@
         <v>122</v>
       </c>
       <c r="C17" s="234">
-        <v>72865918.306536004</v>
+        <v>77739702.055029005</v>
       </c>
       <c r="D17" s="234">
         <v>11277436.9209</v>
       </c>
       <c r="E17" s="234">
-        <v>66284032.579031996</v>
+        <v>69347096.478862002</v>
       </c>
       <c r="F17" s="234">
-        <v>23000000.5</v>
+        <v>26050270.798</v>
       </c>
       <c r="G17" s="234">
-        <v>173427388.30646801</v>
+        <v>184414506.25279099</v>
       </c>
       <c r="H17" s="111"/>
       <c r="I17" s="111"/>
@@ -6924,19 +6924,19 @@
         <v>123</v>
       </c>
       <c r="C18" s="234">
-        <v>8992270</v>
+        <v>9312730</v>
       </c>
       <c r="D18" s="234">
-        <v>107181678.62261599</v>
+        <v>122949245.96236999</v>
       </c>
       <c r="E18" s="234">
-        <v>46461402</v>
+        <v>46851402</v>
       </c>
       <c r="F18" s="234">
-        <v>83978380.159999996</v>
+        <v>85535136.959999993</v>
       </c>
       <c r="G18" s="234">
-        <v>246613730.78261599</v>
+        <v>264648514.92236999</v>
       </c>
       <c r="H18" s="111"/>
       <c r="I18" s="111"/>
@@ -6950,7 +6950,7 @@
         <v>169</v>
       </c>
       <c r="C19" s="234">
-        <v>30253778.960000001</v>
+        <v>57858708.960000001</v>
       </c>
       <c r="D19" s="234" t="s">
         <v>165</v>
@@ -6962,7 +6962,7 @@
         <v>4684684.5599999996</v>
       </c>
       <c r="G19" s="234">
-        <v>34938463.520000003</v>
+        <v>62543393.520000003</v>
       </c>
       <c r="H19" s="111"/>
       <c r="I19" s="111"/>
@@ -7006,26 +7006,26 @@
         <v>124</v>
       </c>
       <c r="C21" s="234">
-        <v>177164270.058642</v>
+        <v>189312108.00953001</v>
       </c>
       <c r="D21" s="234">
-        <v>35900827.783471003</v>
+        <v>36741053.013470002</v>
       </c>
       <c r="E21" s="234">
-        <v>111568653.35986499</v>
+        <v>111820905.619865</v>
       </c>
       <c r="F21" s="234">
-        <v>290454016.77988499</v>
+        <v>297974557.80988503</v>
       </c>
       <c r="G21" s="234">
-        <v>615087767.98186302</v>
+        <v>635848624.45274997</v>
       </c>
       <c r="H21" s="111"/>
       <c r="I21" s="111"/>
       <c r="J21" s="111"/>
       <c r="M21" s="14">
         <f>SUM(C33,C34)+M20</f>
-        <v>454997313.98041403</v>
+        <v>463048341.06039</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>224</v>
@@ -7036,19 +7036,19 @@
         <v>125</v>
       </c>
       <c r="C22" s="234">
-        <v>172201414.51065901</v>
+        <v>184977926.462659</v>
       </c>
       <c r="D22" s="234">
-        <v>49903023.629965</v>
+        <v>52554915.529964998</v>
       </c>
       <c r="E22" s="234">
-        <v>126746353.23747499</v>
+        <v>131137974.866263</v>
       </c>
       <c r="F22" s="234">
-        <v>210355166.919631</v>
+        <v>219748464.559596</v>
       </c>
       <c r="G22" s="234">
-        <v>559205958.29772997</v>
+        <v>588419281.41848302</v>
       </c>
       <c r="H22" s="111"/>
       <c r="I22" s="111"/>
@@ -7059,19 +7059,19 @@
         <v>126</v>
       </c>
       <c r="C23" s="234">
-        <v>323500640.14265001</v>
+        <v>332139712.44659901</v>
       </c>
       <c r="D23" s="234">
-        <v>39057838.754964001</v>
+        <v>44095253.124923997</v>
       </c>
       <c r="E23" s="234">
-        <v>139958091.469908</v>
+        <v>146226785.16990799</v>
       </c>
       <c r="F23" s="234">
-        <v>390890270.92961597</v>
+        <v>418671352.45959097</v>
       </c>
       <c r="G23" s="234">
-        <v>893406841.29713798</v>
+        <v>941133103.20102203</v>
       </c>
       <c r="H23" s="111"/>
       <c r="I23" s="111"/>
@@ -7082,19 +7082,19 @@
         <v>225</v>
       </c>
       <c r="C24" s="234">
-        <v>138586461.24244899</v>
+        <v>139761461.24244899</v>
       </c>
       <c r="D24" s="234">
-        <v>34780160.220744997</v>
+        <v>35731556.620745003</v>
       </c>
       <c r="E24" s="234">
-        <v>116499752.948219</v>
+        <v>116779032.14819901</v>
       </c>
       <c r="F24" s="234">
         <v>36782251.869999997</v>
       </c>
       <c r="G24" s="234">
-        <v>326648626.28141302</v>
+        <v>329054301.88139302</v>
       </c>
       <c r="H24" s="111"/>
       <c r="I24" s="111"/>
@@ -7105,19 +7105,19 @@
         <v>220</v>
       </c>
       <c r="C25" s="234">
-        <v>199516529.892643</v>
+        <v>217151311.43060201</v>
       </c>
       <c r="D25" s="234">
-        <v>62512341.996574</v>
+        <v>71426418.716557994</v>
       </c>
       <c r="E25" s="234">
-        <v>72789644.420606002</v>
+        <v>74463347.148591995</v>
       </c>
       <c r="F25" s="234">
-        <v>29729730.43</v>
+        <v>38054054.829999998</v>
       </c>
       <c r="G25" s="234">
-        <v>364548246.73982298</v>
+        <v>401095132.12575197</v>
       </c>
       <c r="H25" s="111"/>
       <c r="I25" s="111"/>
@@ -7128,10 +7128,10 @@
         <v>127</v>
       </c>
       <c r="C26" s="234">
-        <v>321648535.34862697</v>
+        <v>377468330.90861797</v>
       </c>
       <c r="D26" s="234">
-        <v>173348011.65299401</v>
+        <v>179429092.65289399</v>
       </c>
       <c r="E26" s="234">
         <v>223413017.625983</v>
@@ -7140,7 +7140,7 @@
         <v>15098054.3574</v>
       </c>
       <c r="G26" s="234">
-        <v>733507618.98500395</v>
+        <v>795408495.54489505</v>
       </c>
       <c r="H26" s="111"/>
       <c r="I26" s="111"/>
@@ -7183,7 +7183,7 @@
         <v>131</v>
       </c>
       <c r="C31" s="171">
-        <v>167182405.05536899</v>
+        <v>169720423.085361</v>
       </c>
       <c r="G31" s="111"/>
       <c r="H31" s="111"/>
@@ -7194,7 +7194,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="234">
-        <v>351088868.38575</v>
+        <v>390140315.413225</v>
       </c>
       <c r="G32" s="111"/>
       <c r="H32" s="111"/>
@@ -7205,7 +7205,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="234">
-        <v>95000987.568413004</v>
+        <v>99344987.568413004</v>
       </c>
       <c r="G33" s="111"/>
       <c r="H33" s="111"/>
@@ -7216,7 +7216,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="234">
-        <v>359996326.41200101</v>
+        <v>363703353.49197698</v>
       </c>
       <c r="G34" s="111"/>
       <c r="H34" s="111"/>
@@ -7271,13 +7271,13 @@
       </c>
       <c r="F40" s="174">
         <f ca="1">IF(MONTH(TODAY())=9,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;9,1,0))</f>
-        <v>0.6</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="G40" s="192" t="s">
         <v>187</v>
       </c>
       <c r="H40" s="198">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="I40" s="201" t="s">
         <v>187</v>
@@ -7314,12 +7314,12 @@
       <c r="G41" s="182" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
-100%</v>
+95%</v>
       </c>
       <c r="H41" s="182" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
-100%</v>
+95%</v>
       </c>
       <c r="I41" s="202" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
@@ -7358,35 +7358,35 @@
       </c>
       <c r="E42" s="46">
         <f>H65</f>
-        <v>2437125004.4134622</v>
+        <v>2623124454.4023442</v>
       </c>
       <c r="F42" s="176">
         <f>IFERROR(E42/D42,0)</f>
-        <v>0.54016856876857799</v>
+        <v>0.58139380609136249</v>
       </c>
       <c r="G42" s="184">
         <f>D42*$H$40-E42</f>
-        <v>2074661029.285934</v>
+        <v>1663072277.612082</v>
       </c>
       <c r="H42" s="184">
         <f ca="1">IFERROR(G42/$C$3,0)</f>
-        <v>188605548.1169031</v>
+        <v>166307227.76120821</v>
       </c>
       <c r="I42" s="204">
         <f>D42*$J$40-E42</f>
-        <v>2074661029.285934</v>
+        <v>1888661579.2970519</v>
       </c>
       <c r="J42" s="204">
         <f ca="1">IFERROR(I42/$C$3,0)</f>
-        <v>188605548.1169031</v>
+        <v>188866157.9297052</v>
       </c>
       <c r="K42" s="185">
         <f>D42*$L$40-E42</f>
-        <v>2074661029.285934</v>
+        <v>1888661579.2970519</v>
       </c>
       <c r="L42" s="185">
         <f ca="1">IFERROR(K42/$C$3,0)</f>
-        <v>188605548.1169031</v>
+        <v>188866157.9297052</v>
       </c>
       <c r="S42" s="173">
         <v>0.8</v>
@@ -7405,35 +7405,35 @@
       </c>
       <c r="E43" s="46">
         <f>I65</f>
-        <v>690350593.50908601</v>
+        <v>731233396.76878297</v>
       </c>
       <c r="F43" s="176">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.49262714606170649</v>
+        <v>0.52180069770660953</v>
       </c>
       <c r="G43" s="184">
         <f>D43*$H$40-E43</f>
-        <v>711014717.00632894</v>
+        <v>600063648.22086108</v>
       </c>
       <c r="H43" s="184">
         <f ca="1">IFERROR(G43/$C$3,0)</f>
-        <v>64637701.546029903</v>
+        <v>60006364.822086111</v>
       </c>
       <c r="I43" s="204">
         <f>D43*$J$40-E43</f>
-        <v>711014717.00632894</v>
+        <v>670131913.74663198</v>
       </c>
       <c r="J43" s="204">
         <f ca="1">IFERROR(I43/$C$3,0)</f>
-        <v>64637701.546029903</v>
+        <v>67013191.374663197</v>
       </c>
       <c r="K43" s="185">
         <f>D43*$L$40-E43</f>
-        <v>711014717.00632894</v>
+        <v>670131913.74663198</v>
       </c>
       <c r="L43" s="185">
         <f ca="1">IFERROR(K43/$C$3,0)</f>
-        <v>64637701.546029903</v>
+        <v>67013191.374663197</v>
       </c>
       <c r="S43" s="173">
         <v>0.85</v>
@@ -7452,35 +7452,35 @@
       </c>
       <c r="E44" s="46">
         <f>J65</f>
-        <v>1758290800.9763489</v>
+        <v>1824830311.192816</v>
       </c>
       <c r="F44" s="176">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.59708038733595448</v>
+        <v>0.61967587410704594</v>
       </c>
       <c r="G44" s="184">
         <f>IF(D44=0,0,D44*$H$40-E44)</f>
-        <v>1186523395.3523364</v>
+        <v>972743175.31943488</v>
       </c>
       <c r="H44" s="184">
         <f ca="1">IFERROR(G44/$C$3,0)</f>
-        <v>107865763.21384877</v>
+        <v>97274317.531943485</v>
       </c>
       <c r="I44" s="204">
         <f>IF(D44=0,0,D44*$J$40-E44)</f>
-        <v>1186523395.3523364</v>
+        <v>1119983885.1358693</v>
       </c>
       <c r="J44" s="204">
         <f ca="1">IFERROR(I44/$C$3,0)</f>
-        <v>107865763.21384877</v>
+        <v>111998388.51358692</v>
       </c>
       <c r="K44" s="185">
         <f>IF(D44=0,0,D44*$L$40-E44)</f>
-        <v>1186523395.3523364</v>
+        <v>1119983885.1358693</v>
       </c>
       <c r="L44" s="185">
         <f ca="1">IFERROR(K44/$C$3,0)</f>
-        <v>107865763.21384877</v>
+        <v>111998388.51358692</v>
       </c>
       <c r="S44" s="173">
         <v>0.9</v>
@@ -7499,35 +7499,35 @@
       </c>
       <c r="E45" s="46">
         <f>E74</f>
-        <v>973268587.42153299</v>
+        <v>1022909079.5589759</v>
       </c>
       <c r="F45" s="176">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.55921300255271456</v>
+        <v>0.58773504571237001</v>
       </c>
       <c r="G45" s="184">
         <f>D45*$H$40-E45</f>
-        <v>767156944.49336064</v>
+        <v>630495175.76017284</v>
       </c>
       <c r="H45" s="184">
         <f ca="1">IFERROR(G45/$C$3,0)</f>
-        <v>69741540.408487335</v>
+        <v>63049517.576017283</v>
       </c>
       <c r="I45" s="204">
         <f>D45*$J$40-E45</f>
-        <v>767156944.49336064</v>
+        <v>717516452.35591769</v>
       </c>
       <c r="J45" s="204">
         <f ca="1">IFERROR(I45/$C$3,0)</f>
-        <v>69741540.408487335</v>
+        <v>71751645.235591769</v>
       </c>
       <c r="K45" s="185">
         <f>D45*$L$40-E45</f>
-        <v>767156944.49336064</v>
+        <v>717516452.35591769</v>
       </c>
       <c r="L45" s="185">
         <f ca="1">IFERROR(K45/$C$3,0)</f>
-        <v>69741540.408487335</v>
+        <v>71751645.235591769</v>
       </c>
       <c r="S45" s="173">
         <v>0.95</v>
@@ -7544,35 +7544,35 @@
       </c>
       <c r="E46" s="47">
         <f>SUM(E42:E45)</f>
-        <v>5859034986.3204298</v>
+        <v>6202097241.9229193</v>
       </c>
       <c r="F46" s="177">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.55282306024223493</v>
+        <v>0.58519233716899333</v>
       </c>
       <c r="G46" s="181">
         <f>SUM(G42:G45)</f>
-        <v>4739356086.1379604</v>
+        <v>3866374276.9125509</v>
       </c>
       <c r="H46" s="181">
         <f ca="1">IFERROR(G46/$C$3,0)</f>
-        <v>430850553.28526914</v>
+        <v>386637427.69125509</v>
       </c>
       <c r="I46" s="186">
         <f>SUM(I42:I45)</f>
-        <v>4739356086.1379604</v>
+        <v>4396293830.535471</v>
       </c>
       <c r="J46" s="186">
         <f ca="1">IFERROR(I46/$C$3,0)</f>
-        <v>430850553.28526914</v>
+        <v>439629383.05354708</v>
       </c>
       <c r="K46" s="186">
         <f>SUM(K42:K45)</f>
-        <v>4739356086.1379604</v>
+        <v>4396293830.535471</v>
       </c>
       <c r="L46" s="186">
         <f ca="1">IFERROR(K46/$C$3,0)</f>
-        <v>430850553.28526914</v>
+        <v>439629383.05354708</v>
       </c>
       <c r="S46" s="173">
         <v>1</v>
@@ -7632,12 +7632,12 @@
       <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
-100%</v>
+95%</v>
       </c>
       <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
-100%</v>
+95%</v>
       </c>
       <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
@@ -7726,47 +7726,47 @@
       </c>
       <c r="H51" s="114">
         <f>SUMIF($B$10:$B$26,$T51,C$10:C$26)+SUMIF($B$10:$B$26,$U51,C$10:C$26)</f>
-        <v>177164270.058642</v>
+        <v>189312108.00953001</v>
       </c>
       <c r="I51" s="114">
         <f t="shared" ref="I51:I64" si="1">SUMIF($B$10:$B$26,$T51,D$10:D$26)+SUMIF($B$10:$B$26,$U51,D$10:D$26)</f>
-        <v>35900827.783471003</v>
+        <v>36741053.013470002</v>
       </c>
       <c r="J51" s="114">
         <f t="shared" ref="J51:J64" si="2">SUMIF($B$10:$B$26,$T51,E$10:E$26)+SUMIF($B$10:$B$26,$U51,E$10:E$26)</f>
-        <v>111568653.35986499</v>
+        <v>111820905.619865</v>
       </c>
       <c r="K51" s="114">
         <f t="shared" ref="K51:K64" si="3">SUM(H51:J51)</f>
-        <v>324633751.20197803</v>
+        <v>337874066.642865</v>
       </c>
       <c r="L51" s="187">
         <f t="shared" ref="L51:L65" si="4">IFERROR(K51/G51,0)</f>
-        <v>0.63113190209485415</v>
+        <v>0.65687286537301859</v>
       </c>
       <c r="M51" s="184">
         <f t="shared" ref="M51:M64" si="5">G51*$H$40-K51</f>
-        <v>189733768.68483657</v>
+        <v>150775077.24960881</v>
       </c>
       <c r="N51" s="184">
         <f t="shared" ref="N51:N65" ca="1" si="6">IFERROR(M51/$C$3,0)</f>
-        <v>17248524.425894234</v>
+        <v>15077507.724960882</v>
       </c>
       <c r="O51" s="180">
         <f t="shared" ref="O51:O64" si="7">G51*$J$40-K51</f>
-        <v>189733768.68483657</v>
+        <v>176493453.24394959</v>
       </c>
       <c r="P51" s="180">
         <f t="shared" ref="P51:P65" ca="1" si="8">IFERROR(O51/$C$3,0)</f>
-        <v>17248524.425894234</v>
+        <v>17649345.32439496</v>
       </c>
       <c r="Q51" s="185">
         <f t="shared" ref="Q51:Q64" si="9">G51*$L$40-K51</f>
-        <v>189733768.68483657</v>
+        <v>176493453.24394959</v>
       </c>
       <c r="R51" s="185">
         <f t="shared" ref="R51:R65" ca="1" si="10">IFERROR(Q51/$C$3,0)</f>
-        <v>17248524.425894234</v>
+        <v>17649345.32439496</v>
       </c>
       <c r="T51" t="s">
         <v>124</v>
@@ -7800,47 +7800,47 @@
       </c>
       <c r="H52" s="114">
         <f t="shared" ref="H52:H64" si="11">SUMIF($B$10:$B$26,$T52,C$10:C$26)+SUMIF($B$10:$B$26,$U52,C$10:C$26)</f>
-        <v>137731268.00680199</v>
+        <v>141680591.97742301</v>
       </c>
       <c r="I52" s="114">
         <f t="shared" si="1"/>
-        <v>71071475.741447002</v>
+        <v>71710626.041547</v>
       </c>
       <c r="J52" s="114">
         <f t="shared" si="2"/>
-        <v>233567220.12939</v>
+        <v>242666319.52938998</v>
       </c>
       <c r="K52" s="114">
         <f t="shared" si="3"/>
-        <v>442369963.877639</v>
+        <v>456057537.54835999</v>
       </c>
       <c r="L52" s="187">
         <f t="shared" si="4"/>
-        <v>0.56315278801948365</v>
+        <v>0.58057755892011542</v>
       </c>
       <c r="M52" s="184">
         <f t="shared" si="5"/>
-        <v>343153917.54250258</v>
+        <v>290190149.80077446</v>
       </c>
       <c r="N52" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>31195810.685682055</v>
+        <v>29019014.980077446</v>
       </c>
       <c r="O52" s="180">
         <f t="shared" si="7"/>
-        <v>343153917.54250258</v>
+        <v>329466343.87178159</v>
       </c>
       <c r="P52" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>31195810.685682055</v>
+        <v>32946634.38717816</v>
       </c>
       <c r="Q52" s="185">
         <f t="shared" si="9"/>
-        <v>343153917.54250258</v>
+        <v>329466343.87178159</v>
       </c>
       <c r="R52" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>31195810.685682055</v>
+        <v>32946634.38717816</v>
       </c>
       <c r="T52" t="s">
         <v>70</v>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="H53" s="114">
         <f t="shared" si="11"/>
-        <v>30253778.960000001</v>
+        <v>57858708.960000001</v>
       </c>
       <c r="I53" s="114">
         <f t="shared" si="1"/>
@@ -7886,35 +7886,35 @@
       </c>
       <c r="K53" s="114">
         <f t="shared" si="3"/>
-        <v>30253778.960000001</v>
+        <v>57858708.960000001</v>
       </c>
       <c r="L53" s="187">
         <f t="shared" si="4"/>
-        <v>0.11505389507665395</v>
+        <v>0.22003432492700731</v>
       </c>
       <c r="M53" s="184">
         <f t="shared" si="5"/>
-        <v>232699326.10301074</v>
+        <v>191946740.84986019</v>
       </c>
       <c r="N53" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>21154484.191182796</v>
+        <v>19194674.08498602</v>
       </c>
       <c r="O53" s="180">
         <f t="shared" si="7"/>
-        <v>232699326.10301074</v>
+        <v>205094396.10301074</v>
       </c>
       <c r="P53" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>21154484.191182796</v>
+        <v>20509439.610301074</v>
       </c>
       <c r="Q53" s="185">
         <f t="shared" si="9"/>
-        <v>232699326.10301074</v>
+        <v>205094396.10301074</v>
       </c>
       <c r="R53" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>21154484.191182796</v>
+        <v>20509439.610301074</v>
       </c>
       <c r="T53" t="s">
         <v>169</v>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="H54" s="114">
         <f t="shared" si="11"/>
-        <v>313943352.84965998</v>
+        <v>347582298.36464101</v>
       </c>
       <c r="I54" s="114">
         <f t="shared" si="1"/>
@@ -7956,39 +7956,39 @@
       </c>
       <c r="J54" s="114">
         <f t="shared" si="2"/>
-        <v>101974162.349902</v>
+        <v>108883833.48989999</v>
       </c>
       <c r="K54" s="114">
         <f t="shared" si="3"/>
-        <v>446187173.18504095</v>
+        <v>486735789.84002</v>
       </c>
       <c r="L54" s="187">
         <f t="shared" si="4"/>
-        <v>0.61401470070861475</v>
+        <v>0.66981515445502926</v>
       </c>
       <c r="M54" s="184">
         <f t="shared" si="5"/>
-        <v>280484635.60082459</v>
+        <v>203602428.50655228</v>
       </c>
       <c r="N54" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>25498603.236438598</v>
+        <v>20360242.850655228</v>
       </c>
       <c r="O54" s="180">
         <f t="shared" si="7"/>
-        <v>280484635.60082459</v>
+        <v>239936018.94584554</v>
       </c>
       <c r="P54" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>25498603.236438598</v>
+        <v>23993601.894584555</v>
       </c>
       <c r="Q54" s="185">
         <f t="shared" si="9"/>
-        <v>280484635.60082459</v>
+        <v>239936018.94584554</v>
       </c>
       <c r="R54" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>25498603.236438598</v>
+        <v>23993601.894584555</v>
       </c>
       <c r="T54" t="s">
         <v>115</v>
@@ -8030,39 +8030,39 @@
       </c>
       <c r="J55" s="114">
         <f t="shared" si="2"/>
-        <v>172635135.9993</v>
+        <v>199157658.6392</v>
       </c>
       <c r="K55" s="114">
         <f t="shared" si="3"/>
-        <v>193311875.01929802</v>
+        <v>219834397.65919799</v>
       </c>
       <c r="L55" s="187">
         <f t="shared" si="4"/>
-        <v>0.3598501774452893</v>
+        <v>0.40922187009123739</v>
       </c>
       <c r="M55" s="184">
         <f t="shared" si="5"/>
-        <v>343889124.55138761</v>
+        <v>290506551.93295336</v>
       </c>
       <c r="N55" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>31262647.686489783</v>
+        <v>29050655.193295337</v>
       </c>
       <c r="O55" s="180">
         <f t="shared" si="7"/>
-        <v>343889124.55138761</v>
+        <v>317366601.91148764</v>
       </c>
       <c r="P55" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>31262647.686489783</v>
+        <v>31736660.191148765</v>
       </c>
       <c r="Q55" s="185">
         <f t="shared" si="9"/>
-        <v>343889124.55138761</v>
+        <v>317366601.91148764</v>
       </c>
       <c r="R55" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>31262647.686489783</v>
+        <v>31736660.191148765</v>
       </c>
       <c r="T55" t="s">
         <v>182</v>
@@ -8096,47 +8096,47 @@
       </c>
       <c r="H56" s="114">
         <f t="shared" si="11"/>
-        <v>138586461.24244899</v>
+        <v>139761461.24244899</v>
       </c>
       <c r="I56" s="114">
         <f t="shared" si="1"/>
-        <v>34780160.220744997</v>
+        <v>35731556.620745003</v>
       </c>
       <c r="J56" s="114">
         <f t="shared" si="2"/>
-        <v>116499752.948219</v>
+        <v>116779032.14819901</v>
       </c>
       <c r="K56" s="114">
         <f t="shared" si="3"/>
-        <v>289866374.41141295</v>
+        <v>292272050.01139301</v>
       </c>
       <c r="L56" s="187">
         <f t="shared" si="4"/>
-        <v>0.50416279130418329</v>
+        <v>0.50834696798877133</v>
       </c>
       <c r="M56" s="184">
         <f t="shared" si="5"/>
-        <v>285079614.08880544</v>
+        <v>253926639.06381446</v>
       </c>
       <c r="N56" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>25916328.553527769</v>
+        <v>25392663.906381447</v>
       </c>
       <c r="O56" s="180">
         <f t="shared" si="7"/>
-        <v>285079614.08880544</v>
+        <v>282673938.48882538</v>
       </c>
       <c r="P56" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>25916328.553527769</v>
+        <v>28267393.848882537</v>
       </c>
       <c r="Q56" s="185">
         <f t="shared" si="9"/>
-        <v>285079614.08880544</v>
+        <v>282673938.48882538</v>
       </c>
       <c r="R56" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>25916328.553527769</v>
+        <v>28267393.848882537</v>
       </c>
       <c r="T56" t="s">
         <v>225</v>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="H57" s="114">
         <f t="shared" si="11"/>
-        <v>312494152.79274601</v>
+        <v>316453700.88274598</v>
       </c>
       <c r="I57" s="114">
         <f t="shared" si="1"/>
@@ -8178,39 +8178,39 @@
       </c>
       <c r="J57" s="114">
         <f t="shared" si="2"/>
-        <v>210140451.63960499</v>
+        <v>214955766.96959001</v>
       </c>
       <c r="K57" s="114">
         <f t="shared" si="3"/>
-        <v>552071693.47228193</v>
+        <v>560846556.89226699</v>
       </c>
       <c r="L57" s="187">
         <f t="shared" si="4"/>
-        <v>0.49772775378908907</v>
+        <v>0.50563885140825093</v>
       </c>
       <c r="M57" s="184">
         <f t="shared" si="5"/>
-        <v>557112372.05246472</v>
+        <v>492878305.3562423</v>
       </c>
       <c r="N57" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>50646579.277496792</v>
+        <v>49287830.535624228</v>
       </c>
       <c r="O57" s="180">
         <f t="shared" si="7"/>
-        <v>557112372.05246472</v>
+        <v>548337508.63247967</v>
       </c>
       <c r="P57" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>50646579.277496792</v>
+        <v>54833750.863247968</v>
       </c>
       <c r="Q57" s="185">
         <f t="shared" si="9"/>
-        <v>557112372.05246472</v>
+        <v>548337508.63247967</v>
       </c>
       <c r="R57" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>50646579.277496792</v>
+        <v>54833750.863247968</v>
       </c>
       <c r="T57" t="s">
         <v>120</v>
@@ -8244,47 +8244,47 @@
       </c>
       <c r="H58" s="114">
         <f t="shared" si="11"/>
-        <v>172201414.51065901</v>
+        <v>184977926.462659</v>
       </c>
       <c r="I58" s="114">
         <f t="shared" si="1"/>
-        <v>49903023.629965</v>
+        <v>52554915.529964998</v>
       </c>
       <c r="J58" s="114">
         <f t="shared" si="2"/>
-        <v>126746353.23747499</v>
+        <v>131137974.866263</v>
       </c>
       <c r="K58" s="114">
         <f t="shared" si="3"/>
-        <v>348850791.37809902</v>
+        <v>368670816.85888696</v>
       </c>
       <c r="L58" s="187">
         <f t="shared" si="4"/>
-        <v>0.56762390159917142</v>
+        <v>0.59987356383658996</v>
       </c>
       <c r="M58" s="184">
         <f t="shared" si="5"/>
-        <v>265730078.79892987</v>
+        <v>215181009.80929041</v>
       </c>
       <c r="N58" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>24157279.890811805</v>
+        <v>21518100.980929039</v>
       </c>
       <c r="O58" s="180">
         <f t="shared" si="7"/>
-        <v>265730078.79892987</v>
+        <v>245910053.31814194</v>
       </c>
       <c r="P58" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>24157279.890811805</v>
+        <v>24591005.331814192</v>
       </c>
       <c r="Q58" s="185">
         <f t="shared" si="9"/>
-        <v>265730078.79892987</v>
+        <v>245910053.31814194</v>
       </c>
       <c r="R58" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>24157279.890811805</v>
+        <v>24591005.331814192</v>
       </c>
       <c r="T58" t="s">
         <v>125</v>
@@ -8338,11 +8338,11 @@
       </c>
       <c r="M59" s="184">
         <f t="shared" si="5"/>
-        <v>316711248.41641998</v>
+        <v>294518912.63759899</v>
       </c>
       <c r="N59" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>28791931.674219999</v>
+        <v>29451891.2637599</v>
       </c>
       <c r="O59" s="180">
         <f t="shared" si="7"/>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="P59" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>28791931.674219999</v>
+        <v>31671124.841642</v>
       </c>
       <c r="Q59" s="185">
         <f t="shared" si="9"/>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="R59" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>28791931.674219999</v>
+        <v>31671124.841642</v>
       </c>
       <c r="T59" t="s">
         <v>170</v>
@@ -8392,47 +8392,47 @@
       </c>
       <c r="H60" s="114">
         <f t="shared" si="11"/>
-        <v>199516529.892643</v>
+        <v>217151311.43060201</v>
       </c>
       <c r="I60" s="114">
         <f t="shared" si="1"/>
-        <v>62512341.996574</v>
+        <v>71426418.716557994</v>
       </c>
       <c r="J60" s="114">
         <f t="shared" si="2"/>
-        <v>72789644.420606002</v>
+        <v>74463347.148591995</v>
       </c>
       <c r="K60" s="114">
         <f t="shared" si="3"/>
-        <v>334818516.30982304</v>
+        <v>363041077.29575199</v>
       </c>
       <c r="L60" s="187">
         <f t="shared" si="4"/>
-        <v>0.57808440803945504</v>
+        <v>0.62681236562293319</v>
       </c>
       <c r="M60" s="184">
         <f t="shared" si="5"/>
-        <v>244367691.88656068</v>
+        <v>187185820.49081248</v>
       </c>
       <c r="N60" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>22215244.716960061</v>
+        <v>18718582.049081247</v>
       </c>
       <c r="O60" s="180">
         <f t="shared" si="7"/>
-        <v>244367691.88656068</v>
+        <v>216145130.90063173</v>
       </c>
       <c r="P60" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>22215244.716960061</v>
+        <v>21614513.090063173</v>
       </c>
       <c r="Q60" s="185">
         <f t="shared" si="9"/>
-        <v>244367691.88656068</v>
+        <v>216145130.90063173</v>
       </c>
       <c r="R60" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>22215244.716960061</v>
+        <v>21614513.090063173</v>
       </c>
       <c r="T60" t="s">
         <v>220</v>
@@ -8466,47 +8466,47 @@
       </c>
       <c r="H61" s="114">
         <f t="shared" si="11"/>
-        <v>323500640.14265001</v>
+        <v>332139712.44659901</v>
       </c>
       <c r="I61" s="114">
         <f t="shared" si="1"/>
-        <v>39057838.754964001</v>
+        <v>44095253.124923997</v>
       </c>
       <c r="J61" s="114">
         <f t="shared" si="2"/>
-        <v>139958091.469908</v>
+        <v>146226785.16990799</v>
       </c>
       <c r="K61" s="114">
         <f t="shared" si="3"/>
-        <v>502516570.367522</v>
+        <v>522461750.741431</v>
       </c>
       <c r="L61" s="187">
         <f t="shared" si="4"/>
-        <v>0.70125818913941185</v>
+        <v>0.72909154209897098</v>
       </c>
       <c r="M61" s="184">
         <f t="shared" si="5"/>
-        <v>214076231.18565953</v>
+        <v>158301410.7340914</v>
       </c>
       <c r="N61" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>19461475.562332686</v>
+        <v>15830141.07340914</v>
       </c>
       <c r="O61" s="180">
         <f t="shared" si="7"/>
-        <v>214076231.18565953</v>
+        <v>194131050.81175053</v>
       </c>
       <c r="P61" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>19461475.562332686</v>
+        <v>19413105.081175052</v>
       </c>
       <c r="Q61" s="185">
         <f t="shared" si="9"/>
-        <v>214076231.18565953</v>
+        <v>194131050.81175053</v>
       </c>
       <c r="R61" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>19461475.562332686</v>
+        <v>19413105.081175052</v>
       </c>
       <c r="T61" t="s">
         <v>126</v>
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H62" s="114">
         <f t="shared" si="11"/>
-        <v>96917521.722049996</v>
+        <v>100376981.08205</v>
       </c>
       <c r="I62" s="114">
         <f t="shared" si="1"/>
@@ -8548,39 +8548,39 @@
       </c>
       <c r="J62" s="114">
         <f t="shared" si="2"/>
-        <v>136252883.21706399</v>
+        <v>139127171.50706401</v>
       </c>
       <c r="K62" s="114">
         <f t="shared" si="3"/>
-        <v>262278140.49911398</v>
+        <v>268611888.14911401</v>
       </c>
       <c r="L62" s="187">
         <f t="shared" si="4"/>
-        <v>0.54982254290962729</v>
+        <v>0.56310019247830212</v>
       </c>
       <c r="M62" s="184">
         <f t="shared" si="5"/>
-        <v>214745117.06168753</v>
+        <v>184560206.53364742</v>
       </c>
       <c r="N62" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>19522283.369244322</v>
+        <v>18456020.65336474</v>
       </c>
       <c r="O62" s="180">
         <f t="shared" si="7"/>
-        <v>214745117.06168753</v>
+        <v>208411369.41168749</v>
       </c>
       <c r="P62" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>19522283.369244322</v>
+        <v>20841136.941168748</v>
       </c>
       <c r="Q62" s="185">
         <f t="shared" si="9"/>
-        <v>214745117.06168753</v>
+        <v>208411369.41168749</v>
       </c>
       <c r="R62" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>19522283.369244322</v>
+        <v>20841136.941168748</v>
       </c>
       <c r="T62" t="s">
         <v>112</v>
@@ -8614,11 +8614,11 @@
       </c>
       <c r="H63" s="114">
         <f t="shared" si="11"/>
-        <v>321648535.34862697</v>
+        <v>377468330.90861797</v>
       </c>
       <c r="I63" s="114">
         <f t="shared" si="1"/>
-        <v>173348011.65299401</v>
+        <v>179429092.65289399</v>
       </c>
       <c r="J63" s="114">
         <f t="shared" si="2"/>
@@ -8626,35 +8626,35 @@
       </c>
       <c r="K63" s="114">
         <f t="shared" si="3"/>
-        <v>718409564.62760401</v>
+        <v>780310441.18749499</v>
       </c>
       <c r="L63" s="187">
         <f t="shared" si="4"/>
-        <v>0.73383927112825775</v>
+        <v>0.79706962937168868</v>
       </c>
       <c r="M63" s="184">
         <f t="shared" si="5"/>
-        <v>260564432.66620255</v>
+        <v>149714856.24162114</v>
       </c>
       <c r="N63" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>23687675.696927503</v>
+        <v>14971485.624162113</v>
       </c>
       <c r="O63" s="180">
         <f t="shared" si="7"/>
-        <v>260564432.66620255</v>
+        <v>198663556.10631156</v>
       </c>
       <c r="P63" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>23687675.696927503</v>
+        <v>19866355.610631157</v>
       </c>
       <c r="Q63" s="185">
         <f t="shared" si="9"/>
-        <v>260564432.66620255</v>
+        <v>198663556.10631156</v>
       </c>
       <c r="R63" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>23687675.696927503</v>
+        <v>19866355.610631157</v>
       </c>
       <c r="T63" t="s">
         <v>127</v>
@@ -8688,47 +8688,47 @@
       </c>
       <c r="H64" s="114">
         <f t="shared" si="11"/>
-        <v>81858188.306536004</v>
+        <v>87052432.055029005</v>
       </c>
       <c r="I64" s="114">
         <f t="shared" si="1"/>
-        <v>118459115.543516</v>
+        <v>134226682.88327</v>
       </c>
       <c r="J64" s="114">
         <f t="shared" si="2"/>
-        <v>112745434.579032</v>
+        <v>116198498.478862</v>
       </c>
       <c r="K64" s="114">
         <f t="shared" si="3"/>
-        <v>313062738.429084</v>
+        <v>337477613.41716099</v>
       </c>
       <c r="L64" s="187">
         <f t="shared" si="4"/>
-        <v>0.58307764559664343</v>
+        <v>0.62855021731507243</v>
       </c>
       <c r="M64" s="184">
         <f t="shared" si="5"/>
-        <v>223851583.00530678</v>
+        <v>172590991.94551021</v>
       </c>
       <c r="N64" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>20350143.909573343</v>
+        <v>17259099.194551021</v>
       </c>
       <c r="O64" s="180">
         <f t="shared" si="7"/>
-        <v>223851583.00530678</v>
+        <v>199436708.0172298</v>
       </c>
       <c r="P64" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>20350143.909573343</v>
+        <v>19943670.801722981</v>
       </c>
       <c r="Q64" s="185">
         <f t="shared" si="9"/>
-        <v>223851583.00530678</v>
+        <v>199436708.0172298</v>
       </c>
       <c r="R64" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>20350143.909573343</v>
+        <v>19943670.801722981</v>
       </c>
       <c r="T64" t="s">
         <v>122</v>
@@ -8760,47 +8760,47 @@
       </c>
       <c r="H65" s="135">
         <f t="shared" si="12"/>
-        <v>2437125004.4134622</v>
+        <v>2623124454.4023442</v>
       </c>
       <c r="I65" s="135">
         <f t="shared" si="12"/>
-        <v>690350593.50908601</v>
+        <v>731233396.76878297</v>
       </c>
       <c r="J65" s="135">
         <f t="shared" si="12"/>
-        <v>1758290800.9763489</v>
+        <v>1824830311.192816</v>
       </c>
       <c r="K65" s="135">
         <f t="shared" si="12"/>
-        <v>4885766398.8988962</v>
+        <v>5179188162.3639421</v>
       </c>
       <c r="L65" s="189">
         <f t="shared" si="4"/>
-        <v>0.55156755538689106</v>
+        <v>0.58469274221698597</v>
       </c>
       <c r="M65" s="181">
         <f>SUM(M51:M64)</f>
-        <v>3972199141.6445985</v>
+        <v>3235879101.1523776</v>
       </c>
       <c r="N65" s="181">
         <f t="shared" ca="1" si="6"/>
-        <v>361109012.8767817</v>
+        <v>323587910.11523777</v>
       </c>
       <c r="O65" s="181">
         <f>SUM(O51:O64)</f>
-        <v>3972199141.6445985</v>
+        <v>3678777378.179553</v>
       </c>
       <c r="P65" s="181">
         <f t="shared" ca="1" si="8"/>
-        <v>361109012.8767817</v>
+        <v>367877737.81795532</v>
       </c>
       <c r="Q65" s="186">
         <f>SUM(Q51:Q64)</f>
-        <v>3972199141.6445985</v>
+        <v>3678777378.179553</v>
       </c>
       <c r="R65" s="186">
         <f t="shared" ca="1" si="10"/>
-        <v>361109012.8767817</v>
+        <v>367877737.81795532</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8844,12 +8844,12 @@
       <c r="G68" s="232" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
-100%</v>
+95%</v>
       </c>
       <c r="H68" s="232" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
-100%</v>
+95%</v>
       </c>
       <c r="I68" s="229" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
@@ -8885,35 +8885,35 @@
       </c>
       <c r="E69" s="114">
         <f>IFERROR($C$31,0)</f>
-        <v>167182405.05536899</v>
+        <v>169720423.085361</v>
       </c>
       <c r="F69" s="187">
         <f t="shared" ref="F69:F74" si="13">IFERROR(E69/D69,0)</f>
-        <v>0.65240003862993257</v>
+        <v>0.66230420922887723</v>
       </c>
       <c r="G69" s="184">
         <f>D69*$H$40-E69</f>
-        <v>89075098.249595642</v>
+        <v>73724205.054355383</v>
       </c>
       <c r="H69" s="184">
         <f t="shared" ref="H69:H74" ca="1" si="14">IFERROR(G69/$C$3,0)</f>
-        <v>8097736.2045086948</v>
+        <v>7372420.5054355385</v>
       </c>
       <c r="I69" s="204">
         <f>D69*$J$40-E69</f>
-        <v>89075098.249595642</v>
+        <v>86537080.219603628</v>
       </c>
       <c r="J69" s="204">
         <f t="shared" ref="J69:J74" ca="1" si="15">IFERROR(I69/$C$3,0)</f>
-        <v>8097736.2045086948</v>
+        <v>8653708.0219603628</v>
       </c>
       <c r="K69" s="185">
         <f>D69*$L$40-E69</f>
-        <v>89075098.249595642</v>
+        <v>86537080.219603628</v>
       </c>
       <c r="L69" s="185">
         <f t="shared" ref="L69:L74" ca="1" si="16">IFERROR(K69/$C$3,0)</f>
-        <v>8097736.2045086948</v>
+        <v>8653708.0219603628</v>
       </c>
     </row>
     <row r="70" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8929,35 +8929,35 @@
       </c>
       <c r="E70" s="114">
         <f>IFERROR($C$32,0)</f>
-        <v>351088868.38575</v>
+        <v>390140315.413225</v>
       </c>
       <c r="F70" s="187">
         <f t="shared" si="13"/>
-        <v>0.87869222014472315</v>
+        <v>0.97642873582010525</v>
       </c>
       <c r="G70" s="184">
         <f>D70*$H$40-E70</f>
-        <v>48469543.919214606</v>
+        <v>-10559823.723508656</v>
       </c>
       <c r="H70" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>4406322.1744740549</v>
+        <v>-1055982.3723508655</v>
       </c>
       <c r="I70" s="204">
         <f>D70*$J$40-E70</f>
-        <v>48469543.919214606</v>
+        <v>9418096.8917396069</v>
       </c>
       <c r="J70" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>4406322.1744740549</v>
+        <v>941809.68917396071</v>
       </c>
       <c r="K70" s="185">
         <f>D70*$L$40-E70</f>
-        <v>48469543.919214606</v>
+        <v>9418096.8917396069</v>
       </c>
       <c r="L70" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>4406322.1744740549</v>
+        <v>941809.68917396071</v>
       </c>
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.25">
@@ -8973,35 +8973,35 @@
       </c>
       <c r="E71" s="114">
         <f>M21</f>
-        <v>454997313.98041403</v>
+        <v>463048341.06039</v>
       </c>
       <c r="F71" s="187">
         <f t="shared" si="13"/>
-        <v>0.4195033006718985</v>
+        <v>0.42692627291826685</v>
       </c>
       <c r="G71" s="184">
         <f>D71*$H$40-E71</f>
-        <v>629612302.32455051</v>
+        <v>567330794.4293263</v>
       </c>
       <c r="H71" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>57237482.02950459</v>
+        <v>56733079.442932628</v>
       </c>
       <c r="I71" s="204">
         <f>D71*$J$40-E71</f>
-        <v>629612302.32455051</v>
+        <v>621561275.24457455</v>
       </c>
       <c r="J71" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>57237482.02950459</v>
+        <v>62156127.524457455</v>
       </c>
       <c r="K71" s="185">
         <f>D71*$L$40-E71</f>
-        <v>629612302.32455051</v>
+        <v>621561275.24457455</v>
       </c>
       <c r="L71" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>57237482.02950459</v>
+        <v>62156127.524457455</v>
       </c>
     </row>
     <row r="72" spans="2:21" hidden="1" x14ac:dyDescent="0.25">
@@ -9103,35 +9103,35 @@
       </c>
       <c r="E74" s="115">
         <f>SUM(E69:E73)</f>
-        <v>973268587.42153299</v>
+        <v>1022909079.5589759</v>
       </c>
       <c r="F74" s="177">
         <f t="shared" si="13"/>
-        <v>0.55921300255271456</v>
+        <v>0.58773504571237001</v>
       </c>
       <c r="G74" s="181">
         <f>SUM(G69:G73)</f>
-        <v>767156944.49336076</v>
+        <v>630495175.76017308</v>
       </c>
       <c r="H74" s="181">
         <f t="shared" ca="1" si="14"/>
-        <v>69741540.408487335</v>
+        <v>63049517.576017305</v>
       </c>
       <c r="I74" s="186">
         <f>SUM(I69:I73)</f>
-        <v>767156944.49336076</v>
+        <v>717516452.35591781</v>
       </c>
       <c r="J74" s="186">
         <f t="shared" ca="1" si="15"/>
-        <v>69741540.408487335</v>
+        <v>71751645.235591784</v>
       </c>
       <c r="K74" s="186">
         <f>SUM(K69:K73)</f>
-        <v>767156944.49336076</v>
+        <v>717516452.35591781</v>
       </c>
       <c r="L74" s="186">
         <f t="shared" ca="1" si="16"/>
-        <v>69741540.408487335</v>
+        <v>71751645.235591784</v>
       </c>
     </row>
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="D80" s="131">
         <f>SUMIF($B$10:$B$26,$T80,$F$10:$F$26)+SUMIF($B$10:$B$26,$U80,$F$10:$F$26)</f>
-        <v>290454016.77988499</v>
+        <v>297974557.80988503</v>
       </c>
       <c r="T80" t="str">
         <f t="shared" ref="T80:U93" si="17">T51</f>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="D81" s="132">
         <f t="shared" ref="D81:D93" si="18">SUMIF($B$10:$B$26,$T81,$F$10:$F$26)+SUMIF($B$10:$B$26,$U81,$F$10:$F$26)</f>
-        <v>89177762.789999992</v>
+        <v>94219790.060000002</v>
       </c>
       <c r="T81" t="str">
         <f t="shared" si="17"/>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="D83" s="131">
         <f t="shared" si="18"/>
-        <v>250228878.32984</v>
+        <v>279248599.70980501</v>
       </c>
       <c r="T83" t="str">
         <f t="shared" si="17"/>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="D86" s="132">
         <f t="shared" si="18"/>
-        <v>668372515.47996902</v>
+        <v>653436569.67996895</v>
       </c>
       <c r="T86" t="str">
         <f t="shared" si="17"/>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="D87" s="131">
         <f t="shared" si="18"/>
-        <v>210355166.919631</v>
+        <v>219748464.559596</v>
       </c>
       <c r="T87" t="str">
         <f t="shared" si="17"/>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D89" s="132">
         <f t="shared" si="18"/>
-        <v>29729730.43</v>
+        <v>38054054.829999998</v>
       </c>
       <c r="T89" t="str">
         <f t="shared" si="17"/>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="D90" s="131">
         <f t="shared" si="18"/>
-        <v>390890270.92961597</v>
+        <v>418671352.45959097</v>
       </c>
       <c r="T90" t="str">
         <f t="shared" si="17"/>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="D91" s="132">
         <f t="shared" si="18"/>
-        <v>100110649.099953</v>
+        <v>106507045.649948</v>
       </c>
       <c r="T91" t="str">
         <f t="shared" si="17"/>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="D93" s="132">
         <f t="shared" si="18"/>
-        <v>106978380.66</v>
+        <v>111585407.75799999</v>
       </c>
       <c r="T93" t="str">
         <f t="shared" si="17"/>
@@ -9454,7 +9454,7 @@
       <c r="C94" s="58"/>
       <c r="D94" s="120">
         <f>SUM(D80:D93)</f>
-        <v>2200784253.8862939</v>
+        <v>2283932724.9841938</v>
       </c>
     </row>
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9498,7 +9498,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="41" fitToHeight="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="40" fitToHeight="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -912,7 +912,7 @@
     <t>WIDI</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL —  19 SEPTEMBER 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL —  21 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>
@@ -2559,6 +2559,33 @@
     <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2589,33 +2616,6 @@
     <xf numFmtId="0" fontId="48" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2629,6 +2629,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2650,15 +2659,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4302,11 +4302,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="259" t="s">
         <v>219</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="260"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -4626,33 +4626,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="263"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="270"/>
+      <c r="Q48" s="270"/>
+      <c r="R48" s="271"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -4661,49 +4661,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="268"/>
+      <c r="C50" s="268"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -4728,13 +4728,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="273"/>
+      <c r="N50" s="273"/>
+      <c r="O50" s="275"/>
+      <c r="P50" s="275"/>
+      <c r="Q50" s="277"/>
+      <c r="R50" s="277"/>
       <c r="T50" s="172" t="s">
         <v>216</v>
       </c>
@@ -5850,21 +5850,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="283" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
-      <c r="F67" s="292"/>
-      <c r="G67" s="260" t="s">
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
+      <c r="F67" s="285"/>
+      <c r="G67" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="270"/>
+      <c r="I67" s="270"/>
+      <c r="J67" s="270"/>
+      <c r="K67" s="270"/>
+      <c r="L67" s="271"/>
     </row>
     <row r="68" spans="2:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -6183,10 +6183,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -6498,12 +6498,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -6518,6 +6512,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="C3" s="75">
         <f ca="1">IF($J$5&lt;&gt;"",$J$5,MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),9,1)),EOMONTH(DATE(YEAR(TODAY()),9,1),0),11)-MAX(0,$J$3-$J$4)))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="76" t="s">
         <v>104</v>
@@ -6726,16 +6726,16 @@
         <v>100376981.08205</v>
       </c>
       <c r="D10" s="234">
-        <v>29107735.559999999</v>
+        <v>29510144.3829</v>
       </c>
       <c r="E10" s="234">
-        <v>139127171.50706401</v>
+        <v>144605955.29704899</v>
       </c>
       <c r="F10" s="234">
-        <v>106507045.649948</v>
+        <v>109734631.169943</v>
       </c>
       <c r="G10" s="234">
-        <v>375118933.79906201</v>
+        <v>384227711.93194199</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="111"/>
@@ -6773,19 +6773,19 @@
         <v>70</v>
       </c>
       <c r="C12" s="234">
-        <v>117345624.50743701</v>
+        <v>120586922.06740101</v>
       </c>
       <c r="D12" s="234">
-        <v>55173988.001571998</v>
+        <v>55970384.421572</v>
       </c>
       <c r="E12" s="234">
-        <v>102973209.969696</v>
+        <v>128256940.11960401</v>
       </c>
       <c r="F12" s="234">
         <v>41739148.850000001</v>
       </c>
       <c r="G12" s="234">
-        <v>317231971.32870501</v>
+        <v>346553395.45857698</v>
       </c>
       <c r="H12" s="111"/>
       <c r="I12" s="111"/>
@@ -6798,19 +6798,19 @@
         <v>114</v>
       </c>
       <c r="C13" s="234">
-        <v>24334967.469985999</v>
+        <v>26518751.469962001</v>
       </c>
       <c r="D13" s="234">
-        <v>16536638.039975001</v>
+        <v>17619678.599973001</v>
       </c>
       <c r="E13" s="234">
-        <v>139693109.55969399</v>
+        <v>147359776.31966901</v>
       </c>
       <c r="F13" s="234">
-        <v>52480641.210000001</v>
+        <v>56084244.729999997</v>
       </c>
       <c r="G13" s="234">
-        <v>233045356.27965501</v>
+        <v>247582451.11960399</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="111"/>
@@ -6823,19 +6823,19 @@
         <v>115</v>
       </c>
       <c r="C14" s="234">
-        <v>347582298.36464101</v>
+        <v>376890096.94460398</v>
       </c>
       <c r="D14" s="234">
-        <v>30269657.985479001</v>
+        <v>31805739.065467</v>
       </c>
       <c r="E14" s="234">
-        <v>108883833.48989999</v>
+        <v>110763968.6099</v>
       </c>
       <c r="F14" s="234">
-        <v>279248599.70980501</v>
+        <v>306826077.50980502</v>
       </c>
       <c r="G14" s="234">
-        <v>765984389.54982495</v>
+        <v>826285882.129776</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="111"/>
@@ -6848,19 +6848,19 @@
         <v>118</v>
       </c>
       <c r="C15" s="234">
-        <v>1080265998.3800981</v>
+        <v>1083245254.250098</v>
       </c>
       <c r="D15" s="234">
         <v>8214253.8869240005</v>
       </c>
       <c r="E15" s="234">
-        <v>58176052.949942999</v>
+        <v>58257134.009943001</v>
       </c>
       <c r="F15" s="234">
         <v>12372973.210000001</v>
       </c>
       <c r="G15" s="234">
-        <v>1159029278.426965</v>
+        <v>1162089615.3569651</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="111"/>
@@ -6873,19 +6873,19 @@
         <v>120</v>
       </c>
       <c r="C16" s="234">
-        <v>316453700.88274598</v>
+        <v>342788950.89772499</v>
       </c>
       <c r="D16" s="234">
-        <v>29437089.039930999</v>
+        <v>30711589.039930999</v>
       </c>
       <c r="E16" s="234">
-        <v>214955766.96959001</v>
+        <v>248891217.44951999</v>
       </c>
       <c r="F16" s="234">
-        <v>653436569.67996895</v>
+        <v>751459090.97996902</v>
       </c>
       <c r="G16" s="234">
-        <v>1214283126.5722361</v>
+        <v>1373850848.3671451</v>
       </c>
       <c r="H16" s="111"/>
       <c r="I16" s="111"/>
@@ -6898,19 +6898,19 @@
         <v>122</v>
       </c>
       <c r="C17" s="234">
-        <v>77739702.055029005</v>
+        <v>82312134.715029001</v>
       </c>
       <c r="D17" s="234">
-        <v>11277436.9209</v>
+        <v>12915436.9209</v>
       </c>
       <c r="E17" s="234">
-        <v>69347096.478862002</v>
+        <v>70679078.968842</v>
       </c>
       <c r="F17" s="234">
-        <v>26050270.798</v>
+        <v>35293514.298</v>
       </c>
       <c r="G17" s="234">
-        <v>184414506.25279099</v>
+        <v>201200164.902771</v>
       </c>
       <c r="H17" s="111"/>
       <c r="I17" s="111"/>
@@ -6924,19 +6924,19 @@
         <v>123</v>
       </c>
       <c r="C18" s="234">
-        <v>9312730</v>
+        <v>11129847.589996999</v>
       </c>
       <c r="D18" s="234">
-        <v>122949245.96236999</v>
+        <v>127814110.76229</v>
       </c>
       <c r="E18" s="234">
-        <v>46851402</v>
+        <v>46995546.100000001</v>
       </c>
       <c r="F18" s="234">
-        <v>85535136.959999993</v>
+        <v>86745947.799999997</v>
       </c>
       <c r="G18" s="234">
-        <v>264648514.92236999</v>
+        <v>272685452.25228697</v>
       </c>
       <c r="H18" s="111"/>
       <c r="I18" s="111"/>
@@ -6959,10 +6959,10 @@
         <v>165</v>
       </c>
       <c r="F19" s="234">
-        <v>4684684.5599999996</v>
+        <v>7027026.8399999999</v>
       </c>
       <c r="G19" s="234">
-        <v>62543393.520000003</v>
+        <v>64885735.799999997</v>
       </c>
       <c r="H19" s="111"/>
       <c r="I19" s="111"/>
@@ -6976,7 +6976,7 @@
         <v>170</v>
       </c>
       <c r="C20" s="234">
-        <v>127135467.16</v>
+        <v>153958227.16</v>
       </c>
       <c r="D20" s="234" t="s">
         <v>165</v>
@@ -6985,17 +6985,17 @@
         <v>165</v>
       </c>
       <c r="F20" s="234">
-        <v>7921891.6799999997</v>
+        <v>9813783.5199999996</v>
       </c>
       <c r="G20" s="234">
-        <v>135057358.84</v>
+        <v>163772010.68000001</v>
       </c>
       <c r="H20" s="111"/>
       <c r="I20" s="111"/>
       <c r="J20" s="111"/>
       <c r="M20" s="14">
         <f>SUM(C30,C35)+M7</f>
-        <v>0</v>
+        <v>9300000</v>
       </c>
       <c r="N20" s="10" t="s">
         <v>223</v>
@@ -7006,26 +7006,26 @@
         <v>124</v>
       </c>
       <c r="C21" s="234">
-        <v>189312108.00953001</v>
+        <v>195897681.76952299</v>
       </c>
       <c r="D21" s="234">
-        <v>36741053.013470002</v>
+        <v>39009404.373457998</v>
       </c>
       <c r="E21" s="234">
-        <v>111820905.619865</v>
+        <v>118291581.639805</v>
       </c>
       <c r="F21" s="234">
-        <v>297974557.80988503</v>
+        <v>309253837.03988498</v>
       </c>
       <c r="G21" s="234">
-        <v>635848624.45274997</v>
+        <v>662452504.82267106</v>
       </c>
       <c r="H21" s="111"/>
       <c r="I21" s="111"/>
       <c r="J21" s="111"/>
       <c r="M21" s="14">
         <f>SUM(C33,C34)+M20</f>
-        <v>463048341.06039</v>
+        <v>483922631.14035797</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>224</v>
@@ -7036,19 +7036,19 @@
         <v>125</v>
       </c>
       <c r="C22" s="234">
-        <v>184977926.462659</v>
+        <v>190526075.07154801</v>
       </c>
       <c r="D22" s="234">
         <v>52554915.529964998</v>
       </c>
       <c r="E22" s="234">
-        <v>131137974.866263</v>
+        <v>135282119.23626</v>
       </c>
       <c r="F22" s="234">
-        <v>219748464.559596</v>
+        <v>229480815.92959601</v>
       </c>
       <c r="G22" s="234">
-        <v>588419281.41848302</v>
+        <v>607843925.76736903</v>
       </c>
       <c r="H22" s="111"/>
       <c r="I22" s="111"/>
@@ -7059,19 +7059,19 @@
         <v>126</v>
       </c>
       <c r="C23" s="234">
-        <v>332139712.44659901</v>
+        <v>340158082.01052099</v>
       </c>
       <c r="D23" s="234">
-        <v>44095253.124923997</v>
+        <v>45384772.724923998</v>
       </c>
       <c r="E23" s="234">
-        <v>146226785.16990799</v>
+        <v>148552415.809908</v>
       </c>
       <c r="F23" s="234">
-        <v>418671352.45959097</v>
+        <v>433853334.65957397</v>
       </c>
       <c r="G23" s="234">
-        <v>941133103.20102203</v>
+        <v>967948605.20492697</v>
       </c>
       <c r="H23" s="111"/>
       <c r="I23" s="111"/>
@@ -7082,19 +7082,19 @@
         <v>225</v>
       </c>
       <c r="C24" s="234">
-        <v>139761461.24244899</v>
+        <v>143534246.36451599</v>
       </c>
       <c r="D24" s="234">
-        <v>35731556.620745003</v>
+        <v>37310141.999944001</v>
       </c>
       <c r="E24" s="234">
-        <v>116779032.14819901</v>
+        <v>117280833.94819801</v>
       </c>
       <c r="F24" s="234">
-        <v>36782251.869999997</v>
+        <v>37502972.57</v>
       </c>
       <c r="G24" s="234">
-        <v>329054301.88139302</v>
+        <v>335628194.882658</v>
       </c>
       <c r="H24" s="111"/>
       <c r="I24" s="111"/>
@@ -7105,19 +7105,19 @@
         <v>220</v>
       </c>
       <c r="C25" s="234">
-        <v>217151311.43060201</v>
+        <v>225087203.80412</v>
       </c>
       <c r="D25" s="234">
-        <v>71426418.716557994</v>
+        <v>71590833.136556998</v>
       </c>
       <c r="E25" s="234">
-        <v>74463347.148591995</v>
+        <v>76570716.532584995</v>
       </c>
       <c r="F25" s="234">
         <v>38054054.829999998</v>
       </c>
       <c r="G25" s="234">
-        <v>401095132.12575197</v>
+        <v>411302808.303262</v>
       </c>
       <c r="H25" s="111"/>
       <c r="I25" s="111"/>
@@ -7128,19 +7128,19 @@
         <v>127</v>
       </c>
       <c r="C26" s="234">
-        <v>377468330.90861797</v>
+        <v>382275746.05234897</v>
       </c>
       <c r="D26" s="234">
-        <v>179429092.65289399</v>
+        <v>181355173.74289101</v>
       </c>
       <c r="E26" s="234">
-        <v>223413017.625983</v>
+        <v>225534639.125983</v>
       </c>
       <c r="F26" s="234">
         <v>15098054.3574</v>
       </c>
       <c r="G26" s="234">
-        <v>795408495.54489505</v>
+        <v>804263613.27862298</v>
       </c>
       <c r="H26" s="111"/>
       <c r="I26" s="111"/>
@@ -7183,7 +7183,7 @@
         <v>131</v>
       </c>
       <c r="C31" s="171">
-        <v>169720423.085361</v>
+        <v>170853939.695351</v>
       </c>
       <c r="G31" s="111"/>
       <c r="H31" s="111"/>
@@ -7194,7 +7194,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="234">
-        <v>390140315.413225</v>
+        <v>405654939.35102898</v>
       </c>
       <c r="G32" s="111"/>
       <c r="H32" s="111"/>
@@ -7205,7 +7205,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="234">
-        <v>99344987.568413004</v>
+        <v>103185244.188411</v>
       </c>
       <c r="G33" s="111"/>
       <c r="H33" s="111"/>
@@ -7216,7 +7216,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="234">
-        <v>363703353.49197698</v>
+        <v>371437386.95194697</v>
       </c>
       <c r="G34" s="111"/>
       <c r="H34" s="111"/>
@@ -7226,8 +7226,8 @@
       <c r="B35" s="81" t="s">
         <v>135</v>
       </c>
-      <c r="C35" s="15">
-        <v>0</v>
+      <c r="C35" s="234">
+        <v>9300000</v>
       </c>
       <c r="G35" s="111"/>
       <c r="H35" s="111"/>
@@ -7261,17 +7261,17 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="259" t="s">
         <v>228</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="260"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
       <c r="F40" s="174">
         <f ca="1">IF(MONTH(TODAY())=9,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;9,1,0))</f>
-        <v>0.6333333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="G40" s="192" t="s">
         <v>187</v>
@@ -7358,35 +7358,35 @@
       </c>
       <c r="E42" s="46">
         <f>H65</f>
-        <v>2623124454.4023442</v>
+        <v>2754073079.379343</v>
       </c>
       <c r="F42" s="176">
         <f>IFERROR(E42/D42,0)</f>
-        <v>0.58139380609136249</v>
+        <v>0.61041748407584984</v>
       </c>
       <c r="G42" s="184">
         <f>D42*$H$40-E42</f>
-        <v>1663072277.612082</v>
+        <v>1532123652.6350832</v>
       </c>
       <c r="H42" s="184">
         <f ca="1">IFERROR(G42/$C$3,0)</f>
-        <v>166307227.76120821</v>
+        <v>170235961.40389812</v>
       </c>
       <c r="I42" s="204">
         <f>D42*$J$40-E42</f>
-        <v>1888661579.2970519</v>
+        <v>1757712954.3200531</v>
       </c>
       <c r="J42" s="204">
         <f ca="1">IFERROR(I42/$C$3,0)</f>
-        <v>188866157.9297052</v>
+        <v>195301439.36889479</v>
       </c>
       <c r="K42" s="185">
         <f>D42*$L$40-E42</f>
-        <v>1888661579.2970519</v>
+        <v>1757712954.3200531</v>
       </c>
       <c r="L42" s="185">
         <f ca="1">IFERROR(K42/$C$3,0)</f>
-        <v>188866157.9297052</v>
+        <v>195301439.36889479</v>
       </c>
       <c r="S42" s="173">
         <v>0.8</v>
@@ -7405,35 +7405,35 @@
       </c>
       <c r="E43" s="46">
         <f>I65</f>
-        <v>731233396.76878297</v>
+        <v>750055640.30077207</v>
       </c>
       <c r="F43" s="176">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.52180069770660953</v>
+        <v>0.53523205881620217</v>
       </c>
       <c r="G43" s="184">
         <f>D43*$H$40-E43</f>
-        <v>600063648.22086108</v>
+        <v>581241404.68887198</v>
       </c>
       <c r="H43" s="184">
         <f ca="1">IFERROR(G43/$C$3,0)</f>
-        <v>60006364.822086111</v>
+        <v>64582378.298763551</v>
       </c>
       <c r="I43" s="204">
         <f>D43*$J$40-E43</f>
-        <v>670131913.74663198</v>
+        <v>651309670.21464288</v>
       </c>
       <c r="J43" s="204">
         <f ca="1">IFERROR(I43/$C$3,0)</f>
-        <v>67013191.374663197</v>
+        <v>72367741.134960324</v>
       </c>
       <c r="K43" s="185">
         <f>D43*$L$40-E43</f>
-        <v>670131913.74663198</v>
+        <v>651309670.21464288</v>
       </c>
       <c r="L43" s="185">
         <f ca="1">IFERROR(K43/$C$3,0)</f>
-        <v>67013191.374663197</v>
+        <v>72367741.134960324</v>
       </c>
       <c r="S43" s="173">
         <v>0.85</v>
@@ -7452,35 +7452,35 @@
       </c>
       <c r="E44" s="46">
         <f>J65</f>
-        <v>1824830311.192816</v>
+        <v>1918222447.7965229</v>
       </c>
       <c r="F44" s="176">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.61967587410704594</v>
+        <v>0.65138997570304447</v>
       </c>
       <c r="G44" s="184">
         <f>IF(D44=0,0,D44*$H$40-E44)</f>
-        <v>972743175.31943488</v>
+        <v>879351038.71572804</v>
       </c>
       <c r="H44" s="184">
         <f ca="1">IFERROR(G44/$C$3,0)</f>
-        <v>97274317.531943485</v>
+        <v>97705670.968414232</v>
       </c>
       <c r="I44" s="204">
         <f>IF(D44=0,0,D44*$J$40-E44)</f>
-        <v>1119983885.1358693</v>
+        <v>1026591748.5321624</v>
       </c>
       <c r="J44" s="204">
         <f ca="1">IFERROR(I44/$C$3,0)</f>
-        <v>111998388.51358692</v>
+        <v>114065749.83690694</v>
       </c>
       <c r="K44" s="185">
         <f>IF(D44=0,0,D44*$L$40-E44)</f>
-        <v>1119983885.1358693</v>
+        <v>1026591748.5321624</v>
       </c>
       <c r="L44" s="185">
         <f ca="1">IFERROR(K44/$C$3,0)</f>
-        <v>111998388.51358692</v>
+        <v>114065749.83690694</v>
       </c>
       <c r="S44" s="173">
         <v>0.9</v>
@@ -7499,35 +7499,35 @@
       </c>
       <c r="E45" s="46">
         <f>E74</f>
-        <v>1022909079.5589759</v>
+        <v>1060431510.186738</v>
       </c>
       <c r="F45" s="176">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.58773504571237001</v>
+        <v>0.60929438849360251</v>
       </c>
       <c r="G45" s="184">
         <f>D45*$H$40-E45</f>
-        <v>630495175.76017284</v>
+        <v>592972745.13241076</v>
       </c>
       <c r="H45" s="184">
         <f ca="1">IFERROR(G45/$C$3,0)</f>
-        <v>63049517.576017283</v>
+        <v>65885860.570267864</v>
       </c>
       <c r="I45" s="204">
         <f>D45*$J$40-E45</f>
-        <v>717516452.35591769</v>
+        <v>679994021.72815561</v>
       </c>
       <c r="J45" s="204">
         <f ca="1">IFERROR(I45/$C$3,0)</f>
-        <v>71751645.235591769</v>
+        <v>75554891.303128406</v>
       </c>
       <c r="K45" s="185">
         <f>D45*$L$40-E45</f>
-        <v>717516452.35591769</v>
+        <v>679994021.72815561</v>
       </c>
       <c r="L45" s="185">
         <f ca="1">IFERROR(K45/$C$3,0)</f>
-        <v>71751645.235591769</v>
+        <v>75554891.303128406</v>
       </c>
       <c r="S45" s="173">
         <v>0.95</v>
@@ -7544,35 +7544,35 @@
       </c>
       <c r="E46" s="47">
         <f>SUM(E42:E45)</f>
-        <v>6202097241.9229193</v>
+        <v>6482782677.6633759</v>
       </c>
       <c r="F46" s="177">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.58519233716899333</v>
+        <v>0.61167611511429509</v>
       </c>
       <c r="G46" s="181">
         <f>SUM(G42:G45)</f>
-        <v>3866374276.9125509</v>
+        <v>3585688841.1720943</v>
       </c>
       <c r="H46" s="181">
         <f ca="1">IFERROR(G46/$C$3,0)</f>
-        <v>386637427.69125509</v>
+        <v>398409871.2413438</v>
       </c>
       <c r="I46" s="186">
         <f>SUM(I42:I45)</f>
-        <v>4396293830.535471</v>
+        <v>4115608394.7950139</v>
       </c>
       <c r="J46" s="186">
         <f ca="1">IFERROR(I46/$C$3,0)</f>
-        <v>439629383.05354708</v>
+        <v>457289821.64389044</v>
       </c>
       <c r="K46" s="186">
         <f>SUM(K42:K45)</f>
-        <v>4396293830.535471</v>
+        <v>4115608394.7950139</v>
       </c>
       <c r="L46" s="186">
         <f ca="1">IFERROR(K46/$C$3,0)</f>
-        <v>439629383.05354708</v>
+        <v>457289821.64389044</v>
       </c>
       <c r="S46" s="173">
         <v>1</v>
@@ -7585,33 +7585,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="263"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="270"/>
+      <c r="Q48" s="270"/>
+      <c r="R48" s="271"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -7620,49 +7620,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="268"/>
+      <c r="C50" s="268"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -7687,13 +7687,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="273"/>
+      <c r="N50" s="273"/>
+      <c r="O50" s="275"/>
+      <c r="P50" s="275"/>
+      <c r="Q50" s="277"/>
+      <c r="R50" s="277"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -7726,47 +7726,47 @@
       </c>
       <c r="H51" s="114">
         <f>SUMIF($B$10:$B$26,$T51,C$10:C$26)+SUMIF($B$10:$B$26,$U51,C$10:C$26)</f>
-        <v>189312108.00953001</v>
+        <v>195897681.76952299</v>
       </c>
       <c r="I51" s="114">
         <f t="shared" ref="I51:I64" si="1">SUMIF($B$10:$B$26,$T51,D$10:D$26)+SUMIF($B$10:$B$26,$U51,D$10:D$26)</f>
-        <v>36741053.013470002</v>
+        <v>39009404.373457998</v>
       </c>
       <c r="J51" s="114">
         <f t="shared" ref="J51:J64" si="2">SUMIF($B$10:$B$26,$T51,E$10:E$26)+SUMIF($B$10:$B$26,$U51,E$10:E$26)</f>
-        <v>111820905.619865</v>
+        <v>118291581.639805</v>
       </c>
       <c r="K51" s="114">
         <f t="shared" ref="K51:K64" si="3">SUM(H51:J51)</f>
-        <v>337874066.642865</v>
+        <v>353198667.78278601</v>
       </c>
       <c r="L51" s="187">
         <f t="shared" ref="L51:L65" si="4">IFERROR(K51/G51,0)</f>
-        <v>0.65687286537301859</v>
+        <v>0.68666596184087703</v>
       </c>
       <c r="M51" s="184">
         <f t="shared" ref="M51:M64" si="5">G51*$H$40-K51</f>
-        <v>150775077.24960881</v>
+        <v>135450476.10968781</v>
       </c>
       <c r="N51" s="184">
         <f t="shared" ref="N51:N65" ca="1" si="6">IFERROR(M51/$C$3,0)</f>
-        <v>15077507.724960882</v>
+        <v>15050052.901076423</v>
       </c>
       <c r="O51" s="180">
         <f t="shared" ref="O51:O64" si="7">G51*$J$40-K51</f>
-        <v>176493453.24394959</v>
+        <v>161168852.10402858</v>
       </c>
       <c r="P51" s="180">
         <f t="shared" ref="P51:P65" ca="1" si="8">IFERROR(O51/$C$3,0)</f>
-        <v>17649345.32439496</v>
+        <v>17907650.233780954</v>
       </c>
       <c r="Q51" s="185">
         <f t="shared" ref="Q51:Q64" si="9">G51*$L$40-K51</f>
-        <v>176493453.24394959</v>
+        <v>161168852.10402858</v>
       </c>
       <c r="R51" s="185">
         <f t="shared" ref="R51:R65" ca="1" si="10">IFERROR(Q51/$C$3,0)</f>
-        <v>17649345.32439496</v>
+        <v>17907650.233780954</v>
       </c>
       <c r="T51" t="s">
         <v>124</v>
@@ -7800,47 +7800,47 @@
       </c>
       <c r="H52" s="114">
         <f t="shared" ref="H52:H64" si="11">SUMIF($B$10:$B$26,$T52,C$10:C$26)+SUMIF($B$10:$B$26,$U52,C$10:C$26)</f>
-        <v>141680591.97742301</v>
+        <v>147105673.53736299</v>
       </c>
       <c r="I52" s="114">
         <f t="shared" si="1"/>
-        <v>71710626.041547</v>
+        <v>73590063.021544993</v>
       </c>
       <c r="J52" s="114">
         <f t="shared" si="2"/>
-        <v>242666319.52938998</v>
+        <v>275616716.439273</v>
       </c>
       <c r="K52" s="114">
         <f t="shared" si="3"/>
-        <v>456057537.54835999</v>
+        <v>496312452.99818099</v>
       </c>
       <c r="L52" s="187">
         <f t="shared" si="4"/>
-        <v>0.58057755892011542</v>
+        <v>0.63182350624515982</v>
       </c>
       <c r="M52" s="184">
         <f t="shared" si="5"/>
-        <v>290190149.80077446</v>
+        <v>249935234.35095346</v>
       </c>
       <c r="N52" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>29019014.980077446</v>
+        <v>27770581.594550386</v>
       </c>
       <c r="O52" s="180">
         <f t="shared" si="7"/>
-        <v>329466343.87178159</v>
+        <v>289211428.42196059</v>
       </c>
       <c r="P52" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>32946634.38717816</v>
+        <v>32134603.157995623</v>
       </c>
       <c r="Q52" s="185">
         <f t="shared" si="9"/>
-        <v>329466343.87178159</v>
+        <v>289211428.42196059</v>
       </c>
       <c r="R52" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>32946634.38717816</v>
+        <v>32134603.157995623</v>
       </c>
       <c r="T52" t="s">
         <v>70</v>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="N53" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>19194674.08498602</v>
+        <v>21327415.649984464</v>
       </c>
       <c r="O53" s="180">
         <f t="shared" si="7"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P53" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>20509439.610301074</v>
+        <v>22788266.233667862</v>
       </c>
       <c r="Q53" s="185">
         <f t="shared" si="9"/>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="R53" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>20509439.610301074</v>
+        <v>22788266.233667862</v>
       </c>
       <c r="T53" t="s">
         <v>169</v>
@@ -7948,47 +7948,47 @@
       </c>
       <c r="H54" s="114">
         <f t="shared" si="11"/>
-        <v>347582298.36464101</v>
+        <v>376890096.94460398</v>
       </c>
       <c r="I54" s="114">
         <f t="shared" si="1"/>
-        <v>30269657.985479001</v>
+        <v>31805739.065467</v>
       </c>
       <c r="J54" s="114">
         <f t="shared" si="2"/>
-        <v>108883833.48989999</v>
+        <v>110763968.6099</v>
       </c>
       <c r="K54" s="114">
         <f t="shared" si="3"/>
-        <v>486735789.84002</v>
+        <v>519459804.61997098</v>
       </c>
       <c r="L54" s="187">
         <f t="shared" si="4"/>
-        <v>0.66981515445502926</v>
+        <v>0.714847883651758</v>
       </c>
       <c r="M54" s="184">
         <f t="shared" si="5"/>
-        <v>203602428.50655228</v>
+        <v>170878413.7266013</v>
       </c>
       <c r="N54" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>20360242.850655228</v>
+        <v>18986490.41406681</v>
       </c>
       <c r="O54" s="180">
         <f t="shared" si="7"/>
-        <v>239936018.94584554</v>
+        <v>207212004.16589457</v>
       </c>
       <c r="P54" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>23993601.894584555</v>
+        <v>23023556.018432729</v>
       </c>
       <c r="Q54" s="185">
         <f t="shared" si="9"/>
-        <v>239936018.94584554</v>
+        <v>207212004.16589457</v>
       </c>
       <c r="R54" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>23993601.894584555</v>
+        <v>23023556.018432729</v>
       </c>
       <c r="T54" t="s">
         <v>115</v>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="N55" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>29050655.193295337</v>
+        <v>32278505.770328149</v>
       </c>
       <c r="O55" s="180">
         <f t="shared" si="7"/>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="P55" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>31736660.191148765</v>
+        <v>35262955.767943069</v>
       </c>
       <c r="Q55" s="185">
         <f t="shared" si="9"/>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="R55" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>31736660.191148765</v>
+        <v>35262955.767943069</v>
       </c>
       <c r="T55" t="s">
         <v>182</v>
@@ -8096,47 +8096,47 @@
       </c>
       <c r="H56" s="114">
         <f t="shared" si="11"/>
-        <v>139761461.24244899</v>
+        <v>143534246.36451599</v>
       </c>
       <c r="I56" s="114">
         <f t="shared" si="1"/>
-        <v>35731556.620745003</v>
+        <v>37310141.999944001</v>
       </c>
       <c r="J56" s="114">
         <f t="shared" si="2"/>
-        <v>116779032.14819901</v>
+        <v>117280833.94819801</v>
       </c>
       <c r="K56" s="114">
         <f t="shared" si="3"/>
-        <v>292272050.01139301</v>
+        <v>298125222.31265801</v>
       </c>
       <c r="L56" s="187">
         <f t="shared" si="4"/>
-        <v>0.50834696798877133</v>
+        <v>0.51852735435259889</v>
       </c>
       <c r="M56" s="184">
         <f t="shared" si="5"/>
-        <v>253926639.06381446</v>
+        <v>248073466.76254946</v>
       </c>
       <c r="N56" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>25392663.906381447</v>
+        <v>27563718.529172163</v>
       </c>
       <c r="O56" s="180">
         <f t="shared" si="7"/>
-        <v>282673938.48882538</v>
+        <v>276820766.18756038</v>
       </c>
       <c r="P56" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>28267393.848882537</v>
+        <v>30757862.909728929</v>
       </c>
       <c r="Q56" s="185">
         <f t="shared" si="9"/>
-        <v>282673938.48882538</v>
+        <v>276820766.18756038</v>
       </c>
       <c r="R56" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>28267393.848882537</v>
+        <v>30757862.909728929</v>
       </c>
       <c r="T56" t="s">
         <v>225</v>
@@ -8170,47 +8170,47 @@
       </c>
       <c r="H57" s="114">
         <f t="shared" si="11"/>
-        <v>316453700.88274598</v>
+        <v>342788950.89772499</v>
       </c>
       <c r="I57" s="114">
         <f t="shared" si="1"/>
-        <v>29437089.039930999</v>
+        <v>30711589.039930999</v>
       </c>
       <c r="J57" s="114">
         <f t="shared" si="2"/>
-        <v>214955766.96959001</v>
+        <v>248891217.44951999</v>
       </c>
       <c r="K57" s="114">
         <f t="shared" si="3"/>
-        <v>560846556.89226699</v>
+        <v>622391757.38717604</v>
       </c>
       <c r="L57" s="187">
         <f t="shared" si="4"/>
-        <v>0.50563885140825093</v>
+        <v>0.5611257650845598</v>
       </c>
       <c r="M57" s="184">
         <f t="shared" si="5"/>
-        <v>492878305.3562423</v>
+        <v>431333104.86133325</v>
       </c>
       <c r="N57" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>49287830.535624228</v>
+        <v>47925900.540148139</v>
       </c>
       <c r="O57" s="180">
         <f t="shared" si="7"/>
-        <v>548337508.63247967</v>
+        <v>486792308.13757062</v>
       </c>
       <c r="P57" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>54833750.863247968</v>
+        <v>54088034.23750785</v>
       </c>
       <c r="Q57" s="185">
         <f t="shared" si="9"/>
-        <v>548337508.63247967</v>
+        <v>486792308.13757062</v>
       </c>
       <c r="R57" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>54833750.863247968</v>
+        <v>54088034.23750785</v>
       </c>
       <c r="T57" t="s">
         <v>120</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="H58" s="114">
         <f t="shared" si="11"/>
-        <v>184977926.462659</v>
+        <v>190526075.07154801</v>
       </c>
       <c r="I58" s="114">
         <f t="shared" si="1"/>
@@ -8252,39 +8252,39 @@
       </c>
       <c r="J58" s="114">
         <f t="shared" si="2"/>
-        <v>131137974.866263</v>
+        <v>135282119.23626</v>
       </c>
       <c r="K58" s="114">
         <f t="shared" si="3"/>
-        <v>368670816.85888696</v>
+        <v>378363109.83777303</v>
       </c>
       <c r="L58" s="187">
         <f t="shared" si="4"/>
-        <v>0.59987356383658996</v>
+        <v>0.61564413765235848</v>
       </c>
       <c r="M58" s="184">
         <f t="shared" si="5"/>
-        <v>215181009.80929041</v>
+        <v>205488716.83040434</v>
       </c>
       <c r="N58" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>21518100.980929039</v>
+        <v>22832079.647822704</v>
       </c>
       <c r="O58" s="180">
         <f t="shared" si="7"/>
-        <v>245910053.31814194</v>
+        <v>236217760.33925587</v>
       </c>
       <c r="P58" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>24591005.331814192</v>
+        <v>26246417.815472875</v>
       </c>
       <c r="Q58" s="185">
         <f t="shared" si="9"/>
-        <v>245910053.31814194</v>
+        <v>236217760.33925587</v>
       </c>
       <c r="R58" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>24591005.331814192</v>
+        <v>26246417.815472875</v>
       </c>
       <c r="T58" t="s">
         <v>125</v>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="H59" s="114">
         <f t="shared" si="11"/>
-        <v>127135467.16</v>
+        <v>153958227.16</v>
       </c>
       <c r="I59" s="114">
         <f t="shared" si="1"/>
@@ -8330,35 +8330,35 @@
       </c>
       <c r="K59" s="114">
         <f t="shared" si="3"/>
-        <v>127135467.16</v>
+        <v>153958227.16</v>
       </c>
       <c r="L59" s="187">
         <f t="shared" si="4"/>
-        <v>0.28644003143042351</v>
+        <v>0.34687251647239459</v>
       </c>
       <c r="M59" s="184">
         <f t="shared" si="5"/>
-        <v>294518912.63759899</v>
+        <v>267696152.63759902</v>
       </c>
       <c r="N59" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>29451891.2637599</v>
+        <v>29744016.959733225</v>
       </c>
       <c r="O59" s="180">
         <f t="shared" si="7"/>
-        <v>316711248.41641998</v>
+        <v>289888488.41641998</v>
       </c>
       <c r="P59" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>31671124.841642</v>
+        <v>32209832.046268888</v>
       </c>
       <c r="Q59" s="185">
         <f t="shared" si="9"/>
-        <v>316711248.41641998</v>
+        <v>289888488.41641998</v>
       </c>
       <c r="R59" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>31671124.841642</v>
+        <v>32209832.046268888</v>
       </c>
       <c r="T59" t="s">
         <v>170</v>
@@ -8392,47 +8392,47 @@
       </c>
       <c r="H60" s="114">
         <f t="shared" si="11"/>
-        <v>217151311.43060201</v>
+        <v>225087203.80412</v>
       </c>
       <c r="I60" s="114">
         <f t="shared" si="1"/>
-        <v>71426418.716557994</v>
+        <v>71590833.136556998</v>
       </c>
       <c r="J60" s="114">
         <f t="shared" si="2"/>
-        <v>74463347.148591995</v>
+        <v>76570716.532584995</v>
       </c>
       <c r="K60" s="114">
         <f t="shared" si="3"/>
-        <v>363041077.29575199</v>
+        <v>373248753.47326195</v>
       </c>
       <c r="L60" s="187">
         <f t="shared" si="4"/>
-        <v>0.62681236562293319</v>
+        <v>0.64443653559289371</v>
       </c>
       <c r="M60" s="184">
         <f t="shared" si="5"/>
-        <v>187185820.49081248</v>
+        <v>176978144.31330252</v>
       </c>
       <c r="N60" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>18718582.049081247</v>
+        <v>19664238.257033613</v>
       </c>
       <c r="O60" s="180">
         <f t="shared" si="7"/>
-        <v>216145130.90063173</v>
+        <v>205937454.72312176</v>
       </c>
       <c r="P60" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>21614513.090063173</v>
+        <v>22881939.413680196</v>
       </c>
       <c r="Q60" s="185">
         <f t="shared" si="9"/>
-        <v>216145130.90063173</v>
+        <v>205937454.72312176</v>
       </c>
       <c r="R60" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>21614513.090063173</v>
+        <v>22881939.413680196</v>
       </c>
       <c r="T60" t="s">
         <v>220</v>
@@ -8466,47 +8466,47 @@
       </c>
       <c r="H61" s="114">
         <f t="shared" si="11"/>
-        <v>332139712.44659901</v>
+        <v>340158082.01052099</v>
       </c>
       <c r="I61" s="114">
         <f t="shared" si="1"/>
-        <v>44095253.124923997</v>
+        <v>45384772.724923998</v>
       </c>
       <c r="J61" s="114">
         <f t="shared" si="2"/>
-        <v>146226785.16990799</v>
+        <v>148552415.809908</v>
       </c>
       <c r="K61" s="114">
         <f t="shared" si="3"/>
-        <v>522461750.741431</v>
+        <v>534095270.54535306</v>
       </c>
       <c r="L61" s="187">
         <f t="shared" si="4"/>
-        <v>0.72909154209897098</v>
+        <v>0.74532603368011296</v>
       </c>
       <c r="M61" s="184">
         <f t="shared" si="5"/>
-        <v>158301410.7340914</v>
+        <v>146667890.93016934</v>
       </c>
       <c r="N61" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>15830141.07340914</v>
+        <v>16296432.325574372</v>
       </c>
       <c r="O61" s="180">
         <f t="shared" si="7"/>
-        <v>194131050.81175053</v>
+        <v>182497531.00782847</v>
       </c>
       <c r="P61" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>19413105.081175052</v>
+        <v>20277503.445314273</v>
       </c>
       <c r="Q61" s="185">
         <f t="shared" si="9"/>
-        <v>194131050.81175053</v>
+        <v>182497531.00782847</v>
       </c>
       <c r="R61" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>19413105.081175052</v>
+        <v>20277503.445314273</v>
       </c>
       <c r="T61" t="s">
         <v>126</v>
@@ -8544,43 +8544,43 @@
       </c>
       <c r="I62" s="114">
         <f t="shared" si="1"/>
-        <v>29107735.559999999</v>
+        <v>29510144.3829</v>
       </c>
       <c r="J62" s="114">
         <f t="shared" si="2"/>
-        <v>139127171.50706401</v>
+        <v>144605955.29704899</v>
       </c>
       <c r="K62" s="114">
         <f t="shared" si="3"/>
-        <v>268611888.14911401</v>
+        <v>274493080.76199901</v>
       </c>
       <c r="L62" s="187">
         <f t="shared" si="4"/>
-        <v>0.56310019247830212</v>
+        <v>0.57542913560564091</v>
       </c>
       <c r="M62" s="184">
         <f t="shared" si="5"/>
-        <v>184560206.53364742</v>
+        <v>178679013.92076242</v>
       </c>
       <c r="N62" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>18456020.65336474</v>
+        <v>19853223.768973604</v>
       </c>
       <c r="O62" s="180">
         <f t="shared" si="7"/>
-        <v>208411369.41168749</v>
+        <v>202530176.7988025</v>
       </c>
       <c r="P62" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>20841136.941168748</v>
+        <v>22503352.977644723</v>
       </c>
       <c r="Q62" s="185">
         <f t="shared" si="9"/>
-        <v>208411369.41168749</v>
+        <v>202530176.7988025</v>
       </c>
       <c r="R62" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>20841136.941168748</v>
+        <v>22503352.977644723</v>
       </c>
       <c r="T62" t="s">
         <v>112</v>
@@ -8614,47 +8614,47 @@
       </c>
       <c r="H63" s="114">
         <f t="shared" si="11"/>
-        <v>377468330.90861797</v>
+        <v>382275746.05234897</v>
       </c>
       <c r="I63" s="114">
         <f t="shared" si="1"/>
-        <v>179429092.65289399</v>
+        <v>181355173.74289101</v>
       </c>
       <c r="J63" s="114">
         <f t="shared" si="2"/>
-        <v>223413017.625983</v>
+        <v>225534639.125983</v>
       </c>
       <c r="K63" s="114">
         <f t="shared" si="3"/>
-        <v>780310441.18749499</v>
+        <v>789165558.92122293</v>
       </c>
       <c r="L63" s="187">
         <f t="shared" si="4"/>
-        <v>0.79706962937168868</v>
+        <v>0.80611493369867415</v>
       </c>
       <c r="M63" s="184">
         <f t="shared" si="5"/>
-        <v>149714856.24162114</v>
+        <v>140859738.5078932</v>
       </c>
       <c r="N63" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>14971485.624162113</v>
+        <v>15651082.056432579</v>
       </c>
       <c r="O63" s="180">
         <f t="shared" si="7"/>
-        <v>198663556.10631156</v>
+        <v>189808438.37258363</v>
       </c>
       <c r="P63" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>19866355.610631157</v>
+        <v>21089826.485842627</v>
       </c>
       <c r="Q63" s="185">
         <f t="shared" si="9"/>
-        <v>198663556.10631156</v>
+        <v>189808438.37258363</v>
       </c>
       <c r="R63" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>19866355.610631157</v>
+        <v>21089826.485842627</v>
       </c>
       <c r="T63" t="s">
         <v>127</v>
@@ -8688,47 +8688,47 @@
       </c>
       <c r="H64" s="114">
         <f t="shared" si="11"/>
-        <v>87052432.055029005</v>
+        <v>93441982.305025995</v>
       </c>
       <c r="I64" s="114">
         <f t="shared" si="1"/>
-        <v>134226682.88327</v>
+        <v>140729547.68318999</v>
       </c>
       <c r="J64" s="114">
         <f t="shared" si="2"/>
-        <v>116198498.478862</v>
+        <v>117674625.06884199</v>
       </c>
       <c r="K64" s="114">
         <f t="shared" si="3"/>
-        <v>337477613.41716099</v>
+        <v>351846155.05705798</v>
       </c>
       <c r="L64" s="187">
         <f t="shared" si="4"/>
-        <v>0.62855021731507243</v>
+        <v>0.65531154787803969</v>
       </c>
       <c r="M64" s="184">
         <f t="shared" si="5"/>
-        <v>172590991.94551021</v>
+        <v>158222450.30561322</v>
       </c>
       <c r="N64" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>17259099.194551021</v>
+        <v>17580272.256179247</v>
       </c>
       <c r="O64" s="180">
         <f t="shared" si="7"/>
-        <v>199436708.0172298</v>
+        <v>185068166.37733281</v>
       </c>
       <c r="P64" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>19943670.801722981</v>
+        <v>20563129.597481422</v>
       </c>
       <c r="Q64" s="185">
         <f t="shared" si="9"/>
-        <v>199436708.0172298</v>
+        <v>185068166.37733281</v>
       </c>
       <c r="R64" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>19943670.801722981</v>
+        <v>20563129.597481422</v>
       </c>
       <c r="T64" t="s">
         <v>122</v>
@@ -8760,47 +8760,47 @@
       </c>
       <c r="H65" s="135">
         <f t="shared" si="12"/>
-        <v>2623124454.4023442</v>
+        <v>2754073079.379343</v>
       </c>
       <c r="I65" s="135">
         <f t="shared" si="12"/>
-        <v>731233396.76878297</v>
+        <v>750055640.30077207</v>
       </c>
       <c r="J65" s="135">
         <f t="shared" si="12"/>
-        <v>1824830311.192816</v>
+        <v>1918222447.7965229</v>
       </c>
       <c r="K65" s="135">
         <f t="shared" si="12"/>
-        <v>5179188162.3639421</v>
+        <v>5422351167.4766378</v>
       </c>
       <c r="L65" s="189">
         <f t="shared" si="4"/>
-        <v>0.58469274221698597</v>
+        <v>0.61214408011164378</v>
       </c>
       <c r="M65" s="181">
         <f>SUM(M51:M64)</f>
-        <v>3235879101.1523776</v>
+        <v>2992716096.0396829</v>
       </c>
       <c r="N65" s="181">
         <f t="shared" ca="1" si="6"/>
-        <v>323587910.11523777</v>
+        <v>332524010.67107588</v>
       </c>
       <c r="O65" s="181">
         <f>SUM(O51:O64)</f>
-        <v>3678777378.179553</v>
+        <v>3435614373.0668573</v>
       </c>
       <c r="P65" s="181">
         <f t="shared" ca="1" si="8"/>
-        <v>367877737.81795532</v>
+        <v>381734930.3407619</v>
       </c>
       <c r="Q65" s="186">
         <f>SUM(Q51:Q64)</f>
-        <v>3678777378.179553</v>
+        <v>3435614373.0668573</v>
       </c>
       <c r="R65" s="186">
         <f t="shared" ca="1" si="10"/>
-        <v>367877737.81795532</v>
+        <v>381734930.3407619</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8809,21 +8809,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="283" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="260" t="s">
+      <c r="G67" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="270"/>
+      <c r="I67" s="270"/>
+      <c r="J67" s="270"/>
+      <c r="K67" s="270"/>
+      <c r="L67" s="271"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -8885,35 +8885,35 @@
       </c>
       <c r="E69" s="114">
         <f>IFERROR($C$31,0)</f>
-        <v>169720423.085361</v>
+        <v>170853939.695351</v>
       </c>
       <c r="F69" s="187">
         <f t="shared" ref="F69:F74" si="13">IFERROR(E69/D69,0)</f>
-        <v>0.66230420922887723</v>
+        <v>0.66672755916154647</v>
       </c>
       <c r="G69" s="184">
         <f>D69*$H$40-E69</f>
-        <v>73724205.054355383</v>
+        <v>72590688.444365382</v>
       </c>
       <c r="H69" s="184">
         <f t="shared" ref="H69:H74" ca="1" si="14">IFERROR(G69/$C$3,0)</f>
-        <v>7372420.5054355385</v>
+        <v>8065632.0493739313</v>
       </c>
       <c r="I69" s="204">
         <f>D69*$J$40-E69</f>
-        <v>86537080.219603628</v>
+        <v>85403563.609613627</v>
       </c>
       <c r="J69" s="204">
         <f t="shared" ref="J69:J74" ca="1" si="15">IFERROR(I69/$C$3,0)</f>
-        <v>8653708.0219603628</v>
+        <v>9489284.8455126248</v>
       </c>
       <c r="K69" s="185">
         <f>D69*$L$40-E69</f>
-        <v>86537080.219603628</v>
+        <v>85403563.609613627</v>
       </c>
       <c r="L69" s="185">
         <f t="shared" ref="L69:L74" ca="1" si="16">IFERROR(K69/$C$3,0)</f>
-        <v>8653708.0219603628</v>
+        <v>9489284.8455126248</v>
       </c>
     </row>
     <row r="70" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8929,35 +8929,35 @@
       </c>
       <c r="E70" s="114">
         <f>IFERROR($C$32,0)</f>
-        <v>390140315.413225</v>
+        <v>405654939.35102898</v>
       </c>
       <c r="F70" s="187">
         <f t="shared" si="13"/>
-        <v>0.97642873582010525</v>
+        <v>1.0152581621568042</v>
       </c>
       <c r="G70" s="184">
         <f>D70*$H$40-E70</f>
-        <v>-10559823.723508656</v>
+        <v>-26074447.66131264</v>
       </c>
       <c r="H70" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>-1055982.3723508655</v>
+        <v>-2897160.8512569601</v>
       </c>
       <c r="I70" s="204">
         <f>D70*$J$40-E70</f>
-        <v>9418096.8917396069</v>
+        <v>-6096527.0460643768</v>
       </c>
       <c r="J70" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>941809.68917396071</v>
+        <v>-677391.89400715299</v>
       </c>
       <c r="K70" s="185">
         <f>D70*$L$40-E70</f>
-        <v>9418096.8917396069</v>
+        <v>-6096527.0460643768</v>
       </c>
       <c r="L70" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>941809.68917396071</v>
+        <v>-677391.89400715299</v>
       </c>
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.25">
@@ -8973,35 +8973,35 @@
       </c>
       <c r="E71" s="114">
         <f>M21</f>
-        <v>463048341.06039</v>
+        <v>483922631.14035797</v>
       </c>
       <c r="F71" s="187">
         <f t="shared" si="13"/>
-        <v>0.42692627291826685</v>
+        <v>0.44617217463826292</v>
       </c>
       <c r="G71" s="184">
         <f>D71*$H$40-E71</f>
-        <v>567330794.4293263</v>
+        <v>546456504.34935832</v>
       </c>
       <c r="H71" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>56733079.442932628</v>
+        <v>60717389.372150928</v>
       </c>
       <c r="I71" s="204">
         <f>D71*$J$40-E71</f>
-        <v>621561275.24457455</v>
+        <v>600686985.16460657</v>
       </c>
       <c r="J71" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>62156127.524457455</v>
+        <v>66742998.351622954</v>
       </c>
       <c r="K71" s="185">
         <f>D71*$L$40-E71</f>
-        <v>621561275.24457455</v>
+        <v>600686985.16460657</v>
       </c>
       <c r="L71" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>62156127.524457455</v>
+        <v>66742998.351622954</v>
       </c>
     </row>
     <row r="72" spans="2:21" hidden="1" x14ac:dyDescent="0.25">
@@ -9103,35 +9103,35 @@
       </c>
       <c r="E74" s="115">
         <f>SUM(E69:E73)</f>
-        <v>1022909079.5589759</v>
+        <v>1060431510.186738</v>
       </c>
       <c r="F74" s="177">
         <f t="shared" si="13"/>
-        <v>0.58773504571237001</v>
+        <v>0.60929438849360251</v>
       </c>
       <c r="G74" s="181">
         <f>SUM(G69:G73)</f>
-        <v>630495175.76017308</v>
+        <v>592972745.132411</v>
       </c>
       <c r="H74" s="181">
         <f t="shared" ca="1" si="14"/>
-        <v>63049517.576017305</v>
+        <v>65885860.570267886</v>
       </c>
       <c r="I74" s="186">
         <f>SUM(I69:I73)</f>
-        <v>717516452.35591781</v>
+        <v>679994021.72815585</v>
       </c>
       <c r="J74" s="186">
         <f t="shared" ca="1" si="15"/>
-        <v>71751645.235591784</v>
+        <v>75554891.303128421</v>
       </c>
       <c r="K74" s="186">
         <f>SUM(K69:K73)</f>
-        <v>717516452.35591781</v>
+        <v>679994021.72815585</v>
       </c>
       <c r="L74" s="186">
         <f t="shared" ca="1" si="16"/>
-        <v>71751645.235591784</v>
+        <v>75554891.303128421</v>
       </c>
     </row>
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9144,10 +9144,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="D80" s="131">
         <f>SUMIF($B$10:$B$26,$T80,$F$10:$F$26)+SUMIF($B$10:$B$26,$U80,$F$10:$F$26)</f>
-        <v>297974557.80988503</v>
+        <v>309253837.03988498</v>
       </c>
       <c r="T80" t="str">
         <f t="shared" ref="T80:U93" si="17">T51</f>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="D81" s="132">
         <f t="shared" ref="D81:D93" si="18">SUMIF($B$10:$B$26,$T81,$F$10:$F$26)+SUMIF($B$10:$B$26,$U81,$F$10:$F$26)</f>
-        <v>94219790.060000002</v>
+        <v>97823393.579999998</v>
       </c>
       <c r="T81" t="str">
         <f t="shared" si="17"/>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="D82" s="132">
         <f t="shared" si="18"/>
-        <v>4684684.5599999996</v>
+        <v>7027026.8399999999</v>
       </c>
       <c r="T82" t="str">
         <f t="shared" si="17"/>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="D83" s="131">
         <f t="shared" si="18"/>
-        <v>279248599.70980501</v>
+        <v>306826077.50980502</v>
       </c>
       <c r="T83" t="str">
         <f t="shared" si="17"/>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="D85" s="131">
         <f t="shared" si="18"/>
-        <v>36782251.869999997</v>
+        <v>37502972.57</v>
       </c>
       <c r="T85" t="str">
         <f t="shared" si="17"/>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="D86" s="132">
         <f t="shared" si="18"/>
-        <v>653436569.67996895</v>
+        <v>751459090.97996902</v>
       </c>
       <c r="T86" t="str">
         <f t="shared" si="17"/>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="D87" s="131">
         <f t="shared" si="18"/>
-        <v>219748464.559596</v>
+        <v>229480815.92959601</v>
       </c>
       <c r="T87" t="str">
         <f t="shared" si="17"/>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="D88" s="132">
         <f t="shared" si="18"/>
-        <v>7921891.6799999997</v>
+        <v>9813783.5199999996</v>
       </c>
       <c r="T88" t="str">
         <f t="shared" si="17"/>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="D90" s="131">
         <f t="shared" si="18"/>
-        <v>418671352.45959097</v>
+        <v>433853334.65957397</v>
       </c>
       <c r="T90" t="str">
         <f t="shared" si="17"/>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="D91" s="132">
         <f t="shared" si="18"/>
-        <v>106507045.649948</v>
+        <v>109734631.169943</v>
       </c>
       <c r="T91" t="str">
         <f t="shared" si="17"/>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="D93" s="132">
         <f t="shared" si="18"/>
-        <v>111585407.75799999</v>
+        <v>122039462.09799999</v>
       </c>
       <c r="T93" t="str">
         <f t="shared" si="17"/>
@@ -9454,18 +9454,12 @@
       <c r="C94" s="58"/>
       <c r="D94" s="120">
         <f>SUM(D80:D93)</f>
-        <v>2283932724.9841938</v>
+        <v>2467966535.0841718</v>
       </c>
     </row>
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -9480,6 +9474,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -10107,11 +10107,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="259" t="s">
         <v>163</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="260"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -10431,33 +10431,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="263"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="270"/>
+      <c r="Q48" s="270"/>
+      <c r="R48" s="271"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -10466,49 +10466,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="268"/>
+      <c r="C50" s="268"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -10533,13 +10533,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="273"/>
+      <c r="N50" s="273"/>
+      <c r="O50" s="275"/>
+      <c r="P50" s="275"/>
+      <c r="Q50" s="277"/>
+      <c r="R50" s="277"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -11655,21 +11655,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="283" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="260" t="s">
+      <c r="G67" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="270"/>
+      <c r="I67" s="270"/>
+      <c r="J67" s="270"/>
+      <c r="K67" s="270"/>
+      <c r="L67" s="271"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -11990,10 +11990,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -12306,12 +12306,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -12326,6 +12320,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -12953,11 +12953,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="259" t="s">
         <v>175</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="260"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -13277,33 +13277,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="263"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="270"/>
+      <c r="Q48" s="270"/>
+      <c r="R48" s="271"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -13312,49 +13312,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="268"/>
+      <c r="C50" s="268"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -13379,13 +13379,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="273"/>
+      <c r="N50" s="273"/>
+      <c r="O50" s="275"/>
+      <c r="P50" s="275"/>
+      <c r="Q50" s="277"/>
+      <c r="R50" s="277"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -14501,21 +14501,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="283" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="260" t="s">
+      <c r="G67" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="270"/>
+      <c r="I67" s="270"/>
+      <c r="J67" s="270"/>
+      <c r="K67" s="270"/>
+      <c r="L67" s="271"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -14836,10 +14836,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -15152,12 +15152,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -15172,6 +15166,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -15799,11 +15799,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="259" t="s">
         <v>177</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="260"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -16123,33 +16123,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="263"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="270"/>
+      <c r="Q48" s="270"/>
+      <c r="R48" s="271"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -16158,49 +16158,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="268"/>
+      <c r="C50" s="268"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -16225,13 +16225,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="273"/>
+      <c r="N50" s="273"/>
+      <c r="O50" s="275"/>
+      <c r="P50" s="275"/>
+      <c r="Q50" s="277"/>
+      <c r="R50" s="277"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -17333,21 +17333,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="283" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="260" t="s">
+      <c r="G67" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="270"/>
+      <c r="I67" s="270"/>
+      <c r="J67" s="270"/>
+      <c r="K67" s="270"/>
+      <c r="L67" s="271"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -17668,10 +17668,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -17984,12 +17984,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -18004,6 +17998,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -25783,11 +25783,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="269" t="s">
+      <c r="B41" s="259" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="270"/>
-      <c r="D41" s="271"/>
+      <c r="C41" s="260"/>
+      <c r="D41" s="261"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -26058,59 +26058,59 @@
       </c>
     </row>
     <row r="48" spans="2:19" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="261"/>
-      <c r="M48" s="261"/>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
+      <c r="L48" s="270"/>
+      <c r="M48" s="270"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="271"/>
       <c r="Q48"/>
       <c r="R48"/>
     </row>
     <row r="49" spans="2:18" s="139" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="277" t="s">
+      <c r="B49" s="267" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="277" t="s">
+      <c r="C49" s="267" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="274" t="s">
+      <c r="D49" s="264" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
+      <c r="E49" s="265"/>
+      <c r="F49" s="266"/>
       <c r="G49" s="140" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="140"/>
       <c r="I49" s="140"/>
-      <c r="J49" s="274" t="s">
+      <c r="J49" s="264" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="263" t="str">
+      <c r="K49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="263" t="str">
+      <c r="L49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
@@ -26125,7 +26125,7 @@
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="267" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -26134,8 +26134,8 @@
       <c r="R49"/>
     </row>
     <row r="50" spans="2:18" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="277"/>
-      <c r="C50" s="277"/>
+      <c r="B50" s="267"/>
+      <c r="C50" s="267"/>
       <c r="D50" s="141" t="s">
         <v>149</v>
       </c>
@@ -26154,13 +26154,13 @@
       <c r="I50" s="142" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="274"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="266"/>
+      <c r="J50" s="264"/>
+      <c r="K50" s="273"/>
+      <c r="L50" s="273"/>
+      <c r="M50" s="275"/>
       <c r="N50" s="188"/>
       <c r="O50" s="183"/>
-      <c r="P50" s="268"/>
+      <c r="P50" s="277"/>
       <c r="Q50"/>
       <c r="R50"/>
     </row>
@@ -27501,10 +27501,10 @@
       <c r="I77"/>
     </row>
     <row r="78" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -27703,13 +27703,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="J49:J50"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
     <mergeCell ref="K48:P48"/>
@@ -27719,6 +27712,13 @@
     <mergeCell ref="P49:P50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="J49:J50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="26" priority="8">
@@ -28758,25 +28758,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="261"/>
-      <c r="M48" s="261"/>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
+      <c r="L48" s="270"/>
+      <c r="M48" s="270"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="271"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -28798,32 +28798,32 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="263" t="str">
+      <c r="K49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="263" t="str">
+      <c r="L49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="265" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="267" t="str">
+      <c r="O49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="267" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -28851,12 +28851,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="266"/>
-      <c r="N50" s="266"/>
-      <c r="O50" s="268"/>
-      <c r="P50" s="268"/>
+      <c r="K50" s="273"/>
+      <c r="L50" s="273"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
+      <c r="O50" s="277"/>
+      <c r="P50" s="277"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="167" t="s">
@@ -30093,10 +30093,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -30290,17 +30290,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -30308,6 +30297,17 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -31065,11 +31065,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="269" t="s">
+      <c r="B41" s="259" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="270"/>
-      <c r="D41" s="271"/>
+      <c r="C41" s="260"/>
+      <c r="D41" s="261"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -31344,25 +31344,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="261"/>
-      <c r="M48" s="261"/>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
+      <c r="L48" s="270"/>
+      <c r="M48" s="270"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="271"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -31384,32 +31384,32 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="263" t="str">
+      <c r="K49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="263" t="str">
+      <c r="L49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="265" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="267" t="str">
+      <c r="O49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="267" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -31437,12 +31437,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="266"/>
-      <c r="N50" s="266"/>
-      <c r="O50" s="268"/>
-      <c r="P50" s="268"/>
+      <c r="K50" s="273"/>
+      <c r="L50" s="273"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
+      <c r="O50" s="277"/>
+      <c r="P50" s="277"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -32679,10 +32679,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -32863,17 +32863,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -32881,6 +32870,17 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -33659,11 +33659,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" s="191" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="269" t="s">
+      <c r="B41" s="259" t="s">
         <v>189</v>
       </c>
-      <c r="C41" s="270"/>
-      <c r="D41" s="271"/>
+      <c r="C41" s="260"/>
+      <c r="D41" s="261"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -33938,25 +33938,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="261"/>
-      <c r="M48" s="261"/>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
+      <c r="L48" s="270"/>
+      <c r="M48" s="270"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="271"/>
     </row>
     <row r="49" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -33978,22 +33978,22 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="263" t="str">
+      <c r="K49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="263" t="str">
+      <c r="L49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="265" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
@@ -34031,10 +34031,10 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="266"/>
-      <c r="N50" s="266"/>
+      <c r="K50" s="273"/>
+      <c r="L50" s="273"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
       <c r="O50" s="282"/>
       <c r="P50" s="282"/>
     </row>
@@ -35273,10 +35273,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -35470,11 +35470,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
@@ -35488,6 +35483,11 @@
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="228">
   <si>
     <t>📊  PANDUAN PENGGUNAAN — DATA PENCAPAIAN 2026</t>
   </si>
@@ -909,10 +909,7 @@
     <t>RONALD</t>
   </si>
   <si>
-    <t>WIDI</t>
-  </si>
-  <si>
-    <t>DATA PENCAPAIAN — GLOBAL —  21 SEPTEMBER 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL —  22 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>
@@ -2559,33 +2556,6 @@
     <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2616,6 +2586,33 @@
     <xf numFmtId="0" fontId="48" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2629,15 +2626,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2659,6 +2647,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4302,11 +4299,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>219</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -4626,33 +4623,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -4661,49 +4658,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -4728,13 +4725,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="172" t="s">
         <v>216</v>
       </c>
@@ -5850,21 +5847,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
-      <c r="F67" s="285"/>
-      <c r="G67" s="269" t="s">
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
+      <c r="F67" s="292"/>
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -6183,10 +6180,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -6498,6 +6495,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -6512,12 +6515,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -6595,7 +6592,7 @@
       </c>
       <c r="C3" s="75">
         <f ca="1">IF($J$5&lt;&gt;"",$J$5,MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),9,1)),EOMONTH(DATE(YEAR(TODAY()),9,1),0),11)-MAX(0,$J$3-$J$4)))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="76" t="s">
         <v>104</v>
@@ -6723,19 +6720,19 @@
         <v>112</v>
       </c>
       <c r="C10" s="234">
-        <v>100376981.08205</v>
+        <v>117222800.908739</v>
       </c>
       <c r="D10" s="234">
-        <v>29510144.3829</v>
+        <v>31388455.192899998</v>
       </c>
       <c r="E10" s="234">
-        <v>144605955.29704899</v>
+        <v>173196225.567045</v>
       </c>
       <c r="F10" s="234">
-        <v>109734631.169943</v>
+        <v>122621117.86994299</v>
       </c>
       <c r="G10" s="234">
-        <v>384227711.93194199</v>
+        <v>444428599.53862703</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="111"/>
@@ -6773,19 +6770,19 @@
         <v>70</v>
       </c>
       <c r="C12" s="234">
-        <v>120586922.06740101</v>
+        <v>136887903.46735299</v>
       </c>
       <c r="D12" s="234">
-        <v>55970384.421572</v>
+        <v>64137847.651524998</v>
       </c>
       <c r="E12" s="234">
-        <v>128256940.11960401</v>
+        <v>133871985.199589</v>
       </c>
       <c r="F12" s="234">
-        <v>41739148.850000001</v>
+        <v>63360769.850000001</v>
       </c>
       <c r="G12" s="234">
-        <v>346553395.45857698</v>
+        <v>398258506.16846699</v>
       </c>
       <c r="H12" s="111"/>
       <c r="I12" s="111"/>
@@ -6798,19 +6795,19 @@
         <v>114</v>
       </c>
       <c r="C13" s="234">
-        <v>26518751.469962001</v>
+        <v>28415976.749961998</v>
       </c>
       <c r="D13" s="234">
-        <v>17619678.599973001</v>
+        <v>18071800.219973002</v>
       </c>
       <c r="E13" s="234">
-        <v>147359776.31966901</v>
+        <v>156752028.56966901</v>
       </c>
       <c r="F13" s="234">
-        <v>56084244.729999997</v>
+        <v>64030191.060000002</v>
       </c>
       <c r="G13" s="234">
-        <v>247582451.11960399</v>
+        <v>267269996.59960401</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="111"/>
@@ -6823,19 +6820,19 @@
         <v>115</v>
       </c>
       <c r="C14" s="234">
-        <v>376890096.94460398</v>
+        <v>396973429.52460003</v>
       </c>
       <c r="D14" s="234">
-        <v>31805739.065467</v>
+        <v>37481186.411467001</v>
       </c>
       <c r="E14" s="234">
-        <v>110763968.6099</v>
+        <v>117286536.1999</v>
       </c>
       <c r="F14" s="234">
-        <v>306826077.50980502</v>
+        <v>320372564.56976998</v>
       </c>
       <c r="G14" s="234">
-        <v>826285882.129776</v>
+        <v>872113716.70573699</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="111"/>
@@ -6848,19 +6845,19 @@
         <v>118</v>
       </c>
       <c r="C15" s="234">
-        <v>1083245254.250098</v>
+        <v>1089786700.000098</v>
       </c>
       <c r="D15" s="234">
-        <v>8214253.8869240005</v>
+        <v>8915041.3269239999</v>
       </c>
       <c r="E15" s="234">
-        <v>58257134.009943001</v>
+        <v>59318395.269938998</v>
       </c>
       <c r="F15" s="234">
-        <v>12372973.210000001</v>
+        <v>13983784.08</v>
       </c>
       <c r="G15" s="234">
-        <v>1162089615.3569651</v>
+        <v>1172003920.6769609</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="111"/>
@@ -6873,19 +6870,19 @@
         <v>120</v>
       </c>
       <c r="C16" s="234">
-        <v>342788950.89772499</v>
+        <v>371501562.66268098</v>
       </c>
       <c r="D16" s="234">
-        <v>30711589.039930999</v>
+        <v>36300643.119926997</v>
       </c>
       <c r="E16" s="234">
-        <v>248891217.44951999</v>
+        <v>255160812.04951999</v>
       </c>
       <c r="F16" s="234">
-        <v>751459090.97996902</v>
+        <v>760950711.77996898</v>
       </c>
       <c r="G16" s="234">
-        <v>1373850848.3671451</v>
+        <v>1423913729.612097</v>
       </c>
       <c r="H16" s="111"/>
       <c r="I16" s="111"/>
@@ -6898,7 +6895,7 @@
         <v>122</v>
       </c>
       <c r="C17" s="234">
-        <v>82312134.715029001</v>
+        <v>91170215.815028995</v>
       </c>
       <c r="D17" s="234">
         <v>12915436.9209</v>
@@ -6907,10 +6904,10 @@
         <v>70679078.968842</v>
       </c>
       <c r="F17" s="234">
-        <v>35293514.298</v>
+        <v>36655676.498000003</v>
       </c>
       <c r="G17" s="234">
-        <v>201200164.902771</v>
+        <v>211420408.20277101</v>
       </c>
       <c r="H17" s="111"/>
       <c r="I17" s="111"/>
@@ -6924,19 +6921,19 @@
         <v>123</v>
       </c>
       <c r="C18" s="234">
-        <v>11129847.589996999</v>
+        <v>13080047.589996999</v>
       </c>
       <c r="D18" s="234">
-        <v>127814110.76229</v>
+        <v>129663009.171675</v>
       </c>
       <c r="E18" s="234">
         <v>46995546.100000001</v>
       </c>
       <c r="F18" s="234">
-        <v>86745947.799999997</v>
+        <v>89016218.120000005</v>
       </c>
       <c r="G18" s="234">
-        <v>272685452.25228697</v>
+        <v>278754820.98167199</v>
       </c>
       <c r="H18" s="111"/>
       <c r="I18" s="111"/>
@@ -6976,7 +6973,7 @@
         <v>170</v>
       </c>
       <c r="C20" s="234">
-        <v>153958227.16</v>
+        <v>188527227.16</v>
       </c>
       <c r="D20" s="234" t="s">
         <v>165</v>
@@ -6988,14 +6985,14 @@
         <v>9813783.5199999996</v>
       </c>
       <c r="G20" s="234">
-        <v>163772010.68000001</v>
+        <v>198341010.68000001</v>
       </c>
       <c r="H20" s="111"/>
       <c r="I20" s="111"/>
       <c r="J20" s="111"/>
       <c r="M20" s="14">
         <f>SUM(C30,C35)+M7</f>
-        <v>9300000</v>
+        <v>0</v>
       </c>
       <c r="N20" s="10" t="s">
         <v>223</v>
@@ -7006,26 +7003,26 @@
         <v>124</v>
       </c>
       <c r="C21" s="234">
-        <v>195897681.76952299</v>
+        <v>212724104.35944599</v>
       </c>
       <c r="D21" s="234">
-        <v>39009404.373457998</v>
+        <v>41095408.883458003</v>
       </c>
       <c r="E21" s="234">
-        <v>118291581.639805</v>
+        <v>121013203.27980299</v>
       </c>
       <c r="F21" s="234">
-        <v>309253837.03988498</v>
+        <v>305992102.95987999</v>
       </c>
       <c r="G21" s="234">
-        <v>662452504.82267106</v>
+        <v>680824819.48258698</v>
       </c>
       <c r="H21" s="111"/>
       <c r="I21" s="111"/>
       <c r="J21" s="111"/>
       <c r="M21" s="14">
         <f>SUM(C33,C34)+M20</f>
-        <v>483922631.14035797</v>
+        <v>543057028.79973006</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>224</v>
@@ -7036,19 +7033,19 @@
         <v>125</v>
       </c>
       <c r="C22" s="234">
-        <v>190526075.07154801</v>
+        <v>201386818.38223299</v>
       </c>
       <c r="D22" s="234">
-        <v>52554915.529964998</v>
+        <v>54608591.209964</v>
       </c>
       <c r="E22" s="234">
-        <v>135282119.23626</v>
+        <v>150961804.00620899</v>
       </c>
       <c r="F22" s="234">
-        <v>229480815.92959601</v>
+        <v>246882618.74950501</v>
       </c>
       <c r="G22" s="234">
-        <v>607843925.76736903</v>
+        <v>653839832.347911</v>
       </c>
       <c r="H22" s="111"/>
       <c r="I22" s="111"/>
@@ -7059,19 +7056,19 @@
         <v>126</v>
       </c>
       <c r="C23" s="234">
-        <v>340158082.01052099</v>
+        <v>357807886.12938398</v>
       </c>
       <c r="D23" s="234">
-        <v>45384772.724923998</v>
+        <v>53379470.924923003</v>
       </c>
       <c r="E23" s="234">
-        <v>148552415.809908</v>
+        <v>159507956.34990701</v>
       </c>
       <c r="F23" s="234">
-        <v>433853334.65957397</v>
+        <v>468670407.23952502</v>
       </c>
       <c r="G23" s="234">
-        <v>967948605.20492697</v>
+        <v>1039365720.643739</v>
       </c>
       <c r="H23" s="111"/>
       <c r="I23" s="111"/>
@@ -7082,19 +7079,19 @@
         <v>225</v>
       </c>
       <c r="C24" s="234">
-        <v>143534246.36451599</v>
+        <v>148754687.584483</v>
       </c>
       <c r="D24" s="234">
-        <v>37310141.999944001</v>
+        <v>42615344.709941</v>
       </c>
       <c r="E24" s="234">
-        <v>117280833.94819801</v>
+        <v>126094298.448173</v>
       </c>
       <c r="F24" s="234">
-        <v>37502972.57</v>
+        <v>40335405.060000002</v>
       </c>
       <c r="G24" s="234">
-        <v>335628194.882658</v>
+        <v>357799735.80259699</v>
       </c>
       <c r="H24" s="111"/>
       <c r="I24" s="111"/>
@@ -7105,19 +7102,19 @@
         <v>220</v>
       </c>
       <c r="C25" s="234">
-        <v>225087203.80412</v>
+        <v>233723045.560087</v>
       </c>
       <c r="D25" s="234">
-        <v>71590833.136556998</v>
+        <v>75195779.136546999</v>
       </c>
       <c r="E25" s="234">
-        <v>76570716.532584995</v>
+        <v>77460806.632578999</v>
       </c>
       <c r="F25" s="234">
-        <v>38054054.829999998</v>
+        <v>39783784.579999998</v>
       </c>
       <c r="G25" s="234">
-        <v>411302808.303262</v>
+        <v>426163415.90921301</v>
       </c>
       <c r="H25" s="111"/>
       <c r="I25" s="111"/>
@@ -7128,19 +7125,19 @@
         <v>127</v>
       </c>
       <c r="C26" s="234">
-        <v>382275746.05234897</v>
+        <v>398672594.47329497</v>
       </c>
       <c r="D26" s="234">
-        <v>181355173.74289101</v>
+        <v>225332673.160541</v>
       </c>
       <c r="E26" s="234">
-        <v>225534639.125983</v>
+        <v>227840944.82587299</v>
       </c>
       <c r="F26" s="234">
-        <v>15098054.3574</v>
+        <v>18013297.6536</v>
       </c>
       <c r="G26" s="234">
-        <v>804263613.27862298</v>
+        <v>869859510.11330903</v>
       </c>
       <c r="H26" s="111"/>
       <c r="I26" s="111"/>
@@ -7183,7 +7180,7 @@
         <v>131</v>
       </c>
       <c r="C31" s="171">
-        <v>170853939.695351</v>
+        <v>202988607.005263</v>
       </c>
       <c r="G31" s="111"/>
       <c r="H31" s="111"/>
@@ -7194,7 +7191,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="234">
-        <v>405654939.35102898</v>
+        <v>408029398.87102902</v>
       </c>
       <c r="G32" s="111"/>
       <c r="H32" s="111"/>
@@ -7205,7 +7202,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="234">
-        <v>103185244.188411</v>
+        <v>108960185.688379</v>
       </c>
       <c r="G33" s="111"/>
       <c r="H33" s="111"/>
@@ -7216,7 +7213,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="234">
-        <v>371437386.95194697</v>
+        <v>434096843.11135101</v>
       </c>
       <c r="G34" s="111"/>
       <c r="H34" s="111"/>
@@ -7227,7 +7224,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="234">
-        <v>9300000</v>
+        <v>0</v>
       </c>
       <c r="G35" s="111"/>
       <c r="H35" s="111"/>
@@ -7261,17 +7258,17 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
-        <v>228</v>
-      </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="B40" s="269" t="s">
+        <v>227</v>
+      </c>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
       <c r="F40" s="174">
         <f ca="1">IF(MONTH(TODAY())=9,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;9,1,0))</f>
-        <v>0.7</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="G40" s="192" t="s">
         <v>187</v>
@@ -7358,35 +7355,35 @@
       </c>
       <c r="E42" s="46">
         <f>H65</f>
-        <v>2754073079.379343</v>
+        <v>2958880432.7472873</v>
       </c>
       <c r="F42" s="176">
         <f>IFERROR(E42/D42,0)</f>
-        <v>0.61041748407584984</v>
+        <v>0.65581133738320951</v>
       </c>
       <c r="G42" s="184">
         <f>D42*$H$40-E42</f>
-        <v>1532123652.6350832</v>
+        <v>1327316299.267139</v>
       </c>
       <c r="H42" s="184">
         <f ca="1">IFERROR(G42/$C$3,0)</f>
-        <v>170235961.40389812</v>
+        <v>165914537.40839237</v>
       </c>
       <c r="I42" s="204">
         <f>D42*$J$40-E42</f>
-        <v>1757712954.3200531</v>
+        <v>1552905600.9521089</v>
       </c>
       <c r="J42" s="204">
         <f ca="1">IFERROR(I42/$C$3,0)</f>
-        <v>195301439.36889479</v>
+        <v>194113200.11901361</v>
       </c>
       <c r="K42" s="185">
         <f>D42*$L$40-E42</f>
-        <v>1757712954.3200531</v>
+        <v>1552905600.9521089</v>
       </c>
       <c r="L42" s="185">
         <f ca="1">IFERROR(K42/$C$3,0)</f>
-        <v>195301439.36889479</v>
+        <v>194113200.11901361</v>
       </c>
       <c r="S42" s="173">
         <v>0.8</v>
@@ -7405,35 +7402,35 @@
       </c>
       <c r="E43" s="46">
         <f>I65</f>
-        <v>750055640.30077207</v>
+        <v>838688962.31374085</v>
       </c>
       <c r="F43" s="176">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.53523205881620217</v>
+        <v>0.59847989387240885</v>
       </c>
       <c r="G43" s="184">
         <f>D43*$H$40-E43</f>
-        <v>581241404.68887198</v>
+        <v>492608082.6759032</v>
       </c>
       <c r="H43" s="184">
         <f ca="1">IFERROR(G43/$C$3,0)</f>
-        <v>64582378.298763551</v>
+        <v>61576010.3344879</v>
       </c>
       <c r="I43" s="204">
         <f>D43*$J$40-E43</f>
-        <v>651309670.21464288</v>
+        <v>562676348.2016741</v>
       </c>
       <c r="J43" s="204">
         <f ca="1">IFERROR(I43/$C$3,0)</f>
-        <v>72367741.134960324</v>
+        <v>70334543.525209263</v>
       </c>
       <c r="K43" s="185">
         <f>D43*$L$40-E43</f>
-        <v>651309670.21464288</v>
+        <v>562676348.2016741</v>
       </c>
       <c r="L43" s="185">
         <f ca="1">IFERROR(K43/$C$3,0)</f>
-        <v>72367741.134960324</v>
+        <v>70334543.525209263</v>
       </c>
       <c r="S43" s="173">
         <v>0.85</v>
@@ -7452,35 +7449,35 @@
       </c>
       <c r="E44" s="46">
         <f>J65</f>
-        <v>1918222447.7965229</v>
+        <v>2015978884.8363087</v>
       </c>
       <c r="F44" s="176">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.65138997570304447</v>
+        <v>0.68458610643402895</v>
       </c>
       <c r="G44" s="184">
         <f>IF(D44=0,0,D44*$H$40-E44)</f>
-        <v>879351038.71572804</v>
+        <v>781594601.67594218</v>
       </c>
       <c r="H44" s="184">
         <f ca="1">IFERROR(G44/$C$3,0)</f>
-        <v>97705670.968414232</v>
+        <v>97699325.209492773</v>
       </c>
       <c r="I44" s="204">
         <f>IF(D44=0,0,D44*$J$40-E44)</f>
-        <v>1026591748.5321624</v>
+        <v>928835311.49237657</v>
       </c>
       <c r="J44" s="204">
         <f ca="1">IFERROR(I44/$C$3,0)</f>
-        <v>114065749.83690694</v>
+        <v>116104413.93654707</v>
       </c>
       <c r="K44" s="185">
         <f>IF(D44=0,0,D44*$L$40-E44)</f>
-        <v>1026591748.5321624</v>
+        <v>928835311.49237657</v>
       </c>
       <c r="L44" s="185">
         <f ca="1">IFERROR(K44/$C$3,0)</f>
-        <v>114065749.83690694</v>
+        <v>116104413.93654707</v>
       </c>
       <c r="S44" s="173">
         <v>0.9</v>
@@ -7499,35 +7496,35 @@
       </c>
       <c r="E45" s="46">
         <f>E74</f>
-        <v>1060431510.186738</v>
+        <v>1154075034.6760221</v>
       </c>
       <c r="F45" s="176">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.60929438849360251</v>
+        <v>0.66309934755223765</v>
       </c>
       <c r="G45" s="184">
         <f>D45*$H$40-E45</f>
-        <v>592972745.13241076</v>
+        <v>499329220.64312673</v>
       </c>
       <c r="H45" s="184">
         <f ca="1">IFERROR(G45/$C$3,0)</f>
-        <v>65885860.570267864</v>
+        <v>62416152.580390841</v>
       </c>
       <c r="I45" s="204">
         <f>D45*$J$40-E45</f>
-        <v>679994021.72815561</v>
+        <v>586350497.23887157</v>
       </c>
       <c r="J45" s="204">
         <f ca="1">IFERROR(I45/$C$3,0)</f>
-        <v>75554891.303128406</v>
+        <v>73293812.154858947</v>
       </c>
       <c r="K45" s="185">
         <f>D45*$L$40-E45</f>
-        <v>679994021.72815561</v>
+        <v>586350497.23887157</v>
       </c>
       <c r="L45" s="185">
         <f ca="1">IFERROR(K45/$C$3,0)</f>
-        <v>75554891.303128406</v>
+        <v>73293812.154858947</v>
       </c>
       <c r="S45" s="173">
         <v>0.95</v>
@@ -7544,35 +7541,35 @@
       </c>
       <c r="E46" s="47">
         <f>SUM(E42:E45)</f>
-        <v>6482782677.6633759</v>
+        <v>6967623314.5733585</v>
       </c>
       <c r="F46" s="177">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.61167611511429509</v>
+        <v>0.65742274152157287</v>
       </c>
       <c r="G46" s="181">
         <f>SUM(G42:G45)</f>
-        <v>3585688841.1720943</v>
+        <v>3100848204.2621107</v>
       </c>
       <c r="H46" s="181">
         <f ca="1">IFERROR(G46/$C$3,0)</f>
-        <v>398409871.2413438</v>
+        <v>387606025.53276384</v>
       </c>
       <c r="I46" s="186">
         <f>SUM(I42:I45)</f>
-        <v>4115608394.7950139</v>
+        <v>3630767757.8850307</v>
       </c>
       <c r="J46" s="186">
         <f ca="1">IFERROR(I46/$C$3,0)</f>
-        <v>457289821.64389044</v>
+        <v>453845969.73562884</v>
       </c>
       <c r="K46" s="186">
         <f>SUM(K42:K45)</f>
-        <v>4115608394.7950139</v>
+        <v>3630767757.8850307</v>
       </c>
       <c r="L46" s="186">
         <f ca="1">IFERROR(K46/$C$3,0)</f>
-        <v>457289821.64389044</v>
+        <v>453845969.73562884</v>
       </c>
       <c r="S46" s="173">
         <v>1</v>
@@ -7585,33 +7582,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -7620,49 +7617,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -7687,13 +7684,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -7726,47 +7723,47 @@
       </c>
       <c r="H51" s="114">
         <f>SUMIF($B$10:$B$26,$T51,C$10:C$26)+SUMIF($B$10:$B$26,$U51,C$10:C$26)</f>
-        <v>195897681.76952299</v>
+        <v>212724104.35944599</v>
       </c>
       <c r="I51" s="114">
         <f t="shared" ref="I51:I64" si="1">SUMIF($B$10:$B$26,$T51,D$10:D$26)+SUMIF($B$10:$B$26,$U51,D$10:D$26)</f>
-        <v>39009404.373457998</v>
+        <v>41095408.883458003</v>
       </c>
       <c r="J51" s="114">
         <f t="shared" ref="J51:J64" si="2">SUMIF($B$10:$B$26,$T51,E$10:E$26)+SUMIF($B$10:$B$26,$U51,E$10:E$26)</f>
-        <v>118291581.639805</v>
+        <v>121013203.27980299</v>
       </c>
       <c r="K51" s="114">
         <f t="shared" ref="K51:K64" si="3">SUM(H51:J51)</f>
-        <v>353198667.78278601</v>
+        <v>374832716.52270699</v>
       </c>
       <c r="L51" s="187">
         <f t="shared" ref="L51:L65" si="4">IFERROR(K51/G51,0)</f>
-        <v>0.68666596184087703</v>
+        <v>0.72872547746636118</v>
       </c>
       <c r="M51" s="184">
         <f t="shared" ref="M51:M64" si="5">G51*$H$40-K51</f>
-        <v>135450476.10968781</v>
+        <v>113816427.36976683</v>
       </c>
       <c r="N51" s="184">
         <f t="shared" ref="N51:N65" ca="1" si="6">IFERROR(M51/$C$3,0)</f>
-        <v>15050052.901076423</v>
+        <v>14227053.421220854</v>
       </c>
       <c r="O51" s="180">
         <f t="shared" ref="O51:O64" si="7">G51*$J$40-K51</f>
-        <v>161168852.10402858</v>
+        <v>139534803.36410761</v>
       </c>
       <c r="P51" s="180">
         <f t="shared" ref="P51:P65" ca="1" si="8">IFERROR(O51/$C$3,0)</f>
-        <v>17907650.233780954</v>
+        <v>17441850.420513451</v>
       </c>
       <c r="Q51" s="185">
         <f t="shared" ref="Q51:Q64" si="9">G51*$L$40-K51</f>
-        <v>161168852.10402858</v>
+        <v>139534803.36410761</v>
       </c>
       <c r="R51" s="185">
         <f t="shared" ref="R51:R65" ca="1" si="10">IFERROR(Q51/$C$3,0)</f>
-        <v>17907650.233780954</v>
+        <v>17441850.420513451</v>
       </c>
       <c r="T51" t="s">
         <v>124</v>
@@ -7800,47 +7797,47 @@
       </c>
       <c r="H52" s="114">
         <f t="shared" ref="H52:H64" si="11">SUMIF($B$10:$B$26,$T52,C$10:C$26)+SUMIF($B$10:$B$26,$U52,C$10:C$26)</f>
-        <v>147105673.53736299</v>
+        <v>165303880.21731499</v>
       </c>
       <c r="I52" s="114">
         <f t="shared" si="1"/>
-        <v>73590063.021544993</v>
+        <v>82209647.871498004</v>
       </c>
       <c r="J52" s="114">
         <f t="shared" si="2"/>
-        <v>275616716.439273</v>
+        <v>290624013.76925802</v>
       </c>
       <c r="K52" s="114">
         <f t="shared" si="3"/>
-        <v>496312452.99818099</v>
+        <v>538137541.85807109</v>
       </c>
       <c r="L52" s="187">
         <f t="shared" si="4"/>
-        <v>0.63182350624515982</v>
+        <v>0.68506834048785004</v>
       </c>
       <c r="M52" s="184">
         <f t="shared" si="5"/>
-        <v>249935234.35095346</v>
+        <v>208110145.49106336</v>
       </c>
       <c r="N52" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>27770581.594550386</v>
+        <v>26013768.18638292</v>
       </c>
       <c r="O52" s="180">
         <f t="shared" si="7"/>
-        <v>289211428.42196059</v>
+        <v>247386339.56207049</v>
       </c>
       <c r="P52" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>32134603.157995623</v>
+        <v>30923292.445258811</v>
       </c>
       <c r="Q52" s="185">
         <f t="shared" si="9"/>
-        <v>289211428.42196059</v>
+        <v>247386339.56207049</v>
       </c>
       <c r="R52" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>32134603.157995623</v>
+        <v>30923292.445258811</v>
       </c>
       <c r="T52" t="s">
         <v>70</v>
@@ -7898,7 +7895,7 @@
       </c>
       <c r="N53" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>21327415.649984464</v>
+        <v>23993342.606232524</v>
       </c>
       <c r="O53" s="180">
         <f t="shared" si="7"/>
@@ -7906,7 +7903,7 @@
       </c>
       <c r="P53" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>22788266.233667862</v>
+        <v>25636799.512876343</v>
       </c>
       <c r="Q53" s="185">
         <f t="shared" si="9"/>
@@ -7914,7 +7911,7 @@
       </c>
       <c r="R53" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>22788266.233667862</v>
+        <v>25636799.512876343</v>
       </c>
       <c r="T53" t="s">
         <v>169</v>
@@ -7948,47 +7945,47 @@
       </c>
       <c r="H54" s="114">
         <f t="shared" si="11"/>
-        <v>376890096.94460398</v>
+        <v>396973429.52460003</v>
       </c>
       <c r="I54" s="114">
         <f t="shared" si="1"/>
-        <v>31805739.065467</v>
+        <v>37481186.411467001</v>
       </c>
       <c r="J54" s="114">
         <f t="shared" si="2"/>
-        <v>110763968.6099</v>
+        <v>117286536.1999</v>
       </c>
       <c r="K54" s="114">
         <f t="shared" si="3"/>
-        <v>519459804.61997098</v>
+        <v>551741152.13596702</v>
       </c>
       <c r="L54" s="187">
         <f t="shared" si="4"/>
-        <v>0.714847883651758</v>
+        <v>0.75927144202528596</v>
       </c>
       <c r="M54" s="184">
         <f t="shared" si="5"/>
-        <v>170878413.7266013</v>
+        <v>138597066.21060526</v>
       </c>
       <c r="N54" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>18986490.41406681</v>
+        <v>17324633.276325658</v>
       </c>
       <c r="O54" s="180">
         <f t="shared" si="7"/>
-        <v>207212004.16589457</v>
+        <v>174930656.64989853</v>
       </c>
       <c r="P54" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>23023556.018432729</v>
+        <v>21866332.081237316</v>
       </c>
       <c r="Q54" s="185">
         <f t="shared" si="9"/>
-        <v>207212004.16589457</v>
+        <v>174930656.64989853</v>
       </c>
       <c r="R54" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>23023556.018432729</v>
+        <v>21866332.081237316</v>
       </c>
       <c r="T54" t="s">
         <v>115</v>
@@ -8046,7 +8043,7 @@
       </c>
       <c r="N55" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>32278505.770328149</v>
+        <v>36313318.99161917</v>
       </c>
       <c r="O55" s="180">
         <f t="shared" si="7"/>
@@ -8054,7 +8051,7 @@
       </c>
       <c r="P55" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>35262955.767943069</v>
+        <v>39670825.238935955</v>
       </c>
       <c r="Q55" s="185">
         <f t="shared" si="9"/>
@@ -8062,7 +8059,7 @@
       </c>
       <c r="R55" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>35262955.767943069</v>
+        <v>39670825.238935955</v>
       </c>
       <c r="T55" t="s">
         <v>182</v>
@@ -8096,47 +8093,47 @@
       </c>
       <c r="H56" s="114">
         <f t="shared" si="11"/>
-        <v>143534246.36451599</v>
+        <v>148754687.584483</v>
       </c>
       <c r="I56" s="114">
         <f t="shared" si="1"/>
-        <v>37310141.999944001</v>
+        <v>42615344.709941</v>
       </c>
       <c r="J56" s="114">
         <f t="shared" si="2"/>
-        <v>117280833.94819801</v>
+        <v>126094298.448173</v>
       </c>
       <c r="K56" s="114">
         <f t="shared" si="3"/>
-        <v>298125222.31265801</v>
+        <v>317464330.74259698</v>
       </c>
       <c r="L56" s="187">
         <f t="shared" si="4"/>
-        <v>0.51852735435259889</v>
+        <v>0.55216374597329054</v>
       </c>
       <c r="M56" s="184">
         <f t="shared" si="5"/>
-        <v>248073466.76254946</v>
+        <v>228734358.33261049</v>
       </c>
       <c r="N56" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>27563718.529172163</v>
+        <v>28591794.791576311</v>
       </c>
       <c r="O56" s="180">
         <f t="shared" si="7"/>
-        <v>276820766.18756038</v>
+        <v>257481657.75762141</v>
       </c>
       <c r="P56" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>30757862.909728929</v>
+        <v>32185207.219702676</v>
       </c>
       <c r="Q56" s="185">
         <f t="shared" si="9"/>
-        <v>276820766.18756038</v>
+        <v>257481657.75762141</v>
       </c>
       <c r="R56" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>30757862.909728929</v>
+        <v>32185207.219702676</v>
       </c>
       <c r="T56" t="s">
         <v>225</v>
@@ -8170,47 +8167,47 @@
       </c>
       <c r="H57" s="114">
         <f t="shared" si="11"/>
-        <v>342788950.89772499</v>
+        <v>371501562.66268098</v>
       </c>
       <c r="I57" s="114">
         <f t="shared" si="1"/>
-        <v>30711589.039930999</v>
+        <v>36300643.119926997</v>
       </c>
       <c r="J57" s="114">
         <f t="shared" si="2"/>
-        <v>248891217.44951999</v>
+        <v>255160812.04951999</v>
       </c>
       <c r="K57" s="114">
         <f t="shared" si="3"/>
-        <v>622391757.38717604</v>
+        <v>662963017.83212793</v>
       </c>
       <c r="L57" s="187">
         <f t="shared" si="4"/>
-        <v>0.5611257650845598</v>
+        <v>0.59770333746949844</v>
       </c>
       <c r="M57" s="184">
         <f t="shared" si="5"/>
-        <v>431333104.86133325</v>
+        <v>390761844.41638136</v>
       </c>
       <c r="N57" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>47925900.540148139</v>
+        <v>48845230.55204767</v>
       </c>
       <c r="O57" s="180">
         <f t="shared" si="7"/>
-        <v>486792308.13757062</v>
+        <v>446221047.69261873</v>
       </c>
       <c r="P57" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>54088034.23750785</v>
+        <v>55777630.961577341</v>
       </c>
       <c r="Q57" s="185">
         <f t="shared" si="9"/>
-        <v>486792308.13757062</v>
+        <v>446221047.69261873</v>
       </c>
       <c r="R57" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>54088034.23750785</v>
+        <v>55777630.961577341</v>
       </c>
       <c r="T57" t="s">
         <v>120</v>
@@ -8244,47 +8241,47 @@
       </c>
       <c r="H58" s="114">
         <f t="shared" si="11"/>
-        <v>190526075.07154801</v>
+        <v>201386818.38223299</v>
       </c>
       <c r="I58" s="114">
         <f t="shared" si="1"/>
-        <v>52554915.529964998</v>
+        <v>54608591.209964</v>
       </c>
       <c r="J58" s="114">
         <f t="shared" si="2"/>
-        <v>135282119.23626</v>
+        <v>150961804.00620899</v>
       </c>
       <c r="K58" s="114">
         <f t="shared" si="3"/>
-        <v>378363109.83777303</v>
+        <v>406957213.59840596</v>
       </c>
       <c r="L58" s="187">
         <f t="shared" si="4"/>
-        <v>0.61564413765235848</v>
+        <v>0.66217032346155302</v>
       </c>
       <c r="M58" s="184">
         <f t="shared" si="5"/>
-        <v>205488716.83040434</v>
+        <v>176894613.06977141</v>
       </c>
       <c r="N58" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>22832079.647822704</v>
+        <v>22111826.633721426</v>
       </c>
       <c r="O58" s="180">
         <f t="shared" si="7"/>
-        <v>236217760.33925587</v>
+        <v>207623656.57862294</v>
       </c>
       <c r="P58" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>26246417.815472875</v>
+        <v>25952957.072327867</v>
       </c>
       <c r="Q58" s="185">
         <f t="shared" si="9"/>
-        <v>236217760.33925587</v>
+        <v>207623656.57862294</v>
       </c>
       <c r="R58" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>26246417.815472875</v>
+        <v>25952957.072327867</v>
       </c>
       <c r="T58" t="s">
         <v>125</v>
@@ -8318,7 +8315,7 @@
       </c>
       <c r="H59" s="114">
         <f t="shared" si="11"/>
-        <v>153958227.16</v>
+        <v>188527227.16</v>
       </c>
       <c r="I59" s="114">
         <f t="shared" si="1"/>
@@ -8330,35 +8327,35 @@
       </c>
       <c r="K59" s="114">
         <f t="shared" si="3"/>
-        <v>153958227.16</v>
+        <v>188527227.16</v>
       </c>
       <c r="L59" s="187">
         <f t="shared" si="4"/>
-        <v>0.34687251647239459</v>
+        <v>0.42475751322201688</v>
       </c>
       <c r="M59" s="184">
         <f t="shared" si="5"/>
-        <v>267696152.63759902</v>
+        <v>233127152.63759902</v>
       </c>
       <c r="N59" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>29744016.959733225</v>
+        <v>29140894.079699878</v>
       </c>
       <c r="O59" s="180">
         <f t="shared" si="7"/>
-        <v>289888488.41641998</v>
+        <v>255319488.41642001</v>
       </c>
       <c r="P59" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>32209832.046268888</v>
+        <v>31914936.052052502</v>
       </c>
       <c r="Q59" s="185">
         <f t="shared" si="9"/>
-        <v>289888488.41641998</v>
+        <v>255319488.41642001</v>
       </c>
       <c r="R59" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>32209832.046268888</v>
+        <v>31914936.052052502</v>
       </c>
       <c r="T59" t="s">
         <v>170</v>
@@ -8392,47 +8389,47 @@
       </c>
       <c r="H60" s="114">
         <f t="shared" si="11"/>
-        <v>225087203.80412</v>
+        <v>233723045.560087</v>
       </c>
       <c r="I60" s="114">
         <f t="shared" si="1"/>
-        <v>71590833.136556998</v>
+        <v>75195779.136546999</v>
       </c>
       <c r="J60" s="114">
         <f t="shared" si="2"/>
-        <v>76570716.532584995</v>
+        <v>77460806.632578999</v>
       </c>
       <c r="K60" s="114">
         <f t="shared" si="3"/>
-        <v>373248753.47326195</v>
+        <v>386379631.32921302</v>
       </c>
       <c r="L60" s="187">
         <f t="shared" si="4"/>
-        <v>0.64443653559289371</v>
+        <v>0.66710778996692532</v>
       </c>
       <c r="M60" s="184">
         <f t="shared" si="5"/>
-        <v>176978144.31330252</v>
+        <v>163847266.45735145</v>
       </c>
       <c r="N60" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>19664238.257033613</v>
+        <v>20480908.307168931</v>
       </c>
       <c r="O60" s="180">
         <f t="shared" si="7"/>
-        <v>205937454.72312176</v>
+        <v>192806576.86717069</v>
       </c>
       <c r="P60" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>22881939.413680196</v>
+        <v>24100822.108396336</v>
       </c>
       <c r="Q60" s="185">
         <f t="shared" si="9"/>
-        <v>205937454.72312176</v>
+        <v>192806576.86717069</v>
       </c>
       <c r="R60" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>22881939.413680196</v>
+        <v>24100822.108396336</v>
       </c>
       <c r="T60" t="s">
         <v>220</v>
@@ -8466,47 +8463,47 @@
       </c>
       <c r="H61" s="114">
         <f t="shared" si="11"/>
-        <v>340158082.01052099</v>
+        <v>357807886.12938398</v>
       </c>
       <c r="I61" s="114">
         <f t="shared" si="1"/>
-        <v>45384772.724923998</v>
+        <v>53379470.924923003</v>
       </c>
       <c r="J61" s="114">
         <f t="shared" si="2"/>
-        <v>148552415.809908</v>
+        <v>159507956.34990701</v>
       </c>
       <c r="K61" s="114">
         <f t="shared" si="3"/>
-        <v>534095270.54535306</v>
+        <v>570695313.40421402</v>
       </c>
       <c r="L61" s="187">
         <f t="shared" si="4"/>
-        <v>0.74532603368011296</v>
+        <v>0.79640112511213967</v>
       </c>
       <c r="M61" s="184">
         <f t="shared" si="5"/>
-        <v>146667890.93016934</v>
+        <v>110067848.07130837</v>
       </c>
       <c r="N61" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>16296432.325574372</v>
+        <v>13758481.008913547</v>
       </c>
       <c r="O61" s="180">
         <f t="shared" si="7"/>
-        <v>182497531.00782847</v>
+        <v>145897488.1489675</v>
       </c>
       <c r="P61" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>20277503.445314273</v>
+        <v>18237186.018620938</v>
       </c>
       <c r="Q61" s="185">
         <f t="shared" si="9"/>
-        <v>182497531.00782847</v>
+        <v>145897488.1489675</v>
       </c>
       <c r="R61" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>20277503.445314273</v>
+        <v>18237186.018620938</v>
       </c>
       <c r="T61" t="s">
         <v>126</v>
@@ -8540,47 +8537,47 @@
       </c>
       <c r="H62" s="114">
         <f t="shared" si="11"/>
-        <v>100376981.08205</v>
+        <v>117222800.908739</v>
       </c>
       <c r="I62" s="114">
         <f t="shared" si="1"/>
-        <v>29510144.3829</v>
+        <v>31388455.192899998</v>
       </c>
       <c r="J62" s="114">
         <f t="shared" si="2"/>
-        <v>144605955.29704899</v>
+        <v>173196225.567045</v>
       </c>
       <c r="K62" s="114">
         <f t="shared" si="3"/>
-        <v>274493080.76199901</v>
+        <v>321807481.66868401</v>
       </c>
       <c r="L62" s="187">
         <f t="shared" si="4"/>
-        <v>0.57542913560564091</v>
+        <v>0.67461591561427448</v>
       </c>
       <c r="M62" s="184">
         <f t="shared" si="5"/>
-        <v>178679013.92076242</v>
+        <v>131364613.01407743</v>
       </c>
       <c r="N62" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>19853223.768973604</v>
+        <v>16420576.626759678</v>
       </c>
       <c r="O62" s="180">
         <f t="shared" si="7"/>
-        <v>202530176.7988025</v>
+        <v>155215775.8921175</v>
       </c>
       <c r="P62" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>22503352.977644723</v>
+        <v>19401971.986514688</v>
       </c>
       <c r="Q62" s="185">
         <f t="shared" si="9"/>
-        <v>202530176.7988025</v>
+        <v>155215775.8921175</v>
       </c>
       <c r="R62" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>22503352.977644723</v>
+        <v>19401971.986514688</v>
       </c>
       <c r="T62" t="s">
         <v>112</v>
@@ -8614,47 +8611,47 @@
       </c>
       <c r="H63" s="114">
         <f t="shared" si="11"/>
-        <v>382275746.05234897</v>
+        <v>398672594.47329497</v>
       </c>
       <c r="I63" s="114">
         <f t="shared" si="1"/>
-        <v>181355173.74289101</v>
+        <v>225332673.160541</v>
       </c>
       <c r="J63" s="114">
         <f t="shared" si="2"/>
-        <v>225534639.125983</v>
+        <v>227840944.82587299</v>
       </c>
       <c r="K63" s="114">
         <f t="shared" si="3"/>
-        <v>789165558.92122293</v>
+        <v>851846212.45970905</v>
       </c>
       <c r="L63" s="187">
         <f t="shared" si="4"/>
-        <v>0.80611493369867415</v>
+        <v>0.87014181665139334</v>
       </c>
       <c r="M63" s="184">
         <f t="shared" si="5"/>
-        <v>140859738.5078932</v>
+        <v>78179084.969407082</v>
       </c>
       <c r="N63" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>15651082.056432579</v>
+        <v>9772385.6211758852</v>
       </c>
       <c r="O63" s="180">
         <f t="shared" si="7"/>
-        <v>189808438.37258363</v>
+        <v>127127784.8340975</v>
       </c>
       <c r="P63" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>21089826.485842627</v>
+        <v>15890973.104262188</v>
       </c>
       <c r="Q63" s="185">
         <f t="shared" si="9"/>
-        <v>189808438.37258363</v>
+        <v>127127784.8340975</v>
       </c>
       <c r="R63" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>21089826.485842627</v>
+        <v>15890973.104262188</v>
       </c>
       <c r="T63" t="s">
         <v>127</v>
@@ -8688,11 +8685,11 @@
       </c>
       <c r="H64" s="114">
         <f t="shared" si="11"/>
-        <v>93441982.305025995</v>
+        <v>104250263.40502599</v>
       </c>
       <c r="I64" s="114">
         <f t="shared" si="1"/>
-        <v>140729547.68318999</v>
+        <v>142578446.09257498</v>
       </c>
       <c r="J64" s="114">
         <f t="shared" si="2"/>
@@ -8700,35 +8697,35 @@
       </c>
       <c r="K64" s="114">
         <f t="shared" si="3"/>
-        <v>351846155.05705798</v>
+        <v>364503334.56644297</v>
       </c>
       <c r="L64" s="187">
         <f t="shared" si="4"/>
-        <v>0.65531154787803969</v>
+        <v>0.67888547579184677</v>
       </c>
       <c r="M64" s="184">
         <f t="shared" si="5"/>
-        <v>158222450.30561322</v>
+        <v>145565270.79622823</v>
       </c>
       <c r="N64" s="184">
         <f t="shared" ca="1" si="6"/>
-        <v>17580272.256179247</v>
+        <v>18195658.849528529</v>
       </c>
       <c r="O64" s="180">
         <f t="shared" si="7"/>
-        <v>185068166.37733281</v>
+        <v>172410986.86794782</v>
       </c>
       <c r="P64" s="180">
         <f t="shared" ca="1" si="8"/>
-        <v>20563129.597481422</v>
+        <v>21551373.358493477</v>
       </c>
       <c r="Q64" s="185">
         <f t="shared" si="9"/>
-        <v>185068166.37733281</v>
+        <v>172410986.86794782</v>
       </c>
       <c r="R64" s="185">
         <f t="shared" ca="1" si="10"/>
-        <v>20563129.597481422</v>
+        <v>21551373.358493477</v>
       </c>
       <c r="T64" t="s">
         <v>122</v>
@@ -8760,47 +8757,47 @@
       </c>
       <c r="H65" s="135">
         <f t="shared" si="12"/>
-        <v>2754073079.379343</v>
+        <v>2958880432.7472873</v>
       </c>
       <c r="I65" s="135">
         <f t="shared" si="12"/>
-        <v>750055640.30077207</v>
+        <v>838688962.31374085</v>
       </c>
       <c r="J65" s="135">
         <f t="shared" si="12"/>
-        <v>1918222447.7965229</v>
+        <v>2015978884.8363087</v>
       </c>
       <c r="K65" s="135">
         <f t="shared" si="12"/>
-        <v>5422351167.4766378</v>
+        <v>5813548279.897337</v>
       </c>
       <c r="L65" s="189">
         <f t="shared" si="4"/>
-        <v>0.61214408011164378</v>
+        <v>0.65630739398209903</v>
       </c>
       <c r="M65" s="181">
         <f>SUM(M51:M64)</f>
-        <v>2992716096.0396829</v>
+        <v>2601518983.6189842</v>
       </c>
       <c r="N65" s="181">
         <f t="shared" ca="1" si="6"/>
-        <v>332524010.67107588</v>
+        <v>325189872.95237303</v>
       </c>
       <c r="O65" s="181">
         <f>SUM(O51:O64)</f>
-        <v>3435614373.0668573</v>
+        <v>3044417260.6461592</v>
       </c>
       <c r="P65" s="181">
         <f t="shared" ca="1" si="8"/>
-        <v>381734930.3407619</v>
+        <v>380552157.5807699</v>
       </c>
       <c r="Q65" s="186">
         <f>SUM(Q51:Q64)</f>
-        <v>3435614373.0668573</v>
+        <v>3044417260.6461592</v>
       </c>
       <c r="R65" s="186">
         <f t="shared" ca="1" si="10"/>
-        <v>381734930.3407619</v>
+        <v>380552157.5807699</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8809,21 +8806,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="269" t="s">
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -8885,35 +8882,35 @@
       </c>
       <c r="E69" s="114">
         <f>IFERROR($C$31,0)</f>
-        <v>170853939.695351</v>
+        <v>202988607.005263</v>
       </c>
       <c r="F69" s="187">
         <f t="shared" ref="F69:F74" si="13">IFERROR(E69/D69,0)</f>
-        <v>0.66672755916154647</v>
+        <v>0.79212746704900239</v>
       </c>
       <c r="G69" s="184">
         <f>D69*$H$40-E69</f>
-        <v>72590688.444365382</v>
+        <v>40456021.134453386</v>
       </c>
       <c r="H69" s="184">
         <f t="shared" ref="H69:H74" ca="1" si="14">IFERROR(G69/$C$3,0)</f>
-        <v>8065632.0493739313</v>
+        <v>5057002.6418066733</v>
       </c>
       <c r="I69" s="204">
         <f>D69*$J$40-E69</f>
-        <v>85403563.609613627</v>
+        <v>53268896.299701631</v>
       </c>
       <c r="J69" s="204">
         <f t="shared" ref="J69:J74" ca="1" si="15">IFERROR(I69/$C$3,0)</f>
-        <v>9489284.8455126248</v>
+        <v>6658612.0374627039</v>
       </c>
       <c r="K69" s="185">
         <f>D69*$L$40-E69</f>
-        <v>85403563.609613627</v>
+        <v>53268896.299701631</v>
       </c>
       <c r="L69" s="185">
         <f t="shared" ref="L69:L74" ca="1" si="16">IFERROR(K69/$C$3,0)</f>
-        <v>9489284.8455126248</v>
+        <v>6658612.0374627039</v>
       </c>
     </row>
     <row r="70" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8921,7 +8918,7 @@
         <v>94</v>
       </c>
       <c r="C70" s="56" t="s">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="D70" s="117">
         <f>TARGETS!L23</f>
@@ -8929,35 +8926,35 @@
       </c>
       <c r="E70" s="114">
         <f>IFERROR($C$32,0)</f>
-        <v>405654939.35102898</v>
+        <v>408029398.87102902</v>
       </c>
       <c r="F70" s="187">
         <f t="shared" si="13"/>
-        <v>1.0152581621568042</v>
+        <v>1.0212008715251348</v>
       </c>
       <c r="G70" s="184">
         <f>D70*$H$40-E70</f>
-        <v>-26074447.66131264</v>
+        <v>-28448907.18131268</v>
       </c>
       <c r="H70" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>-2897160.8512569601</v>
+        <v>-3556113.397664085</v>
       </c>
       <c r="I70" s="204">
         <f>D70*$J$40-E70</f>
-        <v>-6096527.0460643768</v>
+        <v>-8470986.5660644174</v>
       </c>
       <c r="J70" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>-677391.89400715299</v>
+        <v>-1058873.3207580522</v>
       </c>
       <c r="K70" s="185">
         <f>D70*$L$40-E70</f>
-        <v>-6096527.0460643768</v>
+        <v>-8470986.5660644174</v>
       </c>
       <c r="L70" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>-677391.89400715299</v>
+        <v>-1058873.3207580522</v>
       </c>
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.25">
@@ -8973,35 +8970,35 @@
       </c>
       <c r="E71" s="114">
         <f>M21</f>
-        <v>483922631.14035797</v>
+        <v>543057028.79973006</v>
       </c>
       <c r="F71" s="187">
         <f t="shared" si="13"/>
-        <v>0.44617217463826292</v>
+        <v>0.50069354045542247</v>
       </c>
       <c r="G71" s="184">
         <f>D71*$H$40-E71</f>
-        <v>546456504.34935832</v>
+        <v>487322106.68998623</v>
       </c>
       <c r="H71" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>60717389.372150928</v>
+        <v>60915263.336248279</v>
       </c>
       <c r="I71" s="204">
         <f>D71*$J$40-E71</f>
-        <v>600686985.16460657</v>
+        <v>541552587.50523448</v>
       </c>
       <c r="J71" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>66742998.351622954</v>
+        <v>67694073.43815431</v>
       </c>
       <c r="K71" s="185">
         <f>D71*$L$40-E71</f>
-        <v>600686985.16460657</v>
+        <v>541552587.50523448</v>
       </c>
       <c r="L71" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>66742998.351622954</v>
+        <v>67694073.43815431</v>
       </c>
     </row>
     <row r="72" spans="2:21" hidden="1" x14ac:dyDescent="0.25">
@@ -9103,35 +9100,35 @@
       </c>
       <c r="E74" s="115">
         <f>SUM(E69:E73)</f>
-        <v>1060431510.186738</v>
+        <v>1154075034.6760221</v>
       </c>
       <c r="F74" s="177">
         <f t="shared" si="13"/>
-        <v>0.60929438849360251</v>
+        <v>0.66309934755223765</v>
       </c>
       <c r="G74" s="181">
         <f>SUM(G69:G73)</f>
-        <v>592972745.132411</v>
+        <v>499329220.64312696</v>
       </c>
       <c r="H74" s="181">
         <f t="shared" ca="1" si="14"/>
-        <v>65885860.570267886</v>
+        <v>62416152.580390871</v>
       </c>
       <c r="I74" s="186">
         <f>SUM(I69:I73)</f>
-        <v>679994021.72815585</v>
+        <v>586350497.23887169</v>
       </c>
       <c r="J74" s="186">
         <f t="shared" ca="1" si="15"/>
-        <v>75554891.303128421</v>
+        <v>73293812.154858962</v>
       </c>
       <c r="K74" s="186">
         <f>SUM(K69:K73)</f>
-        <v>679994021.72815585</v>
+        <v>586350497.23887169</v>
       </c>
       <c r="L74" s="186">
         <f t="shared" ca="1" si="16"/>
-        <v>75554891.303128421</v>
+        <v>73293812.154858962</v>
       </c>
     </row>
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9144,10 +9141,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -9176,7 +9173,7 @@
       </c>
       <c r="D80" s="131">
         <f>SUMIF($B$10:$B$26,$T80,$F$10:$F$26)+SUMIF($B$10:$B$26,$U80,$F$10:$F$26)</f>
-        <v>309253837.03988498</v>
+        <v>305992102.95987999</v>
       </c>
       <c r="T80" t="str">
         <f t="shared" ref="T80:U93" si="17">T51</f>
@@ -9196,7 +9193,7 @@
       </c>
       <c r="D81" s="132">
         <f t="shared" ref="D81:D93" si="18">SUMIF($B$10:$B$26,$T81,$F$10:$F$26)+SUMIF($B$10:$B$26,$U81,$F$10:$F$26)</f>
-        <v>97823393.579999998</v>
+        <v>127390960.91</v>
       </c>
       <c r="T81" t="str">
         <f t="shared" si="17"/>
@@ -9236,7 +9233,7 @@
       </c>
       <c r="D83" s="131">
         <f t="shared" si="18"/>
-        <v>306826077.50980502</v>
+        <v>320372564.56976998</v>
       </c>
       <c r="T83" t="str">
         <f t="shared" si="17"/>
@@ -9276,7 +9273,7 @@
       </c>
       <c r="D85" s="131">
         <f t="shared" si="18"/>
-        <v>37502972.57</v>
+        <v>40335405.060000002</v>
       </c>
       <c r="T85" t="str">
         <f t="shared" si="17"/>
@@ -9296,7 +9293,7 @@
       </c>
       <c r="D86" s="132">
         <f t="shared" si="18"/>
-        <v>751459090.97996902</v>
+        <v>760950711.77996898</v>
       </c>
       <c r="T86" t="str">
         <f t="shared" si="17"/>
@@ -9316,7 +9313,7 @@
       </c>
       <c r="D87" s="131">
         <f t="shared" si="18"/>
-        <v>229480815.92959601</v>
+        <v>246882618.74950501</v>
       </c>
       <c r="T87" t="str">
         <f t="shared" si="17"/>
@@ -9356,7 +9353,7 @@
       </c>
       <c r="D89" s="132">
         <f t="shared" si="18"/>
-        <v>38054054.829999998</v>
+        <v>39783784.579999998</v>
       </c>
       <c r="T89" t="str">
         <f t="shared" si="17"/>
@@ -9376,7 +9373,7 @@
       </c>
       <c r="D90" s="131">
         <f t="shared" si="18"/>
-        <v>433853334.65957397</v>
+        <v>468670407.23952502</v>
       </c>
       <c r="T90" t="str">
         <f t="shared" si="17"/>
@@ -9396,7 +9393,7 @@
       </c>
       <c r="D91" s="132">
         <f t="shared" si="18"/>
-        <v>109734631.169943</v>
+        <v>122621117.86994299</v>
       </c>
       <c r="T91" t="str">
         <f t="shared" si="17"/>
@@ -9416,7 +9413,7 @@
       </c>
       <c r="D92" s="131">
         <f t="shared" si="18"/>
-        <v>15098054.3574</v>
+        <v>18013297.6536</v>
       </c>
       <c r="T92" t="str">
         <f t="shared" si="17"/>
@@ -9436,7 +9433,7 @@
       </c>
       <c r="D93" s="132">
         <f t="shared" si="18"/>
-        <v>122039462.09799999</v>
+        <v>125671894.618</v>
       </c>
       <c r="T93" t="str">
         <f t="shared" si="17"/>
@@ -9454,12 +9451,18 @@
       <c r="C94" s="58"/>
       <c r="D94" s="120">
         <f>SUM(D80:D93)</f>
-        <v>2467966535.0841718</v>
+        <v>2593525676.3501921</v>
       </c>
     </row>
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -9474,12 +9477,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -10107,11 +10104,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>163</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -10431,33 +10428,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -10466,49 +10463,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -10533,13 +10530,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -11655,21 +11652,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="269" t="s">
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -11990,10 +11987,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -12306,6 +12303,12 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -12320,12 +12323,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -12953,11 +12950,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>175</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -13277,33 +13274,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -13312,49 +13309,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -13379,13 +13376,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -14501,21 +14498,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="269" t="s">
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -14836,10 +14833,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -15152,6 +15149,12 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -15166,12 +15169,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -15799,11 +15796,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>177</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -16123,33 +16120,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -16158,49 +16155,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -16225,13 +16222,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -17333,21 +17330,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="269" t="s">
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -17668,10 +17665,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -17984,6 +17981,12 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -17998,12 +18001,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -25783,11 +25780,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="259" t="s">
+      <c r="B41" s="269" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="260"/>
-      <c r="D41" s="261"/>
+      <c r="C41" s="270"/>
+      <c r="D41" s="271"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -26058,59 +26055,59 @@
       </c>
     </row>
     <row r="48" spans="2:19" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="270"/>
-      <c r="M48" s="270"/>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="271"/>
+      <c r="L48" s="261"/>
+      <c r="M48" s="261"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
       <c r="Q48"/>
       <c r="R48"/>
     </row>
     <row r="49" spans="2:18" s="139" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="267" t="s">
+      <c r="B49" s="277" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="267" t="s">
+      <c r="C49" s="277" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="264" t="s">
+      <c r="D49" s="274" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="265"/>
-      <c r="F49" s="266"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
       <c r="G49" s="140" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="140"/>
       <c r="I49" s="140"/>
-      <c r="J49" s="264" t="s">
+      <c r="J49" s="274" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="272" t="str">
+      <c r="K49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="272" t="str">
+      <c r="L49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
@@ -26125,7 +26122,7 @@
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="276" t="str">
+      <c r="P49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -26134,8 +26131,8 @@
       <c r="R49"/>
     </row>
     <row r="50" spans="2:18" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="267"/>
-      <c r="C50" s="267"/>
+      <c r="B50" s="277"/>
+      <c r="C50" s="277"/>
       <c r="D50" s="141" t="s">
         <v>149</v>
       </c>
@@ -26154,13 +26151,13 @@
       <c r="I50" s="142" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="264"/>
-      <c r="K50" s="273"/>
-      <c r="L50" s="273"/>
-      <c r="M50" s="275"/>
+      <c r="J50" s="274"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="266"/>
       <c r="N50" s="188"/>
       <c r="O50" s="183"/>
-      <c r="P50" s="277"/>
+      <c r="P50" s="268"/>
       <c r="Q50"/>
       <c r="R50"/>
     </row>
@@ -27501,10 +27498,10 @@
       <c r="I77"/>
     </row>
     <row r="78" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -27703,6 +27700,13 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="J49:J50"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
     <mergeCell ref="K48:P48"/>
@@ -27712,13 +27716,6 @@
     <mergeCell ref="P49:P50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="J49:J50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="26" priority="8">
@@ -28758,25 +28755,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="270"/>
-      <c r="M48" s="270"/>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="271"/>
+      <c r="L48" s="261"/>
+      <c r="M48" s="261"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -28798,32 +28795,32 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="272" t="str">
+      <c r="K49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="272" t="str">
+      <c r="L49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="274" t="str">
+      <c r="N49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="276" t="str">
+      <c r="O49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="276" t="str">
+      <c r="P49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -28851,12 +28848,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="273"/>
-      <c r="L50" s="273"/>
-      <c r="M50" s="275"/>
-      <c r="N50" s="275"/>
-      <c r="O50" s="277"/>
-      <c r="P50" s="277"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="266"/>
+      <c r="N50" s="266"/>
+      <c r="O50" s="268"/>
+      <c r="P50" s="268"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="167" t="s">
@@ -30093,10 +30090,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -30290,6 +30287,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -30297,17 +30305,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -31065,11 +31062,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="259" t="s">
+      <c r="B41" s="269" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="260"/>
-      <c r="D41" s="261"/>
+      <c r="C41" s="270"/>
+      <c r="D41" s="271"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -31344,25 +31341,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="270"/>
-      <c r="M48" s="270"/>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="271"/>
+      <c r="L48" s="261"/>
+      <c r="M48" s="261"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -31384,32 +31381,32 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="272" t="str">
+      <c r="K49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="272" t="str">
+      <c r="L49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="274" t="str">
+      <c r="N49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="276" t="str">
+      <c r="O49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="276" t="str">
+      <c r="P49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -31437,12 +31434,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="273"/>
-      <c r="L50" s="273"/>
-      <c r="M50" s="275"/>
-      <c r="N50" s="275"/>
-      <c r="O50" s="277"/>
-      <c r="P50" s="277"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="266"/>
+      <c r="N50" s="266"/>
+      <c r="O50" s="268"/>
+      <c r="P50" s="268"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -32679,10 +32676,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -32863,6 +32860,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -32870,17 +32878,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -33659,11 +33656,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" s="191" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="259" t="s">
+      <c r="B41" s="269" t="s">
         <v>189</v>
       </c>
-      <c r="C41" s="260"/>
-      <c r="D41" s="261"/>
+      <c r="C41" s="270"/>
+      <c r="D41" s="271"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -33938,25 +33935,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="270"/>
-      <c r="M48" s="270"/>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="271"/>
+      <c r="L48" s="261"/>
+      <c r="M48" s="261"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
     </row>
     <row r="49" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -33978,22 +33975,22 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="272" t="str">
+      <c r="K49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="272" t="str">
+      <c r="L49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="274" t="str">
+      <c r="N49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
@@ -34031,10 +34028,10 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="273"/>
-      <c r="L50" s="273"/>
-      <c r="M50" s="275"/>
-      <c r="N50" s="275"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="266"/>
+      <c r="N50" s="266"/>
       <c r="O50" s="282"/>
       <c r="P50" s="282"/>
     </row>
@@ -35273,10 +35270,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -35470,6 +35467,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
@@ -35483,11 +35485,6 @@
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -909,7 +909,7 @@
     <t>RONALD</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL —  22 SEPTEMBER 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL —  23 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>
@@ -2556,6 +2556,33 @@
     <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2586,33 +2613,6 @@
     <xf numFmtId="0" fontId="48" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2626,6 +2626,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2647,15 +2656,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4299,11 +4299,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="259" t="s">
         <v>219</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="260"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -4623,33 +4623,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="263"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="270"/>
+      <c r="Q48" s="270"/>
+      <c r="R48" s="271"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -4658,49 +4658,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="268"/>
+      <c r="C50" s="268"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -4725,13 +4725,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="273"/>
+      <c r="N50" s="273"/>
+      <c r="O50" s="275"/>
+      <c r="P50" s="275"/>
+      <c r="Q50" s="277"/>
+      <c r="R50" s="277"/>
       <c r="T50" s="172" t="s">
         <v>216</v>
       </c>
@@ -5847,21 +5847,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="283" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
-      <c r="F67" s="292"/>
-      <c r="G67" s="260" t="s">
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
+      <c r="F67" s="285"/>
+      <c r="G67" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="270"/>
+      <c r="I67" s="270"/>
+      <c r="J67" s="270"/>
+      <c r="K67" s="270"/>
+      <c r="L67" s="271"/>
     </row>
     <row r="68" spans="2:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -6180,10 +6180,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -6495,12 +6495,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -6515,6 +6509,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="C3" s="75">
         <f ca="1">IF($J$5&lt;&gt;"",$J$5,MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),9,1)),EOMONTH(DATE(YEAR(TODAY()),9,1),0),11)-MAX(0,$J$3-$J$4)))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" s="76" t="s">
         <v>104</v>
@@ -6720,19 +6720,19 @@
         <v>112</v>
       </c>
       <c r="C10" s="234">
-        <v>117222800.908739</v>
+        <v>122534293.762722</v>
       </c>
       <c r="D10" s="234">
-        <v>31388455.192899998</v>
+        <v>33718196.818899997</v>
       </c>
       <c r="E10" s="234">
-        <v>173196225.567045</v>
+        <v>175612225.567045</v>
       </c>
       <c r="F10" s="234">
-        <v>122621117.86994299</v>
+        <v>126163149.179938</v>
       </c>
       <c r="G10" s="234">
-        <v>444428599.53862703</v>
+        <v>458027865.328605</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="111"/>
@@ -6748,7 +6748,7 @@
         <v>4173423.4199979999</v>
       </c>
       <c r="D11" s="234">
-        <v>16503315.6</v>
+        <v>30250983.5</v>
       </c>
       <c r="E11" s="234">
         <v>199157658.6392</v>
@@ -6757,7 +6757,7 @@
         <v>165</v>
       </c>
       <c r="G11" s="234">
-        <v>219834397.65919799</v>
+        <v>233582065.55919799</v>
       </c>
       <c r="H11" s="111"/>
       <c r="I11" s="111"/>
@@ -6770,19 +6770,19 @@
         <v>70</v>
       </c>
       <c r="C12" s="234">
-        <v>136887903.46735299</v>
+        <v>144079108.13797399</v>
       </c>
       <c r="D12" s="234">
-        <v>64137847.651524998</v>
+        <v>64996955.761524998</v>
       </c>
       <c r="E12" s="234">
-        <v>133871985.199589</v>
+        <v>139985543.73958299</v>
       </c>
       <c r="F12" s="234">
-        <v>63360769.850000001</v>
+        <v>65596580.700000003</v>
       </c>
       <c r="G12" s="234">
-        <v>398258506.16846699</v>
+        <v>414658188.339082</v>
       </c>
       <c r="H12" s="111"/>
       <c r="I12" s="111"/>
@@ -6795,19 +6795,19 @@
         <v>114</v>
       </c>
       <c r="C13" s="234">
-        <v>28415976.749961998</v>
+        <v>29542102.929949999</v>
       </c>
       <c r="D13" s="234">
-        <v>18071800.219973002</v>
+        <v>18570309.229973</v>
       </c>
       <c r="E13" s="234">
-        <v>156752028.56966901</v>
+        <v>163454911.61964399</v>
       </c>
       <c r="F13" s="234">
-        <v>64030191.060000002</v>
+        <v>66006137.100000001</v>
       </c>
       <c r="G13" s="234">
-        <v>267269996.59960401</v>
+        <v>277573460.87956703</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="111"/>
@@ -6820,19 +6820,19 @@
         <v>115</v>
       </c>
       <c r="C14" s="234">
-        <v>396973429.52460003</v>
+        <v>423669713.43459803</v>
       </c>
       <c r="D14" s="234">
-        <v>37481186.411467001</v>
+        <v>38215060.301464997</v>
       </c>
       <c r="E14" s="234">
-        <v>117286536.1999</v>
+        <v>138709153.37987801</v>
       </c>
       <c r="F14" s="234">
-        <v>320372564.56976998</v>
+        <v>342828960.75976998</v>
       </c>
       <c r="G14" s="234">
-        <v>872113716.70573699</v>
+        <v>943422887.87571096</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="111"/>
@@ -6845,10 +6845,10 @@
         <v>118</v>
       </c>
       <c r="C15" s="234">
-        <v>1089786700.000098</v>
+        <v>1462364582.0499079</v>
       </c>
       <c r="D15" s="234">
-        <v>8915041.3269239999</v>
+        <v>9178230.5349240005</v>
       </c>
       <c r="E15" s="234">
         <v>59318395.269938998</v>
@@ -6857,7 +6857,7 @@
         <v>13983784.08</v>
       </c>
       <c r="G15" s="234">
-        <v>1172003920.6769609</v>
+        <v>1544844991.9347711</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="111"/>
@@ -6870,19 +6870,19 @@
         <v>120</v>
       </c>
       <c r="C16" s="234">
-        <v>371501562.66268098</v>
+        <v>403308935.481655</v>
       </c>
       <c r="D16" s="234">
-        <v>36300643.119926997</v>
+        <v>38062931.419927001</v>
       </c>
       <c r="E16" s="234">
-        <v>255160812.04951999</v>
+        <v>263379730.93952</v>
       </c>
       <c r="F16" s="234">
-        <v>760950711.77996898</v>
+        <v>830718820.72996902</v>
       </c>
       <c r="G16" s="234">
-        <v>1423913729.612097</v>
+        <v>1535470418.5710709</v>
       </c>
       <c r="H16" s="111"/>
       <c r="I16" s="111"/>
@@ -6895,19 +6895,19 @@
         <v>122</v>
       </c>
       <c r="C17" s="234">
-        <v>91170215.815028995</v>
+        <v>93324215.815028995</v>
       </c>
       <c r="D17" s="234">
         <v>12915436.9209</v>
       </c>
       <c r="E17" s="234">
-        <v>70679078.968842</v>
+        <v>72454578.968842</v>
       </c>
       <c r="F17" s="234">
-        <v>36655676.498000003</v>
+        <v>47952973.898000002</v>
       </c>
       <c r="G17" s="234">
-        <v>211420408.20277101</v>
+        <v>226647205.60277101</v>
       </c>
       <c r="H17" s="111"/>
       <c r="I17" s="111"/>
@@ -6924,16 +6924,16 @@
         <v>13080047.589996999</v>
       </c>
       <c r="D18" s="234">
-        <v>129663009.171675</v>
+        <v>133208702.091655</v>
       </c>
       <c r="E18" s="234">
-        <v>46995546.100000001</v>
+        <v>56002106.100000001</v>
       </c>
       <c r="F18" s="234">
-        <v>89016218.120000005</v>
+        <v>93318920.920000002</v>
       </c>
       <c r="G18" s="234">
-        <v>278754820.98167199</v>
+        <v>295609776.70165199</v>
       </c>
       <c r="H18" s="111"/>
       <c r="I18" s="111"/>
@@ -7003,26 +7003,26 @@
         <v>124</v>
       </c>
       <c r="C21" s="234">
-        <v>212724104.35944599</v>
+        <v>221268705.06241599</v>
       </c>
       <c r="D21" s="234">
-        <v>41095408.883458003</v>
+        <v>41719931.423455998</v>
       </c>
       <c r="E21" s="234">
-        <v>121013203.27980299</v>
+        <v>127850860.93978301</v>
       </c>
       <c r="F21" s="234">
-        <v>305992102.95987999</v>
+        <v>340035346.74985999</v>
       </c>
       <c r="G21" s="234">
-        <v>680824819.48258698</v>
+        <v>730874844.17551506</v>
       </c>
       <c r="H21" s="111"/>
       <c r="I21" s="111"/>
       <c r="J21" s="111"/>
       <c r="M21" s="14">
         <f>SUM(C33,C34)+M20</f>
-        <v>543057028.79973006</v>
+        <v>932747039.34663296</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>224</v>
@@ -7033,19 +7033,19 @@
         <v>125</v>
       </c>
       <c r="C22" s="234">
-        <v>201386818.38223299</v>
+        <v>218343790.722233</v>
       </c>
       <c r="D22" s="234">
-        <v>54608591.209964</v>
+        <v>55894289.419963002</v>
       </c>
       <c r="E22" s="234">
-        <v>150961804.00620899</v>
+        <v>162558650.86619499</v>
       </c>
       <c r="F22" s="234">
-        <v>246882618.74950501</v>
+        <v>257288564.68950501</v>
       </c>
       <c r="G22" s="234">
-        <v>653839832.347911</v>
+        <v>694085295.697896</v>
       </c>
       <c r="H22" s="111"/>
       <c r="I22" s="111"/>
@@ -7056,19 +7056,19 @@
         <v>126</v>
       </c>
       <c r="C23" s="234">
-        <v>357807886.12938398</v>
+        <v>386015669.137429</v>
       </c>
       <c r="D23" s="234">
-        <v>53379470.924923003</v>
+        <v>55017470.924923003</v>
       </c>
       <c r="E23" s="234">
-        <v>159507956.34990701</v>
+        <v>174500614.40990701</v>
       </c>
       <c r="F23" s="234">
-        <v>468670407.23952502</v>
+        <v>483452299.52950501</v>
       </c>
       <c r="G23" s="234">
-        <v>1039365720.643739</v>
+        <v>1098986054.0017641</v>
       </c>
       <c r="H23" s="111"/>
       <c r="I23" s="111"/>
@@ -7079,19 +7079,19 @@
         <v>225</v>
       </c>
       <c r="C24" s="234">
-        <v>148754687.584483</v>
+        <v>157144378.35867101</v>
       </c>
       <c r="D24" s="234">
-        <v>42615344.709941</v>
+        <v>44687069.909941003</v>
       </c>
       <c r="E24" s="234">
-        <v>126094298.448173</v>
+        <v>126616820.968173</v>
       </c>
       <c r="F24" s="234">
-        <v>40335405.060000002</v>
+        <v>56855405.259999998</v>
       </c>
       <c r="G24" s="234">
-        <v>357799735.80259699</v>
+        <v>385303674.49678499</v>
       </c>
       <c r="H24" s="111"/>
       <c r="I24" s="111"/>
@@ -7102,19 +7102,19 @@
         <v>220</v>
       </c>
       <c r="C25" s="234">
-        <v>233723045.560087</v>
+        <v>259986756.55092999</v>
       </c>
       <c r="D25" s="234">
-        <v>75195779.136546999</v>
+        <v>75962454.816541001</v>
       </c>
       <c r="E25" s="234">
-        <v>77460806.632578999</v>
+        <v>85307067.912571996</v>
       </c>
       <c r="F25" s="234">
         <v>39783784.579999998</v>
       </c>
       <c r="G25" s="234">
-        <v>426163415.90921301</v>
+        <v>461040063.86004299</v>
       </c>
       <c r="H25" s="111"/>
       <c r="I25" s="111"/>
@@ -7125,19 +7125,19 @@
         <v>127</v>
       </c>
       <c r="C26" s="234">
-        <v>398672594.47329497</v>
+        <v>399272594.47329497</v>
       </c>
       <c r="D26" s="234">
-        <v>225332673.160541</v>
+        <v>254167394.92625701</v>
       </c>
       <c r="E26" s="234">
-        <v>227840944.82587299</v>
+        <v>229102206.125873</v>
       </c>
       <c r="F26" s="234">
         <v>18013297.6536</v>
       </c>
       <c r="G26" s="234">
-        <v>869859510.11330903</v>
+        <v>900555493.17902505</v>
       </c>
       <c r="H26" s="111"/>
       <c r="I26" s="111"/>
@@ -7180,7 +7180,7 @@
         <v>131</v>
       </c>
       <c r="C31" s="171">
-        <v>202988607.005263</v>
+        <v>203469688.08525699</v>
       </c>
       <c r="G31" s="111"/>
       <c r="H31" s="111"/>
@@ -7191,7 +7191,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="234">
-        <v>408029398.87102902</v>
+        <v>415017182.90095901</v>
       </c>
       <c r="G32" s="111"/>
       <c r="H32" s="111"/>
@@ -7201,8 +7201,8 @@
       <c r="B33" s="81" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="234">
-        <v>108960185.688379</v>
+      <c r="C33" s="171">
+        <v>491062628.31530601</v>
       </c>
       <c r="G33" s="111"/>
       <c r="H33" s="111"/>
@@ -7213,7 +7213,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="234">
-        <v>434096843.11135101</v>
+        <v>441684411.03132701</v>
       </c>
       <c r="G34" s="111"/>
       <c r="H34" s="111"/>
@@ -7258,17 +7258,17 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="259" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="260"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
       <c r="F40" s="174">
         <f ca="1">IF(MONTH(TODAY())=9,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;9,1,0))</f>
-        <v>0.73333333333333328</v>
+        <v>0.76666666666666672</v>
       </c>
       <c r="G40" s="192" t="s">
         <v>187</v>
@@ -7355,35 +7355,35 @@
       </c>
       <c r="E42" s="46">
         <f>H65</f>
-        <v>2958880432.7472873</v>
+        <v>3122129670.9968972</v>
       </c>
       <c r="F42" s="176">
         <f>IFERROR(E42/D42,0)</f>
-        <v>0.65581133738320951</v>
+        <v>0.69199417873035451</v>
       </c>
       <c r="G42" s="184">
         <f>D42*$H$40-E42</f>
-        <v>1327316299.267139</v>
+        <v>1164067061.017529</v>
       </c>
       <c r="H42" s="184">
         <f ca="1">IFERROR(G42/$C$3,0)</f>
-        <v>165914537.40839237</v>
+        <v>166295294.43107557</v>
       </c>
       <c r="I42" s="204">
         <f>D42*$J$40-E42</f>
-        <v>1552905600.9521089</v>
+        <v>1389656362.7024989</v>
       </c>
       <c r="J42" s="204">
         <f ca="1">IFERROR(I42/$C$3,0)</f>
-        <v>194113200.11901361</v>
+        <v>198522337.52892843</v>
       </c>
       <c r="K42" s="185">
         <f>D42*$L$40-E42</f>
-        <v>1552905600.9521089</v>
+        <v>1389656362.7024989</v>
       </c>
       <c r="L42" s="185">
         <f ca="1">IFERROR(K42/$C$3,0)</f>
-        <v>194113200.11901361</v>
+        <v>198522337.52892843</v>
       </c>
       <c r="S42" s="173">
         <v>0.8</v>
@@ -7402,35 +7402,35 @@
       </c>
       <c r="E43" s="46">
         <f>I65</f>
-        <v>838688962.31374085</v>
+        <v>897387187.46542609</v>
       </c>
       <c r="F43" s="176">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.59847989387240885</v>
+        <v>0.64036634896818712</v>
       </c>
       <c r="G43" s="184">
         <f>D43*$H$40-E43</f>
-        <v>492608082.6759032</v>
+        <v>433909857.52421796</v>
       </c>
       <c r="H43" s="184">
         <f ca="1">IFERROR(G43/$C$3,0)</f>
-        <v>61576010.3344879</v>
+        <v>61987122.503459707</v>
       </c>
       <c r="I43" s="204">
         <f>D43*$J$40-E43</f>
-        <v>562676348.2016741</v>
+        <v>503978123.04998887</v>
       </c>
       <c r="J43" s="204">
         <f ca="1">IFERROR(I43/$C$3,0)</f>
-        <v>70334543.525209263</v>
+        <v>71996874.721426979</v>
       </c>
       <c r="K43" s="185">
         <f>D43*$L$40-E43</f>
-        <v>562676348.2016741</v>
+        <v>503978123.04998887</v>
       </c>
       <c r="L43" s="185">
         <f ca="1">IFERROR(K43/$C$3,0)</f>
-        <v>70334543.525209263</v>
+        <v>71996874.721426979</v>
       </c>
       <c r="S43" s="173">
         <v>0.85</v>
@@ -7449,35 +7449,35 @@
       </c>
       <c r="E44" s="46">
         <f>J65</f>
-        <v>2015978884.8363087</v>
+        <v>2114692130.1762149</v>
       </c>
       <c r="F44" s="176">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.68458610643402895</v>
+        <v>0.71810715012601212</v>
       </c>
       <c r="G44" s="184">
         <f>IF(D44=0,0,D44*$H$40-E44)</f>
-        <v>781594601.67594218</v>
+        <v>682881356.33603597</v>
       </c>
       <c r="H44" s="184">
         <f ca="1">IFERROR(G44/$C$3,0)</f>
-        <v>97699325.209492773</v>
+        <v>97554479.476576567</v>
       </c>
       <c r="I44" s="204">
         <f>IF(D44=0,0,D44*$J$40-E44)</f>
-        <v>928835311.49237657</v>
+        <v>830122066.15247035</v>
       </c>
       <c r="J44" s="204">
         <f ca="1">IFERROR(I44/$C$3,0)</f>
-        <v>116104413.93654707</v>
+        <v>118588866.59321006</v>
       </c>
       <c r="K44" s="185">
         <f>IF(D44=0,0,D44*$L$40-E44)</f>
-        <v>928835311.49237657</v>
+        <v>830122066.15247035</v>
       </c>
       <c r="L44" s="185">
         <f ca="1">IFERROR(K44/$C$3,0)</f>
-        <v>116104413.93654707</v>
+        <v>118588866.59321006</v>
       </c>
       <c r="S44" s="173">
         <v>0.9</v>
@@ -7496,35 +7496,35 @@
       </c>
       <c r="E45" s="46">
         <f>E74</f>
-        <v>1154075034.6760221</v>
+        <v>1551233910.332849</v>
       </c>
       <c r="F45" s="176">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.66309934755223765</v>
+        <v>0.89129576755065898</v>
       </c>
       <c r="G45" s="184">
         <f>D45*$H$40-E45</f>
-        <v>499329220.64312673</v>
+        <v>102170344.98629975</v>
       </c>
       <c r="H45" s="184">
         <f ca="1">IFERROR(G45/$C$3,0)</f>
-        <v>62416152.580390841</v>
+        <v>14595763.569471393</v>
       </c>
       <c r="I45" s="204">
         <f>D45*$J$40-E45</f>
-        <v>586350497.23887157</v>
+        <v>189191621.5820446</v>
       </c>
       <c r="J45" s="204">
         <f ca="1">IFERROR(I45/$C$3,0)</f>
-        <v>73293812.154858947</v>
+        <v>27027374.511720657</v>
       </c>
       <c r="K45" s="185">
         <f>D45*$L$40-E45</f>
-        <v>586350497.23887157</v>
+        <v>189191621.5820446</v>
       </c>
       <c r="L45" s="185">
         <f ca="1">IFERROR(K45/$C$3,0)</f>
-        <v>73293812.154858947</v>
+        <v>27027374.511720657</v>
       </c>
       <c r="S45" s="173">
         <v>0.95</v>
@@ -7541,35 +7541,35 @@
       </c>
       <c r="E46" s="47">
         <f>SUM(E42:E45)</f>
-        <v>6967623314.5733585</v>
+        <v>7685442898.9713879</v>
       </c>
       <c r="F46" s="177">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.65742274152157287</v>
+        <v>0.72515185054297882</v>
       </c>
       <c r="G46" s="181">
         <f>SUM(G42:G45)</f>
-        <v>3100848204.2621107</v>
+        <v>2383028619.8640823</v>
       </c>
       <c r="H46" s="181">
         <f ca="1">IFERROR(G46/$C$3,0)</f>
-        <v>387606025.53276384</v>
+        <v>340432659.98058319</v>
       </c>
       <c r="I46" s="186">
         <f>SUM(I42:I45)</f>
-        <v>3630767757.8850307</v>
+        <v>2912948173.4870024</v>
       </c>
       <c r="J46" s="186">
         <f ca="1">IFERROR(I46/$C$3,0)</f>
-        <v>453845969.73562884</v>
+        <v>416135453.35528606</v>
       </c>
       <c r="K46" s="186">
         <f>SUM(K42:K45)</f>
-        <v>3630767757.8850307</v>
+        <v>2912948173.4870024</v>
       </c>
       <c r="L46" s="186">
         <f ca="1">IFERROR(K46/$C$3,0)</f>
-        <v>453845969.73562884</v>
+        <v>416135453.35528606</v>
       </c>
       <c r="S46" s="173">
         <v>1</v>
@@ -7582,33 +7582,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="263"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="270"/>
+      <c r="Q48" s="270"/>
+      <c r="R48" s="271"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -7617,49 +7617,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="268"/>
+      <c r="C50" s="268"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -7684,13 +7684,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="273"/>
+      <c r="N50" s="273"/>
+      <c r="O50" s="275"/>
+      <c r="P50" s="275"/>
+      <c r="Q50" s="277"/>
+      <c r="R50" s="277"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -7723,47 +7723,47 @@
       </c>
       <c r="H51" s="114">
         <f>SUMIF($B$10:$B$26,$T51,C$10:C$26)+SUMIF($B$10:$B$26,$U51,C$10:C$26)</f>
-        <v>212724104.35944599</v>
+        <v>221268705.06241599</v>
       </c>
       <c r="I51" s="114">
-        <f t="shared" ref="I51:I64" si="1">SUMIF($B$10:$B$26,$T51,D$10:D$26)+SUMIF($B$10:$B$26,$U51,D$10:D$26)</f>
-        <v>41095408.883458003</v>
+        <f>SUMIF($B$10:$B$26,$T51,D$10:D$26)+SUMIF($B$10:$B$26,$U51,D$10:D$26)</f>
+        <v>41719931.423455998</v>
       </c>
       <c r="J51" s="114">
-        <f t="shared" ref="J51:J64" si="2">SUMIF($B$10:$B$26,$T51,E$10:E$26)+SUMIF($B$10:$B$26,$U51,E$10:E$26)</f>
-        <v>121013203.27980299</v>
+        <f>SUMIF($B$10:$B$26,$T51,E$10:E$26)+SUMIF($B$10:$B$26,$U51,E$10:E$26)</f>
+        <v>127850860.93978301</v>
       </c>
       <c r="K51" s="114">
-        <f t="shared" ref="K51:K64" si="3">SUM(H51:J51)</f>
-        <v>374832716.52270699</v>
+        <f t="shared" ref="K51:K64" si="1">SUM(H51:J51)</f>
+        <v>390839497.42565501</v>
       </c>
       <c r="L51" s="187">
-        <f t="shared" ref="L51:L65" si="4">IFERROR(K51/G51,0)</f>
-        <v>0.72872547746636118</v>
+        <f t="shared" ref="L51:L65" si="2">IFERROR(K51/G51,0)</f>
+        <v>0.75984482362272476</v>
       </c>
       <c r="M51" s="184">
-        <f t="shared" ref="M51:M64" si="5">G51*$H$40-K51</f>
-        <v>113816427.36976683</v>
+        <f t="shared" ref="M51:M64" si="3">G51*$H$40-K51</f>
+        <v>97809646.46681881</v>
       </c>
       <c r="N51" s="184">
-        <f t="shared" ref="N51:N65" ca="1" si="6">IFERROR(M51/$C$3,0)</f>
-        <v>14227053.421220854</v>
+        <f t="shared" ref="N51:N65" ca="1" si="4">IFERROR(M51/$C$3,0)</f>
+        <v>13972806.638116973</v>
       </c>
       <c r="O51" s="180">
-        <f t="shared" ref="O51:O64" si="7">G51*$J$40-K51</f>
-        <v>139534803.36410761</v>
+        <f t="shared" ref="O51:O64" si="5">G51*$J$40-K51</f>
+        <v>123528022.46115959</v>
       </c>
       <c r="P51" s="180">
-        <f t="shared" ref="P51:P65" ca="1" si="8">IFERROR(O51/$C$3,0)</f>
-        <v>17441850.420513451</v>
+        <f t="shared" ref="P51:P65" ca="1" si="6">IFERROR(O51/$C$3,0)</f>
+        <v>17646860.351594228</v>
       </c>
       <c r="Q51" s="185">
-        <f t="shared" ref="Q51:Q64" si="9">G51*$L$40-K51</f>
-        <v>139534803.36410761</v>
+        <f t="shared" ref="Q51:Q64" si="7">G51*$L$40-K51</f>
+        <v>123528022.46115959</v>
       </c>
       <c r="R51" s="185">
-        <f t="shared" ref="R51:R65" ca="1" si="10">IFERROR(Q51/$C$3,0)</f>
-        <v>17441850.420513451</v>
+        <f t="shared" ref="R51:R65" ca="1" si="8">IFERROR(Q51/$C$3,0)</f>
+        <v>17646860.351594228</v>
       </c>
       <c r="T51" t="s">
         <v>124</v>
@@ -7796,48 +7796,48 @@
         <v>785523881.42014158</v>
       </c>
       <c r="H52" s="114">
-        <f t="shared" ref="H52:H64" si="11">SUMIF($B$10:$B$26,$T52,C$10:C$26)+SUMIF($B$10:$B$26,$U52,C$10:C$26)</f>
-        <v>165303880.21731499</v>
+        <f>SUMIF($B$10:$B$26,$T52,C$10:C$26)+SUMIF($B$10:$B$26,$U52,C$10:C$26)</f>
+        <v>173621211.06792399</v>
       </c>
       <c r="I52" s="114">
+        <f>SUMIF($B$10:$B$26,$T52,D$10:D$26)+SUMIF($B$10:$B$26,$U52,D$10:D$26)</f>
+        <v>83567264.991497993</v>
+      </c>
+      <c r="J52" s="114">
+        <f>SUMIF($B$10:$B$26,$T52,E$10:E$26)+SUMIF($B$10:$B$26,$U52,E$10:E$26)</f>
+        <v>303440455.35922694</v>
+      </c>
+      <c r="K52" s="114">
         <f t="shared" si="1"/>
-        <v>82209647.871498004</v>
-      </c>
-      <c r="J52" s="114">
+        <v>560628931.41864896</v>
+      </c>
+      <c r="L52" s="187">
         <f t="shared" si="2"/>
-        <v>290624013.76925802</v>
-      </c>
-      <c r="K52" s="114">
+        <v>0.71370068393731445</v>
+      </c>
+      <c r="M52" s="184">
         <f t="shared" si="3"/>
-        <v>538137541.85807109</v>
-      </c>
-      <c r="L52" s="187">
-        <f t="shared" si="4"/>
-        <v>0.68506834048785004</v>
-      </c>
-      <c r="M52" s="184">
+        <v>185618755.93048549</v>
+      </c>
+      <c r="N52" s="184">
+        <f t="shared" ca="1" si="4"/>
+        <v>26516965.132926498</v>
+      </c>
+      <c r="O52" s="180">
         <f t="shared" si="5"/>
-        <v>208110145.49106336</v>
-      </c>
-      <c r="N52" s="184">
+        <v>224894950.00149262</v>
+      </c>
+      <c r="P52" s="180">
         <f t="shared" ca="1" si="6"/>
-        <v>26013768.18638292</v>
-      </c>
-      <c r="O52" s="180">
+        <v>32127850.000213232</v>
+      </c>
+      <c r="Q52" s="185">
         <f t="shared" si="7"/>
-        <v>247386339.56207049</v>
-      </c>
-      <c r="P52" s="180">
+        <v>224894950.00149262</v>
+      </c>
+      <c r="R52" s="185">
         <f t="shared" ca="1" si="8"/>
-        <v>30923292.445258811</v>
-      </c>
-      <c r="Q52" s="185">
-        <f t="shared" si="9"/>
-        <v>247386339.56207049</v>
-      </c>
-      <c r="R52" s="185">
-        <f t="shared" ca="1" si="10"/>
-        <v>30923292.445258811</v>
+        <v>32127850.000213232</v>
       </c>
       <c r="T52" t="s">
         <v>70</v>
@@ -7870,48 +7870,48 @@
         <v>262953105.06301075</v>
       </c>
       <c r="H53" s="114">
-        <f t="shared" si="11"/>
+        <f>SUMIF($B$10:$B$26,$T53,C$10:C$26)+SUMIF($B$10:$B$26,$U53,C$10:C$26)</f>
         <v>57858708.960000001</v>
       </c>
       <c r="I53" s="114">
+        <f>SUMIF($B$10:$B$26,$T53,D$10:D$26)+SUMIF($B$10:$B$26,$U53,D$10:D$26)</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="114">
+        <f>SUMIF($B$10:$B$26,$T53,E$10:E$26)+SUMIF($B$10:$B$26,$U53,E$10:E$26)</f>
+        <v>0</v>
+      </c>
+      <c r="K53" s="114">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J53" s="114">
+        <v>57858708.960000001</v>
+      </c>
+      <c r="L53" s="187">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K53" s="114">
+        <v>0.22003432492700731</v>
+      </c>
+      <c r="M53" s="184">
         <f t="shared" si="3"/>
-        <v>57858708.960000001</v>
-      </c>
-      <c r="L53" s="187">
-        <f t="shared" si="4"/>
-        <v>0.22003432492700731</v>
-      </c>
-      <c r="M53" s="184">
+        <v>191946740.84986019</v>
+      </c>
+      <c r="N53" s="184">
+        <f t="shared" ca="1" si="4"/>
+        <v>27420962.978551455</v>
+      </c>
+      <c r="O53" s="180">
         <f t="shared" si="5"/>
-        <v>191946740.84986019</v>
-      </c>
-      <c r="N53" s="184">
+        <v>205094396.10301074</v>
+      </c>
+      <c r="P53" s="180">
         <f t="shared" ca="1" si="6"/>
-        <v>23993342.606232524</v>
-      </c>
-      <c r="O53" s="180">
+        <v>29299199.44328725</v>
+      </c>
+      <c r="Q53" s="185">
         <f t="shared" si="7"/>
         <v>205094396.10301074</v>
       </c>
-      <c r="P53" s="180">
+      <c r="R53" s="185">
         <f t="shared" ca="1" si="8"/>
-        <v>25636799.512876343</v>
-      </c>
-      <c r="Q53" s="185">
-        <f t="shared" si="9"/>
-        <v>205094396.10301074</v>
-      </c>
-      <c r="R53" s="185">
-        <f t="shared" ca="1" si="10"/>
-        <v>25636799.512876343</v>
+        <v>29299199.44328725</v>
       </c>
       <c r="T53" t="s">
         <v>169</v>
@@ -7944,48 +7944,48 @@
         <v>726671808.78586555</v>
       </c>
       <c r="H54" s="114">
-        <f t="shared" si="11"/>
-        <v>396973429.52460003</v>
+        <f>SUMIF($B$10:$B$26,$T54,C$10:C$26)+SUMIF($B$10:$B$26,$U54,C$10:C$26)</f>
+        <v>423669713.43459803</v>
       </c>
       <c r="I54" s="114">
+        <f>SUMIF($B$10:$B$26,$T54,D$10:D$26)+SUMIF($B$10:$B$26,$U54,D$10:D$26)</f>
+        <v>38215060.301464997</v>
+      </c>
+      <c r="J54" s="114">
+        <f>SUMIF($B$10:$B$26,$T54,E$10:E$26)+SUMIF($B$10:$B$26,$U54,E$10:E$26)</f>
+        <v>138709153.37987801</v>
+      </c>
+      <c r="K54" s="114">
         <f t="shared" si="1"/>
-        <v>37481186.411467001</v>
-      </c>
-      <c r="J54" s="114">
+        <v>600593927.11594105</v>
+      </c>
+      <c r="L54" s="187">
         <f t="shared" si="2"/>
-        <v>117286536.1999</v>
-      </c>
-      <c r="K54" s="114">
+        <v>0.82649955572023992</v>
+      </c>
+      <c r="M54" s="184">
         <f t="shared" si="3"/>
-        <v>551741152.13596702</v>
-      </c>
-      <c r="L54" s="187">
-        <f t="shared" si="4"/>
-        <v>0.75927144202528596</v>
-      </c>
-      <c r="M54" s="184">
+        <v>89744291.230631232</v>
+      </c>
+      <c r="N54" s="184">
+        <f t="shared" ca="1" si="4"/>
+        <v>12820613.032947319</v>
+      </c>
+      <c r="O54" s="180">
         <f t="shared" si="5"/>
-        <v>138597066.21060526</v>
-      </c>
-      <c r="N54" s="184">
+        <v>126077881.6699245</v>
+      </c>
+      <c r="P54" s="180">
         <f t="shared" ca="1" si="6"/>
-        <v>17324633.276325658</v>
-      </c>
-      <c r="O54" s="180">
+        <v>18011125.952846356</v>
+      </c>
+      <c r="Q54" s="185">
         <f t="shared" si="7"/>
-        <v>174930656.64989853</v>
-      </c>
-      <c r="P54" s="180">
+        <v>126077881.6699245</v>
+      </c>
+      <c r="R54" s="185">
         <f t="shared" ca="1" si="8"/>
-        <v>21866332.081237316</v>
-      </c>
-      <c r="Q54" s="185">
-        <f t="shared" si="9"/>
-        <v>174930656.64989853</v>
-      </c>
-      <c r="R54" s="185">
-        <f t="shared" ca="1" si="10"/>
-        <v>21866332.081237316</v>
+        <v>18011125.952846356</v>
       </c>
       <c r="T54" t="s">
         <v>115</v>
@@ -8018,48 +8018,48 @@
         <v>537200999.57068563</v>
       </c>
       <c r="H55" s="114">
-        <f t="shared" si="11"/>
+        <f>SUMIF($B$10:$B$26,$T55,C$10:C$26)+SUMIF($B$10:$B$26,$U55,C$10:C$26)</f>
         <v>4173423.4199979999</v>
       </c>
       <c r="I55" s="114">
+        <f>SUMIF($B$10:$B$26,$T55,D$10:D$26)+SUMIF($B$10:$B$26,$U55,D$10:D$26)</f>
+        <v>30250983.5</v>
+      </c>
+      <c r="J55" s="114">
+        <f>SUMIF($B$10:$B$26,$T55,E$10:E$26)+SUMIF($B$10:$B$26,$U55,E$10:E$26)</f>
+        <v>199157658.6392</v>
+      </c>
+      <c r="K55" s="114">
         <f t="shared" si="1"/>
-        <v>16503315.6</v>
-      </c>
-      <c r="J55" s="114">
+        <v>233582065.55919799</v>
+      </c>
+      <c r="L55" s="187">
         <f t="shared" si="2"/>
-        <v>199157658.6392</v>
-      </c>
-      <c r="K55" s="114">
+        <v>0.43481316257019165</v>
+      </c>
+      <c r="M55" s="184">
         <f t="shared" si="3"/>
-        <v>219834397.65919799</v>
-      </c>
-      <c r="L55" s="187">
-        <f t="shared" si="4"/>
-        <v>0.40922187009123739</v>
-      </c>
-      <c r="M55" s="184">
+        <v>276758884.03295338</v>
+      </c>
+      <c r="N55" s="184">
+        <f t="shared" ca="1" si="4"/>
+        <v>39536983.433279052</v>
+      </c>
+      <c r="O55" s="180">
         <f t="shared" si="5"/>
-        <v>290506551.93295336</v>
-      </c>
-      <c r="N55" s="184">
+        <v>303618934.0114876</v>
+      </c>
+      <c r="P55" s="180">
         <f t="shared" ca="1" si="6"/>
-        <v>36313318.99161917</v>
-      </c>
-      <c r="O55" s="180">
+        <v>43374133.430212513</v>
+      </c>
+      <c r="Q55" s="185">
         <f t="shared" si="7"/>
-        <v>317366601.91148764</v>
-      </c>
-      <c r="P55" s="180">
+        <v>303618934.0114876</v>
+      </c>
+      <c r="R55" s="185">
         <f t="shared" ca="1" si="8"/>
-        <v>39670825.238935955</v>
-      </c>
-      <c r="Q55" s="185">
-        <f t="shared" si="9"/>
-        <v>317366601.91148764</v>
-      </c>
-      <c r="R55" s="185">
-        <f t="shared" ca="1" si="10"/>
-        <v>39670825.238935955</v>
+        <v>43374133.430212513</v>
       </c>
       <c r="T55" t="s">
         <v>182</v>
@@ -8092,48 +8092,48 @@
         <v>574945988.50021839</v>
       </c>
       <c r="H56" s="114">
-        <f t="shared" si="11"/>
-        <v>148754687.584483</v>
+        <f>SUMIF($B$10:$B$26,$T56,C$10:C$26)+SUMIF($B$10:$B$26,$U56,C$10:C$26)</f>
+        <v>157144378.35867101</v>
       </c>
       <c r="I56" s="114">
+        <f>SUMIF($B$10:$B$26,$T56,D$10:D$26)+SUMIF($B$10:$B$26,$U56,D$10:D$26)</f>
+        <v>44687069.909941003</v>
+      </c>
+      <c r="J56" s="114">
+        <f>SUMIF($B$10:$B$26,$T56,E$10:E$26)+SUMIF($B$10:$B$26,$U56,E$10:E$26)</f>
+        <v>126616820.968173</v>
+      </c>
+      <c r="K56" s="114">
         <f t="shared" si="1"/>
-        <v>42615344.709941</v>
-      </c>
-      <c r="J56" s="114">
+        <v>328448269.23678505</v>
+      </c>
+      <c r="L56" s="187">
         <f t="shared" si="2"/>
-        <v>126094298.448173</v>
-      </c>
-      <c r="K56" s="114">
+        <v>0.57126804222699656</v>
+      </c>
+      <c r="M56" s="184">
         <f t="shared" si="3"/>
-        <v>317464330.74259698</v>
-      </c>
-      <c r="L56" s="187">
-        <f t="shared" si="4"/>
-        <v>0.55216374597329054</v>
-      </c>
-      <c r="M56" s="184">
+        <v>217750419.83842242</v>
+      </c>
+      <c r="N56" s="184">
+        <f t="shared" ca="1" si="4"/>
+        <v>31107202.834060345</v>
+      </c>
+      <c r="O56" s="180">
         <f t="shared" si="5"/>
-        <v>228734358.33261049</v>
-      </c>
-      <c r="N56" s="184">
+        <v>246497719.26343334</v>
+      </c>
+      <c r="P56" s="180">
         <f t="shared" ca="1" si="6"/>
-        <v>28591794.791576311</v>
-      </c>
-      <c r="O56" s="180">
+        <v>35213959.894776188</v>
+      </c>
+      <c r="Q56" s="185">
         <f t="shared" si="7"/>
-        <v>257481657.75762141</v>
-      </c>
-      <c r="P56" s="180">
+        <v>246497719.26343334</v>
+      </c>
+      <c r="R56" s="185">
         <f t="shared" ca="1" si="8"/>
-        <v>32185207.219702676</v>
-      </c>
-      <c r="Q56" s="185">
-        <f t="shared" si="9"/>
-        <v>257481657.75762141</v>
-      </c>
-      <c r="R56" s="185">
-        <f t="shared" ca="1" si="10"/>
-        <v>32185207.219702676</v>
+        <v>35213959.894776188</v>
       </c>
       <c r="T56" t="s">
         <v>225</v>
@@ -8166,48 +8166,48 @@
         <v>1109184065.5247467</v>
       </c>
       <c r="H57" s="114">
-        <f t="shared" si="11"/>
-        <v>371501562.66268098</v>
+        <f>SUMIF($B$10:$B$26,$T57,C$10:C$26)+SUMIF($B$10:$B$26,$U57,C$10:C$26)</f>
+        <v>403308935.481655</v>
       </c>
       <c r="I57" s="114">
+        <f>SUMIF($B$10:$B$26,$T57,D$10:D$26)+SUMIF($B$10:$B$26,$U57,D$10:D$26)</f>
+        <v>38062931.419927001</v>
+      </c>
+      <c r="J57" s="114">
+        <f>SUMIF($B$10:$B$26,$T57,E$10:E$26)+SUMIF($B$10:$B$26,$U57,E$10:E$26)</f>
+        <v>263379730.93952</v>
+      </c>
+      <c r="K57" s="114">
         <f t="shared" si="1"/>
-        <v>36300643.119926997</v>
-      </c>
-      <c r="J57" s="114">
+        <v>704751597.841102</v>
+      </c>
+      <c r="L57" s="187">
         <f t="shared" si="2"/>
-        <v>255160812.04951999</v>
-      </c>
-      <c r="K57" s="114">
+        <v>0.63537840088578024</v>
+      </c>
+      <c r="M57" s="184">
         <f t="shared" si="3"/>
-        <v>662963017.83212793</v>
-      </c>
-      <c r="L57" s="187">
-        <f t="shared" si="4"/>
-        <v>0.59770333746949844</v>
-      </c>
-      <c r="M57" s="184">
+        <v>348973264.40740728</v>
+      </c>
+      <c r="N57" s="184">
+        <f t="shared" ca="1" si="4"/>
+        <v>49853323.48677247</v>
+      </c>
+      <c r="O57" s="180">
         <f t="shared" si="5"/>
-        <v>390761844.41638136</v>
-      </c>
-      <c r="N57" s="184">
+        <v>404432467.68364465</v>
+      </c>
+      <c r="P57" s="180">
         <f t="shared" ca="1" si="6"/>
-        <v>48845230.55204767</v>
-      </c>
-      <c r="O57" s="180">
+        <v>57776066.811949238</v>
+      </c>
+      <c r="Q57" s="185">
         <f t="shared" si="7"/>
-        <v>446221047.69261873</v>
-      </c>
-      <c r="P57" s="180">
+        <v>404432467.68364465</v>
+      </c>
+      <c r="R57" s="185">
         <f t="shared" ca="1" si="8"/>
-        <v>55777630.961577341</v>
-      </c>
-      <c r="Q57" s="185">
-        <f t="shared" si="9"/>
-        <v>446221047.69261873</v>
-      </c>
-      <c r="R57" s="185">
-        <f t="shared" ca="1" si="10"/>
-        <v>55777630.961577341</v>
+        <v>57776066.811949238</v>
       </c>
       <c r="T57" t="s">
         <v>120</v>
@@ -8240,48 +8240,48 @@
         <v>614580870.17702889</v>
       </c>
       <c r="H58" s="114">
-        <f t="shared" si="11"/>
-        <v>201386818.38223299</v>
+        <f>SUMIF($B$10:$B$26,$T58,C$10:C$26)+SUMIF($B$10:$B$26,$U58,C$10:C$26)</f>
+        <v>218343790.722233</v>
       </c>
       <c r="I58" s="114">
+        <f>SUMIF($B$10:$B$26,$T58,D$10:D$26)+SUMIF($B$10:$B$26,$U58,D$10:D$26)</f>
+        <v>55894289.419963002</v>
+      </c>
+      <c r="J58" s="114">
+        <f>SUMIF($B$10:$B$26,$T58,E$10:E$26)+SUMIF($B$10:$B$26,$U58,E$10:E$26)</f>
+        <v>162558650.86619499</v>
+      </c>
+      <c r="K58" s="114">
         <f t="shared" si="1"/>
-        <v>54608591.209964</v>
-      </c>
-      <c r="J58" s="114">
+        <v>436796731.00839102</v>
+      </c>
+      <c r="L58" s="187">
         <f t="shared" si="2"/>
-        <v>150961804.00620899</v>
-      </c>
-      <c r="K58" s="114">
+        <v>0.7107229531608632</v>
+      </c>
+      <c r="M58" s="184">
         <f t="shared" si="3"/>
-        <v>406957213.59840596</v>
-      </c>
-      <c r="L58" s="187">
-        <f t="shared" si="4"/>
-        <v>0.66217032346155302</v>
-      </c>
-      <c r="M58" s="184">
+        <v>147055095.65978634</v>
+      </c>
+      <c r="N58" s="184">
+        <f t="shared" ca="1" si="4"/>
+        <v>21007870.808540907</v>
+      </c>
+      <c r="O58" s="180">
         <f t="shared" si="5"/>
-        <v>176894613.06977141</v>
-      </c>
-      <c r="N58" s="184">
+        <v>177784139.16863787</v>
+      </c>
+      <c r="P58" s="180">
         <f t="shared" ca="1" si="6"/>
-        <v>22111826.633721426</v>
-      </c>
-      <c r="O58" s="180">
+        <v>25397734.166948266</v>
+      </c>
+      <c r="Q58" s="185">
         <f t="shared" si="7"/>
-        <v>207623656.57862294</v>
-      </c>
-      <c r="P58" s="180">
+        <v>177784139.16863787</v>
+      </c>
+      <c r="R58" s="185">
         <f t="shared" ca="1" si="8"/>
-        <v>25952957.072327867</v>
-      </c>
-      <c r="Q58" s="185">
-        <f t="shared" si="9"/>
-        <v>207623656.57862294</v>
-      </c>
-      <c r="R58" s="185">
-        <f t="shared" ca="1" si="10"/>
-        <v>25952957.072327867</v>
+        <v>25397734.166948266</v>
       </c>
       <c r="T58" t="s">
         <v>125</v>
@@ -8314,48 +8314,48 @@
         <v>443846715.57642001</v>
       </c>
       <c r="H59" s="114">
-        <f t="shared" si="11"/>
+        <f>SUMIF($B$10:$B$26,$T59,C$10:C$26)+SUMIF($B$10:$B$26,$U59,C$10:C$26)</f>
         <v>188527227.16</v>
       </c>
       <c r="I59" s="114">
+        <f>SUMIF($B$10:$B$26,$T59,D$10:D$26)+SUMIF($B$10:$B$26,$U59,D$10:D$26)</f>
+        <v>0</v>
+      </c>
+      <c r="J59" s="114">
+        <f>SUMIF($B$10:$B$26,$T59,E$10:E$26)+SUMIF($B$10:$B$26,$U59,E$10:E$26)</f>
+        <v>0</v>
+      </c>
+      <c r="K59" s="114">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J59" s="114">
+        <v>188527227.16</v>
+      </c>
+      <c r="L59" s="187">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K59" s="114">
+        <v>0.42475751322201688</v>
+      </c>
+      <c r="M59" s="184">
         <f t="shared" si="3"/>
-        <v>188527227.16</v>
-      </c>
-      <c r="L59" s="187">
-        <f t="shared" si="4"/>
-        <v>0.42475751322201688</v>
-      </c>
-      <c r="M59" s="184">
+        <v>233127152.63759902</v>
+      </c>
+      <c r="N59" s="184">
+        <f t="shared" ca="1" si="4"/>
+        <v>33303878.94822843</v>
+      </c>
+      <c r="O59" s="180">
         <f t="shared" si="5"/>
-        <v>233127152.63759902</v>
-      </c>
-      <c r="N59" s="184">
+        <v>255319488.41642001</v>
+      </c>
+      <c r="P59" s="180">
         <f t="shared" ca="1" si="6"/>
-        <v>29140894.079699878</v>
-      </c>
-      <c r="O59" s="180">
+        <v>36474212.630917147</v>
+      </c>
+      <c r="Q59" s="185">
         <f t="shared" si="7"/>
         <v>255319488.41642001</v>
       </c>
-      <c r="P59" s="180">
+      <c r="R59" s="185">
         <f t="shared" ca="1" si="8"/>
-        <v>31914936.052052502</v>
-      </c>
-      <c r="Q59" s="185">
-        <f t="shared" si="9"/>
-        <v>255319488.41642001</v>
-      </c>
-      <c r="R59" s="185">
-        <f t="shared" ca="1" si="10"/>
-        <v>31914936.052052502</v>
+        <v>36474212.630917147</v>
       </c>
       <c r="T59" t="s">
         <v>170</v>
@@ -8388,48 +8388,48 @@
         <v>579186208.19638371</v>
       </c>
       <c r="H60" s="114">
-        <f t="shared" si="11"/>
-        <v>233723045.560087</v>
+        <f>SUMIF($B$10:$B$26,$T60,C$10:C$26)+SUMIF($B$10:$B$26,$U60,C$10:C$26)</f>
+        <v>259986756.55092999</v>
       </c>
       <c r="I60" s="114">
+        <f>SUMIF($B$10:$B$26,$T60,D$10:D$26)+SUMIF($B$10:$B$26,$U60,D$10:D$26)</f>
+        <v>75962454.816541001</v>
+      </c>
+      <c r="J60" s="114">
+        <f>SUMIF($B$10:$B$26,$T60,E$10:E$26)+SUMIF($B$10:$B$26,$U60,E$10:E$26)</f>
+        <v>85307067.912571996</v>
+      </c>
+      <c r="K60" s="114">
         <f t="shared" si="1"/>
-        <v>75195779.136546999</v>
-      </c>
-      <c r="J60" s="114">
+        <v>421256279.28004301</v>
+      </c>
+      <c r="L60" s="187">
         <f t="shared" si="2"/>
-        <v>77460806.632578999</v>
-      </c>
-      <c r="K60" s="114">
+        <v>0.72732443093190569</v>
+      </c>
+      <c r="M60" s="184">
         <f t="shared" si="3"/>
-        <v>386379631.32921302</v>
-      </c>
-      <c r="L60" s="187">
-        <f t="shared" si="4"/>
-        <v>0.66710778996692532</v>
-      </c>
-      <c r="M60" s="184">
+        <v>128970618.50652146</v>
+      </c>
+      <c r="N60" s="184">
+        <f t="shared" ca="1" si="4"/>
+        <v>18424374.07236021</v>
+      </c>
+      <c r="O60" s="180">
         <f t="shared" si="5"/>
-        <v>163847266.45735145</v>
-      </c>
-      <c r="N60" s="184">
+        <v>157929928.91634071</v>
+      </c>
+      <c r="P60" s="180">
         <f t="shared" ca="1" si="6"/>
-        <v>20480908.307168931</v>
-      </c>
-      <c r="O60" s="180">
+        <v>22561418.416620102</v>
+      </c>
+      <c r="Q60" s="185">
         <f t="shared" si="7"/>
-        <v>192806576.86717069</v>
-      </c>
-      <c r="P60" s="180">
+        <v>157929928.91634071</v>
+      </c>
+      <c r="R60" s="185">
         <f t="shared" ca="1" si="8"/>
-        <v>24100822.108396336</v>
-      </c>
-      <c r="Q60" s="185">
-        <f t="shared" si="9"/>
-        <v>192806576.86717069</v>
-      </c>
-      <c r="R60" s="185">
-        <f t="shared" ca="1" si="10"/>
-        <v>24100822.108396336</v>
+        <v>22561418.416620102</v>
       </c>
       <c r="T60" t="s">
         <v>220</v>
@@ -8462,48 +8462,48 @@
         <v>716592801.55318153</v>
       </c>
       <c r="H61" s="114">
-        <f t="shared" si="11"/>
-        <v>357807886.12938398</v>
+        <f>SUMIF($B$10:$B$26,$T61,C$10:C$26)+SUMIF($B$10:$B$26,$U61,C$10:C$26)</f>
+        <v>386015669.137429</v>
       </c>
       <c r="I61" s="114">
+        <f>SUMIF($B$10:$B$26,$T61,D$10:D$26)+SUMIF($B$10:$B$26,$U61,D$10:D$26)</f>
+        <v>55017470.924923003</v>
+      </c>
+      <c r="J61" s="114">
+        <f>SUMIF($B$10:$B$26,$T61,E$10:E$26)+SUMIF($B$10:$B$26,$U61,E$10:E$26)</f>
+        <v>174500614.40990701</v>
+      </c>
+      <c r="K61" s="114">
         <f t="shared" si="1"/>
-        <v>53379470.924923003</v>
-      </c>
-      <c r="J61" s="114">
+        <v>615533754.47225904</v>
+      </c>
+      <c r="L61" s="187">
         <f t="shared" si="2"/>
-        <v>159507956.34990701</v>
-      </c>
-      <c r="K61" s="114">
+        <v>0.8589728408352949</v>
+      </c>
+      <c r="M61" s="184">
         <f t="shared" si="3"/>
-        <v>570695313.40421402</v>
-      </c>
-      <c r="L61" s="187">
-        <f t="shared" si="4"/>
-        <v>0.79640112511213967</v>
-      </c>
-      <c r="M61" s="184">
+        <v>65229407.003263354</v>
+      </c>
+      <c r="N61" s="184">
+        <f t="shared" ca="1" si="4"/>
+        <v>9318486.7147519086</v>
+      </c>
+      <c r="O61" s="180">
         <f t="shared" si="5"/>
-        <v>110067848.07130837</v>
-      </c>
-      <c r="N61" s="184">
+        <v>101059047.08092248</v>
+      </c>
+      <c r="P61" s="180">
         <f t="shared" ca="1" si="6"/>
-        <v>13758481.008913547</v>
-      </c>
-      <c r="O61" s="180">
+        <v>14437006.725846069</v>
+      </c>
+      <c r="Q61" s="185">
         <f t="shared" si="7"/>
-        <v>145897488.1489675</v>
-      </c>
-      <c r="P61" s="180">
+        <v>101059047.08092248</v>
+      </c>
+      <c r="R61" s="185">
         <f t="shared" ca="1" si="8"/>
-        <v>18237186.018620938</v>
-      </c>
-      <c r="Q61" s="185">
-        <f t="shared" si="9"/>
-        <v>145897488.1489675</v>
-      </c>
-      <c r="R61" s="185">
-        <f t="shared" ca="1" si="10"/>
-        <v>18237186.018620938</v>
+        <v>14437006.725846069</v>
       </c>
       <c r="T61" t="s">
         <v>126</v>
@@ -8536,48 +8536,48 @@
         <v>477023257.56080151</v>
       </c>
       <c r="H62" s="114">
-        <f t="shared" si="11"/>
-        <v>117222800.908739</v>
+        <f>SUMIF($B$10:$B$26,$T62,C$10:C$26)+SUMIF($B$10:$B$26,$U62,C$10:C$26)</f>
+        <v>122534293.762722</v>
       </c>
       <c r="I62" s="114">
+        <f>SUMIF($B$10:$B$26,$T62,D$10:D$26)+SUMIF($B$10:$B$26,$U62,D$10:D$26)</f>
+        <v>33718196.818899997</v>
+      </c>
+      <c r="J62" s="114">
+        <f>SUMIF($B$10:$B$26,$T62,E$10:E$26)+SUMIF($B$10:$B$26,$U62,E$10:E$26)</f>
+        <v>175612225.567045</v>
+      </c>
+      <c r="K62" s="114">
         <f t="shared" si="1"/>
-        <v>31388455.192899998</v>
-      </c>
-      <c r="J62" s="114">
+        <v>331864716.14866698</v>
+      </c>
+      <c r="L62" s="187">
         <f t="shared" si="2"/>
-        <v>173196225.567045</v>
-      </c>
-      <c r="K62" s="114">
+        <v>0.69569923664857669</v>
+      </c>
+      <c r="M62" s="184">
         <f t="shared" si="3"/>
-        <v>321807481.66868401</v>
-      </c>
-      <c r="L62" s="187">
-        <f t="shared" si="4"/>
-        <v>0.67461591561427448</v>
-      </c>
-      <c r="M62" s="184">
+        <v>121307378.53409445</v>
+      </c>
+      <c r="N62" s="184">
+        <f t="shared" ca="1" si="4"/>
+        <v>17329625.504870635</v>
+      </c>
+      <c r="O62" s="180">
         <f t="shared" si="5"/>
-        <v>131364613.01407743</v>
-      </c>
-      <c r="N62" s="184">
+        <v>145158541.41213453</v>
+      </c>
+      <c r="P62" s="180">
         <f t="shared" ca="1" si="6"/>
-        <v>16420576.626759678</v>
-      </c>
-      <c r="O62" s="180">
+        <v>20736934.487447791</v>
+      </c>
+      <c r="Q62" s="185">
         <f t="shared" si="7"/>
-        <v>155215775.8921175</v>
-      </c>
-      <c r="P62" s="180">
+        <v>145158541.41213453</v>
+      </c>
+      <c r="R62" s="185">
         <f t="shared" ca="1" si="8"/>
-        <v>19401971.986514688</v>
-      </c>
-      <c r="Q62" s="185">
-        <f t="shared" si="9"/>
-        <v>155215775.8921175</v>
-      </c>
-      <c r="R62" s="185">
-        <f t="shared" ca="1" si="10"/>
-        <v>19401971.986514688</v>
+        <v>20736934.487447791</v>
       </c>
       <c r="T62" t="s">
         <v>112</v>
@@ -8610,48 +8610,48 @@
         <v>978973997.29380655</v>
       </c>
       <c r="H63" s="114">
-        <f t="shared" si="11"/>
-        <v>398672594.47329497</v>
+        <f>SUMIF($B$10:$B$26,$T63,C$10:C$26)+SUMIF($B$10:$B$26,$U63,C$10:C$26)</f>
+        <v>399272594.47329497</v>
       </c>
       <c r="I63" s="114">
+        <f>SUMIF($B$10:$B$26,$T63,D$10:D$26)+SUMIF($B$10:$B$26,$U63,D$10:D$26)</f>
+        <v>254167394.92625701</v>
+      </c>
+      <c r="J63" s="114">
+        <f>SUMIF($B$10:$B$26,$T63,E$10:E$26)+SUMIF($B$10:$B$26,$U63,E$10:E$26)</f>
+        <v>229102206.125873</v>
+      </c>
+      <c r="K63" s="114">
         <f t="shared" si="1"/>
-        <v>225332673.160541</v>
-      </c>
-      <c r="J63" s="114">
+        <v>882542195.52542496</v>
+      </c>
+      <c r="L63" s="187">
         <f t="shared" si="2"/>
-        <v>227840944.82587299</v>
-      </c>
-      <c r="K63" s="114">
+        <v>0.90149707547396607</v>
+      </c>
+      <c r="M63" s="184">
         <f t="shared" si="3"/>
-        <v>851846212.45970905</v>
-      </c>
-      <c r="L63" s="187">
-        <f t="shared" si="4"/>
-        <v>0.87014181665139334</v>
-      </c>
-      <c r="M63" s="184">
+        <v>47483101.903691173</v>
+      </c>
+      <c r="N63" s="184">
+        <f t="shared" ca="1" si="4"/>
+        <v>6783300.2719558822</v>
+      </c>
+      <c r="O63" s="180">
         <f t="shared" si="5"/>
-        <v>78179084.969407082</v>
-      </c>
-      <c r="N63" s="184">
+        <v>96431801.768381596</v>
+      </c>
+      <c r="P63" s="180">
         <f t="shared" ca="1" si="6"/>
-        <v>9772385.6211758852</v>
-      </c>
-      <c r="O63" s="180">
+        <v>13775971.681197371</v>
+      </c>
+      <c r="Q63" s="185">
         <f t="shared" si="7"/>
-        <v>127127784.8340975</v>
-      </c>
-      <c r="P63" s="180">
+        <v>96431801.768381596</v>
+      </c>
+      <c r="R63" s="185">
         <f t="shared" ca="1" si="8"/>
-        <v>15890973.104262188</v>
-      </c>
-      <c r="Q63" s="185">
-        <f t="shared" si="9"/>
-        <v>127127784.8340975</v>
-      </c>
-      <c r="R63" s="185">
-        <f t="shared" ca="1" si="10"/>
-        <v>15890973.104262188</v>
+        <v>13775971.681197371</v>
       </c>
       <c r="T63" t="s">
         <v>127</v>
@@ -8684,48 +8684,48 @@
         <v>536914321.43439078</v>
       </c>
       <c r="H64" s="114">
-        <f t="shared" si="11"/>
-        <v>104250263.40502599</v>
+        <f>SUMIF($B$10:$B$26,$T64,C$10:C$26)+SUMIF($B$10:$B$26,$U64,C$10:C$26)</f>
+        <v>106404263.40502599</v>
       </c>
       <c r="I64" s="114">
+        <f>SUMIF($B$10:$B$26,$T64,D$10:D$26)+SUMIF($B$10:$B$26,$U64,D$10:D$26)</f>
+        <v>146124139.012555</v>
+      </c>
+      <c r="J64" s="114">
+        <f>SUMIF($B$10:$B$26,$T64,E$10:E$26)+SUMIF($B$10:$B$26,$U64,E$10:E$26)</f>
+        <v>128456685.06884199</v>
+      </c>
+      <c r="K64" s="114">
         <f t="shared" si="1"/>
-        <v>142578446.09257498</v>
-      </c>
-      <c r="J64" s="114">
+        <v>380985087.48642302</v>
+      </c>
+      <c r="L64" s="187">
         <f t="shared" si="2"/>
-        <v>117674625.06884199</v>
-      </c>
-      <c r="K64" s="114">
+        <v>0.70958265085685213</v>
+      </c>
+      <c r="M64" s="184">
         <f t="shared" si="3"/>
-        <v>364503334.56644297</v>
-      </c>
-      <c r="L64" s="187">
-        <f t="shared" si="4"/>
-        <v>0.67888547579184677</v>
-      </c>
-      <c r="M64" s="184">
+        <v>129083517.87624818</v>
+      </c>
+      <c r="N64" s="184">
+        <f t="shared" ca="1" si="4"/>
+        <v>18440502.55374974</v>
+      </c>
+      <c r="O64" s="180">
         <f t="shared" si="5"/>
-        <v>145565270.79622823</v>
-      </c>
-      <c r="N64" s="184">
+        <v>155929233.94796777</v>
+      </c>
+      <c r="P64" s="180">
         <f t="shared" ca="1" si="6"/>
-        <v>18195658.849528529</v>
-      </c>
-      <c r="O64" s="180">
+        <v>22275604.849709682</v>
+      </c>
+      <c r="Q64" s="185">
         <f t="shared" si="7"/>
-        <v>172410986.86794782</v>
-      </c>
-      <c r="P64" s="180">
+        <v>155929233.94796777</v>
+      </c>
+      <c r="R64" s="185">
         <f t="shared" ca="1" si="8"/>
-        <v>21551373.358493477</v>
-      </c>
-      <c r="Q64" s="185">
-        <f t="shared" si="9"/>
-        <v>172410986.86794782</v>
-      </c>
-      <c r="R64" s="185">
-        <f t="shared" ca="1" si="10"/>
-        <v>21551373.358493477</v>
+        <v>22275604.849709682</v>
       </c>
       <c r="T64" t="s">
         <v>122</v>
@@ -8740,64 +8740,64 @@
       </c>
       <c r="C65" s="58"/>
       <c r="D65" s="134">
-        <f t="shared" ref="D65:K65" si="12">SUM(D51:D64)</f>
+        <f t="shared" ref="D65:K65" si="9">SUM(D51:D64)</f>
         <v>4511786033.6993961</v>
       </c>
       <c r="E65" s="134">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1401365310.515415</v>
       </c>
       <c r="F65" s="134">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>2944814196.3286853</v>
       </c>
       <c r="G65" s="134">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>8857965540.5434952</v>
       </c>
       <c r="H65" s="135">
-        <f t="shared" si="12"/>
-        <v>2958880432.7472873</v>
+        <f t="shared" si="9"/>
+        <v>3122129670.9968972</v>
       </c>
       <c r="I65" s="135">
-        <f t="shared" si="12"/>
-        <v>838688962.31374085</v>
+        <f t="shared" si="9"/>
+        <v>897387187.46542609</v>
       </c>
       <c r="J65" s="135">
-        <f t="shared" si="12"/>
-        <v>2015978884.8363087</v>
+        <f t="shared" si="9"/>
+        <v>2114692130.1762149</v>
       </c>
       <c r="K65" s="135">
-        <f t="shared" si="12"/>
-        <v>5813548279.897337</v>
+        <f t="shared" si="9"/>
+        <v>6134208988.6385384</v>
       </c>
       <c r="L65" s="189">
-        <f t="shared" si="4"/>
-        <v>0.65630739398209903</v>
+        <f t="shared" si="2"/>
+        <v>0.69250765997698427</v>
       </c>
       <c r="M65" s="181">
         <f>SUM(M51:M64)</f>
-        <v>2601518983.6189842</v>
+        <v>2280858274.8777828</v>
       </c>
       <c r="N65" s="181">
-        <f t="shared" ca="1" si="6"/>
-        <v>325189872.95237303</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>325836896.41111183</v>
       </c>
       <c r="O65" s="181">
         <f>SUM(O51:O64)</f>
-        <v>3044417260.6461592</v>
+        <v>2723756551.9049587</v>
       </c>
       <c r="P65" s="181">
-        <f t="shared" ca="1" si="8"/>
-        <v>380552157.5807699</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>389108078.84356552</v>
       </c>
       <c r="Q65" s="186">
         <f>SUM(Q51:Q64)</f>
-        <v>3044417260.6461592</v>
+        <v>2723756551.9049587</v>
       </c>
       <c r="R65" s="186">
-        <f t="shared" ca="1" si="10"/>
-        <v>380552157.5807699</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>389108078.84356552</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8806,21 +8806,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="283" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="260" t="s">
+      <c r="G67" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="270"/>
+      <c r="I67" s="270"/>
+      <c r="J67" s="270"/>
+      <c r="K67" s="270"/>
+      <c r="L67" s="271"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -8882,35 +8882,35 @@
       </c>
       <c r="E69" s="114">
         <f>IFERROR($C$31,0)</f>
-        <v>202988607.005263</v>
+        <v>203469688.08525699</v>
       </c>
       <c r="F69" s="187">
-        <f t="shared" ref="F69:F74" si="13">IFERROR(E69/D69,0)</f>
-        <v>0.79212746704900239</v>
+        <f t="shared" ref="F69:F74" si="10">IFERROR(E69/D69,0)</f>
+        <v>0.79400480165887521</v>
       </c>
       <c r="G69" s="184">
         <f>D69*$H$40-E69</f>
-        <v>40456021.134453386</v>
+        <v>39974940.054459393</v>
       </c>
       <c r="H69" s="184">
-        <f t="shared" ref="H69:H74" ca="1" si="14">IFERROR(G69/$C$3,0)</f>
-        <v>5057002.6418066733</v>
+        <f t="shared" ref="H69:H74" ca="1" si="11">IFERROR(G69/$C$3,0)</f>
+        <v>5710705.7220656276</v>
       </c>
       <c r="I69" s="204">
         <f>D69*$J$40-E69</f>
-        <v>53268896.299701631</v>
+        <v>52787815.219707638</v>
       </c>
       <c r="J69" s="204">
-        <f t="shared" ref="J69:J74" ca="1" si="15">IFERROR(I69/$C$3,0)</f>
-        <v>6658612.0374627039</v>
+        <f t="shared" ref="J69:J74" ca="1" si="12">IFERROR(I69/$C$3,0)</f>
+        <v>7541116.4599582339</v>
       </c>
       <c r="K69" s="185">
         <f>D69*$L$40-E69</f>
-        <v>53268896.299701631</v>
+        <v>52787815.219707638</v>
       </c>
       <c r="L69" s="185">
-        <f t="shared" ref="L69:L74" ca="1" si="16">IFERROR(K69/$C$3,0)</f>
-        <v>6658612.0374627039</v>
+        <f t="shared" ref="L69:L74" ca="1" si="13">IFERROR(K69/$C$3,0)</f>
+        <v>7541116.4599582339</v>
       </c>
     </row>
     <row r="70" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8926,35 +8926,35 @@
       </c>
       <c r="E70" s="114">
         <f>IFERROR($C$32,0)</f>
-        <v>408029398.87102902</v>
+        <v>415017182.90095901</v>
       </c>
       <c r="F70" s="187">
-        <f t="shared" si="13"/>
-        <v>1.0212008715251348</v>
+        <f t="shared" si="10"/>
+        <v>1.038689638660881</v>
       </c>
       <c r="G70" s="184">
         <f>D70*$H$40-E70</f>
-        <v>-28448907.18131268</v>
+        <v>-35436691.211242676</v>
       </c>
       <c r="H70" s="184">
-        <f t="shared" ca="1" si="14"/>
-        <v>-3556113.397664085</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>-5062384.4587489534</v>
       </c>
       <c r="I70" s="204">
         <f>D70*$J$40-E70</f>
-        <v>-8470986.5660644174</v>
+        <v>-15458770.595994413</v>
       </c>
       <c r="J70" s="204">
-        <f t="shared" ca="1" si="15"/>
-        <v>-1058873.3207580522</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>-2208395.7994277733</v>
       </c>
       <c r="K70" s="185">
         <f>D70*$L$40-E70</f>
-        <v>-8470986.5660644174</v>
+        <v>-15458770.595994413</v>
       </c>
       <c r="L70" s="185">
-        <f t="shared" ca="1" si="16"/>
-        <v>-1058873.3207580522</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>-2208395.7994277733</v>
       </c>
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.25">
@@ -8970,35 +8970,35 @@
       </c>
       <c r="E71" s="114">
         <f>M21</f>
-        <v>543057028.79973006</v>
+        <v>932747039.34663296</v>
       </c>
       <c r="F71" s="187">
-        <f t="shared" si="13"/>
-        <v>0.50069354045542247</v>
+        <f t="shared" si="10"/>
+        <v>0.85998411347698056</v>
       </c>
       <c r="G71" s="184">
         <f>D71*$H$40-E71</f>
-        <v>487322106.68998623</v>
+        <v>97632096.143083334</v>
       </c>
       <c r="H71" s="184">
-        <f t="shared" ca="1" si="14"/>
-        <v>60915263.336248279</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>13947442.306154761</v>
       </c>
       <c r="I71" s="204">
         <f>D71*$J$40-E71</f>
-        <v>541552587.50523448</v>
+        <v>151862576.95833158</v>
       </c>
       <c r="J71" s="204">
-        <f t="shared" ca="1" si="15"/>
-        <v>67694073.43815431</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>21694653.851190228</v>
       </c>
       <c r="K71" s="185">
         <f>D71*$L$40-E71</f>
-        <v>541552587.50523448</v>
+        <v>151862576.95833158</v>
       </c>
       <c r="L71" s="185">
-        <f t="shared" ca="1" si="16"/>
-        <v>67694073.43815431</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>21694653.851190228</v>
       </c>
     </row>
     <row r="72" spans="2:21" hidden="1" x14ac:dyDescent="0.25">
@@ -9017,7 +9017,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="187">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G72" s="184">
@@ -9025,7 +9025,7 @@
         <v>0</v>
       </c>
       <c r="H72" s="184">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="I72" s="204">
@@ -9033,7 +9033,7 @@
         <v>0</v>
       </c>
       <c r="J72" s="204">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="K72" s="185">
@@ -9041,7 +9041,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="185">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" ca="1" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -9061,7 +9061,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="187">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G73" s="184">
@@ -9069,7 +9069,7 @@
         <v>0</v>
       </c>
       <c r="H73" s="184">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="11"/>
         <v>0</v>
       </c>
       <c r="I73" s="204">
@@ -9077,7 +9077,7 @@
         <v>0</v>
       </c>
       <c r="J73" s="204">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="K73" s="185">
@@ -9085,7 +9085,7 @@
         <v>0</v>
       </c>
       <c r="L73" s="185">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" ca="1" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -9100,35 +9100,35 @@
       </c>
       <c r="E74" s="115">
         <f>SUM(E69:E73)</f>
-        <v>1154075034.6760221</v>
+        <v>1551233910.332849</v>
       </c>
       <c r="F74" s="177">
-        <f t="shared" si="13"/>
-        <v>0.66309934755223765</v>
+        <f t="shared" si="10"/>
+        <v>0.89129576755065898</v>
       </c>
       <c r="G74" s="181">
         <f>SUM(G69:G73)</f>
-        <v>499329220.64312696</v>
+        <v>102170344.98630005</v>
       </c>
       <c r="H74" s="181">
-        <f t="shared" ca="1" si="14"/>
-        <v>62416152.580390871</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>14595763.569471436</v>
       </c>
       <c r="I74" s="186">
         <f>SUM(I69:I73)</f>
-        <v>586350497.23887169</v>
+        <v>189191621.58204481</v>
       </c>
       <c r="J74" s="186">
-        <f t="shared" ca="1" si="15"/>
-        <v>73293812.154858962</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>27027374.511720687</v>
       </c>
       <c r="K74" s="186">
         <f>SUM(K69:K73)</f>
-        <v>586350497.23887169</v>
+        <v>189191621.58204481</v>
       </c>
       <c r="L74" s="186">
-        <f t="shared" ca="1" si="16"/>
-        <v>73293812.154858962</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>27027374.511720687</v>
       </c>
     </row>
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9141,10 +9141,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -9173,14 +9173,14 @@
       </c>
       <c r="D80" s="131">
         <f>SUMIF($B$10:$B$26,$T80,$F$10:$F$26)+SUMIF($B$10:$B$26,$U80,$F$10:$F$26)</f>
-        <v>305992102.95987999</v>
+        <v>340035346.74985999</v>
       </c>
       <c r="T80" t="str">
-        <f t="shared" ref="T80:U93" si="17">T51</f>
+        <f t="shared" ref="T80:U93" si="14">T51</f>
         <v>Picrom Stalyon</v>
       </c>
       <c r="U80" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9192,15 +9192,15 @@
         <v>70</v>
       </c>
       <c r="D81" s="132">
-        <f t="shared" ref="D81:D93" si="18">SUMIF($B$10:$B$26,$T81,$F$10:$F$26)+SUMIF($B$10:$B$26,$U81,$F$10:$F$26)</f>
-        <v>127390960.91</v>
+        <f>SUMIF($B$10:$B$26,$T81,$F$10:$F$26)+SUMIF($B$10:$B$26,$U81,$F$10:$F$26)</f>
+        <v>131602717.80000001</v>
       </c>
       <c r="T81" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>I MADE LUIH</v>
       </c>
       <c r="U81" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>I Made Luih (Sanur)</v>
       </c>
     </row>
@@ -9212,15 +9212,15 @@
         <v>173</v>
       </c>
       <c r="D82" s="132">
-        <f t="shared" si="18"/>
+        <f>SUMIF($B$10:$B$26,$T82,$F$10:$F$26)+SUMIF($B$10:$B$26,$U82,$F$10:$F$26)</f>
         <v>7027026.8399999999</v>
       </c>
       <c r="T82" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>NN Made Luih</v>
       </c>
       <c r="U82" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9232,15 +9232,15 @@
         <v>72</v>
       </c>
       <c r="D83" s="131">
-        <f t="shared" si="18"/>
-        <v>320372564.56976998</v>
+        <f>SUMIF($B$10:$B$26,$T83,$F$10:$F$26)+SUMIF($B$10:$B$26,$U83,$F$10:$F$26)</f>
+        <v>342828960.75976998</v>
       </c>
       <c r="T83" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Juni</v>
       </c>
       <c r="U83" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9252,15 +9252,15 @@
         <v>74</v>
       </c>
       <c r="D84" s="132">
-        <f t="shared" si="18"/>
+        <f>SUMIF($B$10:$B$26,$T84,$F$10:$F$26)+SUMIF($B$10:$B$26,$U84,$F$10:$F$26)</f>
         <v>0</v>
       </c>
       <c r="T84" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>FIB</v>
       </c>
       <c r="U84" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9272,15 +9272,15 @@
         <v>74</v>
       </c>
       <c r="D85" s="131">
-        <f t="shared" si="18"/>
-        <v>40335405.060000002</v>
+        <f>SUMIF($B$10:$B$26,$T85,$F$10:$F$26)+SUMIF($B$10:$B$26,$U85,$F$10:$F$26)</f>
+        <v>56855405.259999998</v>
       </c>
       <c r="T85" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Ronald</v>
       </c>
       <c r="U85" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9292,15 +9292,15 @@
         <v>77</v>
       </c>
       <c r="D86" s="132">
-        <f t="shared" si="18"/>
-        <v>760950711.77996898</v>
+        <f>SUMIF($B$10:$B$26,$T86,$F$10:$F$26)+SUMIF($B$10:$B$26,$U86,$F$10:$F$26)</f>
+        <v>830718820.72996902</v>
       </c>
       <c r="T86" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Monica</v>
       </c>
       <c r="U86" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9312,15 +9312,15 @@
         <v>79</v>
       </c>
       <c r="D87" s="131">
-        <f t="shared" si="18"/>
-        <v>246882618.74950501</v>
+        <f>SUMIF($B$10:$B$26,$T87,$F$10:$F$26)+SUMIF($B$10:$B$26,$U87,$F$10:$F$26)</f>
+        <v>257288564.68950501</v>
       </c>
       <c r="T87" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Sujana</v>
       </c>
       <c r="U87" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9332,15 +9332,15 @@
         <v>174</v>
       </c>
       <c r="D88" s="132">
-        <f t="shared" si="18"/>
+        <f>SUMIF($B$10:$B$26,$T88,$F$10:$F$26)+SUMIF($B$10:$B$26,$U88,$F$10:$F$26)</f>
         <v>9813783.5199999996</v>
       </c>
       <c r="T88" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>NN Sujana</v>
       </c>
       <c r="U88" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9352,15 +9352,15 @@
         <v>81</v>
       </c>
       <c r="D89" s="132">
-        <f t="shared" si="18"/>
+        <f>SUMIF($B$10:$B$26,$T89,$F$10:$F$26)+SUMIF($B$10:$B$26,$U89,$F$10:$F$26)</f>
         <v>39783784.579999998</v>
       </c>
       <c r="T89" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Wahyu</v>
       </c>
       <c r="U89" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9372,15 +9372,15 @@
         <v>83</v>
       </c>
       <c r="D90" s="131">
-        <f t="shared" si="18"/>
-        <v>468670407.23952502</v>
+        <f>SUMIF($B$10:$B$26,$T90,$F$10:$F$26)+SUMIF($B$10:$B$26,$U90,$F$10:$F$26)</f>
+        <v>483452299.52950501</v>
       </c>
       <c r="T90" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Taufik</v>
       </c>
       <c r="U90" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9392,15 +9392,15 @@
         <v>85</v>
       </c>
       <c r="D91" s="132">
-        <f t="shared" si="18"/>
-        <v>122621117.86994299</v>
+        <f>SUMIF($B$10:$B$26,$T91,$F$10:$F$26)+SUMIF($B$10:$B$26,$U91,$F$10:$F$26)</f>
+        <v>126163149.179938</v>
       </c>
       <c r="T91" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Dewi Kristiani</v>
       </c>
       <c r="U91" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9412,15 +9412,15 @@
         <v>87</v>
       </c>
       <c r="D92" s="131">
-        <f t="shared" si="18"/>
+        <f>SUMIF($B$10:$B$26,$T92,$F$10:$F$26)+SUMIF($B$10:$B$26,$U92,$F$10:$F$26)</f>
         <v>18013297.6536</v>
       </c>
       <c r="T92" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Wira</v>
       </c>
       <c r="U92" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9432,15 +9432,15 @@
         <v>89</v>
       </c>
       <c r="D93" s="132">
-        <f t="shared" si="18"/>
-        <v>125671894.618</v>
+        <f>SUMIF($B$10:$B$26,$T93,$F$10:$F$26)+SUMIF($B$10:$B$26,$U93,$F$10:$F$26)</f>
+        <v>141271894.81800002</v>
       </c>
       <c r="T93" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Ni Ketut Sriasih (GT)</v>
       </c>
       <c r="U93" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>Ni Ketut Sriasih (MT)</v>
       </c>
     </row>
@@ -9451,18 +9451,12 @@
       <c r="C94" s="58"/>
       <c r="D94" s="120">
         <f>SUM(D80:D93)</f>
-        <v>2593525676.3501921</v>
+        <v>2784855052.1101465</v>
       </c>
     </row>
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -9477,6 +9471,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -10104,11 +10104,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="259" t="s">
         <v>163</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="260"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -10428,33 +10428,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="263"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="270"/>
+      <c r="Q48" s="270"/>
+      <c r="R48" s="271"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -10463,49 +10463,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="268"/>
+      <c r="C50" s="268"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -10530,13 +10530,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="273"/>
+      <c r="N50" s="273"/>
+      <c r="O50" s="275"/>
+      <c r="P50" s="275"/>
+      <c r="Q50" s="277"/>
+      <c r="R50" s="277"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -11652,21 +11652,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="283" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="260" t="s">
+      <c r="G67" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="270"/>
+      <c r="I67" s="270"/>
+      <c r="J67" s="270"/>
+      <c r="K67" s="270"/>
+      <c r="L67" s="271"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -11987,10 +11987,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -12303,12 +12303,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -12323,6 +12317,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -12950,11 +12950,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="259" t="s">
         <v>175</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="260"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -13274,33 +13274,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="263"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="270"/>
+      <c r="Q48" s="270"/>
+      <c r="R48" s="271"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -13309,49 +13309,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="268"/>
+      <c r="C50" s="268"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -13376,13 +13376,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="273"/>
+      <c r="N50" s="273"/>
+      <c r="O50" s="275"/>
+      <c r="P50" s="275"/>
+      <c r="Q50" s="277"/>
+      <c r="R50" s="277"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -14498,21 +14498,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="283" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="260" t="s">
+      <c r="G67" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="270"/>
+      <c r="I67" s="270"/>
+      <c r="J67" s="270"/>
+      <c r="K67" s="270"/>
+      <c r="L67" s="271"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -14833,10 +14833,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -15149,12 +15149,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -15169,6 +15163,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -15796,11 +15796,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="259" t="s">
         <v>177</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="260"/>
+      <c r="D40" s="261"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -16120,33 +16120,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="263"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="270"/>
+      <c r="Q48" s="270"/>
+      <c r="R48" s="271"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -16155,49 +16155,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="268"/>
+      <c r="C50" s="268"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -16222,13 +16222,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="273"/>
+      <c r="N50" s="273"/>
+      <c r="O50" s="275"/>
+      <c r="P50" s="275"/>
+      <c r="Q50" s="277"/>
+      <c r="R50" s="277"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -17330,21 +17330,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="283" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="260" t="s">
+      <c r="G67" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="270"/>
+      <c r="I67" s="270"/>
+      <c r="J67" s="270"/>
+      <c r="K67" s="270"/>
+      <c r="L67" s="271"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -17665,10 +17665,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -17981,12 +17981,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -18001,6 +17995,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -25780,11 +25780,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="269" t="s">
+      <c r="B41" s="259" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="270"/>
-      <c r="D41" s="271"/>
+      <c r="C41" s="260"/>
+      <c r="D41" s="261"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -26055,59 +26055,59 @@
       </c>
     </row>
     <row r="48" spans="2:19" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="261"/>
-      <c r="M48" s="261"/>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
+      <c r="L48" s="270"/>
+      <c r="M48" s="270"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="271"/>
       <c r="Q48"/>
       <c r="R48"/>
     </row>
     <row r="49" spans="2:18" s="139" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="277" t="s">
+      <c r="B49" s="267" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="277" t="s">
+      <c r="C49" s="267" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="274" t="s">
+      <c r="D49" s="264" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
+      <c r="E49" s="265"/>
+      <c r="F49" s="266"/>
       <c r="G49" s="140" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="140"/>
       <c r="I49" s="140"/>
-      <c r="J49" s="274" t="s">
+      <c r="J49" s="264" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="263" t="str">
+      <c r="K49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="263" t="str">
+      <c r="L49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
@@ -26122,7 +26122,7 @@
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="267" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -26131,8 +26131,8 @@
       <c r="R49"/>
     </row>
     <row r="50" spans="2:18" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="277"/>
-      <c r="C50" s="277"/>
+      <c r="B50" s="267"/>
+      <c r="C50" s="267"/>
       <c r="D50" s="141" t="s">
         <v>149</v>
       </c>
@@ -26151,13 +26151,13 @@
       <c r="I50" s="142" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="274"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="266"/>
+      <c r="J50" s="264"/>
+      <c r="K50" s="273"/>
+      <c r="L50" s="273"/>
+      <c r="M50" s="275"/>
       <c r="N50" s="188"/>
       <c r="O50" s="183"/>
-      <c r="P50" s="268"/>
+      <c r="P50" s="277"/>
       <c r="Q50"/>
       <c r="R50"/>
     </row>
@@ -27498,10 +27498,10 @@
       <c r="I77"/>
     </row>
     <row r="78" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -27700,13 +27700,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="J49:J50"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
     <mergeCell ref="K48:P48"/>
@@ -27716,6 +27709,13 @@
     <mergeCell ref="P49:P50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="J49:J50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="26" priority="8">
@@ -28755,25 +28755,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="261"/>
-      <c r="M48" s="261"/>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
+      <c r="L48" s="270"/>
+      <c r="M48" s="270"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="271"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -28795,32 +28795,32 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="263" t="str">
+      <c r="K49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="263" t="str">
+      <c r="L49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="265" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="267" t="str">
+      <c r="O49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="267" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -28848,12 +28848,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="266"/>
-      <c r="N50" s="266"/>
-      <c r="O50" s="268"/>
-      <c r="P50" s="268"/>
+      <c r="K50" s="273"/>
+      <c r="L50" s="273"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
+      <c r="O50" s="277"/>
+      <c r="P50" s="277"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="167" t="s">
@@ -30090,10 +30090,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -30287,17 +30287,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -30305,6 +30294,17 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -31062,11 +31062,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="269" t="s">
+      <c r="B41" s="259" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="270"/>
-      <c r="D41" s="271"/>
+      <c r="C41" s="260"/>
+      <c r="D41" s="261"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -31341,25 +31341,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="261"/>
-      <c r="M48" s="261"/>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
+      <c r="L48" s="270"/>
+      <c r="M48" s="270"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="271"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -31381,32 +31381,32 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="263" t="str">
+      <c r="K49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="263" t="str">
+      <c r="L49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="265" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="267" t="str">
+      <c r="O49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="267" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -31434,12 +31434,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="266"/>
-      <c r="N50" s="266"/>
-      <c r="O50" s="268"/>
-      <c r="P50" s="268"/>
+      <c r="K50" s="273"/>
+      <c r="L50" s="273"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
+      <c r="O50" s="277"/>
+      <c r="P50" s="277"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -32676,10 +32676,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -32860,17 +32860,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -32878,6 +32867,17 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -33656,11 +33656,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" s="191" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="269" t="s">
+      <c r="B41" s="259" t="s">
         <v>189</v>
       </c>
-      <c r="C41" s="270"/>
-      <c r="D41" s="271"/>
+      <c r="C41" s="260"/>
+      <c r="D41" s="261"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -33935,25 +33935,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="260" t="s">
+      <c r="C48" s="263"/>
+      <c r="D48" s="263"/>
+      <c r="E48" s="263"/>
+      <c r="F48" s="263"/>
+      <c r="G48" s="263"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="263"/>
+      <c r="J48" s="263"/>
+      <c r="K48" s="269" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="261"/>
-      <c r="M48" s="261"/>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
+      <c r="L48" s="270"/>
+      <c r="M48" s="270"/>
+      <c r="N48" s="270"/>
+      <c r="O48" s="270"/>
+      <c r="P48" s="271"/>
     </row>
     <row r="49" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -33975,22 +33975,22 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="263" t="str">
+      <c r="K49" s="272" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="263" t="str">
+      <c r="L49" s="272" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="265" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
@@ -34028,10 +34028,10 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="266"/>
-      <c r="N50" s="266"/>
+      <c r="K50" s="273"/>
+      <c r="L50" s="273"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
       <c r="O50" s="282"/>
       <c r="P50" s="282"/>
     </row>
@@ -35270,10 +35270,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="268" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="268" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -35467,11 +35467,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
@@ -35485,6 +35480,11 @@
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -909,7 +909,7 @@
     <t>RONALD</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL —  23 SEPTEMBER 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL —  24 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>
@@ -2556,33 +2556,6 @@
     <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2613,6 +2586,33 @@
     <xf numFmtId="0" fontId="48" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2626,15 +2626,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2656,6 +2647,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4299,11 +4299,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>219</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -4623,33 +4623,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -4658,49 +4658,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -4725,13 +4725,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="172" t="s">
         <v>216</v>
       </c>
@@ -5847,21 +5847,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
-      <c r="F67" s="285"/>
-      <c r="G67" s="269" t="s">
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
+      <c r="F67" s="292"/>
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -6180,10 +6180,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -6495,6 +6495,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -6509,12 +6515,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="C3" s="75">
         <f ca="1">IF($J$5&lt;&gt;"",$J$5,MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),9,1)),EOMONTH(DATE(YEAR(TODAY()),9,1),0),11)-MAX(0,$J$3-$J$4)))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="76" t="s">
         <v>104</v>
@@ -6720,19 +6720,19 @@
         <v>112</v>
       </c>
       <c r="C10" s="234">
-        <v>122534293.762722</v>
+        <v>122291455.94272</v>
       </c>
       <c r="D10" s="234">
-        <v>33718196.818899997</v>
+        <v>36845696.872796997</v>
       </c>
       <c r="E10" s="234">
-        <v>175612225.567045</v>
+        <v>179872333.71704</v>
       </c>
       <c r="F10" s="234">
-        <v>126163149.179938</v>
+        <v>137341527.88993299</v>
       </c>
       <c r="G10" s="234">
-        <v>458027865.328605</v>
+        <v>476351014.42249</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="111"/>
@@ -6770,19 +6770,19 @@
         <v>70</v>
       </c>
       <c r="C12" s="234">
-        <v>144079108.13797399</v>
+        <v>154754903.15795001</v>
       </c>
       <c r="D12" s="234">
-        <v>64996955.761524998</v>
+        <v>65434973.791523002</v>
       </c>
       <c r="E12" s="234">
-        <v>139985543.73958299</v>
+        <v>142914057.259583</v>
       </c>
       <c r="F12" s="234">
         <v>65596580.700000003</v>
       </c>
       <c r="G12" s="234">
-        <v>414658188.339082</v>
+        <v>428700514.90905601</v>
       </c>
       <c r="H12" s="111"/>
       <c r="I12" s="111"/>
@@ -6795,19 +6795,19 @@
         <v>114</v>
       </c>
       <c r="C13" s="234">
-        <v>29542102.929949999</v>
+        <v>30349577.699947</v>
       </c>
       <c r="D13" s="234">
-        <v>18570309.229973</v>
+        <v>21848079.549964</v>
       </c>
       <c r="E13" s="234">
-        <v>163454911.61964399</v>
+        <v>182651308.10961899</v>
       </c>
       <c r="F13" s="234">
-        <v>66006137.100000001</v>
+        <v>70939470.450000003</v>
       </c>
       <c r="G13" s="234">
-        <v>277573460.87956703</v>
+        <v>305788435.80953002</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="111"/>
@@ -6820,19 +6820,19 @@
         <v>115</v>
       </c>
       <c r="C14" s="234">
-        <v>423669713.43459803</v>
+        <v>425558938.85456401</v>
       </c>
       <c r="D14" s="234">
-        <v>38215060.301464997</v>
+        <v>41590640.469465002</v>
       </c>
       <c r="E14" s="234">
-        <v>138709153.37987801</v>
+        <v>139353252.479877</v>
       </c>
       <c r="F14" s="234">
-        <v>342828960.75976998</v>
+        <v>346086641.02977002</v>
       </c>
       <c r="G14" s="234">
-        <v>943422887.87571096</v>
+        <v>952589472.83367598</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="111"/>
@@ -6845,19 +6845,19 @@
         <v>118</v>
       </c>
       <c r="C15" s="234">
-        <v>1462364582.0499079</v>
+        <v>1499930492.5599079</v>
       </c>
       <c r="D15" s="234">
-        <v>9178230.5349240005</v>
+        <v>11190936.014923999</v>
       </c>
       <c r="E15" s="234">
-        <v>59318395.269938998</v>
+        <v>76818395.269939005</v>
       </c>
       <c r="F15" s="234">
         <v>13983784.08</v>
       </c>
       <c r="G15" s="234">
-        <v>1544844991.9347711</v>
+        <v>1601923607.9247711</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="111"/>
@@ -6870,19 +6870,19 @@
         <v>120</v>
       </c>
       <c r="C16" s="234">
-        <v>403308935.481655</v>
+        <v>421221722.82963502</v>
       </c>
       <c r="D16" s="234">
-        <v>38062931.419927001</v>
+        <v>41281878.019927002</v>
       </c>
       <c r="E16" s="234">
-        <v>263379730.93952</v>
+        <v>275830181.54944998</v>
       </c>
       <c r="F16" s="234">
-        <v>830718820.72996902</v>
+        <v>858628819.27996898</v>
       </c>
       <c r="G16" s="234">
-        <v>1535470418.5710709</v>
+        <v>1596962601.6789811</v>
       </c>
       <c r="H16" s="111"/>
       <c r="I16" s="111"/>
@@ -6895,19 +6895,19 @@
         <v>122</v>
       </c>
       <c r="C17" s="234">
-        <v>93324215.815028995</v>
+        <v>94697468.216019005</v>
       </c>
       <c r="D17" s="234">
         <v>12915436.9209</v>
       </c>
       <c r="E17" s="234">
-        <v>72454578.968842</v>
+        <v>72504191.618842006</v>
       </c>
       <c r="F17" s="234">
         <v>47952973.898000002</v>
       </c>
       <c r="G17" s="234">
-        <v>226647205.60277101</v>
+        <v>228070070.653761</v>
       </c>
       <c r="H17" s="111"/>
       <c r="I17" s="111"/>
@@ -6924,16 +6924,16 @@
         <v>13080047.589996999</v>
       </c>
       <c r="D18" s="234">
-        <v>133208702.091655</v>
+        <v>133803404.811655</v>
       </c>
       <c r="E18" s="234">
         <v>56002106.100000001</v>
       </c>
       <c r="F18" s="234">
-        <v>93318920.920000002</v>
+        <v>100562164.31999999</v>
       </c>
       <c r="G18" s="234">
-        <v>295609776.70165199</v>
+        <v>303447722.821652</v>
       </c>
       <c r="H18" s="111"/>
       <c r="I18" s="111"/>
@@ -6947,7 +6947,7 @@
         <v>169</v>
       </c>
       <c r="C19" s="234">
-        <v>57858708.960000001</v>
+        <v>45722758.259999998</v>
       </c>
       <c r="D19" s="234" t="s">
         <v>165</v>
@@ -6959,7 +6959,7 @@
         <v>7027026.8399999999</v>
       </c>
       <c r="G19" s="234">
-        <v>64885735.799999997</v>
+        <v>52749785.100000001</v>
       </c>
       <c r="H19" s="111"/>
       <c r="I19" s="111"/>
@@ -7003,26 +7003,26 @@
         <v>124</v>
       </c>
       <c r="C21" s="234">
-        <v>221268705.06241599</v>
+        <v>229659386.58680099</v>
       </c>
       <c r="D21" s="234">
-        <v>41719931.423455998</v>
+        <v>44851670.153456002</v>
       </c>
       <c r="E21" s="234">
-        <v>127850860.93978301</v>
+        <v>129240491.55978499</v>
       </c>
       <c r="F21" s="234">
-        <v>340035346.74985999</v>
+        <v>345823522.47986001</v>
       </c>
       <c r="G21" s="234">
-        <v>730874844.17551506</v>
+        <v>749575070.77990198</v>
       </c>
       <c r="H21" s="111"/>
       <c r="I21" s="111"/>
       <c r="J21" s="111"/>
       <c r="M21" s="14">
         <f>SUM(C33,C34)+M20</f>
-        <v>932747039.34663296</v>
+        <v>934135147.50660896</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>224</v>
@@ -7033,19 +7033,19 @@
         <v>125</v>
       </c>
       <c r="C22" s="234">
-        <v>218343790.722233</v>
+        <v>226738564.12332499</v>
       </c>
       <c r="D22" s="234">
         <v>55894289.419963002</v>
       </c>
       <c r="E22" s="234">
-        <v>162558650.86619499</v>
+        <v>171252696.26218399</v>
       </c>
       <c r="F22" s="234">
-        <v>257288564.68950501</v>
+        <v>260869645.919505</v>
       </c>
       <c r="G22" s="234">
-        <v>694085295.697896</v>
+        <v>714755195.72497702</v>
       </c>
       <c r="H22" s="111"/>
       <c r="I22" s="111"/>
@@ -7056,19 +7056,19 @@
         <v>126</v>
       </c>
       <c r="C23" s="234">
-        <v>386015669.137429</v>
+        <v>402608462.21627998</v>
       </c>
       <c r="D23" s="234">
-        <v>55017470.924923003</v>
+        <v>54954295.924923003</v>
       </c>
       <c r="E23" s="234">
-        <v>174500614.40990701</v>
+        <v>181079758.51990199</v>
       </c>
       <c r="F23" s="234">
-        <v>483452299.52950501</v>
+        <v>514008155.46949601</v>
       </c>
       <c r="G23" s="234">
-        <v>1098986054.0017641</v>
+        <v>1152650672.1306009</v>
       </c>
       <c r="H23" s="111"/>
       <c r="I23" s="111"/>
@@ -7079,19 +7079,19 @@
         <v>225</v>
       </c>
       <c r="C24" s="234">
-        <v>157144378.35867101</v>
+        <v>172496649.28866401</v>
       </c>
       <c r="D24" s="234">
-        <v>44687069.909941003</v>
+        <v>45674574.409941003</v>
       </c>
       <c r="E24" s="234">
-        <v>126616820.968173</v>
+        <v>133534839.06817099</v>
       </c>
       <c r="F24" s="234">
-        <v>56855405.259999998</v>
+        <v>64062612.359999999</v>
       </c>
       <c r="G24" s="234">
-        <v>385303674.49678499</v>
+        <v>415768675.12677598</v>
       </c>
       <c r="H24" s="111"/>
       <c r="I24" s="111"/>
@@ -7102,19 +7102,19 @@
         <v>220</v>
       </c>
       <c r="C25" s="234">
-        <v>259986756.55092999</v>
+        <v>270003598.861857</v>
       </c>
       <c r="D25" s="234">
-        <v>75962454.816541001</v>
+        <v>77822671.056532994</v>
       </c>
       <c r="E25" s="234">
-        <v>85307067.912571996</v>
+        <v>88127833.698561996</v>
       </c>
       <c r="F25" s="234">
-        <v>39783784.579999998</v>
+        <v>49513514.579999998</v>
       </c>
       <c r="G25" s="234">
-        <v>461040063.86004299</v>
+        <v>485467618.19695199</v>
       </c>
       <c r="H25" s="111"/>
       <c r="I25" s="111"/>
@@ -7125,19 +7125,19 @@
         <v>127</v>
       </c>
       <c r="C26" s="234">
-        <v>399272594.47329497</v>
+        <v>413271522.44322699</v>
       </c>
       <c r="D26" s="234">
-        <v>254167394.92625701</v>
+        <v>260467539.04622999</v>
       </c>
       <c r="E26" s="234">
-        <v>229102206.125873</v>
+        <v>238566169.62585801</v>
       </c>
       <c r="F26" s="234">
         <v>18013297.6536</v>
       </c>
       <c r="G26" s="234">
-        <v>900555493.17902505</v>
+        <v>930318528.76891506</v>
       </c>
       <c r="H26" s="111"/>
       <c r="I26" s="111"/>
@@ -7180,7 +7180,7 @@
         <v>131</v>
       </c>
       <c r="C31" s="171">
-        <v>203469688.08525699</v>
+        <v>230771202.18516701</v>
       </c>
       <c r="G31" s="111"/>
       <c r="H31" s="111"/>
@@ -7191,7 +7191,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="234">
-        <v>415017182.90095901</v>
+        <v>427130336.43894702</v>
       </c>
       <c r="G32" s="111"/>
       <c r="H32" s="111"/>
@@ -7213,7 +7213,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="234">
-        <v>441684411.03132701</v>
+        <v>443072519.19130301</v>
       </c>
       <c r="G34" s="111"/>
       <c r="H34" s="111"/>
@@ -7258,17 +7258,17 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
       <c r="F40" s="174">
         <f ca="1">IF(MONTH(TODAY())=9,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;9,1,0))</f>
-        <v>0.76666666666666672</v>
+        <v>0.8</v>
       </c>
       <c r="G40" s="192" t="s">
         <v>187</v>
@@ -7355,35 +7355,35 @@
       </c>
       <c r="E42" s="46">
         <f>H65</f>
-        <v>3122129670.9968972</v>
+        <v>3215155706.6509838</v>
       </c>
       <c r="F42" s="176">
         <f>IFERROR(E42/D42,0)</f>
-        <v>0.69199417873035451</v>
+        <v>0.71261262893150712</v>
       </c>
       <c r="G42" s="184">
         <f>D42*$H$40-E42</f>
-        <v>1164067061.017529</v>
+        <v>1071041025.3634424</v>
       </c>
       <c r="H42" s="184">
         <f ca="1">IFERROR(G42/$C$3,0)</f>
-        <v>166295294.43107557</v>
+        <v>178506837.56057373</v>
       </c>
       <c r="I42" s="204">
         <f>D42*$J$40-E42</f>
-        <v>1389656362.7024989</v>
+        <v>1296630327.0484123</v>
       </c>
       <c r="J42" s="204">
         <f ca="1">IFERROR(I42/$C$3,0)</f>
-        <v>198522337.52892843</v>
+        <v>216105054.50806871</v>
       </c>
       <c r="K42" s="185">
         <f>D42*$L$40-E42</f>
-        <v>1389656362.7024989</v>
+        <v>1296630327.0484123</v>
       </c>
       <c r="L42" s="185">
         <f ca="1">IFERROR(K42/$C$3,0)</f>
-        <v>198522337.52892843</v>
+        <v>216105054.50806871</v>
       </c>
       <c r="S42" s="173">
         <v>0.8</v>
@@ -7402,35 +7402,35 @@
       </c>
       <c r="E43" s="46">
         <f>I65</f>
-        <v>897387187.46542609</v>
+        <v>923636133.94727707</v>
       </c>
       <c r="F43" s="176">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.64036634896818712</v>
+        <v>0.65909732959464251</v>
       </c>
       <c r="G43" s="184">
         <f>D43*$H$40-E43</f>
-        <v>433909857.52421796</v>
+        <v>407660911.04236698</v>
       </c>
       <c r="H43" s="184">
         <f ca="1">IFERROR(G43/$C$3,0)</f>
-        <v>61987122.503459707</v>
+        <v>67943485.173727825</v>
       </c>
       <c r="I43" s="204">
         <f>D43*$J$40-E43</f>
-        <v>503978123.04998887</v>
+        <v>477729176.56813788</v>
       </c>
       <c r="J43" s="204">
         <f ca="1">IFERROR(I43/$C$3,0)</f>
-        <v>71996874.721426979</v>
+        <v>79621529.428022981</v>
       </c>
       <c r="K43" s="185">
         <f>D43*$L$40-E43</f>
-        <v>503978123.04998887</v>
+        <v>477729176.56813788</v>
       </c>
       <c r="L43" s="185">
         <f ca="1">IFERROR(K43/$C$3,0)</f>
-        <v>71996874.721426979</v>
+        <v>79621529.428022981</v>
       </c>
       <c r="S43" s="173">
         <v>0.85</v>
@@ -7449,35 +7449,35 @@
       </c>
       <c r="E44" s="46">
         <f>J65</f>
-        <v>2114692130.1762149</v>
+        <v>2190086878.2080727</v>
       </c>
       <c r="F44" s="176">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.71810715012601212</v>
+        <v>0.7437096985400522</v>
       </c>
       <c r="G44" s="184">
         <f>IF(D44=0,0,D44*$H$40-E44)</f>
-        <v>682881356.33603597</v>
+        <v>607486608.30417824</v>
       </c>
       <c r="H44" s="184">
         <f ca="1">IFERROR(G44/$C$3,0)</f>
-        <v>97554479.476576567</v>
+        <v>101247768.05069637</v>
       </c>
       <c r="I44" s="204">
         <f>IF(D44=0,0,D44*$J$40-E44)</f>
-        <v>830122066.15247035</v>
+        <v>754727318.12061262</v>
       </c>
       <c r="J44" s="204">
         <f ca="1">IFERROR(I44/$C$3,0)</f>
-        <v>118588866.59321006</v>
+        <v>125787886.35343544</v>
       </c>
       <c r="K44" s="185">
         <f>IF(D44=0,0,D44*$L$40-E44)</f>
-        <v>830122066.15247035</v>
+        <v>754727318.12061262</v>
       </c>
       <c r="L44" s="185">
         <f ca="1">IFERROR(K44/$C$3,0)</f>
-        <v>118588866.59321006</v>
+        <v>125787886.35343544</v>
       </c>
       <c r="S44" s="173">
         <v>0.9</v>
@@ -7496,35 +7496,35 @@
       </c>
       <c r="E45" s="46">
         <f>E74</f>
-        <v>1551233910.332849</v>
+        <v>1592036686.130723</v>
       </c>
       <c r="F45" s="176">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.89129576755065898</v>
+        <v>0.91473990523403403</v>
       </c>
       <c r="G45" s="184">
         <f>D45*$H$40-E45</f>
-        <v>102170344.98629975</v>
+        <v>61367569.188425779</v>
       </c>
       <c r="H45" s="184">
         <f ca="1">IFERROR(G45/$C$3,0)</f>
-        <v>14595763.569471393</v>
+        <v>10227928.198070964</v>
       </c>
       <c r="I45" s="204">
         <f>D45*$J$40-E45</f>
-        <v>189191621.5820446</v>
+        <v>148388845.78417063</v>
       </c>
       <c r="J45" s="204">
         <f ca="1">IFERROR(I45/$C$3,0)</f>
-        <v>27027374.511720657</v>
+        <v>24731474.297361773</v>
       </c>
       <c r="K45" s="185">
         <f>D45*$L$40-E45</f>
-        <v>189191621.5820446</v>
+        <v>148388845.78417063</v>
       </c>
       <c r="L45" s="185">
         <f ca="1">IFERROR(K45/$C$3,0)</f>
-        <v>27027374.511720657</v>
+        <v>24731474.297361773</v>
       </c>
       <c r="S45" s="173">
         <v>0.95</v>
@@ -7541,35 +7541,35 @@
       </c>
       <c r="E46" s="47">
         <f>SUM(E42:E45)</f>
-        <v>7685442898.9713879</v>
+        <v>7920915404.9370565</v>
       </c>
       <c r="F46" s="177">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.72515185054297882</v>
+        <v>0.74736961023459669</v>
       </c>
       <c r="G46" s="181">
         <f>SUM(G42:G45)</f>
-        <v>2383028619.8640823</v>
+        <v>2147556113.8984137</v>
       </c>
       <c r="H46" s="181">
         <f ca="1">IFERROR(G46/$C$3,0)</f>
-        <v>340432659.98058319</v>
+        <v>357926018.98306894</v>
       </c>
       <c r="I46" s="186">
         <f>SUM(I42:I45)</f>
-        <v>2912948173.4870024</v>
+        <v>2677475667.5213332</v>
       </c>
       <c r="J46" s="186">
         <f ca="1">IFERROR(I46/$C$3,0)</f>
-        <v>416135453.35528606</v>
+        <v>446245944.58688885</v>
       </c>
       <c r="K46" s="186">
         <f>SUM(K42:K45)</f>
-        <v>2912948173.4870024</v>
+        <v>2677475667.5213332</v>
       </c>
       <c r="L46" s="186">
         <f ca="1">IFERROR(K46/$C$3,0)</f>
-        <v>416135453.35528606</v>
+        <v>446245944.58688885</v>
       </c>
       <c r="S46" s="173">
         <v>1</v>
@@ -7582,33 +7582,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -7617,49 +7617,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -7684,13 +7684,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -7722,48 +7722,48 @@
         <v>514367519.88681459</v>
       </c>
       <c r="H51" s="114">
-        <f>SUMIF($B$10:$B$26,$T51,C$10:C$26)+SUMIF($B$10:$B$26,$U51,C$10:C$26)</f>
-        <v>221268705.06241599</v>
+        <f t="shared" ref="H51:H64" si="1">SUMIF($B$10:$B$26,$T51,C$10:C$26)+SUMIF($B$10:$B$26,$U51,C$10:C$26)</f>
+        <v>229659386.58680099</v>
       </c>
       <c r="I51" s="114">
-        <f>SUMIF($B$10:$B$26,$T51,D$10:D$26)+SUMIF($B$10:$B$26,$U51,D$10:D$26)</f>
-        <v>41719931.423455998</v>
+        <f t="shared" ref="I51:I64" si="2">SUMIF($B$10:$B$26,$T51,D$10:D$26)+SUMIF($B$10:$B$26,$U51,D$10:D$26)</f>
+        <v>44851670.153456002</v>
       </c>
       <c r="J51" s="114">
-        <f>SUMIF($B$10:$B$26,$T51,E$10:E$26)+SUMIF($B$10:$B$26,$U51,E$10:E$26)</f>
-        <v>127850860.93978301</v>
+        <f t="shared" ref="J51:J64" si="3">SUMIF($B$10:$B$26,$T51,E$10:E$26)+SUMIF($B$10:$B$26,$U51,E$10:E$26)</f>
+        <v>129240491.55978499</v>
       </c>
       <c r="K51" s="114">
-        <f t="shared" ref="K51:K64" si="1">SUM(H51:J51)</f>
-        <v>390839497.42565501</v>
+        <f t="shared" ref="K51:K64" si="4">SUM(H51:J51)</f>
+        <v>403751548.30004203</v>
       </c>
       <c r="L51" s="187">
-        <f t="shared" ref="L51:L65" si="2">IFERROR(K51/G51,0)</f>
-        <v>0.75984482362272476</v>
+        <f t="shared" ref="L51:L65" si="5">IFERROR(K51/G51,0)</f>
+        <v>0.78494759620297694</v>
       </c>
       <c r="M51" s="184">
-        <f t="shared" ref="M51:M64" si="3">G51*$H$40-K51</f>
-        <v>97809646.46681881</v>
+        <f t="shared" ref="M51:M64" si="6">G51*$H$40-K51</f>
+        <v>84897595.592431784</v>
       </c>
       <c r="N51" s="184">
-        <f t="shared" ref="N51:N65" ca="1" si="4">IFERROR(M51/$C$3,0)</f>
-        <v>13972806.638116973</v>
+        <f t="shared" ref="N51:N65" ca="1" si="7">IFERROR(M51/$C$3,0)</f>
+        <v>14149599.265405297</v>
       </c>
       <c r="O51" s="180">
-        <f t="shared" ref="O51:O64" si="5">G51*$J$40-K51</f>
-        <v>123528022.46115959</v>
+        <f t="shared" ref="O51:O64" si="8">G51*$J$40-K51</f>
+        <v>110615971.58677256</v>
       </c>
       <c r="P51" s="180">
-        <f t="shared" ref="P51:P65" ca="1" si="6">IFERROR(O51/$C$3,0)</f>
-        <v>17646860.351594228</v>
+        <f t="shared" ref="P51:P65" ca="1" si="9">IFERROR(O51/$C$3,0)</f>
+        <v>18435995.264462095</v>
       </c>
       <c r="Q51" s="185">
-        <f t="shared" ref="Q51:Q64" si="7">G51*$L$40-K51</f>
-        <v>123528022.46115959</v>
+        <f t="shared" ref="Q51:Q64" si="10">G51*$L$40-K51</f>
+        <v>110615971.58677256</v>
       </c>
       <c r="R51" s="185">
-        <f t="shared" ref="R51:R65" ca="1" si="8">IFERROR(Q51/$C$3,0)</f>
-        <v>17646860.351594228</v>
+        <f t="shared" ref="R51:R65" ca="1" si="11">IFERROR(Q51/$C$3,0)</f>
+        <v>18435995.264462095</v>
       </c>
       <c r="T51" t="s">
         <v>124</v>
@@ -7796,48 +7796,48 @@
         <v>785523881.42014158</v>
       </c>
       <c r="H52" s="114">
-        <f>SUMIF($B$10:$B$26,$T52,C$10:C$26)+SUMIF($B$10:$B$26,$U52,C$10:C$26)</f>
-        <v>173621211.06792399</v>
+        <f t="shared" si="1"/>
+        <v>185104480.85789701</v>
       </c>
       <c r="I52" s="114">
-        <f>SUMIF($B$10:$B$26,$T52,D$10:D$26)+SUMIF($B$10:$B$26,$U52,D$10:D$26)</f>
-        <v>83567264.991497993</v>
+        <f t="shared" si="2"/>
+        <v>87283053.341487005</v>
       </c>
       <c r="J52" s="114">
-        <f>SUMIF($B$10:$B$26,$T52,E$10:E$26)+SUMIF($B$10:$B$26,$U52,E$10:E$26)</f>
-        <v>303440455.35922694</v>
+        <f t="shared" si="3"/>
+        <v>325565365.36920202</v>
       </c>
       <c r="K52" s="114">
-        <f t="shared" si="1"/>
-        <v>560628931.41864896</v>
+        <f t="shared" si="4"/>
+        <v>597952899.56858611</v>
       </c>
       <c r="L52" s="187">
-        <f t="shared" si="2"/>
-        <v>0.71370068393731445</v>
+        <f t="shared" si="5"/>
+        <v>0.7612154305067752</v>
       </c>
       <c r="M52" s="184">
-        <f t="shared" si="3"/>
-        <v>185618755.93048549</v>
+        <f t="shared" si="6"/>
+        <v>148294787.78054833</v>
       </c>
       <c r="N52" s="184">
-        <f t="shared" ca="1" si="4"/>
-        <v>26516965.132926498</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>24715797.963424724</v>
       </c>
       <c r="O52" s="180">
-        <f t="shared" si="5"/>
-        <v>224894950.00149262</v>
+        <f t="shared" si="8"/>
+        <v>187570981.85155547</v>
       </c>
       <c r="P52" s="180">
-        <f t="shared" ca="1" si="6"/>
-        <v>32127850.000213232</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>31261830.308592577</v>
       </c>
       <c r="Q52" s="185">
-        <f t="shared" si="7"/>
-        <v>224894950.00149262</v>
+        <f t="shared" si="10"/>
+        <v>187570981.85155547</v>
       </c>
       <c r="R52" s="185">
-        <f t="shared" ca="1" si="8"/>
-        <v>32127850.000213232</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>31261830.308592577</v>
       </c>
       <c r="T52" t="s">
         <v>70</v>
@@ -7870,48 +7870,48 @@
         <v>262953105.06301075</v>
       </c>
       <c r="H53" s="114">
-        <f>SUMIF($B$10:$B$26,$T53,C$10:C$26)+SUMIF($B$10:$B$26,$U53,C$10:C$26)</f>
-        <v>57858708.960000001</v>
+        <f t="shared" si="1"/>
+        <v>45722758.259999998</v>
       </c>
       <c r="I53" s="114">
-        <f>SUMIF($B$10:$B$26,$T53,D$10:D$26)+SUMIF($B$10:$B$26,$U53,D$10:D$26)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J53" s="114">
-        <f>SUMIF($B$10:$B$26,$T53,E$10:E$26)+SUMIF($B$10:$B$26,$U53,E$10:E$26)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K53" s="114">
-        <f t="shared" si="1"/>
-        <v>57858708.960000001</v>
+        <f t="shared" si="4"/>
+        <v>45722758.259999998</v>
       </c>
       <c r="L53" s="187">
-        <f t="shared" si="2"/>
-        <v>0.22003432492700731</v>
+        <f t="shared" si="5"/>
+        <v>0.17388179633415463</v>
       </c>
       <c r="M53" s="184">
-        <f t="shared" si="3"/>
-        <v>191946740.84986019</v>
+        <f t="shared" si="6"/>
+        <v>204082691.54986021</v>
       </c>
       <c r="N53" s="184">
-        <f t="shared" ca="1" si="4"/>
-        <v>27420962.978551455</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>34013781.924976699</v>
       </c>
       <c r="O53" s="180">
-        <f t="shared" si="5"/>
-        <v>205094396.10301074</v>
+        <f t="shared" si="8"/>
+        <v>217230346.80301076</v>
       </c>
       <c r="P53" s="180">
-        <f t="shared" ca="1" si="6"/>
-        <v>29299199.44328725</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>36205057.800501794</v>
       </c>
       <c r="Q53" s="185">
-        <f t="shared" si="7"/>
-        <v>205094396.10301074</v>
+        <f t="shared" si="10"/>
+        <v>217230346.80301076</v>
       </c>
       <c r="R53" s="185">
-        <f t="shared" ca="1" si="8"/>
-        <v>29299199.44328725</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>36205057.800501794</v>
       </c>
       <c r="T53" t="s">
         <v>169</v>
@@ -7944,48 +7944,48 @@
         <v>726671808.78586555</v>
       </c>
       <c r="H54" s="114">
-        <f>SUMIF($B$10:$B$26,$T54,C$10:C$26)+SUMIF($B$10:$B$26,$U54,C$10:C$26)</f>
-        <v>423669713.43459803</v>
+        <f t="shared" si="1"/>
+        <v>425558938.85456401</v>
       </c>
       <c r="I54" s="114">
-        <f>SUMIF($B$10:$B$26,$T54,D$10:D$26)+SUMIF($B$10:$B$26,$U54,D$10:D$26)</f>
-        <v>38215060.301464997</v>
+        <f t="shared" si="2"/>
+        <v>41590640.469465002</v>
       </c>
       <c r="J54" s="114">
-        <f>SUMIF($B$10:$B$26,$T54,E$10:E$26)+SUMIF($B$10:$B$26,$U54,E$10:E$26)</f>
-        <v>138709153.37987801</v>
+        <f t="shared" si="3"/>
+        <v>139353252.479877</v>
       </c>
       <c r="K54" s="114">
-        <f t="shared" si="1"/>
-        <v>600593927.11594105</v>
+        <f t="shared" si="4"/>
+        <v>606502831.80390596</v>
       </c>
       <c r="L54" s="187">
-        <f t="shared" si="2"/>
-        <v>0.82649955572023992</v>
+        <f t="shared" si="5"/>
+        <v>0.83463101839227838</v>
       </c>
       <c r="M54" s="184">
-        <f t="shared" si="3"/>
-        <v>89744291.230631232</v>
+        <f t="shared" si="6"/>
+        <v>83835386.542666316</v>
       </c>
       <c r="N54" s="184">
-        <f t="shared" ca="1" si="4"/>
-        <v>12820613.032947319</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>13972564.42377772</v>
       </c>
       <c r="O54" s="180">
-        <f t="shared" si="5"/>
-        <v>126077881.6699245</v>
+        <f t="shared" si="8"/>
+        <v>120168976.98195958</v>
       </c>
       <c r="P54" s="180">
-        <f t="shared" ca="1" si="6"/>
-        <v>18011125.952846356</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>20028162.830326598</v>
       </c>
       <c r="Q54" s="185">
-        <f t="shared" si="7"/>
-        <v>126077881.6699245</v>
+        <f t="shared" si="10"/>
+        <v>120168976.98195958</v>
       </c>
       <c r="R54" s="185">
-        <f t="shared" ca="1" si="8"/>
-        <v>18011125.952846356</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>20028162.830326598</v>
       </c>
       <c r="T54" t="s">
         <v>115</v>
@@ -8018,48 +8018,48 @@
         <v>537200999.57068563</v>
       </c>
       <c r="H55" s="114">
-        <f>SUMIF($B$10:$B$26,$T55,C$10:C$26)+SUMIF($B$10:$B$26,$U55,C$10:C$26)</f>
+        <f t="shared" si="1"/>
         <v>4173423.4199979999</v>
       </c>
       <c r="I55" s="114">
-        <f>SUMIF($B$10:$B$26,$T55,D$10:D$26)+SUMIF($B$10:$B$26,$U55,D$10:D$26)</f>
+        <f t="shared" si="2"/>
         <v>30250983.5</v>
       </c>
       <c r="J55" s="114">
-        <f>SUMIF($B$10:$B$26,$T55,E$10:E$26)+SUMIF($B$10:$B$26,$U55,E$10:E$26)</f>
+        <f t="shared" si="3"/>
         <v>199157658.6392</v>
       </c>
       <c r="K55" s="114">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>233582065.55919799</v>
       </c>
       <c r="L55" s="187">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.43481316257019165</v>
       </c>
       <c r="M55" s="184">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>276758884.03295338</v>
       </c>
       <c r="N55" s="184">
-        <f t="shared" ca="1" si="4"/>
-        <v>39536983.433279052</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>46126480.672158897</v>
       </c>
       <c r="O55" s="180">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>303618934.0114876</v>
       </c>
       <c r="P55" s="180">
-        <f t="shared" ca="1" si="6"/>
-        <v>43374133.430212513</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>50603155.66858127</v>
       </c>
       <c r="Q55" s="185">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>303618934.0114876</v>
       </c>
       <c r="R55" s="185">
-        <f t="shared" ca="1" si="8"/>
-        <v>43374133.430212513</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>50603155.66858127</v>
       </c>
       <c r="T55" t="s">
         <v>182</v>
@@ -8092,48 +8092,48 @@
         <v>574945988.50021839</v>
       </c>
       <c r="H56" s="114">
-        <f>SUMIF($B$10:$B$26,$T56,C$10:C$26)+SUMIF($B$10:$B$26,$U56,C$10:C$26)</f>
-        <v>157144378.35867101</v>
+        <f t="shared" si="1"/>
+        <v>172496649.28866401</v>
       </c>
       <c r="I56" s="114">
-        <f>SUMIF($B$10:$B$26,$T56,D$10:D$26)+SUMIF($B$10:$B$26,$U56,D$10:D$26)</f>
-        <v>44687069.909941003</v>
+        <f t="shared" si="2"/>
+        <v>45674574.409941003</v>
       </c>
       <c r="J56" s="114">
-        <f>SUMIF($B$10:$B$26,$T56,E$10:E$26)+SUMIF($B$10:$B$26,$U56,E$10:E$26)</f>
-        <v>126616820.968173</v>
+        <f t="shared" si="3"/>
+        <v>133534839.06817099</v>
       </c>
       <c r="K56" s="114">
-        <f t="shared" si="1"/>
-        <v>328448269.23678505</v>
+        <f t="shared" si="4"/>
+        <v>351706062.76677597</v>
       </c>
       <c r="L56" s="187">
-        <f t="shared" si="2"/>
-        <v>0.57126804222699656</v>
+        <f t="shared" si="5"/>
+        <v>0.61172017859316252</v>
       </c>
       <c r="M56" s="184">
-        <f t="shared" si="3"/>
-        <v>217750419.83842242</v>
+        <f t="shared" si="6"/>
+        <v>194492626.30843151</v>
       </c>
       <c r="N56" s="184">
-        <f t="shared" ca="1" si="4"/>
-        <v>31107202.834060345</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>32415437.718071919</v>
       </c>
       <c r="O56" s="180">
-        <f t="shared" si="5"/>
-        <v>246497719.26343334</v>
+        <f t="shared" si="8"/>
+        <v>223239925.73344243</v>
       </c>
       <c r="P56" s="180">
-        <f t="shared" ca="1" si="6"/>
-        <v>35213959.894776188</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>37206654.288907073</v>
       </c>
       <c r="Q56" s="185">
-        <f t="shared" si="7"/>
-        <v>246497719.26343334</v>
+        <f t="shared" si="10"/>
+        <v>223239925.73344243</v>
       </c>
       <c r="R56" s="185">
-        <f t="shared" ca="1" si="8"/>
-        <v>35213959.894776188</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>37206654.288907073</v>
       </c>
       <c r="T56" t="s">
         <v>225</v>
@@ -8166,48 +8166,48 @@
         <v>1109184065.5247467</v>
       </c>
       <c r="H57" s="114">
-        <f>SUMIF($B$10:$B$26,$T57,C$10:C$26)+SUMIF($B$10:$B$26,$U57,C$10:C$26)</f>
-        <v>403308935.481655</v>
+        <f t="shared" si="1"/>
+        <v>421221722.82963502</v>
       </c>
       <c r="I57" s="114">
-        <f>SUMIF($B$10:$B$26,$T57,D$10:D$26)+SUMIF($B$10:$B$26,$U57,D$10:D$26)</f>
-        <v>38062931.419927001</v>
+        <f t="shared" si="2"/>
+        <v>41281878.019927002</v>
       </c>
       <c r="J57" s="114">
-        <f>SUMIF($B$10:$B$26,$T57,E$10:E$26)+SUMIF($B$10:$B$26,$U57,E$10:E$26)</f>
-        <v>263379730.93952</v>
+        <f t="shared" si="3"/>
+        <v>275830181.54944998</v>
       </c>
       <c r="K57" s="114">
-        <f t="shared" si="1"/>
-        <v>704751597.841102</v>
+        <f t="shared" si="4"/>
+        <v>738333782.39901209</v>
       </c>
       <c r="L57" s="187">
-        <f t="shared" si="2"/>
-        <v>0.63537840088578024</v>
+        <f t="shared" si="5"/>
+        <v>0.66565487672211732</v>
       </c>
       <c r="M57" s="184">
-        <f t="shared" si="3"/>
-        <v>348973264.40740728</v>
+        <f t="shared" si="6"/>
+        <v>315391079.8494972</v>
       </c>
       <c r="N57" s="184">
-        <f t="shared" ca="1" si="4"/>
-        <v>49853323.48677247</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>52565179.974916197</v>
       </c>
       <c r="O57" s="180">
-        <f t="shared" si="5"/>
-        <v>404432467.68364465</v>
+        <f t="shared" si="8"/>
+        <v>370850283.12573457</v>
       </c>
       <c r="P57" s="180">
-        <f t="shared" ca="1" si="6"/>
-        <v>57776066.811949238</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>61808380.520955764</v>
       </c>
       <c r="Q57" s="185">
-        <f t="shared" si="7"/>
-        <v>404432467.68364465</v>
+        <f t="shared" si="10"/>
+        <v>370850283.12573457</v>
       </c>
       <c r="R57" s="185">
-        <f t="shared" ca="1" si="8"/>
-        <v>57776066.811949238</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>61808380.520955764</v>
       </c>
       <c r="T57" t="s">
         <v>120</v>
@@ -8240,48 +8240,48 @@
         <v>614580870.17702889</v>
       </c>
       <c r="H58" s="114">
-        <f>SUMIF($B$10:$B$26,$T58,C$10:C$26)+SUMIF($B$10:$B$26,$U58,C$10:C$26)</f>
-        <v>218343790.722233</v>
+        <f t="shared" si="1"/>
+        <v>226738564.12332499</v>
       </c>
       <c r="I58" s="114">
-        <f>SUMIF($B$10:$B$26,$T58,D$10:D$26)+SUMIF($B$10:$B$26,$U58,D$10:D$26)</f>
+        <f t="shared" si="2"/>
         <v>55894289.419963002</v>
       </c>
       <c r="J58" s="114">
-        <f>SUMIF($B$10:$B$26,$T58,E$10:E$26)+SUMIF($B$10:$B$26,$U58,E$10:E$26)</f>
-        <v>162558650.86619499</v>
+        <f t="shared" si="3"/>
+        <v>171252696.26218399</v>
       </c>
       <c r="K58" s="114">
-        <f t="shared" si="1"/>
-        <v>436796731.00839102</v>
+        <f t="shared" si="4"/>
+        <v>453885549.80547202</v>
       </c>
       <c r="L58" s="187">
-        <f t="shared" si="2"/>
-        <v>0.7107229531608632</v>
+        <f t="shared" si="5"/>
+        <v>0.73852860027148437</v>
       </c>
       <c r="M58" s="184">
-        <f t="shared" si="3"/>
-        <v>147055095.65978634</v>
+        <f t="shared" si="6"/>
+        <v>129966276.86270535</v>
       </c>
       <c r="N58" s="184">
-        <f t="shared" ca="1" si="4"/>
-        <v>21007870.808540907</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>21661046.143784225</v>
       </c>
       <c r="O58" s="180">
-        <f t="shared" si="5"/>
-        <v>177784139.16863787</v>
+        <f t="shared" si="8"/>
+        <v>160695320.37155688</v>
       </c>
       <c r="P58" s="180">
-        <f t="shared" ca="1" si="6"/>
-        <v>25397734.166948266</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>26782553.395259481</v>
       </c>
       <c r="Q58" s="185">
-        <f t="shared" si="7"/>
-        <v>177784139.16863787</v>
+        <f t="shared" si="10"/>
+        <v>160695320.37155688</v>
       </c>
       <c r="R58" s="185">
-        <f t="shared" ca="1" si="8"/>
-        <v>25397734.166948266</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>26782553.395259481</v>
       </c>
       <c r="T58" t="s">
         <v>125</v>
@@ -8314,48 +8314,48 @@
         <v>443846715.57642001</v>
       </c>
       <c r="H59" s="114">
-        <f>SUMIF($B$10:$B$26,$T59,C$10:C$26)+SUMIF($B$10:$B$26,$U59,C$10:C$26)</f>
-        <v>188527227.16</v>
-      </c>
-      <c r="I59" s="114">
-        <f>SUMIF($B$10:$B$26,$T59,D$10:D$26)+SUMIF($B$10:$B$26,$U59,D$10:D$26)</f>
-        <v>0</v>
-      </c>
-      <c r="J59" s="114">
-        <f>SUMIF($B$10:$B$26,$T59,E$10:E$26)+SUMIF($B$10:$B$26,$U59,E$10:E$26)</f>
-        <v>0</v>
-      </c>
-      <c r="K59" s="114">
         <f t="shared" si="1"/>
         <v>188527227.16</v>
       </c>
+      <c r="I59" s="114">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="114">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="114">
+        <f t="shared" si="4"/>
+        <v>188527227.16</v>
+      </c>
       <c r="L59" s="187">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.42475751322201688</v>
       </c>
       <c r="M59" s="184">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>233127152.63759902</v>
       </c>
       <c r="N59" s="184">
-        <f t="shared" ca="1" si="4"/>
-        <v>33303878.94822843</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>38854525.439599834</v>
       </c>
       <c r="O59" s="180">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>255319488.41642001</v>
       </c>
       <c r="P59" s="180">
-        <f t="shared" ca="1" si="6"/>
-        <v>36474212.630917147</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>42553248.069403335</v>
       </c>
       <c r="Q59" s="185">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>255319488.41642001</v>
       </c>
       <c r="R59" s="185">
-        <f t="shared" ca="1" si="8"/>
-        <v>36474212.630917147</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>42553248.069403335</v>
       </c>
       <c r="T59" t="s">
         <v>170</v>
@@ -8388,48 +8388,48 @@
         <v>579186208.19638371</v>
       </c>
       <c r="H60" s="114">
-        <f>SUMIF($B$10:$B$26,$T60,C$10:C$26)+SUMIF($B$10:$B$26,$U60,C$10:C$26)</f>
-        <v>259986756.55092999</v>
+        <f t="shared" si="1"/>
+        <v>270003598.861857</v>
       </c>
       <c r="I60" s="114">
-        <f>SUMIF($B$10:$B$26,$T60,D$10:D$26)+SUMIF($B$10:$B$26,$U60,D$10:D$26)</f>
-        <v>75962454.816541001</v>
+        <f t="shared" si="2"/>
+        <v>77822671.056532994</v>
       </c>
       <c r="J60" s="114">
-        <f>SUMIF($B$10:$B$26,$T60,E$10:E$26)+SUMIF($B$10:$B$26,$U60,E$10:E$26)</f>
-        <v>85307067.912571996</v>
+        <f t="shared" si="3"/>
+        <v>88127833.698561996</v>
       </c>
       <c r="K60" s="114">
-        <f t="shared" si="1"/>
-        <v>421256279.28004301</v>
+        <f t="shared" si="4"/>
+        <v>435954103.61695194</v>
       </c>
       <c r="L60" s="187">
-        <f t="shared" si="2"/>
-        <v>0.72732443093190569</v>
+        <f t="shared" si="5"/>
+        <v>0.75270111312652965</v>
       </c>
       <c r="M60" s="184">
-        <f t="shared" si="3"/>
-        <v>128970618.50652146</v>
+        <f t="shared" si="6"/>
+        <v>114272794.16961253</v>
       </c>
       <c r="N60" s="184">
-        <f t="shared" ca="1" si="4"/>
-        <v>18424374.07236021</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>19045465.694935422</v>
       </c>
       <c r="O60" s="180">
-        <f t="shared" si="5"/>
-        <v>157929928.91634071</v>
+        <f t="shared" si="8"/>
+        <v>143232104.57943177</v>
       </c>
       <c r="P60" s="180">
-        <f t="shared" ca="1" si="6"/>
-        <v>22561418.416620102</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>23872017.429905295</v>
       </c>
       <c r="Q60" s="185">
-        <f t="shared" si="7"/>
-        <v>157929928.91634071</v>
+        <f t="shared" si="10"/>
+        <v>143232104.57943177</v>
       </c>
       <c r="R60" s="185">
-        <f t="shared" ca="1" si="8"/>
-        <v>22561418.416620102</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>23872017.429905295</v>
       </c>
       <c r="T60" t="s">
         <v>220</v>
@@ -8462,48 +8462,48 @@
         <v>716592801.55318153</v>
       </c>
       <c r="H61" s="114">
-        <f>SUMIF($B$10:$B$26,$T61,C$10:C$26)+SUMIF($B$10:$B$26,$U61,C$10:C$26)</f>
-        <v>386015669.137429</v>
+        <f t="shared" si="1"/>
+        <v>402608462.21627998</v>
       </c>
       <c r="I61" s="114">
-        <f>SUMIF($B$10:$B$26,$T61,D$10:D$26)+SUMIF($B$10:$B$26,$U61,D$10:D$26)</f>
-        <v>55017470.924923003</v>
+        <f t="shared" si="2"/>
+        <v>54954295.924923003</v>
       </c>
       <c r="J61" s="114">
-        <f>SUMIF($B$10:$B$26,$T61,E$10:E$26)+SUMIF($B$10:$B$26,$U61,E$10:E$26)</f>
-        <v>174500614.40990701</v>
+        <f t="shared" si="3"/>
+        <v>181079758.51990199</v>
       </c>
       <c r="K61" s="114">
-        <f t="shared" si="1"/>
-        <v>615533754.47225904</v>
+        <f t="shared" si="4"/>
+        <v>638642516.66110492</v>
       </c>
       <c r="L61" s="187">
-        <f t="shared" si="2"/>
-        <v>0.8589728408352949</v>
+        <f t="shared" si="5"/>
+        <v>0.89122094901996918</v>
       </c>
       <c r="M61" s="184">
-        <f t="shared" si="3"/>
-        <v>65229407.003263354</v>
+        <f t="shared" si="6"/>
+        <v>42120644.814417481</v>
       </c>
       <c r="N61" s="184">
-        <f t="shared" ca="1" si="4"/>
-        <v>9318486.7147519086</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>7020107.4690695805</v>
       </c>
       <c r="O61" s="180">
-        <f t="shared" si="5"/>
-        <v>101059047.08092248</v>
+        <f t="shared" si="8"/>
+        <v>77950284.892076612</v>
       </c>
       <c r="P61" s="180">
-        <f t="shared" ca="1" si="6"/>
-        <v>14437006.725846069</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>12991714.148679435</v>
       </c>
       <c r="Q61" s="185">
-        <f t="shared" si="7"/>
-        <v>101059047.08092248</v>
+        <f t="shared" si="10"/>
+        <v>77950284.892076612</v>
       </c>
       <c r="R61" s="185">
-        <f t="shared" ca="1" si="8"/>
-        <v>14437006.725846069</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>12991714.148679435</v>
       </c>
       <c r="T61" t="s">
         <v>126</v>
@@ -8536,48 +8536,48 @@
         <v>477023257.56080151</v>
       </c>
       <c r="H62" s="114">
-        <f>SUMIF($B$10:$B$26,$T62,C$10:C$26)+SUMIF($B$10:$B$26,$U62,C$10:C$26)</f>
-        <v>122534293.762722</v>
+        <f t="shared" si="1"/>
+        <v>122291455.94272</v>
       </c>
       <c r="I62" s="114">
-        <f>SUMIF($B$10:$B$26,$T62,D$10:D$26)+SUMIF($B$10:$B$26,$U62,D$10:D$26)</f>
-        <v>33718196.818899997</v>
+        <f t="shared" si="2"/>
+        <v>36845696.872796997</v>
       </c>
       <c r="J62" s="114">
-        <f>SUMIF($B$10:$B$26,$T62,E$10:E$26)+SUMIF($B$10:$B$26,$U62,E$10:E$26)</f>
-        <v>175612225.567045</v>
+        <f t="shared" si="3"/>
+        <v>179872333.71704</v>
       </c>
       <c r="K62" s="114">
-        <f t="shared" si="1"/>
-        <v>331864716.14866698</v>
+        <f t="shared" si="4"/>
+        <v>339009486.53255701</v>
       </c>
       <c r="L62" s="187">
-        <f t="shared" si="2"/>
-        <v>0.69569923664857669</v>
+        <f t="shared" si="5"/>
+        <v>0.71067706062391889</v>
       </c>
       <c r="M62" s="184">
-        <f t="shared" si="3"/>
-        <v>121307378.53409445</v>
+        <f t="shared" si="6"/>
+        <v>114162608.15020442</v>
       </c>
       <c r="N62" s="184">
-        <f t="shared" ca="1" si="4"/>
-        <v>17329625.504870635</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>19027101.358367402</v>
       </c>
       <c r="O62" s="180">
-        <f t="shared" si="5"/>
-        <v>145158541.41213453</v>
+        <f t="shared" si="8"/>
+        <v>138013771.0282445</v>
       </c>
       <c r="P62" s="180">
-        <f t="shared" ca="1" si="6"/>
-        <v>20736934.487447791</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>23002295.171374083</v>
       </c>
       <c r="Q62" s="185">
-        <f t="shared" si="7"/>
-        <v>145158541.41213453</v>
+        <f t="shared" si="10"/>
+        <v>138013771.0282445</v>
       </c>
       <c r="R62" s="185">
-        <f t="shared" ca="1" si="8"/>
-        <v>20736934.487447791</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>23002295.171374083</v>
       </c>
       <c r="T62" t="s">
         <v>112</v>
@@ -8610,48 +8610,48 @@
         <v>978973997.29380655</v>
       </c>
       <c r="H63" s="114">
-        <f>SUMIF($B$10:$B$26,$T63,C$10:C$26)+SUMIF($B$10:$B$26,$U63,C$10:C$26)</f>
-        <v>399272594.47329497</v>
+        <f t="shared" si="1"/>
+        <v>413271522.44322699</v>
       </c>
       <c r="I63" s="114">
-        <f>SUMIF($B$10:$B$26,$T63,D$10:D$26)+SUMIF($B$10:$B$26,$U63,D$10:D$26)</f>
-        <v>254167394.92625701</v>
+        <f t="shared" si="2"/>
+        <v>260467539.04622999</v>
       </c>
       <c r="J63" s="114">
-        <f>SUMIF($B$10:$B$26,$T63,E$10:E$26)+SUMIF($B$10:$B$26,$U63,E$10:E$26)</f>
-        <v>229102206.125873</v>
+        <f t="shared" si="3"/>
+        <v>238566169.62585801</v>
       </c>
       <c r="K63" s="114">
-        <f t="shared" si="1"/>
-        <v>882542195.52542496</v>
+        <f t="shared" si="4"/>
+        <v>912305231.11531496</v>
       </c>
       <c r="L63" s="187">
-        <f t="shared" si="2"/>
-        <v>0.90149707547396607</v>
+        <f t="shared" si="5"/>
+        <v>0.93189934935679075</v>
       </c>
       <c r="M63" s="184">
-        <f t="shared" si="3"/>
-        <v>47483101.903691173</v>
+        <f t="shared" si="6"/>
+        <v>17720066.313801169</v>
       </c>
       <c r="N63" s="184">
-        <f t="shared" ca="1" si="4"/>
-        <v>6783300.2719558822</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>2953344.3856335282</v>
       </c>
       <c r="O63" s="180">
-        <f t="shared" si="5"/>
-        <v>96431801.768381596</v>
+        <f t="shared" si="8"/>
+        <v>66668766.178491592</v>
       </c>
       <c r="P63" s="180">
-        <f t="shared" ca="1" si="6"/>
-        <v>13775971.681197371</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>11111461.029748598</v>
       </c>
       <c r="Q63" s="185">
-        <f t="shared" si="7"/>
-        <v>96431801.768381596</v>
+        <f t="shared" si="10"/>
+        <v>66668766.178491592</v>
       </c>
       <c r="R63" s="185">
-        <f t="shared" ca="1" si="8"/>
-        <v>13775971.681197371</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>11111461.029748598</v>
       </c>
       <c r="T63" t="s">
         <v>127</v>
@@ -8684,48 +8684,48 @@
         <v>536914321.43439078</v>
       </c>
       <c r="H64" s="114">
-        <f>SUMIF($B$10:$B$26,$T64,C$10:C$26)+SUMIF($B$10:$B$26,$U64,C$10:C$26)</f>
-        <v>106404263.40502599</v>
+        <f t="shared" si="1"/>
+        <v>107777515.806016</v>
       </c>
       <c r="I64" s="114">
-        <f>SUMIF($B$10:$B$26,$T64,D$10:D$26)+SUMIF($B$10:$B$26,$U64,D$10:D$26)</f>
-        <v>146124139.012555</v>
+        <f t="shared" si="2"/>
+        <v>146718841.732555</v>
       </c>
       <c r="J64" s="114">
-        <f>SUMIF($B$10:$B$26,$T64,E$10:E$26)+SUMIF($B$10:$B$26,$U64,E$10:E$26)</f>
-        <v>128456685.06884199</v>
+        <f t="shared" si="3"/>
+        <v>128506297.718842</v>
       </c>
       <c r="K64" s="114">
-        <f t="shared" si="1"/>
-        <v>380985087.48642302</v>
+        <f t="shared" si="4"/>
+        <v>383002655.25741303</v>
       </c>
       <c r="L64" s="187">
-        <f t="shared" si="2"/>
-        <v>0.70958265085685213</v>
+        <f t="shared" si="5"/>
+        <v>0.71334035984401423</v>
       </c>
       <c r="M64" s="184">
-        <f t="shared" si="3"/>
-        <v>129083517.87624818</v>
+        <f t="shared" si="6"/>
+        <v>127065950.10525817</v>
       </c>
       <c r="N64" s="184">
-        <f t="shared" ca="1" si="4"/>
-        <v>18440502.55374974</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>21177658.350876361</v>
       </c>
       <c r="O64" s="180">
-        <f t="shared" si="5"/>
-        <v>155929233.94796777</v>
+        <f t="shared" si="8"/>
+        <v>153911666.17697775</v>
       </c>
       <c r="P64" s="180">
-        <f t="shared" ca="1" si="6"/>
-        <v>22275604.849709682</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>25651944.362829626</v>
       </c>
       <c r="Q64" s="185">
-        <f t="shared" si="7"/>
-        <v>155929233.94796777</v>
+        <f t="shared" si="10"/>
+        <v>153911666.17697775</v>
       </c>
       <c r="R64" s="185">
-        <f t="shared" ca="1" si="8"/>
-        <v>22275604.849709682</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>25651944.362829626</v>
       </c>
       <c r="T64" t="s">
         <v>122</v>
@@ -8740,64 +8740,64 @@
       </c>
       <c r="C65" s="58"/>
       <c r="D65" s="134">
-        <f t="shared" ref="D65:K65" si="9">SUM(D51:D64)</f>
+        <f t="shared" ref="D65:K65" si="12">SUM(D51:D64)</f>
         <v>4511786033.6993961</v>
       </c>
       <c r="E65" s="134">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1401365310.515415</v>
       </c>
       <c r="F65" s="134">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2944814196.3286853</v>
       </c>
       <c r="G65" s="134">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>8857965540.5434952</v>
       </c>
       <c r="H65" s="135">
-        <f t="shared" si="9"/>
-        <v>3122129670.9968972</v>
+        <f t="shared" si="12"/>
+        <v>3215155706.6509838</v>
       </c>
       <c r="I65" s="135">
-        <f t="shared" si="9"/>
-        <v>897387187.46542609</v>
+        <f t="shared" si="12"/>
+        <v>923636133.94727707</v>
       </c>
       <c r="J65" s="135">
-        <f t="shared" si="9"/>
-        <v>2114692130.1762149</v>
+        <f t="shared" si="12"/>
+        <v>2190086878.2080727</v>
       </c>
       <c r="K65" s="135">
-        <f t="shared" si="9"/>
-        <v>6134208988.6385384</v>
+        <f t="shared" si="12"/>
+        <v>6328878718.8063326</v>
       </c>
       <c r="L65" s="189">
-        <f t="shared" si="2"/>
-        <v>0.69250765997698427</v>
+        <f t="shared" si="5"/>
+        <v>0.71448445919535764</v>
       </c>
       <c r="M65" s="181">
         <f>SUM(M51:M64)</f>
-        <v>2280858274.8777828</v>
+        <v>2086188544.7099864</v>
       </c>
       <c r="N65" s="181">
-        <f t="shared" ca="1" si="4"/>
-        <v>325836896.41111183</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>347698090.78499776</v>
       </c>
       <c r="O65" s="181">
         <f>SUM(O51:O64)</f>
-        <v>2723756551.9049587</v>
+        <v>2529086821.7371621</v>
       </c>
       <c r="P65" s="181">
-        <f t="shared" ca="1" si="6"/>
-        <v>389108078.84356552</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>421514470.289527</v>
       </c>
       <c r="Q65" s="186">
         <f>SUM(Q51:Q64)</f>
-        <v>2723756551.9049587</v>
+        <v>2529086821.7371621</v>
       </c>
       <c r="R65" s="186">
-        <f t="shared" ca="1" si="8"/>
-        <v>389108078.84356552</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>421514470.289527</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8806,21 +8806,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="269" t="s">
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -8882,35 +8882,35 @@
       </c>
       <c r="E69" s="114">
         <f>IFERROR($C$31,0)</f>
-        <v>203469688.08525699</v>
+        <v>230771202.18516701</v>
       </c>
       <c r="F69" s="187">
-        <f t="shared" ref="F69:F74" si="10">IFERROR(E69/D69,0)</f>
-        <v>0.79400480165887521</v>
+        <f t="shared" ref="F69:F74" si="13">IFERROR(E69/D69,0)</f>
+        <v>0.90054417610762749</v>
       </c>
       <c r="G69" s="184">
         <f>D69*$H$40-E69</f>
-        <v>39974940.054459393</v>
+        <v>12673425.954549372</v>
       </c>
       <c r="H69" s="184">
-        <f t="shared" ref="H69:H74" ca="1" si="11">IFERROR(G69/$C$3,0)</f>
-        <v>5710705.7220656276</v>
+        <f t="shared" ref="H69:H74" ca="1" si="14">IFERROR(G69/$C$3,0)</f>
+        <v>2112237.659091562</v>
       </c>
       <c r="I69" s="204">
         <f>D69*$J$40-E69</f>
-        <v>52787815.219707638</v>
+        <v>25486301.119797617</v>
       </c>
       <c r="J69" s="204">
-        <f t="shared" ref="J69:J74" ca="1" si="12">IFERROR(I69/$C$3,0)</f>
-        <v>7541116.4599582339</v>
+        <f t="shared" ref="J69:J74" ca="1" si="15">IFERROR(I69/$C$3,0)</f>
+        <v>4247716.8532996029</v>
       </c>
       <c r="K69" s="185">
         <f>D69*$L$40-E69</f>
-        <v>52787815.219707638</v>
+        <v>25486301.119797617</v>
       </c>
       <c r="L69" s="185">
-        <f t="shared" ref="L69:L74" ca="1" si="13">IFERROR(K69/$C$3,0)</f>
-        <v>7541116.4599582339</v>
+        <f t="shared" ref="L69:L74" ca="1" si="16">IFERROR(K69/$C$3,0)</f>
+        <v>4247716.8532996029</v>
       </c>
     </row>
     <row r="70" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8926,35 +8926,35 @@
       </c>
       <c r="E70" s="114">
         <f>IFERROR($C$32,0)</f>
-        <v>415017182.90095901</v>
+        <v>427130336.43894702</v>
       </c>
       <c r="F70" s="187">
-        <f t="shared" si="10"/>
-        <v>1.038689638660881</v>
+        <f t="shared" si="13"/>
+        <v>1.0690059908260372</v>
       </c>
       <c r="G70" s="184">
         <f>D70*$H$40-E70</f>
-        <v>-35436691.211242676</v>
+        <v>-47549844.749230683</v>
       </c>
       <c r="H70" s="184">
-        <f t="shared" ca="1" si="11"/>
-        <v>-5062384.4587489534</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>-7924974.1248717802</v>
       </c>
       <c r="I70" s="204">
         <f>D70*$J$40-E70</f>
-        <v>-15458770.595994413</v>
+        <v>-27571924.13398242</v>
       </c>
       <c r="J70" s="204">
-        <f t="shared" ca="1" si="12"/>
-        <v>-2208395.7994277733</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>-4595320.6889970703</v>
       </c>
       <c r="K70" s="185">
         <f>D70*$L$40-E70</f>
-        <v>-15458770.595994413</v>
+        <v>-27571924.13398242</v>
       </c>
       <c r="L70" s="185">
-        <f t="shared" ca="1" si="13"/>
-        <v>-2208395.7994277733</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>-4595320.6889970703</v>
       </c>
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.25">
@@ -8970,35 +8970,35 @@
       </c>
       <c r="E71" s="114">
         <f>M21</f>
-        <v>932747039.34663296</v>
+        <v>934135147.50660896</v>
       </c>
       <c r="F71" s="187">
-        <f t="shared" si="10"/>
-        <v>0.85998411347698056</v>
+        <f t="shared" si="13"/>
+        <v>0.86126393631748333</v>
       </c>
       <c r="G71" s="184">
         <f>D71*$H$40-E71</f>
-        <v>97632096.143083334</v>
+        <v>96243987.983107328</v>
       </c>
       <c r="H71" s="184">
-        <f t="shared" ca="1" si="11"/>
-        <v>13947442.306154761</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>16040664.663851222</v>
       </c>
       <c r="I71" s="204">
         <f>D71*$J$40-E71</f>
-        <v>151862576.95833158</v>
+        <v>150474468.79835558</v>
       </c>
       <c r="J71" s="204">
-        <f t="shared" ca="1" si="12"/>
-        <v>21694653.851190228</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>25079078.133059263</v>
       </c>
       <c r="K71" s="185">
         <f>D71*$L$40-E71</f>
-        <v>151862576.95833158</v>
+        <v>150474468.79835558</v>
       </c>
       <c r="L71" s="185">
-        <f t="shared" ca="1" si="13"/>
-        <v>21694653.851190228</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>25079078.133059263</v>
       </c>
     </row>
     <row r="72" spans="2:21" hidden="1" x14ac:dyDescent="0.25">
@@ -9017,7 +9017,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="187">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G72" s="184">
@@ -9025,7 +9025,7 @@
         <v>0</v>
       </c>
       <c r="H72" s="184">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="14"/>
         <v>0</v>
       </c>
       <c r="I72" s="204">
@@ -9033,7 +9033,7 @@
         <v>0</v>
       </c>
       <c r="J72" s="204">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="15"/>
         <v>0</v>
       </c>
       <c r="K72" s="185">
@@ -9041,7 +9041,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="185">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -9061,7 +9061,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="187">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G73" s="184">
@@ -9069,7 +9069,7 @@
         <v>0</v>
       </c>
       <c r="H73" s="184">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ca="1" si="14"/>
         <v>0</v>
       </c>
       <c r="I73" s="204">
@@ -9077,7 +9077,7 @@
         <v>0</v>
       </c>
       <c r="J73" s="204">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="15"/>
         <v>0</v>
       </c>
       <c r="K73" s="185">
@@ -9085,7 +9085,7 @@
         <v>0</v>
       </c>
       <c r="L73" s="185">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -9100,35 +9100,35 @@
       </c>
       <c r="E74" s="115">
         <f>SUM(E69:E73)</f>
-        <v>1551233910.332849</v>
+        <v>1592036686.130723</v>
       </c>
       <c r="F74" s="177">
-        <f t="shared" si="10"/>
-        <v>0.89129576755065898</v>
+        <f t="shared" si="13"/>
+        <v>0.91473990523403403</v>
       </c>
       <c r="G74" s="181">
         <f>SUM(G69:G73)</f>
-        <v>102170344.98630005</v>
+        <v>61367569.188426018</v>
       </c>
       <c r="H74" s="181">
-        <f t="shared" ca="1" si="11"/>
-        <v>14595763.569471436</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>10227928.198071003</v>
       </c>
       <c r="I74" s="186">
         <f>SUM(I69:I73)</f>
-        <v>189191621.58204481</v>
+        <v>148388845.78417078</v>
       </c>
       <c r="J74" s="186">
-        <f t="shared" ca="1" si="12"/>
-        <v>27027374.511720687</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>24731474.297361795</v>
       </c>
       <c r="K74" s="186">
         <f>SUM(K69:K73)</f>
-        <v>189191621.58204481</v>
+        <v>148388845.78417078</v>
       </c>
       <c r="L74" s="186">
-        <f t="shared" ca="1" si="13"/>
-        <v>27027374.511720687</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>24731474.297361795</v>
       </c>
     </row>
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9141,10 +9141,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -9172,15 +9172,15 @@
         <v>68</v>
       </c>
       <c r="D80" s="131">
-        <f>SUMIF($B$10:$B$26,$T80,$F$10:$F$26)+SUMIF($B$10:$B$26,$U80,$F$10:$F$26)</f>
-        <v>340035346.74985999</v>
+        <f t="shared" ref="D80:D93" si="17">SUMIF($B$10:$B$26,$T80,$F$10:$F$26)+SUMIF($B$10:$B$26,$U80,$F$10:$F$26)</f>
+        <v>345823522.47986001</v>
       </c>
       <c r="T80" t="str">
-        <f t="shared" ref="T80:U93" si="14">T51</f>
+        <f t="shared" ref="T80:U93" si="18">T51</f>
         <v>Picrom Stalyon</v>
       </c>
       <c r="U80" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9192,15 +9192,15 @@
         <v>70</v>
       </c>
       <c r="D81" s="132">
-        <f>SUMIF($B$10:$B$26,$T81,$F$10:$F$26)+SUMIF($B$10:$B$26,$U81,$F$10:$F$26)</f>
-        <v>131602717.80000001</v>
+        <f t="shared" si="17"/>
+        <v>136536051.15000001</v>
       </c>
       <c r="T81" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>I MADE LUIH</v>
       </c>
       <c r="U81" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>I Made Luih (Sanur)</v>
       </c>
     </row>
@@ -9212,15 +9212,15 @@
         <v>173</v>
       </c>
       <c r="D82" s="132">
-        <f>SUMIF($B$10:$B$26,$T82,$F$10:$F$26)+SUMIF($B$10:$B$26,$U82,$F$10:$F$26)</f>
+        <f t="shared" si="17"/>
         <v>7027026.8399999999</v>
       </c>
       <c r="T82" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>NN Made Luih</v>
       </c>
       <c r="U82" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9232,15 +9232,15 @@
         <v>72</v>
       </c>
       <c r="D83" s="131">
-        <f>SUMIF($B$10:$B$26,$T83,$F$10:$F$26)+SUMIF($B$10:$B$26,$U83,$F$10:$F$26)</f>
-        <v>342828960.75976998</v>
+        <f t="shared" si="17"/>
+        <v>346086641.02977002</v>
       </c>
       <c r="T83" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Juni</v>
       </c>
       <c r="U83" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9252,15 +9252,15 @@
         <v>74</v>
       </c>
       <c r="D84" s="132">
-        <f>SUMIF($B$10:$B$26,$T84,$F$10:$F$26)+SUMIF($B$10:$B$26,$U84,$F$10:$F$26)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="T84" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>FIB</v>
       </c>
       <c r="U84" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9272,15 +9272,15 @@
         <v>74</v>
       </c>
       <c r="D85" s="131">
-        <f>SUMIF($B$10:$B$26,$T85,$F$10:$F$26)+SUMIF($B$10:$B$26,$U85,$F$10:$F$26)</f>
-        <v>56855405.259999998</v>
+        <f t="shared" si="17"/>
+        <v>64062612.359999999</v>
       </c>
       <c r="T85" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Ronald</v>
       </c>
       <c r="U85" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9292,15 +9292,15 @@
         <v>77</v>
       </c>
       <c r="D86" s="132">
-        <f>SUMIF($B$10:$B$26,$T86,$F$10:$F$26)+SUMIF($B$10:$B$26,$U86,$F$10:$F$26)</f>
-        <v>830718820.72996902</v>
+        <f t="shared" si="17"/>
+        <v>858628819.27996898</v>
       </c>
       <c r="T86" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Monica</v>
       </c>
       <c r="U86" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9312,15 +9312,15 @@
         <v>79</v>
       </c>
       <c r="D87" s="131">
-        <f>SUMIF($B$10:$B$26,$T87,$F$10:$F$26)+SUMIF($B$10:$B$26,$U87,$F$10:$F$26)</f>
-        <v>257288564.68950501</v>
+        <f t="shared" si="17"/>
+        <v>260869645.919505</v>
       </c>
       <c r="T87" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Sujana</v>
       </c>
       <c r="U87" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9332,15 +9332,15 @@
         <v>174</v>
       </c>
       <c r="D88" s="132">
-        <f>SUMIF($B$10:$B$26,$T88,$F$10:$F$26)+SUMIF($B$10:$B$26,$U88,$F$10:$F$26)</f>
+        <f t="shared" si="17"/>
         <v>9813783.5199999996</v>
       </c>
       <c r="T88" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>NN Sujana</v>
       </c>
       <c r="U88" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9352,15 +9352,15 @@
         <v>81</v>
       </c>
       <c r="D89" s="132">
-        <f>SUMIF($B$10:$B$26,$T89,$F$10:$F$26)+SUMIF($B$10:$B$26,$U89,$F$10:$F$26)</f>
-        <v>39783784.579999998</v>
+        <f t="shared" si="17"/>
+        <v>49513514.579999998</v>
       </c>
       <c r="T89" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Wahyu</v>
       </c>
       <c r="U89" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9372,15 +9372,15 @@
         <v>83</v>
       </c>
       <c r="D90" s="131">
-        <f>SUMIF($B$10:$B$26,$T90,$F$10:$F$26)+SUMIF($B$10:$B$26,$U90,$F$10:$F$26)</f>
-        <v>483452299.52950501</v>
+        <f t="shared" si="17"/>
+        <v>514008155.46949601</v>
       </c>
       <c r="T90" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Taufik</v>
       </c>
       <c r="U90" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9392,15 +9392,15 @@
         <v>85</v>
       </c>
       <c r="D91" s="132">
-        <f>SUMIF($B$10:$B$26,$T91,$F$10:$F$26)+SUMIF($B$10:$B$26,$U91,$F$10:$F$26)</f>
-        <v>126163149.179938</v>
+        <f t="shared" si="17"/>
+        <v>137341527.88993299</v>
       </c>
       <c r="T91" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Dewi Kristiani</v>
       </c>
       <c r="U91" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9412,15 +9412,15 @@
         <v>87</v>
       </c>
       <c r="D92" s="131">
-        <f>SUMIF($B$10:$B$26,$T92,$F$10:$F$26)+SUMIF($B$10:$B$26,$U92,$F$10:$F$26)</f>
+        <f t="shared" si="17"/>
         <v>18013297.6536</v>
       </c>
       <c r="T92" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Wira</v>
       </c>
       <c r="U92" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>n/a</v>
       </c>
     </row>
@@ -9432,15 +9432,15 @@
         <v>89</v>
       </c>
       <c r="D93" s="132">
-        <f>SUMIF($B$10:$B$26,$T93,$F$10:$F$26)+SUMIF($B$10:$B$26,$U93,$F$10:$F$26)</f>
-        <v>141271894.81800002</v>
+        <f t="shared" si="17"/>
+        <v>148515138.21799999</v>
       </c>
       <c r="T93" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Ni Ketut Sriasih (GT)</v>
       </c>
       <c r="U93" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Ni Ketut Sriasih (MT)</v>
       </c>
     </row>
@@ -9451,12 +9451,18 @@
       <c r="C94" s="58"/>
       <c r="D94" s="120">
         <f>SUM(D80:D93)</f>
-        <v>2784855052.1101465</v>
+        <v>2896239736.3901334</v>
       </c>
     </row>
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -9471,12 +9477,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -10104,11 +10104,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>163</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -10428,33 +10428,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -10463,49 +10463,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -10530,13 +10530,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -11652,21 +11652,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="269" t="s">
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -11987,10 +11987,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -12303,6 +12303,12 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -12317,12 +12323,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -12950,11 +12950,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>175</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -13274,33 +13274,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -13309,49 +13309,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -13376,13 +13376,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -14498,21 +14498,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="269" t="s">
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -14833,10 +14833,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -15149,6 +15149,12 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -15163,12 +15169,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -15796,11 +15796,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="259" t="s">
+      <c r="B40" s="269" t="s">
         <v>177</v>
       </c>
-      <c r="C40" s="260"/>
-      <c r="D40" s="261"/>
+      <c r="C40" s="270"/>
+      <c r="D40" s="271"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -16120,33 +16120,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="263"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="273"/>
+      <c r="L48" s="283"/>
+      <c r="M48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="270"/>
-      <c r="Q48" s="270"/>
-      <c r="R48" s="271"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="261"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="262"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="284" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="284" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="253" t="s">
@@ -16155,49 +16155,49 @@
       <c r="E49" s="254"/>
       <c r="F49" s="254"/>
       <c r="G49" s="255"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="285" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="286"/>
+      <c r="J49" s="286"/>
+      <c r="K49" s="287"/>
+      <c r="L49" s="288" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="272" t="str">
+      <c r="M49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="272" t="str">
+      <c r="N49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="274" t="str">
+      <c r="O49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="274" t="str">
+      <c r="P49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="276" t="str">
+      <c r="Q49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="276" t="str">
+      <c r="R49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="268"/>
-      <c r="C50" s="268"/>
+      <c r="B50" s="259"/>
+      <c r="C50" s="259"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -16222,13 +16222,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="273"/>
-      <c r="N50" s="273"/>
-      <c r="O50" s="275"/>
-      <c r="P50" s="275"/>
-      <c r="Q50" s="277"/>
-      <c r="R50" s="277"/>
+      <c r="L50" s="289"/>
+      <c r="M50" s="264"/>
+      <c r="N50" s="264"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="268"/>
+      <c r="R50" s="268"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -17330,21 +17330,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="283" t="s">
+      <c r="B67" s="290" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="284"/>
-      <c r="D67" s="284"/>
-      <c r="E67" s="284"/>
+      <c r="C67" s="291"/>
+      <c r="D67" s="291"/>
+      <c r="E67" s="291"/>
       <c r="F67" s="293"/>
-      <c r="G67" s="269" t="s">
+      <c r="G67" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="270"/>
-      <c r="I67" s="270"/>
-      <c r="J67" s="270"/>
-      <c r="K67" s="270"/>
-      <c r="L67" s="271"/>
+      <c r="H67" s="261"/>
+      <c r="I67" s="261"/>
+      <c r="J67" s="261"/>
+      <c r="K67" s="261"/>
+      <c r="L67" s="262"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -17665,10 +17665,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -17981,6 +17981,12 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -17995,12 +18001,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -25780,11 +25780,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="259" t="s">
+      <c r="B41" s="269" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="260"/>
-      <c r="D41" s="261"/>
+      <c r="C41" s="270"/>
+      <c r="D41" s="271"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -26055,59 +26055,59 @@
       </c>
     </row>
     <row r="48" spans="2:19" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="270"/>
-      <c r="M48" s="270"/>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="271"/>
+      <c r="L48" s="261"/>
+      <c r="M48" s="261"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
       <c r="Q48"/>
       <c r="R48"/>
     </row>
     <row r="49" spans="2:18" s="139" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="267" t="s">
+      <c r="B49" s="277" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="267" t="s">
+      <c r="C49" s="277" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="264" t="s">
+      <c r="D49" s="274" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="265"/>
-      <c r="F49" s="266"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
       <c r="G49" s="140" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="140"/>
       <c r="I49" s="140"/>
-      <c r="J49" s="264" t="s">
+      <c r="J49" s="274" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="272" t="str">
+      <c r="K49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="272" t="str">
+      <c r="L49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
@@ -26122,7 +26122,7 @@
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="276" t="str">
+      <c r="P49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -26131,8 +26131,8 @@
       <c r="R49"/>
     </row>
     <row r="50" spans="2:18" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="267"/>
-      <c r="C50" s="267"/>
+      <c r="B50" s="277"/>
+      <c r="C50" s="277"/>
       <c r="D50" s="141" t="s">
         <v>149</v>
       </c>
@@ -26151,13 +26151,13 @@
       <c r="I50" s="142" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="264"/>
-      <c r="K50" s="273"/>
-      <c r="L50" s="273"/>
-      <c r="M50" s="275"/>
+      <c r="J50" s="274"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="266"/>
       <c r="N50" s="188"/>
       <c r="O50" s="183"/>
-      <c r="P50" s="277"/>
+      <c r="P50" s="268"/>
       <c r="Q50"/>
       <c r="R50"/>
     </row>
@@ -27498,10 +27498,10 @@
       <c r="I77"/>
     </row>
     <row r="78" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -27700,6 +27700,13 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="J49:J50"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
     <mergeCell ref="K48:P48"/>
@@ -27709,13 +27716,6 @@
     <mergeCell ref="P49:P50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="J49:J50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="26" priority="8">
@@ -28755,25 +28755,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="270"/>
-      <c r="M48" s="270"/>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="271"/>
+      <c r="L48" s="261"/>
+      <c r="M48" s="261"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -28795,32 +28795,32 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="272" t="str">
+      <c r="K49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="272" t="str">
+      <c r="L49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="274" t="str">
+      <c r="N49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="276" t="str">
+      <c r="O49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="276" t="str">
+      <c r="P49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -28848,12 +28848,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="273"/>
-      <c r="L50" s="273"/>
-      <c r="M50" s="275"/>
-      <c r="N50" s="275"/>
-      <c r="O50" s="277"/>
-      <c r="P50" s="277"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="266"/>
+      <c r="N50" s="266"/>
+      <c r="O50" s="268"/>
+      <c r="P50" s="268"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="167" t="s">
@@ -30090,10 +30090,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -30287,6 +30287,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -30294,17 +30305,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -31062,11 +31062,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="259" t="s">
+      <c r="B41" s="269" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="260"/>
-      <c r="D41" s="261"/>
+      <c r="C41" s="270"/>
+      <c r="D41" s="271"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -31341,25 +31341,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="270"/>
-      <c r="M48" s="270"/>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="271"/>
+      <c r="L48" s="261"/>
+      <c r="M48" s="261"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -31381,32 +31381,32 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="272" t="str">
+      <c r="K49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="272" t="str">
+      <c r="L49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="274" t="str">
+      <c r="N49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="276" t="str">
+      <c r="O49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="276" t="str">
+      <c r="P49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -31434,12 +31434,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="273"/>
-      <c r="L50" s="273"/>
-      <c r="M50" s="275"/>
-      <c r="N50" s="275"/>
-      <c r="O50" s="277"/>
-      <c r="P50" s="277"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="266"/>
+      <c r="N50" s="266"/>
+      <c r="O50" s="268"/>
+      <c r="P50" s="268"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -32676,10 +32676,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -32860,6 +32860,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -32867,17 +32878,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -33656,11 +33656,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" s="191" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="259" t="s">
+      <c r="B41" s="269" t="s">
         <v>189</v>
       </c>
-      <c r="C41" s="260"/>
-      <c r="D41" s="261"/>
+      <c r="C41" s="270"/>
+      <c r="D41" s="271"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -33935,25 +33935,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="262" t="s">
+      <c r="B48" s="272" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="263"/>
-      <c r="D48" s="263"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="263"/>
-      <c r="J48" s="263"/>
-      <c r="K48" s="269" t="s">
+      <c r="C48" s="273"/>
+      <c r="D48" s="273"/>
+      <c r="E48" s="273"/>
+      <c r="F48" s="273"/>
+      <c r="G48" s="273"/>
+      <c r="H48" s="273"/>
+      <c r="I48" s="273"/>
+      <c r="J48" s="273"/>
+      <c r="K48" s="260" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="270"/>
-      <c r="M48" s="270"/>
-      <c r="N48" s="270"/>
-      <c r="O48" s="270"/>
-      <c r="P48" s="271"/>
+      <c r="L48" s="261"/>
+      <c r="M48" s="261"/>
+      <c r="N48" s="261"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
     </row>
     <row r="49" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="258" t="s">
@@ -33975,22 +33975,22 @@
       <c r="J49" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="272" t="str">
+      <c r="K49" s="263" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="272" t="str">
+      <c r="L49" s="263" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="274" t="str">
+      <c r="N49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
@@ -34028,10 +34028,10 @@
         <v>130</v>
       </c>
       <c r="J50" s="253"/>
-      <c r="K50" s="273"/>
-      <c r="L50" s="273"/>
-      <c r="M50" s="275"/>
-      <c r="N50" s="275"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="264"/>
+      <c r="M50" s="266"/>
+      <c r="N50" s="266"/>
       <c r="O50" s="282"/>
       <c r="P50" s="282"/>
     </row>
@@ -35270,10 +35270,10 @@
       <c r="D77" s="251"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="268" t="s">
+      <c r="B78" s="259" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="259" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -35467,6 +35467,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
@@ -35480,11 +35485,6 @@
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="12000" windowHeight="4335" tabRatio="500" firstSheet="1" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" tabRatio="500" firstSheet="6" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="HOW TO USE" sheetId="1" r:id="rId1"/>
@@ -909,7 +909,7 @@
     <t>RONALD</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL —  24 SEPTEMBER 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL —  25 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>
@@ -1806,7 +1806,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="294">
+  <cellXfs count="299">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2481,6 +2481,13 @@
     <xf numFmtId="41" fontId="47" fillId="35" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2660,6 +2667,12 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3428,16 +3441,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="B1" s="235" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="235"/>
+      <c r="B1" s="238" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="238"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="236" t="s">
+      <c r="B3" s="239" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="236"/>
+      <c r="C3" s="239"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -3488,10 +3501,10 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="237" t="s">
+      <c r="B11" s="240" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="237"/>
+      <c r="C11" s="240"/>
     </row>
     <row r="12" spans="2:3" ht="24" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -4299,11 +4312,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="272" t="s">
         <v>219</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="273"/>
+      <c r="D40" s="274"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -4572,10 +4585,10 @@
       </c>
     </row>
     <row r="46" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B46" s="256" t="s">
+      <c r="B46" s="259" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="257"/>
+      <c r="C46" s="260"/>
       <c r="D46" s="47">
         <f>SUM(D42:D45)</f>
         <v>11304209690.274448</v>
@@ -4623,84 +4636,84 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="275" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="276"/>
+      <c r="D48" s="276"/>
+      <c r="E48" s="276"/>
+      <c r="F48" s="276"/>
+      <c r="G48" s="276"/>
+      <c r="H48" s="276"/>
+      <c r="I48" s="276"/>
+      <c r="J48" s="276"/>
+      <c r="K48" s="276"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="264"/>
+      <c r="O48" s="264"/>
+      <c r="P48" s="264"/>
+      <c r="Q48" s="264"/>
+      <c r="R48" s="265"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="253" t="s">
+      <c r="D49" s="256" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="254"/>
-      <c r="F49" s="254"/>
-      <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="E49" s="257"/>
+      <c r="F49" s="257"/>
+      <c r="G49" s="258"/>
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="266" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="266" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="268" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="268" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="270" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="270" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="262"/>
+      <c r="C50" s="262"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -4725,13 +4738,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="267"/>
+      <c r="N50" s="267"/>
+      <c r="O50" s="269"/>
+      <c r="P50" s="269"/>
+      <c r="Q50" s="271"/>
+      <c r="R50" s="271"/>
       <c r="T50" s="172" t="s">
         <v>216</v>
       </c>
@@ -5847,21 +5860,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="293" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
-      <c r="F67" s="292"/>
-      <c r="G67" s="260" t="s">
+      <c r="C67" s="294"/>
+      <c r="D67" s="294"/>
+      <c r="E67" s="294"/>
+      <c r="F67" s="295"/>
+      <c r="G67" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="264"/>
+      <c r="I67" s="264"/>
+      <c r="J67" s="264"/>
+      <c r="K67" s="264"/>
+      <c r="L67" s="265"/>
     </row>
     <row r="68" spans="2:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -6173,17 +6186,17 @@
       </c>
     </row>
     <row r="77" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="249" t="s">
+      <c r="B77" s="252" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="250"/>
-      <c r="D77" s="251"/>
+      <c r="C77" s="253"/>
+      <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="262" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -6191,8 +6204,8 @@
       </c>
     </row>
     <row r="79" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B79" s="258"/>
-      <c r="C79" s="258"/>
+      <c r="B79" s="261"/>
+      <c r="C79" s="261"/>
       <c r="D79" s="70" t="s">
         <v>168</v>
       </c>
@@ -6548,9 +6561,9 @@
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="37.42578125" customWidth="1"/>
-    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="16.42578125" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
+    <col min="7" max="7" width="18.42578125" customWidth="1"/>
     <col min="8" max="10" width="16.42578125" customWidth="1"/>
     <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="18" width="16.42578125" customWidth="1"/>
@@ -6592,7 +6605,7 @@
       </c>
       <c r="C3" s="75">
         <f ca="1">IF($J$5&lt;&gt;"",$J$5,MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),9,1)),EOMONTH(DATE(YEAR(TODAY()),9,1),0),11)-MAX(0,$J$3-$J$4)))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="76" t="s">
         <v>104</v>
@@ -6719,20 +6732,20 @@
       <c r="B10" s="72" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="234">
-        <v>122291455.94272</v>
-      </c>
-      <c r="D10" s="234">
-        <v>36845696.872796997</v>
-      </c>
-      <c r="E10" s="234">
-        <v>179872333.71704</v>
-      </c>
-      <c r="F10" s="234">
-        <v>137341527.88993299</v>
-      </c>
-      <c r="G10" s="234">
-        <v>476351014.42249</v>
+      <c r="C10" s="237">
+        <v>129114514.549408</v>
+      </c>
+      <c r="D10" s="237">
+        <v>37038940.117797002</v>
+      </c>
+      <c r="E10" s="237">
+        <v>181176342.72703999</v>
+      </c>
+      <c r="F10" s="237">
+        <v>141725852.38993299</v>
+      </c>
+      <c r="G10" s="237">
+        <v>489055649.78417802</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="111"/>
@@ -6744,19 +6757,19 @@
       <c r="B11" s="72" t="s">
         <v>182</v>
       </c>
-      <c r="C11" s="234">
+      <c r="C11" s="237">
         <v>4173423.4199979999</v>
       </c>
-      <c r="D11" s="234">
+      <c r="D11" s="237">
         <v>30250983.5</v>
       </c>
-      <c r="E11" s="234">
+      <c r="E11" s="237">
         <v>199157658.6392</v>
       </c>
-      <c r="F11" s="234" t="s">
+      <c r="F11" s="237" t="s">
         <v>165</v>
       </c>
-      <c r="G11" s="234">
+      <c r="G11" s="237">
         <v>233582065.55919799</v>
       </c>
       <c r="H11" s="111"/>
@@ -6769,20 +6782,20 @@
       <c r="B12" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="234">
-        <v>154754903.15795001</v>
-      </c>
-      <c r="D12" s="234">
-        <v>65434973.791523002</v>
-      </c>
-      <c r="E12" s="234">
-        <v>142914057.259583</v>
-      </c>
-      <c r="F12" s="234">
-        <v>65596580.700000003</v>
-      </c>
-      <c r="G12" s="234">
-        <v>428700514.90905601</v>
+      <c r="C12" s="237">
+        <v>158097388.15795001</v>
+      </c>
+      <c r="D12" s="237">
+        <v>67902257.621514007</v>
+      </c>
+      <c r="E12" s="237">
+        <v>144886174.379583</v>
+      </c>
+      <c r="F12" s="237">
+        <v>67696580.700000003</v>
+      </c>
+      <c r="G12" s="237">
+        <v>438582400.859047</v>
       </c>
       <c r="H12" s="111"/>
       <c r="I12" s="111"/>
@@ -6794,20 +6807,20 @@
       <c r="B13" s="72" t="s">
         <v>114</v>
       </c>
-      <c r="C13" s="234">
+      <c r="C13" s="237">
         <v>30349577.699947</v>
       </c>
-      <c r="D13" s="234">
-        <v>21848079.549964</v>
-      </c>
-      <c r="E13" s="234">
-        <v>182651308.10961899</v>
-      </c>
-      <c r="F13" s="234">
-        <v>70939470.450000003</v>
-      </c>
-      <c r="G13" s="234">
-        <v>305788435.80953002</v>
+      <c r="D13" s="237">
+        <v>22046277.749963999</v>
+      </c>
+      <c r="E13" s="237">
+        <v>190561218.02961701</v>
+      </c>
+      <c r="F13" s="237">
+        <v>81607939.109999999</v>
+      </c>
+      <c r="G13" s="237">
+        <v>324565012.58952802</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="111"/>
@@ -6819,20 +6832,20 @@
       <c r="B14" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="C14" s="234">
-        <v>425558938.85456401</v>
-      </c>
-      <c r="D14" s="234">
-        <v>41590640.469465002</v>
-      </c>
-      <c r="E14" s="234">
-        <v>139353252.479877</v>
-      </c>
-      <c r="F14" s="234">
-        <v>346086641.02977002</v>
-      </c>
-      <c r="G14" s="234">
-        <v>952589472.83367598</v>
+      <c r="C14" s="237">
+        <v>437151614.40455902</v>
+      </c>
+      <c r="D14" s="237">
+        <v>42720135.969465002</v>
+      </c>
+      <c r="E14" s="237">
+        <v>142801315.51987499</v>
+      </c>
+      <c r="F14" s="237">
+        <v>359312587.47977</v>
+      </c>
+      <c r="G14" s="237">
+        <v>981985653.37366903</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="111"/>
@@ -6844,20 +6857,20 @@
       <c r="B15" s="72" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="234">
-        <v>1499930492.5599079</v>
-      </c>
-      <c r="D15" s="234">
+      <c r="C15" s="237">
+        <v>1502915183.6099081</v>
+      </c>
+      <c r="D15" s="237">
         <v>11190936.014923999</v>
       </c>
-      <c r="E15" s="234">
-        <v>76818395.269939005</v>
-      </c>
-      <c r="F15" s="234">
-        <v>13983784.08</v>
-      </c>
-      <c r="G15" s="234">
-        <v>1601923607.9247711</v>
+      <c r="E15" s="237">
+        <v>76858935.799939007</v>
+      </c>
+      <c r="F15" s="237">
+        <v>14632432.720000001</v>
+      </c>
+      <c r="G15" s="237">
+        <v>1605597488.1447711</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="111"/>
@@ -6869,20 +6882,20 @@
       <c r="B16" s="72" t="s">
         <v>120</v>
       </c>
-      <c r="C16" s="234">
-        <v>421221722.82963502</v>
-      </c>
-      <c r="D16" s="234">
-        <v>41281878.019927002</v>
-      </c>
-      <c r="E16" s="234">
-        <v>275830181.54944998</v>
-      </c>
-      <c r="F16" s="234">
-        <v>858628819.27996898</v>
-      </c>
-      <c r="G16" s="234">
-        <v>1596962601.6789811</v>
+      <c r="C16" s="237">
+        <v>465821952.54762101</v>
+      </c>
+      <c r="D16" s="237">
+        <v>51819828.479924001</v>
+      </c>
+      <c r="E16" s="237">
+        <v>299276352.78941</v>
+      </c>
+      <c r="F16" s="237">
+        <v>952267556.879969</v>
+      </c>
+      <c r="G16" s="237">
+        <v>1769185690.696924</v>
       </c>
       <c r="H16" s="111"/>
       <c r="I16" s="111"/>
@@ -6894,20 +6907,20 @@
       <c r="B17" s="72" t="s">
         <v>122</v>
       </c>
-      <c r="C17" s="234">
-        <v>94697468.216019005</v>
-      </c>
-      <c r="D17" s="234">
+      <c r="C17" s="237">
+        <v>97903468.216019005</v>
+      </c>
+      <c r="D17" s="237">
         <v>12915436.9209</v>
       </c>
-      <c r="E17" s="234">
-        <v>72504191.618842006</v>
-      </c>
-      <c r="F17" s="234">
+      <c r="E17" s="237">
+        <v>103260945.468842</v>
+      </c>
+      <c r="F17" s="237">
         <v>47952973.898000002</v>
       </c>
-      <c r="G17" s="234">
-        <v>228070070.653761</v>
+      <c r="G17" s="237">
+        <v>262032824.50376099</v>
       </c>
       <c r="H17" s="111"/>
       <c r="I17" s="111"/>
@@ -6920,20 +6933,20 @@
       <c r="B18" s="72" t="s">
         <v>123</v>
       </c>
-      <c r="C18" s="234">
+      <c r="C18" s="237">
         <v>13080047.589996999</v>
       </c>
-      <c r="D18" s="234">
-        <v>133803404.811655</v>
-      </c>
-      <c r="E18" s="234">
-        <v>56002106.100000001</v>
-      </c>
-      <c r="F18" s="234">
-        <v>100562164.31999999</v>
-      </c>
-      <c r="G18" s="234">
-        <v>303447722.821652</v>
+      <c r="D18" s="237">
+        <v>134100404.811655</v>
+      </c>
+      <c r="E18" s="237">
+        <v>58453106.100000001</v>
+      </c>
+      <c r="F18" s="237">
+        <v>103589191.42</v>
+      </c>
+      <c r="G18" s="237">
+        <v>309222749.92165202</v>
       </c>
       <c r="H18" s="111"/>
       <c r="I18" s="111"/>
@@ -6946,20 +6959,20 @@
       <c r="B19" s="72" t="s">
         <v>169</v>
       </c>
-      <c r="C19" s="234">
-        <v>45722758.259999998</v>
-      </c>
-      <c r="D19" s="234" t="s">
+      <c r="C19" s="237">
+        <v>46889334.859999999</v>
+      </c>
+      <c r="D19" s="237" t="s">
         <v>165</v>
       </c>
-      <c r="E19" s="234" t="s">
+      <c r="E19" s="237" t="s">
         <v>165</v>
       </c>
-      <c r="F19" s="234">
+      <c r="F19" s="237">
         <v>7027026.8399999999</v>
       </c>
-      <c r="G19" s="234">
-        <v>52749785.100000001</v>
+      <c r="G19" s="237">
+        <v>53916361.700000003</v>
       </c>
       <c r="H19" s="111"/>
       <c r="I19" s="111"/>
@@ -6972,20 +6985,20 @@
       <c r="B20" s="72" t="s">
         <v>170</v>
       </c>
-      <c r="C20" s="234">
-        <v>188527227.16</v>
-      </c>
-      <c r="D20" s="234" t="s">
+      <c r="C20" s="237">
+        <v>215561847.16</v>
+      </c>
+      <c r="D20" s="237" t="s">
         <v>165</v>
       </c>
-      <c r="E20" s="234" t="s">
+      <c r="E20" s="237" t="s">
         <v>165</v>
       </c>
-      <c r="F20" s="234">
-        <v>9813783.5199999996</v>
-      </c>
-      <c r="G20" s="234">
-        <v>198341010.68000001</v>
+      <c r="F20" s="237">
+        <v>11975945.619999999</v>
+      </c>
+      <c r="G20" s="237">
+        <v>227537792.78</v>
       </c>
       <c r="H20" s="111"/>
       <c r="I20" s="111"/>
@@ -7002,27 +7015,27 @@
       <c r="B21" s="72" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="234">
-        <v>229659386.58680099</v>
-      </c>
-      <c r="D21" s="234">
-        <v>44851670.153456002</v>
-      </c>
-      <c r="E21" s="234">
-        <v>129240491.55978499</v>
-      </c>
-      <c r="F21" s="234">
-        <v>345823522.47986001</v>
-      </c>
-      <c r="G21" s="234">
-        <v>749575070.77990198</v>
+      <c r="C21" s="237">
+        <v>250622165.38778701</v>
+      </c>
+      <c r="D21" s="237">
+        <v>46331940.443448998</v>
+      </c>
+      <c r="E21" s="237">
+        <v>135756942.00977701</v>
+      </c>
+      <c r="F21" s="237">
+        <v>343488851.45986003</v>
+      </c>
+      <c r="G21" s="237">
+        <v>776199899.30087304</v>
       </c>
       <c r="H21" s="111"/>
       <c r="I21" s="111"/>
       <c r="J21" s="111"/>
       <c r="M21" s="14">
         <f>SUM(C33,C34)+M20</f>
-        <v>934135147.50660896</v>
+        <v>948476673.30109191</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>224</v>
@@ -7030,22 +7043,22 @@
     </row>
     <row r="22" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="72" t="s">
-        <v>125</v>
-      </c>
-      <c r="C22" s="234">
-        <v>226738564.12332499</v>
-      </c>
-      <c r="D22" s="234">
-        <v>55894289.419963002</v>
-      </c>
-      <c r="E22" s="234">
-        <v>171252696.26218399</v>
-      </c>
-      <c r="F22" s="234">
-        <v>260869645.919505</v>
-      </c>
-      <c r="G22" s="234">
-        <v>714755195.72497702</v>
+        <v>225</v>
+      </c>
+      <c r="C22" s="237">
+        <v>183815526.976354</v>
+      </c>
+      <c r="D22" s="237">
+        <v>46626385.219940998</v>
+      </c>
+      <c r="E22" s="237">
+        <v>137495154.28817099</v>
+      </c>
+      <c r="F22" s="237">
+        <v>64092612.359999999</v>
+      </c>
+      <c r="G22" s="237">
+        <v>432029678.84446597</v>
       </c>
       <c r="H22" s="111"/>
       <c r="I22" s="111"/>
@@ -7053,22 +7066,22 @@
     </row>
     <row r="23" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="72" t="s">
-        <v>126</v>
-      </c>
-      <c r="C23" s="234">
-        <v>402608462.21627998</v>
-      </c>
-      <c r="D23" s="234">
-        <v>54954295.924923003</v>
-      </c>
-      <c r="E23" s="234">
-        <v>181079758.51990199</v>
-      </c>
-      <c r="F23" s="234">
-        <v>514008155.46949601</v>
-      </c>
-      <c r="G23" s="234">
-        <v>1152650672.1306009</v>
+        <v>125</v>
+      </c>
+      <c r="C23" s="237">
+        <v>241361191.13532299</v>
+      </c>
+      <c r="D23" s="237">
+        <v>63404429.039943002</v>
+      </c>
+      <c r="E23" s="237">
+        <v>176031885.582169</v>
+      </c>
+      <c r="F23" s="237">
+        <v>278739195.65947998</v>
+      </c>
+      <c r="G23" s="237">
+        <v>759536701.41691506</v>
       </c>
       <c r="H23" s="111"/>
       <c r="I23" s="111"/>
@@ -7076,22 +7089,22 @@
     </row>
     <row r="24" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="72" t="s">
-        <v>225</v>
-      </c>
-      <c r="C24" s="234">
-        <v>172496649.28866401</v>
-      </c>
-      <c r="D24" s="234">
-        <v>45674574.409941003</v>
-      </c>
-      <c r="E24" s="234">
-        <v>133534839.06817099</v>
-      </c>
-      <c r="F24" s="234">
-        <v>64062612.359999999</v>
-      </c>
-      <c r="G24" s="234">
-        <v>415768675.12677598</v>
+        <v>126</v>
+      </c>
+      <c r="C24" s="237">
+        <v>420220553.48265302</v>
+      </c>
+      <c r="D24" s="237">
+        <v>57722998.644919001</v>
+      </c>
+      <c r="E24" s="237">
+        <v>189249443.53988701</v>
+      </c>
+      <c r="F24" s="237">
+        <v>534549561.39945602</v>
+      </c>
+      <c r="G24" s="237">
+        <v>1201742557.066915</v>
       </c>
       <c r="H24" s="111"/>
       <c r="I24" s="111"/>
@@ -7101,20 +7114,20 @@
       <c r="B25" s="72" t="s">
         <v>220</v>
       </c>
-      <c r="C25" s="234">
-        <v>270003598.861857</v>
-      </c>
-      <c r="D25" s="234">
-        <v>77822671.056532994</v>
-      </c>
-      <c r="E25" s="234">
-        <v>88127833.698561996</v>
-      </c>
-      <c r="F25" s="234">
+      <c r="C25" s="237">
+        <v>283697018.83984798</v>
+      </c>
+      <c r="D25" s="237">
+        <v>80203472.886524007</v>
+      </c>
+      <c r="E25" s="237">
+        <v>93333896.788552999</v>
+      </c>
+      <c r="F25" s="237">
         <v>49513514.579999998</v>
       </c>
-      <c r="G25" s="234">
-        <v>485467618.19695199</v>
+      <c r="G25" s="237">
+        <v>506747903.09492499</v>
       </c>
       <c r="H25" s="111"/>
       <c r="I25" s="111"/>
@@ -7124,20 +7137,20 @@
       <c r="B26" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="234">
-        <v>413271522.44322699</v>
-      </c>
-      <c r="D26" s="234">
-        <v>260467539.04622999</v>
-      </c>
-      <c r="E26" s="234">
-        <v>238566169.62585801</v>
-      </c>
-      <c r="F26" s="234">
-        <v>18013297.6536</v>
-      </c>
-      <c r="G26" s="234">
-        <v>930318528.76891506</v>
+      <c r="C26" s="237">
+        <v>426130063.79518402</v>
+      </c>
+      <c r="D26" s="237">
+        <v>281504998.24590999</v>
+      </c>
+      <c r="E26" s="237">
+        <v>248507610.975813</v>
+      </c>
+      <c r="F26" s="237">
+        <v>18820757.1204</v>
+      </c>
+      <c r="G26" s="237">
+        <v>974963430.13730705</v>
       </c>
       <c r="H26" s="111"/>
       <c r="I26" s="111"/>
@@ -7169,8 +7182,8 @@
       <c r="I29" s="111"/>
     </row>
     <row r="30" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="73"/>
-      <c r="C30" s="107"/>
+      <c r="B30" s="234"/>
+      <c r="C30" s="298"/>
       <c r="G30" s="111"/>
       <c r="H30" s="111"/>
       <c r="I30" s="111"/>
@@ -7179,8 +7192,8 @@
       <c r="B31" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="C31" s="171">
-        <v>230771202.18516701</v>
+      <c r="C31" s="235">
+        <v>239090594.19514599</v>
       </c>
       <c r="G31" s="111"/>
       <c r="H31" s="111"/>
@@ -7190,7 +7203,7 @@
       <c r="B32" s="81" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="234">
+      <c r="C32" s="297">
         <v>427130336.43894702</v>
       </c>
       <c r="G32" s="111"/>
@@ -7201,8 +7214,8 @@
       <c r="B33" s="81" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="171">
-        <v>491062628.31530601</v>
+      <c r="C33" s="237">
+        <v>503000911.10980099</v>
       </c>
       <c r="G33" s="111"/>
       <c r="H33" s="111"/>
@@ -7212,8 +7225,8 @@
       <c r="B34" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="234">
-        <v>443072519.19130301</v>
+      <c r="C34" s="237">
+        <v>445475762.19129097</v>
       </c>
       <c r="G34" s="111"/>
       <c r="H34" s="111"/>
@@ -7223,7 +7236,7 @@
       <c r="B35" s="81" t="s">
         <v>135</v>
       </c>
-      <c r="C35" s="234">
+      <c r="C35" s="236">
         <v>0</v>
       </c>
       <c r="G35" s="111"/>
@@ -7258,17 +7271,17 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="272" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="273"/>
+      <c r="D40" s="274"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
       <c r="F40" s="174">
         <f ca="1">IF(MONTH(TODAY())=9,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;9,1,0))</f>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="G40" s="192" t="s">
         <v>187</v>
@@ -7355,35 +7368,35 @@
       </c>
       <c r="E42" s="46">
         <f>H65</f>
-        <v>3215155706.6509838</v>
+        <v>3403989688.2226486</v>
       </c>
       <c r="F42" s="176">
         <f>IFERROR(E42/D42,0)</f>
-        <v>0.71261262893150712</v>
+        <v>0.75446611669915109</v>
       </c>
       <c r="G42" s="184">
         <f>D42*$H$40-E42</f>
-        <v>1071041025.3634424</v>
+        <v>882207043.79177761</v>
       </c>
       <c r="H42" s="184">
         <f ca="1">IFERROR(G42/$C$3,0)</f>
-        <v>178506837.56057373</v>
+        <v>176441408.75835553</v>
       </c>
       <c r="I42" s="204">
         <f>D42*$J$40-E42</f>
-        <v>1296630327.0484123</v>
+        <v>1107796345.4767475</v>
       </c>
       <c r="J42" s="204">
         <f ca="1">IFERROR(I42/$C$3,0)</f>
-        <v>216105054.50806871</v>
+        <v>221559269.09534949</v>
       </c>
       <c r="K42" s="185">
         <f>D42*$L$40-E42</f>
-        <v>1296630327.0484123</v>
+        <v>1107796345.4767475</v>
       </c>
       <c r="L42" s="185">
         <f ca="1">IFERROR(K42/$C$3,0)</f>
-        <v>216105054.50806871</v>
+        <v>221559269.09534949</v>
       </c>
       <c r="S42" s="173">
         <v>0.8</v>
@@ -7402,35 +7415,35 @@
       </c>
       <c r="E43" s="46">
         <f>I65</f>
-        <v>923636133.94727707</v>
+        <v>974588489.65190494</v>
       </c>
       <c r="F43" s="176">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.65909732959464251</v>
+        <v>0.69545641121475765</v>
       </c>
       <c r="G43" s="184">
         <f>D43*$H$40-E43</f>
-        <v>407660911.04236698</v>
+        <v>356708555.33773911</v>
       </c>
       <c r="H43" s="184">
         <f ca="1">IFERROR(G43/$C$3,0)</f>
-        <v>67943485.173727825</v>
+        <v>71341711.067547828</v>
       </c>
       <c r="I43" s="204">
         <f>D43*$J$40-E43</f>
-        <v>477729176.56813788</v>
+        <v>426776820.86351001</v>
       </c>
       <c r="J43" s="204">
         <f ca="1">IFERROR(I43/$C$3,0)</f>
-        <v>79621529.428022981</v>
+        <v>85355364.172702</v>
       </c>
       <c r="K43" s="185">
         <f>D43*$L$40-E43</f>
-        <v>477729176.56813788</v>
+        <v>426776820.86351001</v>
       </c>
       <c r="L43" s="185">
         <f ca="1">IFERROR(K43/$C$3,0)</f>
-        <v>79621529.428022981</v>
+        <v>85355364.172702</v>
       </c>
       <c r="S43" s="173">
         <v>0.85</v>
@@ -7449,35 +7462,35 @@
       </c>
       <c r="E44" s="46">
         <f>J65</f>
-        <v>2190086878.2080727</v>
+        <v>2299948046.8379369</v>
       </c>
       <c r="F44" s="176">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.7437096985400522</v>
+        <v>0.78101635400470892</v>
       </c>
       <c r="G44" s="184">
         <f>IF(D44=0,0,D44*$H$40-E44)</f>
-        <v>607486608.30417824</v>
+        <v>497625439.67431402</v>
       </c>
       <c r="H44" s="184">
         <f ca="1">IFERROR(G44/$C$3,0)</f>
-        <v>101247768.05069637</v>
+        <v>99525087.934862807</v>
       </c>
       <c r="I44" s="204">
         <f>IF(D44=0,0,D44*$J$40-E44)</f>
-        <v>754727318.12061262</v>
+        <v>644866149.49074841</v>
       </c>
       <c r="J44" s="204">
         <f ca="1">IFERROR(I44/$C$3,0)</f>
-        <v>125787886.35343544</v>
+        <v>128973229.89814968</v>
       </c>
       <c r="K44" s="185">
         <f>IF(D44=0,0,D44*$L$40-E44)</f>
-        <v>754727318.12061262</v>
+        <v>644866149.49074841</v>
       </c>
       <c r="L44" s="185">
         <f ca="1">IFERROR(K44/$C$3,0)</f>
-        <v>125787886.35343544</v>
+        <v>128973229.89814968</v>
       </c>
       <c r="S44" s="173">
         <v>0.9</v>
@@ -7496,80 +7509,80 @@
       </c>
       <c r="E45" s="46">
         <f>E74</f>
-        <v>1592036686.130723</v>
+        <v>1614697603.935185</v>
       </c>
       <c r="F45" s="176">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.91473990523403403</v>
+        <v>0.92776023697987398</v>
       </c>
       <c r="G45" s="184">
         <f>D45*$H$40-E45</f>
-        <v>61367569.188425779</v>
+        <v>38706651.383963823</v>
       </c>
       <c r="H45" s="184">
         <f ca="1">IFERROR(G45/$C$3,0)</f>
-        <v>10227928.198070964</v>
+        <v>7741330.2767927647</v>
       </c>
       <c r="I45" s="204">
         <f>D45*$J$40-E45</f>
-        <v>148388845.78417063</v>
+        <v>125727927.97970867</v>
       </c>
       <c r="J45" s="204">
         <f ca="1">IFERROR(I45/$C$3,0)</f>
-        <v>24731474.297361773</v>
+        <v>25145585.595941734</v>
       </c>
       <c r="K45" s="185">
         <f>D45*$L$40-E45</f>
-        <v>148388845.78417063</v>
+        <v>125727927.97970867</v>
       </c>
       <c r="L45" s="185">
         <f ca="1">IFERROR(K45/$C$3,0)</f>
-        <v>24731474.297361773</v>
+        <v>25145585.595941734</v>
       </c>
       <c r="S45" s="173">
         <v>0.95</v>
       </c>
     </row>
     <row r="46" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="256" t="s">
+      <c r="B46" s="259" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="257"/>
+      <c r="C46" s="260"/>
       <c r="D46" s="47">
         <f>SUM(D42:D45)</f>
         <v>10598391072.458391</v>
       </c>
       <c r="E46" s="47">
         <f>SUM(E42:E45)</f>
-        <v>7920915404.9370565</v>
+        <v>8293223828.6476746</v>
       </c>
       <c r="F46" s="177">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.74736961023459669</v>
+        <v>0.7824983784754781</v>
       </c>
       <c r="G46" s="181">
         <f>SUM(G42:G45)</f>
-        <v>2147556113.8984137</v>
+        <v>1775247690.1877944</v>
       </c>
       <c r="H46" s="181">
         <f ca="1">IFERROR(G46/$C$3,0)</f>
-        <v>357926018.98306894</v>
+        <v>355049538.03755891</v>
       </c>
       <c r="I46" s="186">
         <f>SUM(I42:I45)</f>
-        <v>2677475667.5213332</v>
+        <v>2305167243.8107147</v>
       </c>
       <c r="J46" s="186">
         <f ca="1">IFERROR(I46/$C$3,0)</f>
-        <v>446245944.58688885</v>
+        <v>461033448.76214296</v>
       </c>
       <c r="K46" s="186">
         <f>SUM(K42:K45)</f>
-        <v>2677475667.5213332</v>
+        <v>2305167243.8107147</v>
       </c>
       <c r="L46" s="186">
         <f ca="1">IFERROR(K46/$C$3,0)</f>
-        <v>446245944.58688885</v>
+        <v>461033448.76214296</v>
       </c>
       <c r="S46" s="173">
         <v>1</v>
@@ -7582,84 +7595,84 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="275" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="276"/>
+      <c r="D48" s="276"/>
+      <c r="E48" s="276"/>
+      <c r="F48" s="276"/>
+      <c r="G48" s="276"/>
+      <c r="H48" s="276"/>
+      <c r="I48" s="276"/>
+      <c r="J48" s="276"/>
+      <c r="K48" s="276"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="264"/>
+      <c r="O48" s="264"/>
+      <c r="P48" s="264"/>
+      <c r="Q48" s="264"/>
+      <c r="R48" s="265"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="253" t="s">
+      <c r="D49" s="256" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="254"/>
-      <c r="F49" s="254"/>
-      <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="E49" s="257"/>
+      <c r="F49" s="257"/>
+      <c r="G49" s="258"/>
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="266" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="266" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="268" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="268" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="270" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="270" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="262"/>
+      <c r="C50" s="262"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -7684,13 +7697,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="267"/>
+      <c r="N50" s="267"/>
+      <c r="O50" s="269"/>
+      <c r="P50" s="269"/>
+      <c r="Q50" s="271"/>
+      <c r="R50" s="271"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -7723,47 +7736,47 @@
       </c>
       <c r="H51" s="114">
         <f t="shared" ref="H51:H64" si="1">SUMIF($B$10:$B$26,$T51,C$10:C$26)+SUMIF($B$10:$B$26,$U51,C$10:C$26)</f>
-        <v>229659386.58680099</v>
+        <v>250622165.38778701</v>
       </c>
       <c r="I51" s="114">
         <f t="shared" ref="I51:I64" si="2">SUMIF($B$10:$B$26,$T51,D$10:D$26)+SUMIF($B$10:$B$26,$U51,D$10:D$26)</f>
-        <v>44851670.153456002</v>
+        <v>46331940.443448998</v>
       </c>
       <c r="J51" s="114">
         <f t="shared" ref="J51:J64" si="3">SUMIF($B$10:$B$26,$T51,E$10:E$26)+SUMIF($B$10:$B$26,$U51,E$10:E$26)</f>
-        <v>129240491.55978499</v>
+        <v>135756942.00977701</v>
       </c>
       <c r="K51" s="114">
         <f t="shared" ref="K51:K64" si="4">SUM(H51:J51)</f>
-        <v>403751548.30004203</v>
+        <v>432711047.84101301</v>
       </c>
       <c r="L51" s="187">
         <f t="shared" ref="L51:L65" si="5">IFERROR(K51/G51,0)</f>
-        <v>0.78494759620297694</v>
+        <v>0.84124877857029168</v>
       </c>
       <c r="M51" s="184">
         <f t="shared" ref="M51:M64" si="6">G51*$H$40-K51</f>
-        <v>84897595.592431784</v>
+        <v>55938096.051460803</v>
       </c>
       <c r="N51" s="184">
         <f t="shared" ref="N51:N65" ca="1" si="7">IFERROR(M51/$C$3,0)</f>
-        <v>14149599.265405297</v>
+        <v>11187619.210292161</v>
       </c>
       <c r="O51" s="180">
         <f t="shared" ref="O51:O64" si="8">G51*$J$40-K51</f>
-        <v>110615971.58677256</v>
+        <v>81656472.04580158</v>
       </c>
       <c r="P51" s="180">
         <f t="shared" ref="P51:P65" ca="1" si="9">IFERROR(O51/$C$3,0)</f>
-        <v>18435995.264462095</v>
+        <v>16331294.409160316</v>
       </c>
       <c r="Q51" s="185">
         <f t="shared" ref="Q51:Q64" si="10">G51*$L$40-K51</f>
-        <v>110615971.58677256</v>
+        <v>81656472.04580158</v>
       </c>
       <c r="R51" s="185">
         <f t="shared" ref="R51:R65" ca="1" si="11">IFERROR(Q51/$C$3,0)</f>
-        <v>18435995.264462095</v>
+        <v>16331294.409160316</v>
       </c>
       <c r="T51" t="s">
         <v>124</v>
@@ -7797,47 +7810,47 @@
       </c>
       <c r="H52" s="114">
         <f t="shared" si="1"/>
-        <v>185104480.85789701</v>
+        <v>188446965.85789701</v>
       </c>
       <c r="I52" s="114">
         <f t="shared" si="2"/>
-        <v>87283053.341487005</v>
+        <v>89948535.371478006</v>
       </c>
       <c r="J52" s="114">
         <f t="shared" si="3"/>
-        <v>325565365.36920202</v>
+        <v>335447392.40920001</v>
       </c>
       <c r="K52" s="114">
         <f t="shared" si="4"/>
-        <v>597952899.56858611</v>
+        <v>613842893.63857508</v>
       </c>
       <c r="L52" s="187">
         <f t="shared" si="5"/>
-        <v>0.7612154305067752</v>
+        <v>0.78144396135839178</v>
       </c>
       <c r="M52" s="184">
         <f t="shared" si="6"/>
-        <v>148294787.78054833</v>
+        <v>132404793.71055937</v>
       </c>
       <c r="N52" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>24715797.963424724</v>
+        <v>26480958.742111873</v>
       </c>
       <c r="O52" s="180">
         <f t="shared" si="8"/>
-        <v>187570981.85155547</v>
+        <v>171680987.7815665</v>
       </c>
       <c r="P52" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>31261830.308592577</v>
+        <v>34336197.556313299</v>
       </c>
       <c r="Q52" s="185">
         <f t="shared" si="10"/>
-        <v>187570981.85155547</v>
+        <v>171680987.7815665</v>
       </c>
       <c r="R52" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>31261830.308592577</v>
+        <v>34336197.556313299</v>
       </c>
       <c r="T52" t="s">
         <v>70</v>
@@ -7871,7 +7884,7 @@
       </c>
       <c r="H53" s="114">
         <f t="shared" si="1"/>
-        <v>45722758.259999998</v>
+        <v>46889334.859999999</v>
       </c>
       <c r="I53" s="114">
         <f t="shared" si="2"/>
@@ -7883,35 +7896,35 @@
       </c>
       <c r="K53" s="114">
         <f t="shared" si="4"/>
-        <v>45722758.259999998</v>
+        <v>46889334.859999999</v>
       </c>
       <c r="L53" s="187">
         <f t="shared" si="5"/>
-        <v>0.17388179633415463</v>
+        <v>0.17831823985787898</v>
       </c>
       <c r="M53" s="184">
         <f t="shared" si="6"/>
-        <v>204082691.54986021</v>
+        <v>202916114.94986022</v>
       </c>
       <c r="N53" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>34013781.924976699</v>
+        <v>40583222.98997204</v>
       </c>
       <c r="O53" s="180">
         <f t="shared" si="8"/>
-        <v>217230346.80301076</v>
+        <v>216063770.20301074</v>
       </c>
       <c r="P53" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>36205057.800501794</v>
+        <v>43212754.040602148</v>
       </c>
       <c r="Q53" s="185">
         <f t="shared" si="10"/>
-        <v>217230346.80301076</v>
+        <v>216063770.20301074</v>
       </c>
       <c r="R53" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>36205057.800501794</v>
+        <v>43212754.040602148</v>
       </c>
       <c r="T53" t="s">
         <v>169</v>
@@ -7945,47 +7958,47 @@
       </c>
       <c r="H54" s="114">
         <f t="shared" si="1"/>
-        <v>425558938.85456401</v>
+        <v>437151614.40455902</v>
       </c>
       <c r="I54" s="114">
         <f t="shared" si="2"/>
-        <v>41590640.469465002</v>
+        <v>42720135.969465002</v>
       </c>
       <c r="J54" s="114">
         <f t="shared" si="3"/>
-        <v>139353252.479877</v>
+        <v>142801315.51987499</v>
       </c>
       <c r="K54" s="114">
         <f t="shared" si="4"/>
-        <v>606502831.80390596</v>
+        <v>622673065.89389896</v>
       </c>
       <c r="L54" s="187">
         <f t="shared" si="5"/>
-        <v>0.83463101839227838</v>
+        <v>0.85688347664714104</v>
       </c>
       <c r="M54" s="184">
         <f t="shared" si="6"/>
-        <v>83835386.542666316</v>
+        <v>67665152.452673316</v>
       </c>
       <c r="N54" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>13972564.42377772</v>
+        <v>13533030.490534663</v>
       </c>
       <c r="O54" s="180">
         <f t="shared" si="8"/>
-        <v>120168976.98195958</v>
+        <v>103998742.89196658</v>
       </c>
       <c r="P54" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>20028162.830326598</v>
+        <v>20799748.578393318</v>
       </c>
       <c r="Q54" s="185">
         <f t="shared" si="10"/>
-        <v>120168976.98195958</v>
+        <v>103998742.89196658</v>
       </c>
       <c r="R54" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>20028162.830326598</v>
+        <v>20799748.578393318</v>
       </c>
       <c r="T54" t="s">
         <v>115</v>
@@ -8043,7 +8056,7 @@
       </c>
       <c r="N55" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>46126480.672158897</v>
+        <v>55351776.806590676</v>
       </c>
       <c r="O55" s="180">
         <f t="shared" si="8"/>
@@ -8051,7 +8064,7 @@
       </c>
       <c r="P55" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>50603155.66858127</v>
+        <v>60723786.802297518</v>
       </c>
       <c r="Q55" s="185">
         <f t="shared" si="10"/>
@@ -8059,7 +8072,7 @@
       </c>
       <c r="R55" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>50603155.66858127</v>
+        <v>60723786.802297518</v>
       </c>
       <c r="T55" t="s">
         <v>182</v>
@@ -8093,47 +8106,47 @@
       </c>
       <c r="H56" s="114">
         <f t="shared" si="1"/>
-        <v>172496649.28866401</v>
+        <v>183815526.976354</v>
       </c>
       <c r="I56" s="114">
         <f t="shared" si="2"/>
-        <v>45674574.409941003</v>
+        <v>46626385.219940998</v>
       </c>
       <c r="J56" s="114">
         <f t="shared" si="3"/>
-        <v>133534839.06817099</v>
+        <v>137495154.28817099</v>
       </c>
       <c r="K56" s="114">
         <f t="shared" si="4"/>
-        <v>351706062.76677597</v>
+        <v>367937066.48446596</v>
       </c>
       <c r="L56" s="187">
         <f t="shared" si="5"/>
-        <v>0.61172017859316252</v>
+        <v>0.63995066292096792</v>
       </c>
       <c r="M56" s="184">
         <f t="shared" si="6"/>
-        <v>194492626.30843151</v>
+        <v>178261622.59074152</v>
       </c>
       <c r="N56" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>32415437.718071919</v>
+        <v>35652324.518148303</v>
       </c>
       <c r="O56" s="180">
         <f t="shared" si="8"/>
-        <v>223239925.73344243</v>
+        <v>207008922.01575243</v>
       </c>
       <c r="P56" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>37206654.288907073</v>
+        <v>41401784.403150484</v>
       </c>
       <c r="Q56" s="185">
         <f t="shared" si="10"/>
-        <v>223239925.73344243</v>
+        <v>207008922.01575243</v>
       </c>
       <c r="R56" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>37206654.288907073</v>
+        <v>41401784.403150484</v>
       </c>
       <c r="T56" t="s">
         <v>225</v>
@@ -8167,47 +8180,47 @@
       </c>
       <c r="H57" s="114">
         <f t="shared" si="1"/>
-        <v>421221722.82963502</v>
+        <v>465821952.54762101</v>
       </c>
       <c r="I57" s="114">
         <f t="shared" si="2"/>
-        <v>41281878.019927002</v>
+        <v>51819828.479924001</v>
       </c>
       <c r="J57" s="114">
         <f t="shared" si="3"/>
-        <v>275830181.54944998</v>
+        <v>299276352.78941</v>
       </c>
       <c r="K57" s="114">
         <f t="shared" si="4"/>
-        <v>738333782.39901209</v>
+        <v>816918133.81695509</v>
       </c>
       <c r="L57" s="187">
         <f t="shared" si="5"/>
-        <v>0.66565487672211732</v>
+        <v>0.73650366896541852</v>
       </c>
       <c r="M57" s="184">
         <f t="shared" si="6"/>
-        <v>315391079.8494972</v>
+        <v>236806728.4315542</v>
       </c>
       <c r="N57" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>52565179.974916197</v>
+        <v>47361345.686310843</v>
       </c>
       <c r="O57" s="180">
         <f t="shared" si="8"/>
-        <v>370850283.12573457</v>
+        <v>292265931.70779157</v>
       </c>
       <c r="P57" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>61808380.520955764</v>
+        <v>58453186.341558315</v>
       </c>
       <c r="Q57" s="185">
         <f t="shared" si="10"/>
-        <v>370850283.12573457</v>
+        <v>292265931.70779157</v>
       </c>
       <c r="R57" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>61808380.520955764</v>
+        <v>58453186.341558315</v>
       </c>
       <c r="T57" t="s">
         <v>120</v>
@@ -8241,47 +8254,47 @@
       </c>
       <c r="H58" s="114">
         <f t="shared" si="1"/>
-        <v>226738564.12332499</v>
+        <v>241361191.13532299</v>
       </c>
       <c r="I58" s="114">
         <f t="shared" si="2"/>
-        <v>55894289.419963002</v>
+        <v>63404429.039943002</v>
       </c>
       <c r="J58" s="114">
         <f t="shared" si="3"/>
-        <v>171252696.26218399</v>
+        <v>176031885.582169</v>
       </c>
       <c r="K58" s="114">
         <f t="shared" si="4"/>
-        <v>453885549.80547202</v>
+        <v>480797505.75743496</v>
       </c>
       <c r="L58" s="187">
         <f t="shared" si="5"/>
-        <v>0.73852860027148437</v>
+        <v>0.78231772104937491</v>
       </c>
       <c r="M58" s="184">
         <f t="shared" si="6"/>
-        <v>129966276.86270535</v>
+        <v>103054320.9107424</v>
       </c>
       <c r="N58" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>21661046.143784225</v>
+        <v>20610864.182148479</v>
       </c>
       <c r="O58" s="180">
         <f t="shared" si="8"/>
-        <v>160695320.37155688</v>
+        <v>133783364.41959393</v>
       </c>
       <c r="P58" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>26782553.395259481</v>
+        <v>26756672.883918785</v>
       </c>
       <c r="Q58" s="185">
         <f t="shared" si="10"/>
-        <v>160695320.37155688</v>
+        <v>133783364.41959393</v>
       </c>
       <c r="R58" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>26782553.395259481</v>
+        <v>26756672.883918785</v>
       </c>
       <c r="T58" t="s">
         <v>125</v>
@@ -8315,7 +8328,7 @@
       </c>
       <c r="H59" s="114">
         <f t="shared" si="1"/>
-        <v>188527227.16</v>
+        <v>215561847.16</v>
       </c>
       <c r="I59" s="114">
         <f t="shared" si="2"/>
@@ -8327,35 +8340,35 @@
       </c>
       <c r="K59" s="114">
         <f t="shared" si="4"/>
-        <v>188527227.16</v>
+        <v>215561847.16</v>
       </c>
       <c r="L59" s="187">
         <f t="shared" si="5"/>
-        <v>0.42475751322201688</v>
+        <v>0.48566732521621037</v>
       </c>
       <c r="M59" s="184">
         <f t="shared" si="6"/>
-        <v>233127152.63759902</v>
+        <v>206092532.63759902</v>
       </c>
       <c r="N59" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>38854525.439599834</v>
+        <v>41218506.527519807</v>
       </c>
       <c r="O59" s="180">
         <f t="shared" si="8"/>
-        <v>255319488.41642001</v>
+        <v>228284868.41642001</v>
       </c>
       <c r="P59" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>42553248.069403335</v>
+        <v>45656973.683284</v>
       </c>
       <c r="Q59" s="185">
         <f t="shared" si="10"/>
-        <v>255319488.41642001</v>
+        <v>228284868.41642001</v>
       </c>
       <c r="R59" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>42553248.069403335</v>
+        <v>45656973.683284</v>
       </c>
       <c r="T59" t="s">
         <v>170</v>
@@ -8389,47 +8402,47 @@
       </c>
       <c r="H60" s="114">
         <f t="shared" si="1"/>
-        <v>270003598.861857</v>
+        <v>283697018.83984798</v>
       </c>
       <c r="I60" s="114">
         <f t="shared" si="2"/>
-        <v>77822671.056532994</v>
+        <v>80203472.886524007</v>
       </c>
       <c r="J60" s="114">
         <f t="shared" si="3"/>
-        <v>88127833.698561996</v>
+        <v>93333896.788552999</v>
       </c>
       <c r="K60" s="114">
         <f t="shared" si="4"/>
-        <v>435954103.61695194</v>
+        <v>457234388.514925</v>
       </c>
       <c r="L60" s="187">
         <f t="shared" si="5"/>
-        <v>0.75270111312652965</v>
+        <v>0.78944281138664696</v>
       </c>
       <c r="M60" s="184">
         <f t="shared" si="6"/>
-        <v>114272794.16961253</v>
+        <v>92992509.271639466</v>
       </c>
       <c r="N60" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>19045465.694935422</v>
+        <v>18598501.854327895</v>
       </c>
       <c r="O60" s="180">
         <f t="shared" si="8"/>
-        <v>143232104.57943177</v>
+        <v>121951819.68145871</v>
       </c>
       <c r="P60" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>23872017.429905295</v>
+        <v>24390363.936291743</v>
       </c>
       <c r="Q60" s="185">
         <f t="shared" si="10"/>
-        <v>143232104.57943177</v>
+        <v>121951819.68145871</v>
       </c>
       <c r="R60" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>23872017.429905295</v>
+        <v>24390363.936291743</v>
       </c>
       <c r="T60" t="s">
         <v>220</v>
@@ -8463,47 +8476,47 @@
       </c>
       <c r="H61" s="114">
         <f t="shared" si="1"/>
-        <v>402608462.21627998</v>
+        <v>420220553.48265302</v>
       </c>
       <c r="I61" s="114">
         <f t="shared" si="2"/>
-        <v>54954295.924923003</v>
+        <v>57722998.644919001</v>
       </c>
       <c r="J61" s="114">
         <f t="shared" si="3"/>
-        <v>181079758.51990199</v>
+        <v>189249443.53988701</v>
       </c>
       <c r="K61" s="114">
         <f t="shared" si="4"/>
-        <v>638642516.66110492</v>
+        <v>667192995.66745901</v>
       </c>
       <c r="L61" s="187">
         <f t="shared" si="5"/>
-        <v>0.89122094901996918</v>
+        <v>0.93106293312094301</v>
       </c>
       <c r="M61" s="184">
         <f t="shared" si="6"/>
-        <v>42120644.814417481</v>
+        <v>13570165.808063388</v>
       </c>
       <c r="N61" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>7020107.4690695805</v>
+        <v>2714033.1616126774</v>
       </c>
       <c r="O61" s="180">
         <f t="shared" si="8"/>
-        <v>77950284.892076612</v>
+        <v>49399805.885722518</v>
       </c>
       <c r="P61" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>12991714.148679435</v>
+        <v>9879961.1771445032</v>
       </c>
       <c r="Q61" s="185">
         <f t="shared" si="10"/>
-        <v>77950284.892076612</v>
+        <v>49399805.885722518</v>
       </c>
       <c r="R61" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>12991714.148679435</v>
+        <v>9879961.1771445032</v>
       </c>
       <c r="T61" t="s">
         <v>126</v>
@@ -8537,47 +8550,47 @@
       </c>
       <c r="H62" s="114">
         <f t="shared" si="1"/>
-        <v>122291455.94272</v>
+        <v>129114514.549408</v>
       </c>
       <c r="I62" s="114">
         <f t="shared" si="2"/>
-        <v>36845696.872796997</v>
+        <v>37038940.117797002</v>
       </c>
       <c r="J62" s="114">
         <f t="shared" si="3"/>
-        <v>179872333.71704</v>
+        <v>181176342.72703999</v>
       </c>
       <c r="K62" s="114">
         <f t="shared" si="4"/>
-        <v>339009486.53255701</v>
+        <v>347329797.39424503</v>
       </c>
       <c r="L62" s="187">
         <f t="shared" si="5"/>
-        <v>0.71067706062391889</v>
+        <v>0.72811920988983281</v>
       </c>
       <c r="M62" s="184">
         <f t="shared" si="6"/>
-        <v>114162608.15020442</v>
+        <v>105842297.2885164</v>
       </c>
       <c r="N62" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>19027101.358367402</v>
+        <v>21168459.457703281</v>
       </c>
       <c r="O62" s="180">
         <f t="shared" si="8"/>
-        <v>138013771.0282445</v>
+        <v>129693460.16655648</v>
       </c>
       <c r="P62" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>23002295.171374083</v>
+        <v>25938692.033311296</v>
       </c>
       <c r="Q62" s="185">
         <f t="shared" si="10"/>
-        <v>138013771.0282445</v>
+        <v>129693460.16655648</v>
       </c>
       <c r="R62" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>23002295.171374083</v>
+        <v>25938692.033311296</v>
       </c>
       <c r="T62" t="s">
         <v>112</v>
@@ -8611,47 +8624,47 @@
       </c>
       <c r="H63" s="114">
         <f t="shared" si="1"/>
-        <v>413271522.44322699</v>
+        <v>426130063.79518402</v>
       </c>
       <c r="I63" s="114">
         <f t="shared" si="2"/>
-        <v>260467539.04622999</v>
+        <v>281504998.24590999</v>
       </c>
       <c r="J63" s="114">
         <f t="shared" si="3"/>
-        <v>238566169.62585801</v>
+        <v>248507610.975813</v>
       </c>
       <c r="K63" s="114">
         <f t="shared" si="4"/>
-        <v>912305231.11531496</v>
+        <v>956142673.0169071</v>
       </c>
       <c r="L63" s="187">
         <f t="shared" si="5"/>
-        <v>0.93189934935679075</v>
+        <v>0.97667831388779225</v>
       </c>
       <c r="M63" s="184">
         <f t="shared" si="6"/>
-        <v>17720066.313801169</v>
+        <v>-26117375.587790966</v>
       </c>
       <c r="N63" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>2953344.3856335282</v>
+        <v>-5223475.1175581934</v>
       </c>
       <c r="O63" s="180">
         <f t="shared" si="8"/>
-        <v>66668766.178491592</v>
+        <v>22831324.276899457</v>
       </c>
       <c r="P63" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>11111461.029748598</v>
+        <v>4566264.8553798916</v>
       </c>
       <c r="Q63" s="185">
         <f t="shared" si="10"/>
-        <v>66668766.178491592</v>
+        <v>22831324.276899457</v>
       </c>
       <c r="R63" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>11111461.029748598</v>
+        <v>4566264.8553798916</v>
       </c>
       <c r="T63" t="s">
         <v>127</v>
@@ -8685,47 +8698,47 @@
       </c>
       <c r="H64" s="114">
         <f t="shared" si="1"/>
-        <v>107777515.806016</v>
+        <v>110983515.806016</v>
       </c>
       <c r="I64" s="114">
         <f t="shared" si="2"/>
-        <v>146718841.732555</v>
+        <v>147015841.732555</v>
       </c>
       <c r="J64" s="114">
         <f t="shared" si="3"/>
-        <v>128506297.718842</v>
+        <v>161714051.56884199</v>
       </c>
       <c r="K64" s="114">
         <f t="shared" si="4"/>
-        <v>383002655.25741303</v>
+        <v>419713409.10741299</v>
       </c>
       <c r="L64" s="187">
         <f t="shared" si="5"/>
-        <v>0.71334035984401423</v>
+        <v>0.78171393898775088</v>
       </c>
       <c r="M64" s="184">
         <f t="shared" si="6"/>
-        <v>127065950.10525817</v>
+        <v>90355196.255258203</v>
       </c>
       <c r="N64" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>21177658.350876361</v>
+        <v>18071039.251051642</v>
       </c>
       <c r="O64" s="180">
         <f t="shared" si="8"/>
-        <v>153911666.17697775</v>
+        <v>117200912.32697779</v>
       </c>
       <c r="P64" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>25651944.362829626</v>
+        <v>23440182.465395559</v>
       </c>
       <c r="Q64" s="185">
         <f t="shared" si="10"/>
-        <v>153911666.17697775</v>
+        <v>117200912.32697779</v>
       </c>
       <c r="R64" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>25651944.362829626</v>
+        <v>23440182.465395559</v>
       </c>
       <c r="T64" t="s">
         <v>122</v>
@@ -8757,47 +8770,47 @@
       </c>
       <c r="H65" s="135">
         <f t="shared" si="12"/>
-        <v>3215155706.6509838</v>
+        <v>3403989688.2226486</v>
       </c>
       <c r="I65" s="135">
         <f t="shared" si="12"/>
-        <v>923636133.94727707</v>
+        <v>974588489.65190494</v>
       </c>
       <c r="J65" s="135">
         <f t="shared" si="12"/>
-        <v>2190086878.2080727</v>
+        <v>2299948046.8379369</v>
       </c>
       <c r="K65" s="135">
         <f t="shared" si="12"/>
-        <v>6328878718.8063326</v>
+        <v>6678526224.7124891</v>
       </c>
       <c r="L65" s="189">
         <f t="shared" si="5"/>
-        <v>0.71448445919535764</v>
+        <v>0.75395712414373617</v>
       </c>
       <c r="M65" s="181">
         <f>SUM(M51:M64)</f>
-        <v>2086188544.7099864</v>
+        <v>1736541038.8038306</v>
       </c>
       <c r="N65" s="181">
         <f t="shared" ca="1" si="7"/>
-        <v>347698090.78499776</v>
+        <v>347308207.76076615</v>
       </c>
       <c r="O65" s="181">
         <f>SUM(O51:O64)</f>
-        <v>2529086821.7371621</v>
+        <v>2179439315.8310056</v>
       </c>
       <c r="P65" s="181">
         <f t="shared" ca="1" si="9"/>
-        <v>421514470.289527</v>
+        <v>435887863.16620111</v>
       </c>
       <c r="Q65" s="186">
         <f>SUM(Q51:Q64)</f>
-        <v>2529086821.7371621</v>
+        <v>2179439315.8310056</v>
       </c>
       <c r="R65" s="186">
         <f t="shared" ca="1" si="11"/>
-        <v>421514470.289527</v>
+        <v>435887863.16620111</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8806,21 +8819,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="293" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
-      <c r="F67" s="293"/>
-      <c r="G67" s="260" t="s">
+      <c r="C67" s="294"/>
+      <c r="D67" s="294"/>
+      <c r="E67" s="294"/>
+      <c r="F67" s="296"/>
+      <c r="G67" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="264"/>
+      <c r="I67" s="264"/>
+      <c r="J67" s="264"/>
+      <c r="K67" s="264"/>
+      <c r="L67" s="265"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -8882,35 +8895,35 @@
       </c>
       <c r="E69" s="114">
         <f>IFERROR($C$31,0)</f>
-        <v>230771202.18516701</v>
+        <v>239090594.19514599</v>
       </c>
       <c r="F69" s="187">
         <f t="shared" ref="F69:F74" si="13">IFERROR(E69/D69,0)</f>
-        <v>0.90054417610762749</v>
+        <v>0.93300914553362835</v>
       </c>
       <c r="G69" s="184">
         <f>D69*$H$40-E69</f>
-        <v>12673425.954549372</v>
+        <v>4354033.9445703924</v>
       </c>
       <c r="H69" s="184">
         <f t="shared" ref="H69:H74" ca="1" si="14">IFERROR(G69/$C$3,0)</f>
-        <v>2112237.659091562</v>
+        <v>870806.7889140785</v>
       </c>
       <c r="I69" s="204">
         <f>D69*$J$40-E69</f>
-        <v>25486301.119797617</v>
+        <v>17166909.109818637</v>
       </c>
       <c r="J69" s="204">
         <f t="shared" ref="J69:J74" ca="1" si="15">IFERROR(I69/$C$3,0)</f>
-        <v>4247716.8532996029</v>
+        <v>3433381.8219637275</v>
       </c>
       <c r="K69" s="185">
         <f>D69*$L$40-E69</f>
-        <v>25486301.119797617</v>
+        <v>17166909.109818637</v>
       </c>
       <c r="L69" s="185">
         <f t="shared" ref="L69:L74" ca="1" si="16">IFERROR(K69/$C$3,0)</f>
-        <v>4247716.8532996029</v>
+        <v>3433381.8219637275</v>
       </c>
     </row>
     <row r="70" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8938,7 +8951,7 @@
       </c>
       <c r="H70" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>-7924974.1248717802</v>
+        <v>-9509968.9498461373</v>
       </c>
       <c r="I70" s="204">
         <f>D70*$J$40-E70</f>
@@ -8946,7 +8959,7 @@
       </c>
       <c r="J70" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>-4595320.6889970703</v>
+        <v>-5514384.8267964842</v>
       </c>
       <c r="K70" s="185">
         <f>D70*$L$40-E70</f>
@@ -8954,7 +8967,7 @@
       </c>
       <c r="L70" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>-4595320.6889970703</v>
+        <v>-5514384.8267964842</v>
       </c>
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.25">
@@ -8970,35 +8983,35 @@
       </c>
       <c r="E71" s="114">
         <f>M21</f>
-        <v>934135147.50660896</v>
+        <v>948476673.30109191</v>
       </c>
       <c r="F71" s="187">
         <f t="shared" si="13"/>
-        <v>0.86126393631748333</v>
+        <v>0.87448668999667478</v>
       </c>
       <c r="G71" s="184">
         <f>D71*$H$40-E71</f>
-        <v>96243987.983107328</v>
+        <v>81902462.188624382</v>
       </c>
       <c r="H71" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>16040664.663851222</v>
+        <v>16380492.437724877</v>
       </c>
       <c r="I71" s="204">
         <f>D71*$J$40-E71</f>
-        <v>150474468.79835558</v>
+        <v>136132943.00387263</v>
       </c>
       <c r="J71" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>25079078.133059263</v>
+        <v>27226588.600774527</v>
       </c>
       <c r="K71" s="185">
         <f>D71*$L$40-E71</f>
-        <v>150474468.79835558</v>
+        <v>136132943.00387263</v>
       </c>
       <c r="L71" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>25079078.133059263</v>
+        <v>27226588.600774527</v>
       </c>
     </row>
     <row r="72" spans="2:21" hidden="1" x14ac:dyDescent="0.25">
@@ -9100,51 +9113,51 @@
       </c>
       <c r="E74" s="115">
         <f>SUM(E69:E73)</f>
-        <v>1592036686.130723</v>
+        <v>1614697603.935185</v>
       </c>
       <c r="F74" s="177">
         <f t="shared" si="13"/>
-        <v>0.91473990523403403</v>
+        <v>0.92776023697987398</v>
       </c>
       <c r="G74" s="181">
         <f>SUM(G69:G73)</f>
-        <v>61367569.188426018</v>
+        <v>38706651.383964092</v>
       </c>
       <c r="H74" s="181">
         <f t="shared" ca="1" si="14"/>
-        <v>10227928.198071003</v>
+        <v>7741330.2767928187</v>
       </c>
       <c r="I74" s="186">
         <f>SUM(I69:I73)</f>
-        <v>148388845.78417078</v>
+        <v>125727927.97970885</v>
       </c>
       <c r="J74" s="186">
         <f t="shared" ca="1" si="15"/>
-        <v>24731474.297361795</v>
+        <v>25145585.595941771</v>
       </c>
       <c r="K74" s="186">
         <f>SUM(K69:K73)</f>
-        <v>148388845.78417078</v>
+        <v>125727927.97970885</v>
       </c>
       <c r="L74" s="186">
         <f t="shared" ca="1" si="16"/>
-        <v>24731474.297361795</v>
+        <v>25145585.595941771</v>
       </c>
     </row>
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="76" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="249" t="s">
+      <c r="B77" s="252" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="250"/>
-      <c r="D77" s="251"/>
+      <c r="C77" s="253"/>
+      <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="262" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -9152,8 +9165,8 @@
       </c>
     </row>
     <row r="79" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="258"/>
-      <c r="C79" s="258"/>
+      <c r="B79" s="261"/>
+      <c r="C79" s="261"/>
       <c r="D79" s="70" t="s">
         <v>168</v>
       </c>
@@ -9173,7 +9186,7 @@
       </c>
       <c r="D80" s="131">
         <f t="shared" ref="D80:D93" si="17">SUMIF($B$10:$B$26,$T80,$F$10:$F$26)+SUMIF($B$10:$B$26,$U80,$F$10:$F$26)</f>
-        <v>345823522.47986001</v>
+        <v>343488851.45986003</v>
       </c>
       <c r="T80" t="str">
         <f t="shared" ref="T80:U93" si="18">T51</f>
@@ -9193,7 +9206,7 @@
       </c>
       <c r="D81" s="132">
         <f t="shared" si="17"/>
-        <v>136536051.15000001</v>
+        <v>149304519.81</v>
       </c>
       <c r="T81" t="str">
         <f t="shared" si="18"/>
@@ -9233,7 +9246,7 @@
       </c>
       <c r="D83" s="131">
         <f t="shared" si="17"/>
-        <v>346086641.02977002</v>
+        <v>359312587.47977</v>
       </c>
       <c r="T83" t="str">
         <f t="shared" si="18"/>
@@ -9249,7 +9262,7 @@
         <v>73</v>
       </c>
       <c r="C84" s="56" t="s">
-        <v>74</v>
+        <v>222</v>
       </c>
       <c r="D84" s="132">
         <f t="shared" si="17"/>
@@ -9269,11 +9282,11 @@
         <v>75</v>
       </c>
       <c r="C85" s="55" t="s">
-        <v>74</v>
+        <v>226</v>
       </c>
       <c r="D85" s="131">
         <f t="shared" si="17"/>
-        <v>64062612.359999999</v>
+        <v>64092612.359999999</v>
       </c>
       <c r="T85" t="str">
         <f t="shared" si="18"/>
@@ -9293,7 +9306,7 @@
       </c>
       <c r="D86" s="132">
         <f t="shared" si="17"/>
-        <v>858628819.27996898</v>
+        <v>952267556.879969</v>
       </c>
       <c r="T86" t="str">
         <f t="shared" si="18"/>
@@ -9313,7 +9326,7 @@
       </c>
       <c r="D87" s="131">
         <f t="shared" si="17"/>
-        <v>260869645.919505</v>
+        <v>278739195.65947998</v>
       </c>
       <c r="T87" t="str">
         <f t="shared" si="18"/>
@@ -9333,7 +9346,7 @@
       </c>
       <c r="D88" s="132">
         <f t="shared" si="17"/>
-        <v>9813783.5199999996</v>
+        <v>11975945.619999999</v>
       </c>
       <c r="T88" t="str">
         <f t="shared" si="18"/>
@@ -9373,7 +9386,7 @@
       </c>
       <c r="D90" s="131">
         <f t="shared" si="17"/>
-        <v>514008155.46949601</v>
+        <v>534549561.39945602</v>
       </c>
       <c r="T90" t="str">
         <f t="shared" si="18"/>
@@ -9393,7 +9406,7 @@
       </c>
       <c r="D91" s="132">
         <f t="shared" si="17"/>
-        <v>137341527.88993299</v>
+        <v>141725852.38993299</v>
       </c>
       <c r="T91" t="str">
         <f t="shared" si="18"/>
@@ -9413,7 +9426,7 @@
       </c>
       <c r="D92" s="131">
         <f t="shared" si="17"/>
-        <v>18013297.6536</v>
+        <v>18820757.1204</v>
       </c>
       <c r="T92" t="str">
         <f t="shared" si="18"/>
@@ -9433,7 +9446,7 @@
       </c>
       <c r="D93" s="132">
         <f t="shared" si="17"/>
-        <v>148515138.21799999</v>
+        <v>151542165.31800002</v>
       </c>
       <c r="T93" t="str">
         <f t="shared" si="18"/>
@@ -9451,7 +9464,7 @@
       <c r="C94" s="58"/>
       <c r="D94" s="120">
         <f>SUM(D80:D93)</f>
-        <v>2896239736.3901334</v>
+        <v>3062360146.9168677</v>
       </c>
     </row>
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9463,8 +9476,8 @@
     <mergeCell ref="C78:C79"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B48:L48"/>
     <mergeCell ref="G67:L67"/>
-    <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="C49:C50"/>
@@ -10104,11 +10117,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="272" t="s">
         <v>163</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="273"/>
+      <c r="D40" s="274"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -10377,10 +10390,10 @@
       </c>
     </row>
     <row r="46" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="256" t="s">
+      <c r="B46" s="259" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="257"/>
+      <c r="C46" s="260"/>
       <c r="D46" s="47">
         <f>SUM(D42:D45)</f>
         <v>0</v>
@@ -10428,84 +10441,84 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="275" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="276"/>
+      <c r="D48" s="276"/>
+      <c r="E48" s="276"/>
+      <c r="F48" s="276"/>
+      <c r="G48" s="276"/>
+      <c r="H48" s="276"/>
+      <c r="I48" s="276"/>
+      <c r="J48" s="276"/>
+      <c r="K48" s="276"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="264"/>
+      <c r="O48" s="264"/>
+      <c r="P48" s="264"/>
+      <c r="Q48" s="264"/>
+      <c r="R48" s="265"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="253" t="s">
+      <c r="D49" s="256" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="254"/>
-      <c r="F49" s="254"/>
-      <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="E49" s="257"/>
+      <c r="F49" s="257"/>
+      <c r="G49" s="258"/>
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="266" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="266" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="268" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="268" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="270" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="270" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="262"/>
+      <c r="C50" s="262"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -10530,13 +10543,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="267"/>
+      <c r="N50" s="267"/>
+      <c r="O50" s="269"/>
+      <c r="P50" s="269"/>
+      <c r="Q50" s="271"/>
+      <c r="R50" s="271"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -11652,21 +11665,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="293" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
-      <c r="F67" s="293"/>
-      <c r="G67" s="260" t="s">
+      <c r="C67" s="294"/>
+      <c r="D67" s="294"/>
+      <c r="E67" s="294"/>
+      <c r="F67" s="296"/>
+      <c r="G67" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="264"/>
+      <c r="I67" s="264"/>
+      <c r="J67" s="264"/>
+      <c r="K67" s="264"/>
+      <c r="L67" s="265"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -11980,17 +11993,17 @@
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="76" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="249" t="s">
+      <c r="B77" s="252" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="250"/>
-      <c r="D77" s="251"/>
+      <c r="C77" s="253"/>
+      <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="262" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -11998,8 +12011,8 @@
       </c>
     </row>
     <row r="79" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="258"/>
-      <c r="C79" s="258"/>
+      <c r="B79" s="261"/>
+      <c r="C79" s="261"/>
       <c r="D79" s="70" t="s">
         <v>168</v>
       </c>
@@ -12950,11 +12963,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="272" t="s">
         <v>175</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="273"/>
+      <c r="D40" s="274"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -13223,10 +13236,10 @@
       </c>
     </row>
     <row r="46" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="256" t="s">
+      <c r="B46" s="259" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="257"/>
+      <c r="C46" s="260"/>
       <c r="D46" s="47">
         <f>SUM(D42:D45)</f>
         <v>0</v>
@@ -13274,84 +13287,84 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="275" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="276"/>
+      <c r="D48" s="276"/>
+      <c r="E48" s="276"/>
+      <c r="F48" s="276"/>
+      <c r="G48" s="276"/>
+      <c r="H48" s="276"/>
+      <c r="I48" s="276"/>
+      <c r="J48" s="276"/>
+      <c r="K48" s="276"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="264"/>
+      <c r="O48" s="264"/>
+      <c r="P48" s="264"/>
+      <c r="Q48" s="264"/>
+      <c r="R48" s="265"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="253" t="s">
+      <c r="D49" s="256" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="254"/>
-      <c r="F49" s="254"/>
-      <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="E49" s="257"/>
+      <c r="F49" s="257"/>
+      <c r="G49" s="258"/>
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="266" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="266" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="268" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="268" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="270" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="270" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="262"/>
+      <c r="C50" s="262"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -13376,13 +13389,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="267"/>
+      <c r="N50" s="267"/>
+      <c r="O50" s="269"/>
+      <c r="P50" s="269"/>
+      <c r="Q50" s="271"/>
+      <c r="R50" s="271"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -14498,21 +14511,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="293" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
-      <c r="F67" s="293"/>
-      <c r="G67" s="260" t="s">
+      <c r="C67" s="294"/>
+      <c r="D67" s="294"/>
+      <c r="E67" s="294"/>
+      <c r="F67" s="296"/>
+      <c r="G67" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="264"/>
+      <c r="I67" s="264"/>
+      <c r="J67" s="264"/>
+      <c r="K67" s="264"/>
+      <c r="L67" s="265"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -14826,17 +14839,17 @@
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="76" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="249" t="s">
+      <c r="B77" s="252" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="250"/>
-      <c r="D77" s="251"/>
+      <c r="C77" s="253"/>
+      <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="262" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -14844,8 +14857,8 @@
       </c>
     </row>
     <row r="79" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="258"/>
-      <c r="C79" s="258"/>
+      <c r="B79" s="261"/>
+      <c r="C79" s="261"/>
       <c r="D79" s="70" t="s">
         <v>168</v>
       </c>
@@ -15796,11 +15809,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="269" t="s">
+      <c r="B40" s="272" t="s">
         <v>177</v>
       </c>
-      <c r="C40" s="270"/>
-      <c r="D40" s="271"/>
+      <c r="C40" s="273"/>
+      <c r="D40" s="274"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -16069,10 +16082,10 @@
       </c>
     </row>
     <row r="46" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="256" t="s">
+      <c r="B46" s="259" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="257"/>
+      <c r="C46" s="260"/>
       <c r="D46" s="47">
         <f>SUM(D42:D45)</f>
         <v>0</v>
@@ -16120,84 +16133,84 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="275" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="273"/>
-      <c r="L48" s="283"/>
-      <c r="M48" s="260" t="s">
+      <c r="C48" s="276"/>
+      <c r="D48" s="276"/>
+      <c r="E48" s="276"/>
+      <c r="F48" s="276"/>
+      <c r="G48" s="276"/>
+      <c r="H48" s="276"/>
+      <c r="I48" s="276"/>
+      <c r="J48" s="276"/>
+      <c r="K48" s="276"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="261"/>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="262"/>
+      <c r="N48" s="264"/>
+      <c r="O48" s="264"/>
+      <c r="P48" s="264"/>
+      <c r="Q48" s="264"/>
+      <c r="R48" s="265"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="284" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="284" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="253" t="s">
+      <c r="D49" s="256" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="254"/>
-      <c r="F49" s="254"/>
-      <c r="G49" s="255"/>
-      <c r="H49" s="285" t="s">
+      <c r="E49" s="257"/>
+      <c r="F49" s="257"/>
+      <c r="G49" s="258"/>
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="286"/>
-      <c r="J49" s="286"/>
-      <c r="K49" s="287"/>
-      <c r="L49" s="288" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="263" t="str">
+      <c r="M49" s="266" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="263" t="str">
+      <c r="N49" s="266" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="265" t="str">
+      <c r="O49" s="268" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="265" t="str">
+      <c r="P49" s="268" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="267" t="str">
+      <c r="Q49" s="270" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="267" t="str">
+      <c r="R49" s="270" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="259"/>
-      <c r="C50" s="259"/>
+      <c r="B50" s="262"/>
+      <c r="C50" s="262"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -16222,13 +16235,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="289"/>
-      <c r="M50" s="264"/>
-      <c r="N50" s="264"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="268"/>
-      <c r="R50" s="268"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="267"/>
+      <c r="N50" s="267"/>
+      <c r="O50" s="269"/>
+      <c r="P50" s="269"/>
+      <c r="Q50" s="271"/>
+      <c r="R50" s="271"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -17330,21 +17343,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="290" t="s">
+      <c r="B67" s="293" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="291"/>
-      <c r="D67" s="291"/>
-      <c r="E67" s="291"/>
-      <c r="F67" s="293"/>
-      <c r="G67" s="260" t="s">
+      <c r="C67" s="294"/>
+      <c r="D67" s="294"/>
+      <c r="E67" s="294"/>
+      <c r="F67" s="296"/>
+      <c r="G67" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="261"/>
-      <c r="I67" s="261"/>
-      <c r="J67" s="261"/>
-      <c r="K67" s="261"/>
-      <c r="L67" s="262"/>
+      <c r="H67" s="264"/>
+      <c r="I67" s="264"/>
+      <c r="J67" s="264"/>
+      <c r="K67" s="264"/>
+      <c r="L67" s="265"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -17658,17 +17671,17 @@
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="76" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="249" t="s">
+      <c r="B77" s="252" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="250"/>
-      <c r="D77" s="251"/>
+      <c r="C77" s="253"/>
+      <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="262" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -17676,8 +17689,8 @@
       </c>
     </row>
     <row r="79" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="258"/>
-      <c r="C79" s="258"/>
+      <c r="B79" s="261"/>
+      <c r="C79" s="261"/>
       <c r="D79" s="70" t="s">
         <v>168</v>
       </c>
@@ -18100,10 +18113,10 @@
       <c r="AM1" s="20"/>
     </row>
     <row r="3" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B3" s="236" t="s">
+      <c r="B3" s="239" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="236"/>
+      <c r="C3" s="239"/>
       <c r="D3" s="17" t="s">
         <v>29</v>
       </c>
@@ -20148,13 +20161,13 @@
       </c>
     </row>
     <row r="29" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B29" s="238" t="s">
+      <c r="B29" s="241" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="238"/>
-      <c r="D29" s="238"/>
-      <c r="E29" s="238"/>
-      <c r="F29" s="238"/>
+      <c r="C29" s="241"/>
+      <c r="D29" s="241"/>
+      <c r="E29" s="241"/>
+      <c r="F29" s="241"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -20717,10 +20730,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="243" t="s">
+      <c r="B44" s="246" t="s">
         <v>145</v>
       </c>
-      <c r="C44" s="244"/>
+      <c r="C44" s="247"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>10658901739</v>
@@ -20760,23 +20773,23 @@
       <c r="N46" s="97"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="245" t="s">
+      <c r="B47" s="248" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="245" t="s">
+      <c r="C47" s="248" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="246" t="s">
+      <c r="D47" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="E47" s="247"/>
-      <c r="F47" s="248"/>
+      <c r="E47" s="250"/>
+      <c r="F47" s="251"/>
       <c r="G47" s="98" t="s">
         <v>138</v>
       </c>
       <c r="H47" s="98"/>
       <c r="I47" s="98"/>
-      <c r="J47" s="245" t="s">
+      <c r="J47" s="248" t="s">
         <v>139</v>
       </c>
       <c r="K47" s="99" t="s">
@@ -20784,13 +20797,13 @@
       </c>
       <c r="L47" s="99"/>
       <c r="M47" s="99"/>
-      <c r="N47" s="242" t="s">
+      <c r="N47" s="245" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="245"/>
-      <c r="C48" s="245"/>
+      <c r="B48" s="248"/>
+      <c r="C48" s="248"/>
       <c r="D48" s="100" t="s">
         <v>149</v>
       </c>
@@ -20809,7 +20822,7 @@
       <c r="I48" s="100" t="s">
         <v>130</v>
       </c>
-      <c r="J48" s="245"/>
+      <c r="J48" s="248"/>
       <c r="K48" s="101" t="s">
         <v>142</v>
       </c>
@@ -20819,7 +20832,7 @@
       <c r="M48" s="101" t="s">
         <v>145</v>
       </c>
-      <c r="N48" s="242"/>
+      <c r="N48" s="245"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -21496,15 +21509,15 @@
       </c>
     </row>
     <row r="63" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B63" s="239" t="s">
+      <c r="B63" s="242" t="s">
         <v>144</v>
       </c>
-      <c r="C63" s="240"/>
-      <c r="D63" s="240"/>
-      <c r="E63" s="240"/>
-      <c r="F63" s="240"/>
-      <c r="G63" s="240"/>
-      <c r="H63" s="241"/>
+      <c r="C63" s="243"/>
+      <c r="D63" s="243"/>
+      <c r="E63" s="243"/>
+      <c r="F63" s="243"/>
+      <c r="G63" s="243"/>
+      <c r="H63" s="244"/>
     </row>
     <row r="64" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B64" s="224" t="s">
@@ -22284,10 +22297,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="243" t="s">
+      <c r="B44" s="246" t="s">
         <v>145</v>
       </c>
-      <c r="C44" s="244"/>
+      <c r="C44" s="247"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9776434571</v>
@@ -22327,23 +22340,23 @@
       <c r="N46" s="97"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="245" t="s">
+      <c r="B47" s="248" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="245" t="s">
+      <c r="C47" s="248" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="246" t="s">
+      <c r="D47" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="E47" s="247"/>
-      <c r="F47" s="248"/>
+      <c r="E47" s="250"/>
+      <c r="F47" s="251"/>
       <c r="G47" s="98" t="s">
         <v>138</v>
       </c>
       <c r="H47" s="98"/>
       <c r="I47" s="98"/>
-      <c r="J47" s="245" t="s">
+      <c r="J47" s="248" t="s">
         <v>139</v>
       </c>
       <c r="K47" s="99" t="s">
@@ -22351,13 +22364,13 @@
       </c>
       <c r="L47" s="99"/>
       <c r="M47" s="99"/>
-      <c r="N47" s="242" t="s">
+      <c r="N47" s="245" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="245"/>
-      <c r="C48" s="245"/>
+      <c r="B48" s="248"/>
+      <c r="C48" s="248"/>
       <c r="D48" s="100" t="s">
         <v>149</v>
       </c>
@@ -22376,7 +22389,7 @@
       <c r="I48" s="100" t="s">
         <v>130</v>
       </c>
-      <c r="J48" s="245"/>
+      <c r="J48" s="248"/>
       <c r="K48" s="101" t="s">
         <v>142</v>
       </c>
@@ -22386,7 +22399,7 @@
       <c r="M48" s="101" t="s">
         <v>145</v>
       </c>
-      <c r="N48" s="242"/>
+      <c r="N48" s="245"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -23063,15 +23076,15 @@
       </c>
     </row>
     <row r="63" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B63" s="239" t="s">
+      <c r="B63" s="242" t="s">
         <v>144</v>
       </c>
-      <c r="C63" s="240"/>
-      <c r="D63" s="240"/>
-      <c r="E63" s="240"/>
-      <c r="F63" s="240"/>
-      <c r="G63" s="240"/>
-      <c r="H63" s="241"/>
+      <c r="C63" s="243"/>
+      <c r="D63" s="243"/>
+      <c r="E63" s="243"/>
+      <c r="F63" s="243"/>
+      <c r="G63" s="243"/>
+      <c r="H63" s="244"/>
     </row>
     <row r="64" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B64" s="224" t="s">
@@ -24003,10 +24016,10 @@
       <c r="N43" s="24"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="256" t="s">
+      <c r="B44" s="259" t="s">
         <v>145</v>
       </c>
-      <c r="C44" s="257"/>
+      <c r="C44" s="260"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9764990416</v>
@@ -24071,23 +24084,23 @@
       <c r="Q46" s="48"/>
     </row>
     <row r="47" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="258" t="s">
+      <c r="B47" s="261" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="258" t="s">
+      <c r="C47" s="261" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="253" t="s">
+      <c r="D47" s="256" t="s">
         <v>137</v>
       </c>
-      <c r="E47" s="254"/>
-      <c r="F47" s="255"/>
+      <c r="E47" s="257"/>
+      <c r="F47" s="258"/>
       <c r="G47" s="69" t="s">
         <v>138</v>
       </c>
       <c r="H47" s="69"/>
       <c r="I47" s="69"/>
-      <c r="J47" s="258" t="s">
+      <c r="J47" s="261" t="s">
         <v>139</v>
       </c>
       <c r="K47" s="35" t="s">
@@ -24095,13 +24108,13 @@
       </c>
       <c r="L47" s="35"/>
       <c r="M47" s="35"/>
-      <c r="N47" s="252" t="s">
+      <c r="N47" s="255" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="48" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="258"/>
-      <c r="C48" s="258"/>
+      <c r="B48" s="261"/>
+      <c r="C48" s="261"/>
       <c r="D48" s="70" t="s">
         <v>149</v>
       </c>
@@ -24120,7 +24133,7 @@
       <c r="I48" s="70" t="s">
         <v>130</v>
       </c>
-      <c r="J48" s="258"/>
+      <c r="J48" s="261"/>
       <c r="K48" s="34" t="s">
         <v>142</v>
       </c>
@@ -24130,7 +24143,7 @@
       <c r="M48" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="N48" s="252"/>
+      <c r="N48" s="255"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -24822,15 +24835,15 @@
       <c r="N62" s="24"/>
     </row>
     <row r="63" spans="2:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="249" t="s">
+      <c r="B63" s="252" t="s">
         <v>144</v>
       </c>
-      <c r="C63" s="250"/>
-      <c r="D63" s="250"/>
-      <c r="E63" s="250"/>
-      <c r="F63" s="250"/>
-      <c r="G63" s="250"/>
-      <c r="H63" s="251"/>
+      <c r="C63" s="253"/>
+      <c r="D63" s="253"/>
+      <c r="E63" s="253"/>
+      <c r="F63" s="253"/>
+      <c r="G63" s="253"/>
+      <c r="H63" s="254"/>
       <c r="I63" s="24"/>
       <c r="J63" s="24"/>
       <c r="K63" s="24"/>
@@ -25780,11 +25793,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="269" t="s">
+      <c r="B41" s="272" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="270"/>
-      <c r="D41" s="271"/>
+      <c r="C41" s="273"/>
+      <c r="D41" s="274"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -26005,10 +26018,10 @@
       </c>
     </row>
     <row r="46" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="256" t="s">
+      <c r="B46" s="259" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="257"/>
+      <c r="C46" s="260"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>9680534906.7669907</v>
@@ -26055,59 +26068,59 @@
       </c>
     </row>
     <row r="48" spans="2:19" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="275" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="260" t="s">
+      <c r="C48" s="276"/>
+      <c r="D48" s="276"/>
+      <c r="E48" s="276"/>
+      <c r="F48" s="276"/>
+      <c r="G48" s="276"/>
+      <c r="H48" s="276"/>
+      <c r="I48" s="276"/>
+      <c r="J48" s="276"/>
+      <c r="K48" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="261"/>
-      <c r="M48" s="261"/>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
+      <c r="L48" s="264"/>
+      <c r="M48" s="264"/>
+      <c r="N48" s="264"/>
+      <c r="O48" s="264"/>
+      <c r="P48" s="265"/>
       <c r="Q48"/>
       <c r="R48"/>
     </row>
     <row r="49" spans="2:18" s="139" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="277" t="s">
+      <c r="B49" s="280" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="277" t="s">
+      <c r="C49" s="280" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="274" t="s">
+      <c r="D49" s="277" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
+      <c r="E49" s="278"/>
+      <c r="F49" s="279"/>
       <c r="G49" s="140" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="140"/>
       <c r="I49" s="140"/>
-      <c r="J49" s="274" t="s">
+      <c r="J49" s="277" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="263" t="str">
+      <c r="K49" s="266" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="263" t="str">
+      <c r="L49" s="266" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="268" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
@@ -26122,7 +26135,7 @@
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="267" t="str">
+      <c r="P49" s="270" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -26131,8 +26144,8 @@
       <c r="R49"/>
     </row>
     <row r="50" spans="2:18" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="277"/>
-      <c r="C50" s="277"/>
+      <c r="B50" s="280"/>
+      <c r="C50" s="280"/>
       <c r="D50" s="141" t="s">
         <v>149</v>
       </c>
@@ -26151,13 +26164,13 @@
       <c r="I50" s="142" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="274"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="266"/>
+      <c r="J50" s="277"/>
+      <c r="K50" s="267"/>
+      <c r="L50" s="267"/>
+      <c r="M50" s="269"/>
       <c r="N50" s="188"/>
       <c r="O50" s="183"/>
-      <c r="P50" s="268"/>
+      <c r="P50" s="271"/>
       <c r="Q50"/>
       <c r="R50"/>
     </row>
@@ -27091,19 +27104,19 @@
     </row>
     <row r="67" spans="1:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="139"/>
-      <c r="B67" s="249" t="s">
+      <c r="B67" s="252" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="250"/>
-      <c r="D67" s="250"/>
-      <c r="E67" s="250"/>
-      <c r="F67" s="250"/>
-      <c r="G67" s="250"/>
-      <c r="H67" s="250"/>
-      <c r="I67" s="250"/>
-      <c r="J67" s="250"/>
-      <c r="K67" s="250"/>
-      <c r="L67" s="251"/>
+      <c r="C67" s="253"/>
+      <c r="D67" s="253"/>
+      <c r="E67" s="253"/>
+      <c r="F67" s="253"/>
+      <c r="G67" s="253"/>
+      <c r="H67" s="253"/>
+      <c r="I67" s="253"/>
+      <c r="J67" s="253"/>
+      <c r="K67" s="253"/>
+      <c r="L67" s="254"/>
       <c r="M67" s="139"/>
       <c r="N67" s="139"/>
       <c r="O67" s="139"/>
@@ -27488,20 +27501,20 @@
       <c r="I76"/>
     </row>
     <row r="77" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="249" t="s">
+      <c r="B77" s="252" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="250"/>
-      <c r="D77" s="251"/>
+      <c r="C77" s="253"/>
+      <c r="D77" s="254"/>
       <c r="G77"/>
       <c r="H77"/>
       <c r="I77"/>
     </row>
     <row r="78" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="262" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -27512,8 +27525,8 @@
       <c r="I78"/>
     </row>
     <row r="79" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="258"/>
-      <c r="C79" s="258"/>
+      <c r="B79" s="261"/>
+      <c r="C79" s="261"/>
       <c r="D79" s="70" t="s">
         <v>168</v>
       </c>
@@ -28477,11 +28490,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="278" t="s">
+      <c r="B41" s="281" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="279"/>
-      <c r="D41" s="280"/>
+      <c r="C41" s="282"/>
+      <c r="D41" s="283"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -28702,10 +28715,10 @@
       </c>
     </row>
     <row r="46" spans="2:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="256" t="s">
+      <c r="B46" s="259" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="257"/>
+      <c r="C46" s="260"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10097522879.624619</v>
@@ -28755,80 +28768,80 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="275" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="260" t="s">
+      <c r="C48" s="276"/>
+      <c r="D48" s="276"/>
+      <c r="E48" s="276"/>
+      <c r="F48" s="276"/>
+      <c r="G48" s="276"/>
+      <c r="H48" s="276"/>
+      <c r="I48" s="276"/>
+      <c r="J48" s="276"/>
+      <c r="K48" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="261"/>
-      <c r="M48" s="261"/>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
+      <c r="L48" s="264"/>
+      <c r="M48" s="264"/>
+      <c r="N48" s="264"/>
+      <c r="O48" s="264"/>
+      <c r="P48" s="265"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="258" t="s">
+      <c r="B49" s="261" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="258" t="s">
+      <c r="C49" s="261" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="253" t="s">
+      <c r="D49" s="256" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="254"/>
-      <c r="F49" s="255"/>
+      <c r="E49" s="257"/>
+      <c r="F49" s="258"/>
       <c r="G49" s="112" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="112"/>
       <c r="I49" s="112"/>
-      <c r="J49" s="253" t="s">
+      <c r="J49" s="256" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="263" t="str">
+      <c r="K49" s="266" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="263" t="str">
+      <c r="L49" s="266" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="268" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="265" t="str">
+      <c r="N49" s="268" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="267" t="str">
+      <c r="O49" s="270" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="267" t="str">
+      <c r="P49" s="270" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="258"/>
-      <c r="C50" s="258"/>
+      <c r="B50" s="261"/>
+      <c r="C50" s="261"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -28847,13 +28860,13 @@
       <c r="I50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="253"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="266"/>
-      <c r="N50" s="266"/>
-      <c r="O50" s="268"/>
-      <c r="P50" s="268"/>
+      <c r="J50" s="256"/>
+      <c r="K50" s="267"/>
+      <c r="L50" s="267"/>
+      <c r="M50" s="269"/>
+      <c r="N50" s="269"/>
+      <c r="O50" s="271"/>
+      <c r="P50" s="271"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="167" t="s">
@@ -29759,19 +29772,19 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:16" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="249" t="s">
+      <c r="B67" s="252" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="250"/>
-      <c r="D67" s="250"/>
-      <c r="E67" s="250"/>
-      <c r="F67" s="250"/>
-      <c r="G67" s="250"/>
-      <c r="H67" s="250"/>
-      <c r="I67" s="250"/>
-      <c r="J67" s="250"/>
-      <c r="K67" s="250"/>
-      <c r="L67" s="251"/>
+      <c r="C67" s="253"/>
+      <c r="D67" s="253"/>
+      <c r="E67" s="253"/>
+      <c r="F67" s="253"/>
+      <c r="G67" s="253"/>
+      <c r="H67" s="253"/>
+      <c r="I67" s="253"/>
+      <c r="J67" s="253"/>
+      <c r="K67" s="253"/>
+      <c r="L67" s="254"/>
     </row>
     <row r="68" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -30083,17 +30096,17 @@
       </c>
     </row>
     <row r="77" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="249" t="s">
+      <c r="B77" s="252" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="250"/>
-      <c r="D77" s="251"/>
+      <c r="C77" s="253"/>
+      <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="262" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -30101,8 +30114,8 @@
       </c>
     </row>
     <row r="79" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="258"/>
-      <c r="C79" s="258"/>
+      <c r="B79" s="261"/>
+      <c r="C79" s="261"/>
       <c r="D79" s="70" t="s">
         <v>168</v>
       </c>
@@ -31062,11 +31075,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="269" t="s">
+      <c r="B41" s="272" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="270"/>
-      <c r="D41" s="271"/>
+      <c r="C41" s="273"/>
+      <c r="D41" s="274"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -31288,10 +31301,10 @@
       </c>
     </row>
     <row r="46" spans="2:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="256" t="s">
+      <c r="B46" s="259" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="257"/>
+      <c r="C46" s="260"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10899555455</v>
@@ -31341,80 +31354,80 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="275" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="260" t="s">
+      <c r="C48" s="276"/>
+      <c r="D48" s="276"/>
+      <c r="E48" s="276"/>
+      <c r="F48" s="276"/>
+      <c r="G48" s="276"/>
+      <c r="H48" s="276"/>
+      <c r="I48" s="276"/>
+      <c r="J48" s="276"/>
+      <c r="K48" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="261"/>
-      <c r="M48" s="261"/>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
+      <c r="L48" s="264"/>
+      <c r="M48" s="264"/>
+      <c r="N48" s="264"/>
+      <c r="O48" s="264"/>
+      <c r="P48" s="265"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="258" t="s">
+      <c r="B49" s="261" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="258" t="s">
+      <c r="C49" s="261" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="253" t="s">
+      <c r="D49" s="256" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="254"/>
-      <c r="F49" s="255"/>
+      <c r="E49" s="257"/>
+      <c r="F49" s="258"/>
       <c r="G49" s="112" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="112"/>
       <c r="I49" s="112"/>
-      <c r="J49" s="253" t="s">
+      <c r="J49" s="256" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="263" t="str">
+      <c r="K49" s="266" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="263" t="str">
+      <c r="L49" s="266" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="268" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="265" t="str">
+      <c r="N49" s="268" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="267" t="str">
+      <c r="O49" s="270" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="267" t="str">
+      <c r="P49" s="270" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="258"/>
-      <c r="C50" s="258"/>
+      <c r="B50" s="261"/>
+      <c r="C50" s="261"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -31433,13 +31446,13 @@
       <c r="I50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="253"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="266"/>
-      <c r="N50" s="266"/>
-      <c r="O50" s="268"/>
-      <c r="P50" s="268"/>
+      <c r="J50" s="256"/>
+      <c r="K50" s="267"/>
+      <c r="L50" s="267"/>
+      <c r="M50" s="269"/>
+      <c r="N50" s="269"/>
+      <c r="O50" s="271"/>
+      <c r="P50" s="271"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -32345,19 +32358,19 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:16" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="249" t="s">
+      <c r="B67" s="252" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="250"/>
-      <c r="D67" s="250"/>
-      <c r="E67" s="250"/>
-      <c r="F67" s="250"/>
-      <c r="G67" s="250"/>
-      <c r="H67" s="250"/>
-      <c r="I67" s="250"/>
-      <c r="J67" s="250"/>
-      <c r="K67" s="250"/>
-      <c r="L67" s="251"/>
+      <c r="C67" s="253"/>
+      <c r="D67" s="253"/>
+      <c r="E67" s="253"/>
+      <c r="F67" s="253"/>
+      <c r="G67" s="253"/>
+      <c r="H67" s="253"/>
+      <c r="I67" s="253"/>
+      <c r="J67" s="253"/>
+      <c r="K67" s="253"/>
+      <c r="L67" s="254"/>
     </row>
     <row r="68" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -32669,17 +32682,17 @@
       </c>
     </row>
     <row r="77" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="249" t="s">
+      <c r="B77" s="252" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="250"/>
-      <c r="D77" s="251"/>
+      <c r="C77" s="253"/>
+      <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="262" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -32687,8 +32700,8 @@
       </c>
     </row>
     <row r="79" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B79" s="258"/>
-      <c r="C79" s="258"/>
+      <c r="B79" s="261"/>
+      <c r="C79" s="261"/>
       <c r="D79" s="70" t="s">
         <v>168</v>
       </c>
@@ -33656,11 +33669,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" s="191" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="269" t="s">
+      <c r="B41" s="272" t="s">
         <v>189</v>
       </c>
-      <c r="C41" s="270"/>
-      <c r="D41" s="271"/>
+      <c r="C41" s="273"/>
+      <c r="D41" s="274"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -33882,10 +33895,10 @@
       </c>
     </row>
     <row r="46" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B46" s="256" t="s">
+      <c r="B46" s="259" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="257"/>
+      <c r="C46" s="260"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>11281613287.225662</v>
@@ -33935,80 +33948,80 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="272" t="s">
+      <c r="B48" s="275" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="273"/>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="273"/>
-      <c r="H48" s="273"/>
-      <c r="I48" s="273"/>
-      <c r="J48" s="273"/>
-      <c r="K48" s="260" t="s">
+      <c r="C48" s="276"/>
+      <c r="D48" s="276"/>
+      <c r="E48" s="276"/>
+      <c r="F48" s="276"/>
+      <c r="G48" s="276"/>
+      <c r="H48" s="276"/>
+      <c r="I48" s="276"/>
+      <c r="J48" s="276"/>
+      <c r="K48" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="261"/>
-      <c r="M48" s="261"/>
-      <c r="N48" s="261"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
+      <c r="L48" s="264"/>
+      <c r="M48" s="264"/>
+      <c r="N48" s="264"/>
+      <c r="O48" s="264"/>
+      <c r="P48" s="265"/>
     </row>
     <row r="49" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="258" t="s">
+      <c r="B49" s="261" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="258" t="s">
+      <c r="C49" s="261" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="253" t="s">
+      <c r="D49" s="256" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="254"/>
-      <c r="F49" s="255"/>
+      <c r="E49" s="257"/>
+      <c r="F49" s="258"/>
       <c r="G49" s="112" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="112"/>
       <c r="I49" s="112"/>
-      <c r="J49" s="253" t="s">
+      <c r="J49" s="256" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="263" t="str">
+      <c r="K49" s="266" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="263" t="str">
+      <c r="L49" s="266" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="268" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="265" t="str">
+      <c r="N49" s="268" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="281" t="str">
+      <c r="O49" s="284" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="281" t="str">
+      <c r="P49" s="284" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="258"/>
-      <c r="C50" s="258"/>
+      <c r="B50" s="261"/>
+      <c r="C50" s="261"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -34027,13 +34040,13 @@
       <c r="I50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="253"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="266"/>
-      <c r="N50" s="266"/>
-      <c r="O50" s="282"/>
-      <c r="P50" s="282"/>
+      <c r="J50" s="256"/>
+      <c r="K50" s="267"/>
+      <c r="L50" s="267"/>
+      <c r="M50" s="269"/>
+      <c r="N50" s="269"/>
+      <c r="O50" s="285"/>
+      <c r="P50" s="285"/>
     </row>
     <row r="51" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -34939,19 +34952,19 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:16" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="249" t="s">
+      <c r="B67" s="252" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="250"/>
-      <c r="D67" s="250"/>
-      <c r="E67" s="250"/>
-      <c r="F67" s="250"/>
-      <c r="G67" s="250"/>
-      <c r="H67" s="250"/>
-      <c r="I67" s="250"/>
-      <c r="J67" s="250"/>
-      <c r="K67" s="250"/>
-      <c r="L67" s="251"/>
+      <c r="C67" s="253"/>
+      <c r="D67" s="253"/>
+      <c r="E67" s="253"/>
+      <c r="F67" s="253"/>
+      <c r="G67" s="253"/>
+      <c r="H67" s="253"/>
+      <c r="I67" s="253"/>
+      <c r="J67" s="253"/>
+      <c r="K67" s="253"/>
+      <c r="L67" s="254"/>
     </row>
     <row r="68" spans="2:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -35263,17 +35276,17 @@
       </c>
     </row>
     <row r="77" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="249" t="s">
+      <c r="B77" s="252" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="250"/>
-      <c r="D77" s="251"/>
+      <c r="C77" s="253"/>
+      <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="259" t="s">
+      <c r="B78" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="262" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -35281,8 +35294,8 @@
       </c>
     </row>
     <row r="79" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B79" s="258"/>
-      <c r="C79" s="258"/>
+      <c r="B79" s="261"/>
+      <c r="C79" s="261"/>
       <c r="D79" s="70" t="s">
         <v>168</v>
       </c>

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -909,7 +909,7 @@
     <t>RONALD</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL —  25 SEPTEMBER 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL —  26 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>
@@ -1806,7 +1806,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="299">
+  <cellXfs count="297">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2484,11 +2484,13 @@
     <xf numFmtId="0" fontId="9" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2563,6 +2565,33 @@
     <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2593,33 +2622,6 @@
     <xf numFmtId="0" fontId="48" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2633,6 +2635,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2656,23 +2667,8 @@
     <xf numFmtId="0" fontId="29" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4312,11 +4308,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="272" t="s">
+      <c r="B40" s="262" t="s">
         <v>219</v>
       </c>
-      <c r="C40" s="273"/>
-      <c r="D40" s="274"/>
+      <c r="C40" s="263"/>
+      <c r="D40" s="264"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -4636,33 +4632,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="275" t="s">
+      <c r="B48" s="265" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="276"/>
-      <c r="D48" s="276"/>
-      <c r="E48" s="276"/>
-      <c r="F48" s="276"/>
-      <c r="G48" s="276"/>
-      <c r="H48" s="276"/>
-      <c r="I48" s="276"/>
-      <c r="J48" s="276"/>
-      <c r="K48" s="276"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="263" t="s">
+      <c r="C48" s="266"/>
+      <c r="D48" s="266"/>
+      <c r="E48" s="266"/>
+      <c r="F48" s="266"/>
+      <c r="G48" s="266"/>
+      <c r="H48" s="266"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="266"/>
+      <c r="K48" s="266"/>
+      <c r="L48" s="289"/>
+      <c r="M48" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="264"/>
-      <c r="O48" s="264"/>
-      <c r="P48" s="264"/>
-      <c r="Q48" s="264"/>
-      <c r="R48" s="265"/>
+      <c r="N48" s="273"/>
+      <c r="O48" s="273"/>
+      <c r="P48" s="273"/>
+      <c r="Q48" s="273"/>
+      <c r="R48" s="274"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="290" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="290" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="256" t="s">
@@ -4671,49 +4667,49 @@
       <c r="E49" s="257"/>
       <c r="F49" s="257"/>
       <c r="G49" s="258"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="291" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="292"/>
+      <c r="J49" s="292"/>
+      <c r="K49" s="293"/>
+      <c r="L49" s="294" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="266" t="str">
+      <c r="M49" s="275" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="266" t="str">
+      <c r="N49" s="275" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="268" t="str">
+      <c r="O49" s="277" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="268" t="str">
+      <c r="P49" s="277" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="270" t="str">
+      <c r="Q49" s="279" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="270" t="str">
+      <c r="R49" s="279" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="262"/>
-      <c r="C50" s="262"/>
+      <c r="B50" s="271"/>
+      <c r="C50" s="271"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -4738,13 +4734,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="267"/>
-      <c r="N50" s="267"/>
-      <c r="O50" s="269"/>
-      <c r="P50" s="269"/>
-      <c r="Q50" s="271"/>
-      <c r="R50" s="271"/>
+      <c r="L50" s="295"/>
+      <c r="M50" s="276"/>
+      <c r="N50" s="276"/>
+      <c r="O50" s="278"/>
+      <c r="P50" s="278"/>
+      <c r="Q50" s="280"/>
+      <c r="R50" s="280"/>
       <c r="T50" s="172" t="s">
         <v>216</v>
       </c>
@@ -5860,21 +5856,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="293" t="s">
+      <c r="B67" s="286" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="294"/>
-      <c r="D67" s="294"/>
-      <c r="E67" s="294"/>
-      <c r="F67" s="295"/>
-      <c r="G67" s="263" t="s">
+      <c r="C67" s="287"/>
+      <c r="D67" s="287"/>
+      <c r="E67" s="287"/>
+      <c r="F67" s="288"/>
+      <c r="G67" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="264"/>
-      <c r="I67" s="264"/>
-      <c r="J67" s="264"/>
-      <c r="K67" s="264"/>
-      <c r="L67" s="265"/>
+      <c r="H67" s="273"/>
+      <c r="I67" s="273"/>
+      <c r="J67" s="273"/>
+      <c r="K67" s="273"/>
+      <c r="L67" s="274"/>
     </row>
     <row r="68" spans="2:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -6193,10 +6189,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="262" t="s">
+      <c r="B78" s="271" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="262" t="s">
+      <c r="C78" s="271" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -6508,12 +6504,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -6528,6 +6518,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -6605,7 +6601,7 @@
       </c>
       <c r="C3" s="75">
         <f ca="1">IF($J$5&lt;&gt;"",$J$5,MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),9,1)),EOMONTH(DATE(YEAR(TODAY()),9,1),0),11)-MAX(0,$J$3-$J$4)))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="76" t="s">
         <v>104</v>
@@ -6732,20 +6728,20 @@
       <c r="B10" s="72" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="237">
-        <v>129114514.549408</v>
-      </c>
-      <c r="D10" s="237">
-        <v>37038940.117797002</v>
-      </c>
-      <c r="E10" s="237">
-        <v>181176342.72703999</v>
-      </c>
-      <c r="F10" s="237">
-        <v>141725852.38993299</v>
-      </c>
-      <c r="G10" s="237">
-        <v>489055649.78417802</v>
+      <c r="C10" s="236">
+        <v>130775176.729406</v>
+      </c>
+      <c r="D10" s="236">
+        <v>38616940.117797002</v>
+      </c>
+      <c r="E10" s="236">
+        <v>185920937.347022</v>
+      </c>
+      <c r="F10" s="236">
+        <v>148907397.44993299</v>
+      </c>
+      <c r="G10" s="236">
+        <v>504220451.64415801</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="111"/>
@@ -6757,20 +6753,20 @@
       <c r="B11" s="72" t="s">
         <v>182</v>
       </c>
-      <c r="C11" s="237">
-        <v>4173423.4199979999</v>
-      </c>
-      <c r="D11" s="237">
-        <v>30250983.5</v>
-      </c>
-      <c r="E11" s="237">
-        <v>199157658.6392</v>
-      </c>
-      <c r="F11" s="237" t="s">
+      <c r="C11" s="236">
+        <v>5673423.4199980004</v>
+      </c>
+      <c r="D11" s="236">
+        <v>32629360.699999999</v>
+      </c>
+      <c r="E11" s="236">
+        <v>271000001.35890001</v>
+      </c>
+      <c r="F11" s="236" t="s">
         <v>165</v>
       </c>
-      <c r="G11" s="237">
-        <v>233582065.55919799</v>
+      <c r="G11" s="236">
+        <v>309302785.47889799</v>
       </c>
       <c r="H11" s="111"/>
       <c r="I11" s="111"/>
@@ -6782,20 +6778,20 @@
       <c r="B12" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="237">
-        <v>158097388.15795001</v>
-      </c>
-      <c r="D12" s="237">
-        <v>67902257.621514007</v>
-      </c>
-      <c r="E12" s="237">
-        <v>144886174.379583</v>
-      </c>
-      <c r="F12" s="237">
-        <v>67696580.700000003</v>
-      </c>
-      <c r="G12" s="237">
-        <v>438582400.859047</v>
+      <c r="C12" s="236">
+        <v>158839730.55793801</v>
+      </c>
+      <c r="D12" s="236">
+        <v>68100455.821513996</v>
+      </c>
+      <c r="E12" s="236">
+        <v>149647841.07957</v>
+      </c>
+      <c r="F12" s="236">
+        <v>68507391.549999997</v>
+      </c>
+      <c r="G12" s="236">
+        <v>445095419.009022</v>
       </c>
       <c r="H12" s="111"/>
       <c r="I12" s="111"/>
@@ -6807,20 +6803,20 @@
       <c r="B13" s="72" t="s">
         <v>114</v>
       </c>
-      <c r="C13" s="237">
-        <v>30349577.699947</v>
-      </c>
-      <c r="D13" s="237">
+      <c r="C13" s="236">
+        <v>31056577.699947</v>
+      </c>
+      <c r="D13" s="236">
         <v>22046277.749963999</v>
       </c>
-      <c r="E13" s="237">
-        <v>190561218.02961701</v>
-      </c>
-      <c r="F13" s="237">
-        <v>81607939.109999999</v>
-      </c>
-      <c r="G13" s="237">
-        <v>324565012.58952802</v>
+      <c r="E13" s="236">
+        <v>190861218.02961701</v>
+      </c>
+      <c r="F13" s="236">
+        <v>85824155.530000001</v>
+      </c>
+      <c r="G13" s="236">
+        <v>329788229.00952798</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="111"/>
@@ -6832,20 +6828,20 @@
       <c r="B14" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="C14" s="237">
-        <v>437151614.40455902</v>
-      </c>
-      <c r="D14" s="237">
+      <c r="C14" s="236">
+        <v>464604407.979559</v>
+      </c>
+      <c r="D14" s="236">
         <v>42720135.969465002</v>
       </c>
-      <c r="E14" s="237">
-        <v>142801315.51987499</v>
-      </c>
-      <c r="F14" s="237">
-        <v>359312587.47977</v>
-      </c>
-      <c r="G14" s="237">
-        <v>981985653.37366903</v>
+      <c r="E14" s="236">
+        <v>150846270.519853</v>
+      </c>
+      <c r="F14" s="236">
+        <v>382969885.31973499</v>
+      </c>
+      <c r="G14" s="236">
+        <v>1041140699.788612</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="111"/>
@@ -6857,20 +6853,20 @@
       <c r="B15" s="72" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="237">
-        <v>1502915183.6099081</v>
-      </c>
-      <c r="D15" s="237">
+      <c r="C15" s="236">
+        <v>1505892643.1199069</v>
+      </c>
+      <c r="D15" s="236">
         <v>11190936.014923999</v>
       </c>
-      <c r="E15" s="237">
+      <c r="E15" s="236">
         <v>76858935.799939007</v>
       </c>
-      <c r="F15" s="237">
-        <v>14632432.720000001</v>
-      </c>
-      <c r="G15" s="237">
-        <v>1605597488.1447711</v>
+      <c r="F15" s="236">
+        <v>14956757.039999999</v>
+      </c>
+      <c r="G15" s="236">
+        <v>1608899271.9747701</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="111"/>
@@ -6882,20 +6878,20 @@
       <c r="B16" s="72" t="s">
         <v>120</v>
       </c>
-      <c r="C16" s="237">
-        <v>465821952.54762101</v>
-      </c>
-      <c r="D16" s="237">
-        <v>51819828.479924001</v>
-      </c>
-      <c r="E16" s="237">
-        <v>299276352.78941</v>
-      </c>
-      <c r="F16" s="237">
-        <v>952267556.879969</v>
-      </c>
-      <c r="G16" s="237">
-        <v>1769185690.696924</v>
+      <c r="C16" s="236">
+        <v>469087694.35771102</v>
+      </c>
+      <c r="D16" s="236">
+        <v>52390125.779923998</v>
+      </c>
+      <c r="E16" s="236">
+        <v>301606082.52941</v>
+      </c>
+      <c r="F16" s="236">
+        <v>955586205.67996895</v>
+      </c>
+      <c r="G16" s="236">
+        <v>1778670108.347014</v>
       </c>
       <c r="H16" s="111"/>
       <c r="I16" s="111"/>
@@ -6907,20 +6903,20 @@
       <c r="B17" s="72" t="s">
         <v>122</v>
       </c>
-      <c r="C17" s="237">
-        <v>97903468.216019005</v>
-      </c>
-      <c r="D17" s="237">
-        <v>12915436.9209</v>
-      </c>
-      <c r="E17" s="237">
+      <c r="C17" s="236">
+        <v>98586351.086017996</v>
+      </c>
+      <c r="D17" s="236">
+        <v>13122554.039898001</v>
+      </c>
+      <c r="E17" s="236">
         <v>103260945.468842</v>
       </c>
-      <c r="F17" s="237">
+      <c r="F17" s="236">
         <v>47952973.898000002</v>
       </c>
-      <c r="G17" s="237">
-        <v>262032824.50376099</v>
+      <c r="G17" s="236">
+        <v>262922824.49275801</v>
       </c>
       <c r="H17" s="111"/>
       <c r="I17" s="111"/>
@@ -6933,20 +6929,20 @@
       <c r="B18" s="72" t="s">
         <v>123</v>
       </c>
-      <c r="C18" s="237">
-        <v>13080047.589996999</v>
-      </c>
-      <c r="D18" s="237">
-        <v>134100404.811655</v>
-      </c>
-      <c r="E18" s="237">
+      <c r="C18" s="236">
+        <v>13656047.589996999</v>
+      </c>
+      <c r="D18" s="236">
+        <v>135022363.55165499</v>
+      </c>
+      <c r="E18" s="236">
         <v>58453106.100000001</v>
       </c>
-      <c r="F18" s="237">
-        <v>103589191.42</v>
-      </c>
-      <c r="G18" s="237">
-        <v>309222749.92165202</v>
+      <c r="F18" s="236">
+        <v>104562164.42</v>
+      </c>
+      <c r="G18" s="236">
+        <v>311693681.66165203</v>
       </c>
       <c r="H18" s="111"/>
       <c r="I18" s="111"/>
@@ -6959,20 +6955,20 @@
       <c r="B19" s="72" t="s">
         <v>169</v>
       </c>
-      <c r="C19" s="237">
-        <v>46889334.859999999</v>
-      </c>
-      <c r="D19" s="237" t="s">
+      <c r="C19" s="236">
+        <v>47429875.460000001</v>
+      </c>
+      <c r="D19" s="236" t="s">
         <v>165</v>
       </c>
-      <c r="E19" s="237" t="s">
+      <c r="E19" s="236" t="s">
         <v>165</v>
       </c>
-      <c r="F19" s="237">
+      <c r="F19" s="236">
         <v>7027026.8399999999</v>
       </c>
-      <c r="G19" s="237">
-        <v>53916361.700000003</v>
+      <c r="G19" s="236">
+        <v>54456902.299999997</v>
       </c>
       <c r="H19" s="111"/>
       <c r="I19" s="111"/>
@@ -6985,19 +6981,19 @@
       <c r="B20" s="72" t="s">
         <v>170</v>
       </c>
-      <c r="C20" s="237">
+      <c r="C20" s="236">
         <v>215561847.16</v>
       </c>
-      <c r="D20" s="237" t="s">
+      <c r="D20" s="236" t="s">
         <v>165</v>
       </c>
-      <c r="E20" s="237" t="s">
+      <c r="E20" s="236" t="s">
         <v>165</v>
       </c>
-      <c r="F20" s="237">
+      <c r="F20" s="236">
         <v>11975945.619999999</v>
       </c>
-      <c r="G20" s="237">
+      <c r="G20" s="236">
         <v>227537792.78</v>
       </c>
       <c r="H20" s="111"/>
@@ -7015,27 +7011,27 @@
       <c r="B21" s="72" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="237">
-        <v>250622165.38778701</v>
-      </c>
-      <c r="D21" s="237">
-        <v>46331940.443448998</v>
-      </c>
-      <c r="E21" s="237">
-        <v>135756942.00977701</v>
-      </c>
-      <c r="F21" s="237">
-        <v>343488851.45986003</v>
-      </c>
-      <c r="G21" s="237">
-        <v>776199899.30087304</v>
+      <c r="C21" s="236">
+        <v>258036727.34778699</v>
+      </c>
+      <c r="D21" s="236">
+        <v>46523994.503447004</v>
+      </c>
+      <c r="E21" s="236">
+        <v>140234870.34977701</v>
+      </c>
+      <c r="F21" s="236">
+        <v>385081374.45986003</v>
+      </c>
+      <c r="G21" s="236">
+        <v>829876966.66087103</v>
       </c>
       <c r="H21" s="111"/>
       <c r="I21" s="111"/>
       <c r="J21" s="111"/>
       <c r="M21" s="14">
         <f>SUM(C33,C34)+M20</f>
-        <v>948476673.30109191</v>
+        <v>951040727.40107894</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>224</v>
@@ -7045,20 +7041,20 @@
       <c r="B22" s="72" t="s">
         <v>225</v>
       </c>
-      <c r="C22" s="237">
-        <v>183815526.976354</v>
-      </c>
-      <c r="D22" s="237">
-        <v>46626385.219940998</v>
-      </c>
-      <c r="E22" s="237">
-        <v>137495154.28817099</v>
-      </c>
-      <c r="F22" s="237">
-        <v>64092612.359999999</v>
-      </c>
-      <c r="G22" s="237">
-        <v>432029678.84446597</v>
+      <c r="C22" s="236">
+        <v>184450526.976354</v>
+      </c>
+      <c r="D22" s="236">
+        <v>47411295.139939003</v>
+      </c>
+      <c r="E22" s="236">
+        <v>144992226.38817099</v>
+      </c>
+      <c r="F22" s="236">
+        <v>65692612.399999999</v>
+      </c>
+      <c r="G22" s="236">
+        <v>442546660.90446401</v>
       </c>
       <c r="H22" s="111"/>
       <c r="I22" s="111"/>
@@ -7068,20 +7064,20 @@
       <c r="B23" s="72" t="s">
         <v>125</v>
       </c>
-      <c r="C23" s="237">
-        <v>241361191.13532299</v>
-      </c>
-      <c r="D23" s="237">
-        <v>63404429.039943002</v>
-      </c>
-      <c r="E23" s="237">
-        <v>176031885.582169</v>
-      </c>
-      <c r="F23" s="237">
-        <v>278739195.65947998</v>
-      </c>
-      <c r="G23" s="237">
-        <v>759536701.41691506</v>
+      <c r="C23" s="236">
+        <v>253561209.328915</v>
+      </c>
+      <c r="D23" s="236">
+        <v>63950429.039943002</v>
+      </c>
+      <c r="E23" s="236">
+        <v>180549813.52216801</v>
+      </c>
+      <c r="F23" s="236">
+        <v>297399826.70943499</v>
+      </c>
+      <c r="G23" s="236">
+        <v>795461278.60046101</v>
       </c>
       <c r="H23" s="111"/>
       <c r="I23" s="111"/>
@@ -7091,20 +7087,20 @@
       <c r="B24" s="72" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="237">
-        <v>420220553.48265302</v>
-      </c>
-      <c r="D24" s="237">
-        <v>57722998.644919001</v>
-      </c>
-      <c r="E24" s="237">
-        <v>189249443.53988701</v>
-      </c>
-      <c r="F24" s="237">
-        <v>534549561.39945602</v>
-      </c>
-      <c r="G24" s="237">
-        <v>1201742557.066915</v>
+      <c r="C24" s="236">
+        <v>428037130.09258002</v>
+      </c>
+      <c r="D24" s="236">
+        <v>58268998.644919001</v>
+      </c>
+      <c r="E24" s="236">
+        <v>192989083.319877</v>
+      </c>
+      <c r="F24" s="236">
+        <v>569324336.12944102</v>
+      </c>
+      <c r="G24" s="236">
+        <v>1248619548.1868169</v>
       </c>
       <c r="H24" s="111"/>
       <c r="I24" s="111"/>
@@ -7114,20 +7110,20 @@
       <c r="B25" s="72" t="s">
         <v>220</v>
       </c>
-      <c r="C25" s="237">
-        <v>283697018.83984798</v>
-      </c>
-      <c r="D25" s="237">
-        <v>80203472.886524007</v>
-      </c>
-      <c r="E25" s="237">
-        <v>93333896.788552999</v>
-      </c>
-      <c r="F25" s="237">
-        <v>49513514.579999998</v>
-      </c>
-      <c r="G25" s="237">
-        <v>506747903.09492499</v>
+      <c r="C25" s="236">
+        <v>309803234.24329299</v>
+      </c>
+      <c r="D25" s="236">
+        <v>81584972.886524007</v>
+      </c>
+      <c r="E25" s="236">
+        <v>96322302.232531995</v>
+      </c>
+      <c r="F25" s="236">
+        <v>50324325.43</v>
+      </c>
+      <c r="G25" s="236">
+        <v>538034834.79234898</v>
       </c>
       <c r="H25" s="111"/>
       <c r="I25" s="111"/>
@@ -7137,20 +7133,20 @@
       <c r="B26" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="237">
-        <v>426130063.79518402</v>
-      </c>
-      <c r="D26" s="237">
-        <v>281504998.24590999</v>
-      </c>
-      <c r="E26" s="237">
-        <v>248507610.975813</v>
-      </c>
-      <c r="F26" s="237">
+      <c r="C26" s="236">
+        <v>434916433.51514399</v>
+      </c>
+      <c r="D26" s="236">
+        <v>285495088.43090999</v>
+      </c>
+      <c r="E26" s="236">
+        <v>280204913.43528301</v>
+      </c>
+      <c r="F26" s="236">
         <v>18820757.1204</v>
       </c>
-      <c r="G26" s="237">
-        <v>974963430.13730705</v>
+      <c r="G26" s="236">
+        <v>1019437192.501737</v>
       </c>
       <c r="H26" s="111"/>
       <c r="I26" s="111"/>
@@ -7183,7 +7179,7 @@
     </row>
     <row r="30" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="234"/>
-      <c r="C30" s="298"/>
+      <c r="C30" s="237"/>
       <c r="G30" s="111"/>
       <c r="H30" s="111"/>
       <c r="I30" s="111"/>
@@ -7192,8 +7188,8 @@
       <c r="B31" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="C31" s="235">
-        <v>239090594.19514599</v>
+      <c r="C31" s="171">
+        <v>251052873.62514299</v>
       </c>
       <c r="G31" s="111"/>
       <c r="H31" s="111"/>
@@ -7203,8 +7199,8 @@
       <c r="B32" s="81" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="297">
-        <v>427130336.43894702</v>
+      <c r="C32" s="236">
+        <v>443836083.938923</v>
       </c>
       <c r="G32" s="111"/>
       <c r="H32" s="111"/>
@@ -7214,8 +7210,8 @@
       <c r="B33" s="81" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="237">
-        <v>503000911.10980099</v>
+      <c r="C33" s="236">
+        <v>503733073.28979498</v>
       </c>
       <c r="G33" s="111"/>
       <c r="H33" s="111"/>
@@ -7225,8 +7221,8 @@
       <c r="B34" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="237">
-        <v>445475762.19129097</v>
+      <c r="C34" s="236">
+        <v>447307654.11128402</v>
       </c>
       <c r="G34" s="111"/>
       <c r="H34" s="111"/>
@@ -7236,7 +7232,7 @@
       <c r="B35" s="81" t="s">
         <v>135</v>
       </c>
-      <c r="C35" s="236">
+      <c r="C35" s="235">
         <v>0</v>
       </c>
       <c r="G35" s="111"/>
@@ -7271,17 +7267,17 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="272" t="s">
+      <c r="B40" s="262" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="273"/>
-      <c r="D40" s="274"/>
+      <c r="C40" s="263"/>
+      <c r="D40" s="264"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
       <c r="F40" s="174">
         <f ca="1">IF(MONTH(TODAY())=9,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;9,1,0))</f>
-        <v>0.83333333333333337</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="G40" s="192" t="s">
         <v>187</v>
@@ -7368,35 +7364,35 @@
       </c>
       <c r="E42" s="46">
         <f>H65</f>
-        <v>3403989688.2226486</v>
+        <v>3504076393.5446467</v>
       </c>
       <c r="F42" s="176">
         <f>IFERROR(E42/D42,0)</f>
-        <v>0.75446611669915109</v>
+        <v>0.77664950584358994</v>
       </c>
       <c r="G42" s="184">
         <f>D42*$H$40-E42</f>
-        <v>882207043.79177761</v>
+        <v>782120338.46977949</v>
       </c>
       <c r="H42" s="184">
         <f ca="1">IFERROR(G42/$C$3,0)</f>
-        <v>176441408.75835553</v>
+        <v>195530084.61744487</v>
       </c>
       <c r="I42" s="204">
         <f>D42*$J$40-E42</f>
-        <v>1107796345.4767475</v>
+        <v>1007709640.1547494</v>
       </c>
       <c r="J42" s="204">
         <f ca="1">IFERROR(I42/$C$3,0)</f>
-        <v>221559269.09534949</v>
+        <v>251927410.03868735</v>
       </c>
       <c r="K42" s="185">
         <f>D42*$L$40-E42</f>
-        <v>1107796345.4767475</v>
+        <v>1007709640.1547494</v>
       </c>
       <c r="L42" s="185">
         <f ca="1">IFERROR(K42/$C$3,0)</f>
-        <v>221559269.09534949</v>
+        <v>251927410.03868735</v>
       </c>
       <c r="S42" s="173">
         <v>0.8</v>
@@ -7415,35 +7411,35 @@
       </c>
       <c r="E43" s="46">
         <f>I65</f>
-        <v>974588489.65190494</v>
+        <v>987882992.37589896</v>
       </c>
       <c r="F43" s="176">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.69545641121475765</v>
+        <v>0.70494323283381455</v>
       </c>
       <c r="G43" s="184">
         <f>D43*$H$40-E43</f>
-        <v>356708555.33773911</v>
+        <v>343414052.61374509</v>
       </c>
       <c r="H43" s="184">
         <f ca="1">IFERROR(G43/$C$3,0)</f>
-        <v>71341711.067547828</v>
+        <v>85853513.153436273</v>
       </c>
       <c r="I43" s="204">
         <f>D43*$J$40-E43</f>
-        <v>426776820.86351001</v>
+        <v>413482318.139516</v>
       </c>
       <c r="J43" s="204">
         <f ca="1">IFERROR(I43/$C$3,0)</f>
-        <v>85355364.172702</v>
+        <v>103370579.534879</v>
       </c>
       <c r="K43" s="185">
         <f>D43*$L$40-E43</f>
-        <v>426776820.86351001</v>
+        <v>413482318.139516</v>
       </c>
       <c r="L43" s="185">
         <f ca="1">IFERROR(K43/$C$3,0)</f>
-        <v>85355364.172702</v>
+        <v>103370579.534879</v>
       </c>
       <c r="S43" s="173">
         <v>0.85</v>
@@ -7462,35 +7458,35 @@
       </c>
       <c r="E44" s="46">
         <f>J65</f>
-        <v>2299948046.8379369</v>
+        <v>2446889611.6810222</v>
       </c>
       <c r="F44" s="176">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.78101635400470892</v>
+        <v>0.8309147703551456</v>
       </c>
       <c r="G44" s="184">
         <f>IF(D44=0,0,D44*$H$40-E44)</f>
-        <v>497625439.67431402</v>
+        <v>350683874.83122873</v>
       </c>
       <c r="H44" s="184">
         <f ca="1">IFERROR(G44/$C$3,0)</f>
-        <v>99525087.934862807</v>
+        <v>87670968.707807183</v>
       </c>
       <c r="I44" s="204">
         <f>IF(D44=0,0,D44*$J$40-E44)</f>
-        <v>644866149.49074841</v>
+        <v>497924584.64766312</v>
       </c>
       <c r="J44" s="204">
         <f ca="1">IFERROR(I44/$C$3,0)</f>
-        <v>128973229.89814968</v>
+        <v>124481146.16191578</v>
       </c>
       <c r="K44" s="185">
         <f>IF(D44=0,0,D44*$L$40-E44)</f>
-        <v>644866149.49074841</v>
+        <v>497924584.64766312</v>
       </c>
       <c r="L44" s="185">
         <f ca="1">IFERROR(K44/$C$3,0)</f>
-        <v>128973229.89814968</v>
+        <v>124481146.16191578</v>
       </c>
       <c r="S44" s="173">
         <v>0.9</v>
@@ -7509,35 +7505,35 @@
       </c>
       <c r="E45" s="46">
         <f>E74</f>
-        <v>1614697603.935185</v>
+        <v>1645929684.9651449</v>
       </c>
       <c r="F45" s="176">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.92776023697987398</v>
+        <v>0.94570532021224707</v>
       </c>
       <c r="G45" s="184">
         <f>D45*$H$40-E45</f>
-        <v>38706651.383963823</v>
+        <v>7474570.3540039063</v>
       </c>
       <c r="H45" s="184">
         <f ca="1">IFERROR(G45/$C$3,0)</f>
-        <v>7741330.2767927647</v>
+        <v>1868642.5885009766</v>
       </c>
       <c r="I45" s="204">
         <f>D45*$J$40-E45</f>
-        <v>125727927.97970867</v>
+        <v>94495846.949748755</v>
       </c>
       <c r="J45" s="204">
         <f ca="1">IFERROR(I45/$C$3,0)</f>
-        <v>25145585.595941734</v>
+        <v>23623961.737437189</v>
       </c>
       <c r="K45" s="185">
         <f>D45*$L$40-E45</f>
-        <v>125727927.97970867</v>
+        <v>94495846.949748755</v>
       </c>
       <c r="L45" s="185">
         <f ca="1">IFERROR(K45/$C$3,0)</f>
-        <v>25145585.595941734</v>
+        <v>23623961.737437189</v>
       </c>
       <c r="S45" s="173">
         <v>0.95</v>
@@ -7554,35 +7550,35 @@
       </c>
       <c r="E46" s="47">
         <f>SUM(E42:E45)</f>
-        <v>8293223828.6476746</v>
+        <v>8584778682.5667133</v>
       </c>
       <c r="F46" s="177">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.7824983784754781</v>
+        <v>0.81000772889723138</v>
       </c>
       <c r="G46" s="181">
         <f>SUM(G42:G45)</f>
-        <v>1775247690.1877944</v>
+        <v>1483692836.2687573</v>
       </c>
       <c r="H46" s="181">
         <f ca="1">IFERROR(G46/$C$3,0)</f>
-        <v>355049538.03755891</v>
+        <v>370923209.06718934</v>
       </c>
       <c r="I46" s="186">
         <f>SUM(I42:I45)</f>
-        <v>2305167243.8107147</v>
+        <v>2013612389.8916771</v>
       </c>
       <c r="J46" s="186">
         <f ca="1">IFERROR(I46/$C$3,0)</f>
-        <v>461033448.76214296</v>
+        <v>503403097.47291929</v>
       </c>
       <c r="K46" s="186">
         <f>SUM(K42:K45)</f>
-        <v>2305167243.8107147</v>
+        <v>2013612389.8916771</v>
       </c>
       <c r="L46" s="186">
         <f ca="1">IFERROR(K46/$C$3,0)</f>
-        <v>461033448.76214296</v>
+        <v>503403097.47291929</v>
       </c>
       <c r="S46" s="173">
         <v>1</v>
@@ -7595,33 +7591,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="275" t="s">
+      <c r="B48" s="265" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="276"/>
-      <c r="D48" s="276"/>
-      <c r="E48" s="276"/>
-      <c r="F48" s="276"/>
-      <c r="G48" s="276"/>
-      <c r="H48" s="276"/>
-      <c r="I48" s="276"/>
-      <c r="J48" s="276"/>
-      <c r="K48" s="276"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="263" t="s">
+      <c r="C48" s="266"/>
+      <c r="D48" s="266"/>
+      <c r="E48" s="266"/>
+      <c r="F48" s="266"/>
+      <c r="G48" s="266"/>
+      <c r="H48" s="266"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="266"/>
+      <c r="K48" s="266"/>
+      <c r="L48" s="289"/>
+      <c r="M48" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="264"/>
-      <c r="O48" s="264"/>
-      <c r="P48" s="264"/>
-      <c r="Q48" s="264"/>
-      <c r="R48" s="265"/>
+      <c r="N48" s="273"/>
+      <c r="O48" s="273"/>
+      <c r="P48" s="273"/>
+      <c r="Q48" s="273"/>
+      <c r="R48" s="274"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="290" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="290" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="256" t="s">
@@ -7630,49 +7626,49 @@
       <c r="E49" s="257"/>
       <c r="F49" s="257"/>
       <c r="G49" s="258"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="291" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="292"/>
+      <c r="J49" s="292"/>
+      <c r="K49" s="293"/>
+      <c r="L49" s="294" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="266" t="str">
+      <c r="M49" s="275" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="266" t="str">
+      <c r="N49" s="275" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="268" t="str">
+      <c r="O49" s="277" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="268" t="str">
+      <c r="P49" s="277" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="Q49" s="270" t="str">
+      <c r="Q49" s="279" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="270" t="str">
+      <c r="R49" s="279" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="262"/>
-      <c r="C50" s="262"/>
+      <c r="B50" s="271"/>
+      <c r="C50" s="271"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -7697,13 +7693,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="267"/>
-      <c r="N50" s="267"/>
-      <c r="O50" s="269"/>
-      <c r="P50" s="269"/>
-      <c r="Q50" s="271"/>
-      <c r="R50" s="271"/>
+      <c r="L50" s="295"/>
+      <c r="M50" s="276"/>
+      <c r="N50" s="276"/>
+      <c r="O50" s="278"/>
+      <c r="P50" s="278"/>
+      <c r="Q50" s="280"/>
+      <c r="R50" s="280"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -7736,47 +7732,47 @@
       </c>
       <c r="H51" s="114">
         <f t="shared" ref="H51:H64" si="1">SUMIF($B$10:$B$26,$T51,C$10:C$26)+SUMIF($B$10:$B$26,$U51,C$10:C$26)</f>
-        <v>250622165.38778701</v>
+        <v>258036727.34778699</v>
       </c>
       <c r="I51" s="114">
         <f t="shared" ref="I51:I64" si="2">SUMIF($B$10:$B$26,$T51,D$10:D$26)+SUMIF($B$10:$B$26,$U51,D$10:D$26)</f>
-        <v>46331940.443448998</v>
+        <v>46523994.503447004</v>
       </c>
       <c r="J51" s="114">
         <f t="shared" ref="J51:J64" si="3">SUMIF($B$10:$B$26,$T51,E$10:E$26)+SUMIF($B$10:$B$26,$U51,E$10:E$26)</f>
-        <v>135756942.00977701</v>
+        <v>140234870.34977701</v>
       </c>
       <c r="K51" s="114">
         <f t="shared" ref="K51:K64" si="4">SUM(H51:J51)</f>
-        <v>432711047.84101301</v>
+        <v>444795592.20101106</v>
       </c>
       <c r="L51" s="187">
         <f t="shared" ref="L51:L65" si="5">IFERROR(K51/G51,0)</f>
-        <v>0.84124877857029168</v>
+        <v>0.86474276660953886</v>
       </c>
       <c r="M51" s="184">
         <f t="shared" ref="M51:M64" si="6">G51*$H$40-K51</f>
-        <v>55938096.051460803</v>
+        <v>43853551.691462755</v>
       </c>
       <c r="N51" s="184">
         <f t="shared" ref="N51:N65" ca="1" si="7">IFERROR(M51/$C$3,0)</f>
-        <v>11187619.210292161</v>
+        <v>10963387.922865689</v>
       </c>
       <c r="O51" s="180">
         <f t="shared" ref="O51:O64" si="8">G51*$J$40-K51</f>
-        <v>81656472.04580158</v>
+        <v>69571927.685803533</v>
       </c>
       <c r="P51" s="180">
         <f t="shared" ref="P51:P65" ca="1" si="9">IFERROR(O51/$C$3,0)</f>
-        <v>16331294.409160316</v>
+        <v>17392981.921450883</v>
       </c>
       <c r="Q51" s="185">
         <f t="shared" ref="Q51:Q64" si="10">G51*$L$40-K51</f>
-        <v>81656472.04580158</v>
+        <v>69571927.685803533</v>
       </c>
       <c r="R51" s="185">
         <f t="shared" ref="R51:R65" ca="1" si="11">IFERROR(Q51/$C$3,0)</f>
-        <v>16331294.409160316</v>
+        <v>17392981.921450883</v>
       </c>
       <c r="T51" t="s">
         <v>124</v>
@@ -7810,47 +7806,47 @@
       </c>
       <c r="H52" s="114">
         <f t="shared" si="1"/>
-        <v>188446965.85789701</v>
+        <v>189896308.25788501</v>
       </c>
       <c r="I52" s="114">
         <f t="shared" si="2"/>
-        <v>89948535.371478006</v>
+        <v>90146733.571477994</v>
       </c>
       <c r="J52" s="114">
         <f t="shared" si="3"/>
-        <v>335447392.40920001</v>
+        <v>340509059.10918701</v>
       </c>
       <c r="K52" s="114">
         <f t="shared" si="4"/>
-        <v>613842893.63857508</v>
+        <v>620552100.93855</v>
       </c>
       <c r="L52" s="187">
         <f t="shared" si="5"/>
-        <v>0.78144396135839178</v>
+        <v>0.78998502224612122</v>
       </c>
       <c r="M52" s="184">
         <f t="shared" si="6"/>
-        <v>132404793.71055937</v>
+        <v>125695586.41058445</v>
       </c>
       <c r="N52" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>26480958.742111873</v>
+        <v>31423896.602646112</v>
       </c>
       <c r="O52" s="180">
         <f t="shared" si="8"/>
-        <v>171680987.7815665</v>
+        <v>164971780.48159158</v>
       </c>
       <c r="P52" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>34336197.556313299</v>
+        <v>41242945.120397896</v>
       </c>
       <c r="Q52" s="185">
         <f t="shared" si="10"/>
-        <v>171680987.7815665</v>
+        <v>164971780.48159158</v>
       </c>
       <c r="R52" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>34336197.556313299</v>
+        <v>41242945.120397896</v>
       </c>
       <c r="T52" t="s">
         <v>70</v>
@@ -7884,7 +7880,7 @@
       </c>
       <c r="H53" s="114">
         <f t="shared" si="1"/>
-        <v>46889334.859999999</v>
+        <v>47429875.460000001</v>
       </c>
       <c r="I53" s="114">
         <f t="shared" si="2"/>
@@ -7896,35 +7892,35 @@
       </c>
       <c r="K53" s="114">
         <f t="shared" si="4"/>
-        <v>46889334.859999999</v>
+        <v>47429875.460000001</v>
       </c>
       <c r="L53" s="187">
         <f t="shared" si="5"/>
-        <v>0.17831823985787898</v>
+        <v>0.1803738938493786</v>
       </c>
       <c r="M53" s="184">
         <f t="shared" si="6"/>
-        <v>202916114.94986022</v>
+        <v>202375574.34986019</v>
       </c>
       <c r="N53" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>40583222.98997204</v>
+        <v>50593893.587465048</v>
       </c>
       <c r="O53" s="180">
         <f t="shared" si="8"/>
-        <v>216063770.20301074</v>
+        <v>215523229.60301074</v>
       </c>
       <c r="P53" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>43212754.040602148</v>
+        <v>53880807.400752686</v>
       </c>
       <c r="Q53" s="185">
         <f t="shared" si="10"/>
-        <v>216063770.20301074</v>
+        <v>215523229.60301074</v>
       </c>
       <c r="R53" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>43212754.040602148</v>
+        <v>53880807.400752686</v>
       </c>
       <c r="T53" t="s">
         <v>169</v>
@@ -7958,7 +7954,7 @@
       </c>
       <c r="H54" s="114">
         <f t="shared" si="1"/>
-        <v>437151614.40455902</v>
+        <v>464604407.979559</v>
       </c>
       <c r="I54" s="114">
         <f t="shared" si="2"/>
@@ -7966,39 +7962,39 @@
       </c>
       <c r="J54" s="114">
         <f t="shared" si="3"/>
-        <v>142801315.51987499</v>
+        <v>150846270.519853</v>
       </c>
       <c r="K54" s="114">
         <f t="shared" si="4"/>
-        <v>622673065.89389896</v>
+        <v>658170814.46887708</v>
       </c>
       <c r="L54" s="187">
         <f t="shared" si="5"/>
-        <v>0.85688347664714104</v>
+        <v>0.90573324368886554</v>
       </c>
       <c r="M54" s="184">
         <f t="shared" si="6"/>
-        <v>67665152.452673316</v>
+        <v>32167403.877695203</v>
       </c>
       <c r="N54" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>13533030.490534663</v>
+        <v>8041850.9694238007</v>
       </c>
       <c r="O54" s="180">
         <f t="shared" si="8"/>
-        <v>103998742.89196658</v>
+        <v>68500994.316988468</v>
       </c>
       <c r="P54" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>20799748.578393318</v>
+        <v>17125248.579247117</v>
       </c>
       <c r="Q54" s="185">
         <f t="shared" si="10"/>
-        <v>103998742.89196658</v>
+        <v>68500994.316988468</v>
       </c>
       <c r="R54" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>20799748.578393318</v>
+        <v>17125248.579247117</v>
       </c>
       <c r="T54" t="s">
         <v>115</v>
@@ -8032,47 +8028,47 @@
       </c>
       <c r="H55" s="114">
         <f t="shared" si="1"/>
-        <v>4173423.4199979999</v>
+        <v>5673423.4199980004</v>
       </c>
       <c r="I55" s="114">
         <f t="shared" si="2"/>
-        <v>30250983.5</v>
+        <v>32629360.699999999</v>
       </c>
       <c r="J55" s="114">
         <f t="shared" si="3"/>
-        <v>199157658.6392</v>
+        <v>271000001.35890001</v>
       </c>
       <c r="K55" s="114">
         <f t="shared" si="4"/>
-        <v>233582065.55919799</v>
+        <v>309302785.47889799</v>
       </c>
       <c r="L55" s="187">
         <f t="shared" si="5"/>
-        <v>0.43481316257019165</v>
+        <v>0.57576733052634521</v>
       </c>
       <c r="M55" s="184">
         <f t="shared" si="6"/>
-        <v>276758884.03295338</v>
+        <v>201038164.11325336</v>
       </c>
       <c r="N55" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>55351776.806590676</v>
+        <v>50259541.028313339</v>
       </c>
       <c r="O55" s="180">
         <f t="shared" si="8"/>
-        <v>303618934.0114876</v>
+        <v>227898214.09178764</v>
       </c>
       <c r="P55" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>60723786.802297518</v>
+        <v>56974553.522946909</v>
       </c>
       <c r="Q55" s="185">
         <f t="shared" si="10"/>
-        <v>303618934.0114876</v>
+        <v>227898214.09178764</v>
       </c>
       <c r="R55" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>60723786.802297518</v>
+        <v>56974553.522946909</v>
       </c>
       <c r="T55" t="s">
         <v>182</v>
@@ -8106,47 +8102,47 @@
       </c>
       <c r="H56" s="114">
         <f t="shared" si="1"/>
-        <v>183815526.976354</v>
+        <v>184450526.976354</v>
       </c>
       <c r="I56" s="114">
         <f t="shared" si="2"/>
-        <v>46626385.219940998</v>
+        <v>47411295.139939003</v>
       </c>
       <c r="J56" s="114">
         <f t="shared" si="3"/>
-        <v>137495154.28817099</v>
+        <v>144992226.38817099</v>
       </c>
       <c r="K56" s="114">
         <f t="shared" si="4"/>
-        <v>367937066.48446596</v>
+        <v>376854048.50446403</v>
       </c>
       <c r="L56" s="187">
         <f t="shared" si="5"/>
-        <v>0.63995066292096792</v>
+        <v>0.65545991456955943</v>
       </c>
       <c r="M56" s="184">
         <f t="shared" si="6"/>
-        <v>178261622.59074152</v>
+        <v>169344640.57074344</v>
       </c>
       <c r="N56" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>35652324.518148303</v>
+        <v>42336160.14268586</v>
       </c>
       <c r="O56" s="180">
         <f t="shared" si="8"/>
-        <v>207008922.01575243</v>
+        <v>198091939.99575436</v>
       </c>
       <c r="P56" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>41401784.403150484</v>
+        <v>49522984.99893859</v>
       </c>
       <c r="Q56" s="185">
         <f t="shared" si="10"/>
-        <v>207008922.01575243</v>
+        <v>198091939.99575436</v>
       </c>
       <c r="R56" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>41401784.403150484</v>
+        <v>49522984.99893859</v>
       </c>
       <c r="T56" t="s">
         <v>225</v>
@@ -8180,47 +8176,47 @@
       </c>
       <c r="H57" s="114">
         <f t="shared" si="1"/>
-        <v>465821952.54762101</v>
+        <v>469087694.35771102</v>
       </c>
       <c r="I57" s="114">
         <f t="shared" si="2"/>
-        <v>51819828.479924001</v>
+        <v>52390125.779923998</v>
       </c>
       <c r="J57" s="114">
         <f t="shared" si="3"/>
-        <v>299276352.78941</v>
+        <v>301606082.52941</v>
       </c>
       <c r="K57" s="114">
         <f t="shared" si="4"/>
-        <v>816918133.81695509</v>
+        <v>823083902.667045</v>
       </c>
       <c r="L57" s="187">
         <f t="shared" si="5"/>
-        <v>0.73650366896541852</v>
+        <v>0.74206250184242428</v>
       </c>
       <c r="M57" s="184">
         <f t="shared" si="6"/>
-        <v>236806728.4315542</v>
+        <v>230640959.58146429</v>
       </c>
       <c r="N57" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>47361345.686310843</v>
+        <v>57660239.895366073</v>
       </c>
       <c r="O57" s="180">
         <f t="shared" si="8"/>
-        <v>292265931.70779157</v>
+        <v>286100162.85770166</v>
       </c>
       <c r="P57" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>58453186.341558315</v>
+        <v>71525040.714425415</v>
       </c>
       <c r="Q57" s="185">
         <f t="shared" si="10"/>
-        <v>292265931.70779157</v>
+        <v>286100162.85770166</v>
       </c>
       <c r="R57" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>58453186.341558315</v>
+        <v>71525040.714425415</v>
       </c>
       <c r="T57" t="s">
         <v>120</v>
@@ -8254,47 +8250,47 @@
       </c>
       <c r="H58" s="114">
         <f t="shared" si="1"/>
-        <v>241361191.13532299</v>
+        <v>253561209.328915</v>
       </c>
       <c r="I58" s="114">
         <f t="shared" si="2"/>
-        <v>63404429.039943002</v>
+        <v>63950429.039943002</v>
       </c>
       <c r="J58" s="114">
         <f t="shared" si="3"/>
-        <v>176031885.582169</v>
+        <v>180549813.52216801</v>
       </c>
       <c r="K58" s="114">
         <f t="shared" si="4"/>
-        <v>480797505.75743496</v>
+        <v>498061451.89102602</v>
       </c>
       <c r="L58" s="187">
         <f t="shared" si="5"/>
-        <v>0.78231772104937491</v>
+        <v>0.81040832225637016</v>
       </c>
       <c r="M58" s="184">
         <f t="shared" si="6"/>
-        <v>103054320.9107424</v>
+        <v>85790374.777151346</v>
       </c>
       <c r="N58" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>20610864.182148479</v>
+        <v>21447593.694287837</v>
       </c>
       <c r="O58" s="180">
         <f t="shared" si="8"/>
-        <v>133783364.41959393</v>
+        <v>116519418.28600287</v>
       </c>
       <c r="P58" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>26756672.883918785</v>
+        <v>29129854.571500719</v>
       </c>
       <c r="Q58" s="185">
         <f t="shared" si="10"/>
-        <v>133783364.41959393</v>
+        <v>116519418.28600287</v>
       </c>
       <c r="R58" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>26756672.883918785</v>
+        <v>29129854.571500719</v>
       </c>
       <c r="T58" t="s">
         <v>125</v>
@@ -8352,7 +8348,7 @@
       </c>
       <c r="N59" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>41218506.527519807</v>
+        <v>51523133.159399755</v>
       </c>
       <c r="O59" s="180">
         <f t="shared" si="8"/>
@@ -8360,7 +8356,7 @@
       </c>
       <c r="P59" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>45656973.683284</v>
+        <v>57071217.104105003</v>
       </c>
       <c r="Q59" s="185">
         <f t="shared" si="10"/>
@@ -8368,7 +8364,7 @@
       </c>
       <c r="R59" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>45656973.683284</v>
+        <v>57071217.104105003</v>
       </c>
       <c r="T59" t="s">
         <v>170</v>
@@ -8402,47 +8398,47 @@
       </c>
       <c r="H60" s="114">
         <f t="shared" si="1"/>
-        <v>283697018.83984798</v>
+        <v>309803234.24329299</v>
       </c>
       <c r="I60" s="114">
         <f t="shared" si="2"/>
-        <v>80203472.886524007</v>
+        <v>81584972.886524007</v>
       </c>
       <c r="J60" s="114">
         <f t="shared" si="3"/>
-        <v>93333896.788552999</v>
+        <v>96322302.232531995</v>
       </c>
       <c r="K60" s="114">
         <f t="shared" si="4"/>
-        <v>457234388.514925</v>
+        <v>487710509.36234903</v>
       </c>
       <c r="L60" s="187">
         <f t="shared" si="5"/>
-        <v>0.78944281138664696</v>
+        <v>0.8420616762976888</v>
       </c>
       <c r="M60" s="184">
         <f t="shared" si="6"/>
-        <v>92992509.271639466</v>
+        <v>62516388.424215436</v>
       </c>
       <c r="N60" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>18598501.854327895</v>
+        <v>15629097.106053859</v>
       </c>
       <c r="O60" s="180">
         <f t="shared" si="8"/>
-        <v>121951819.68145871</v>
+        <v>91475698.834034681</v>
       </c>
       <c r="P60" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>24390363.936291743</v>
+        <v>22868924.70850867</v>
       </c>
       <c r="Q60" s="185">
         <f t="shared" si="10"/>
-        <v>121951819.68145871</v>
+        <v>91475698.834034681</v>
       </c>
       <c r="R60" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>24390363.936291743</v>
+        <v>22868924.70850867</v>
       </c>
       <c r="T60" t="s">
         <v>220</v>
@@ -8476,47 +8472,47 @@
       </c>
       <c r="H61" s="114">
         <f t="shared" si="1"/>
-        <v>420220553.48265302</v>
+        <v>428037130.09258002</v>
       </c>
       <c r="I61" s="114">
         <f t="shared" si="2"/>
-        <v>57722998.644919001</v>
+        <v>58268998.644919001</v>
       </c>
       <c r="J61" s="114">
         <f t="shared" si="3"/>
-        <v>189249443.53988701</v>
+        <v>192989083.319877</v>
       </c>
       <c r="K61" s="114">
         <f t="shared" si="4"/>
-        <v>667192995.66745901</v>
+        <v>679295212.05737603</v>
       </c>
       <c r="L61" s="187">
         <f t="shared" si="5"/>
-        <v>0.93106293312094301</v>
+        <v>0.94795148735102464</v>
       </c>
       <c r="M61" s="184">
         <f t="shared" si="6"/>
-        <v>13570165.808063388</v>
+        <v>1467949.4181463718</v>
       </c>
       <c r="N61" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>2714033.1616126774</v>
+        <v>366987.35453659296</v>
       </c>
       <c r="O61" s="180">
         <f t="shared" si="8"/>
-        <v>49399805.885722518</v>
+        <v>37297589.495805502</v>
       </c>
       <c r="P61" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>9879961.1771445032</v>
+        <v>9324397.3739513755</v>
       </c>
       <c r="Q61" s="185">
         <f t="shared" si="10"/>
-        <v>49399805.885722518</v>
+        <v>37297589.495805502</v>
       </c>
       <c r="R61" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>9879961.1771445032</v>
+        <v>9324397.3739513755</v>
       </c>
       <c r="T61" t="s">
         <v>126</v>
@@ -8550,47 +8546,47 @@
       </c>
       <c r="H62" s="114">
         <f t="shared" si="1"/>
-        <v>129114514.549408</v>
+        <v>130775176.729406</v>
       </c>
       <c r="I62" s="114">
         <f t="shared" si="2"/>
-        <v>37038940.117797002</v>
+        <v>38616940.117797002</v>
       </c>
       <c r="J62" s="114">
         <f t="shared" si="3"/>
-        <v>181176342.72703999</v>
+        <v>185920937.347022</v>
       </c>
       <c r="K62" s="114">
         <f t="shared" si="4"/>
-        <v>347329797.39424503</v>
+        <v>355313054.19422501</v>
       </c>
       <c r="L62" s="187">
         <f t="shared" si="5"/>
-        <v>0.72811920988983281</v>
+        <v>0.74485478131836524</v>
       </c>
       <c r="M62" s="184">
         <f t="shared" si="6"/>
-        <v>105842297.2885164</v>
+        <v>97859040.488536417</v>
       </c>
       <c r="N62" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>21168459.457703281</v>
+        <v>24464760.122134104</v>
       </c>
       <c r="O62" s="180">
         <f t="shared" si="8"/>
-        <v>129693460.16655648</v>
+        <v>121710203.36657649</v>
       </c>
       <c r="P62" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>25938692.033311296</v>
+        <v>30427550.841644123</v>
       </c>
       <c r="Q62" s="185">
         <f t="shared" si="10"/>
-        <v>129693460.16655648</v>
+        <v>121710203.36657649</v>
       </c>
       <c r="R62" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>25938692.033311296</v>
+        <v>30427550.841644123</v>
       </c>
       <c r="T62" t="s">
         <v>112</v>
@@ -8624,47 +8620,47 @@
       </c>
       <c r="H63" s="114">
         <f t="shared" si="1"/>
-        <v>426130063.79518402</v>
+        <v>434916433.51514399</v>
       </c>
       <c r="I63" s="114">
         <f t="shared" si="2"/>
-        <v>281504998.24590999</v>
+        <v>285495088.43090999</v>
       </c>
       <c r="J63" s="114">
         <f t="shared" si="3"/>
-        <v>248507610.975813</v>
+        <v>280204913.43528301</v>
       </c>
       <c r="K63" s="114">
         <f t="shared" si="4"/>
-        <v>956142673.0169071</v>
+        <v>1000616435.3813369</v>
       </c>
       <c r="L63" s="187">
         <f t="shared" si="5"/>
-        <v>0.97667831388779225</v>
+        <v>1.0221072655120125</v>
       </c>
       <c r="M63" s="184">
         <f t="shared" si="6"/>
-        <v>-26117375.587790966</v>
+        <v>-70591137.952220798</v>
       </c>
       <c r="N63" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>-5223475.1175581934</v>
+        <v>-17647784.488055199</v>
       </c>
       <c r="O63" s="180">
         <f t="shared" si="8"/>
-        <v>22831324.276899457</v>
+        <v>-21642438.087530375</v>
       </c>
       <c r="P63" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>4566264.8553798916</v>
+        <v>-5410609.5218825936</v>
       </c>
       <c r="Q63" s="185">
         <f t="shared" si="10"/>
-        <v>22831324.276899457</v>
+        <v>-21642438.087530375</v>
       </c>
       <c r="R63" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>4566264.8553798916</v>
+        <v>-5410609.5218825936</v>
       </c>
       <c r="T63" t="s">
         <v>127</v>
@@ -8698,11 +8694,11 @@
       </c>
       <c r="H64" s="114">
         <f t="shared" si="1"/>
-        <v>110983515.806016</v>
+        <v>112242398.67601499</v>
       </c>
       <c r="I64" s="114">
         <f t="shared" si="2"/>
-        <v>147015841.732555</v>
+        <v>148144917.591553</v>
       </c>
       <c r="J64" s="114">
         <f t="shared" si="3"/>
@@ -8710,35 +8706,35 @@
       </c>
       <c r="K64" s="114">
         <f t="shared" si="4"/>
-        <v>419713409.10741299</v>
+        <v>422101367.83640999</v>
       </c>
       <c r="L64" s="187">
         <f t="shared" si="5"/>
-        <v>0.78171393898775088</v>
+        <v>0.78616149911730271</v>
       </c>
       <c r="M64" s="184">
         <f t="shared" si="6"/>
-        <v>90355196.255258203</v>
+        <v>87967237.52626121</v>
       </c>
       <c r="N64" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>18071039.251051642</v>
+        <v>21991809.381565303</v>
       </c>
       <c r="O64" s="180">
         <f t="shared" si="8"/>
-        <v>117200912.32697779</v>
+        <v>114812953.5979808</v>
       </c>
       <c r="P64" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>23440182.465395559</v>
+        <v>28703238.399495199</v>
       </c>
       <c r="Q64" s="185">
         <f t="shared" si="10"/>
-        <v>117200912.32697779</v>
+        <v>114812953.5979808</v>
       </c>
       <c r="R64" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>23440182.465395559</v>
+        <v>28703238.399495199</v>
       </c>
       <c r="T64" t="s">
         <v>122</v>
@@ -8770,47 +8766,47 @@
       </c>
       <c r="H65" s="135">
         <f t="shared" si="12"/>
-        <v>3403989688.2226486</v>
+        <v>3504076393.5446467</v>
       </c>
       <c r="I65" s="135">
         <f t="shared" si="12"/>
-        <v>974588489.65190494</v>
+        <v>987882992.37589896</v>
       </c>
       <c r="J65" s="135">
         <f t="shared" si="12"/>
-        <v>2299948046.8379369</v>
+        <v>2446889611.6810222</v>
       </c>
       <c r="K65" s="135">
         <f t="shared" si="12"/>
-        <v>6678526224.7124891</v>
+        <v>6938848997.6015682</v>
       </c>
       <c r="L65" s="189">
         <f t="shared" si="5"/>
-        <v>0.75395712414373617</v>
+        <v>0.7833456752390825</v>
       </c>
       <c r="M65" s="181">
         <f>SUM(M51:M64)</f>
-        <v>1736541038.8038306</v>
+        <v>1476218265.914753</v>
       </c>
       <c r="N65" s="181">
         <f t="shared" ca="1" si="7"/>
-        <v>347308207.76076615</v>
+        <v>369054566.47868824</v>
       </c>
       <c r="O65" s="181">
         <f>SUM(O51:O64)</f>
-        <v>2179439315.8310056</v>
+        <v>1919116542.9419279</v>
       </c>
       <c r="P65" s="181">
         <f t="shared" ca="1" si="9"/>
-        <v>435887863.16620111</v>
+        <v>479779135.73548198</v>
       </c>
       <c r="Q65" s="186">
         <f>SUM(Q51:Q64)</f>
-        <v>2179439315.8310056</v>
+        <v>1919116542.9419279</v>
       </c>
       <c r="R65" s="186">
         <f t="shared" ca="1" si="11"/>
-        <v>435887863.16620111</v>
+        <v>479779135.73548198</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8819,21 +8815,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="293" t="s">
+      <c r="B67" s="286" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="294"/>
-      <c r="D67" s="294"/>
-      <c r="E67" s="294"/>
+      <c r="C67" s="287"/>
+      <c r="D67" s="287"/>
+      <c r="E67" s="287"/>
       <c r="F67" s="296"/>
-      <c r="G67" s="263" t="s">
+      <c r="G67" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="264"/>
-      <c r="I67" s="264"/>
-      <c r="J67" s="264"/>
-      <c r="K67" s="264"/>
-      <c r="L67" s="265"/>
+      <c r="H67" s="273"/>
+      <c r="I67" s="273"/>
+      <c r="J67" s="273"/>
+      <c r="K67" s="273"/>
+      <c r="L67" s="274"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -8895,35 +8891,35 @@
       </c>
       <c r="E69" s="114">
         <f>IFERROR($C$31,0)</f>
-        <v>239090594.19514599</v>
+        <v>251052873.62514299</v>
       </c>
       <c r="F69" s="187">
         <f t="shared" ref="F69:F74" si="13">IFERROR(E69/D69,0)</f>
-        <v>0.93300914553362835</v>
+        <v>0.97968984473548171</v>
       </c>
       <c r="G69" s="184">
         <f>D69*$H$40-E69</f>
-        <v>4354033.9445703924</v>
+        <v>-7608245.4854266047</v>
       </c>
       <c r="H69" s="184">
         <f t="shared" ref="H69:H74" ca="1" si="14">IFERROR(G69/$C$3,0)</f>
-        <v>870806.7889140785</v>
+        <v>-1902061.3713566512</v>
       </c>
       <c r="I69" s="204">
         <f>D69*$J$40-E69</f>
-        <v>17166909.109818637</v>
+        <v>5204629.6798216403</v>
       </c>
       <c r="J69" s="204">
         <f t="shared" ref="J69:J74" ca="1" si="15">IFERROR(I69/$C$3,0)</f>
-        <v>3433381.8219637275</v>
+        <v>1301157.4199554101</v>
       </c>
       <c r="K69" s="185">
         <f>D69*$L$40-E69</f>
-        <v>17166909.109818637</v>
+        <v>5204629.6798216403</v>
       </c>
       <c r="L69" s="185">
         <f t="shared" ref="L69:L74" ca="1" si="16">IFERROR(K69/$C$3,0)</f>
-        <v>3433381.8219637275</v>
+        <v>1301157.4199554101</v>
       </c>
     </row>
     <row r="70" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8939,35 +8935,35 @@
       </c>
       <c r="E70" s="114">
         <f>IFERROR($C$32,0)</f>
-        <v>427130336.43894702</v>
+        <v>443836083.938923</v>
       </c>
       <c r="F70" s="187">
         <f t="shared" si="13"/>
-        <v>1.0690059908260372</v>
+        <v>1.1108165171108031</v>
       </c>
       <c r="G70" s="184">
         <f>D70*$H$40-E70</f>
-        <v>-47549844.749230683</v>
+        <v>-64255592.249206662</v>
       </c>
       <c r="H70" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>-9509968.9498461373</v>
+        <v>-16063898.062301666</v>
       </c>
       <c r="I70" s="204">
         <f>D70*$J$40-E70</f>
-        <v>-27571924.13398242</v>
+        <v>-44277671.633958399</v>
       </c>
       <c r="J70" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>-5514384.8267964842</v>
+        <v>-11069417.9084896</v>
       </c>
       <c r="K70" s="185">
         <f>D70*$L$40-E70</f>
-        <v>-27571924.13398242</v>
+        <v>-44277671.633958399</v>
       </c>
       <c r="L70" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>-5514384.8267964842</v>
+        <v>-11069417.9084896</v>
       </c>
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.25">
@@ -8983,35 +8979,35 @@
       </c>
       <c r="E71" s="114">
         <f>M21</f>
-        <v>948476673.30109191</v>
+        <v>951040727.40107894</v>
       </c>
       <c r="F71" s="187">
         <f t="shared" si="13"/>
-        <v>0.87448668999667478</v>
+        <v>0.87685072407994447</v>
       </c>
       <c r="G71" s="184">
         <f>D71*$H$40-E71</f>
-        <v>81902462.188624382</v>
+        <v>79338408.088637352</v>
       </c>
       <c r="H71" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>16380492.437724877</v>
+        <v>19834602.022159338</v>
       </c>
       <c r="I71" s="204">
         <f>D71*$J$40-E71</f>
-        <v>136132943.00387263</v>
+        <v>133568888.9038856</v>
       </c>
       <c r="J71" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>27226588.600774527</v>
+        <v>33392222.225971401</v>
       </c>
       <c r="K71" s="185">
         <f>D71*$L$40-E71</f>
-        <v>136132943.00387263</v>
+        <v>133568888.9038856</v>
       </c>
       <c r="L71" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>27226588.600774527</v>
+        <v>33392222.225971401</v>
       </c>
     </row>
     <row r="72" spans="2:21" hidden="1" x14ac:dyDescent="0.25">
@@ -9113,35 +9109,35 @@
       </c>
       <c r="E74" s="115">
         <f>SUM(E69:E73)</f>
-        <v>1614697603.935185</v>
+        <v>1645929684.9651449</v>
       </c>
       <c r="F74" s="177">
         <f t="shared" si="13"/>
-        <v>0.92776023697987398</v>
+        <v>0.94570532021224707</v>
       </c>
       <c r="G74" s="181">
         <f>SUM(G69:G73)</f>
-        <v>38706651.383964092</v>
+        <v>7474570.3540040851</v>
       </c>
       <c r="H74" s="181">
         <f t="shared" ca="1" si="14"/>
-        <v>7741330.2767928187</v>
+        <v>1868642.5885010213</v>
       </c>
       <c r="I74" s="186">
         <f>SUM(I69:I73)</f>
-        <v>125727927.97970885</v>
+        <v>94495846.949748844</v>
       </c>
       <c r="J74" s="186">
         <f t="shared" ca="1" si="15"/>
-        <v>25145585.595941771</v>
+        <v>23623961.737437211</v>
       </c>
       <c r="K74" s="186">
         <f>SUM(K69:K73)</f>
-        <v>125727927.97970885</v>
+        <v>94495846.949748844</v>
       </c>
       <c r="L74" s="186">
         <f t="shared" ca="1" si="16"/>
-        <v>25145585.595941771</v>
+        <v>23623961.737437211</v>
       </c>
     </row>
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9154,10 +9150,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="262" t="s">
+      <c r="B78" s="271" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="262" t="s">
+      <c r="C78" s="271" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -9186,7 +9182,7 @@
       </c>
       <c r="D80" s="131">
         <f t="shared" ref="D80:D93" si="17">SUMIF($B$10:$B$26,$T80,$F$10:$F$26)+SUMIF($B$10:$B$26,$U80,$F$10:$F$26)</f>
-        <v>343488851.45986003</v>
+        <v>385081374.45986003</v>
       </c>
       <c r="T80" t="str">
         <f t="shared" ref="T80:U93" si="18">T51</f>
@@ -9206,7 +9202,7 @@
       </c>
       <c r="D81" s="132">
         <f t="shared" si="17"/>
-        <v>149304519.81</v>
+        <v>154331547.07999998</v>
       </c>
       <c r="T81" t="str">
         <f t="shared" si="18"/>
@@ -9246,7 +9242,7 @@
       </c>
       <c r="D83" s="131">
         <f t="shared" si="17"/>
-        <v>359312587.47977</v>
+        <v>382969885.31973499</v>
       </c>
       <c r="T83" t="str">
         <f t="shared" si="18"/>
@@ -9286,7 +9282,7 @@
       </c>
       <c r="D85" s="131">
         <f t="shared" si="17"/>
-        <v>64092612.359999999</v>
+        <v>65692612.399999999</v>
       </c>
       <c r="T85" t="str">
         <f t="shared" si="18"/>
@@ -9306,7 +9302,7 @@
       </c>
       <c r="D86" s="132">
         <f t="shared" si="17"/>
-        <v>952267556.879969</v>
+        <v>955586205.67996895</v>
       </c>
       <c r="T86" t="str">
         <f t="shared" si="18"/>
@@ -9326,7 +9322,7 @@
       </c>
       <c r="D87" s="131">
         <f t="shared" si="17"/>
-        <v>278739195.65947998</v>
+        <v>297399826.70943499</v>
       </c>
       <c r="T87" t="str">
         <f t="shared" si="18"/>
@@ -9366,7 +9362,7 @@
       </c>
       <c r="D89" s="132">
         <f t="shared" si="17"/>
-        <v>49513514.579999998</v>
+        <v>50324325.43</v>
       </c>
       <c r="T89" t="str">
         <f t="shared" si="18"/>
@@ -9386,7 +9382,7 @@
       </c>
       <c r="D90" s="131">
         <f t="shared" si="17"/>
-        <v>534549561.39945602</v>
+        <v>569324336.12944102</v>
       </c>
       <c r="T90" t="str">
         <f t="shared" si="18"/>
@@ -9406,7 +9402,7 @@
       </c>
       <c r="D91" s="132">
         <f t="shared" si="17"/>
-        <v>141725852.38993299</v>
+        <v>148907397.44993299</v>
       </c>
       <c r="T91" t="str">
         <f t="shared" si="18"/>
@@ -9446,7 +9442,7 @@
       </c>
       <c r="D93" s="132">
         <f t="shared" si="17"/>
-        <v>151542165.31800002</v>
+        <v>152515138.31800002</v>
       </c>
       <c r="T93" t="str">
         <f t="shared" si="18"/>
@@ -9464,20 +9460,12 @@
       <c r="C94" s="58"/>
       <c r="D94" s="120">
         <f>SUM(D80:D93)</f>
-        <v>3062360146.9168677</v>
+        <v>3199956378.5567727</v>
       </c>
     </row>
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B48:L48"/>
-    <mergeCell ref="G67:L67"/>
     <mergeCell ref="M48:R48"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="C49:C50"/>
@@ -9490,6 +9478,14 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B48:L48"/>
+    <mergeCell ref="G67:L67"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -10117,11 +10113,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="272" t="s">
+      <c r="B40" s="262" t="s">
         <v>163</v>
       </c>
-      <c r="C40" s="273"/>
-      <c r="D40" s="274"/>
+      <c r="C40" s="263"/>
+      <c r="D40" s="264"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -10441,33 +10437,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="275" t="s">
+      <c r="B48" s="265" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="276"/>
-      <c r="D48" s="276"/>
-      <c r="E48" s="276"/>
-      <c r="F48" s="276"/>
-      <c r="G48" s="276"/>
-      <c r="H48" s="276"/>
-      <c r="I48" s="276"/>
-      <c r="J48" s="276"/>
-      <c r="K48" s="276"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="263" t="s">
+      <c r="C48" s="266"/>
+      <c r="D48" s="266"/>
+      <c r="E48" s="266"/>
+      <c r="F48" s="266"/>
+      <c r="G48" s="266"/>
+      <c r="H48" s="266"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="266"/>
+      <c r="K48" s="266"/>
+      <c r="L48" s="289"/>
+      <c r="M48" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="264"/>
-      <c r="O48" s="264"/>
-      <c r="P48" s="264"/>
-      <c r="Q48" s="264"/>
-      <c r="R48" s="265"/>
+      <c r="N48" s="273"/>
+      <c r="O48" s="273"/>
+      <c r="P48" s="273"/>
+      <c r="Q48" s="273"/>
+      <c r="R48" s="274"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="290" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="290" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="256" t="s">
@@ -10476,49 +10472,49 @@
       <c r="E49" s="257"/>
       <c r="F49" s="257"/>
       <c r="G49" s="258"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="291" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="292"/>
+      <c r="J49" s="292"/>
+      <c r="K49" s="293"/>
+      <c r="L49" s="294" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="266" t="str">
+      <c r="M49" s="275" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="266" t="str">
+      <c r="N49" s="275" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="268" t="str">
+      <c r="O49" s="277" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="268" t="str">
+      <c r="P49" s="277" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="270" t="str">
+      <c r="Q49" s="279" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="270" t="str">
+      <c r="R49" s="279" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="262"/>
-      <c r="C50" s="262"/>
+      <c r="B50" s="271"/>
+      <c r="C50" s="271"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -10543,13 +10539,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="267"/>
-      <c r="N50" s="267"/>
-      <c r="O50" s="269"/>
-      <c r="P50" s="269"/>
-      <c r="Q50" s="271"/>
-      <c r="R50" s="271"/>
+      <c r="L50" s="295"/>
+      <c r="M50" s="276"/>
+      <c r="N50" s="276"/>
+      <c r="O50" s="278"/>
+      <c r="P50" s="278"/>
+      <c r="Q50" s="280"/>
+      <c r="R50" s="280"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -11665,21 +11661,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="293" t="s">
+      <c r="B67" s="286" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="294"/>
-      <c r="D67" s="294"/>
-      <c r="E67" s="294"/>
+      <c r="C67" s="287"/>
+      <c r="D67" s="287"/>
+      <c r="E67" s="287"/>
       <c r="F67" s="296"/>
-      <c r="G67" s="263" t="s">
+      <c r="G67" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="264"/>
-      <c r="I67" s="264"/>
-      <c r="J67" s="264"/>
-      <c r="K67" s="264"/>
-      <c r="L67" s="265"/>
+      <c r="H67" s="273"/>
+      <c r="I67" s="273"/>
+      <c r="J67" s="273"/>
+      <c r="K67" s="273"/>
+      <c r="L67" s="274"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -12000,10 +11996,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="262" t="s">
+      <c r="B78" s="271" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="262" t="s">
+      <c r="C78" s="271" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -12316,12 +12312,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -12336,6 +12326,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -12963,11 +12959,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="272" t="s">
+      <c r="B40" s="262" t="s">
         <v>175</v>
       </c>
-      <c r="C40" s="273"/>
-      <c r="D40" s="274"/>
+      <c r="C40" s="263"/>
+      <c r="D40" s="264"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -13287,33 +13283,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="275" t="s">
+      <c r="B48" s="265" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="276"/>
-      <c r="D48" s="276"/>
-      <c r="E48" s="276"/>
-      <c r="F48" s="276"/>
-      <c r="G48" s="276"/>
-      <c r="H48" s="276"/>
-      <c r="I48" s="276"/>
-      <c r="J48" s="276"/>
-      <c r="K48" s="276"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="263" t="s">
+      <c r="C48" s="266"/>
+      <c r="D48" s="266"/>
+      <c r="E48" s="266"/>
+      <c r="F48" s="266"/>
+      <c r="G48" s="266"/>
+      <c r="H48" s="266"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="266"/>
+      <c r="K48" s="266"/>
+      <c r="L48" s="289"/>
+      <c r="M48" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="264"/>
-      <c r="O48" s="264"/>
-      <c r="P48" s="264"/>
-      <c r="Q48" s="264"/>
-      <c r="R48" s="265"/>
+      <c r="N48" s="273"/>
+      <c r="O48" s="273"/>
+      <c r="P48" s="273"/>
+      <c r="Q48" s="273"/>
+      <c r="R48" s="274"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="290" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="290" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="256" t="s">
@@ -13322,49 +13318,49 @@
       <c r="E49" s="257"/>
       <c r="F49" s="257"/>
       <c r="G49" s="258"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="291" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="292"/>
+      <c r="J49" s="292"/>
+      <c r="K49" s="293"/>
+      <c r="L49" s="294" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="266" t="str">
+      <c r="M49" s="275" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="266" t="str">
+      <c r="N49" s="275" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="268" t="str">
+      <c r="O49" s="277" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="268" t="str">
+      <c r="P49" s="277" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="270" t="str">
+      <c r="Q49" s="279" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="270" t="str">
+      <c r="R49" s="279" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="262"/>
-      <c r="C50" s="262"/>
+      <c r="B50" s="271"/>
+      <c r="C50" s="271"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -13389,13 +13385,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="267"/>
-      <c r="N50" s="267"/>
-      <c r="O50" s="269"/>
-      <c r="P50" s="269"/>
-      <c r="Q50" s="271"/>
-      <c r="R50" s="271"/>
+      <c r="L50" s="295"/>
+      <c r="M50" s="276"/>
+      <c r="N50" s="276"/>
+      <c r="O50" s="278"/>
+      <c r="P50" s="278"/>
+      <c r="Q50" s="280"/>
+      <c r="R50" s="280"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -14511,21 +14507,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="293" t="s">
+      <c r="B67" s="286" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="294"/>
-      <c r="D67" s="294"/>
-      <c r="E67" s="294"/>
+      <c r="C67" s="287"/>
+      <c r="D67" s="287"/>
+      <c r="E67" s="287"/>
       <c r="F67" s="296"/>
-      <c r="G67" s="263" t="s">
+      <c r="G67" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="264"/>
-      <c r="I67" s="264"/>
-      <c r="J67" s="264"/>
-      <c r="K67" s="264"/>
-      <c r="L67" s="265"/>
+      <c r="H67" s="273"/>
+      <c r="I67" s="273"/>
+      <c r="J67" s="273"/>
+      <c r="K67" s="273"/>
+      <c r="L67" s="274"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -14846,10 +14842,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="262" t="s">
+      <c r="B78" s="271" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="262" t="s">
+      <c r="C78" s="271" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -15162,12 +15158,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -15182,6 +15172,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -15809,11 +15805,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="272" t="s">
+      <c r="B40" s="262" t="s">
         <v>177</v>
       </c>
-      <c r="C40" s="273"/>
-      <c r="D40" s="274"/>
+      <c r="C40" s="263"/>
+      <c r="D40" s="264"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -16133,33 +16129,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="275" t="s">
+      <c r="B48" s="265" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="276"/>
-      <c r="D48" s="276"/>
-      <c r="E48" s="276"/>
-      <c r="F48" s="276"/>
-      <c r="G48" s="276"/>
-      <c r="H48" s="276"/>
-      <c r="I48" s="276"/>
-      <c r="J48" s="276"/>
-      <c r="K48" s="276"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="263" t="s">
+      <c r="C48" s="266"/>
+      <c r="D48" s="266"/>
+      <c r="E48" s="266"/>
+      <c r="F48" s="266"/>
+      <c r="G48" s="266"/>
+      <c r="H48" s="266"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="266"/>
+      <c r="K48" s="266"/>
+      <c r="L48" s="289"/>
+      <c r="M48" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="264"/>
-      <c r="O48" s="264"/>
-      <c r="P48" s="264"/>
-      <c r="Q48" s="264"/>
-      <c r="R48" s="265"/>
+      <c r="N48" s="273"/>
+      <c r="O48" s="273"/>
+      <c r="P48" s="273"/>
+      <c r="Q48" s="273"/>
+      <c r="R48" s="274"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="290" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="290" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="256" t="s">
@@ -16168,49 +16164,49 @@
       <c r="E49" s="257"/>
       <c r="F49" s="257"/>
       <c r="G49" s="258"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="291" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="292"/>
+      <c r="J49" s="292"/>
+      <c r="K49" s="293"/>
+      <c r="L49" s="294" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="266" t="str">
+      <c r="M49" s="275" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="266" t="str">
+      <c r="N49" s="275" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="268" t="str">
+      <c r="O49" s="277" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="268" t="str">
+      <c r="P49" s="277" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="270" t="str">
+      <c r="Q49" s="279" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="270" t="str">
+      <c r="R49" s="279" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="262"/>
-      <c r="C50" s="262"/>
+      <c r="B50" s="271"/>
+      <c r="C50" s="271"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -16235,13 +16231,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="267"/>
-      <c r="N50" s="267"/>
-      <c r="O50" s="269"/>
-      <c r="P50" s="269"/>
-      <c r="Q50" s="271"/>
-      <c r="R50" s="271"/>
+      <c r="L50" s="295"/>
+      <c r="M50" s="276"/>
+      <c r="N50" s="276"/>
+      <c r="O50" s="278"/>
+      <c r="P50" s="278"/>
+      <c r="Q50" s="280"/>
+      <c r="R50" s="280"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -17343,21 +17339,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="293" t="s">
+      <c r="B67" s="286" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="294"/>
-      <c r="D67" s="294"/>
-      <c r="E67" s="294"/>
+      <c r="C67" s="287"/>
+      <c r="D67" s="287"/>
+      <c r="E67" s="287"/>
       <c r="F67" s="296"/>
-      <c r="G67" s="263" t="s">
+      <c r="G67" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="264"/>
-      <c r="I67" s="264"/>
-      <c r="J67" s="264"/>
-      <c r="K67" s="264"/>
-      <c r="L67" s="265"/>
+      <c r="H67" s="273"/>
+      <c r="I67" s="273"/>
+      <c r="J67" s="273"/>
+      <c r="K67" s="273"/>
+      <c r="L67" s="274"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -17678,10 +17674,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="262" t="s">
+      <c r="B78" s="271" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="262" t="s">
+      <c r="C78" s="271" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -17994,12 +17990,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -18014,6 +18004,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -25793,11 +25789,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="272" t="s">
+      <c r="B41" s="262" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="273"/>
-      <c r="D41" s="274"/>
+      <c r="C41" s="263"/>
+      <c r="D41" s="264"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -26068,59 +26064,59 @@
       </c>
     </row>
     <row r="48" spans="2:19" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="275" t="s">
+      <c r="B48" s="265" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="276"/>
-      <c r="D48" s="276"/>
-      <c r="E48" s="276"/>
-      <c r="F48" s="276"/>
-      <c r="G48" s="276"/>
-      <c r="H48" s="276"/>
-      <c r="I48" s="276"/>
-      <c r="J48" s="276"/>
-      <c r="K48" s="263" t="s">
+      <c r="C48" s="266"/>
+      <c r="D48" s="266"/>
+      <c r="E48" s="266"/>
+      <c r="F48" s="266"/>
+      <c r="G48" s="266"/>
+      <c r="H48" s="266"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="266"/>
+      <c r="K48" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="264"/>
-      <c r="M48" s="264"/>
-      <c r="N48" s="264"/>
-      <c r="O48" s="264"/>
-      <c r="P48" s="265"/>
+      <c r="L48" s="273"/>
+      <c r="M48" s="273"/>
+      <c r="N48" s="273"/>
+      <c r="O48" s="273"/>
+      <c r="P48" s="274"/>
       <c r="Q48"/>
       <c r="R48"/>
     </row>
     <row r="49" spans="2:18" s="139" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="280" t="s">
+      <c r="B49" s="270" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="280" t="s">
+      <c r="C49" s="270" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="277" t="s">
+      <c r="D49" s="267" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="278"/>
-      <c r="F49" s="279"/>
+      <c r="E49" s="268"/>
+      <c r="F49" s="269"/>
       <c r="G49" s="140" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="140"/>
       <c r="I49" s="140"/>
-      <c r="J49" s="277" t="s">
+      <c r="J49" s="267" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="266" t="str">
+      <c r="K49" s="275" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="266" t="str">
+      <c r="L49" s="275" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="268" t="str">
+      <c r="M49" s="277" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
@@ -26135,7 +26131,7 @@
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="270" t="str">
+      <c r="P49" s="279" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -26144,8 +26140,8 @@
       <c r="R49"/>
     </row>
     <row r="50" spans="2:18" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="280"/>
-      <c r="C50" s="280"/>
+      <c r="B50" s="270"/>
+      <c r="C50" s="270"/>
       <c r="D50" s="141" t="s">
         <v>149</v>
       </c>
@@ -26164,13 +26160,13 @@
       <c r="I50" s="142" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="277"/>
-      <c r="K50" s="267"/>
-      <c r="L50" s="267"/>
-      <c r="M50" s="269"/>
+      <c r="J50" s="267"/>
+      <c r="K50" s="276"/>
+      <c r="L50" s="276"/>
+      <c r="M50" s="278"/>
       <c r="N50" s="188"/>
       <c r="O50" s="183"/>
-      <c r="P50" s="271"/>
+      <c r="P50" s="280"/>
       <c r="Q50"/>
       <c r="R50"/>
     </row>
@@ -27511,10 +27507,10 @@
       <c r="I77"/>
     </row>
     <row r="78" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="262" t="s">
+      <c r="B78" s="271" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="262" t="s">
+      <c r="C78" s="271" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -27713,13 +27709,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="J49:J50"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
     <mergeCell ref="K48:P48"/>
@@ -27729,6 +27718,13 @@
     <mergeCell ref="P49:P50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="J49:J50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="26" priority="8">
@@ -28768,25 +28764,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="275" t="s">
+      <c r="B48" s="265" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="276"/>
-      <c r="D48" s="276"/>
-      <c r="E48" s="276"/>
-      <c r="F48" s="276"/>
-      <c r="G48" s="276"/>
-      <c r="H48" s="276"/>
-      <c r="I48" s="276"/>
-      <c r="J48" s="276"/>
-      <c r="K48" s="263" t="s">
+      <c r="C48" s="266"/>
+      <c r="D48" s="266"/>
+      <c r="E48" s="266"/>
+      <c r="F48" s="266"/>
+      <c r="G48" s="266"/>
+      <c r="H48" s="266"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="266"/>
+      <c r="K48" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="264"/>
-      <c r="M48" s="264"/>
-      <c r="N48" s="264"/>
-      <c r="O48" s="264"/>
-      <c r="P48" s="265"/>
+      <c r="L48" s="273"/>
+      <c r="M48" s="273"/>
+      <c r="N48" s="273"/>
+      <c r="O48" s="273"/>
+      <c r="P48" s="274"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="261" t="s">
@@ -28808,32 +28804,32 @@
       <c r="J49" s="256" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="266" t="str">
+      <c r="K49" s="275" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="266" t="str">
+      <c r="L49" s="275" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="268" t="str">
+      <c r="M49" s="277" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="268" t="str">
+      <c r="N49" s="277" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="270" t="str">
+      <c r="O49" s="279" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="270" t="str">
+      <c r="P49" s="279" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -28861,12 +28857,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="256"/>
-      <c r="K50" s="267"/>
-      <c r="L50" s="267"/>
-      <c r="M50" s="269"/>
-      <c r="N50" s="269"/>
-      <c r="O50" s="271"/>
-      <c r="P50" s="271"/>
+      <c r="K50" s="276"/>
+      <c r="L50" s="276"/>
+      <c r="M50" s="278"/>
+      <c r="N50" s="278"/>
+      <c r="O50" s="280"/>
+      <c r="P50" s="280"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="167" t="s">
@@ -30103,10 +30099,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="262" t="s">
+      <c r="B78" s="271" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="262" t="s">
+      <c r="C78" s="271" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -30300,17 +30296,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -30318,6 +30303,17 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -31075,11 +31071,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="272" t="s">
+      <c r="B41" s="262" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="273"/>
-      <c r="D41" s="274"/>
+      <c r="C41" s="263"/>
+      <c r="D41" s="264"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -31354,25 +31350,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="275" t="s">
+      <c r="B48" s="265" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="276"/>
-      <c r="D48" s="276"/>
-      <c r="E48" s="276"/>
-      <c r="F48" s="276"/>
-      <c r="G48" s="276"/>
-      <c r="H48" s="276"/>
-      <c r="I48" s="276"/>
-      <c r="J48" s="276"/>
-      <c r="K48" s="263" t="s">
+      <c r="C48" s="266"/>
+      <c r="D48" s="266"/>
+      <c r="E48" s="266"/>
+      <c r="F48" s="266"/>
+      <c r="G48" s="266"/>
+      <c r="H48" s="266"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="266"/>
+      <c r="K48" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="264"/>
-      <c r="M48" s="264"/>
-      <c r="N48" s="264"/>
-      <c r="O48" s="264"/>
-      <c r="P48" s="265"/>
+      <c r="L48" s="273"/>
+      <c r="M48" s="273"/>
+      <c r="N48" s="273"/>
+      <c r="O48" s="273"/>
+      <c r="P48" s="274"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="261" t="s">
@@ -31394,32 +31390,32 @@
       <c r="J49" s="256" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="266" t="str">
+      <c r="K49" s="275" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="266" t="str">
+      <c r="L49" s="275" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="268" t="str">
+      <c r="M49" s="277" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="268" t="str">
+      <c r="N49" s="277" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="270" t="str">
+      <c r="O49" s="279" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="270" t="str">
+      <c r="P49" s="279" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -31447,12 +31443,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="256"/>
-      <c r="K50" s="267"/>
-      <c r="L50" s="267"/>
-      <c r="M50" s="269"/>
-      <c r="N50" s="269"/>
-      <c r="O50" s="271"/>
-      <c r="P50" s="271"/>
+      <c r="K50" s="276"/>
+      <c r="L50" s="276"/>
+      <c r="M50" s="278"/>
+      <c r="N50" s="278"/>
+      <c r="O50" s="280"/>
+      <c r="P50" s="280"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -32689,10 +32685,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="262" t="s">
+      <c r="B78" s="271" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="262" t="s">
+      <c r="C78" s="271" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -32873,17 +32869,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -32891,6 +32876,17 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -33669,11 +33665,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" s="191" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="272" t="s">
+      <c r="B41" s="262" t="s">
         <v>189</v>
       </c>
-      <c r="C41" s="273"/>
-      <c r="D41" s="274"/>
+      <c r="C41" s="263"/>
+      <c r="D41" s="264"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -33948,25 +33944,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="275" t="s">
+      <c r="B48" s="265" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="276"/>
-      <c r="D48" s="276"/>
-      <c r="E48" s="276"/>
-      <c r="F48" s="276"/>
-      <c r="G48" s="276"/>
-      <c r="H48" s="276"/>
-      <c r="I48" s="276"/>
-      <c r="J48" s="276"/>
-      <c r="K48" s="263" t="s">
+      <c r="C48" s="266"/>
+      <c r="D48" s="266"/>
+      <c r="E48" s="266"/>
+      <c r="F48" s="266"/>
+      <c r="G48" s="266"/>
+      <c r="H48" s="266"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="266"/>
+      <c r="K48" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="264"/>
-      <c r="M48" s="264"/>
-      <c r="N48" s="264"/>
-      <c r="O48" s="264"/>
-      <c r="P48" s="265"/>
+      <c r="L48" s="273"/>
+      <c r="M48" s="273"/>
+      <c r="N48" s="273"/>
+      <c r="O48" s="273"/>
+      <c r="P48" s="274"/>
     </row>
     <row r="49" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="261" t="s">
@@ -33988,22 +33984,22 @@
       <c r="J49" s="256" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="266" t="str">
+      <c r="K49" s="275" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="266" t="str">
+      <c r="L49" s="275" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="268" t="str">
+      <c r="M49" s="277" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="268" t="str">
+      <c r="N49" s="277" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
@@ -34041,10 +34037,10 @@
         <v>130</v>
       </c>
       <c r="J50" s="256"/>
-      <c r="K50" s="267"/>
-      <c r="L50" s="267"/>
-      <c r="M50" s="269"/>
-      <c r="N50" s="269"/>
+      <c r="K50" s="276"/>
+      <c r="L50" s="276"/>
+      <c r="M50" s="278"/>
+      <c r="N50" s="278"/>
       <c r="O50" s="285"/>
       <c r="P50" s="285"/>
     </row>
@@ -35283,10 +35279,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="262" t="s">
+      <c r="B78" s="271" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="262" t="s">
+      <c r="C78" s="271" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -35480,11 +35476,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
@@ -35498,6 +35489,11 @@
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -909,7 +909,7 @@
     <t>RONALD</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL —  26 SEPTEMBER 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL —  28 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>
@@ -2565,33 +2565,6 @@
     <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2622,6 +2595,33 @@
     <xf numFmtId="0" fontId="48" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2635,15 +2635,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2665,6 +2656,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4308,11 +4308,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="262" t="s">
+      <c r="B40" s="272" t="s">
         <v>219</v>
       </c>
-      <c r="C40" s="263"/>
-      <c r="D40" s="264"/>
+      <c r="C40" s="273"/>
+      <c r="D40" s="274"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -4632,33 +4632,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="265" t="s">
+      <c r="B48" s="275" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="266"/>
-      <c r="D48" s="266"/>
-      <c r="E48" s="266"/>
-      <c r="F48" s="266"/>
-      <c r="G48" s="266"/>
-      <c r="H48" s="266"/>
-      <c r="I48" s="266"/>
-      <c r="J48" s="266"/>
-      <c r="K48" s="266"/>
-      <c r="L48" s="289"/>
-      <c r="M48" s="272" t="s">
+      <c r="C48" s="276"/>
+      <c r="D48" s="276"/>
+      <c r="E48" s="276"/>
+      <c r="F48" s="276"/>
+      <c r="G48" s="276"/>
+      <c r="H48" s="276"/>
+      <c r="I48" s="276"/>
+      <c r="J48" s="276"/>
+      <c r="K48" s="276"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="273"/>
-      <c r="O48" s="273"/>
-      <c r="P48" s="273"/>
-      <c r="Q48" s="273"/>
-      <c r="R48" s="274"/>
+      <c r="N48" s="264"/>
+      <c r="O48" s="264"/>
+      <c r="P48" s="264"/>
+      <c r="Q48" s="264"/>
+      <c r="R48" s="265"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="290" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="290" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="256" t="s">
@@ -4667,49 +4667,49 @@
       <c r="E49" s="257"/>
       <c r="F49" s="257"/>
       <c r="G49" s="258"/>
-      <c r="H49" s="291" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="292"/>
-      <c r="J49" s="292"/>
-      <c r="K49" s="293"/>
-      <c r="L49" s="294" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="275" t="str">
+      <c r="M49" s="266" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="275" t="str">
+      <c r="N49" s="266" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="277" t="str">
+      <c r="O49" s="268" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="277" t="str">
+      <c r="P49" s="268" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="279" t="str">
+      <c r="Q49" s="270" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="279" t="str">
+      <c r="R49" s="270" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="271"/>
-      <c r="C50" s="271"/>
+      <c r="B50" s="262"/>
+      <c r="C50" s="262"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -4734,13 +4734,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="295"/>
-      <c r="M50" s="276"/>
-      <c r="N50" s="276"/>
-      <c r="O50" s="278"/>
-      <c r="P50" s="278"/>
-      <c r="Q50" s="280"/>
-      <c r="R50" s="280"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="267"/>
+      <c r="N50" s="267"/>
+      <c r="O50" s="269"/>
+      <c r="P50" s="269"/>
+      <c r="Q50" s="271"/>
+      <c r="R50" s="271"/>
       <c r="T50" s="172" t="s">
         <v>216</v>
       </c>
@@ -5856,21 +5856,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="286" t="s">
+      <c r="B67" s="293" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="287"/>
-      <c r="D67" s="287"/>
-      <c r="E67" s="287"/>
-      <c r="F67" s="288"/>
-      <c r="G67" s="272" t="s">
+      <c r="C67" s="294"/>
+      <c r="D67" s="294"/>
+      <c r="E67" s="294"/>
+      <c r="F67" s="295"/>
+      <c r="G67" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="273"/>
-      <c r="I67" s="273"/>
-      <c r="J67" s="273"/>
-      <c r="K67" s="273"/>
-      <c r="L67" s="274"/>
+      <c r="H67" s="264"/>
+      <c r="I67" s="264"/>
+      <c r="J67" s="264"/>
+      <c r="K67" s="264"/>
+      <c r="L67" s="265"/>
     </row>
     <row r="68" spans="2:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -6189,10 +6189,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="271" t="s">
+      <c r="B78" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="271" t="s">
+      <c r="C78" s="262" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -6504,6 +6504,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -6518,12 +6524,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="C3" s="75">
         <f ca="1">IF($J$5&lt;&gt;"",$J$5,MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),9,1)),EOMONTH(DATE(YEAR(TODAY()),9,1),0),11)-MAX(0,$J$3-$J$4)))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" s="76" t="s">
         <v>104</v>
@@ -6729,19 +6729,19 @@
         <v>112</v>
       </c>
       <c r="C10" s="236">
-        <v>130775176.729406</v>
+        <v>133182163.255797</v>
       </c>
       <c r="D10" s="236">
-        <v>38616940.117797002</v>
+        <v>39865291.477794997</v>
       </c>
       <c r="E10" s="236">
-        <v>185920937.347022</v>
+        <v>191182198.64701799</v>
       </c>
       <c r="F10" s="236">
-        <v>148907397.44993299</v>
+        <v>155970460.17992401</v>
       </c>
       <c r="G10" s="236">
-        <v>504220451.64415801</v>
+        <v>520200113.560534</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="111"/>
@@ -6782,16 +6782,16 @@
         <v>158839730.55793801</v>
       </c>
       <c r="D12" s="236">
-        <v>68100455.821513996</v>
+        <v>68299955.821513996</v>
       </c>
       <c r="E12" s="236">
-        <v>149647841.07957</v>
+        <v>153961805.60950899</v>
       </c>
       <c r="F12" s="236">
-        <v>68507391.549999997</v>
+        <v>68657391.549999997</v>
       </c>
       <c r="G12" s="236">
-        <v>445095419.009022</v>
+        <v>449758883.53896099</v>
       </c>
       <c r="H12" s="111"/>
       <c r="I12" s="111"/>
@@ -6804,19 +6804,19 @@
         <v>114</v>
       </c>
       <c r="C13" s="236">
-        <v>31056577.699947</v>
+        <v>31456577.699947</v>
       </c>
       <c r="D13" s="236">
-        <v>22046277.749963999</v>
+        <v>22521953.429963</v>
       </c>
       <c r="E13" s="236">
-        <v>190861218.02961701</v>
+        <v>199683245.129592</v>
       </c>
       <c r="F13" s="236">
-        <v>85824155.530000001</v>
+        <v>85854155.530000001</v>
       </c>
       <c r="G13" s="236">
-        <v>329788229.00952798</v>
+        <v>339515931.78950202</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="111"/>
@@ -6829,19 +6829,19 @@
         <v>115</v>
       </c>
       <c r="C14" s="236">
-        <v>464604407.979559</v>
+        <v>482508837.979559</v>
       </c>
       <c r="D14" s="236">
-        <v>42720135.969465002</v>
+        <v>43096712.549465001</v>
       </c>
       <c r="E14" s="236">
-        <v>150846270.519853</v>
+        <v>151436270.519853</v>
       </c>
       <c r="F14" s="236">
-        <v>382969885.31973499</v>
+        <v>383780696.16973501</v>
       </c>
       <c r="G14" s="236">
-        <v>1041140699.788612</v>
+        <v>1060822517.218612</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="111"/>
@@ -6854,19 +6854,19 @@
         <v>118</v>
       </c>
       <c r="C15" s="236">
-        <v>1505892643.1199069</v>
+        <v>1583048264.799907</v>
       </c>
       <c r="D15" s="236">
-        <v>11190936.014923999</v>
+        <v>11461206.304924</v>
       </c>
       <c r="E15" s="236">
-        <v>76858935.799939007</v>
+        <v>94358935.799939007</v>
       </c>
       <c r="F15" s="236">
-        <v>14956757.039999999</v>
+        <v>16805405.75</v>
       </c>
       <c r="G15" s="236">
-        <v>1608899271.9747701</v>
+        <v>1705673812.6547699</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="111"/>
@@ -6879,19 +6879,19 @@
         <v>120</v>
       </c>
       <c r="C16" s="236">
-        <v>469087694.35771102</v>
+        <v>491342417.01869798</v>
       </c>
       <c r="D16" s="236">
-        <v>52390125.779923998</v>
+        <v>56669125.779923998</v>
       </c>
       <c r="E16" s="236">
-        <v>301606082.52941</v>
+        <v>312947839.26937002</v>
       </c>
       <c r="F16" s="236">
-        <v>955586205.67996895</v>
+        <v>990682602.56996906</v>
       </c>
       <c r="G16" s="236">
-        <v>1778670108.347014</v>
+        <v>1851641984.6379609</v>
       </c>
       <c r="H16" s="111"/>
       <c r="I16" s="111"/>
@@ -6904,19 +6904,19 @@
         <v>122</v>
       </c>
       <c r="C17" s="236">
-        <v>98586351.086017996</v>
+        <v>103155630.48592401</v>
       </c>
       <c r="D17" s="236">
         <v>13122554.039898001</v>
       </c>
       <c r="E17" s="236">
-        <v>103260945.468842</v>
+        <v>106463647.96879201</v>
       </c>
       <c r="F17" s="236">
-        <v>47952973.898000002</v>
+        <v>49898919.898000002</v>
       </c>
       <c r="G17" s="236">
-        <v>262922824.49275801</v>
+        <v>272640752.39261401</v>
       </c>
       <c r="H17" s="111"/>
       <c r="I17" s="111"/>
@@ -6936,13 +6936,13 @@
         <v>135022363.55165499</v>
       </c>
       <c r="E18" s="236">
-        <v>58453106.100000001</v>
+        <v>59041106.100000001</v>
       </c>
       <c r="F18" s="236">
         <v>104562164.42</v>
       </c>
       <c r="G18" s="236">
-        <v>311693681.66165203</v>
+        <v>312281681.66165203</v>
       </c>
       <c r="H18" s="111"/>
       <c r="I18" s="111"/>
@@ -6956,7 +6956,7 @@
         <v>169</v>
       </c>
       <c r="C19" s="236">
-        <v>47429875.460000001</v>
+        <v>48019875.460000001</v>
       </c>
       <c r="D19" s="236" t="s">
         <v>165</v>
@@ -6965,10 +6965,10 @@
         <v>165</v>
       </c>
       <c r="F19" s="236">
-        <v>7027026.8399999999</v>
+        <v>9945945.6799999997</v>
       </c>
       <c r="G19" s="236">
-        <v>54456902.299999997</v>
+        <v>57965821.140000001</v>
       </c>
       <c r="H19" s="111"/>
       <c r="I19" s="111"/>
@@ -6982,7 +6982,7 @@
         <v>170</v>
       </c>
       <c r="C20" s="236">
-        <v>215561847.16</v>
+        <v>206615067.16</v>
       </c>
       <c r="D20" s="236" t="s">
         <v>165</v>
@@ -6991,10 +6991,10 @@
         <v>165</v>
       </c>
       <c r="F20" s="236">
-        <v>11975945.619999999</v>
+        <v>13579549.18</v>
       </c>
       <c r="G20" s="236">
-        <v>227537792.78</v>
+        <v>220194616.34</v>
       </c>
       <c r="H20" s="111"/>
       <c r="I20" s="111"/>
@@ -7012,26 +7012,26 @@
         <v>124</v>
       </c>
       <c r="C21" s="236">
-        <v>258036727.34778699</v>
+        <v>263996098.743774</v>
       </c>
       <c r="D21" s="236">
-        <v>46523994.503447004</v>
+        <v>47932129.623447001</v>
       </c>
       <c r="E21" s="236">
-        <v>140234870.34977701</v>
+        <v>143083924.36977699</v>
       </c>
       <c r="F21" s="236">
-        <v>385081374.45986003</v>
+        <v>414273536.65985</v>
       </c>
       <c r="G21" s="236">
-        <v>829876966.66087103</v>
+        <v>869285689.39684796</v>
       </c>
       <c r="H21" s="111"/>
       <c r="I21" s="111"/>
       <c r="J21" s="111"/>
       <c r="M21" s="14">
         <f>SUM(C33,C34)+M20</f>
-        <v>951040727.40107894</v>
+        <v>1014347446.480343</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>224</v>
@@ -7042,19 +7042,19 @@
         <v>225</v>
       </c>
       <c r="C22" s="236">
-        <v>184450526.976354</v>
+        <v>190036588.29052001</v>
       </c>
       <c r="D22" s="236">
-        <v>47411295.139939003</v>
+        <v>55882903.289934002</v>
       </c>
       <c r="E22" s="236">
-        <v>144992226.38817099</v>
+        <v>151739974.348151</v>
       </c>
       <c r="F22" s="236">
-        <v>65692612.399999999</v>
+        <v>65782612.399999999</v>
       </c>
       <c r="G22" s="236">
-        <v>442546660.90446401</v>
+        <v>463442078.328605</v>
       </c>
       <c r="H22" s="111"/>
       <c r="I22" s="111"/>
@@ -7065,19 +7065,19 @@
         <v>125</v>
       </c>
       <c r="C23" s="236">
-        <v>253561209.328915</v>
+        <v>255492042.620024</v>
       </c>
       <c r="D23" s="236">
-        <v>63950429.039943002</v>
+        <v>67695304.759942994</v>
       </c>
       <c r="E23" s="236">
-        <v>180549813.52216801</v>
+        <v>183532696.38125801</v>
       </c>
       <c r="F23" s="236">
-        <v>297399826.70943499</v>
+        <v>315237664.88943499</v>
       </c>
       <c r="G23" s="236">
-        <v>795461278.60046101</v>
+        <v>821957708.65066004</v>
       </c>
       <c r="H23" s="111"/>
       <c r="I23" s="111"/>
@@ -7088,19 +7088,19 @@
         <v>126</v>
       </c>
       <c r="C24" s="236">
-        <v>428037130.09258002</v>
+        <v>440052239.37646002</v>
       </c>
       <c r="D24" s="236">
-        <v>58268998.644919001</v>
+        <v>59219998.644919001</v>
       </c>
       <c r="E24" s="236">
-        <v>192989083.319877</v>
+        <v>200790750.04987699</v>
       </c>
       <c r="F24" s="236">
-        <v>569324336.12944102</v>
+        <v>579669561.29943395</v>
       </c>
       <c r="G24" s="236">
-        <v>1248619548.1868169</v>
+        <v>1279732549.3706901</v>
       </c>
       <c r="H24" s="111"/>
       <c r="I24" s="111"/>
@@ -7111,19 +7111,19 @@
         <v>220</v>
       </c>
       <c r="C25" s="236">
-        <v>309803234.24329299</v>
+        <v>334965416.39326602</v>
       </c>
       <c r="D25" s="236">
         <v>81584972.886524007</v>
       </c>
       <c r="E25" s="236">
-        <v>96322302.232531995</v>
+        <v>97847527.472525001</v>
       </c>
       <c r="F25" s="236">
         <v>50324325.43</v>
       </c>
       <c r="G25" s="236">
-        <v>538034834.79234898</v>
+        <v>564722242.18231499</v>
       </c>
       <c r="H25" s="111"/>
       <c r="I25" s="111"/>
@@ -7134,19 +7134,19 @@
         <v>127</v>
       </c>
       <c r="C26" s="236">
-        <v>434916433.51514399</v>
+        <v>480229048.13510603</v>
       </c>
       <c r="D26" s="236">
-        <v>285495088.43090999</v>
+        <v>286587088.43090999</v>
       </c>
       <c r="E26" s="236">
-        <v>280204913.43528301</v>
+        <v>283835544.43512303</v>
       </c>
       <c r="F26" s="236">
         <v>18820757.1204</v>
       </c>
       <c r="G26" s="236">
-        <v>1019437192.501737</v>
+        <v>1069472438.121539</v>
       </c>
       <c r="H26" s="111"/>
       <c r="I26" s="111"/>
@@ -7189,7 +7189,7 @@
         <v>131</v>
       </c>
       <c r="C31" s="171">
-        <v>251052873.62514299</v>
+        <v>259365932.35194299</v>
       </c>
       <c r="G31" s="111"/>
       <c r="H31" s="111"/>
@@ -7200,7 +7200,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="236">
-        <v>443836083.938923</v>
+        <v>457145084.04292297</v>
       </c>
       <c r="G32" s="111"/>
       <c r="H32" s="111"/>
@@ -7211,7 +7211,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="236">
-        <v>503733073.28979498</v>
+        <v>506982262.40976697</v>
       </c>
       <c r="G33" s="111"/>
       <c r="H33" s="111"/>
@@ -7222,7 +7222,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="236">
-        <v>447307654.11128402</v>
+        <v>507365184.07057601</v>
       </c>
       <c r="G34" s="111"/>
       <c r="H34" s="111"/>
@@ -7267,17 +7267,17 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="262" t="s">
+      <c r="B40" s="272" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="263"/>
-      <c r="D40" s="264"/>
+      <c r="C40" s="273"/>
+      <c r="D40" s="274"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
       <c r="F40" s="174">
         <f ca="1">IF(MONTH(TODAY())=9,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;9,1,0))</f>
-        <v>0.8666666666666667</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="G40" s="192" t="s">
         <v>187</v>
@@ -7364,35 +7364,35 @@
       </c>
       <c r="E42" s="46">
         <f>H65</f>
-        <v>3504076393.5446467</v>
+        <v>3639221204.1870084</v>
       </c>
       <c r="F42" s="176">
         <f>IFERROR(E42/D42,0)</f>
-        <v>0.77664950584358994</v>
+        <v>0.80660323362078046</v>
       </c>
       <c r="G42" s="184">
         <f>D42*$H$40-E42</f>
-        <v>782120338.46977949</v>
+        <v>646975527.82741785</v>
       </c>
       <c r="H42" s="184">
         <f ca="1">IFERROR(G42/$C$3,0)</f>
-        <v>195530084.61744487</v>
+        <v>215658509.27580595</v>
       </c>
       <c r="I42" s="204">
         <f>D42*$J$40-E42</f>
-        <v>1007709640.1547494</v>
+        <v>872564829.51238775</v>
       </c>
       <c r="J42" s="204">
         <f ca="1">IFERROR(I42/$C$3,0)</f>
-        <v>251927410.03868735</v>
+        <v>290854943.17079592</v>
       </c>
       <c r="K42" s="185">
         <f>D42*$L$40-E42</f>
-        <v>1007709640.1547494</v>
+        <v>872564829.51238775</v>
       </c>
       <c r="L42" s="185">
         <f ca="1">IFERROR(K42/$C$3,0)</f>
-        <v>251927410.03868735</v>
+        <v>290854943.17079592</v>
       </c>
       <c r="S42" s="173">
         <v>0.8</v>
@@ -7411,35 +7411,35 @@
       </c>
       <c r="E43" s="46">
         <f>I65</f>
-        <v>987882992.37589896</v>
+        <v>1010129714.9858909</v>
       </c>
       <c r="F43" s="176">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.70494323283381455</v>
+        <v>0.72081826730416954</v>
       </c>
       <c r="G43" s="184">
         <f>D43*$H$40-E43</f>
-        <v>343414052.61374509</v>
+        <v>321167330.00375319</v>
       </c>
       <c r="H43" s="184">
         <f ca="1">IFERROR(G43/$C$3,0)</f>
-        <v>85853513.153436273</v>
+        <v>107055776.66791773</v>
       </c>
       <c r="I43" s="204">
         <f>D43*$J$40-E43</f>
-        <v>413482318.139516</v>
+        <v>391235595.52952409</v>
       </c>
       <c r="J43" s="204">
         <f ca="1">IFERROR(I43/$C$3,0)</f>
-        <v>103370579.534879</v>
+        <v>130411865.17650802</v>
       </c>
       <c r="K43" s="185">
         <f>D43*$L$40-E43</f>
-        <v>413482318.139516</v>
+        <v>391235595.52952409</v>
       </c>
       <c r="L43" s="185">
         <f ca="1">IFERROR(K43/$C$3,0)</f>
-        <v>103370579.534879</v>
+        <v>130411865.17650802</v>
       </c>
       <c r="S43" s="173">
         <v>0.85</v>
@@ -7458,35 +7458,35 @@
       </c>
       <c r="E44" s="46">
         <f>J65</f>
-        <v>2446889611.6810222</v>
+        <v>2506546531.6597452</v>
       </c>
       <c r="F44" s="176">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.8309147703551456</v>
+        <v>0.85117306714449736</v>
       </c>
       <c r="G44" s="184">
         <f>IF(D44=0,0,D44*$H$40-E44)</f>
-        <v>350683874.83122873</v>
+        <v>291026954.85250568</v>
       </c>
       <c r="H44" s="184">
         <f ca="1">IFERROR(G44/$C$3,0)</f>
-        <v>87670968.707807183</v>
+        <v>97008984.950835228</v>
       </c>
       <c r="I44" s="204">
         <f>IF(D44=0,0,D44*$J$40-E44)</f>
-        <v>497924584.64766312</v>
+        <v>438267664.66894007</v>
       </c>
       <c r="J44" s="204">
         <f ca="1">IFERROR(I44/$C$3,0)</f>
-        <v>124481146.16191578</v>
+        <v>146089221.55631337</v>
       </c>
       <c r="K44" s="185">
         <f>IF(D44=0,0,D44*$L$40-E44)</f>
-        <v>497924584.64766312</v>
+        <v>438267664.66894007</v>
       </c>
       <c r="L44" s="185">
         <f ca="1">IFERROR(K44/$C$3,0)</f>
-        <v>124481146.16191578</v>
+        <v>146089221.55631337</v>
       </c>
       <c r="S44" s="173">
         <v>0.9</v>
@@ -7505,35 +7505,35 @@
       </c>
       <c r="E45" s="46">
         <f>E74</f>
-        <v>1645929684.9651449</v>
+        <v>1730858462.8752089</v>
       </c>
       <c r="F45" s="176">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.94570532021224707</v>
+        <v>0.9945030287913792</v>
       </c>
       <c r="G45" s="184">
         <f>D45*$H$40-E45</f>
-        <v>7474570.3540039063</v>
+        <v>-77454207.556060076</v>
       </c>
       <c r="H45" s="184">
         <f ca="1">IFERROR(G45/$C$3,0)</f>
-        <v>1868642.5885009766</v>
+        <v>-25818069.185353357</v>
       </c>
       <c r="I45" s="204">
         <f>D45*$J$40-E45</f>
-        <v>94495846.949748755</v>
+        <v>9567069.0396847725</v>
       </c>
       <c r="J45" s="204">
         <f ca="1">IFERROR(I45/$C$3,0)</f>
-        <v>23623961.737437189</v>
+        <v>3189023.0132282577</v>
       </c>
       <c r="K45" s="185">
         <f>D45*$L$40-E45</f>
-        <v>94495846.949748755</v>
+        <v>9567069.0396847725</v>
       </c>
       <c r="L45" s="185">
         <f ca="1">IFERROR(K45/$C$3,0)</f>
-        <v>23623961.737437189</v>
+        <v>3189023.0132282577</v>
       </c>
       <c r="S45" s="173">
         <v>0.95</v>
@@ -7550,35 +7550,35 @@
       </c>
       <c r="E46" s="47">
         <f>SUM(E42:E45)</f>
-        <v>8584778682.5667133</v>
+        <v>8886755913.7078533</v>
       </c>
       <c r="F46" s="177">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.81000772889723138</v>
+        <v>0.83850047171796716</v>
       </c>
       <c r="G46" s="181">
         <f>SUM(G42:G45)</f>
-        <v>1483692836.2687573</v>
+        <v>1181715605.1276166</v>
       </c>
       <c r="H46" s="181">
         <f ca="1">IFERROR(G46/$C$3,0)</f>
-        <v>370923209.06718934</v>
+        <v>393905201.70920557</v>
       </c>
       <c r="I46" s="186">
         <f>SUM(I42:I45)</f>
-        <v>2013612389.8916771</v>
+        <v>1711635158.7505367</v>
       </c>
       <c r="J46" s="186">
         <f ca="1">IFERROR(I46/$C$3,0)</f>
-        <v>503403097.47291929</v>
+        <v>570545052.91684556</v>
       </c>
       <c r="K46" s="186">
         <f>SUM(K42:K45)</f>
-        <v>2013612389.8916771</v>
+        <v>1711635158.7505367</v>
       </c>
       <c r="L46" s="186">
         <f ca="1">IFERROR(K46/$C$3,0)</f>
-        <v>503403097.47291929</v>
+        <v>570545052.91684556</v>
       </c>
       <c r="S46" s="173">
         <v>1</v>
@@ -7591,33 +7591,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="265" t="s">
+      <c r="B48" s="275" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="266"/>
-      <c r="D48" s="266"/>
-      <c r="E48" s="266"/>
-      <c r="F48" s="266"/>
-      <c r="G48" s="266"/>
-      <c r="H48" s="266"/>
-      <c r="I48" s="266"/>
-      <c r="J48" s="266"/>
-      <c r="K48" s="266"/>
-      <c r="L48" s="289"/>
-      <c r="M48" s="272" t="s">
+      <c r="C48" s="276"/>
+      <c r="D48" s="276"/>
+      <c r="E48" s="276"/>
+      <c r="F48" s="276"/>
+      <c r="G48" s="276"/>
+      <c r="H48" s="276"/>
+      <c r="I48" s="276"/>
+      <c r="J48" s="276"/>
+      <c r="K48" s="276"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="273"/>
-      <c r="O48" s="273"/>
-      <c r="P48" s="273"/>
-      <c r="Q48" s="273"/>
-      <c r="R48" s="274"/>
+      <c r="N48" s="264"/>
+      <c r="O48" s="264"/>
+      <c r="P48" s="264"/>
+      <c r="Q48" s="264"/>
+      <c r="R48" s="265"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="290" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="290" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="256" t="s">
@@ -7626,49 +7626,49 @@
       <c r="E49" s="257"/>
       <c r="F49" s="257"/>
       <c r="G49" s="258"/>
-      <c r="H49" s="291" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="292"/>
-      <c r="J49" s="292"/>
-      <c r="K49" s="293"/>
-      <c r="L49" s="294" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="275" t="str">
+      <c r="M49" s="266" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="275" t="str">
+      <c r="N49" s="266" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="277" t="str">
+      <c r="O49" s="268" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="277" t="str">
+      <c r="P49" s="268" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="Q49" s="279" t="str">
+      <c r="Q49" s="270" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="279" t="str">
+      <c r="R49" s="270" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="271"/>
-      <c r="C50" s="271"/>
+      <c r="B50" s="262"/>
+      <c r="C50" s="262"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -7693,13 +7693,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="295"/>
-      <c r="M50" s="276"/>
-      <c r="N50" s="276"/>
-      <c r="O50" s="278"/>
-      <c r="P50" s="278"/>
-      <c r="Q50" s="280"/>
-      <c r="R50" s="280"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="267"/>
+      <c r="N50" s="267"/>
+      <c r="O50" s="269"/>
+      <c r="P50" s="269"/>
+      <c r="Q50" s="271"/>
+      <c r="R50" s="271"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -7732,47 +7732,47 @@
       </c>
       <c r="H51" s="114">
         <f t="shared" ref="H51:H64" si="1">SUMIF($B$10:$B$26,$T51,C$10:C$26)+SUMIF($B$10:$B$26,$U51,C$10:C$26)</f>
-        <v>258036727.34778699</v>
+        <v>263996098.743774</v>
       </c>
       <c r="I51" s="114">
         <f t="shared" ref="I51:I64" si="2">SUMIF($B$10:$B$26,$T51,D$10:D$26)+SUMIF($B$10:$B$26,$U51,D$10:D$26)</f>
-        <v>46523994.503447004</v>
+        <v>47932129.623447001</v>
       </c>
       <c r="J51" s="114">
         <f t="shared" ref="J51:J64" si="3">SUMIF($B$10:$B$26,$T51,E$10:E$26)+SUMIF($B$10:$B$26,$U51,E$10:E$26)</f>
-        <v>140234870.34977701</v>
+        <v>143083924.36977699</v>
       </c>
       <c r="K51" s="114">
         <f t="shared" ref="K51:K64" si="4">SUM(H51:J51)</f>
-        <v>444795592.20101106</v>
+        <v>455012152.73699796</v>
       </c>
       <c r="L51" s="187">
         <f t="shared" ref="L51:L65" si="5">IFERROR(K51/G51,0)</f>
-        <v>0.86474276660953886</v>
+        <v>0.88460514154766678</v>
       </c>
       <c r="M51" s="184">
         <f t="shared" ref="M51:M64" si="6">G51*$H$40-K51</f>
-        <v>43853551.691462755</v>
+        <v>33636991.155475855</v>
       </c>
       <c r="N51" s="184">
         <f t="shared" ref="N51:N65" ca="1" si="7">IFERROR(M51/$C$3,0)</f>
-        <v>10963387.922865689</v>
+        <v>11212330.385158619</v>
       </c>
       <c r="O51" s="180">
         <f t="shared" ref="O51:O64" si="8">G51*$J$40-K51</f>
-        <v>69571927.685803533</v>
+        <v>59355367.149816632</v>
       </c>
       <c r="P51" s="180">
         <f t="shared" ref="P51:P65" ca="1" si="9">IFERROR(O51/$C$3,0)</f>
-        <v>17392981.921450883</v>
+        <v>19785122.383272212</v>
       </c>
       <c r="Q51" s="185">
         <f t="shared" ref="Q51:Q64" si="10">G51*$L$40-K51</f>
-        <v>69571927.685803533</v>
+        <v>59355367.149816632</v>
       </c>
       <c r="R51" s="185">
         <f t="shared" ref="R51:R65" ca="1" si="11">IFERROR(Q51/$C$3,0)</f>
-        <v>17392981.921450883</v>
+        <v>19785122.383272212</v>
       </c>
       <c r="T51" t="s">
         <v>124</v>
@@ -7806,47 +7806,47 @@
       </c>
       <c r="H52" s="114">
         <f t="shared" si="1"/>
-        <v>189896308.25788501</v>
+        <v>190296308.25788501</v>
       </c>
       <c r="I52" s="114">
         <f t="shared" si="2"/>
-        <v>90146733.571477994</v>
+        <v>90821909.251477003</v>
       </c>
       <c r="J52" s="114">
         <f t="shared" si="3"/>
-        <v>340509059.10918701</v>
+        <v>353645050.73910099</v>
       </c>
       <c r="K52" s="114">
         <f t="shared" si="4"/>
-        <v>620552100.93855</v>
+        <v>634763268.24846292</v>
       </c>
       <c r="L52" s="187">
         <f t="shared" si="5"/>
-        <v>0.78998502224612122</v>
+        <v>0.80807634657889726</v>
       </c>
       <c r="M52" s="184">
         <f t="shared" si="6"/>
-        <v>125695586.41058445</v>
+        <v>111484419.10067153</v>
       </c>
       <c r="N52" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>31423896.602646112</v>
+        <v>37161473.033557177</v>
       </c>
       <c r="O52" s="180">
         <f t="shared" si="8"/>
-        <v>164971780.48159158</v>
+        <v>150760613.17167866</v>
       </c>
       <c r="P52" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>41242945.120397896</v>
+        <v>50253537.72389289</v>
       </c>
       <c r="Q52" s="185">
         <f t="shared" si="10"/>
-        <v>164971780.48159158</v>
+        <v>150760613.17167866</v>
       </c>
       <c r="R52" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>41242945.120397896</v>
+        <v>50253537.72389289</v>
       </c>
       <c r="T52" t="s">
         <v>70</v>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="H53" s="114">
         <f t="shared" si="1"/>
-        <v>47429875.460000001</v>
+        <v>48019875.460000001</v>
       </c>
       <c r="I53" s="114">
         <f t="shared" si="2"/>
@@ -7892,35 +7892,35 @@
       </c>
       <c r="K53" s="114">
         <f t="shared" si="4"/>
-        <v>47429875.460000001</v>
+        <v>48019875.460000001</v>
       </c>
       <c r="L53" s="187">
         <f t="shared" si="5"/>
-        <v>0.1803738938493786</v>
+        <v>0.18261763993428839</v>
       </c>
       <c r="M53" s="184">
         <f t="shared" si="6"/>
-        <v>202375574.34986019</v>
+        <v>201785574.34986019</v>
       </c>
       <c r="N53" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>50593893.587465048</v>
+        <v>67261858.116620064</v>
       </c>
       <c r="O53" s="180">
         <f t="shared" si="8"/>
-        <v>215523229.60301074</v>
+        <v>214933229.60301074</v>
       </c>
       <c r="P53" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>53880807.400752686</v>
+        <v>71644409.867670253</v>
       </c>
       <c r="Q53" s="185">
         <f t="shared" si="10"/>
-        <v>215523229.60301074</v>
+        <v>214933229.60301074</v>
       </c>
       <c r="R53" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>53880807.400752686</v>
+        <v>71644409.867670253</v>
       </c>
       <c r="T53" t="s">
         <v>169</v>
@@ -7954,47 +7954,47 @@
       </c>
       <c r="H54" s="114">
         <f t="shared" si="1"/>
-        <v>464604407.979559</v>
+        <v>482508837.979559</v>
       </c>
       <c r="I54" s="114">
         <f t="shared" si="2"/>
-        <v>42720135.969465002</v>
+        <v>43096712.549465001</v>
       </c>
       <c r="J54" s="114">
         <f t="shared" si="3"/>
-        <v>150846270.519853</v>
+        <v>151436270.519853</v>
       </c>
       <c r="K54" s="114">
         <f t="shared" si="4"/>
-        <v>658170814.46887708</v>
+        <v>677041821.048877</v>
       </c>
       <c r="L54" s="187">
         <f t="shared" si="5"/>
-        <v>0.90573324368886554</v>
+        <v>0.93170233503359501</v>
       </c>
       <c r="M54" s="184">
         <f t="shared" si="6"/>
-        <v>32167403.877695203</v>
+        <v>13296397.297695279</v>
       </c>
       <c r="N54" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>8041850.9694238007</v>
+        <v>4432132.432565093</v>
       </c>
       <c r="O54" s="180">
         <f t="shared" si="8"/>
-        <v>68500994.316988468</v>
+        <v>49629987.736988544</v>
       </c>
       <c r="P54" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>17125248.579247117</v>
+        <v>16543329.245662848</v>
       </c>
       <c r="Q54" s="185">
         <f t="shared" si="10"/>
-        <v>68500994.316988468</v>
+        <v>49629987.736988544</v>
       </c>
       <c r="R54" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>17125248.579247117</v>
+        <v>16543329.245662848</v>
       </c>
       <c r="T54" t="s">
         <v>115</v>
@@ -8052,7 +8052,7 @@
       </c>
       <c r="N55" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>50259541.028313339</v>
+        <v>67012721.371084452</v>
       </c>
       <c r="O55" s="180">
         <f t="shared" si="8"/>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="P55" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>56974553.522946909</v>
+        <v>75966071.363929212</v>
       </c>
       <c r="Q55" s="185">
         <f t="shared" si="10"/>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="R55" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>56974553.522946909</v>
+        <v>75966071.363929212</v>
       </c>
       <c r="T55" t="s">
         <v>182</v>
@@ -8102,47 +8102,47 @@
       </c>
       <c r="H56" s="114">
         <f t="shared" si="1"/>
-        <v>184450526.976354</v>
+        <v>190036588.29052001</v>
       </c>
       <c r="I56" s="114">
         <f t="shared" si="2"/>
-        <v>47411295.139939003</v>
+        <v>55882903.289934002</v>
       </c>
       <c r="J56" s="114">
         <f t="shared" si="3"/>
-        <v>144992226.38817099</v>
+        <v>151739974.348151</v>
       </c>
       <c r="K56" s="114">
         <f t="shared" si="4"/>
-        <v>376854048.50446403</v>
+        <v>397659465.92860502</v>
       </c>
       <c r="L56" s="187">
         <f t="shared" si="5"/>
-        <v>0.65545991456955943</v>
+        <v>0.69164664835026324</v>
       </c>
       <c r="M56" s="184">
         <f t="shared" si="6"/>
-        <v>169344640.57074344</v>
+        <v>148539223.14660245</v>
       </c>
       <c r="N56" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>42336160.14268586</v>
+        <v>49513074.382200815</v>
       </c>
       <c r="O56" s="180">
         <f t="shared" si="8"/>
-        <v>198091939.99575436</v>
+        <v>177286522.57161337</v>
       </c>
       <c r="P56" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>49522984.99893859</v>
+        <v>59095507.523871124</v>
       </c>
       <c r="Q56" s="185">
         <f t="shared" si="10"/>
-        <v>198091939.99575436</v>
+        <v>177286522.57161337</v>
       </c>
       <c r="R56" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>49522984.99893859</v>
+        <v>59095507.523871124</v>
       </c>
       <c r="T56" t="s">
         <v>225</v>
@@ -8176,47 +8176,47 @@
       </c>
       <c r="H57" s="114">
         <f t="shared" si="1"/>
-        <v>469087694.35771102</v>
+        <v>491342417.01869798</v>
       </c>
       <c r="I57" s="114">
         <f t="shared" si="2"/>
-        <v>52390125.779923998</v>
+        <v>56669125.779923998</v>
       </c>
       <c r="J57" s="114">
         <f t="shared" si="3"/>
-        <v>301606082.52941</v>
+        <v>312947839.26937002</v>
       </c>
       <c r="K57" s="114">
         <f t="shared" si="4"/>
-        <v>823083902.667045</v>
+        <v>860959382.06799197</v>
       </c>
       <c r="L57" s="187">
         <f t="shared" si="5"/>
-        <v>0.74206250184242428</v>
+        <v>0.7762096561139098</v>
       </c>
       <c r="M57" s="184">
         <f t="shared" si="6"/>
-        <v>230640959.58146429</v>
+        <v>192765480.18051732</v>
       </c>
       <c r="N57" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>57660239.895366073</v>
+        <v>64255160.060172439</v>
       </c>
       <c r="O57" s="180">
         <f t="shared" si="8"/>
-        <v>286100162.85770166</v>
+        <v>248224683.45675468</v>
       </c>
       <c r="P57" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>71525040.714425415</v>
+        <v>82741561.152251557</v>
       </c>
       <c r="Q57" s="185">
         <f t="shared" si="10"/>
-        <v>286100162.85770166</v>
+        <v>248224683.45675468</v>
       </c>
       <c r="R57" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>71525040.714425415</v>
+        <v>82741561.152251557</v>
       </c>
       <c r="T57" t="s">
         <v>120</v>
@@ -8250,47 +8250,47 @@
       </c>
       <c r="H58" s="114">
         <f t="shared" si="1"/>
-        <v>253561209.328915</v>
+        <v>255492042.620024</v>
       </c>
       <c r="I58" s="114">
         <f t="shared" si="2"/>
-        <v>63950429.039943002</v>
+        <v>67695304.759942994</v>
       </c>
       <c r="J58" s="114">
         <f t="shared" si="3"/>
-        <v>180549813.52216801</v>
+        <v>183532696.38125801</v>
       </c>
       <c r="K58" s="114">
         <f t="shared" si="4"/>
-        <v>498061451.89102602</v>
+        <v>506720043.76122499</v>
       </c>
       <c r="L58" s="187">
         <f t="shared" si="5"/>
-        <v>0.81040832225637016</v>
+        <v>0.82449693498475674</v>
       </c>
       <c r="M58" s="184">
         <f t="shared" si="6"/>
-        <v>85790374.777151346</v>
+        <v>77131782.906952381</v>
       </c>
       <c r="N58" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>21447593.694287837</v>
+        <v>25710594.302317459</v>
       </c>
       <c r="O58" s="180">
         <f t="shared" si="8"/>
-        <v>116519418.28600287</v>
+        <v>107860826.41580391</v>
       </c>
       <c r="P58" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>29129854.571500719</v>
+        <v>35953608.805267967</v>
       </c>
       <c r="Q58" s="185">
         <f t="shared" si="10"/>
-        <v>116519418.28600287</v>
+        <v>107860826.41580391</v>
       </c>
       <c r="R58" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>29129854.571500719</v>
+        <v>35953608.805267967</v>
       </c>
       <c r="T58" t="s">
         <v>125</v>
@@ -8324,7 +8324,7 @@
       </c>
       <c r="H59" s="114">
         <f t="shared" si="1"/>
-        <v>215561847.16</v>
+        <v>206615067.16</v>
       </c>
       <c r="I59" s="114">
         <f t="shared" si="2"/>
@@ -8336,35 +8336,35 @@
       </c>
       <c r="K59" s="114">
         <f t="shared" si="4"/>
-        <v>215561847.16</v>
+        <v>206615067.16</v>
       </c>
       <c r="L59" s="187">
         <f t="shared" si="5"/>
-        <v>0.48566732521621037</v>
+        <v>0.46550996077929907</v>
       </c>
       <c r="M59" s="184">
         <f t="shared" si="6"/>
-        <v>206092532.63759902</v>
+        <v>215039312.63759902</v>
       </c>
       <c r="N59" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>51523133.159399755</v>
+        <v>71679770.879199669</v>
       </c>
       <c r="O59" s="180">
         <f t="shared" si="8"/>
-        <v>228284868.41642001</v>
+        <v>237231648.41642001</v>
       </c>
       <c r="P59" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>57071217.104105003</v>
+        <v>79077216.138806671</v>
       </c>
       <c r="Q59" s="185">
         <f t="shared" si="10"/>
-        <v>228284868.41642001</v>
+        <v>237231648.41642001</v>
       </c>
       <c r="R59" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>57071217.104105003</v>
+        <v>79077216.138806671</v>
       </c>
       <c r="T59" t="s">
         <v>170</v>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="H60" s="114">
         <f t="shared" si="1"/>
-        <v>309803234.24329299</v>
+        <v>334965416.39326602</v>
       </c>
       <c r="I60" s="114">
         <f t="shared" si="2"/>
@@ -8406,39 +8406,39 @@
       </c>
       <c r="J60" s="114">
         <f t="shared" si="3"/>
-        <v>96322302.232531995</v>
+        <v>97847527.472525001</v>
       </c>
       <c r="K60" s="114">
         <f t="shared" si="4"/>
-        <v>487710509.36234903</v>
+        <v>514397916.75231504</v>
       </c>
       <c r="L60" s="187">
         <f t="shared" si="5"/>
-        <v>0.8420616762976888</v>
+        <v>0.88813909839838412</v>
       </c>
       <c r="M60" s="184">
         <f t="shared" si="6"/>
-        <v>62516388.424215436</v>
+        <v>35828981.034249425</v>
       </c>
       <c r="N60" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>15629097.106053859</v>
+        <v>11942993.678083142</v>
       </c>
       <c r="O60" s="180">
         <f t="shared" si="8"/>
-        <v>91475698.834034681</v>
+        <v>64788291.44406867</v>
       </c>
       <c r="P60" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>22868924.70850867</v>
+        <v>21596097.14802289</v>
       </c>
       <c r="Q60" s="185">
         <f t="shared" si="10"/>
-        <v>91475698.834034681</v>
+        <v>64788291.44406867</v>
       </c>
       <c r="R60" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>22868924.70850867</v>
+        <v>21596097.14802289</v>
       </c>
       <c r="T60" t="s">
         <v>220</v>
@@ -8472,47 +8472,47 @@
       </c>
       <c r="H61" s="114">
         <f t="shared" si="1"/>
-        <v>428037130.09258002</v>
+        <v>440052239.37646002</v>
       </c>
       <c r="I61" s="114">
         <f t="shared" si="2"/>
-        <v>58268998.644919001</v>
+        <v>59219998.644919001</v>
       </c>
       <c r="J61" s="114">
         <f t="shared" si="3"/>
-        <v>192989083.319877</v>
+        <v>200790750.04987699</v>
       </c>
       <c r="K61" s="114">
         <f t="shared" si="4"/>
-        <v>679295212.05737603</v>
+        <v>700062988.07125592</v>
       </c>
       <c r="L61" s="187">
         <f t="shared" si="5"/>
-        <v>0.94795148735102464</v>
+        <v>0.97693276649430749</v>
       </c>
       <c r="M61" s="184">
         <f t="shared" si="6"/>
-        <v>1467949.4181463718</v>
+        <v>-19299826.595733523</v>
       </c>
       <c r="N61" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>366987.35453659296</v>
+        <v>-6433275.5319111748</v>
       </c>
       <c r="O61" s="180">
         <f t="shared" si="8"/>
-        <v>37297589.495805502</v>
+        <v>16529813.481925607</v>
       </c>
       <c r="P61" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>9324397.3739513755</v>
+        <v>5509937.8273085356</v>
       </c>
       <c r="Q61" s="185">
         <f t="shared" si="10"/>
-        <v>37297589.495805502</v>
+        <v>16529813.481925607</v>
       </c>
       <c r="R61" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>9324397.3739513755</v>
+        <v>5509937.8273085356</v>
       </c>
       <c r="T61" t="s">
         <v>126</v>
@@ -8546,47 +8546,47 @@
       </c>
       <c r="H62" s="114">
         <f t="shared" si="1"/>
-        <v>130775176.729406</v>
+        <v>133182163.255797</v>
       </c>
       <c r="I62" s="114">
         <f t="shared" si="2"/>
-        <v>38616940.117797002</v>
+        <v>39865291.477794997</v>
       </c>
       <c r="J62" s="114">
         <f t="shared" si="3"/>
-        <v>185920937.347022</v>
+        <v>191182198.64701799</v>
       </c>
       <c r="K62" s="114">
         <f t="shared" si="4"/>
-        <v>355313054.19422501</v>
+        <v>364229653.38060999</v>
       </c>
       <c r="L62" s="187">
         <f t="shared" si="5"/>
-        <v>0.74485478131836524</v>
+        <v>0.76354694998112371</v>
       </c>
       <c r="M62" s="184">
         <f t="shared" si="6"/>
-        <v>97859040.488536417</v>
+        <v>88942441.302151442</v>
       </c>
       <c r="N62" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>24464760.122134104</v>
+        <v>29647480.434050482</v>
       </c>
       <c r="O62" s="180">
         <f t="shared" si="8"/>
-        <v>121710203.36657649</v>
+        <v>112793604.18019152</v>
       </c>
       <c r="P62" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>30427550.841644123</v>
+        <v>37597868.060063839</v>
       </c>
       <c r="Q62" s="185">
         <f t="shared" si="10"/>
-        <v>121710203.36657649</v>
+        <v>112793604.18019152</v>
       </c>
       <c r="R62" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>30427550.841644123</v>
+        <v>37597868.060063839</v>
       </c>
       <c r="T62" t="s">
         <v>112</v>
@@ -8620,47 +8620,47 @@
       </c>
       <c r="H63" s="114">
         <f t="shared" si="1"/>
-        <v>434916433.51514399</v>
+        <v>480229048.13510603</v>
       </c>
       <c r="I63" s="114">
         <f t="shared" si="2"/>
-        <v>285495088.43090999</v>
+        <v>286587088.43090999</v>
       </c>
       <c r="J63" s="114">
         <f t="shared" si="3"/>
-        <v>280204913.43528301</v>
+        <v>283835544.43512303</v>
       </c>
       <c r="K63" s="114">
         <f t="shared" si="4"/>
-        <v>1000616435.3813369</v>
+        <v>1050651681.0011389</v>
       </c>
       <c r="L63" s="187">
         <f t="shared" si="5"/>
-        <v>1.0221072655120125</v>
+        <v>1.0732171476520032</v>
       </c>
       <c r="M63" s="184">
         <f t="shared" si="6"/>
-        <v>-70591137.952220798</v>
+        <v>-120626383.5720228</v>
       </c>
       <c r="N63" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>-17647784.488055199</v>
+        <v>-40208794.524007596</v>
       </c>
       <c r="O63" s="180">
         <f t="shared" si="8"/>
-        <v>-21642438.087530375</v>
+        <v>-71677683.707332373</v>
       </c>
       <c r="P63" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>-5410609.5218825936</v>
+        <v>-23892561.235777456</v>
       </c>
       <c r="Q63" s="185">
         <f t="shared" si="10"/>
-        <v>-21642438.087530375</v>
+        <v>-71677683.707332373</v>
       </c>
       <c r="R63" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>-5410609.5218825936</v>
+        <v>-23892561.235777456</v>
       </c>
       <c r="T63" t="s">
         <v>127</v>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="H64" s="114">
         <f t="shared" si="1"/>
-        <v>112242398.67601499</v>
+        <v>116811678.075921</v>
       </c>
       <c r="I64" s="114">
         <f t="shared" si="2"/>
@@ -8702,39 +8702,39 @@
       </c>
       <c r="J64" s="114">
         <f t="shared" si="3"/>
-        <v>161714051.56884199</v>
+        <v>165504754.06879202</v>
       </c>
       <c r="K64" s="114">
         <f t="shared" si="4"/>
-        <v>422101367.83640999</v>
+        <v>430461349.73626602</v>
       </c>
       <c r="L64" s="187">
         <f t="shared" si="5"/>
-        <v>0.78616149911730271</v>
+        <v>0.80173191988298831</v>
       </c>
       <c r="M64" s="184">
         <f t="shared" si="6"/>
-        <v>87967237.52626121</v>
+        <v>79607255.62640518</v>
       </c>
       <c r="N64" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>21991809.381565303</v>
+        <v>26535751.875468392</v>
       </c>
       <c r="O64" s="180">
         <f t="shared" si="8"/>
-        <v>114812953.5979808</v>
+        <v>106452971.69812477</v>
       </c>
       <c r="P64" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>28703238.399495199</v>
+        <v>35484323.899374925</v>
       </c>
       <c r="Q64" s="185">
         <f t="shared" si="10"/>
-        <v>114812953.5979808</v>
+        <v>106452971.69812477</v>
       </c>
       <c r="R64" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>28703238.399495199</v>
+        <v>35484323.899374925</v>
       </c>
       <c r="T64" t="s">
         <v>122</v>
@@ -8766,47 +8766,47 @@
       </c>
       <c r="H65" s="135">
         <f t="shared" si="12"/>
-        <v>3504076393.5446467</v>
+        <v>3639221204.1870084</v>
       </c>
       <c r="I65" s="135">
         <f t="shared" si="12"/>
-        <v>987882992.37589896</v>
+        <v>1010129714.9858909</v>
       </c>
       <c r="J65" s="135">
         <f t="shared" si="12"/>
-        <v>2446889611.6810222</v>
+        <v>2506546531.6597452</v>
       </c>
       <c r="K65" s="135">
         <f t="shared" si="12"/>
-        <v>6938848997.6015682</v>
+        <v>7155897450.8326426</v>
       </c>
       <c r="L65" s="189">
         <f t="shared" si="5"/>
-        <v>0.7833456752390825</v>
+        <v>0.80784886982000847</v>
       </c>
       <c r="M65" s="181">
         <f>SUM(M51:M64)</f>
-        <v>1476218265.914753</v>
+        <v>1259169812.6836772</v>
       </c>
       <c r="N65" s="181">
         <f t="shared" ca="1" si="7"/>
-        <v>369054566.47868824</v>
+        <v>419723270.89455909</v>
       </c>
       <c r="O65" s="181">
         <f>SUM(O51:O64)</f>
-        <v>1919116542.9419279</v>
+        <v>1702068089.7108521</v>
       </c>
       <c r="P65" s="181">
         <f t="shared" ca="1" si="9"/>
-        <v>479779135.73548198</v>
+        <v>567356029.90361738</v>
       </c>
       <c r="Q65" s="186">
         <f>SUM(Q51:Q64)</f>
-        <v>1919116542.9419279</v>
+        <v>1702068089.7108521</v>
       </c>
       <c r="R65" s="186">
         <f t="shared" ca="1" si="11"/>
-        <v>479779135.73548198</v>
+        <v>567356029.90361738</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8815,21 +8815,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="286" t="s">
+      <c r="B67" s="293" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="287"/>
-      <c r="D67" s="287"/>
-      <c r="E67" s="287"/>
+      <c r="C67" s="294"/>
+      <c r="D67" s="294"/>
+      <c r="E67" s="294"/>
       <c r="F67" s="296"/>
-      <c r="G67" s="272" t="s">
+      <c r="G67" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="273"/>
-      <c r="I67" s="273"/>
-      <c r="J67" s="273"/>
-      <c r="K67" s="273"/>
-      <c r="L67" s="274"/>
+      <c r="H67" s="264"/>
+      <c r="I67" s="264"/>
+      <c r="J67" s="264"/>
+      <c r="K67" s="264"/>
+      <c r="L67" s="265"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -8891,35 +8891,35 @@
       </c>
       <c r="E69" s="114">
         <f>IFERROR($C$31,0)</f>
-        <v>251052873.62514299</v>
+        <v>259365932.35194299</v>
       </c>
       <c r="F69" s="187">
         <f t="shared" ref="F69:F74" si="13">IFERROR(E69/D69,0)</f>
-        <v>0.97968984473548171</v>
+        <v>1.012130099633723</v>
       </c>
       <c r="G69" s="184">
         <f>D69*$H$40-E69</f>
-        <v>-7608245.4854266047</v>
+        <v>-15921304.212226599</v>
       </c>
       <c r="H69" s="184">
         <f t="shared" ref="H69:H74" ca="1" si="14">IFERROR(G69/$C$3,0)</f>
-        <v>-1902061.3713566512</v>
+        <v>-5307101.4040755332</v>
       </c>
       <c r="I69" s="204">
         <f>D69*$J$40-E69</f>
-        <v>5204629.6798216403</v>
+        <v>-3108429.0469783545</v>
       </c>
       <c r="J69" s="204">
         <f t="shared" ref="J69:J74" ca="1" si="15">IFERROR(I69/$C$3,0)</f>
-        <v>1301157.4199554101</v>
+        <v>-1036143.0156594515</v>
       </c>
       <c r="K69" s="185">
         <f>D69*$L$40-E69</f>
-        <v>5204629.6798216403</v>
+        <v>-3108429.0469783545</v>
       </c>
       <c r="L69" s="185">
         <f t="shared" ref="L69:L74" ca="1" si="16">IFERROR(K69/$C$3,0)</f>
-        <v>1301157.4199554101</v>
+        <v>-1036143.0156594515</v>
       </c>
     </row>
     <row r="70" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8935,35 +8935,35 @@
       </c>
       <c r="E70" s="114">
         <f>IFERROR($C$32,0)</f>
-        <v>443836083.938923</v>
+        <v>457145084.04292297</v>
       </c>
       <c r="F70" s="187">
         <f t="shared" si="13"/>
-        <v>1.1108165171108031</v>
+        <v>1.1441257897831596</v>
       </c>
       <c r="G70" s="184">
         <f>D70*$H$40-E70</f>
-        <v>-64255592.249206662</v>
+        <v>-77564592.353206635</v>
       </c>
       <c r="H70" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>-16063898.062301666</v>
+        <v>-25854864.117735546</v>
       </c>
       <c r="I70" s="204">
         <f>D70*$J$40-E70</f>
-        <v>-44277671.633958399</v>
+        <v>-57586671.737958372</v>
       </c>
       <c r="J70" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>-11069417.9084896</v>
+        <v>-19195557.245986123</v>
       </c>
       <c r="K70" s="185">
         <f>D70*$L$40-E70</f>
-        <v>-44277671.633958399</v>
+        <v>-57586671.737958372</v>
       </c>
       <c r="L70" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>-11069417.9084896</v>
+        <v>-19195557.245986123</v>
       </c>
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.25">
@@ -8979,35 +8979,35 @@
       </c>
       <c r="E71" s="114">
         <f>M21</f>
-        <v>951040727.40107894</v>
+        <v>1014347446.480343</v>
       </c>
       <c r="F71" s="187">
         <f t="shared" si="13"/>
-        <v>0.87685072407994447</v>
+        <v>0.9352189315230397</v>
       </c>
       <c r="G71" s="184">
         <f>D71*$H$40-E71</f>
-        <v>79338408.088637352</v>
+        <v>16031689.009373307</v>
       </c>
       <c r="H71" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>19834602.022159338</v>
+        <v>5343896.3364577694</v>
       </c>
       <c r="I71" s="204">
         <f>D71*$J$40-E71</f>
-        <v>133568888.9038856</v>
+        <v>70262169.824621558</v>
       </c>
       <c r="J71" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>33392222.225971401</v>
+        <v>23420723.274873853</v>
       </c>
       <c r="K71" s="185">
         <f>D71*$L$40-E71</f>
-        <v>133568888.9038856</v>
+        <v>70262169.824621558</v>
       </c>
       <c r="L71" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>33392222.225971401</v>
+        <v>23420723.274873853</v>
       </c>
     </row>
     <row r="72" spans="2:21" hidden="1" x14ac:dyDescent="0.25">
@@ -9109,35 +9109,35 @@
       </c>
       <c r="E74" s="115">
         <f>SUM(E69:E73)</f>
-        <v>1645929684.9651449</v>
+        <v>1730858462.8752089</v>
       </c>
       <c r="F74" s="177">
         <f t="shared" si="13"/>
-        <v>0.94570532021224707</v>
+        <v>0.9945030287913792</v>
       </c>
       <c r="G74" s="181">
         <f>SUM(G69:G73)</f>
-        <v>7474570.3540040851</v>
+        <v>-77454207.556059927</v>
       </c>
       <c r="H74" s="181">
         <f t="shared" ca="1" si="14"/>
-        <v>1868642.5885010213</v>
+        <v>-25818069.185353309</v>
       </c>
       <c r="I74" s="186">
         <f>SUM(I69:I73)</f>
-        <v>94495846.949748844</v>
+        <v>9567069.0396848321</v>
       </c>
       <c r="J74" s="186">
         <f t="shared" ca="1" si="15"/>
-        <v>23623961.737437211</v>
+        <v>3189023.0132282772</v>
       </c>
       <c r="K74" s="186">
         <f>SUM(K69:K73)</f>
-        <v>94495846.949748844</v>
+        <v>9567069.0396848321</v>
       </c>
       <c r="L74" s="186">
         <f t="shared" ca="1" si="16"/>
-        <v>23623961.737437211</v>
+        <v>3189023.0132282772</v>
       </c>
     </row>
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9150,10 +9150,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="271" t="s">
+      <c r="B78" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="271" t="s">
+      <c r="C78" s="262" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="D80" s="131">
         <f t="shared" ref="D80:D93" si="17">SUMIF($B$10:$B$26,$T80,$F$10:$F$26)+SUMIF($B$10:$B$26,$U80,$F$10:$F$26)</f>
-        <v>385081374.45986003</v>
+        <v>414273536.65985</v>
       </c>
       <c r="T80" t="str">
         <f t="shared" ref="T80:U93" si="18">T51</f>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D81" s="132">
         <f t="shared" si="17"/>
-        <v>154331547.07999998</v>
+        <v>154511547.07999998</v>
       </c>
       <c r="T81" t="str">
         <f t="shared" si="18"/>
@@ -9222,7 +9222,7 @@
       </c>
       <c r="D82" s="132">
         <f t="shared" si="17"/>
-        <v>7027026.8399999999</v>
+        <v>9945945.6799999997</v>
       </c>
       <c r="T82" t="str">
         <f t="shared" si="18"/>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="D83" s="131">
         <f t="shared" si="17"/>
-        <v>382969885.31973499</v>
+        <v>383780696.16973501</v>
       </c>
       <c r="T83" t="str">
         <f t="shared" si="18"/>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="D85" s="131">
         <f t="shared" si="17"/>
-        <v>65692612.399999999</v>
+        <v>65782612.399999999</v>
       </c>
       <c r="T85" t="str">
         <f t="shared" si="18"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="D86" s="132">
         <f t="shared" si="17"/>
-        <v>955586205.67996895</v>
+        <v>990682602.56996906</v>
       </c>
       <c r="T86" t="str">
         <f t="shared" si="18"/>
@@ -9322,7 +9322,7 @@
       </c>
       <c r="D87" s="131">
         <f t="shared" si="17"/>
-        <v>297399826.70943499</v>
+        <v>315237664.88943499</v>
       </c>
       <c r="T87" t="str">
         <f t="shared" si="18"/>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="D88" s="132">
         <f t="shared" si="17"/>
-        <v>11975945.619999999</v>
+        <v>13579549.18</v>
       </c>
       <c r="T88" t="str">
         <f t="shared" si="18"/>
@@ -9382,7 +9382,7 @@
       </c>
       <c r="D90" s="131">
         <f t="shared" si="17"/>
-        <v>569324336.12944102</v>
+        <v>579669561.29943395</v>
       </c>
       <c r="T90" t="str">
         <f t="shared" si="18"/>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="D91" s="132">
         <f t="shared" si="17"/>
-        <v>148907397.44993299</v>
+        <v>155970460.17992401</v>
       </c>
       <c r="T91" t="str">
         <f t="shared" si="18"/>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="D93" s="132">
         <f t="shared" si="17"/>
-        <v>152515138.31800002</v>
+        <v>154461084.31800002</v>
       </c>
       <c r="T93" t="str">
         <f t="shared" si="18"/>
@@ -9460,12 +9460,20 @@
       <c r="C94" s="58"/>
       <c r="D94" s="120">
         <f>SUM(D80:D93)</f>
-        <v>3199956378.5567727</v>
+        <v>3307040342.9767461</v>
       </c>
     </row>
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B48:L48"/>
+    <mergeCell ref="G67:L67"/>
     <mergeCell ref="M48:R48"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="C49:C50"/>
@@ -9478,14 +9486,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B48:L48"/>
-    <mergeCell ref="G67:L67"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -10113,11 +10113,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="262" t="s">
+      <c r="B40" s="272" t="s">
         <v>163</v>
       </c>
-      <c r="C40" s="263"/>
-      <c r="D40" s="264"/>
+      <c r="C40" s="273"/>
+      <c r="D40" s="274"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -10437,33 +10437,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="265" t="s">
+      <c r="B48" s="275" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="266"/>
-      <c r="D48" s="266"/>
-      <c r="E48" s="266"/>
-      <c r="F48" s="266"/>
-      <c r="G48" s="266"/>
-      <c r="H48" s="266"/>
-      <c r="I48" s="266"/>
-      <c r="J48" s="266"/>
-      <c r="K48" s="266"/>
-      <c r="L48" s="289"/>
-      <c r="M48" s="272" t="s">
+      <c r="C48" s="276"/>
+      <c r="D48" s="276"/>
+      <c r="E48" s="276"/>
+      <c r="F48" s="276"/>
+      <c r="G48" s="276"/>
+      <c r="H48" s="276"/>
+      <c r="I48" s="276"/>
+      <c r="J48" s="276"/>
+      <c r="K48" s="276"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="273"/>
-      <c r="O48" s="273"/>
-      <c r="P48" s="273"/>
-      <c r="Q48" s="273"/>
-      <c r="R48" s="274"/>
+      <c r="N48" s="264"/>
+      <c r="O48" s="264"/>
+      <c r="P48" s="264"/>
+      <c r="Q48" s="264"/>
+      <c r="R48" s="265"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="290" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="290" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="256" t="s">
@@ -10472,49 +10472,49 @@
       <c r="E49" s="257"/>
       <c r="F49" s="257"/>
       <c r="G49" s="258"/>
-      <c r="H49" s="291" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="292"/>
-      <c r="J49" s="292"/>
-      <c r="K49" s="293"/>
-      <c r="L49" s="294" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="275" t="str">
+      <c r="M49" s="266" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="275" t="str">
+      <c r="N49" s="266" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="277" t="str">
+      <c r="O49" s="268" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="277" t="str">
+      <c r="P49" s="268" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="279" t="str">
+      <c r="Q49" s="270" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="279" t="str">
+      <c r="R49" s="270" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="271"/>
-      <c r="C50" s="271"/>
+      <c r="B50" s="262"/>
+      <c r="C50" s="262"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -10539,13 +10539,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="295"/>
-      <c r="M50" s="276"/>
-      <c r="N50" s="276"/>
-      <c r="O50" s="278"/>
-      <c r="P50" s="278"/>
-      <c r="Q50" s="280"/>
-      <c r="R50" s="280"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="267"/>
+      <c r="N50" s="267"/>
+      <c r="O50" s="269"/>
+      <c r="P50" s="269"/>
+      <c r="Q50" s="271"/>
+      <c r="R50" s="271"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -11661,21 +11661,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="286" t="s">
+      <c r="B67" s="293" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="287"/>
-      <c r="D67" s="287"/>
-      <c r="E67" s="287"/>
+      <c r="C67" s="294"/>
+      <c r="D67" s="294"/>
+      <c r="E67" s="294"/>
       <c r="F67" s="296"/>
-      <c r="G67" s="272" t="s">
+      <c r="G67" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="273"/>
-      <c r="I67" s="273"/>
-      <c r="J67" s="273"/>
-      <c r="K67" s="273"/>
-      <c r="L67" s="274"/>
+      <c r="H67" s="264"/>
+      <c r="I67" s="264"/>
+      <c r="J67" s="264"/>
+      <c r="K67" s="264"/>
+      <c r="L67" s="265"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -11996,10 +11996,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="271" t="s">
+      <c r="B78" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="271" t="s">
+      <c r="C78" s="262" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -12312,6 +12312,12 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -12326,12 +12332,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -12959,11 +12959,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="262" t="s">
+      <c r="B40" s="272" t="s">
         <v>175</v>
       </c>
-      <c r="C40" s="263"/>
-      <c r="D40" s="264"/>
+      <c r="C40" s="273"/>
+      <c r="D40" s="274"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -13283,33 +13283,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="265" t="s">
+      <c r="B48" s="275" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="266"/>
-      <c r="D48" s="266"/>
-      <c r="E48" s="266"/>
-      <c r="F48" s="266"/>
-      <c r="G48" s="266"/>
-      <c r="H48" s="266"/>
-      <c r="I48" s="266"/>
-      <c r="J48" s="266"/>
-      <c r="K48" s="266"/>
-      <c r="L48" s="289"/>
-      <c r="M48" s="272" t="s">
+      <c r="C48" s="276"/>
+      <c r="D48" s="276"/>
+      <c r="E48" s="276"/>
+      <c r="F48" s="276"/>
+      <c r="G48" s="276"/>
+      <c r="H48" s="276"/>
+      <c r="I48" s="276"/>
+      <c r="J48" s="276"/>
+      <c r="K48" s="276"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="273"/>
-      <c r="O48" s="273"/>
-      <c r="P48" s="273"/>
-      <c r="Q48" s="273"/>
-      <c r="R48" s="274"/>
+      <c r="N48" s="264"/>
+      <c r="O48" s="264"/>
+      <c r="P48" s="264"/>
+      <c r="Q48" s="264"/>
+      <c r="R48" s="265"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="290" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="290" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="256" t="s">
@@ -13318,49 +13318,49 @@
       <c r="E49" s="257"/>
       <c r="F49" s="257"/>
       <c r="G49" s="258"/>
-      <c r="H49" s="291" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="292"/>
-      <c r="J49" s="292"/>
-      <c r="K49" s="293"/>
-      <c r="L49" s="294" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="275" t="str">
+      <c r="M49" s="266" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="275" t="str">
+      <c r="N49" s="266" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="277" t="str">
+      <c r="O49" s="268" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="277" t="str">
+      <c r="P49" s="268" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="279" t="str">
+      <c r="Q49" s="270" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="279" t="str">
+      <c r="R49" s="270" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="271"/>
-      <c r="C50" s="271"/>
+      <c r="B50" s="262"/>
+      <c r="C50" s="262"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -13385,13 +13385,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="295"/>
-      <c r="M50" s="276"/>
-      <c r="N50" s="276"/>
-      <c r="O50" s="278"/>
-      <c r="P50" s="278"/>
-      <c r="Q50" s="280"/>
-      <c r="R50" s="280"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="267"/>
+      <c r="N50" s="267"/>
+      <c r="O50" s="269"/>
+      <c r="P50" s="269"/>
+      <c r="Q50" s="271"/>
+      <c r="R50" s="271"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -14507,21 +14507,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="286" t="s">
+      <c r="B67" s="293" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="287"/>
-      <c r="D67" s="287"/>
-      <c r="E67" s="287"/>
+      <c r="C67" s="294"/>
+      <c r="D67" s="294"/>
+      <c r="E67" s="294"/>
       <c r="F67" s="296"/>
-      <c r="G67" s="272" t="s">
+      <c r="G67" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="273"/>
-      <c r="I67" s="273"/>
-      <c r="J67" s="273"/>
-      <c r="K67" s="273"/>
-      <c r="L67" s="274"/>
+      <c r="H67" s="264"/>
+      <c r="I67" s="264"/>
+      <c r="J67" s="264"/>
+      <c r="K67" s="264"/>
+      <c r="L67" s="265"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -14842,10 +14842,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="271" t="s">
+      <c r="B78" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="271" t="s">
+      <c r="C78" s="262" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -15158,6 +15158,12 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -15172,12 +15178,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -15805,11 +15805,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="262" t="s">
+      <c r="B40" s="272" t="s">
         <v>177</v>
       </c>
-      <c r="C40" s="263"/>
-      <c r="D40" s="264"/>
+      <c r="C40" s="273"/>
+      <c r="D40" s="274"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -16129,33 +16129,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="265" t="s">
+      <c r="B48" s="275" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="266"/>
-      <c r="D48" s="266"/>
-      <c r="E48" s="266"/>
-      <c r="F48" s="266"/>
-      <c r="G48" s="266"/>
-      <c r="H48" s="266"/>
-      <c r="I48" s="266"/>
-      <c r="J48" s="266"/>
-      <c r="K48" s="266"/>
-      <c r="L48" s="289"/>
-      <c r="M48" s="272" t="s">
+      <c r="C48" s="276"/>
+      <c r="D48" s="276"/>
+      <c r="E48" s="276"/>
+      <c r="F48" s="276"/>
+      <c r="G48" s="276"/>
+      <c r="H48" s="276"/>
+      <c r="I48" s="276"/>
+      <c r="J48" s="276"/>
+      <c r="K48" s="276"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="273"/>
-      <c r="O48" s="273"/>
-      <c r="P48" s="273"/>
-      <c r="Q48" s="273"/>
-      <c r="R48" s="274"/>
+      <c r="N48" s="264"/>
+      <c r="O48" s="264"/>
+      <c r="P48" s="264"/>
+      <c r="Q48" s="264"/>
+      <c r="R48" s="265"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="290" t="s">
+      <c r="B49" s="287" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="290" t="s">
+      <c r="C49" s="287" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="256" t="s">
@@ -16164,49 +16164,49 @@
       <c r="E49" s="257"/>
       <c r="F49" s="257"/>
       <c r="G49" s="258"/>
-      <c r="H49" s="291" t="s">
+      <c r="H49" s="288" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="292"/>
-      <c r="J49" s="292"/>
-      <c r="K49" s="293"/>
-      <c r="L49" s="294" t="s">
+      <c r="I49" s="289"/>
+      <c r="J49" s="289"/>
+      <c r="K49" s="290"/>
+      <c r="L49" s="291" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="275" t="str">
+      <c r="M49" s="266" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="275" t="str">
+      <c r="N49" s="266" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="277" t="str">
+      <c r="O49" s="268" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="277" t="str">
+      <c r="P49" s="268" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="279" t="str">
+      <c r="Q49" s="270" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="279" t="str">
+      <c r="R49" s="270" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="271"/>
-      <c r="C50" s="271"/>
+      <c r="B50" s="262"/>
+      <c r="C50" s="262"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -16231,13 +16231,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="295"/>
-      <c r="M50" s="276"/>
-      <c r="N50" s="276"/>
-      <c r="O50" s="278"/>
-      <c r="P50" s="278"/>
-      <c r="Q50" s="280"/>
-      <c r="R50" s="280"/>
+      <c r="L50" s="292"/>
+      <c r="M50" s="267"/>
+      <c r="N50" s="267"/>
+      <c r="O50" s="269"/>
+      <c r="P50" s="269"/>
+      <c r="Q50" s="271"/>
+      <c r="R50" s="271"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -17339,21 +17339,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="286" t="s">
+      <c r="B67" s="293" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="287"/>
-      <c r="D67" s="287"/>
-      <c r="E67" s="287"/>
+      <c r="C67" s="294"/>
+      <c r="D67" s="294"/>
+      <c r="E67" s="294"/>
       <c r="F67" s="296"/>
-      <c r="G67" s="272" t="s">
+      <c r="G67" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="273"/>
-      <c r="I67" s="273"/>
-      <c r="J67" s="273"/>
-      <c r="K67" s="273"/>
-      <c r="L67" s="274"/>
+      <c r="H67" s="264"/>
+      <c r="I67" s="264"/>
+      <c r="J67" s="264"/>
+      <c r="K67" s="264"/>
+      <c r="L67" s="265"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -17674,10 +17674,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="271" t="s">
+      <c r="B78" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="271" t="s">
+      <c r="C78" s="262" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -17990,6 +17990,12 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -18004,12 +18010,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -25789,11 +25789,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="262" t="s">
+      <c r="B41" s="272" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="263"/>
-      <c r="D41" s="264"/>
+      <c r="C41" s="273"/>
+      <c r="D41" s="274"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -26064,59 +26064,59 @@
       </c>
     </row>
     <row r="48" spans="2:19" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="265" t="s">
+      <c r="B48" s="275" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="266"/>
-      <c r="D48" s="266"/>
-      <c r="E48" s="266"/>
-      <c r="F48" s="266"/>
-      <c r="G48" s="266"/>
-      <c r="H48" s="266"/>
-      <c r="I48" s="266"/>
-      <c r="J48" s="266"/>
-      <c r="K48" s="272" t="s">
+      <c r="C48" s="276"/>
+      <c r="D48" s="276"/>
+      <c r="E48" s="276"/>
+      <c r="F48" s="276"/>
+      <c r="G48" s="276"/>
+      <c r="H48" s="276"/>
+      <c r="I48" s="276"/>
+      <c r="J48" s="276"/>
+      <c r="K48" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="273"/>
-      <c r="M48" s="273"/>
-      <c r="N48" s="273"/>
-      <c r="O48" s="273"/>
-      <c r="P48" s="274"/>
+      <c r="L48" s="264"/>
+      <c r="M48" s="264"/>
+      <c r="N48" s="264"/>
+      <c r="O48" s="264"/>
+      <c r="P48" s="265"/>
       <c r="Q48"/>
       <c r="R48"/>
     </row>
     <row r="49" spans="2:18" s="139" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="270" t="s">
+      <c r="B49" s="280" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="270" t="s">
+      <c r="C49" s="280" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="267" t="s">
+      <c r="D49" s="277" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="268"/>
-      <c r="F49" s="269"/>
+      <c r="E49" s="278"/>
+      <c r="F49" s="279"/>
       <c r="G49" s="140" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="140"/>
       <c r="I49" s="140"/>
-      <c r="J49" s="267" t="s">
+      <c r="J49" s="277" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="275" t="str">
+      <c r="K49" s="266" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="275" t="str">
+      <c r="L49" s="266" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="277" t="str">
+      <c r="M49" s="268" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
@@ -26131,7 +26131,7 @@
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="279" t="str">
+      <c r="P49" s="270" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -26140,8 +26140,8 @@
       <c r="R49"/>
     </row>
     <row r="50" spans="2:18" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="270"/>
-      <c r="C50" s="270"/>
+      <c r="B50" s="280"/>
+      <c r="C50" s="280"/>
       <c r="D50" s="141" t="s">
         <v>149</v>
       </c>
@@ -26160,13 +26160,13 @@
       <c r="I50" s="142" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="267"/>
-      <c r="K50" s="276"/>
-      <c r="L50" s="276"/>
-      <c r="M50" s="278"/>
+      <c r="J50" s="277"/>
+      <c r="K50" s="267"/>
+      <c r="L50" s="267"/>
+      <c r="M50" s="269"/>
       <c r="N50" s="188"/>
       <c r="O50" s="183"/>
-      <c r="P50" s="280"/>
+      <c r="P50" s="271"/>
       <c r="Q50"/>
       <c r="R50"/>
     </row>
@@ -27507,10 +27507,10 @@
       <c r="I77"/>
     </row>
     <row r="78" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="271" t="s">
+      <c r="B78" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="271" t="s">
+      <c r="C78" s="262" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -27709,6 +27709,13 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="J49:J50"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
     <mergeCell ref="K48:P48"/>
@@ -27718,13 +27725,6 @@
     <mergeCell ref="P49:P50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="J49:J50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="26" priority="8">
@@ -28764,25 +28764,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="265" t="s">
+      <c r="B48" s="275" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="266"/>
-      <c r="D48" s="266"/>
-      <c r="E48" s="266"/>
-      <c r="F48" s="266"/>
-      <c r="G48" s="266"/>
-      <c r="H48" s="266"/>
-      <c r="I48" s="266"/>
-      <c r="J48" s="266"/>
-      <c r="K48" s="272" t="s">
+      <c r="C48" s="276"/>
+      <c r="D48" s="276"/>
+      <c r="E48" s="276"/>
+      <c r="F48" s="276"/>
+      <c r="G48" s="276"/>
+      <c r="H48" s="276"/>
+      <c r="I48" s="276"/>
+      <c r="J48" s="276"/>
+      <c r="K48" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="273"/>
-      <c r="M48" s="273"/>
-      <c r="N48" s="273"/>
-      <c r="O48" s="273"/>
-      <c r="P48" s="274"/>
+      <c r="L48" s="264"/>
+      <c r="M48" s="264"/>
+      <c r="N48" s="264"/>
+      <c r="O48" s="264"/>
+      <c r="P48" s="265"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="261" t="s">
@@ -28804,32 +28804,32 @@
       <c r="J49" s="256" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="275" t="str">
+      <c r="K49" s="266" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="275" t="str">
+      <c r="L49" s="266" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="277" t="str">
+      <c r="M49" s="268" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="277" t="str">
+      <c r="N49" s="268" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="279" t="str">
+      <c r="O49" s="270" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="279" t="str">
+      <c r="P49" s="270" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -28857,12 +28857,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="256"/>
-      <c r="K50" s="276"/>
-      <c r="L50" s="276"/>
-      <c r="M50" s="278"/>
-      <c r="N50" s="278"/>
-      <c r="O50" s="280"/>
-      <c r="P50" s="280"/>
+      <c r="K50" s="267"/>
+      <c r="L50" s="267"/>
+      <c r="M50" s="269"/>
+      <c r="N50" s="269"/>
+      <c r="O50" s="271"/>
+      <c r="P50" s="271"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="167" t="s">
@@ -30099,10 +30099,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="271" t="s">
+      <c r="B78" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="271" t="s">
+      <c r="C78" s="262" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -30296,6 +30296,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -30303,17 +30314,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -31071,11 +31071,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="262" t="s">
+      <c r="B41" s="272" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="263"/>
-      <c r="D41" s="264"/>
+      <c r="C41" s="273"/>
+      <c r="D41" s="274"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -31350,25 +31350,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="265" t="s">
+      <c r="B48" s="275" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="266"/>
-      <c r="D48" s="266"/>
-      <c r="E48" s="266"/>
-      <c r="F48" s="266"/>
-      <c r="G48" s="266"/>
-      <c r="H48" s="266"/>
-      <c r="I48" s="266"/>
-      <c r="J48" s="266"/>
-      <c r="K48" s="272" t="s">
+      <c r="C48" s="276"/>
+      <c r="D48" s="276"/>
+      <c r="E48" s="276"/>
+      <c r="F48" s="276"/>
+      <c r="G48" s="276"/>
+      <c r="H48" s="276"/>
+      <c r="I48" s="276"/>
+      <c r="J48" s="276"/>
+      <c r="K48" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="273"/>
-      <c r="M48" s="273"/>
-      <c r="N48" s="273"/>
-      <c r="O48" s="273"/>
-      <c r="P48" s="274"/>
+      <c r="L48" s="264"/>
+      <c r="M48" s="264"/>
+      <c r="N48" s="264"/>
+      <c r="O48" s="264"/>
+      <c r="P48" s="265"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="261" t="s">
@@ -31390,32 +31390,32 @@
       <c r="J49" s="256" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="275" t="str">
+      <c r="K49" s="266" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="275" t="str">
+      <c r="L49" s="266" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="277" t="str">
+      <c r="M49" s="268" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="277" t="str">
+      <c r="N49" s="268" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="279" t="str">
+      <c r="O49" s="270" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="279" t="str">
+      <c r="P49" s="270" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -31443,12 +31443,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="256"/>
-      <c r="K50" s="276"/>
-      <c r="L50" s="276"/>
-      <c r="M50" s="278"/>
-      <c r="N50" s="278"/>
-      <c r="O50" s="280"/>
-      <c r="P50" s="280"/>
+      <c r="K50" s="267"/>
+      <c r="L50" s="267"/>
+      <c r="M50" s="269"/>
+      <c r="N50" s="269"/>
+      <c r="O50" s="271"/>
+      <c r="P50" s="271"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -32685,10 +32685,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="271" t="s">
+      <c r="B78" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="271" t="s">
+      <c r="C78" s="262" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -32869,6 +32869,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -32876,17 +32887,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -33665,11 +33665,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" s="191" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="262" t="s">
+      <c r="B41" s="272" t="s">
         <v>189</v>
       </c>
-      <c r="C41" s="263"/>
-      <c r="D41" s="264"/>
+      <c r="C41" s="273"/>
+      <c r="D41" s="274"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -33944,25 +33944,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="265" t="s">
+      <c r="B48" s="275" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="266"/>
-      <c r="D48" s="266"/>
-      <c r="E48" s="266"/>
-      <c r="F48" s="266"/>
-      <c r="G48" s="266"/>
-      <c r="H48" s="266"/>
-      <c r="I48" s="266"/>
-      <c r="J48" s="266"/>
-      <c r="K48" s="272" t="s">
+      <c r="C48" s="276"/>
+      <c r="D48" s="276"/>
+      <c r="E48" s="276"/>
+      <c r="F48" s="276"/>
+      <c r="G48" s="276"/>
+      <c r="H48" s="276"/>
+      <c r="I48" s="276"/>
+      <c r="J48" s="276"/>
+      <c r="K48" s="263" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="273"/>
-      <c r="M48" s="273"/>
-      <c r="N48" s="273"/>
-      <c r="O48" s="273"/>
-      <c r="P48" s="274"/>
+      <c r="L48" s="264"/>
+      <c r="M48" s="264"/>
+      <c r="N48" s="264"/>
+      <c r="O48" s="264"/>
+      <c r="P48" s="265"/>
     </row>
     <row r="49" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="261" t="s">
@@ -33984,22 +33984,22 @@
       <c r="J49" s="256" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="275" t="str">
+      <c r="K49" s="266" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="275" t="str">
+      <c r="L49" s="266" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="277" t="str">
+      <c r="M49" s="268" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="277" t="str">
+      <c r="N49" s="268" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
@@ -34037,10 +34037,10 @@
         <v>130</v>
       </c>
       <c r="J50" s="256"/>
-      <c r="K50" s="276"/>
-      <c r="L50" s="276"/>
-      <c r="M50" s="278"/>
-      <c r="N50" s="278"/>
+      <c r="K50" s="267"/>
+      <c r="L50" s="267"/>
+      <c r="M50" s="269"/>
+      <c r="N50" s="269"/>
       <c r="O50" s="285"/>
       <c r="P50" s="285"/>
     </row>
@@ -35279,10 +35279,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="271" t="s">
+      <c r="B78" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="271" t="s">
+      <c r="C78" s="262" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -35476,6 +35476,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
@@ -35489,11 +35494,6 @@
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -909,7 +909,7 @@
     <t>RONALD</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL —  28 SEPTEMBER 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL —  29 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>
@@ -2565,6 +2565,33 @@
     <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2595,33 +2622,6 @@
     <xf numFmtId="0" fontId="48" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2635,6 +2635,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2656,15 +2665,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4308,11 +4308,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="272" t="s">
+      <c r="B40" s="262" t="s">
         <v>219</v>
       </c>
-      <c r="C40" s="273"/>
-      <c r="D40" s="274"/>
+      <c r="C40" s="263"/>
+      <c r="D40" s="264"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -4632,33 +4632,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="275" t="s">
+      <c r="B48" s="265" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="276"/>
-      <c r="D48" s="276"/>
-      <c r="E48" s="276"/>
-      <c r="F48" s="276"/>
-      <c r="G48" s="276"/>
-      <c r="H48" s="276"/>
-      <c r="I48" s="276"/>
-      <c r="J48" s="276"/>
-      <c r="K48" s="276"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="263" t="s">
+      <c r="C48" s="266"/>
+      <c r="D48" s="266"/>
+      <c r="E48" s="266"/>
+      <c r="F48" s="266"/>
+      <c r="G48" s="266"/>
+      <c r="H48" s="266"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="266"/>
+      <c r="K48" s="266"/>
+      <c r="L48" s="289"/>
+      <c r="M48" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="264"/>
-      <c r="O48" s="264"/>
-      <c r="P48" s="264"/>
-      <c r="Q48" s="264"/>
-      <c r="R48" s="265"/>
+      <c r="N48" s="273"/>
+      <c r="O48" s="273"/>
+      <c r="P48" s="273"/>
+      <c r="Q48" s="273"/>
+      <c r="R48" s="274"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="290" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="290" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="256" t="s">
@@ -4667,49 +4667,49 @@
       <c r="E49" s="257"/>
       <c r="F49" s="257"/>
       <c r="G49" s="258"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="291" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="292"/>
+      <c r="J49" s="292"/>
+      <c r="K49" s="293"/>
+      <c r="L49" s="294" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="266" t="str">
+      <c r="M49" s="275" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="266" t="str">
+      <c r="N49" s="275" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="268" t="str">
+      <c r="O49" s="277" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="268" t="str">
+      <c r="P49" s="277" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="270" t="str">
+      <c r="Q49" s="279" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="270" t="str">
+      <c r="R49" s="279" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="262"/>
-      <c r="C50" s="262"/>
+      <c r="B50" s="271"/>
+      <c r="C50" s="271"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -4734,13 +4734,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="267"/>
-      <c r="N50" s="267"/>
-      <c r="O50" s="269"/>
-      <c r="P50" s="269"/>
-      <c r="Q50" s="271"/>
-      <c r="R50" s="271"/>
+      <c r="L50" s="295"/>
+      <c r="M50" s="276"/>
+      <c r="N50" s="276"/>
+      <c r="O50" s="278"/>
+      <c r="P50" s="278"/>
+      <c r="Q50" s="280"/>
+      <c r="R50" s="280"/>
       <c r="T50" s="172" t="s">
         <v>216</v>
       </c>
@@ -5856,21 +5856,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="293" t="s">
+      <c r="B67" s="286" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="294"/>
-      <c r="D67" s="294"/>
-      <c r="E67" s="294"/>
-      <c r="F67" s="295"/>
-      <c r="G67" s="263" t="s">
+      <c r="C67" s="287"/>
+      <c r="D67" s="287"/>
+      <c r="E67" s="287"/>
+      <c r="F67" s="288"/>
+      <c r="G67" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="264"/>
-      <c r="I67" s="264"/>
-      <c r="J67" s="264"/>
-      <c r="K67" s="264"/>
-      <c r="L67" s="265"/>
+      <c r="H67" s="273"/>
+      <c r="I67" s="273"/>
+      <c r="J67" s="273"/>
+      <c r="K67" s="273"/>
+      <c r="L67" s="274"/>
     </row>
     <row r="68" spans="2:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -6189,10 +6189,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="262" t="s">
+      <c r="B78" s="271" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="262" t="s">
+      <c r="C78" s="271" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -6504,12 +6504,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -6524,6 +6518,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="C3" s="75">
         <f ca="1">IF($J$5&lt;&gt;"",$J$5,MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),9,1)),EOMONTH(DATE(YEAR(TODAY()),9,1),0),11)-MAX(0,$J$3-$J$4)))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" s="76" t="s">
         <v>104</v>
@@ -6729,19 +6729,19 @@
         <v>112</v>
       </c>
       <c r="C10" s="236">
-        <v>133182163.255797</v>
+        <v>144279163.255797</v>
       </c>
       <c r="D10" s="236">
         <v>39865291.477794997</v>
       </c>
       <c r="E10" s="236">
-        <v>191182198.64701799</v>
+        <v>201225937.40701801</v>
       </c>
       <c r="F10" s="236">
-        <v>155970460.17992401</v>
+        <v>159875865.75992399</v>
       </c>
       <c r="G10" s="236">
-        <v>520200113.560534</v>
+        <v>545246257.90053403</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="111"/>
@@ -6779,19 +6779,19 @@
         <v>70</v>
       </c>
       <c r="C12" s="236">
-        <v>158839730.55793801</v>
+        <v>161219730.55793801</v>
       </c>
       <c r="D12" s="236">
-        <v>68299955.821513996</v>
+        <v>70791542.079612002</v>
       </c>
       <c r="E12" s="236">
-        <v>153961805.60950899</v>
+        <v>171970814.99950901</v>
       </c>
       <c r="F12" s="236">
-        <v>68657391.549999997</v>
+        <v>72387121.459999993</v>
       </c>
       <c r="G12" s="236">
-        <v>449758883.53896099</v>
+        <v>476369209.09705901</v>
       </c>
       <c r="H12" s="111"/>
       <c r="I12" s="111"/>
@@ -6807,16 +6807,16 @@
         <v>31456577.699947</v>
       </c>
       <c r="D13" s="236">
-        <v>22521953.429963</v>
+        <v>22878710.189963002</v>
       </c>
       <c r="E13" s="236">
-        <v>199683245.129592</v>
+        <v>209687749.75959</v>
       </c>
       <c r="F13" s="236">
-        <v>85854155.530000001</v>
+        <v>91255957.469999999</v>
       </c>
       <c r="G13" s="236">
-        <v>339515931.78950202</v>
+        <v>355278995.11949998</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="111"/>
@@ -6829,19 +6829,19 @@
         <v>115</v>
       </c>
       <c r="C14" s="236">
-        <v>482508837.979559</v>
+        <v>499277061.85955799</v>
       </c>
       <c r="D14" s="236">
-        <v>43096712.549465001</v>
+        <v>45658406.209425002</v>
       </c>
       <c r="E14" s="236">
-        <v>151436270.519853</v>
+        <v>153352892.139853</v>
       </c>
       <c r="F14" s="236">
-        <v>383780696.16973501</v>
+        <v>417669886.18970001</v>
       </c>
       <c r="G14" s="236">
-        <v>1060822517.218612</v>
+        <v>1115958246.398536</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="111"/>
@@ -6854,19 +6854,19 @@
         <v>118</v>
       </c>
       <c r="C15" s="236">
-        <v>1583048264.799907</v>
+        <v>1668540388.249907</v>
       </c>
       <c r="D15" s="236">
-        <v>11461206.304924</v>
+        <v>11781314.416924</v>
       </c>
       <c r="E15" s="236">
-        <v>94358935.799939007</v>
+        <v>94399476.329938993</v>
       </c>
       <c r="F15" s="236">
-        <v>16805405.75</v>
+        <v>17616216.550000001</v>
       </c>
       <c r="G15" s="236">
-        <v>1705673812.6547699</v>
+        <v>1792337395.5467701</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="111"/>
@@ -6879,19 +6879,19 @@
         <v>120</v>
       </c>
       <c r="C16" s="236">
-        <v>491342417.01869798</v>
+        <v>510002008.569673</v>
       </c>
       <c r="D16" s="236">
-        <v>56669125.779923998</v>
+        <v>57215125.779923998</v>
       </c>
       <c r="E16" s="236">
-        <v>312947839.26937002</v>
+        <v>323013334.79936802</v>
       </c>
       <c r="F16" s="236">
-        <v>990682602.56996906</v>
+        <v>1054625484.149969</v>
       </c>
       <c r="G16" s="236">
-        <v>1851641984.6379609</v>
+        <v>1944855953.298934</v>
       </c>
       <c r="H16" s="111"/>
       <c r="I16" s="111"/>
@@ -6904,19 +6904,19 @@
         <v>122</v>
       </c>
       <c r="C17" s="236">
-        <v>103155630.48592401</v>
+        <v>108130900.985884</v>
       </c>
       <c r="D17" s="236">
         <v>13122554.039898001</v>
       </c>
       <c r="E17" s="236">
-        <v>106463647.96879201</v>
+        <v>111572926.73874199</v>
       </c>
       <c r="F17" s="236">
         <v>49898919.898000002</v>
       </c>
       <c r="G17" s="236">
-        <v>272640752.39261401</v>
+        <v>282725301.66252398</v>
       </c>
       <c r="H17" s="111"/>
       <c r="I17" s="111"/>
@@ -6933,16 +6933,16 @@
         <v>13656047.589996999</v>
       </c>
       <c r="D18" s="236">
-        <v>135022363.55165499</v>
+        <v>147184525.55145499</v>
       </c>
       <c r="E18" s="236">
         <v>59041106.100000001</v>
       </c>
       <c r="F18" s="236">
-        <v>104562164.42</v>
+        <v>107718921.26000001</v>
       </c>
       <c r="G18" s="236">
-        <v>312281681.66165203</v>
+        <v>327600600.50145203</v>
       </c>
       <c r="H18" s="111"/>
       <c r="I18" s="111"/>
@@ -7012,26 +7012,26 @@
         <v>124</v>
       </c>
       <c r="C21" s="236">
-        <v>263996098.743774</v>
+        <v>279474951.69377297</v>
       </c>
       <c r="D21" s="236">
-        <v>47932129.623447001</v>
+        <v>50971930.973436996</v>
       </c>
       <c r="E21" s="236">
-        <v>143083924.36977699</v>
+        <v>156172437.89974299</v>
       </c>
       <c r="F21" s="236">
-        <v>414273536.65985</v>
+        <v>418959663.01985002</v>
       </c>
       <c r="G21" s="236">
-        <v>869285689.39684796</v>
+        <v>905578983.58680296</v>
       </c>
       <c r="H21" s="111"/>
       <c r="I21" s="111"/>
       <c r="J21" s="111"/>
       <c r="M21" s="14">
         <f>SUM(C33,C34)+M20</f>
-        <v>1014347446.480343</v>
+        <v>1029524757.540693</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>224</v>
@@ -7042,19 +7042,19 @@
         <v>225</v>
       </c>
       <c r="C22" s="236">
-        <v>190036588.29052001</v>
+        <v>194178770.260515</v>
       </c>
       <c r="D22" s="236">
         <v>55882903.289934002</v>
       </c>
       <c r="E22" s="236">
-        <v>151739974.348151</v>
+        <v>158811370.80815101</v>
       </c>
       <c r="F22" s="236">
-        <v>65782612.399999999</v>
+        <v>66593423.25</v>
       </c>
       <c r="G22" s="236">
-        <v>463442078.328605</v>
+        <v>475466467.60860002</v>
       </c>
       <c r="H22" s="111"/>
       <c r="I22" s="111"/>
@@ -7065,19 +7065,19 @@
         <v>125</v>
       </c>
       <c r="C23" s="236">
-        <v>255492042.620024</v>
+        <v>272154150.611709</v>
       </c>
       <c r="D23" s="236">
-        <v>67695304.759942994</v>
+        <v>73116453.419943005</v>
       </c>
       <c r="E23" s="236">
-        <v>183532696.38125801</v>
+        <v>191422516.331242</v>
       </c>
       <c r="F23" s="236">
-        <v>315237664.88943499</v>
+        <v>338386814.24937999</v>
       </c>
       <c r="G23" s="236">
-        <v>821957708.65066004</v>
+        <v>875079934.61227405</v>
       </c>
       <c r="H23" s="111"/>
       <c r="I23" s="111"/>
@@ -7088,19 +7088,19 @@
         <v>126</v>
       </c>
       <c r="C24" s="236">
-        <v>440052239.37646002</v>
+        <v>451192557.081352</v>
       </c>
       <c r="D24" s="236">
-        <v>59219998.644919001</v>
+        <v>62998196.844919004</v>
       </c>
       <c r="E24" s="236">
-        <v>200790750.04987699</v>
+        <v>210758723.08987701</v>
       </c>
       <c r="F24" s="236">
-        <v>579669561.29943395</v>
+        <v>621824291.65936995</v>
       </c>
       <c r="G24" s="236">
-        <v>1279732549.3706901</v>
+        <v>1346773768.675518</v>
       </c>
       <c r="H24" s="111"/>
       <c r="I24" s="111"/>
@@ -7111,19 +7111,19 @@
         <v>220</v>
       </c>
       <c r="C25" s="236">
-        <v>334965416.39326602</v>
+        <v>348281390.32724202</v>
       </c>
       <c r="D25" s="236">
-        <v>81584972.886524007</v>
+        <v>82526864.846503004</v>
       </c>
       <c r="E25" s="236">
-        <v>97847527.472525001</v>
+        <v>99668158.112520993</v>
       </c>
       <c r="F25" s="236">
         <v>50324325.43</v>
       </c>
       <c r="G25" s="236">
-        <v>564722242.18231499</v>
+        <v>580800738.71626604</v>
       </c>
       <c r="H25" s="111"/>
       <c r="I25" s="111"/>
@@ -7134,19 +7134,19 @@
         <v>127</v>
       </c>
       <c r="C26" s="236">
-        <v>480229048.13510603</v>
+        <v>506101282.89459699</v>
       </c>
       <c r="D26" s="236">
-        <v>286587088.43090999</v>
+        <v>290879574.89086801</v>
       </c>
       <c r="E26" s="236">
-        <v>283835544.43512303</v>
+        <v>286978787.695113</v>
       </c>
       <c r="F26" s="236">
-        <v>18820757.1204</v>
+        <v>19764540.930399999</v>
       </c>
       <c r="G26" s="236">
-        <v>1069472438.121539</v>
+        <v>1103724186.4109781</v>
       </c>
       <c r="H26" s="111"/>
       <c r="I26" s="111"/>
@@ -7189,7 +7189,7 @@
         <v>131</v>
       </c>
       <c r="C31" s="171">
-        <v>259365932.35194299</v>
+        <v>276916748.691921</v>
       </c>
       <c r="G31" s="111"/>
       <c r="H31" s="111"/>
@@ -7200,7 +7200,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="236">
-        <v>457145084.04292297</v>
+        <v>458181336.78289902</v>
       </c>
       <c r="G32" s="111"/>
       <c r="H32" s="111"/>
@@ -7211,7 +7211,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="236">
-        <v>506982262.40976697</v>
+        <v>509412546.19026101</v>
       </c>
       <c r="G33" s="111"/>
       <c r="H33" s="111"/>
@@ -7222,7 +7222,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="236">
-        <v>507365184.07057601</v>
+        <v>520112211.35043198</v>
       </c>
       <c r="G34" s="111"/>
       <c r="H34" s="111"/>
@@ -7267,17 +7267,17 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="272" t="s">
+      <c r="B40" s="262" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="273"/>
-      <c r="D40" s="274"/>
+      <c r="C40" s="263"/>
+      <c r="D40" s="264"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
       <c r="F40" s="174">
         <f ca="1">IF(MONTH(TODAY())=9,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;9,1,0))</f>
-        <v>0.93333333333333335</v>
+        <v>0.96666666666666667</v>
       </c>
       <c r="G40" s="192" t="s">
         <v>187</v>
@@ -7364,35 +7364,35 @@
       </c>
       <c r="E42" s="46">
         <f>H65</f>
-        <v>3639221204.1870084</v>
+        <v>3779712959.4279799</v>
       </c>
       <c r="F42" s="176">
         <f>IFERROR(E42/D42,0)</f>
-        <v>0.80660323362078046</v>
+        <v>0.83774206737566415</v>
       </c>
       <c r="G42" s="184">
         <f>D42*$H$40-E42</f>
-        <v>646975527.82741785</v>
+        <v>506483772.58644629</v>
       </c>
       <c r="H42" s="184">
         <f ca="1">IFERROR(G42/$C$3,0)</f>
-        <v>215658509.27580595</v>
+        <v>253241886.29322314</v>
       </c>
       <c r="I42" s="204">
         <f>D42*$J$40-E42</f>
-        <v>872564829.51238775</v>
+        <v>732073074.27141619</v>
       </c>
       <c r="J42" s="204">
         <f ca="1">IFERROR(I42/$C$3,0)</f>
-        <v>290854943.17079592</v>
+        <v>366036537.13570809</v>
       </c>
       <c r="K42" s="185">
         <f>D42*$L$40-E42</f>
-        <v>872564829.51238775</v>
+        <v>732073074.27141619</v>
       </c>
       <c r="L42" s="185">
         <f ca="1">IFERROR(K42/$C$3,0)</f>
-        <v>290854943.17079592</v>
+        <v>366036537.13570809</v>
       </c>
       <c r="S42" s="173">
         <v>0.8</v>
@@ -7411,35 +7411,35 @@
       </c>
       <c r="E43" s="46">
         <f>I65</f>
-        <v>1010129714.9858909</v>
+        <v>1045721440.2936759</v>
       </c>
       <c r="F43" s="176">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.72081826730416954</v>
+        <v>0.74621615966008525</v>
       </c>
       <c r="G43" s="184">
         <f>D43*$H$40-E43</f>
-        <v>321167330.00375319</v>
+        <v>285575604.69596815</v>
       </c>
       <c r="H43" s="184">
         <f ca="1">IFERROR(G43/$C$3,0)</f>
-        <v>107055776.66791773</v>
+        <v>142787802.34798408</v>
       </c>
       <c r="I43" s="204">
         <f>D43*$J$40-E43</f>
-        <v>391235595.52952409</v>
+        <v>355643870.22173905</v>
       </c>
       <c r="J43" s="204">
         <f ca="1">IFERROR(I43/$C$3,0)</f>
-        <v>130411865.17650802</v>
+        <v>177821935.11086953</v>
       </c>
       <c r="K43" s="185">
         <f>D43*$L$40-E43</f>
-        <v>391235595.52952409</v>
+        <v>355643870.22173905</v>
       </c>
       <c r="L43" s="185">
         <f ca="1">IFERROR(K43/$C$3,0)</f>
-        <v>130411865.17650802</v>
+        <v>177821935.11086953</v>
       </c>
       <c r="S43" s="173">
         <v>0.85</v>
@@ -7458,35 +7458,35 @@
       </c>
       <c r="E44" s="46">
         <f>J65</f>
-        <v>2506546531.6597452</v>
+        <v>2604676757.2396264</v>
       </c>
       <c r="F44" s="176">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.85117306714449736</v>
+        <v>0.88449612898731944</v>
       </c>
       <c r="G44" s="184">
         <f>IF(D44=0,0,D44*$H$40-E44)</f>
-        <v>291026954.85250568</v>
+        <v>192896729.27262449</v>
       </c>
       <c r="H44" s="184">
         <f ca="1">IFERROR(G44/$C$3,0)</f>
-        <v>97008984.950835228</v>
+        <v>96448364.636312246</v>
       </c>
       <c r="I44" s="204">
         <f>IF(D44=0,0,D44*$J$40-E44)</f>
-        <v>438267664.66894007</v>
+        <v>340137439.08905888</v>
       </c>
       <c r="J44" s="204">
         <f ca="1">IFERROR(I44/$C$3,0)</f>
-        <v>146089221.55631337</v>
+        <v>170068719.54452944</v>
       </c>
       <c r="K44" s="185">
         <f>IF(D44=0,0,D44*$L$40-E44)</f>
-        <v>438267664.66894007</v>
+        <v>340137439.08905888</v>
       </c>
       <c r="L44" s="185">
         <f ca="1">IFERROR(K44/$C$3,0)</f>
-        <v>146089221.55631337</v>
+        <v>170068719.54452944</v>
       </c>
       <c r="S44" s="173">
         <v>0.9</v>
@@ -7505,35 +7505,35 @@
       </c>
       <c r="E45" s="46">
         <f>E74</f>
-        <v>1730858462.8752089</v>
+        <v>1764622843.0155129</v>
       </c>
       <c r="F45" s="176">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0.9945030287913792</v>
+        <v>1.0139031005101358</v>
       </c>
       <c r="G45" s="184">
         <f>D45*$H$40-E45</f>
-        <v>-77454207.556060076</v>
+        <v>-111218587.69636416</v>
       </c>
       <c r="H45" s="184">
         <f ca="1">IFERROR(G45/$C$3,0)</f>
-        <v>-25818069.185353357</v>
+        <v>-55609293.848182082</v>
       </c>
       <c r="I45" s="204">
         <f>D45*$J$40-E45</f>
-        <v>9567069.0396847725</v>
+        <v>-24197311.100619316</v>
       </c>
       <c r="J45" s="204">
         <f ca="1">IFERROR(I45/$C$3,0)</f>
-        <v>3189023.0132282577</v>
+        <v>-12098655.550309658</v>
       </c>
       <c r="K45" s="185">
         <f>D45*$L$40-E45</f>
-        <v>9567069.0396847725</v>
+        <v>-24197311.100619316</v>
       </c>
       <c r="L45" s="185">
         <f ca="1">IFERROR(K45/$C$3,0)</f>
-        <v>3189023.0132282577</v>
+        <v>-12098655.550309658</v>
       </c>
       <c r="S45" s="173">
         <v>0.95</v>
@@ -7550,35 +7550,35 @@
       </c>
       <c r="E46" s="47">
         <f>SUM(E42:E45)</f>
-        <v>8886755913.7078533</v>
+        <v>9194733999.9767952</v>
       </c>
       <c r="F46" s="177">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.83850047171796716</v>
+        <v>0.86755941888866295</v>
       </c>
       <c r="G46" s="181">
         <f>SUM(G42:G45)</f>
-        <v>1181715605.1276166</v>
+        <v>873737518.85867476</v>
       </c>
       <c r="H46" s="181">
         <f ca="1">IFERROR(G46/$C$3,0)</f>
-        <v>393905201.70920557</v>
+        <v>436868759.42933738</v>
       </c>
       <c r="I46" s="186">
         <f>SUM(I42:I45)</f>
-        <v>1711635158.7505367</v>
+        <v>1403657072.4815948</v>
       </c>
       <c r="J46" s="186">
         <f ca="1">IFERROR(I46/$C$3,0)</f>
-        <v>570545052.91684556</v>
+        <v>701828536.2407974</v>
       </c>
       <c r="K46" s="186">
         <f>SUM(K42:K45)</f>
-        <v>1711635158.7505367</v>
+        <v>1403657072.4815948</v>
       </c>
       <c r="L46" s="186">
         <f ca="1">IFERROR(K46/$C$3,0)</f>
-        <v>570545052.91684556</v>
+        <v>701828536.2407974</v>
       </c>
       <c r="S46" s="173">
         <v>1</v>
@@ -7591,33 +7591,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="275" t="s">
+      <c r="B48" s="265" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="276"/>
-      <c r="D48" s="276"/>
-      <c r="E48" s="276"/>
-      <c r="F48" s="276"/>
-      <c r="G48" s="276"/>
-      <c r="H48" s="276"/>
-      <c r="I48" s="276"/>
-      <c r="J48" s="276"/>
-      <c r="K48" s="276"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="263" t="s">
+      <c r="C48" s="266"/>
+      <c r="D48" s="266"/>
+      <c r="E48" s="266"/>
+      <c r="F48" s="266"/>
+      <c r="G48" s="266"/>
+      <c r="H48" s="266"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="266"/>
+      <c r="K48" s="266"/>
+      <c r="L48" s="289"/>
+      <c r="M48" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="264"/>
-      <c r="O48" s="264"/>
-      <c r="P48" s="264"/>
-      <c r="Q48" s="264"/>
-      <c r="R48" s="265"/>
+      <c r="N48" s="273"/>
+      <c r="O48" s="273"/>
+      <c r="P48" s="273"/>
+      <c r="Q48" s="273"/>
+      <c r="R48" s="274"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="290" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="290" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="256" t="s">
@@ -7626,49 +7626,49 @@
       <c r="E49" s="257"/>
       <c r="F49" s="257"/>
       <c r="G49" s="258"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="291" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="292"/>
+      <c r="J49" s="292"/>
+      <c r="K49" s="293"/>
+      <c r="L49" s="294" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="266" t="str">
+      <c r="M49" s="275" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="266" t="str">
+      <c r="N49" s="275" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="268" t="str">
+      <c r="O49" s="277" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="268" t="str">
+      <c r="P49" s="277" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="Q49" s="270" t="str">
+      <c r="Q49" s="279" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="270" t="str">
+      <c r="R49" s="279" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="262"/>
-      <c r="C50" s="262"/>
+      <c r="B50" s="271"/>
+      <c r="C50" s="271"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -7693,13 +7693,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="267"/>
-      <c r="N50" s="267"/>
-      <c r="O50" s="269"/>
-      <c r="P50" s="269"/>
-      <c r="Q50" s="271"/>
-      <c r="R50" s="271"/>
+      <c r="L50" s="295"/>
+      <c r="M50" s="276"/>
+      <c r="N50" s="276"/>
+      <c r="O50" s="278"/>
+      <c r="P50" s="278"/>
+      <c r="Q50" s="280"/>
+      <c r="R50" s="280"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -7732,47 +7732,47 @@
       </c>
       <c r="H51" s="114">
         <f t="shared" ref="H51:H64" si="1">SUMIF($B$10:$B$26,$T51,C$10:C$26)+SUMIF($B$10:$B$26,$U51,C$10:C$26)</f>
-        <v>263996098.743774</v>
+        <v>279474951.69377297</v>
       </c>
       <c r="I51" s="114">
         <f t="shared" ref="I51:I64" si="2">SUMIF($B$10:$B$26,$T51,D$10:D$26)+SUMIF($B$10:$B$26,$U51,D$10:D$26)</f>
-        <v>47932129.623447001</v>
+        <v>50971930.973436996</v>
       </c>
       <c r="J51" s="114">
         <f t="shared" ref="J51:J64" si="3">SUMIF($B$10:$B$26,$T51,E$10:E$26)+SUMIF($B$10:$B$26,$U51,E$10:E$26)</f>
-        <v>143083924.36977699</v>
+        <v>156172437.89974299</v>
       </c>
       <c r="K51" s="114">
         <f t="shared" ref="K51:K64" si="4">SUM(H51:J51)</f>
-        <v>455012152.73699796</v>
+        <v>486619320.56695294</v>
       </c>
       <c r="L51" s="187">
         <f t="shared" ref="L51:L65" si="5">IFERROR(K51/G51,0)</f>
-        <v>0.88460514154766678</v>
+        <v>0.94605374902760664</v>
       </c>
       <c r="M51" s="184">
         <f t="shared" ref="M51:M64" si="6">G51*$H$40-K51</f>
-        <v>33636991.155475855</v>
+        <v>2029823.3255208731</v>
       </c>
       <c r="N51" s="184">
         <f t="shared" ref="N51:N65" ca="1" si="7">IFERROR(M51/$C$3,0)</f>
-        <v>11212330.385158619</v>
+        <v>1014911.6627604365</v>
       </c>
       <c r="O51" s="180">
         <f t="shared" ref="O51:O64" si="8">G51*$J$40-K51</f>
-        <v>59355367.149816632</v>
+        <v>27748199.31986165</v>
       </c>
       <c r="P51" s="180">
         <f t="shared" ref="P51:P65" ca="1" si="9">IFERROR(O51/$C$3,0)</f>
-        <v>19785122.383272212</v>
+        <v>13874099.659930825</v>
       </c>
       <c r="Q51" s="185">
         <f t="shared" ref="Q51:Q64" si="10">G51*$L$40-K51</f>
-        <v>59355367.149816632</v>
+        <v>27748199.31986165</v>
       </c>
       <c r="R51" s="185">
         <f t="shared" ref="R51:R65" ca="1" si="11">IFERROR(Q51/$C$3,0)</f>
-        <v>19785122.383272212</v>
+        <v>13874099.659930825</v>
       </c>
       <c r="T51" t="s">
         <v>124</v>
@@ -7806,47 +7806,47 @@
       </c>
       <c r="H52" s="114">
         <f t="shared" si="1"/>
-        <v>190296308.25788501</v>
+        <v>192676308.25788501</v>
       </c>
       <c r="I52" s="114">
         <f t="shared" si="2"/>
-        <v>90821909.251477003</v>
+        <v>93670252.269575</v>
       </c>
       <c r="J52" s="114">
         <f t="shared" si="3"/>
-        <v>353645050.73910099</v>
+        <v>381658564.75909901</v>
       </c>
       <c r="K52" s="114">
         <f t="shared" si="4"/>
-        <v>634763268.24846292</v>
+        <v>668005125.28655899</v>
       </c>
       <c r="L52" s="187">
         <f t="shared" si="5"/>
-        <v>0.80807634657889726</v>
+        <v>0.85039441968190521</v>
       </c>
       <c r="M52" s="184">
         <f t="shared" si="6"/>
-        <v>111484419.10067153</v>
+        <v>78242562.062575459</v>
       </c>
       <c r="N52" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>37161473.033557177</v>
+        <v>39121281.03128773</v>
       </c>
       <c r="O52" s="180">
         <f t="shared" si="8"/>
-        <v>150760613.17167866</v>
+        <v>117518756.13358259</v>
       </c>
       <c r="P52" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>50253537.72389289</v>
+        <v>58759378.066791296</v>
       </c>
       <c r="Q52" s="185">
         <f t="shared" si="10"/>
-        <v>150760613.17167866</v>
+        <v>117518756.13358259</v>
       </c>
       <c r="R52" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>50253537.72389289</v>
+        <v>58759378.066791296</v>
       </c>
       <c r="T52" t="s">
         <v>70</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="N53" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>67261858.116620064</v>
+        <v>100892787.1749301</v>
       </c>
       <c r="O53" s="180">
         <f t="shared" si="8"/>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="P53" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>71644409.867670253</v>
+        <v>107466614.80150537</v>
       </c>
       <c r="Q53" s="185">
         <f t="shared" si="10"/>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="R53" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>71644409.867670253</v>
+        <v>107466614.80150537</v>
       </c>
       <c r="T53" t="s">
         <v>169</v>
@@ -7954,47 +7954,47 @@
       </c>
       <c r="H54" s="114">
         <f t="shared" si="1"/>
-        <v>482508837.979559</v>
+        <v>499277061.85955799</v>
       </c>
       <c r="I54" s="114">
         <f t="shared" si="2"/>
-        <v>43096712.549465001</v>
+        <v>45658406.209425002</v>
       </c>
       <c r="J54" s="114">
         <f t="shared" si="3"/>
-        <v>151436270.519853</v>
+        <v>153352892.139853</v>
       </c>
       <c r="K54" s="114">
         <f t="shared" si="4"/>
-        <v>677041821.048877</v>
+        <v>698288360.20883596</v>
       </c>
       <c r="L54" s="187">
         <f t="shared" si="5"/>
-        <v>0.93170233503359501</v>
+        <v>0.96094048477750482</v>
       </c>
       <c r="M54" s="184">
         <f t="shared" si="6"/>
-        <v>13296397.297695279</v>
+        <v>-7950141.8622636795</v>
       </c>
       <c r="N54" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>4432132.432565093</v>
+        <v>-3975070.9311318398</v>
       </c>
       <c r="O54" s="180">
         <f t="shared" si="8"/>
-        <v>49629987.736988544</v>
+        <v>28383448.577029586</v>
       </c>
       <c r="P54" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>16543329.245662848</v>
+        <v>14191724.288514793</v>
       </c>
       <c r="Q54" s="185">
         <f t="shared" si="10"/>
-        <v>49629987.736988544</v>
+        <v>28383448.577029586</v>
       </c>
       <c r="R54" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>16543329.245662848</v>
+        <v>14191724.288514793</v>
       </c>
       <c r="T54" t="s">
         <v>115</v>
@@ -8052,7 +8052,7 @@
       </c>
       <c r="N55" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>67012721.371084452</v>
+        <v>100519082.05662668</v>
       </c>
       <c r="O55" s="180">
         <f t="shared" si="8"/>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="P55" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>75966071.363929212</v>
+        <v>113949107.04589382</v>
       </c>
       <c r="Q55" s="185">
         <f t="shared" si="10"/>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="R55" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>75966071.363929212</v>
+        <v>113949107.04589382</v>
       </c>
       <c r="T55" t="s">
         <v>182</v>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="H56" s="114">
         <f t="shared" si="1"/>
-        <v>190036588.29052001</v>
+        <v>194178770.260515</v>
       </c>
       <c r="I56" s="114">
         <f t="shared" si="2"/>
@@ -8110,39 +8110,39 @@
       </c>
       <c r="J56" s="114">
         <f t="shared" si="3"/>
-        <v>151739974.348151</v>
+        <v>158811370.80815101</v>
       </c>
       <c r="K56" s="114">
         <f t="shared" si="4"/>
-        <v>397659465.92860502</v>
+        <v>408873044.35860002</v>
       </c>
       <c r="L56" s="187">
         <f t="shared" si="5"/>
-        <v>0.69164664835026324</v>
+        <v>0.71115035592329334</v>
       </c>
       <c r="M56" s="184">
         <f t="shared" si="6"/>
-        <v>148539223.14660245</v>
+        <v>137325644.71660745</v>
       </c>
       <c r="N56" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>49513074.382200815</v>
+        <v>68662822.358303726</v>
       </c>
       <c r="O56" s="180">
         <f t="shared" si="8"/>
-        <v>177286522.57161337</v>
+        <v>166072944.14161837</v>
       </c>
       <c r="P56" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>59095507.523871124</v>
+        <v>83036472.070809186</v>
       </c>
       <c r="Q56" s="185">
         <f t="shared" si="10"/>
-        <v>177286522.57161337</v>
+        <v>166072944.14161837</v>
       </c>
       <c r="R56" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>59095507.523871124</v>
+        <v>83036472.070809186</v>
       </c>
       <c r="T56" t="s">
         <v>225</v>
@@ -8176,47 +8176,47 @@
       </c>
       <c r="H57" s="114">
         <f t="shared" si="1"/>
-        <v>491342417.01869798</v>
+        <v>510002008.569673</v>
       </c>
       <c r="I57" s="114">
         <f t="shared" si="2"/>
-        <v>56669125.779923998</v>
+        <v>57215125.779923998</v>
       </c>
       <c r="J57" s="114">
         <f t="shared" si="3"/>
-        <v>312947839.26937002</v>
+        <v>323013334.79936802</v>
       </c>
       <c r="K57" s="114">
         <f t="shared" si="4"/>
-        <v>860959382.06799197</v>
+        <v>890230469.148965</v>
       </c>
       <c r="L57" s="187">
         <f t="shared" si="5"/>
-        <v>0.7762096561139098</v>
+        <v>0.80259940330805568</v>
       </c>
       <c r="M57" s="184">
         <f t="shared" si="6"/>
-        <v>192765480.18051732</v>
+        <v>163494393.09954429</v>
       </c>
       <c r="N57" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>64255160.060172439</v>
+        <v>81747196.549772143</v>
       </c>
       <c r="O57" s="180">
         <f t="shared" si="8"/>
-        <v>248224683.45675468</v>
+        <v>218953596.37578166</v>
       </c>
       <c r="P57" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>82741561.152251557</v>
+        <v>109476798.18789083</v>
       </c>
       <c r="Q57" s="185">
         <f t="shared" si="10"/>
-        <v>248224683.45675468</v>
+        <v>218953596.37578166</v>
       </c>
       <c r="R57" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>82741561.152251557</v>
+        <v>109476798.18789083</v>
       </c>
       <c r="T57" t="s">
         <v>120</v>
@@ -8250,47 +8250,47 @@
       </c>
       <c r="H58" s="114">
         <f t="shared" si="1"/>
-        <v>255492042.620024</v>
+        <v>272154150.611709</v>
       </c>
       <c r="I58" s="114">
         <f t="shared" si="2"/>
-        <v>67695304.759942994</v>
+        <v>73116453.419943005</v>
       </c>
       <c r="J58" s="114">
         <f t="shared" si="3"/>
-        <v>183532696.38125801</v>
+        <v>191422516.331242</v>
       </c>
       <c r="K58" s="114">
         <f t="shared" si="4"/>
-        <v>506720043.76122499</v>
+        <v>536693120.36289394</v>
       </c>
       <c r="L58" s="187">
         <f t="shared" si="5"/>
-        <v>0.82449693498475674</v>
+        <v>0.87326688220591775</v>
       </c>
       <c r="M58" s="184">
         <f t="shared" si="6"/>
-        <v>77131782.906952381</v>
+        <v>47158706.305283427</v>
       </c>
       <c r="N58" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>25710594.302317459</v>
+        <v>23579353.152641714</v>
       </c>
       <c r="O58" s="180">
         <f t="shared" si="8"/>
-        <v>107860826.41580391</v>
+        <v>77887749.814134955</v>
       </c>
       <c r="P58" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>35953608.805267967</v>
+        <v>38943874.907067478</v>
       </c>
       <c r="Q58" s="185">
         <f t="shared" si="10"/>
-        <v>107860826.41580391</v>
+        <v>77887749.814134955</v>
       </c>
       <c r="R58" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>35953608.805267967</v>
+        <v>38943874.907067478</v>
       </c>
       <c r="T58" t="s">
         <v>125</v>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="N59" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>71679770.879199669</v>
+        <v>107519656.31879951</v>
       </c>
       <c r="O59" s="180">
         <f t="shared" si="8"/>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P59" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>79077216.138806671</v>
+        <v>118615824.20821001</v>
       </c>
       <c r="Q59" s="185">
         <f t="shared" si="10"/>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="R59" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>79077216.138806671</v>
+        <v>118615824.20821001</v>
       </c>
       <c r="T59" t="s">
         <v>170</v>
@@ -8398,47 +8398,47 @@
       </c>
       <c r="H60" s="114">
         <f t="shared" si="1"/>
-        <v>334965416.39326602</v>
+        <v>348281390.32724202</v>
       </c>
       <c r="I60" s="114">
         <f t="shared" si="2"/>
-        <v>81584972.886524007</v>
+        <v>82526864.846503004</v>
       </c>
       <c r="J60" s="114">
         <f t="shared" si="3"/>
-        <v>97847527.472525001</v>
+        <v>99668158.112520993</v>
       </c>
       <c r="K60" s="114">
         <f t="shared" si="4"/>
-        <v>514397916.75231504</v>
+        <v>530476413.28626603</v>
       </c>
       <c r="L60" s="187">
         <f t="shared" si="5"/>
-        <v>0.88813909839838412</v>
+        <v>0.91589959460222203</v>
       </c>
       <c r="M60" s="184">
         <f t="shared" si="6"/>
-        <v>35828981.034249425</v>
+        <v>19750484.50029844</v>
       </c>
       <c r="N60" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>11942993.678083142</v>
+        <v>9875242.2501492202</v>
       </c>
       <c r="O60" s="180">
         <f t="shared" si="8"/>
-        <v>64788291.44406867</v>
+        <v>48709794.910117686</v>
       </c>
       <c r="P60" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>21596097.14802289</v>
+        <v>24354897.455058843</v>
       </c>
       <c r="Q60" s="185">
         <f t="shared" si="10"/>
-        <v>64788291.44406867</v>
+        <v>48709794.910117686</v>
       </c>
       <c r="R60" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>21596097.14802289</v>
+        <v>24354897.455058843</v>
       </c>
       <c r="T60" t="s">
         <v>220</v>
@@ -8472,47 +8472,47 @@
       </c>
       <c r="H61" s="114">
         <f t="shared" si="1"/>
-        <v>440052239.37646002</v>
+        <v>451192557.081352</v>
       </c>
       <c r="I61" s="114">
         <f t="shared" si="2"/>
-        <v>59219998.644919001</v>
+        <v>62998196.844919004</v>
       </c>
       <c r="J61" s="114">
         <f t="shared" si="3"/>
-        <v>200790750.04987699</v>
+        <v>210758723.08987701</v>
       </c>
       <c r="K61" s="114">
         <f t="shared" si="4"/>
-        <v>700062988.07125592</v>
+        <v>724949477.01614809</v>
       </c>
       <c r="L61" s="187">
         <f t="shared" si="5"/>
-        <v>0.97693276649430749</v>
+        <v>1.011661679331489</v>
       </c>
       <c r="M61" s="184">
         <f t="shared" si="6"/>
-        <v>-19299826.595733523</v>
+        <v>-44186315.540625691</v>
       </c>
       <c r="N61" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>-6433275.5319111748</v>
+        <v>-22093157.770312846</v>
       </c>
       <c r="O61" s="180">
         <f t="shared" si="8"/>
-        <v>16529813.481925607</v>
+        <v>-8356675.4629665613</v>
       </c>
       <c r="P61" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>5509937.8273085356</v>
+        <v>-4178337.7314832807</v>
       </c>
       <c r="Q61" s="185">
         <f t="shared" si="10"/>
-        <v>16529813.481925607</v>
+        <v>-8356675.4629665613</v>
       </c>
       <c r="R61" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>5509937.8273085356</v>
+        <v>-4178337.7314832807</v>
       </c>
       <c r="T61" t="s">
         <v>126</v>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="H62" s="114">
         <f t="shared" si="1"/>
-        <v>133182163.255797</v>
+        <v>144279163.255797</v>
       </c>
       <c r="I62" s="114">
         <f t="shared" si="2"/>
@@ -8554,39 +8554,39 @@
       </c>
       <c r="J62" s="114">
         <f t="shared" si="3"/>
-        <v>191182198.64701799</v>
+        <v>201225937.40701801</v>
       </c>
       <c r="K62" s="114">
         <f t="shared" si="4"/>
-        <v>364229653.38060999</v>
+        <v>385370392.14060998</v>
       </c>
       <c r="L62" s="187">
         <f t="shared" si="5"/>
-        <v>0.76354694998112371</v>
+        <v>0.80786499616633589</v>
       </c>
       <c r="M62" s="184">
         <f t="shared" si="6"/>
-        <v>88942441.302151442</v>
+        <v>67801702.542151451</v>
       </c>
       <c r="N62" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>29647480.434050482</v>
+        <v>33900851.271075726</v>
       </c>
       <c r="O62" s="180">
         <f t="shared" si="8"/>
-        <v>112793604.18019152</v>
+        <v>91652865.420191526</v>
       </c>
       <c r="P62" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>37597868.060063839</v>
+        <v>45826432.710095763</v>
       </c>
       <c r="Q62" s="185">
         <f t="shared" si="10"/>
-        <v>112793604.18019152</v>
+        <v>91652865.420191526</v>
       </c>
       <c r="R62" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>37597868.060063839</v>
+        <v>45826432.710095763</v>
       </c>
       <c r="T62" t="s">
         <v>112</v>
@@ -8620,47 +8620,47 @@
       </c>
       <c r="H63" s="114">
         <f t="shared" si="1"/>
-        <v>480229048.13510603</v>
+        <v>506101282.89459699</v>
       </c>
       <c r="I63" s="114">
         <f t="shared" si="2"/>
-        <v>286587088.43090999</v>
+        <v>290879574.89086801</v>
       </c>
       <c r="J63" s="114">
         <f t="shared" si="3"/>
-        <v>283835544.43512303</v>
+        <v>286978787.695113</v>
       </c>
       <c r="K63" s="114">
         <f t="shared" si="4"/>
-        <v>1050651681.0011389</v>
+        <v>1083959645.4805779</v>
       </c>
       <c r="L63" s="187">
         <f t="shared" si="5"/>
-        <v>1.0732171476520032</v>
+        <v>1.1072404869557158</v>
       </c>
       <c r="M63" s="184">
         <f t="shared" si="6"/>
-        <v>-120626383.5720228</v>
+        <v>-153934348.05146182</v>
       </c>
       <c r="N63" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>-40208794.524007596</v>
+        <v>-76967174.025730908</v>
       </c>
       <c r="O63" s="180">
         <f t="shared" si="8"/>
-        <v>-71677683.707332373</v>
+        <v>-104985648.18677139</v>
       </c>
       <c r="P63" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>-23892561.235777456</v>
+        <v>-52492824.093385696</v>
       </c>
       <c r="Q63" s="185">
         <f t="shared" si="10"/>
-        <v>-71677683.707332373</v>
+        <v>-104985648.18677139</v>
       </c>
       <c r="R63" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>-23892561.235777456</v>
+        <v>-52492824.093385696</v>
       </c>
       <c r="T63" t="s">
         <v>127</v>
@@ -8694,47 +8694,47 @@
       </c>
       <c r="H64" s="114">
         <f t="shared" si="1"/>
-        <v>116811678.075921</v>
+        <v>121786948.57588099</v>
       </c>
       <c r="I64" s="114">
         <f t="shared" si="2"/>
-        <v>148144917.591553</v>
+        <v>160307079.591353</v>
       </c>
       <c r="J64" s="114">
         <f t="shared" si="3"/>
-        <v>165504754.06879202</v>
+        <v>170614032.83874199</v>
       </c>
       <c r="K64" s="114">
         <f t="shared" si="4"/>
-        <v>430461349.73626602</v>
+        <v>452708061.00597596</v>
       </c>
       <c r="L64" s="187">
         <f t="shared" si="5"/>
-        <v>0.80173191988298831</v>
+        <v>0.84316629848230906</v>
       </c>
       <c r="M64" s="184">
         <f t="shared" si="6"/>
-        <v>79607255.62640518</v>
+        <v>57360544.356695235</v>
       </c>
       <c r="N64" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>26535751.875468392</v>
+        <v>28680272.178347617</v>
       </c>
       <c r="O64" s="180">
         <f t="shared" si="8"/>
-        <v>106452971.69812477</v>
+        <v>84206260.428414822</v>
       </c>
       <c r="P64" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>35484323.899374925</v>
+        <v>42103130.214207411</v>
       </c>
       <c r="Q64" s="185">
         <f t="shared" si="10"/>
-        <v>106452971.69812477</v>
+        <v>84206260.428414822</v>
       </c>
       <c r="R64" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>35484323.899374925</v>
+        <v>42103130.214207411</v>
       </c>
       <c r="T64" t="s">
         <v>122</v>
@@ -8766,47 +8766,47 @@
       </c>
       <c r="H65" s="135">
         <f t="shared" si="12"/>
-        <v>3639221204.1870084</v>
+        <v>3779712959.4279799</v>
       </c>
       <c r="I65" s="135">
         <f t="shared" si="12"/>
-        <v>1010129714.9858909</v>
+        <v>1045721440.2936759</v>
       </c>
       <c r="J65" s="135">
         <f t="shared" si="12"/>
-        <v>2506546531.6597452</v>
+        <v>2604676757.2396264</v>
       </c>
       <c r="K65" s="135">
         <f t="shared" si="12"/>
-        <v>7155897450.8326426</v>
+        <v>7430111156.9612827</v>
       </c>
       <c r="L65" s="189">
         <f t="shared" si="5"/>
-        <v>0.80784886982000847</v>
+        <v>0.83880560642883195</v>
       </c>
       <c r="M65" s="181">
         <f>SUM(M51:M64)</f>
-        <v>1259169812.6836772</v>
+        <v>984956106.55503798</v>
       </c>
       <c r="N65" s="181">
         <f t="shared" ca="1" si="7"/>
-        <v>419723270.89455909</v>
+        <v>492478053.27751899</v>
       </c>
       <c r="O65" s="181">
         <f>SUM(O51:O64)</f>
-        <v>1702068089.7108521</v>
+        <v>1427854383.5822132</v>
       </c>
       <c r="P65" s="181">
         <f t="shared" ca="1" si="9"/>
-        <v>567356029.90361738</v>
+        <v>713927191.79110658</v>
       </c>
       <c r="Q65" s="186">
         <f>SUM(Q51:Q64)</f>
-        <v>1702068089.7108521</v>
+        <v>1427854383.5822132</v>
       </c>
       <c r="R65" s="186">
         <f t="shared" ca="1" si="11"/>
-        <v>567356029.90361738</v>
+        <v>713927191.79110658</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8815,21 +8815,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="293" t="s">
+      <c r="B67" s="286" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="294"/>
-      <c r="D67" s="294"/>
-      <c r="E67" s="294"/>
+      <c r="C67" s="287"/>
+      <c r="D67" s="287"/>
+      <c r="E67" s="287"/>
       <c r="F67" s="296"/>
-      <c r="G67" s="263" t="s">
+      <c r="G67" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="264"/>
-      <c r="I67" s="264"/>
-      <c r="J67" s="264"/>
-      <c r="K67" s="264"/>
-      <c r="L67" s="265"/>
+      <c r="H67" s="273"/>
+      <c r="I67" s="273"/>
+      <c r="J67" s="273"/>
+      <c r="K67" s="273"/>
+      <c r="L67" s="274"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -8891,35 +8891,35 @@
       </c>
       <c r="E69" s="114">
         <f>IFERROR($C$31,0)</f>
-        <v>259365932.35194299</v>
+        <v>276916748.691921</v>
       </c>
       <c r="F69" s="187">
         <f t="shared" ref="F69:F74" si="13">IFERROR(E69/D69,0)</f>
-        <v>1.012130099633723</v>
+        <v>1.0806190847897648</v>
       </c>
       <c r="G69" s="184">
         <f>D69*$H$40-E69</f>
-        <v>-15921304.212226599</v>
+        <v>-33472120.552204609</v>
       </c>
       <c r="H69" s="184">
         <f t="shared" ref="H69:H74" ca="1" si="14">IFERROR(G69/$C$3,0)</f>
-        <v>-5307101.4040755332</v>
+        <v>-16736060.276102304</v>
       </c>
       <c r="I69" s="204">
         <f>D69*$J$40-E69</f>
-        <v>-3108429.0469783545</v>
+        <v>-20659245.386956364</v>
       </c>
       <c r="J69" s="204">
         <f t="shared" ref="J69:J74" ca="1" si="15">IFERROR(I69/$C$3,0)</f>
-        <v>-1036143.0156594515</v>
+        <v>-10329622.693478182</v>
       </c>
       <c r="K69" s="185">
         <f>D69*$L$40-E69</f>
-        <v>-3108429.0469783545</v>
+        <v>-20659245.386956364</v>
       </c>
       <c r="L69" s="185">
         <f t="shared" ref="L69:L74" ca="1" si="16">IFERROR(K69/$C$3,0)</f>
-        <v>-1036143.0156594515</v>
+        <v>-10329622.693478182</v>
       </c>
     </row>
     <row r="70" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8935,35 +8935,35 @@
       </c>
       <c r="E70" s="114">
         <f>IFERROR($C$32,0)</f>
-        <v>457145084.04292297</v>
+        <v>458181336.78289902</v>
       </c>
       <c r="F70" s="187">
         <f t="shared" si="13"/>
-        <v>1.1441257897831596</v>
+        <v>1.1467192847717851</v>
       </c>
       <c r="G70" s="184">
         <f>D70*$H$40-E70</f>
-        <v>-77564592.353206635</v>
+        <v>-78600845.093182683</v>
       </c>
       <c r="H70" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>-25854864.117735546</v>
+        <v>-39300422.546591341</v>
       </c>
       <c r="I70" s="204">
         <f>D70*$J$40-E70</f>
-        <v>-57586671.737958372</v>
+        <v>-58622924.47793442</v>
       </c>
       <c r="J70" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>-19195557.245986123</v>
+        <v>-29311462.23896721</v>
       </c>
       <c r="K70" s="185">
         <f>D70*$L$40-E70</f>
-        <v>-57586671.737958372</v>
+        <v>-58622924.47793442</v>
       </c>
       <c r="L70" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>-19195557.245986123</v>
+        <v>-29311462.23896721</v>
       </c>
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.25">
@@ -8979,35 +8979,35 @@
       </c>
       <c r="E71" s="114">
         <f>M21</f>
-        <v>1014347446.480343</v>
+        <v>1029524757.540693</v>
       </c>
       <c r="F71" s="187">
         <f t="shared" si="13"/>
-        <v>0.9352189315230397</v>
+        <v>0.94921227146045972</v>
       </c>
       <c r="G71" s="184">
         <f>D71*$H$40-E71</f>
-        <v>16031689.009373307</v>
+        <v>854377.94902324677</v>
       </c>
       <c r="H71" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>5343896.3364577694</v>
+        <v>427188.97451162338</v>
       </c>
       <c r="I71" s="204">
         <f>D71*$J$40-E71</f>
-        <v>70262169.824621558</v>
+        <v>55084858.764271498</v>
       </c>
       <c r="J71" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>23420723.274873853</v>
+        <v>27542429.382135749</v>
       </c>
       <c r="K71" s="185">
         <f>D71*$L$40-E71</f>
-        <v>70262169.824621558</v>
+        <v>55084858.764271498</v>
       </c>
       <c r="L71" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>23420723.274873853</v>
+        <v>27542429.382135749</v>
       </c>
     </row>
     <row r="72" spans="2:21" hidden="1" x14ac:dyDescent="0.25">
@@ -9109,35 +9109,35 @@
       </c>
       <c r="E74" s="115">
         <f>SUM(E69:E73)</f>
-        <v>1730858462.8752089</v>
+        <v>1764622843.0155129</v>
       </c>
       <c r="F74" s="177">
         <f t="shared" si="13"/>
-        <v>0.9945030287913792</v>
+        <v>1.0139031005101358</v>
       </c>
       <c r="G74" s="181">
         <f>SUM(G69:G73)</f>
-        <v>-77454207.556059927</v>
+        <v>-111218587.69636405</v>
       </c>
       <c r="H74" s="181">
         <f t="shared" ca="1" si="14"/>
-        <v>-25818069.185353309</v>
+        <v>-55609293.848182023</v>
       </c>
       <c r="I74" s="186">
         <f>SUM(I69:I73)</f>
-        <v>9567069.0396848321</v>
+        <v>-24197311.100619286</v>
       </c>
       <c r="J74" s="186">
         <f t="shared" ca="1" si="15"/>
-        <v>3189023.0132282772</v>
+        <v>-12098655.550309643</v>
       </c>
       <c r="K74" s="186">
         <f>SUM(K69:K73)</f>
-        <v>9567069.0396848321</v>
+        <v>-24197311.100619286</v>
       </c>
       <c r="L74" s="186">
         <f t="shared" ca="1" si="16"/>
-        <v>3189023.0132282772</v>
+        <v>-12098655.550309643</v>
       </c>
     </row>
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9150,10 +9150,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="262" t="s">
+      <c r="B78" s="271" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="262" t="s">
+      <c r="C78" s="271" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="D80" s="131">
         <f t="shared" ref="D80:D93" si="17">SUMIF($B$10:$B$26,$T80,$F$10:$F$26)+SUMIF($B$10:$B$26,$U80,$F$10:$F$26)</f>
-        <v>414273536.65985</v>
+        <v>418959663.01985002</v>
       </c>
       <c r="T80" t="str">
         <f t="shared" ref="T80:U93" si="18">T51</f>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D81" s="132">
         <f t="shared" si="17"/>
-        <v>154511547.07999998</v>
+        <v>163643078.93000001</v>
       </c>
       <c r="T81" t="str">
         <f t="shared" si="18"/>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="D83" s="131">
         <f t="shared" si="17"/>
-        <v>383780696.16973501</v>
+        <v>417669886.18970001</v>
       </c>
       <c r="T83" t="str">
         <f t="shared" si="18"/>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="D85" s="131">
         <f t="shared" si="17"/>
-        <v>65782612.399999999</v>
+        <v>66593423.25</v>
       </c>
       <c r="T85" t="str">
         <f t="shared" si="18"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="D86" s="132">
         <f t="shared" si="17"/>
-        <v>990682602.56996906</v>
+        <v>1054625484.149969</v>
       </c>
       <c r="T86" t="str">
         <f t="shared" si="18"/>
@@ -9322,7 +9322,7 @@
       </c>
       <c r="D87" s="131">
         <f t="shared" si="17"/>
-        <v>315237664.88943499</v>
+        <v>338386814.24937999</v>
       </c>
       <c r="T87" t="str">
         <f t="shared" si="18"/>
@@ -9382,7 +9382,7 @@
       </c>
       <c r="D90" s="131">
         <f t="shared" si="17"/>
-        <v>579669561.29943395</v>
+        <v>621824291.65936995</v>
       </c>
       <c r="T90" t="str">
         <f t="shared" si="18"/>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="D91" s="132">
         <f t="shared" si="17"/>
-        <v>155970460.17992401</v>
+        <v>159875865.75992399</v>
       </c>
       <c r="T91" t="str">
         <f t="shared" si="18"/>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D92" s="131">
         <f t="shared" si="17"/>
-        <v>18820757.1204</v>
+        <v>19764540.930399999</v>
       </c>
       <c r="T92" t="str">
         <f t="shared" si="18"/>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="D93" s="132">
         <f t="shared" si="17"/>
-        <v>154461084.31800002</v>
+        <v>157617841.15799999</v>
       </c>
       <c r="T93" t="str">
         <f t="shared" si="18"/>
@@ -9460,20 +9460,12 @@
       <c r="C94" s="58"/>
       <c r="D94" s="120">
         <f>SUM(D80:D93)</f>
-        <v>3307040342.9767461</v>
+        <v>3492810709.5865927</v>
       </c>
     </row>
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B48:L48"/>
-    <mergeCell ref="G67:L67"/>
     <mergeCell ref="M48:R48"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="C49:C50"/>
@@ -9486,6 +9478,14 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B48:L48"/>
+    <mergeCell ref="G67:L67"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -10113,11 +10113,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="272" t="s">
+      <c r="B40" s="262" t="s">
         <v>163</v>
       </c>
-      <c r="C40" s="273"/>
-      <c r="D40" s="274"/>
+      <c r="C40" s="263"/>
+      <c r="D40" s="264"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -10437,33 +10437,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="275" t="s">
+      <c r="B48" s="265" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="276"/>
-      <c r="D48" s="276"/>
-      <c r="E48" s="276"/>
-      <c r="F48" s="276"/>
-      <c r="G48" s="276"/>
-      <c r="H48" s="276"/>
-      <c r="I48" s="276"/>
-      <c r="J48" s="276"/>
-      <c r="K48" s="276"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="263" t="s">
+      <c r="C48" s="266"/>
+      <c r="D48" s="266"/>
+      <c r="E48" s="266"/>
+      <c r="F48" s="266"/>
+      <c r="G48" s="266"/>
+      <c r="H48" s="266"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="266"/>
+      <c r="K48" s="266"/>
+      <c r="L48" s="289"/>
+      <c r="M48" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="264"/>
-      <c r="O48" s="264"/>
-      <c r="P48" s="264"/>
-      <c r="Q48" s="264"/>
-      <c r="R48" s="265"/>
+      <c r="N48" s="273"/>
+      <c r="O48" s="273"/>
+      <c r="P48" s="273"/>
+      <c r="Q48" s="273"/>
+      <c r="R48" s="274"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="290" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="290" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="256" t="s">
@@ -10472,49 +10472,49 @@
       <c r="E49" s="257"/>
       <c r="F49" s="257"/>
       <c r="G49" s="258"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="291" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="292"/>
+      <c r="J49" s="292"/>
+      <c r="K49" s="293"/>
+      <c r="L49" s="294" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="266" t="str">
+      <c r="M49" s="275" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="266" t="str">
+      <c r="N49" s="275" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="268" t="str">
+      <c r="O49" s="277" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="268" t="str">
+      <c r="P49" s="277" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="270" t="str">
+      <c r="Q49" s="279" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="270" t="str">
+      <c r="R49" s="279" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="262"/>
-      <c r="C50" s="262"/>
+      <c r="B50" s="271"/>
+      <c r="C50" s="271"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -10539,13 +10539,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="267"/>
-      <c r="N50" s="267"/>
-      <c r="O50" s="269"/>
-      <c r="P50" s="269"/>
-      <c r="Q50" s="271"/>
-      <c r="R50" s="271"/>
+      <c r="L50" s="295"/>
+      <c r="M50" s="276"/>
+      <c r="N50" s="276"/>
+      <c r="O50" s="278"/>
+      <c r="P50" s="278"/>
+      <c r="Q50" s="280"/>
+      <c r="R50" s="280"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -11661,21 +11661,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="293" t="s">
+      <c r="B67" s="286" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="294"/>
-      <c r="D67" s="294"/>
-      <c r="E67" s="294"/>
+      <c r="C67" s="287"/>
+      <c r="D67" s="287"/>
+      <c r="E67" s="287"/>
       <c r="F67" s="296"/>
-      <c r="G67" s="263" t="s">
+      <c r="G67" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="264"/>
-      <c r="I67" s="264"/>
-      <c r="J67" s="264"/>
-      <c r="K67" s="264"/>
-      <c r="L67" s="265"/>
+      <c r="H67" s="273"/>
+      <c r="I67" s="273"/>
+      <c r="J67" s="273"/>
+      <c r="K67" s="273"/>
+      <c r="L67" s="274"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -11996,10 +11996,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="262" t="s">
+      <c r="B78" s="271" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="262" t="s">
+      <c r="C78" s="271" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -12312,12 +12312,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -12332,6 +12326,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -12959,11 +12959,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="272" t="s">
+      <c r="B40" s="262" t="s">
         <v>175</v>
       </c>
-      <c r="C40" s="273"/>
-      <c r="D40" s="274"/>
+      <c r="C40" s="263"/>
+      <c r="D40" s="264"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -13283,33 +13283,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="275" t="s">
+      <c r="B48" s="265" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="276"/>
-      <c r="D48" s="276"/>
-      <c r="E48" s="276"/>
-      <c r="F48" s="276"/>
-      <c r="G48" s="276"/>
-      <c r="H48" s="276"/>
-      <c r="I48" s="276"/>
-      <c r="J48" s="276"/>
-      <c r="K48" s="276"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="263" t="s">
+      <c r="C48" s="266"/>
+      <c r="D48" s="266"/>
+      <c r="E48" s="266"/>
+      <c r="F48" s="266"/>
+      <c r="G48" s="266"/>
+      <c r="H48" s="266"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="266"/>
+      <c r="K48" s="266"/>
+      <c r="L48" s="289"/>
+      <c r="M48" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="264"/>
-      <c r="O48" s="264"/>
-      <c r="P48" s="264"/>
-      <c r="Q48" s="264"/>
-      <c r="R48" s="265"/>
+      <c r="N48" s="273"/>
+      <c r="O48" s="273"/>
+      <c r="P48" s="273"/>
+      <c r="Q48" s="273"/>
+      <c r="R48" s="274"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="290" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="290" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="256" t="s">
@@ -13318,49 +13318,49 @@
       <c r="E49" s="257"/>
       <c r="F49" s="257"/>
       <c r="G49" s="258"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="291" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="292"/>
+      <c r="J49" s="292"/>
+      <c r="K49" s="293"/>
+      <c r="L49" s="294" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="266" t="str">
+      <c r="M49" s="275" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="266" t="str">
+      <c r="N49" s="275" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="268" t="str">
+      <c r="O49" s="277" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="268" t="str">
+      <c r="P49" s="277" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="270" t="str">
+      <c r="Q49" s="279" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="270" t="str">
+      <c r="R49" s="279" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="262"/>
-      <c r="C50" s="262"/>
+      <c r="B50" s="271"/>
+      <c r="C50" s="271"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -13385,13 +13385,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="267"/>
-      <c r="N50" s="267"/>
-      <c r="O50" s="269"/>
-      <c r="P50" s="269"/>
-      <c r="Q50" s="271"/>
-      <c r="R50" s="271"/>
+      <c r="L50" s="295"/>
+      <c r="M50" s="276"/>
+      <c r="N50" s="276"/>
+      <c r="O50" s="278"/>
+      <c r="P50" s="278"/>
+      <c r="Q50" s="280"/>
+      <c r="R50" s="280"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -14507,21 +14507,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="293" t="s">
+      <c r="B67" s="286" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="294"/>
-      <c r="D67" s="294"/>
-      <c r="E67" s="294"/>
+      <c r="C67" s="287"/>
+      <c r="D67" s="287"/>
+      <c r="E67" s="287"/>
       <c r="F67" s="296"/>
-      <c r="G67" s="263" t="s">
+      <c r="G67" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="264"/>
-      <c r="I67" s="264"/>
-      <c r="J67" s="264"/>
-      <c r="K67" s="264"/>
-      <c r="L67" s="265"/>
+      <c r="H67" s="273"/>
+      <c r="I67" s="273"/>
+      <c r="J67" s="273"/>
+      <c r="K67" s="273"/>
+      <c r="L67" s="274"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -14842,10 +14842,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="262" t="s">
+      <c r="B78" s="271" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="262" t="s">
+      <c r="C78" s="271" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -15158,12 +15158,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -15178,6 +15172,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -15805,11 +15805,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="272" t="s">
+      <c r="B40" s="262" t="s">
         <v>177</v>
       </c>
-      <c r="C40" s="273"/>
-      <c r="D40" s="274"/>
+      <c r="C40" s="263"/>
+      <c r="D40" s="264"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -16129,33 +16129,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="275" t="s">
+      <c r="B48" s="265" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="276"/>
-      <c r="D48" s="276"/>
-      <c r="E48" s="276"/>
-      <c r="F48" s="276"/>
-      <c r="G48" s="276"/>
-      <c r="H48" s="276"/>
-      <c r="I48" s="276"/>
-      <c r="J48" s="276"/>
-      <c r="K48" s="276"/>
-      <c r="L48" s="286"/>
-      <c r="M48" s="263" t="s">
+      <c r="C48" s="266"/>
+      <c r="D48" s="266"/>
+      <c r="E48" s="266"/>
+      <c r="F48" s="266"/>
+      <c r="G48" s="266"/>
+      <c r="H48" s="266"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="266"/>
+      <c r="K48" s="266"/>
+      <c r="L48" s="289"/>
+      <c r="M48" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="264"/>
-      <c r="O48" s="264"/>
-      <c r="P48" s="264"/>
-      <c r="Q48" s="264"/>
-      <c r="R48" s="265"/>
+      <c r="N48" s="273"/>
+      <c r="O48" s="273"/>
+      <c r="P48" s="273"/>
+      <c r="Q48" s="273"/>
+      <c r="R48" s="274"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="s">
+      <c r="B49" s="290" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="287" t="s">
+      <c r="C49" s="290" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="256" t="s">
@@ -16164,49 +16164,49 @@
       <c r="E49" s="257"/>
       <c r="F49" s="257"/>
       <c r="G49" s="258"/>
-      <c r="H49" s="288" t="s">
+      <c r="H49" s="291" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="289"/>
-      <c r="J49" s="289"/>
-      <c r="K49" s="290"/>
-      <c r="L49" s="291" t="s">
+      <c r="I49" s="292"/>
+      <c r="J49" s="292"/>
+      <c r="K49" s="293"/>
+      <c r="L49" s="294" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="266" t="str">
+      <c r="M49" s="275" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="266" t="str">
+      <c r="N49" s="275" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="268" t="str">
+      <c r="O49" s="277" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="268" t="str">
+      <c r="P49" s="277" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="270" t="str">
+      <c r="Q49" s="279" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="270" t="str">
+      <c r="R49" s="279" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="262"/>
-      <c r="C50" s="262"/>
+      <c r="B50" s="271"/>
+      <c r="C50" s="271"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -16231,13 +16231,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="292"/>
-      <c r="M50" s="267"/>
-      <c r="N50" s="267"/>
-      <c r="O50" s="269"/>
-      <c r="P50" s="269"/>
-      <c r="Q50" s="271"/>
-      <c r="R50" s="271"/>
+      <c r="L50" s="295"/>
+      <c r="M50" s="276"/>
+      <c r="N50" s="276"/>
+      <c r="O50" s="278"/>
+      <c r="P50" s="278"/>
+      <c r="Q50" s="280"/>
+      <c r="R50" s="280"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -17339,21 +17339,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="293" t="s">
+      <c r="B67" s="286" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="294"/>
-      <c r="D67" s="294"/>
-      <c r="E67" s="294"/>
+      <c r="C67" s="287"/>
+      <c r="D67" s="287"/>
+      <c r="E67" s="287"/>
       <c r="F67" s="296"/>
-      <c r="G67" s="263" t="s">
+      <c r="G67" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="264"/>
-      <c r="I67" s="264"/>
-      <c r="J67" s="264"/>
-      <c r="K67" s="264"/>
-      <c r="L67" s="265"/>
+      <c r="H67" s="273"/>
+      <c r="I67" s="273"/>
+      <c r="J67" s="273"/>
+      <c r="K67" s="273"/>
+      <c r="L67" s="274"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -17674,10 +17674,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="262" t="s">
+      <c r="B78" s="271" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="262" t="s">
+      <c r="C78" s="271" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -17990,12 +17990,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -18010,6 +18004,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -25789,11 +25789,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="272" t="s">
+      <c r="B41" s="262" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="273"/>
-      <c r="D41" s="274"/>
+      <c r="C41" s="263"/>
+      <c r="D41" s="264"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -26064,59 +26064,59 @@
       </c>
     </row>
     <row r="48" spans="2:19" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="275" t="s">
+      <c r="B48" s="265" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="276"/>
-      <c r="D48" s="276"/>
-      <c r="E48" s="276"/>
-      <c r="F48" s="276"/>
-      <c r="G48" s="276"/>
-      <c r="H48" s="276"/>
-      <c r="I48" s="276"/>
-      <c r="J48" s="276"/>
-      <c r="K48" s="263" t="s">
+      <c r="C48" s="266"/>
+      <c r="D48" s="266"/>
+      <c r="E48" s="266"/>
+      <c r="F48" s="266"/>
+      <c r="G48" s="266"/>
+      <c r="H48" s="266"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="266"/>
+      <c r="K48" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="264"/>
-      <c r="M48" s="264"/>
-      <c r="N48" s="264"/>
-      <c r="O48" s="264"/>
-      <c r="P48" s="265"/>
+      <c r="L48" s="273"/>
+      <c r="M48" s="273"/>
+      <c r="N48" s="273"/>
+      <c r="O48" s="273"/>
+      <c r="P48" s="274"/>
       <c r="Q48"/>
       <c r="R48"/>
     </row>
     <row r="49" spans="2:18" s="139" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="280" t="s">
+      <c r="B49" s="270" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="280" t="s">
+      <c r="C49" s="270" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="277" t="s">
+      <c r="D49" s="267" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="278"/>
-      <c r="F49" s="279"/>
+      <c r="E49" s="268"/>
+      <c r="F49" s="269"/>
       <c r="G49" s="140" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="140"/>
       <c r="I49" s="140"/>
-      <c r="J49" s="277" t="s">
+      <c r="J49" s="267" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="266" t="str">
+      <c r="K49" s="275" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="266" t="str">
+      <c r="L49" s="275" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="268" t="str">
+      <c r="M49" s="277" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
@@ -26131,7 +26131,7 @@
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="270" t="str">
+      <c r="P49" s="279" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -26140,8 +26140,8 @@
       <c r="R49"/>
     </row>
     <row r="50" spans="2:18" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="280"/>
-      <c r="C50" s="280"/>
+      <c r="B50" s="270"/>
+      <c r="C50" s="270"/>
       <c r="D50" s="141" t="s">
         <v>149</v>
       </c>
@@ -26160,13 +26160,13 @@
       <c r="I50" s="142" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="277"/>
-      <c r="K50" s="267"/>
-      <c r="L50" s="267"/>
-      <c r="M50" s="269"/>
+      <c r="J50" s="267"/>
+      <c r="K50" s="276"/>
+      <c r="L50" s="276"/>
+      <c r="M50" s="278"/>
       <c r="N50" s="188"/>
       <c r="O50" s="183"/>
-      <c r="P50" s="271"/>
+      <c r="P50" s="280"/>
       <c r="Q50"/>
       <c r="R50"/>
     </row>
@@ -27507,10 +27507,10 @@
       <c r="I77"/>
     </row>
     <row r="78" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="262" t="s">
+      <c r="B78" s="271" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="262" t="s">
+      <c r="C78" s="271" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -27709,13 +27709,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="J49:J50"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
     <mergeCell ref="K48:P48"/>
@@ -27725,6 +27718,13 @@
     <mergeCell ref="P49:P50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="J49:J50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="26" priority="8">
@@ -28764,25 +28764,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="275" t="s">
+      <c r="B48" s="265" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="276"/>
-      <c r="D48" s="276"/>
-      <c r="E48" s="276"/>
-      <c r="F48" s="276"/>
-      <c r="G48" s="276"/>
-      <c r="H48" s="276"/>
-      <c r="I48" s="276"/>
-      <c r="J48" s="276"/>
-      <c r="K48" s="263" t="s">
+      <c r="C48" s="266"/>
+      <c r="D48" s="266"/>
+      <c r="E48" s="266"/>
+      <c r="F48" s="266"/>
+      <c r="G48" s="266"/>
+      <c r="H48" s="266"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="266"/>
+      <c r="K48" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="264"/>
-      <c r="M48" s="264"/>
-      <c r="N48" s="264"/>
-      <c r="O48" s="264"/>
-      <c r="P48" s="265"/>
+      <c r="L48" s="273"/>
+      <c r="M48" s="273"/>
+      <c r="N48" s="273"/>
+      <c r="O48" s="273"/>
+      <c r="P48" s="274"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="261" t="s">
@@ -28804,32 +28804,32 @@
       <c r="J49" s="256" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="266" t="str">
+      <c r="K49" s="275" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="266" t="str">
+      <c r="L49" s="275" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="268" t="str">
+      <c r="M49" s="277" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="268" t="str">
+      <c r="N49" s="277" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="270" t="str">
+      <c r="O49" s="279" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="270" t="str">
+      <c r="P49" s="279" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -28857,12 +28857,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="256"/>
-      <c r="K50" s="267"/>
-      <c r="L50" s="267"/>
-      <c r="M50" s="269"/>
-      <c r="N50" s="269"/>
-      <c r="O50" s="271"/>
-      <c r="P50" s="271"/>
+      <c r="K50" s="276"/>
+      <c r="L50" s="276"/>
+      <c r="M50" s="278"/>
+      <c r="N50" s="278"/>
+      <c r="O50" s="280"/>
+      <c r="P50" s="280"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="167" t="s">
@@ -30099,10 +30099,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="262" t="s">
+      <c r="B78" s="271" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="262" t="s">
+      <c r="C78" s="271" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -30296,17 +30296,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -30314,6 +30303,17 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -31071,11 +31071,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="272" t="s">
+      <c r="B41" s="262" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="273"/>
-      <c r="D41" s="274"/>
+      <c r="C41" s="263"/>
+      <c r="D41" s="264"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -31350,25 +31350,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="275" t="s">
+      <c r="B48" s="265" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="276"/>
-      <c r="D48" s="276"/>
-      <c r="E48" s="276"/>
-      <c r="F48" s="276"/>
-      <c r="G48" s="276"/>
-      <c r="H48" s="276"/>
-      <c r="I48" s="276"/>
-      <c r="J48" s="276"/>
-      <c r="K48" s="263" t="s">
+      <c r="C48" s="266"/>
+      <c r="D48" s="266"/>
+      <c r="E48" s="266"/>
+      <c r="F48" s="266"/>
+      <c r="G48" s="266"/>
+      <c r="H48" s="266"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="266"/>
+      <c r="K48" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="264"/>
-      <c r="M48" s="264"/>
-      <c r="N48" s="264"/>
-      <c r="O48" s="264"/>
-      <c r="P48" s="265"/>
+      <c r="L48" s="273"/>
+      <c r="M48" s="273"/>
+      <c r="N48" s="273"/>
+      <c r="O48" s="273"/>
+      <c r="P48" s="274"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="261" t="s">
@@ -31390,32 +31390,32 @@
       <c r="J49" s="256" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="266" t="str">
+      <c r="K49" s="275" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="266" t="str">
+      <c r="L49" s="275" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="268" t="str">
+      <c r="M49" s="277" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="268" t="str">
+      <c r="N49" s="277" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="270" t="str">
+      <c r="O49" s="279" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="270" t="str">
+      <c r="P49" s="279" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -31443,12 +31443,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="256"/>
-      <c r="K50" s="267"/>
-      <c r="L50" s="267"/>
-      <c r="M50" s="269"/>
-      <c r="N50" s="269"/>
-      <c r="O50" s="271"/>
-      <c r="P50" s="271"/>
+      <c r="K50" s="276"/>
+      <c r="L50" s="276"/>
+      <c r="M50" s="278"/>
+      <c r="N50" s="278"/>
+      <c r="O50" s="280"/>
+      <c r="P50" s="280"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -32685,10 +32685,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="262" t="s">
+      <c r="B78" s="271" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="262" t="s">
+      <c r="C78" s="271" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -32869,17 +32869,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -32887,6 +32876,17 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -33665,11 +33665,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" s="191" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="272" t="s">
+      <c r="B41" s="262" t="s">
         <v>189</v>
       </c>
-      <c r="C41" s="273"/>
-      <c r="D41" s="274"/>
+      <c r="C41" s="263"/>
+      <c r="D41" s="264"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -33944,25 +33944,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="275" t="s">
+      <c r="B48" s="265" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="276"/>
-      <c r="D48" s="276"/>
-      <c r="E48" s="276"/>
-      <c r="F48" s="276"/>
-      <c r="G48" s="276"/>
-      <c r="H48" s="276"/>
-      <c r="I48" s="276"/>
-      <c r="J48" s="276"/>
-      <c r="K48" s="263" t="s">
+      <c r="C48" s="266"/>
+      <c r="D48" s="266"/>
+      <c r="E48" s="266"/>
+      <c r="F48" s="266"/>
+      <c r="G48" s="266"/>
+      <c r="H48" s="266"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="266"/>
+      <c r="K48" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="264"/>
-      <c r="M48" s="264"/>
-      <c r="N48" s="264"/>
-      <c r="O48" s="264"/>
-      <c r="P48" s="265"/>
+      <c r="L48" s="273"/>
+      <c r="M48" s="273"/>
+      <c r="N48" s="273"/>
+      <c r="O48" s="273"/>
+      <c r="P48" s="274"/>
     </row>
     <row r="49" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="261" t="s">
@@ -33984,22 +33984,22 @@
       <c r="J49" s="256" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="266" t="str">
+      <c r="K49" s="275" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="266" t="str">
+      <c r="L49" s="275" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="268" t="str">
+      <c r="M49" s="277" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="268" t="str">
+      <c r="N49" s="277" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
@@ -34037,10 +34037,10 @@
         <v>130</v>
       </c>
       <c r="J50" s="256"/>
-      <c r="K50" s="267"/>
-      <c r="L50" s="267"/>
-      <c r="M50" s="269"/>
-      <c r="N50" s="269"/>
+      <c r="K50" s="276"/>
+      <c r="L50" s="276"/>
+      <c r="M50" s="278"/>
+      <c r="N50" s="278"/>
       <c r="O50" s="285"/>
       <c r="P50" s="285"/>
     </row>
@@ -35279,10 +35279,10 @@
       <c r="D77" s="254"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="262" t="s">
+      <c r="B78" s="271" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="262" t="s">
+      <c r="C78" s="271" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -35476,11 +35476,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
@@ -35494,6 +35489,11 @@
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" tabRatio="500" firstSheet="6" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" tabRatio="500" firstSheet="1" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="HOW TO USE" sheetId="1" r:id="rId1"/>
@@ -909,7 +909,7 @@
     <t>RONALD</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL —  29 SEPTEMBER 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL —  30 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>
@@ -1806,7 +1806,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="297">
+  <cellXfs count="296">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2482,9 +2482,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3437,16 +3434,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="B1" s="238" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="238"/>
+      <c r="B1" s="237" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="237"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="239" t="s">
+      <c r="B3" s="238" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="239"/>
+      <c r="C3" s="238"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -3497,10 +3494,10 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="240" t="s">
+      <c r="B11" s="239" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="240"/>
+      <c r="C11" s="239"/>
     </row>
     <row r="12" spans="2:3" ht="24" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -4308,11 +4305,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="262" t="s">
+      <c r="B40" s="261" t="s">
         <v>219</v>
       </c>
-      <c r="C40" s="263"/>
-      <c r="D40" s="264"/>
+      <c r="C40" s="262"/>
+      <c r="D40" s="263"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -4581,10 +4578,10 @@
       </c>
     </row>
     <row r="46" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B46" s="259" t="s">
+      <c r="B46" s="258" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="260"/>
+      <c r="C46" s="259"/>
       <c r="D46" s="47">
         <f>SUM(D42:D45)</f>
         <v>11304209690.274448</v>
@@ -4632,84 +4629,84 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="265" t="s">
+      <c r="B48" s="264" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="266"/>
-      <c r="D48" s="266"/>
-      <c r="E48" s="266"/>
-      <c r="F48" s="266"/>
-      <c r="G48" s="266"/>
-      <c r="H48" s="266"/>
-      <c r="I48" s="266"/>
-      <c r="J48" s="266"/>
-      <c r="K48" s="266"/>
-      <c r="L48" s="289"/>
-      <c r="M48" s="272" t="s">
+      <c r="C48" s="265"/>
+      <c r="D48" s="265"/>
+      <c r="E48" s="265"/>
+      <c r="F48" s="265"/>
+      <c r="G48" s="265"/>
+      <c r="H48" s="265"/>
+      <c r="I48" s="265"/>
+      <c r="J48" s="265"/>
+      <c r="K48" s="265"/>
+      <c r="L48" s="288"/>
+      <c r="M48" s="271" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="273"/>
-      <c r="O48" s="273"/>
-      <c r="P48" s="273"/>
-      <c r="Q48" s="273"/>
-      <c r="R48" s="274"/>
+      <c r="N48" s="272"/>
+      <c r="O48" s="272"/>
+      <c r="P48" s="272"/>
+      <c r="Q48" s="272"/>
+      <c r="R48" s="273"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="290" t="s">
+      <c r="B49" s="289" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="290" t="s">
+      <c r="C49" s="289" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="256" t="s">
+      <c r="D49" s="255" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="257"/>
-      <c r="F49" s="257"/>
-      <c r="G49" s="258"/>
-      <c r="H49" s="291" t="s">
+      <c r="E49" s="256"/>
+      <c r="F49" s="256"/>
+      <c r="G49" s="257"/>
+      <c r="H49" s="290" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="292"/>
-      <c r="J49" s="292"/>
-      <c r="K49" s="293"/>
-      <c r="L49" s="294" t="s">
+      <c r="I49" s="291"/>
+      <c r="J49" s="291"/>
+      <c r="K49" s="292"/>
+      <c r="L49" s="293" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="275" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="275" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="277" t="str">
+      <c r="O49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="277" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="279" t="str">
+      <c r="Q49" s="278" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="279" t="str">
+      <c r="R49" s="278" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="271"/>
-      <c r="C50" s="271"/>
+      <c r="B50" s="270"/>
+      <c r="C50" s="270"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -4734,13 +4731,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="295"/>
-      <c r="M50" s="276"/>
-      <c r="N50" s="276"/>
-      <c r="O50" s="278"/>
-      <c r="P50" s="278"/>
-      <c r="Q50" s="280"/>
-      <c r="R50" s="280"/>
+      <c r="L50" s="294"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
+      <c r="O50" s="277"/>
+      <c r="P50" s="277"/>
+      <c r="Q50" s="279"/>
+      <c r="R50" s="279"/>
       <c r="T50" s="172" t="s">
         <v>216</v>
       </c>
@@ -5856,21 +5853,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="286" t="s">
+      <c r="B67" s="285" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="287"/>
-      <c r="D67" s="287"/>
-      <c r="E67" s="287"/>
-      <c r="F67" s="288"/>
-      <c r="G67" s="272" t="s">
+      <c r="C67" s="286"/>
+      <c r="D67" s="286"/>
+      <c r="E67" s="286"/>
+      <c r="F67" s="287"/>
+      <c r="G67" s="271" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="273"/>
-      <c r="I67" s="273"/>
-      <c r="J67" s="273"/>
-      <c r="K67" s="273"/>
-      <c r="L67" s="274"/>
+      <c r="H67" s="272"/>
+      <c r="I67" s="272"/>
+      <c r="J67" s="272"/>
+      <c r="K67" s="272"/>
+      <c r="L67" s="273"/>
     </row>
     <row r="68" spans="2:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -6182,17 +6179,17 @@
       </c>
     </row>
     <row r="77" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="252" t="s">
+      <c r="B77" s="251" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="253"/>
-      <c r="D77" s="254"/>
+      <c r="C77" s="252"/>
+      <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="271" t="s">
+      <c r="B78" s="270" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="271" t="s">
+      <c r="C78" s="270" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -6200,8 +6197,8 @@
       </c>
     </row>
     <row r="79" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B79" s="261"/>
-      <c r="C79" s="261"/>
+      <c r="B79" s="260"/>
+      <c r="C79" s="260"/>
       <c r="D79" s="70" t="s">
         <v>168</v>
       </c>
@@ -6601,7 +6598,7 @@
       </c>
       <c r="C3" s="75">
         <f ca="1">IF($J$5&lt;&gt;"",$J$5,MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),9,1)),EOMONTH(DATE(YEAR(TODAY()),9,1),0),11)-MAX(0,$J$3-$J$4)))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="76" t="s">
         <v>104</v>
@@ -6728,20 +6725,20 @@
       <c r="B10" s="72" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="236">
-        <v>144279163.255797</v>
-      </c>
-      <c r="D10" s="236">
-        <v>39865291.477794997</v>
-      </c>
-      <c r="E10" s="236">
-        <v>201225937.40701801</v>
-      </c>
-      <c r="F10" s="236">
-        <v>159875865.75992399</v>
-      </c>
-      <c r="G10" s="236">
-        <v>545246257.90053403</v>
+      <c r="C10" s="235">
+        <v>144740163.23579499</v>
+      </c>
+      <c r="D10" s="235">
+        <v>42947490.453594998</v>
+      </c>
+      <c r="E10" s="235">
+        <v>203025937.43701801</v>
+      </c>
+      <c r="F10" s="235">
+        <v>167020820.35991901</v>
+      </c>
+      <c r="G10" s="235">
+        <v>557734411.48632705</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="111"/>
@@ -6753,20 +6750,20 @@
       <c r="B11" s="72" t="s">
         <v>182</v>
       </c>
-      <c r="C11" s="236">
+      <c r="C11" s="235">
         <v>5673423.4199980004</v>
       </c>
-      <c r="D11" s="236">
-        <v>32629360.699999999</v>
-      </c>
-      <c r="E11" s="236">
-        <v>271000001.35890001</v>
-      </c>
-      <c r="F11" s="236" t="s">
+      <c r="D11" s="235">
+        <v>42317826.700000003</v>
+      </c>
+      <c r="E11" s="235">
+        <v>294873875.35879999</v>
+      </c>
+      <c r="F11" s="235" t="s">
         <v>165</v>
       </c>
-      <c r="G11" s="236">
-        <v>309302785.47889799</v>
+      <c r="G11" s="235">
+        <v>342865125.47879797</v>
       </c>
       <c r="H11" s="111"/>
       <c r="I11" s="111"/>
@@ -6778,20 +6775,20 @@
       <c r="B12" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="236">
-        <v>161219730.55793801</v>
-      </c>
-      <c r="D12" s="236">
-        <v>70791542.079612002</v>
-      </c>
-      <c r="E12" s="236">
-        <v>171970814.99950901</v>
-      </c>
-      <c r="F12" s="236">
-        <v>72387121.459999993</v>
-      </c>
-      <c r="G12" s="236">
-        <v>476369209.09705901</v>
+      <c r="C12" s="235">
+        <v>184342048.20793799</v>
+      </c>
+      <c r="D12" s="235">
+        <v>73221834.879611</v>
+      </c>
+      <c r="E12" s="235">
+        <v>179141986.31949699</v>
+      </c>
+      <c r="F12" s="235">
+        <v>73537256.650000006</v>
+      </c>
+      <c r="G12" s="235">
+        <v>510243126.057046</v>
       </c>
       <c r="H12" s="111"/>
       <c r="I12" s="111"/>
@@ -6803,20 +6800,20 @@
       <c r="B13" s="72" t="s">
         <v>114</v>
       </c>
-      <c r="C13" s="236">
-        <v>31456577.699947</v>
-      </c>
-      <c r="D13" s="236">
-        <v>22878710.189963002</v>
-      </c>
-      <c r="E13" s="236">
-        <v>209687749.75959</v>
-      </c>
-      <c r="F13" s="236">
-        <v>91255957.469999999</v>
-      </c>
-      <c r="G13" s="236">
-        <v>355278995.11949998</v>
+      <c r="C13" s="235">
+        <v>34096172.366747998</v>
+      </c>
+      <c r="D13" s="235">
+        <v>24478710.189963002</v>
+      </c>
+      <c r="E13" s="235">
+        <v>220912974.83954</v>
+      </c>
+      <c r="F13" s="235">
+        <v>92206408.069999993</v>
+      </c>
+      <c r="G13" s="235">
+        <v>371694265.46625102</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="111"/>
@@ -6828,20 +6825,20 @@
       <c r="B14" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="C14" s="236">
-        <v>499277061.85955799</v>
-      </c>
-      <c r="D14" s="236">
-        <v>45658406.209425002</v>
-      </c>
-      <c r="E14" s="236">
-        <v>153352892.139853</v>
-      </c>
-      <c r="F14" s="236">
-        <v>417669886.18970001</v>
-      </c>
-      <c r="G14" s="236">
-        <v>1115958246.398536</v>
+      <c r="C14" s="235">
+        <v>519605596.399562</v>
+      </c>
+      <c r="D14" s="235">
+        <v>46985541.356622003</v>
+      </c>
+      <c r="E14" s="235">
+        <v>154687892.139853</v>
+      </c>
+      <c r="F14" s="235">
+        <v>435182498.96969998</v>
+      </c>
+      <c r="G14" s="235">
+        <v>1156461528.865737</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="111"/>
@@ -6853,20 +6850,20 @@
       <c r="B15" s="72" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="236">
-        <v>1668540388.249907</v>
-      </c>
-      <c r="D15" s="236">
-        <v>11781314.416924</v>
-      </c>
-      <c r="E15" s="236">
-        <v>94399476.329938993</v>
-      </c>
-      <c r="F15" s="236">
-        <v>17616216.550000001</v>
-      </c>
-      <c r="G15" s="236">
-        <v>1792337395.5467701</v>
+      <c r="C15" s="235">
+        <v>1671930373.3399069</v>
+      </c>
+      <c r="D15" s="235">
+        <v>12877002.040921999</v>
+      </c>
+      <c r="E15" s="235">
+        <v>95420197.059935004</v>
+      </c>
+      <c r="F15" s="235">
+        <v>18848648.969999999</v>
+      </c>
+      <c r="G15" s="235">
+        <v>1799076221.410764</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="111"/>
@@ -6878,20 +6875,20 @@
       <c r="B16" s="72" t="s">
         <v>120</v>
       </c>
-      <c r="C16" s="236">
-        <v>510002008.569673</v>
-      </c>
-      <c r="D16" s="236">
-        <v>57215125.779923998</v>
-      </c>
-      <c r="E16" s="236">
-        <v>323013334.79936802</v>
-      </c>
-      <c r="F16" s="236">
-        <v>1054625484.149969</v>
-      </c>
-      <c r="G16" s="236">
-        <v>1944855953.298934</v>
+      <c r="C16" s="235">
+        <v>521089786.50765902</v>
+      </c>
+      <c r="D16" s="235">
+        <v>57488125.779923998</v>
+      </c>
+      <c r="E16" s="235">
+        <v>331550587.10936803</v>
+      </c>
+      <c r="F16" s="235">
+        <v>1083995754.9499691</v>
+      </c>
+      <c r="G16" s="235">
+        <v>1994124254.34692</v>
       </c>
       <c r="H16" s="111"/>
       <c r="I16" s="111"/>
@@ -6903,20 +6900,20 @@
       <c r="B17" s="72" t="s">
         <v>122</v>
       </c>
-      <c r="C17" s="236">
-        <v>108130900.985884</v>
-      </c>
-      <c r="D17" s="236">
+      <c r="C17" s="235">
+        <v>109815225.42588399</v>
+      </c>
+      <c r="D17" s="235">
         <v>13122554.039898001</v>
       </c>
-      <c r="E17" s="236">
+      <c r="E17" s="235">
         <v>111572926.73874199</v>
       </c>
-      <c r="F17" s="236">
-        <v>49898919.898000002</v>
-      </c>
-      <c r="G17" s="236">
-        <v>282725301.66252398</v>
+      <c r="F17" s="235">
+        <v>50871892.898000002</v>
+      </c>
+      <c r="G17" s="235">
+        <v>285382599.10252398</v>
       </c>
       <c r="H17" s="111"/>
       <c r="I17" s="111"/>
@@ -6929,20 +6926,20 @@
       <c r="B18" s="72" t="s">
         <v>123</v>
       </c>
-      <c r="C18" s="236">
-        <v>13656047.589996999</v>
-      </c>
-      <c r="D18" s="236">
-        <v>147184525.55145499</v>
-      </c>
-      <c r="E18" s="236">
-        <v>59041106.100000001</v>
-      </c>
-      <c r="F18" s="236">
-        <v>107718921.26000001</v>
-      </c>
-      <c r="G18" s="236">
-        <v>327600600.50145203</v>
+      <c r="C18" s="235">
+        <v>15069697.589996999</v>
+      </c>
+      <c r="D18" s="235">
+        <v>159433424.38816899</v>
+      </c>
+      <c r="E18" s="235">
+        <v>64345106.100000001</v>
+      </c>
+      <c r="F18" s="235">
+        <v>109416218.59999999</v>
+      </c>
+      <c r="G18" s="235">
+        <v>348264446.67816597</v>
       </c>
       <c r="H18" s="111"/>
       <c r="I18" s="111"/>
@@ -6955,19 +6952,19 @@
       <c r="B19" s="72" t="s">
         <v>169</v>
       </c>
-      <c r="C19" s="236">
+      <c r="C19" s="235">
         <v>48019875.460000001</v>
       </c>
-      <c r="D19" s="236" t="s">
+      <c r="D19" s="235" t="s">
         <v>165</v>
       </c>
-      <c r="E19" s="236" t="s">
+      <c r="E19" s="235" t="s">
         <v>165</v>
       </c>
-      <c r="F19" s="236">
+      <c r="F19" s="235">
         <v>9945945.6799999997</v>
       </c>
-      <c r="G19" s="236">
+      <c r="G19" s="235">
         <v>57965821.140000001</v>
       </c>
       <c r="H19" s="111"/>
@@ -6981,20 +6978,20 @@
       <c r="B20" s="72" t="s">
         <v>170</v>
       </c>
-      <c r="C20" s="236">
-        <v>206615067.16</v>
-      </c>
-      <c r="D20" s="236" t="s">
+      <c r="C20" s="235">
+        <v>228406676.46000001</v>
+      </c>
+      <c r="D20" s="235" t="s">
         <v>165</v>
       </c>
-      <c r="E20" s="236" t="s">
+      <c r="E20" s="235" t="s">
         <v>165</v>
       </c>
-      <c r="F20" s="236">
+      <c r="F20" s="235">
         <v>13579549.18</v>
       </c>
-      <c r="G20" s="236">
-        <v>220194616.34</v>
+      <c r="G20" s="235">
+        <v>241986225.63999999</v>
       </c>
       <c r="H20" s="111"/>
       <c r="I20" s="111"/>
@@ -7011,27 +7008,27 @@
       <c r="B21" s="72" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="236">
-        <v>279474951.69377297</v>
-      </c>
-      <c r="D21" s="236">
-        <v>50971930.973436996</v>
-      </c>
-      <c r="E21" s="236">
-        <v>156172437.89974299</v>
-      </c>
-      <c r="F21" s="236">
-        <v>418959663.01985002</v>
-      </c>
-      <c r="G21" s="236">
-        <v>905578983.58680296</v>
+      <c r="C21" s="235">
+        <v>293251949.48080099</v>
+      </c>
+      <c r="D21" s="235">
+        <v>52174490.493436001</v>
+      </c>
+      <c r="E21" s="235">
+        <v>160692167.65973499</v>
+      </c>
+      <c r="F21" s="235">
+        <v>440958537.05983001</v>
+      </c>
+      <c r="G21" s="235">
+        <v>947077144.693802</v>
       </c>
       <c r="H21" s="111"/>
       <c r="I21" s="111"/>
       <c r="J21" s="111"/>
       <c r="M21" s="14">
         <f>SUM(C33,C34)+M20</f>
-        <v>1029524757.540693</v>
+        <v>1048400865.610592</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>224</v>
@@ -7041,20 +7038,20 @@
       <c r="B22" s="72" t="s">
         <v>225</v>
       </c>
-      <c r="C22" s="236">
-        <v>194178770.260515</v>
-      </c>
-      <c r="D22" s="236">
-        <v>55882903.289934002</v>
-      </c>
-      <c r="E22" s="236">
-        <v>158811370.80815101</v>
-      </c>
-      <c r="F22" s="236">
-        <v>66593423.25</v>
-      </c>
-      <c r="G22" s="236">
-        <v>475466467.60860002</v>
+      <c r="C22" s="235">
+        <v>203254368.21468899</v>
+      </c>
+      <c r="D22" s="235">
+        <v>64276669.089911997</v>
+      </c>
+      <c r="E22" s="235">
+        <v>164086145.60814101</v>
+      </c>
+      <c r="F22" s="235">
+        <v>65793423.229999997</v>
+      </c>
+      <c r="G22" s="235">
+        <v>497410606.14274198</v>
       </c>
       <c r="H22" s="111"/>
       <c r="I22" s="111"/>
@@ -7064,20 +7061,20 @@
       <c r="B23" s="72" t="s">
         <v>125</v>
       </c>
-      <c r="C23" s="236">
-        <v>272154150.611709</v>
-      </c>
-      <c r="D23" s="236">
-        <v>73116453.419943005</v>
-      </c>
-      <c r="E23" s="236">
-        <v>191422516.331242</v>
-      </c>
-      <c r="F23" s="236">
-        <v>338386814.24937999</v>
-      </c>
-      <c r="G23" s="236">
-        <v>875079934.61227405</v>
+      <c r="C23" s="235">
+        <v>282011574.08168399</v>
+      </c>
+      <c r="D23" s="235">
+        <v>74809273.259940997</v>
+      </c>
+      <c r="E23" s="235">
+        <v>193650083.903642</v>
+      </c>
+      <c r="F23" s="235">
+        <v>347098526.07937998</v>
+      </c>
+      <c r="G23" s="235">
+        <v>897569457.32464695</v>
       </c>
       <c r="H23" s="111"/>
       <c r="I23" s="111"/>
@@ -7087,20 +7084,20 @@
       <c r="B24" s="72" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="236">
-        <v>451192557.081352</v>
-      </c>
-      <c r="D24" s="236">
-        <v>62998196.844919004</v>
-      </c>
-      <c r="E24" s="236">
-        <v>210758723.08987701</v>
-      </c>
-      <c r="F24" s="236">
-        <v>621824291.65936995</v>
-      </c>
-      <c r="G24" s="236">
-        <v>1346773768.675518</v>
+      <c r="C24" s="235">
+        <v>473358692.59722602</v>
+      </c>
+      <c r="D24" s="235">
+        <v>68355376.974876001</v>
+      </c>
+      <c r="E24" s="235">
+        <v>214221011.39987901</v>
+      </c>
+      <c r="F24" s="235">
+        <v>637076364.45931995</v>
+      </c>
+      <c r="G24" s="235">
+        <v>1393011445.4313011</v>
       </c>
       <c r="H24" s="111"/>
       <c r="I24" s="111"/>
@@ -7110,20 +7107,20 @@
       <c r="B25" s="72" t="s">
         <v>220</v>
       </c>
-      <c r="C25" s="236">
-        <v>348281390.32724202</v>
-      </c>
-      <c r="D25" s="236">
-        <v>82526864.846503004</v>
-      </c>
-      <c r="E25" s="236">
-        <v>99668158.112520993</v>
-      </c>
-      <c r="F25" s="236">
+      <c r="C25" s="235">
+        <v>350127609.35823399</v>
+      </c>
+      <c r="D25" s="235">
+        <v>90343081.166443005</v>
+      </c>
+      <c r="E25" s="235">
+        <v>104230158.082516</v>
+      </c>
+      <c r="F25" s="235">
         <v>50324325.43</v>
       </c>
-      <c r="G25" s="236">
-        <v>580800738.71626604</v>
+      <c r="G25" s="235">
+        <v>595025174.03719294</v>
       </c>
       <c r="H25" s="111"/>
       <c r="I25" s="111"/>
@@ -7133,20 +7130,20 @@
       <c r="B26" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="236">
-        <v>506101282.89459699</v>
-      </c>
-      <c r="D26" s="236">
+      <c r="C26" s="235">
+        <v>547959392.77456105</v>
+      </c>
+      <c r="D26" s="235">
         <v>290879574.89086801</v>
       </c>
-      <c r="E26" s="236">
-        <v>286978787.695113</v>
-      </c>
-      <c r="F26" s="236">
-        <v>19764540.930399999</v>
-      </c>
-      <c r="G26" s="236">
-        <v>1103724186.4109781</v>
+      <c r="E26" s="235">
+        <v>286513427.54513299</v>
+      </c>
+      <c r="F26" s="235">
+        <v>21926703.130399998</v>
+      </c>
+      <c r="G26" s="235">
+        <v>1147279098.3409619</v>
       </c>
       <c r="H26" s="111"/>
       <c r="I26" s="111"/>
@@ -7179,7 +7176,7 @@
     </row>
     <row r="30" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="234"/>
-      <c r="C30" s="237"/>
+      <c r="C30" s="236"/>
       <c r="G30" s="111"/>
       <c r="H30" s="111"/>
       <c r="I30" s="111"/>
@@ -7189,7 +7186,7 @@
         <v>131</v>
       </c>
       <c r="C31" s="171">
-        <v>276916748.691921</v>
+        <v>280535172.19189399</v>
       </c>
       <c r="G31" s="111"/>
       <c r="H31" s="111"/>
@@ -7199,8 +7196,8 @@
       <c r="B32" s="81" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="236">
-        <v>458181336.78289902</v>
+      <c r="C32" s="171">
+        <v>473492851.69265503</v>
       </c>
       <c r="G32" s="111"/>
       <c r="H32" s="111"/>
@@ -7210,8 +7207,8 @@
       <c r="B33" s="81" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="236">
-        <v>509412546.19026101</v>
+      <c r="C33" s="235">
+        <v>515158924.34026402</v>
       </c>
       <c r="G33" s="111"/>
       <c r="H33" s="111"/>
@@ -7221,8 +7218,8 @@
       <c r="B34" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="236">
-        <v>520112211.35043198</v>
+      <c r="C34" s="235">
+        <v>533241941.27032799</v>
       </c>
       <c r="G34" s="111"/>
       <c r="H34" s="111"/>
@@ -7267,17 +7264,17 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="262" t="s">
+      <c r="B40" s="261" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="263"/>
-      <c r="D40" s="264"/>
+      <c r="C40" s="262"/>
+      <c r="D40" s="263"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
       <c r="F40" s="174">
         <f ca="1">IF(MONTH(TODAY())=9,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;9,1,0))</f>
-        <v>0.96666666666666667</v>
+        <v>1</v>
       </c>
       <c r="G40" s="192" t="s">
         <v>187</v>
@@ -7364,35 +7361,35 @@
       </c>
       <c r="E42" s="46">
         <f>H65</f>
-        <v>3779712959.4279799</v>
+        <v>3960822251.5807762</v>
       </c>
       <c r="F42" s="176">
         <f>IFERROR(E42/D42,0)</f>
-        <v>0.83774206737566415</v>
+        <v>0.87788344172277555</v>
       </c>
       <c r="G42" s="184">
         <f>D42*$H$40-E42</f>
-        <v>506483772.58644629</v>
+        <v>325374480.43365002</v>
       </c>
       <c r="H42" s="184">
         <f ca="1">IFERROR(G42/$C$3,0)</f>
-        <v>253241886.29322314</v>
+        <v>325374480.43365002</v>
       </c>
       <c r="I42" s="204">
         <f>D42*$J$40-E42</f>
-        <v>732073074.27141619</v>
+        <v>550963782.11861992</v>
       </c>
       <c r="J42" s="204">
         <f ca="1">IFERROR(I42/$C$3,0)</f>
-        <v>366036537.13570809</v>
+        <v>550963782.11861992</v>
       </c>
       <c r="K42" s="185">
         <f>D42*$L$40-E42</f>
-        <v>732073074.27141619</v>
+        <v>550963782.11861992</v>
       </c>
       <c r="L42" s="185">
         <f ca="1">IFERROR(K42/$C$3,0)</f>
-        <v>366036537.13570809</v>
+        <v>550963782.11861992</v>
       </c>
       <c r="S42" s="173">
         <v>0.8</v>
@@ -7411,35 +7408,35 @@
       </c>
       <c r="E43" s="46">
         <f>I65</f>
-        <v>1045721440.2936759</v>
+        <v>1100833973.6632581</v>
       </c>
       <c r="F43" s="176">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0.74621615966008525</v>
+        <v>0.78554390165286525</v>
       </c>
       <c r="G43" s="184">
         <f>D43*$H$40-E43</f>
-        <v>285575604.69596815</v>
+        <v>230463071.32638597</v>
       </c>
       <c r="H43" s="184">
         <f ca="1">IFERROR(G43/$C$3,0)</f>
-        <v>142787802.34798408</v>
+        <v>230463071.32638597</v>
       </c>
       <c r="I43" s="204">
         <f>D43*$J$40-E43</f>
-        <v>355643870.22173905</v>
+        <v>300531336.85215688</v>
       </c>
       <c r="J43" s="204">
         <f ca="1">IFERROR(I43/$C$3,0)</f>
-        <v>177821935.11086953</v>
+        <v>300531336.85215688</v>
       </c>
       <c r="K43" s="185">
         <f>D43*$L$40-E43</f>
-        <v>355643870.22173905</v>
+        <v>300531336.85215688</v>
       </c>
       <c r="L43" s="185">
         <f ca="1">IFERROR(K43/$C$3,0)</f>
-        <v>177821935.11086953</v>
+        <v>300531336.85215688</v>
       </c>
       <c r="S43" s="173">
         <v>0.85</v>
@@ -7458,35 +7455,35 @@
       </c>
       <c r="E44" s="46">
         <f>J65</f>
-        <v>2604676757.2396264</v>
+        <v>2683504280.2418637</v>
       </c>
       <c r="F44" s="176">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0.88449612898731944</v>
+        <v>0.91126437912021818</v>
       </c>
       <c r="G44" s="184">
         <f>IF(D44=0,0,D44*$H$40-E44)</f>
-        <v>192896729.27262449</v>
+        <v>114069206.27038717</v>
       </c>
       <c r="H44" s="184">
         <f ca="1">IFERROR(G44/$C$3,0)</f>
-        <v>96448364.636312246</v>
+        <v>114069206.27038717</v>
       </c>
       <c r="I44" s="204">
         <f>IF(D44=0,0,D44*$J$40-E44)</f>
-        <v>340137439.08905888</v>
+        <v>261309916.08682156</v>
       </c>
       <c r="J44" s="204">
         <f ca="1">IFERROR(I44/$C$3,0)</f>
-        <v>170068719.54452944</v>
+        <v>261309916.08682156</v>
       </c>
       <c r="K44" s="185">
         <f>IF(D44=0,0,D44*$L$40-E44)</f>
-        <v>340137439.08905888</v>
+        <v>261309916.08682156</v>
       </c>
       <c r="L44" s="185">
         <f ca="1">IFERROR(K44/$C$3,0)</f>
-        <v>170068719.54452944</v>
+        <v>261309916.08682156</v>
       </c>
       <c r="S44" s="173">
         <v>0.9</v>
@@ -7505,80 +7502,80 @@
       </c>
       <c r="E45" s="46">
         <f>E74</f>
-        <v>1764622843.0155129</v>
+        <v>1802428889.495141</v>
       </c>
       <c r="F45" s="176">
         <f>IFERROR(E45/D45,0)</f>
-        <v>1.0139031005101358</v>
+        <v>1.0356254010546653</v>
       </c>
       <c r="G45" s="184">
         <f>D45*$H$40-E45</f>
-        <v>-111218587.69636416</v>
+        <v>-149024634.17599225</v>
       </c>
       <c r="H45" s="184">
         <f ca="1">IFERROR(G45/$C$3,0)</f>
-        <v>-55609293.848182082</v>
+        <v>-149024634.17599225</v>
       </c>
       <c r="I45" s="204">
         <f>D45*$J$40-E45</f>
-        <v>-24197311.100619316</v>
+        <v>-62003357.580247402</v>
       </c>
       <c r="J45" s="204">
         <f ca="1">IFERROR(I45/$C$3,0)</f>
-        <v>-12098655.550309658</v>
+        <v>-62003357.580247402</v>
       </c>
       <c r="K45" s="185">
         <f>D45*$L$40-E45</f>
-        <v>-24197311.100619316</v>
+        <v>-62003357.580247402</v>
       </c>
       <c r="L45" s="185">
         <f ca="1">IFERROR(K45/$C$3,0)</f>
-        <v>-12098655.550309658</v>
+        <v>-62003357.580247402</v>
       </c>
       <c r="S45" s="173">
         <v>0.95</v>
       </c>
     </row>
     <row r="46" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="259" t="s">
+      <c r="B46" s="258" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="260"/>
+      <c r="C46" s="259"/>
       <c r="D46" s="47">
         <f>SUM(D42:D45)</f>
         <v>10598391072.458391</v>
       </c>
       <c r="E46" s="47">
         <f>SUM(E42:E45)</f>
-        <v>9194733999.9767952</v>
+        <v>9547589394.9810371</v>
       </c>
       <c r="F46" s="177">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0.86755941888866295</v>
+        <v>0.90085271714420601</v>
       </c>
       <c r="G46" s="181">
         <f>SUM(G42:G45)</f>
-        <v>873737518.85867476</v>
+        <v>520882123.85443091</v>
       </c>
       <c r="H46" s="181">
         <f ca="1">IFERROR(G46/$C$3,0)</f>
-        <v>436868759.42933738</v>
+        <v>520882123.85443091</v>
       </c>
       <c r="I46" s="186">
         <f>SUM(I42:I45)</f>
-        <v>1403657072.4815948</v>
+        <v>1050801677.477351</v>
       </c>
       <c r="J46" s="186">
         <f ca="1">IFERROR(I46/$C$3,0)</f>
-        <v>701828536.2407974</v>
+        <v>1050801677.477351</v>
       </c>
       <c r="K46" s="186">
         <f>SUM(K42:K45)</f>
-        <v>1403657072.4815948</v>
+        <v>1050801677.477351</v>
       </c>
       <c r="L46" s="186">
         <f ca="1">IFERROR(K46/$C$3,0)</f>
-        <v>701828536.2407974</v>
+        <v>1050801677.477351</v>
       </c>
       <c r="S46" s="173">
         <v>1</v>
@@ -7591,84 +7588,84 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="265" t="s">
+      <c r="B48" s="264" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="266"/>
-      <c r="D48" s="266"/>
-      <c r="E48" s="266"/>
-      <c r="F48" s="266"/>
-      <c r="G48" s="266"/>
-      <c r="H48" s="266"/>
-      <c r="I48" s="266"/>
-      <c r="J48" s="266"/>
-      <c r="K48" s="266"/>
-      <c r="L48" s="289"/>
-      <c r="M48" s="272" t="s">
+      <c r="C48" s="265"/>
+      <c r="D48" s="265"/>
+      <c r="E48" s="265"/>
+      <c r="F48" s="265"/>
+      <c r="G48" s="265"/>
+      <c r="H48" s="265"/>
+      <c r="I48" s="265"/>
+      <c r="J48" s="265"/>
+      <c r="K48" s="265"/>
+      <c r="L48" s="288"/>
+      <c r="M48" s="271" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="273"/>
-      <c r="O48" s="273"/>
-      <c r="P48" s="273"/>
-      <c r="Q48" s="273"/>
-      <c r="R48" s="274"/>
+      <c r="N48" s="272"/>
+      <c r="O48" s="272"/>
+      <c r="P48" s="272"/>
+      <c r="Q48" s="272"/>
+      <c r="R48" s="273"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="290" t="s">
+      <c r="B49" s="289" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="290" t="s">
+      <c r="C49" s="289" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="256" t="s">
+      <c r="D49" s="255" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="257"/>
-      <c r="F49" s="257"/>
-      <c r="G49" s="258"/>
-      <c r="H49" s="291" t="s">
+      <c r="E49" s="256"/>
+      <c r="F49" s="256"/>
+      <c r="G49" s="257"/>
+      <c r="H49" s="290" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="292"/>
-      <c r="J49" s="292"/>
-      <c r="K49" s="293"/>
-      <c r="L49" s="294" t="s">
+      <c r="I49" s="291"/>
+      <c r="J49" s="291"/>
+      <c r="K49" s="292"/>
+      <c r="L49" s="293" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="275" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="275" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="277" t="str">
+      <c r="O49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="277" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="Q49" s="279" t="str">
+      <c r="Q49" s="278" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="279" t="str">
+      <c r="R49" s="278" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="271"/>
-      <c r="C50" s="271"/>
+      <c r="B50" s="270"/>
+      <c r="C50" s="270"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -7693,13 +7690,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="295"/>
-      <c r="M50" s="276"/>
-      <c r="N50" s="276"/>
-      <c r="O50" s="278"/>
-      <c r="P50" s="278"/>
-      <c r="Q50" s="280"/>
-      <c r="R50" s="280"/>
+      <c r="L50" s="294"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
+      <c r="O50" s="277"/>
+      <c r="P50" s="277"/>
+      <c r="Q50" s="279"/>
+      <c r="R50" s="279"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -7732,47 +7729,47 @@
       </c>
       <c r="H51" s="114">
         <f t="shared" ref="H51:H64" si="1">SUMIF($B$10:$B$26,$T51,C$10:C$26)+SUMIF($B$10:$B$26,$U51,C$10:C$26)</f>
-        <v>279474951.69377297</v>
+        <v>293251949.48080099</v>
       </c>
       <c r="I51" s="114">
         <f t="shared" ref="I51:I64" si="2">SUMIF($B$10:$B$26,$T51,D$10:D$26)+SUMIF($B$10:$B$26,$U51,D$10:D$26)</f>
-        <v>50971930.973436996</v>
+        <v>52174490.493436001</v>
       </c>
       <c r="J51" s="114">
         <f t="shared" ref="J51:J64" si="3">SUMIF($B$10:$B$26,$T51,E$10:E$26)+SUMIF($B$10:$B$26,$U51,E$10:E$26)</f>
-        <v>156172437.89974299</v>
+        <v>160692167.65973499</v>
       </c>
       <c r="K51" s="114">
         <f t="shared" ref="K51:K64" si="4">SUM(H51:J51)</f>
-        <v>486619320.56695294</v>
+        <v>506118607.63397193</v>
       </c>
       <c r="L51" s="187">
         <f t="shared" ref="L51:L65" si="5">IFERROR(K51/G51,0)</f>
-        <v>0.94605374902760664</v>
+        <v>0.98396299934595832</v>
       </c>
       <c r="M51" s="184">
         <f t="shared" ref="M51:M64" si="6">G51*$H$40-K51</f>
-        <v>2029823.3255208731</v>
+        <v>-17469463.741498113</v>
       </c>
       <c r="N51" s="184">
         <f t="shared" ref="N51:N65" ca="1" si="7">IFERROR(M51/$C$3,0)</f>
-        <v>1014911.6627604365</v>
+        <v>-17469463.741498113</v>
       </c>
       <c r="O51" s="180">
         <f t="shared" ref="O51:O64" si="8">G51*$J$40-K51</f>
-        <v>27748199.31986165</v>
+        <v>8248912.2528426647</v>
       </c>
       <c r="P51" s="180">
         <f t="shared" ref="P51:P65" ca="1" si="9">IFERROR(O51/$C$3,0)</f>
-        <v>13874099.659930825</v>
+        <v>8248912.2528426647</v>
       </c>
       <c r="Q51" s="185">
         <f t="shared" ref="Q51:Q64" si="10">G51*$L$40-K51</f>
-        <v>27748199.31986165</v>
+        <v>8248912.2528426647</v>
       </c>
       <c r="R51" s="185">
         <f t="shared" ref="R51:R65" ca="1" si="11">IFERROR(Q51/$C$3,0)</f>
-        <v>13874099.659930825</v>
+        <v>8248912.2528426647</v>
       </c>
       <c r="T51" t="s">
         <v>124</v>
@@ -7806,47 +7803,47 @@
       </c>
       <c r="H52" s="114">
         <f t="shared" si="1"/>
-        <v>192676308.25788501</v>
+        <v>218438220.57468599</v>
       </c>
       <c r="I52" s="114">
         <f t="shared" si="2"/>
-        <v>93670252.269575</v>
+        <v>97700545.069573998</v>
       </c>
       <c r="J52" s="114">
         <f t="shared" si="3"/>
-        <v>381658564.75909901</v>
+        <v>400054961.15903699</v>
       </c>
       <c r="K52" s="114">
         <f t="shared" si="4"/>
-        <v>668005125.28655899</v>
+        <v>716193726.80329704</v>
       </c>
       <c r="L52" s="187">
         <f t="shared" si="5"/>
-        <v>0.85039441968190521</v>
+        <v>0.911740233165791</v>
       </c>
       <c r="M52" s="184">
         <f t="shared" si="6"/>
-        <v>78242562.062575459</v>
+        <v>30053960.545837402</v>
       </c>
       <c r="N52" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>39121281.03128773</v>
+        <v>30053960.545837402</v>
       </c>
       <c r="O52" s="180">
         <f t="shared" si="8"/>
-        <v>117518756.13358259</v>
+        <v>69330154.616844535</v>
       </c>
       <c r="P52" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>58759378.066791296</v>
+        <v>69330154.616844535</v>
       </c>
       <c r="Q52" s="185">
         <f t="shared" si="10"/>
-        <v>117518756.13358259</v>
+        <v>69330154.616844535</v>
       </c>
       <c r="R52" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>58759378.066791296</v>
+        <v>69330154.616844535</v>
       </c>
       <c r="T52" t="s">
         <v>70</v>
@@ -7904,7 +7901,7 @@
       </c>
       <c r="N53" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>100892787.1749301</v>
+        <v>201785574.34986019</v>
       </c>
       <c r="O53" s="180">
         <f t="shared" si="8"/>
@@ -7912,7 +7909,7 @@
       </c>
       <c r="P53" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>107466614.80150537</v>
+        <v>214933229.60301074</v>
       </c>
       <c r="Q53" s="185">
         <f t="shared" si="10"/>
@@ -7920,7 +7917,7 @@
       </c>
       <c r="R53" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>107466614.80150537</v>
+        <v>214933229.60301074</v>
       </c>
       <c r="T53" t="s">
         <v>169</v>
@@ -7954,47 +7951,47 @@
       </c>
       <c r="H54" s="114">
         <f t="shared" si="1"/>
-        <v>499277061.85955799</v>
+        <v>519605596.399562</v>
       </c>
       <c r="I54" s="114">
         <f t="shared" si="2"/>
-        <v>45658406.209425002</v>
+        <v>46985541.356622003</v>
       </c>
       <c r="J54" s="114">
         <f t="shared" si="3"/>
-        <v>153352892.139853</v>
+        <v>154687892.139853</v>
       </c>
       <c r="K54" s="114">
         <f t="shared" si="4"/>
-        <v>698288360.20883596</v>
+        <v>721279029.89603698</v>
       </c>
       <c r="L54" s="187">
         <f t="shared" si="5"/>
-        <v>0.96094048477750482</v>
+        <v>0.99257879716176289</v>
       </c>
       <c r="M54" s="184">
         <f t="shared" si="6"/>
-        <v>-7950141.8622636795</v>
+        <v>-30940811.549464703</v>
       </c>
       <c r="N54" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>-3975070.9311318398</v>
+        <v>-30940811.549464703</v>
       </c>
       <c r="O54" s="180">
         <f t="shared" si="8"/>
-        <v>28383448.577029586</v>
+        <v>5392778.8898285627</v>
       </c>
       <c r="P54" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>14191724.288514793</v>
+        <v>5392778.8898285627</v>
       </c>
       <c r="Q54" s="185">
         <f t="shared" si="10"/>
-        <v>28383448.577029586</v>
+        <v>5392778.8898285627</v>
       </c>
       <c r="R54" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>14191724.288514793</v>
+        <v>5392778.8898285627</v>
       </c>
       <c r="T54" t="s">
         <v>115</v>
@@ -8032,43 +8029,43 @@
       </c>
       <c r="I55" s="114">
         <f t="shared" si="2"/>
-        <v>32629360.699999999</v>
+        <v>42317826.700000003</v>
       </c>
       <c r="J55" s="114">
         <f t="shared" si="3"/>
-        <v>271000001.35890001</v>
+        <v>294873875.35879999</v>
       </c>
       <c r="K55" s="114">
         <f t="shared" si="4"/>
-        <v>309302785.47889799</v>
+        <v>342865125.47879797</v>
       </c>
       <c r="L55" s="187">
         <f t="shared" si="5"/>
-        <v>0.57576733052634521</v>
+        <v>0.63824364763432151</v>
       </c>
       <c r="M55" s="184">
         <f t="shared" si="6"/>
-        <v>201038164.11325336</v>
+        <v>167475824.11335337</v>
       </c>
       <c r="N55" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>100519082.05662668</v>
+        <v>167475824.11335337</v>
       </c>
       <c r="O55" s="180">
         <f t="shared" si="8"/>
-        <v>227898214.09178764</v>
+        <v>194335874.09188765</v>
       </c>
       <c r="P55" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>113949107.04589382</v>
+        <v>194335874.09188765</v>
       </c>
       <c r="Q55" s="185">
         <f t="shared" si="10"/>
-        <v>227898214.09178764</v>
+        <v>194335874.09188765</v>
       </c>
       <c r="R55" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>113949107.04589382</v>
+        <v>194335874.09188765</v>
       </c>
       <c r="T55" t="s">
         <v>182</v>
@@ -8102,47 +8099,47 @@
       </c>
       <c r="H56" s="114">
         <f t="shared" si="1"/>
-        <v>194178770.260515</v>
+        <v>203254368.21468899</v>
       </c>
       <c r="I56" s="114">
         <f t="shared" si="2"/>
-        <v>55882903.289934002</v>
+        <v>64276669.089911997</v>
       </c>
       <c r="J56" s="114">
         <f t="shared" si="3"/>
-        <v>158811370.80815101</v>
+        <v>164086145.60814101</v>
       </c>
       <c r="K56" s="114">
         <f t="shared" si="4"/>
-        <v>408873044.35860002</v>
+        <v>431617182.91274202</v>
       </c>
       <c r="L56" s="187">
         <f t="shared" si="5"/>
-        <v>0.71115035592329334</v>
+        <v>0.7507090953684914</v>
       </c>
       <c r="M56" s="184">
         <f t="shared" si="6"/>
-        <v>137325644.71660745</v>
+        <v>114581506.16246545</v>
       </c>
       <c r="N56" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>68662822.358303726</v>
+        <v>114581506.16246545</v>
       </c>
       <c r="O56" s="180">
         <f t="shared" si="8"/>
-        <v>166072944.14161837</v>
+        <v>143328805.58747637</v>
       </c>
       <c r="P56" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>83036472.070809186</v>
+        <v>143328805.58747637</v>
       </c>
       <c r="Q56" s="185">
         <f t="shared" si="10"/>
-        <v>166072944.14161837</v>
+        <v>143328805.58747637</v>
       </c>
       <c r="R56" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>83036472.070809186</v>
+        <v>143328805.58747637</v>
       </c>
       <c r="T56" t="s">
         <v>225</v>
@@ -8176,47 +8173,47 @@
       </c>
       <c r="H57" s="114">
         <f t="shared" si="1"/>
-        <v>510002008.569673</v>
+        <v>521089786.50765902</v>
       </c>
       <c r="I57" s="114">
         <f t="shared" si="2"/>
-        <v>57215125.779923998</v>
+        <v>57488125.779923998</v>
       </c>
       <c r="J57" s="114">
         <f t="shared" si="3"/>
-        <v>323013334.79936802</v>
+        <v>331550587.10936803</v>
       </c>
       <c r="K57" s="114">
         <f t="shared" si="4"/>
-        <v>890230469.148965</v>
+        <v>910128499.39695096</v>
       </c>
       <c r="L57" s="187">
         <f t="shared" si="5"/>
-        <v>0.80259940330805568</v>
+        <v>0.82053874346488742</v>
       </c>
       <c r="M57" s="184">
         <f t="shared" si="6"/>
-        <v>163494393.09954429</v>
+        <v>143596362.85155833</v>
       </c>
       <c r="N57" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>81747196.549772143</v>
+        <v>143596362.85155833</v>
       </c>
       <c r="O57" s="180">
         <f t="shared" si="8"/>
-        <v>218953596.37578166</v>
+        <v>199055566.1277957</v>
       </c>
       <c r="P57" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>109476798.18789083</v>
+        <v>199055566.1277957</v>
       </c>
       <c r="Q57" s="185">
         <f t="shared" si="10"/>
-        <v>218953596.37578166</v>
+        <v>199055566.1277957</v>
       </c>
       <c r="R57" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>109476798.18789083</v>
+        <v>199055566.1277957</v>
       </c>
       <c r="T57" t="s">
         <v>120</v>
@@ -8250,47 +8247,47 @@
       </c>
       <c r="H58" s="114">
         <f t="shared" si="1"/>
-        <v>272154150.611709</v>
+        <v>282011574.08168399</v>
       </c>
       <c r="I58" s="114">
         <f t="shared" si="2"/>
-        <v>73116453.419943005</v>
+        <v>74809273.259940997</v>
       </c>
       <c r="J58" s="114">
         <f t="shared" si="3"/>
-        <v>191422516.331242</v>
+        <v>193650083.903642</v>
       </c>
       <c r="K58" s="114">
         <f t="shared" si="4"/>
-        <v>536693120.36289394</v>
+        <v>550470931.24526691</v>
       </c>
       <c r="L58" s="187">
         <f t="shared" si="5"/>
-        <v>0.87326688220591775</v>
+        <v>0.89568510501588627</v>
       </c>
       <c r="M58" s="184">
         <f t="shared" si="6"/>
-        <v>47158706.305283427</v>
+        <v>33380895.422910452</v>
       </c>
       <c r="N58" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>23579353.152641714</v>
+        <v>33380895.422910452</v>
       </c>
       <c r="O58" s="180">
         <f t="shared" si="8"/>
-        <v>77887749.814134955</v>
+        <v>64109938.93176198</v>
       </c>
       <c r="P58" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>38943874.907067478</v>
+        <v>64109938.93176198</v>
       </c>
       <c r="Q58" s="185">
         <f t="shared" si="10"/>
-        <v>77887749.814134955</v>
+        <v>64109938.93176198</v>
       </c>
       <c r="R58" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>38943874.907067478</v>
+        <v>64109938.93176198</v>
       </c>
       <c r="T58" t="s">
         <v>125</v>
@@ -8324,7 +8321,7 @@
       </c>
       <c r="H59" s="114">
         <f t="shared" si="1"/>
-        <v>206615067.16</v>
+        <v>228406676.46000001</v>
       </c>
       <c r="I59" s="114">
         <f t="shared" si="2"/>
@@ -8336,35 +8333,35 @@
       </c>
       <c r="K59" s="114">
         <f t="shared" si="4"/>
-        <v>206615067.16</v>
+        <v>228406676.46000001</v>
       </c>
       <c r="L59" s="187">
         <f t="shared" si="5"/>
-        <v>0.46550996077929907</v>
+        <v>0.51460711196965869</v>
       </c>
       <c r="M59" s="184">
         <f t="shared" si="6"/>
-        <v>215039312.63759902</v>
+        <v>193247703.33759901</v>
       </c>
       <c r="N59" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>107519656.31879951</v>
+        <v>193247703.33759901</v>
       </c>
       <c r="O59" s="180">
         <f t="shared" si="8"/>
-        <v>237231648.41642001</v>
+        <v>215440039.11642</v>
       </c>
       <c r="P59" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>118615824.20821001</v>
+        <v>215440039.11642</v>
       </c>
       <c r="Q59" s="185">
         <f t="shared" si="10"/>
-        <v>237231648.41642001</v>
+        <v>215440039.11642</v>
       </c>
       <c r="R59" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>118615824.20821001</v>
+        <v>215440039.11642</v>
       </c>
       <c r="T59" t="s">
         <v>170</v>
@@ -8398,47 +8395,47 @@
       </c>
       <c r="H60" s="114">
         <f t="shared" si="1"/>
-        <v>348281390.32724202</v>
+        <v>350127609.35823399</v>
       </c>
       <c r="I60" s="114">
         <f t="shared" si="2"/>
-        <v>82526864.846503004</v>
+        <v>90343081.166443005</v>
       </c>
       <c r="J60" s="114">
         <f t="shared" si="3"/>
-        <v>99668158.112520993</v>
+        <v>104230158.082516</v>
       </c>
       <c r="K60" s="114">
         <f t="shared" si="4"/>
-        <v>530476413.28626603</v>
+        <v>544700848.60719299</v>
       </c>
       <c r="L60" s="187">
         <f t="shared" si="5"/>
-        <v>0.91589959460222203</v>
+        <v>0.94045894204459746</v>
       </c>
       <c r="M60" s="184">
         <f t="shared" si="6"/>
-        <v>19750484.50029844</v>
+        <v>5526049.1793714762</v>
       </c>
       <c r="N60" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>9875242.2501492202</v>
+        <v>5526049.1793714762</v>
       </c>
       <c r="O60" s="180">
         <f t="shared" si="8"/>
-        <v>48709794.910117686</v>
+        <v>34485359.589190722</v>
       </c>
       <c r="P60" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>24354897.455058843</v>
+        <v>34485359.589190722</v>
       </c>
       <c r="Q60" s="185">
         <f t="shared" si="10"/>
-        <v>48709794.910117686</v>
+        <v>34485359.589190722</v>
       </c>
       <c r="R60" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>24354897.455058843</v>
+        <v>34485359.589190722</v>
       </c>
       <c r="T60" t="s">
         <v>220</v>
@@ -8472,47 +8469,47 @@
       </c>
       <c r="H61" s="114">
         <f t="shared" si="1"/>
-        <v>451192557.081352</v>
+        <v>473358692.59722602</v>
       </c>
       <c r="I61" s="114">
         <f t="shared" si="2"/>
-        <v>62998196.844919004</v>
+        <v>68355376.974876001</v>
       </c>
       <c r="J61" s="114">
         <f t="shared" si="3"/>
-        <v>210758723.08987701</v>
+        <v>214221011.39987901</v>
       </c>
       <c r="K61" s="114">
         <f t="shared" si="4"/>
-        <v>724949477.01614809</v>
+        <v>755935080.97198105</v>
       </c>
       <c r="L61" s="187">
         <f t="shared" si="5"/>
-        <v>1.011661679331489</v>
+        <v>1.0549018624433946</v>
       </c>
       <c r="M61" s="184">
         <f t="shared" si="6"/>
-        <v>-44186315.540625691</v>
+        <v>-75171919.49645865</v>
       </c>
       <c r="N61" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>-22093157.770312846</v>
+        <v>-75171919.49645865</v>
       </c>
       <c r="O61" s="180">
         <f t="shared" si="8"/>
-        <v>-8356675.4629665613</v>
+        <v>-39342279.41879952</v>
       </c>
       <c r="P61" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>-4178337.7314832807</v>
+        <v>-39342279.41879952</v>
       </c>
       <c r="Q61" s="185">
         <f t="shared" si="10"/>
-        <v>-8356675.4629665613</v>
+        <v>-39342279.41879952</v>
       </c>
       <c r="R61" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>-4178337.7314832807</v>
+        <v>-39342279.41879952</v>
       </c>
       <c r="T61" t="s">
         <v>126</v>
@@ -8546,47 +8543,47 @@
       </c>
       <c r="H62" s="114">
         <f t="shared" si="1"/>
-        <v>144279163.255797</v>
+        <v>144740163.23579499</v>
       </c>
       <c r="I62" s="114">
         <f t="shared" si="2"/>
-        <v>39865291.477794997</v>
+        <v>42947490.453594998</v>
       </c>
       <c r="J62" s="114">
         <f t="shared" si="3"/>
-        <v>201225937.40701801</v>
+        <v>203025937.43701801</v>
       </c>
       <c r="K62" s="114">
         <f t="shared" si="4"/>
-        <v>385370392.14060998</v>
+        <v>390713591.12640798</v>
       </c>
       <c r="L62" s="187">
         <f t="shared" si="5"/>
-        <v>0.80786499616633589</v>
+        <v>0.81906612504445342</v>
       </c>
       <c r="M62" s="184">
         <f t="shared" si="6"/>
-        <v>67801702.542151451</v>
+        <v>62458503.55635345</v>
       </c>
       <c r="N62" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>33900851.271075726</v>
+        <v>62458503.55635345</v>
       </c>
       <c r="O62" s="180">
         <f t="shared" si="8"/>
-        <v>91652865.420191526</v>
+        <v>86309666.434393525</v>
       </c>
       <c r="P62" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>45826432.710095763</v>
+        <v>86309666.434393525</v>
       </c>
       <c r="Q62" s="185">
         <f t="shared" si="10"/>
-        <v>91652865.420191526</v>
+        <v>86309666.434393525</v>
       </c>
       <c r="R62" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>45826432.710095763</v>
+        <v>86309666.434393525</v>
       </c>
       <c r="T62" t="s">
         <v>112</v>
@@ -8620,7 +8617,7 @@
       </c>
       <c r="H63" s="114">
         <f t="shared" si="1"/>
-        <v>506101282.89459699</v>
+        <v>547959392.77456105</v>
       </c>
       <c r="I63" s="114">
         <f t="shared" si="2"/>
@@ -8628,39 +8625,39 @@
       </c>
       <c r="J63" s="114">
         <f t="shared" si="3"/>
-        <v>286978787.695113</v>
+        <v>286513427.54513299</v>
       </c>
       <c r="K63" s="114">
         <f t="shared" si="4"/>
-        <v>1083959645.4805779</v>
+        <v>1125352395.2105622</v>
       </c>
       <c r="L63" s="187">
         <f t="shared" si="5"/>
-        <v>1.1072404869557158</v>
+        <v>1.149522253217544</v>
       </c>
       <c r="M63" s="184">
         <f t="shared" si="6"/>
-        <v>-153934348.05146182</v>
+        <v>-195327097.7814461</v>
       </c>
       <c r="N63" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>-76967174.025730908</v>
+        <v>-195327097.7814461</v>
       </c>
       <c r="O63" s="180">
         <f t="shared" si="8"/>
-        <v>-104985648.18677139</v>
+        <v>-146378397.91675568</v>
       </c>
       <c r="P63" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>-52492824.093385696</v>
+        <v>-146378397.91675568</v>
       </c>
       <c r="Q63" s="185">
         <f t="shared" si="10"/>
-        <v>-104985648.18677139</v>
+        <v>-146378397.91675568</v>
       </c>
       <c r="R63" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>-52492824.093385696</v>
+        <v>-146378397.91675568</v>
       </c>
       <c r="T63" t="s">
         <v>127</v>
@@ -8694,47 +8691,47 @@
       </c>
       <c r="H64" s="114">
         <f t="shared" si="1"/>
-        <v>121786948.57588099</v>
+        <v>124884923.01588099</v>
       </c>
       <c r="I64" s="114">
         <f t="shared" si="2"/>
-        <v>160307079.591353</v>
+        <v>172555978.428067</v>
       </c>
       <c r="J64" s="114">
         <f t="shared" si="3"/>
-        <v>170614032.83874199</v>
+        <v>175918032.83874199</v>
       </c>
       <c r="K64" s="114">
         <f t="shared" si="4"/>
-        <v>452708061.00597596</v>
+        <v>473358934.28268993</v>
       </c>
       <c r="L64" s="187">
         <f t="shared" si="5"/>
-        <v>0.84316629848230906</v>
+        <v>0.88162843750952713</v>
       </c>
       <c r="M64" s="184">
         <f t="shared" si="6"/>
-        <v>57360544.356695235</v>
+        <v>36709671.079981267</v>
       </c>
       <c r="N64" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>28680272.178347617</v>
+        <v>36709671.079981267</v>
       </c>
       <c r="O64" s="180">
         <f t="shared" si="8"/>
-        <v>84206260.428414822</v>
+        <v>63555387.151700854</v>
       </c>
       <c r="P64" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>42103130.214207411</v>
+        <v>63555387.151700854</v>
       </c>
       <c r="Q64" s="185">
         <f t="shared" si="10"/>
-        <v>84206260.428414822</v>
+        <v>63555387.151700854</v>
       </c>
       <c r="R64" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>42103130.214207411</v>
+        <v>63555387.151700854</v>
       </c>
       <c r="T64" t="s">
         <v>122</v>
@@ -8766,47 +8763,47 @@
       </c>
       <c r="H65" s="135">
         <f t="shared" si="12"/>
-        <v>3779712959.4279799</v>
+        <v>3960822251.5807762</v>
       </c>
       <c r="I65" s="135">
         <f t="shared" si="12"/>
-        <v>1045721440.2936759</v>
+        <v>1100833973.6632581</v>
       </c>
       <c r="J65" s="135">
         <f t="shared" si="12"/>
-        <v>2604676757.2396264</v>
+        <v>2683504280.2418637</v>
       </c>
       <c r="K65" s="135">
         <f t="shared" si="12"/>
-        <v>7430111156.9612827</v>
+        <v>7745160505.4858971</v>
       </c>
       <c r="L65" s="189">
         <f t="shared" si="5"/>
-        <v>0.83880560642883195</v>
+        <v>0.87437239059418148</v>
       </c>
       <c r="M65" s="181">
         <f>SUM(M51:M64)</f>
-        <v>984956106.55503798</v>
+        <v>669906758.03042293</v>
       </c>
       <c r="N65" s="181">
         <f t="shared" ca="1" si="7"/>
-        <v>492478053.27751899</v>
+        <v>669906758.03042293</v>
       </c>
       <c r="O65" s="181">
         <f>SUM(O51:O64)</f>
-        <v>1427854383.5822132</v>
+        <v>1112805035.0575981</v>
       </c>
       <c r="P65" s="181">
         <f t="shared" ca="1" si="9"/>
-        <v>713927191.79110658</v>
+        <v>1112805035.0575981</v>
       </c>
       <c r="Q65" s="186">
         <f>SUM(Q51:Q64)</f>
-        <v>1427854383.5822132</v>
+        <v>1112805035.0575981</v>
       </c>
       <c r="R65" s="186">
         <f t="shared" ca="1" si="11"/>
-        <v>713927191.79110658</v>
+        <v>1112805035.0575981</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8815,21 +8812,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="286" t="s">
+      <c r="B67" s="285" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="287"/>
-      <c r="D67" s="287"/>
-      <c r="E67" s="287"/>
-      <c r="F67" s="296"/>
-      <c r="G67" s="272" t="s">
+      <c r="C67" s="286"/>
+      <c r="D67" s="286"/>
+      <c r="E67" s="286"/>
+      <c r="F67" s="295"/>
+      <c r="G67" s="271" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="273"/>
-      <c r="I67" s="273"/>
-      <c r="J67" s="273"/>
-      <c r="K67" s="273"/>
-      <c r="L67" s="274"/>
+      <c r="H67" s="272"/>
+      <c r="I67" s="272"/>
+      <c r="J67" s="272"/>
+      <c r="K67" s="272"/>
+      <c r="L67" s="273"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -8891,35 +8888,35 @@
       </c>
       <c r="E69" s="114">
         <f>IFERROR($C$31,0)</f>
-        <v>276916748.691921</v>
+        <v>280535172.19189399</v>
       </c>
       <c r="F69" s="187">
         <f t="shared" ref="F69:F74" si="13">IFERROR(E69/D69,0)</f>
-        <v>1.0806190847897648</v>
+        <v>1.0947393484047068</v>
       </c>
       <c r="G69" s="184">
         <f>D69*$H$40-E69</f>
-        <v>-33472120.552204609</v>
+        <v>-37090544.052177608</v>
       </c>
       <c r="H69" s="184">
         <f t="shared" ref="H69:H74" ca="1" si="14">IFERROR(G69/$C$3,0)</f>
-        <v>-16736060.276102304</v>
+        <v>-37090544.052177608</v>
       </c>
       <c r="I69" s="204">
         <f>D69*$J$40-E69</f>
-        <v>-20659245.386956364</v>
+        <v>-24277668.886929363</v>
       </c>
       <c r="J69" s="204">
         <f t="shared" ref="J69:J74" ca="1" si="15">IFERROR(I69/$C$3,0)</f>
-        <v>-10329622.693478182</v>
+        <v>-24277668.886929363</v>
       </c>
       <c r="K69" s="185">
         <f>D69*$L$40-E69</f>
-        <v>-20659245.386956364</v>
+        <v>-24277668.886929363</v>
       </c>
       <c r="L69" s="185">
         <f t="shared" ref="L69:L74" ca="1" si="16">IFERROR(K69/$C$3,0)</f>
-        <v>-10329622.693478182</v>
+        <v>-24277668.886929363</v>
       </c>
     </row>
     <row r="70" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8935,35 +8932,35 @@
       </c>
       <c r="E70" s="114">
         <f>IFERROR($C$32,0)</f>
-        <v>458181336.78289902</v>
+        <v>473492851.69265503</v>
       </c>
       <c r="F70" s="187">
         <f t="shared" si="13"/>
-        <v>1.1467192847717851</v>
+        <v>1.1850403773535361</v>
       </c>
       <c r="G70" s="184">
         <f>D70*$H$40-E70</f>
-        <v>-78600845.093182683</v>
+        <v>-93912360.002938688</v>
       </c>
       <c r="H70" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>-39300422.546591341</v>
+        <v>-93912360.002938688</v>
       </c>
       <c r="I70" s="204">
         <f>D70*$J$40-E70</f>
-        <v>-58622924.47793442</v>
+        <v>-73934439.387690425</v>
       </c>
       <c r="J70" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>-29311462.23896721</v>
+        <v>-73934439.387690425</v>
       </c>
       <c r="K70" s="185">
         <f>D70*$L$40-E70</f>
-        <v>-58622924.47793442</v>
+        <v>-73934439.387690425</v>
       </c>
       <c r="L70" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>-29311462.23896721</v>
+        <v>-73934439.387690425</v>
       </c>
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.25">
@@ -8979,35 +8976,35 @@
       </c>
       <c r="E71" s="114">
         <f>M21</f>
-        <v>1029524757.540693</v>
+        <v>1048400865.610592</v>
       </c>
       <c r="F71" s="187">
         <f t="shared" si="13"/>
-        <v>0.94921227146045972</v>
+        <v>0.96661586791224652</v>
       </c>
       <c r="G71" s="184">
         <f>D71*$H$40-E71</f>
-        <v>854377.94902324677</v>
+        <v>-18021730.120875716</v>
       </c>
       <c r="H71" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>427188.97451162338</v>
+        <v>-18021730.120875716</v>
       </c>
       <c r="I71" s="204">
         <f>D71*$J$40-E71</f>
-        <v>55084858.764271498</v>
+        <v>36208750.694372535</v>
       </c>
       <c r="J71" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>27542429.382135749</v>
+        <v>36208750.694372535</v>
       </c>
       <c r="K71" s="185">
         <f>D71*$L$40-E71</f>
-        <v>55084858.764271498</v>
+        <v>36208750.694372535</v>
       </c>
       <c r="L71" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>27542429.382135749</v>
+        <v>36208750.694372535</v>
       </c>
     </row>
     <row r="72" spans="2:21" hidden="1" x14ac:dyDescent="0.25">
@@ -9109,51 +9106,51 @@
       </c>
       <c r="E74" s="115">
         <f>SUM(E69:E73)</f>
-        <v>1764622843.0155129</v>
+        <v>1802428889.495141</v>
       </c>
       <c r="F74" s="177">
         <f t="shared" si="13"/>
-        <v>1.0139031005101358</v>
+        <v>1.0356254010546653</v>
       </c>
       <c r="G74" s="181">
         <f>SUM(G69:G73)</f>
-        <v>-111218587.69636405</v>
+        <v>-149024634.17599201</v>
       </c>
       <c r="H74" s="181">
         <f t="shared" ca="1" si="14"/>
-        <v>-55609293.848182023</v>
+        <v>-149024634.17599201</v>
       </c>
       <c r="I74" s="186">
         <f>SUM(I69:I73)</f>
-        <v>-24197311.100619286</v>
+        <v>-62003357.580247253</v>
       </c>
       <c r="J74" s="186">
         <f t="shared" ca="1" si="15"/>
-        <v>-12098655.550309643</v>
+        <v>-62003357.580247253</v>
       </c>
       <c r="K74" s="186">
         <f>SUM(K69:K73)</f>
-        <v>-24197311.100619286</v>
+        <v>-62003357.580247253</v>
       </c>
       <c r="L74" s="186">
         <f t="shared" ca="1" si="16"/>
-        <v>-12098655.550309643</v>
+        <v>-62003357.580247253</v>
       </c>
     </row>
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="76" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="252" t="s">
+      <c r="B77" s="251" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="253"/>
-      <c r="D77" s="254"/>
+      <c r="C77" s="252"/>
+      <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="271" t="s">
+      <c r="B78" s="270" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="271" t="s">
+      <c r="C78" s="270" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -9161,8 +9158,8 @@
       </c>
     </row>
     <row r="79" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="261"/>
-      <c r="C79" s="261"/>
+      <c r="B79" s="260"/>
+      <c r="C79" s="260"/>
       <c r="D79" s="70" t="s">
         <v>168</v>
       </c>
@@ -9182,7 +9179,7 @@
       </c>
       <c r="D80" s="131">
         <f t="shared" ref="D80:D93" si="17">SUMIF($B$10:$B$26,$T80,$F$10:$F$26)+SUMIF($B$10:$B$26,$U80,$F$10:$F$26)</f>
-        <v>418959663.01985002</v>
+        <v>440958537.05983001</v>
       </c>
       <c r="T80" t="str">
         <f t="shared" ref="T80:U93" si="18">T51</f>
@@ -9202,7 +9199,7 @@
       </c>
       <c r="D81" s="132">
         <f t="shared" si="17"/>
-        <v>163643078.93000001</v>
+        <v>165743664.72</v>
       </c>
       <c r="T81" t="str">
         <f t="shared" si="18"/>
@@ -9242,7 +9239,7 @@
       </c>
       <c r="D83" s="131">
         <f t="shared" si="17"/>
-        <v>417669886.18970001</v>
+        <v>435182498.96969998</v>
       </c>
       <c r="T83" t="str">
         <f t="shared" si="18"/>
@@ -9282,7 +9279,7 @@
       </c>
       <c r="D85" s="131">
         <f t="shared" si="17"/>
-        <v>66593423.25</v>
+        <v>65793423.229999997</v>
       </c>
       <c r="T85" t="str">
         <f t="shared" si="18"/>
@@ -9302,7 +9299,7 @@
       </c>
       <c r="D86" s="132">
         <f t="shared" si="17"/>
-        <v>1054625484.149969</v>
+        <v>1083995754.9499691</v>
       </c>
       <c r="T86" t="str">
         <f t="shared" si="18"/>
@@ -9322,7 +9319,7 @@
       </c>
       <c r="D87" s="131">
         <f t="shared" si="17"/>
-        <v>338386814.24937999</v>
+        <v>347098526.07937998</v>
       </c>
       <c r="T87" t="str">
         <f t="shared" si="18"/>
@@ -9382,7 +9379,7 @@
       </c>
       <c r="D90" s="131">
         <f t="shared" si="17"/>
-        <v>621824291.65936995</v>
+        <v>637076364.45931995</v>
       </c>
       <c r="T90" t="str">
         <f t="shared" si="18"/>
@@ -9402,7 +9399,7 @@
       </c>
       <c r="D91" s="132">
         <f t="shared" si="17"/>
-        <v>159875865.75992399</v>
+        <v>167020820.35991901</v>
       </c>
       <c r="T91" t="str">
         <f t="shared" si="18"/>
@@ -9422,7 +9419,7 @@
       </c>
       <c r="D92" s="131">
         <f t="shared" si="17"/>
-        <v>19764540.930399999</v>
+        <v>21926703.130399998</v>
       </c>
       <c r="T92" t="str">
         <f t="shared" si="18"/>
@@ -9442,7 +9439,7 @@
       </c>
       <c r="D93" s="132">
         <f t="shared" si="17"/>
-        <v>157617841.15799999</v>
+        <v>160288111.498</v>
       </c>
       <c r="T93" t="str">
         <f t="shared" si="18"/>
@@ -9460,7 +9457,7 @@
       <c r="C94" s="58"/>
       <c r="D94" s="120">
         <f>SUM(D80:D93)</f>
-        <v>3492810709.5865927</v>
+        <v>3598934224.7465181</v>
       </c>
     </row>
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9968,7 +9965,7 @@
     </row>
     <row r="25" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="72" t="s">
-        <v>183</v>
+        <v>225</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="15"/>
@@ -10113,11 +10110,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="262" t="s">
+      <c r="B40" s="261" t="s">
         <v>163</v>
       </c>
-      <c r="C40" s="263"/>
-      <c r="D40" s="264"/>
+      <c r="C40" s="262"/>
+      <c r="D40" s="263"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -10386,10 +10383,10 @@
       </c>
     </row>
     <row r="46" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="259" t="s">
+      <c r="B46" s="258" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="260"/>
+      <c r="C46" s="259"/>
       <c r="D46" s="47">
         <f>SUM(D42:D45)</f>
         <v>0</v>
@@ -10437,84 +10434,84 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="265" t="s">
+      <c r="B48" s="264" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="266"/>
-      <c r="D48" s="266"/>
-      <c r="E48" s="266"/>
-      <c r="F48" s="266"/>
-      <c r="G48" s="266"/>
-      <c r="H48" s="266"/>
-      <c r="I48" s="266"/>
-      <c r="J48" s="266"/>
-      <c r="K48" s="266"/>
-      <c r="L48" s="289"/>
-      <c r="M48" s="272" t="s">
+      <c r="C48" s="265"/>
+      <c r="D48" s="265"/>
+      <c r="E48" s="265"/>
+      <c r="F48" s="265"/>
+      <c r="G48" s="265"/>
+      <c r="H48" s="265"/>
+      <c r="I48" s="265"/>
+      <c r="J48" s="265"/>
+      <c r="K48" s="265"/>
+      <c r="L48" s="288"/>
+      <c r="M48" s="271" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="273"/>
-      <c r="O48" s="273"/>
-      <c r="P48" s="273"/>
-      <c r="Q48" s="273"/>
-      <c r="R48" s="274"/>
+      <c r="N48" s="272"/>
+      <c r="O48" s="272"/>
+      <c r="P48" s="272"/>
+      <c r="Q48" s="272"/>
+      <c r="R48" s="273"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="290" t="s">
+      <c r="B49" s="289" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="290" t="s">
+      <c r="C49" s="289" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="256" t="s">
+      <c r="D49" s="255" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="257"/>
-      <c r="F49" s="257"/>
-      <c r="G49" s="258"/>
-      <c r="H49" s="291" t="s">
+      <c r="E49" s="256"/>
+      <c r="F49" s="256"/>
+      <c r="G49" s="257"/>
+      <c r="H49" s="290" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="292"/>
-      <c r="J49" s="292"/>
-      <c r="K49" s="293"/>
-      <c r="L49" s="294" t="s">
+      <c r="I49" s="291"/>
+      <c r="J49" s="291"/>
+      <c r="K49" s="292"/>
+      <c r="L49" s="293" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="275" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="275" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="277" t="str">
+      <c r="O49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="277" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="279" t="str">
+      <c r="Q49" s="278" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="279" t="str">
+      <c r="R49" s="278" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="271"/>
-      <c r="C50" s="271"/>
+      <c r="B50" s="270"/>
+      <c r="C50" s="270"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -10539,13 +10536,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="295"/>
-      <c r="M50" s="276"/>
-      <c r="N50" s="276"/>
-      <c r="O50" s="278"/>
-      <c r="P50" s="278"/>
-      <c r="Q50" s="280"/>
-      <c r="R50" s="280"/>
+      <c r="L50" s="294"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
+      <c r="O50" s="277"/>
+      <c r="P50" s="277"/>
+      <c r="Q50" s="279"/>
+      <c r="R50" s="279"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -10928,7 +10925,7 @@
         <v>75</v>
       </c>
       <c r="C56" s="56" t="s">
-        <v>99</v>
+        <v>226</v>
       </c>
       <c r="D56" s="119">
         <f>TARGETS!AE10</f>
@@ -10991,7 +10988,7 @@
         <v>0</v>
       </c>
       <c r="T56" t="s">
-        <v>183</v>
+        <v>225</v>
       </c>
       <c r="U56" t="s">
         <v>218</v>
@@ -11661,21 +11658,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="286" t="s">
+      <c r="B67" s="285" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="287"/>
-      <c r="D67" s="287"/>
-      <c r="E67" s="287"/>
-      <c r="F67" s="296"/>
-      <c r="G67" s="272" t="s">
+      <c r="C67" s="286"/>
+      <c r="D67" s="286"/>
+      <c r="E67" s="286"/>
+      <c r="F67" s="295"/>
+      <c r="G67" s="271" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="273"/>
-      <c r="I67" s="273"/>
-      <c r="J67" s="273"/>
-      <c r="K67" s="273"/>
-      <c r="L67" s="274"/>
+      <c r="H67" s="272"/>
+      <c r="I67" s="272"/>
+      <c r="J67" s="272"/>
+      <c r="K67" s="272"/>
+      <c r="L67" s="273"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -11773,7 +11770,7 @@
         <v>94</v>
       </c>
       <c r="C70" s="56" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D70" s="117">
         <f>TARGETS!M23</f>
@@ -11989,17 +11986,17 @@
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="76" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="252" t="s">
+      <c r="B77" s="251" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="253"/>
-      <c r="D77" s="254"/>
+      <c r="C77" s="252"/>
+      <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="271" t="s">
+      <c r="B78" s="270" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="271" t="s">
+      <c r="C78" s="270" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -12007,8 +12004,8 @@
       </c>
     </row>
     <row r="79" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="261"/>
-      <c r="C79" s="261"/>
+      <c r="B79" s="260"/>
+      <c r="C79" s="260"/>
       <c r="D79" s="70" t="s">
         <v>168</v>
       </c>
@@ -12104,7 +12101,7 @@
         <v>73</v>
       </c>
       <c r="C84" s="56" t="s">
-        <v>74</v>
+        <v>222</v>
       </c>
       <c r="D84" s="132">
         <f t="shared" si="19"/>
@@ -12124,7 +12121,7 @@
         <v>75</v>
       </c>
       <c r="C85" s="55" t="s">
-        <v>74</v>
+        <v>226</v>
       </c>
       <c r="D85" s="131">
         <f t="shared" si="19"/>
@@ -12132,7 +12129,7 @@
       </c>
       <c r="T85" t="str">
         <f t="shared" si="18"/>
-        <v>Vacant Hotel Kuta Seminyak</v>
+        <v>Ronald</v>
       </c>
       <c r="U85" t="str">
         <f t="shared" si="18"/>
@@ -12959,11 +12956,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="262" t="s">
+      <c r="B40" s="261" t="s">
         <v>175</v>
       </c>
-      <c r="C40" s="263"/>
-      <c r="D40" s="264"/>
+      <c r="C40" s="262"/>
+      <c r="D40" s="263"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -13232,10 +13229,10 @@
       </c>
     </row>
     <row r="46" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="259" t="s">
+      <c r="B46" s="258" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="260"/>
+      <c r="C46" s="259"/>
       <c r="D46" s="47">
         <f>SUM(D42:D45)</f>
         <v>0</v>
@@ -13283,84 +13280,84 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="265" t="s">
+      <c r="B48" s="264" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="266"/>
-      <c r="D48" s="266"/>
-      <c r="E48" s="266"/>
-      <c r="F48" s="266"/>
-      <c r="G48" s="266"/>
-      <c r="H48" s="266"/>
-      <c r="I48" s="266"/>
-      <c r="J48" s="266"/>
-      <c r="K48" s="266"/>
-      <c r="L48" s="289"/>
-      <c r="M48" s="272" t="s">
+      <c r="C48" s="265"/>
+      <c r="D48" s="265"/>
+      <c r="E48" s="265"/>
+      <c r="F48" s="265"/>
+      <c r="G48" s="265"/>
+      <c r="H48" s="265"/>
+      <c r="I48" s="265"/>
+      <c r="J48" s="265"/>
+      <c r="K48" s="265"/>
+      <c r="L48" s="288"/>
+      <c r="M48" s="271" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="273"/>
-      <c r="O48" s="273"/>
-      <c r="P48" s="273"/>
-      <c r="Q48" s="273"/>
-      <c r="R48" s="274"/>
+      <c r="N48" s="272"/>
+      <c r="O48" s="272"/>
+      <c r="P48" s="272"/>
+      <c r="Q48" s="272"/>
+      <c r="R48" s="273"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="290" t="s">
+      <c r="B49" s="289" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="290" t="s">
+      <c r="C49" s="289" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="256" t="s">
+      <c r="D49" s="255" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="257"/>
-      <c r="F49" s="257"/>
-      <c r="G49" s="258"/>
-      <c r="H49" s="291" t="s">
+      <c r="E49" s="256"/>
+      <c r="F49" s="256"/>
+      <c r="G49" s="257"/>
+      <c r="H49" s="290" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="292"/>
-      <c r="J49" s="292"/>
-      <c r="K49" s="293"/>
-      <c r="L49" s="294" t="s">
+      <c r="I49" s="291"/>
+      <c r="J49" s="291"/>
+      <c r="K49" s="292"/>
+      <c r="L49" s="293" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="275" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="275" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="277" t="str">
+      <c r="O49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="277" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="279" t="str">
+      <c r="Q49" s="278" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="279" t="str">
+      <c r="R49" s="278" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="271"/>
-      <c r="C50" s="271"/>
+      <c r="B50" s="270"/>
+      <c r="C50" s="270"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -13385,13 +13382,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="295"/>
-      <c r="M50" s="276"/>
-      <c r="N50" s="276"/>
-      <c r="O50" s="278"/>
-      <c r="P50" s="278"/>
-      <c r="Q50" s="280"/>
-      <c r="R50" s="280"/>
+      <c r="L50" s="294"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
+      <c r="O50" s="277"/>
+      <c r="P50" s="277"/>
+      <c r="Q50" s="279"/>
+      <c r="R50" s="279"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -14507,21 +14504,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="286" t="s">
+      <c r="B67" s="285" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="287"/>
-      <c r="D67" s="287"/>
-      <c r="E67" s="287"/>
-      <c r="F67" s="296"/>
-      <c r="G67" s="272" t="s">
+      <c r="C67" s="286"/>
+      <c r="D67" s="286"/>
+      <c r="E67" s="286"/>
+      <c r="F67" s="295"/>
+      <c r="G67" s="271" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="273"/>
-      <c r="I67" s="273"/>
-      <c r="J67" s="273"/>
-      <c r="K67" s="273"/>
-      <c r="L67" s="274"/>
+      <c r="H67" s="272"/>
+      <c r="I67" s="272"/>
+      <c r="J67" s="272"/>
+      <c r="K67" s="272"/>
+      <c r="L67" s="273"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -14835,17 +14832,17 @@
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="76" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="252" t="s">
+      <c r="B77" s="251" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="253"/>
-      <c r="D77" s="254"/>
+      <c r="C77" s="252"/>
+      <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="271" t="s">
+      <c r="B78" s="270" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="271" t="s">
+      <c r="C78" s="270" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -14853,8 +14850,8 @@
       </c>
     </row>
     <row r="79" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="261"/>
-      <c r="C79" s="261"/>
+      <c r="B79" s="260"/>
+      <c r="C79" s="260"/>
       <c r="D79" s="70" t="s">
         <v>168</v>
       </c>
@@ -15805,11 +15802,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="262" t="s">
+      <c r="B40" s="261" t="s">
         <v>177</v>
       </c>
-      <c r="C40" s="263"/>
-      <c r="D40" s="264"/>
+      <c r="C40" s="262"/>
+      <c r="D40" s="263"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -16078,10 +16075,10 @@
       </c>
     </row>
     <row r="46" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="259" t="s">
+      <c r="B46" s="258" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="260"/>
+      <c r="C46" s="259"/>
       <c r="D46" s="47">
         <f>SUM(D42:D45)</f>
         <v>0</v>
@@ -16129,84 +16126,84 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="265" t="s">
+      <c r="B48" s="264" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="266"/>
-      <c r="D48" s="266"/>
-      <c r="E48" s="266"/>
-      <c r="F48" s="266"/>
-      <c r="G48" s="266"/>
-      <c r="H48" s="266"/>
-      <c r="I48" s="266"/>
-      <c r="J48" s="266"/>
-      <c r="K48" s="266"/>
-      <c r="L48" s="289"/>
-      <c r="M48" s="272" t="s">
+      <c r="C48" s="265"/>
+      <c r="D48" s="265"/>
+      <c r="E48" s="265"/>
+      <c r="F48" s="265"/>
+      <c r="G48" s="265"/>
+      <c r="H48" s="265"/>
+      <c r="I48" s="265"/>
+      <c r="J48" s="265"/>
+      <c r="K48" s="265"/>
+      <c r="L48" s="288"/>
+      <c r="M48" s="271" t="s">
         <v>186</v>
       </c>
-      <c r="N48" s="273"/>
-      <c r="O48" s="273"/>
-      <c r="P48" s="273"/>
-      <c r="Q48" s="273"/>
-      <c r="R48" s="274"/>
+      <c r="N48" s="272"/>
+      <c r="O48" s="272"/>
+      <c r="P48" s="272"/>
+      <c r="Q48" s="272"/>
+      <c r="R48" s="273"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="290" t="s">
+      <c r="B49" s="289" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="290" t="s">
+      <c r="C49" s="289" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="256" t="s">
+      <c r="D49" s="255" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="257"/>
-      <c r="F49" s="257"/>
-      <c r="G49" s="258"/>
-      <c r="H49" s="291" t="s">
+      <c r="E49" s="256"/>
+      <c r="F49" s="256"/>
+      <c r="G49" s="257"/>
+      <c r="H49" s="290" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="292"/>
-      <c r="J49" s="292"/>
-      <c r="K49" s="293"/>
-      <c r="L49" s="294" t="s">
+      <c r="I49" s="291"/>
+      <c r="J49" s="291"/>
+      <c r="K49" s="292"/>
+      <c r="L49" s="293" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="275" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="275" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="277" t="str">
+      <c r="O49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="277" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="279" t="str">
+      <c r="Q49" s="278" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="279" t="str">
+      <c r="R49" s="278" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="271"/>
-      <c r="C50" s="271"/>
+      <c r="B50" s="270"/>
+      <c r="C50" s="270"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -16231,13 +16228,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="295"/>
-      <c r="M50" s="276"/>
-      <c r="N50" s="276"/>
-      <c r="O50" s="278"/>
-      <c r="P50" s="278"/>
-      <c r="Q50" s="280"/>
-      <c r="R50" s="280"/>
+      <c r="L50" s="294"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
+      <c r="O50" s="277"/>
+      <c r="P50" s="277"/>
+      <c r="Q50" s="279"/>
+      <c r="R50" s="279"/>
       <c r="T50" s="178" t="s">
         <v>216</v>
       </c>
@@ -17339,21 +17336,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="286" t="s">
+      <c r="B67" s="285" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="287"/>
-      <c r="D67" s="287"/>
-      <c r="E67" s="287"/>
-      <c r="F67" s="296"/>
-      <c r="G67" s="272" t="s">
+      <c r="C67" s="286"/>
+      <c r="D67" s="286"/>
+      <c r="E67" s="286"/>
+      <c r="F67" s="295"/>
+      <c r="G67" s="271" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="273"/>
-      <c r="I67" s="273"/>
-      <c r="J67" s="273"/>
-      <c r="K67" s="273"/>
-      <c r="L67" s="274"/>
+      <c r="H67" s="272"/>
+      <c r="I67" s="272"/>
+      <c r="J67" s="272"/>
+      <c r="K67" s="272"/>
+      <c r="L67" s="273"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -17667,17 +17664,17 @@
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="76" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="252" t="s">
+      <c r="B77" s="251" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="253"/>
-      <c r="D77" s="254"/>
+      <c r="C77" s="252"/>
+      <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="271" t="s">
+      <c r="B78" s="270" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="271" t="s">
+      <c r="C78" s="270" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -17685,8 +17682,8 @@
       </c>
     </row>
     <row r="79" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="261"/>
-      <c r="C79" s="261"/>
+      <c r="B79" s="260"/>
+      <c r="C79" s="260"/>
       <c r="D79" s="70" t="s">
         <v>168</v>
       </c>
@@ -18109,10 +18106,10 @@
       <c r="AM1" s="20"/>
     </row>
     <row r="3" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B3" s="239" t="s">
+      <c r="B3" s="238" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="239"/>
+      <c r="C3" s="238"/>
       <c r="D3" s="17" t="s">
         <v>29</v>
       </c>
@@ -20157,13 +20154,13 @@
       </c>
     </row>
     <row r="29" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B29" s="241" t="s">
+      <c r="B29" s="240" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="241"/>
-      <c r="D29" s="241"/>
-      <c r="E29" s="241"/>
-      <c r="F29" s="241"/>
+      <c r="C29" s="240"/>
+      <c r="D29" s="240"/>
+      <c r="E29" s="240"/>
+      <c r="F29" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -20726,10 +20723,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="246" t="s">
+      <c r="B44" s="245" t="s">
         <v>145</v>
       </c>
-      <c r="C44" s="247"/>
+      <c r="C44" s="246"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>10658901739</v>
@@ -20769,23 +20766,23 @@
       <c r="N46" s="97"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="248" t="s">
+      <c r="B47" s="247" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="248" t="s">
+      <c r="C47" s="247" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="249" t="s">
+      <c r="D47" s="248" t="s">
         <v>137</v>
       </c>
-      <c r="E47" s="250"/>
-      <c r="F47" s="251"/>
+      <c r="E47" s="249"/>
+      <c r="F47" s="250"/>
       <c r="G47" s="98" t="s">
         <v>138</v>
       </c>
       <c r="H47" s="98"/>
       <c r="I47" s="98"/>
-      <c r="J47" s="248" t="s">
+      <c r="J47" s="247" t="s">
         <v>139</v>
       </c>
       <c r="K47" s="99" t="s">
@@ -20793,13 +20790,13 @@
       </c>
       <c r="L47" s="99"/>
       <c r="M47" s="99"/>
-      <c r="N47" s="245" t="s">
+      <c r="N47" s="244" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="248"/>
-      <c r="C48" s="248"/>
+      <c r="B48" s="247"/>
+      <c r="C48" s="247"/>
       <c r="D48" s="100" t="s">
         <v>149</v>
       </c>
@@ -20818,7 +20815,7 @@
       <c r="I48" s="100" t="s">
         <v>130</v>
       </c>
-      <c r="J48" s="248"/>
+      <c r="J48" s="247"/>
       <c r="K48" s="101" t="s">
         <v>142</v>
       </c>
@@ -20828,7 +20825,7 @@
       <c r="M48" s="101" t="s">
         <v>145</v>
       </c>
-      <c r="N48" s="245"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -21505,15 +21502,15 @@
       </c>
     </row>
     <row r="63" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B63" s="242" t="s">
+      <c r="B63" s="241" t="s">
         <v>144</v>
       </c>
-      <c r="C63" s="243"/>
-      <c r="D63" s="243"/>
-      <c r="E63" s="243"/>
-      <c r="F63" s="243"/>
-      <c r="G63" s="243"/>
-      <c r="H63" s="244"/>
+      <c r="C63" s="242"/>
+      <c r="D63" s="242"/>
+      <c r="E63" s="242"/>
+      <c r="F63" s="242"/>
+      <c r="G63" s="242"/>
+      <c r="H63" s="243"/>
     </row>
     <row r="64" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B64" s="224" t="s">
@@ -22293,10 +22290,10 @@
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="246" t="s">
+      <c r="B44" s="245" t="s">
         <v>145</v>
       </c>
-      <c r="C44" s="247"/>
+      <c r="C44" s="246"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9776434571</v>
@@ -22336,23 +22333,23 @@
       <c r="N46" s="97"/>
     </row>
     <row r="47" spans="2:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="248" t="s">
+      <c r="B47" s="247" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="248" t="s">
+      <c r="C47" s="247" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="249" t="s">
+      <c r="D47" s="248" t="s">
         <v>137</v>
       </c>
-      <c r="E47" s="250"/>
-      <c r="F47" s="251"/>
+      <c r="E47" s="249"/>
+      <c r="F47" s="250"/>
       <c r="G47" s="98" t="s">
         <v>138</v>
       </c>
       <c r="H47" s="98"/>
       <c r="I47" s="98"/>
-      <c r="J47" s="248" t="s">
+      <c r="J47" s="247" t="s">
         <v>139</v>
       </c>
       <c r="K47" s="99" t="s">
@@ -22360,13 +22357,13 @@
       </c>
       <c r="L47" s="99"/>
       <c r="M47" s="99"/>
-      <c r="N47" s="245" t="s">
+      <c r="N47" s="244" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="48" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="248"/>
-      <c r="C48" s="248"/>
+      <c r="B48" s="247"/>
+      <c r="C48" s="247"/>
       <c r="D48" s="100" t="s">
         <v>149</v>
       </c>
@@ -22385,7 +22382,7 @@
       <c r="I48" s="100" t="s">
         <v>130</v>
       </c>
-      <c r="J48" s="248"/>
+      <c r="J48" s="247"/>
       <c r="K48" s="101" t="s">
         <v>142</v>
       </c>
@@ -22395,7 +22392,7 @@
       <c r="M48" s="101" t="s">
         <v>145</v>
       </c>
-      <c r="N48" s="245"/>
+      <c r="N48" s="244"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -23072,15 +23069,15 @@
       </c>
     </row>
     <row r="63" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B63" s="242" t="s">
+      <c r="B63" s="241" t="s">
         <v>144</v>
       </c>
-      <c r="C63" s="243"/>
-      <c r="D63" s="243"/>
-      <c r="E63" s="243"/>
-      <c r="F63" s="243"/>
-      <c r="G63" s="243"/>
-      <c r="H63" s="244"/>
+      <c r="C63" s="242"/>
+      <c r="D63" s="242"/>
+      <c r="E63" s="242"/>
+      <c r="F63" s="242"/>
+      <c r="G63" s="242"/>
+      <c r="H63" s="243"/>
     </row>
     <row r="64" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B64" s="224" t="s">
@@ -24012,10 +24009,10 @@
       <c r="N43" s="24"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="259" t="s">
+      <c r="B44" s="258" t="s">
         <v>145</v>
       </c>
-      <c r="C44" s="260"/>
+      <c r="C44" s="259"/>
       <c r="D44" s="47">
         <f>D41+D42+D43</f>
         <v>9764990416</v>
@@ -24080,23 +24077,23 @@
       <c r="Q46" s="48"/>
     </row>
     <row r="47" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="261" t="s">
+      <c r="B47" s="260" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="261" t="s">
+      <c r="C47" s="260" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="256" t="s">
+      <c r="D47" s="255" t="s">
         <v>137</v>
       </c>
-      <c r="E47" s="257"/>
-      <c r="F47" s="258"/>
+      <c r="E47" s="256"/>
+      <c r="F47" s="257"/>
       <c r="G47" s="69" t="s">
         <v>138</v>
       </c>
       <c r="H47" s="69"/>
       <c r="I47" s="69"/>
-      <c r="J47" s="261" t="s">
+      <c r="J47" s="260" t="s">
         <v>139</v>
       </c>
       <c r="K47" s="35" t="s">
@@ -24104,13 +24101,13 @@
       </c>
       <c r="L47" s="35"/>
       <c r="M47" s="35"/>
-      <c r="N47" s="255" t="s">
+      <c r="N47" s="254" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="48" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="261"/>
-      <c r="C48" s="261"/>
+      <c r="B48" s="260"/>
+      <c r="C48" s="260"/>
       <c r="D48" s="70" t="s">
         <v>149</v>
       </c>
@@ -24129,7 +24126,7 @@
       <c r="I48" s="70" t="s">
         <v>130</v>
       </c>
-      <c r="J48" s="261"/>
+      <c r="J48" s="260"/>
       <c r="K48" s="34" t="s">
         <v>142</v>
       </c>
@@ -24139,7 +24136,7 @@
       <c r="M48" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="N48" s="255"/>
+      <c r="N48" s="254"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
@@ -24831,15 +24828,15 @@
       <c r="N62" s="24"/>
     </row>
     <row r="63" spans="2:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="252" t="s">
+      <c r="B63" s="251" t="s">
         <v>144</v>
       </c>
-      <c r="C63" s="253"/>
-      <c r="D63" s="253"/>
-      <c r="E63" s="253"/>
-      <c r="F63" s="253"/>
-      <c r="G63" s="253"/>
-      <c r="H63" s="254"/>
+      <c r="C63" s="252"/>
+      <c r="D63" s="252"/>
+      <c r="E63" s="252"/>
+      <c r="F63" s="252"/>
+      <c r="G63" s="252"/>
+      <c r="H63" s="253"/>
       <c r="I63" s="24"/>
       <c r="J63" s="24"/>
       <c r="K63" s="24"/>
@@ -25789,11 +25786,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="262" t="s">
+      <c r="B41" s="261" t="s">
         <v>178</v>
       </c>
-      <c r="C41" s="263"/>
-      <c r="D41" s="264"/>
+      <c r="C41" s="262"/>
+      <c r="D41" s="263"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -26014,10 +26011,10 @@
       </c>
     </row>
     <row r="46" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="259" t="s">
+      <c r="B46" s="258" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="260"/>
+      <c r="C46" s="259"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>9680534906.7669907</v>
@@ -26064,59 +26061,59 @@
       </c>
     </row>
     <row r="48" spans="2:19" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="265" t="s">
+      <c r="B48" s="264" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="266"/>
-      <c r="D48" s="266"/>
-      <c r="E48" s="266"/>
-      <c r="F48" s="266"/>
-      <c r="G48" s="266"/>
-      <c r="H48" s="266"/>
-      <c r="I48" s="266"/>
-      <c r="J48" s="266"/>
-      <c r="K48" s="272" t="s">
+      <c r="C48" s="265"/>
+      <c r="D48" s="265"/>
+      <c r="E48" s="265"/>
+      <c r="F48" s="265"/>
+      <c r="G48" s="265"/>
+      <c r="H48" s="265"/>
+      <c r="I48" s="265"/>
+      <c r="J48" s="265"/>
+      <c r="K48" s="271" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="273"/>
-      <c r="M48" s="273"/>
-      <c r="N48" s="273"/>
-      <c r="O48" s="273"/>
-      <c r="P48" s="274"/>
+      <c r="L48" s="272"/>
+      <c r="M48" s="272"/>
+      <c r="N48" s="272"/>
+      <c r="O48" s="272"/>
+      <c r="P48" s="273"/>
       <c r="Q48"/>
       <c r="R48"/>
     </row>
     <row r="49" spans="2:18" s="139" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="270" t="s">
+      <c r="B49" s="269" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="270" t="s">
+      <c r="C49" s="269" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="267" t="s">
+      <c r="D49" s="266" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="268"/>
-      <c r="F49" s="269"/>
+      <c r="E49" s="267"/>
+      <c r="F49" s="268"/>
       <c r="G49" s="140" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="140"/>
       <c r="I49" s="140"/>
-      <c r="J49" s="267" t="s">
+      <c r="J49" s="266" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="275" t="str">
+      <c r="K49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="275" t="str">
+      <c r="L49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="277" t="str">
+      <c r="M49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
@@ -26131,7 +26128,7 @@
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="279" t="str">
+      <c r="P49" s="278" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -26140,8 +26137,8 @@
       <c r="R49"/>
     </row>
     <row r="50" spans="2:18" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="270"/>
-      <c r="C50" s="270"/>
+      <c r="B50" s="269"/>
+      <c r="C50" s="269"/>
       <c r="D50" s="141" t="s">
         <v>149</v>
       </c>
@@ -26160,13 +26157,13 @@
       <c r="I50" s="142" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="267"/>
-      <c r="K50" s="276"/>
-      <c r="L50" s="276"/>
-      <c r="M50" s="278"/>
+      <c r="J50" s="266"/>
+      <c r="K50" s="275"/>
+      <c r="L50" s="275"/>
+      <c r="M50" s="277"/>
       <c r="N50" s="188"/>
       <c r="O50" s="183"/>
-      <c r="P50" s="280"/>
+      <c r="P50" s="279"/>
       <c r="Q50"/>
       <c r="R50"/>
     </row>
@@ -27100,19 +27097,19 @@
     </row>
     <row r="67" spans="1:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="139"/>
-      <c r="B67" s="252" t="s">
+      <c r="B67" s="251" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="253"/>
-      <c r="D67" s="253"/>
-      <c r="E67" s="253"/>
-      <c r="F67" s="253"/>
-      <c r="G67" s="253"/>
-      <c r="H67" s="253"/>
-      <c r="I67" s="253"/>
-      <c r="J67" s="253"/>
-      <c r="K67" s="253"/>
-      <c r="L67" s="254"/>
+      <c r="C67" s="252"/>
+      <c r="D67" s="252"/>
+      <c r="E67" s="252"/>
+      <c r="F67" s="252"/>
+      <c r="G67" s="252"/>
+      <c r="H67" s="252"/>
+      <c r="I67" s="252"/>
+      <c r="J67" s="252"/>
+      <c r="K67" s="252"/>
+      <c r="L67" s="253"/>
       <c r="M67" s="139"/>
       <c r="N67" s="139"/>
       <c r="O67" s="139"/>
@@ -27497,20 +27494,20 @@
       <c r="I76"/>
     </row>
     <row r="77" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="252" t="s">
+      <c r="B77" s="251" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="253"/>
-      <c r="D77" s="254"/>
+      <c r="C77" s="252"/>
+      <c r="D77" s="253"/>
       <c r="G77"/>
       <c r="H77"/>
       <c r="I77"/>
     </row>
     <row r="78" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="271" t="s">
+      <c r="B78" s="270" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="271" t="s">
+      <c r="C78" s="270" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -27521,8 +27518,8 @@
       <c r="I78"/>
     </row>
     <row r="79" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="261"/>
-      <c r="C79" s="261"/>
+      <c r="B79" s="260"/>
+      <c r="C79" s="260"/>
       <c r="D79" s="70" t="s">
         <v>168</v>
       </c>
@@ -28486,11 +28483,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="281" t="s">
+      <c r="B41" s="280" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="282"/>
-      <c r="D41" s="283"/>
+      <c r="C41" s="281"/>
+      <c r="D41" s="282"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -28711,10 +28708,10 @@
       </c>
     </row>
     <row r="46" spans="2:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="259" t="s">
+      <c r="B46" s="258" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="260"/>
+      <c r="C46" s="259"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10097522879.624619</v>
@@ -28764,80 +28761,80 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="265" t="s">
+      <c r="B48" s="264" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="266"/>
-      <c r="D48" s="266"/>
-      <c r="E48" s="266"/>
-      <c r="F48" s="266"/>
-      <c r="G48" s="266"/>
-      <c r="H48" s="266"/>
-      <c r="I48" s="266"/>
-      <c r="J48" s="266"/>
-      <c r="K48" s="272" t="s">
+      <c r="C48" s="265"/>
+      <c r="D48" s="265"/>
+      <c r="E48" s="265"/>
+      <c r="F48" s="265"/>
+      <c r="G48" s="265"/>
+      <c r="H48" s="265"/>
+      <c r="I48" s="265"/>
+      <c r="J48" s="265"/>
+      <c r="K48" s="271" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="273"/>
-      <c r="M48" s="273"/>
-      <c r="N48" s="273"/>
-      <c r="O48" s="273"/>
-      <c r="P48" s="274"/>
+      <c r="L48" s="272"/>
+      <c r="M48" s="272"/>
+      <c r="N48" s="272"/>
+      <c r="O48" s="272"/>
+      <c r="P48" s="273"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="261" t="s">
+      <c r="B49" s="260" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="261" t="s">
+      <c r="C49" s="260" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="256" t="s">
+      <c r="D49" s="255" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="257"/>
-      <c r="F49" s="258"/>
+      <c r="E49" s="256"/>
+      <c r="F49" s="257"/>
       <c r="G49" s="112" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="112"/>
       <c r="I49" s="112"/>
-      <c r="J49" s="256" t="s">
+      <c r="J49" s="255" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="275" t="str">
+      <c r="K49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="275" t="str">
+      <c r="L49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="277" t="str">
+      <c r="M49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="277" t="str">
+      <c r="N49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="279" t="str">
+      <c r="O49" s="278" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="279" t="str">
+      <c r="P49" s="278" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="261"/>
-      <c r="C50" s="261"/>
+      <c r="B50" s="260"/>
+      <c r="C50" s="260"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -28856,13 +28853,13 @@
       <c r="I50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="256"/>
-      <c r="K50" s="276"/>
-      <c r="L50" s="276"/>
-      <c r="M50" s="278"/>
-      <c r="N50" s="278"/>
-      <c r="O50" s="280"/>
-      <c r="P50" s="280"/>
+      <c r="J50" s="255"/>
+      <c r="K50" s="275"/>
+      <c r="L50" s="275"/>
+      <c r="M50" s="277"/>
+      <c r="N50" s="277"/>
+      <c r="O50" s="279"/>
+      <c r="P50" s="279"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="167" t="s">
@@ -29768,19 +29765,19 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:16" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="252" t="s">
+      <c r="B67" s="251" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="253"/>
-      <c r="D67" s="253"/>
-      <c r="E67" s="253"/>
-      <c r="F67" s="253"/>
-      <c r="G67" s="253"/>
-      <c r="H67" s="253"/>
-      <c r="I67" s="253"/>
-      <c r="J67" s="253"/>
-      <c r="K67" s="253"/>
-      <c r="L67" s="254"/>
+      <c r="C67" s="252"/>
+      <c r="D67" s="252"/>
+      <c r="E67" s="252"/>
+      <c r="F67" s="252"/>
+      <c r="G67" s="252"/>
+      <c r="H67" s="252"/>
+      <c r="I67" s="252"/>
+      <c r="J67" s="252"/>
+      <c r="K67" s="252"/>
+      <c r="L67" s="253"/>
     </row>
     <row r="68" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -30092,17 +30089,17 @@
       </c>
     </row>
     <row r="77" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="252" t="s">
+      <c r="B77" s="251" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="253"/>
-      <c r="D77" s="254"/>
+      <c r="C77" s="252"/>
+      <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="271" t="s">
+      <c r="B78" s="270" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="271" t="s">
+      <c r="C78" s="270" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -30110,8 +30107,8 @@
       </c>
     </row>
     <row r="79" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="261"/>
-      <c r="C79" s="261"/>
+      <c r="B79" s="260"/>
+      <c r="C79" s="260"/>
       <c r="D79" s="70" t="s">
         <v>168</v>
       </c>
@@ -31071,11 +31068,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="262" t="s">
+      <c r="B41" s="261" t="s">
         <v>180</v>
       </c>
-      <c r="C41" s="263"/>
-      <c r="D41" s="264"/>
+      <c r="C41" s="262"/>
+      <c r="D41" s="263"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -31297,10 +31294,10 @@
       </c>
     </row>
     <row r="46" spans="2:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="259" t="s">
+      <c r="B46" s="258" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="260"/>
+      <c r="C46" s="259"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>10899555455</v>
@@ -31350,80 +31347,80 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="265" t="s">
+      <c r="B48" s="264" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="266"/>
-      <c r="D48" s="266"/>
-      <c r="E48" s="266"/>
-      <c r="F48" s="266"/>
-      <c r="G48" s="266"/>
-      <c r="H48" s="266"/>
-      <c r="I48" s="266"/>
-      <c r="J48" s="266"/>
-      <c r="K48" s="272" t="s">
+      <c r="C48" s="265"/>
+      <c r="D48" s="265"/>
+      <c r="E48" s="265"/>
+      <c r="F48" s="265"/>
+      <c r="G48" s="265"/>
+      <c r="H48" s="265"/>
+      <c r="I48" s="265"/>
+      <c r="J48" s="265"/>
+      <c r="K48" s="271" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="273"/>
-      <c r="M48" s="273"/>
-      <c r="N48" s="273"/>
-      <c r="O48" s="273"/>
-      <c r="P48" s="274"/>
+      <c r="L48" s="272"/>
+      <c r="M48" s="272"/>
+      <c r="N48" s="272"/>
+      <c r="O48" s="272"/>
+      <c r="P48" s="273"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="261" t="s">
+      <c r="B49" s="260" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="261" t="s">
+      <c r="C49" s="260" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="256" t="s">
+      <c r="D49" s="255" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="257"/>
-      <c r="F49" s="258"/>
+      <c r="E49" s="256"/>
+      <c r="F49" s="257"/>
       <c r="G49" s="112" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="112"/>
       <c r="I49" s="112"/>
-      <c r="J49" s="256" t="s">
+      <c r="J49" s="255" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="275" t="str">
+      <c r="K49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="275" t="str">
+      <c r="L49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="277" t="str">
+      <c r="M49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="277" t="str">
+      <c r="N49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="279" t="str">
+      <c r="O49" s="278" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="279" t="str">
+      <c r="P49" s="278" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="261"/>
-      <c r="C50" s="261"/>
+      <c r="B50" s="260"/>
+      <c r="C50" s="260"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -31442,13 +31439,13 @@
       <c r="I50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="256"/>
-      <c r="K50" s="276"/>
-      <c r="L50" s="276"/>
-      <c r="M50" s="278"/>
-      <c r="N50" s="278"/>
-      <c r="O50" s="280"/>
-      <c r="P50" s="280"/>
+      <c r="J50" s="255"/>
+      <c r="K50" s="275"/>
+      <c r="L50" s="275"/>
+      <c r="M50" s="277"/>
+      <c r="N50" s="277"/>
+      <c r="O50" s="279"/>
+      <c r="P50" s="279"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -32354,19 +32351,19 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:16" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="252" t="s">
+      <c r="B67" s="251" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="253"/>
-      <c r="D67" s="253"/>
-      <c r="E67" s="253"/>
-      <c r="F67" s="253"/>
-      <c r="G67" s="253"/>
-      <c r="H67" s="253"/>
-      <c r="I67" s="253"/>
-      <c r="J67" s="253"/>
-      <c r="K67" s="253"/>
-      <c r="L67" s="254"/>
+      <c r="C67" s="252"/>
+      <c r="D67" s="252"/>
+      <c r="E67" s="252"/>
+      <c r="F67" s="252"/>
+      <c r="G67" s="252"/>
+      <c r="H67" s="252"/>
+      <c r="I67" s="252"/>
+      <c r="J67" s="252"/>
+      <c r="K67" s="252"/>
+      <c r="L67" s="253"/>
     </row>
     <row r="68" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -32678,17 +32675,17 @@
       </c>
     </row>
     <row r="77" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="252" t="s">
+      <c r="B77" s="251" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="253"/>
-      <c r="D77" s="254"/>
+      <c r="C77" s="252"/>
+      <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="271" t="s">
+      <c r="B78" s="270" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="271" t="s">
+      <c r="C78" s="270" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -32696,8 +32693,8 @@
       </c>
     </row>
     <row r="79" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B79" s="261"/>
-      <c r="C79" s="261"/>
+      <c r="B79" s="260"/>
+      <c r="C79" s="260"/>
       <c r="D79" s="70" t="s">
         <v>168</v>
       </c>
@@ -33665,11 +33662,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" s="191" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="262" t="s">
+      <c r="B41" s="261" t="s">
         <v>189</v>
       </c>
-      <c r="C41" s="263"/>
-      <c r="D41" s="264"/>
+      <c r="C41" s="262"/>
+      <c r="D41" s="263"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -33891,10 +33888,10 @@
       </c>
     </row>
     <row r="46" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B46" s="259" t="s">
+      <c r="B46" s="258" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="260"/>
+      <c r="C46" s="259"/>
       <c r="D46" s="47">
         <f>D43+D44+D45</f>
         <v>11281613287.225662</v>
@@ -33944,80 +33941,80 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="265" t="s">
+      <c r="B48" s="264" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="266"/>
-      <c r="D48" s="266"/>
-      <c r="E48" s="266"/>
-      <c r="F48" s="266"/>
-      <c r="G48" s="266"/>
-      <c r="H48" s="266"/>
-      <c r="I48" s="266"/>
-      <c r="J48" s="266"/>
-      <c r="K48" s="272" t="s">
+      <c r="C48" s="265"/>
+      <c r="D48" s="265"/>
+      <c r="E48" s="265"/>
+      <c r="F48" s="265"/>
+      <c r="G48" s="265"/>
+      <c r="H48" s="265"/>
+      <c r="I48" s="265"/>
+      <c r="J48" s="265"/>
+      <c r="K48" s="271" t="s">
         <v>186</v>
       </c>
-      <c r="L48" s="273"/>
-      <c r="M48" s="273"/>
-      <c r="N48" s="273"/>
-      <c r="O48" s="273"/>
-      <c r="P48" s="274"/>
+      <c r="L48" s="272"/>
+      <c r="M48" s="272"/>
+      <c r="N48" s="272"/>
+      <c r="O48" s="272"/>
+      <c r="P48" s="273"/>
     </row>
     <row r="49" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="261" t="s">
+      <c r="B49" s="260" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="261" t="s">
+      <c r="C49" s="260" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="256" t="s">
+      <c r="D49" s="255" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="257"/>
-      <c r="F49" s="258"/>
+      <c r="E49" s="256"/>
+      <c r="F49" s="257"/>
       <c r="G49" s="112" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="112"/>
       <c r="I49" s="112"/>
-      <c r="J49" s="256" t="s">
+      <c r="J49" s="255" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="275" t="str">
+      <c r="K49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="275" t="str">
+      <c r="L49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="277" t="str">
+      <c r="M49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="277" t="str">
+      <c r="N49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="284" t="str">
+      <c r="O49" s="283" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="284" t="str">
+      <c r="P49" s="283" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="261"/>
-      <c r="C50" s="261"/>
+      <c r="B50" s="260"/>
+      <c r="C50" s="260"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -34036,13 +34033,13 @@
       <c r="I50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="256"/>
-      <c r="K50" s="276"/>
-      <c r="L50" s="276"/>
-      <c r="M50" s="278"/>
-      <c r="N50" s="278"/>
-      <c r="O50" s="285"/>
-      <c r="P50" s="285"/>
+      <c r="J50" s="255"/>
+      <c r="K50" s="275"/>
+      <c r="L50" s="275"/>
+      <c r="M50" s="277"/>
+      <c r="N50" s="277"/>
+      <c r="O50" s="284"/>
+      <c r="P50" s="284"/>
     </row>
     <row r="51" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -34948,19 +34945,19 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:16" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="252" t="s">
+      <c r="B67" s="251" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="253"/>
-      <c r="D67" s="253"/>
-      <c r="E67" s="253"/>
-      <c r="F67" s="253"/>
-      <c r="G67" s="253"/>
-      <c r="H67" s="253"/>
-      <c r="I67" s="253"/>
-      <c r="J67" s="253"/>
-      <c r="K67" s="253"/>
-      <c r="L67" s="254"/>
+      <c r="C67" s="252"/>
+      <c r="D67" s="252"/>
+      <c r="E67" s="252"/>
+      <c r="F67" s="252"/>
+      <c r="G67" s="252"/>
+      <c r="H67" s="252"/>
+      <c r="I67" s="252"/>
+      <c r="J67" s="252"/>
+      <c r="K67" s="252"/>
+      <c r="L67" s="253"/>
     </row>
     <row r="68" spans="2:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -35272,17 +35269,17 @@
       </c>
     </row>
     <row r="77" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="252" t="s">
+      <c r="B77" s="251" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="253"/>
-      <c r="D77" s="254"/>
+      <c r="C77" s="252"/>
+      <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="271" t="s">
+      <c r="B78" s="270" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="271" t="s">
+      <c r="C78" s="270" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -35290,8 +35287,8 @@
       </c>
     </row>
     <row r="79" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B79" s="261"/>
-      <c r="C79" s="261"/>
+      <c r="B79" s="260"/>
+      <c r="C79" s="260"/>
       <c r="D79" s="70" t="s">
         <v>168</v>
       </c>

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" tabRatio="500" firstSheet="1" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" tabRatio="500" firstSheet="4" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="HOW TO USE" sheetId="1" r:id="rId1"/>
@@ -717,9 +717,6 @@
     <t>DATA PENCAPAIAN — OKTOBER 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL — OKTOBER 2026</t>
-  </si>
-  <si>
     <t>DATA PENCAPAIAN — NOVEMBER 2026</t>
   </si>
   <si>
@@ -910,6 +907,9 @@
   </si>
   <si>
     <t>DATA PENCAPAIAN — GLOBAL —  30 SEPTEMBER 2026</t>
+  </si>
+  <si>
+    <t>DATA PENCAPAIAN — GLOBAL —  1 OKTOBER 2026</t>
   </si>
 </sst>
 </file>
@@ -2562,33 +2562,6 @@
     <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2619,6 +2592,33 @@
     <xf numFmtId="0" fontId="48" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2632,15 +2632,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2662,6 +2653,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3557,10 +3557,10 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -3599,7 +3599,7 @@
       <c r="E1" s="83"/>
       <c r="F1" s="83"/>
       <c r="G1" s="220" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H1" s="110"/>
       <c r="I1" s="110"/>
@@ -3611,7 +3611,7 @@
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G2" s="221" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H2" s="111"/>
       <c r="I2" s="111"/>
@@ -3636,7 +3636,7 @@
         <v>31</v>
       </c>
       <c r="G3" s="221" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H3" s="111"/>
       <c r="I3" s="111"/>
@@ -3646,7 +3646,7 @@
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G4" s="221" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H4" s="111"/>
       <c r="I4" s="111"/>
@@ -3656,7 +3656,7 @@
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G5" s="221" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H5" s="111"/>
       <c r="I5" s="111"/>
@@ -3683,7 +3683,7 @@
         <v>107</v>
       </c>
       <c r="O6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
@@ -3722,10 +3722,10 @@
         <v>110</v>
       </c>
       <c r="E8" s="80" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F8" s="80" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G8" s="80" t="s">
         <v>111</v>
@@ -3783,7 +3783,7 @@
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="72" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C11" s="15">
         <v>391754161.13883197</v>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="72" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C12" s="15">
         <v>3123423.4199979999</v>
@@ -3821,7 +3821,7 @@
         <v>352954956.67859</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G12" s="15">
         <v>386481596.69858801</v>
@@ -4017,16 +4017,16 @@
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C20" s="15">
         <v>186237371.06</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F20" s="15">
         <v>13081080.720000001</v>
@@ -4042,21 +4042,21 @@
         <v>155439124.9975</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B21" s="72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C21" s="15">
         <v>427491232.60000002</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F21" s="15">
         <v>16534323.880000001</v>
@@ -4072,7 +4072,7 @@
         <v>957241971.304317</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
@@ -4146,7 +4146,7 @@
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25" s="72" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C25" s="15">
         <v>160197012.810229</v>
@@ -4301,15 +4301,15 @@
       <c r="H39" s="111"/>
       <c r="I39" s="111"/>
       <c r="S39" s="172" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="261" t="s">
-        <v>219</v>
-      </c>
-      <c r="C40" s="262"/>
-      <c r="D40" s="263"/>
+      <c r="B40" s="271" t="s">
+        <v>218</v>
+      </c>
+      <c r="C40" s="272"/>
+      <c r="D40" s="273"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -4318,19 +4318,19 @@
         <v>1</v>
       </c>
       <c r="G40" s="192" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H40" s="198">
         <v>0.9</v>
       </c>
       <c r="I40" s="201" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J40" s="199">
         <v>0.95</v>
       </c>
       <c r="K40" s="194" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L40" s="200">
         <v>1</v>
@@ -4485,7 +4485,7 @@
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B44" s="109" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C44" s="41" t="s">
         <v>143</v>
@@ -4629,33 +4629,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="264" t="s">
-        <v>213</v>
-      </c>
-      <c r="C48" s="265"/>
-      <c r="D48" s="265"/>
-      <c r="E48" s="265"/>
-      <c r="F48" s="265"/>
-      <c r="G48" s="265"/>
-      <c r="H48" s="265"/>
-      <c r="I48" s="265"/>
-      <c r="J48" s="265"/>
-      <c r="K48" s="265"/>
-      <c r="L48" s="288"/>
-      <c r="M48" s="271" t="s">
-        <v>186</v>
-      </c>
-      <c r="N48" s="272"/>
-      <c r="O48" s="272"/>
-      <c r="P48" s="272"/>
-      <c r="Q48" s="272"/>
-      <c r="R48" s="273"/>
+      <c r="B48" s="274" t="s">
+        <v>212</v>
+      </c>
+      <c r="C48" s="275"/>
+      <c r="D48" s="275"/>
+      <c r="E48" s="275"/>
+      <c r="F48" s="275"/>
+      <c r="G48" s="275"/>
+      <c r="H48" s="275"/>
+      <c r="I48" s="275"/>
+      <c r="J48" s="275"/>
+      <c r="K48" s="275"/>
+      <c r="L48" s="285"/>
+      <c r="M48" s="262" t="s">
+        <v>185</v>
+      </c>
+      <c r="N48" s="263"/>
+      <c r="O48" s="263"/>
+      <c r="P48" s="263"/>
+      <c r="Q48" s="263"/>
+      <c r="R48" s="264"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="286" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="289" t="s">
+      <c r="C49" s="286" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="255" t="s">
@@ -4664,49 +4664,49 @@
       <c r="E49" s="256"/>
       <c r="F49" s="256"/>
       <c r="G49" s="257"/>
-      <c r="H49" s="290" t="s">
+      <c r="H49" s="287" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="291"/>
-      <c r="J49" s="291"/>
-      <c r="K49" s="292"/>
-      <c r="L49" s="293" t="s">
+      <c r="I49" s="288"/>
+      <c r="J49" s="288"/>
+      <c r="K49" s="289"/>
+      <c r="L49" s="290" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="274" t="str">
+      <c r="N49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="276" t="str">
+      <c r="O49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="276" t="str">
+      <c r="P49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="278" t="str">
+      <c r="Q49" s="269" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="278" t="str">
+      <c r="R49" s="269" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="270"/>
-      <c r="C50" s="270"/>
+      <c r="B50" s="261"/>
+      <c r="C50" s="261"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -4714,7 +4714,7 @@
         <v>150</v>
       </c>
       <c r="F50" s="70" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G50" s="70" t="s">
         <v>130</v>
@@ -4726,23 +4726,23 @@
         <v>150</v>
       </c>
       <c r="J50" s="113" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="294"/>
-      <c r="M50" s="275"/>
-      <c r="N50" s="275"/>
-      <c r="O50" s="277"/>
-      <c r="P50" s="277"/>
-      <c r="Q50" s="279"/>
-      <c r="R50" s="279"/>
+      <c r="L50" s="291"/>
+      <c r="M50" s="266"/>
+      <c r="N50" s="266"/>
+      <c r="O50" s="268"/>
+      <c r="P50" s="268"/>
+      <c r="Q50" s="270"/>
+      <c r="R50" s="270"/>
       <c r="T50" s="172" t="s">
+        <v>215</v>
+      </c>
+      <c r="U50" s="172" t="s">
         <v>216</v>
-      </c>
-      <c r="U50" s="172" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="51" spans="2:21" x14ac:dyDescent="0.25">
@@ -4816,7 +4816,7 @@
         <v>124</v>
       </c>
       <c r="U51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="52" spans="2:21" x14ac:dyDescent="0.25">
@@ -4895,10 +4895,10 @@
     </row>
     <row r="53" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B53" s="136" t="s">
+        <v>171</v>
+      </c>
+      <c r="C53" s="137" t="s">
         <v>172</v>
-      </c>
-      <c r="C53" s="137" t="s">
-        <v>173</v>
       </c>
       <c r="D53" s="138">
         <f>TARGETS!Y7</f>
@@ -4961,10 +4961,10 @@
         <v>0</v>
       </c>
       <c r="T53" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="U53" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="54" spans="2:21" x14ac:dyDescent="0.25">
@@ -5038,7 +5038,7 @@
         <v>115</v>
       </c>
       <c r="U54" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="55" spans="2:21" x14ac:dyDescent="0.25">
@@ -5046,7 +5046,7 @@
         <v>73</v>
       </c>
       <c r="C55" s="55" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D55" s="118">
         <f>TARGETS!Y9</f>
@@ -5109,10 +5109,10 @@
         <v>0</v>
       </c>
       <c r="T55" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="U55" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="2:21" x14ac:dyDescent="0.25">
@@ -5183,10 +5183,10 @@
         <v>0</v>
       </c>
       <c r="T56" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="U56" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="57" spans="2:21" x14ac:dyDescent="0.25">
@@ -5260,7 +5260,7 @@
         <v>120</v>
       </c>
       <c r="U57" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58" spans="2:21" x14ac:dyDescent="0.25">
@@ -5334,15 +5334,15 @@
         <v>125</v>
       </c>
       <c r="U58" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="59" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B59" s="136" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C59" s="137" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D59" s="138">
         <f>TARGETS!Y13</f>
@@ -5405,10 +5405,10 @@
         <v>0</v>
       </c>
       <c r="T59" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="U59" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="60" spans="2:21" x14ac:dyDescent="0.25">
@@ -5416,7 +5416,7 @@
         <v>80</v>
       </c>
       <c r="C60" s="56" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D60" s="119">
         <f>TARGETS!Y14</f>
@@ -5479,10 +5479,10 @@
         <v>0</v>
       </c>
       <c r="T60" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="U60" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="61" spans="2:21" x14ac:dyDescent="0.25">
@@ -5556,7 +5556,7 @@
         <v>126</v>
       </c>
       <c r="U61" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="62" spans="2:21" x14ac:dyDescent="0.25">
@@ -5630,7 +5630,7 @@
         <v>112</v>
       </c>
       <c r="U62" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63" spans="2:21" x14ac:dyDescent="0.25">
@@ -5704,7 +5704,7 @@
         <v>127</v>
       </c>
       <c r="U63" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="64" spans="2:21" x14ac:dyDescent="0.25">
@@ -5853,21 +5853,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="285" t="s">
+      <c r="B67" s="292" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="286"/>
-      <c r="D67" s="286"/>
-      <c r="E67" s="286"/>
-      <c r="F67" s="287"/>
-      <c r="G67" s="271" t="s">
-        <v>186</v>
-      </c>
-      <c r="H67" s="272"/>
-      <c r="I67" s="272"/>
-      <c r="J67" s="272"/>
-      <c r="K67" s="272"/>
-      <c r="L67" s="273"/>
+      <c r="C67" s="293"/>
+      <c r="D67" s="293"/>
+      <c r="E67" s="293"/>
+      <c r="F67" s="294"/>
+      <c r="G67" s="262" t="s">
+        <v>185</v>
+      </c>
+      <c r="H67" s="263"/>
+      <c r="I67" s="263"/>
+      <c r="J67" s="263"/>
+      <c r="K67" s="263"/>
+      <c r="L67" s="264"/>
     </row>
     <row r="68" spans="2:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -6180,16 +6180,16 @@
     </row>
     <row r="77" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="251" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C77" s="252"/>
       <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="270" t="s">
+      <c r="B78" s="261" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="270" t="s">
+      <c r="C78" s="261" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -6200,13 +6200,13 @@
       <c r="B79" s="260"/>
       <c r="C79" s="260"/>
       <c r="D79" s="70" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T79" s="172" t="s">
+        <v>215</v>
+      </c>
+      <c r="U79" s="172" t="s">
         <v>216</v>
-      </c>
-      <c r="U79" s="172" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="80" spans="2:21" x14ac:dyDescent="0.25">
@@ -6251,10 +6251,10 @@
     </row>
     <row r="82" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B82" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="C82" s="56" t="s">
         <v>172</v>
-      </c>
-      <c r="C82" s="56" t="s">
-        <v>173</v>
       </c>
       <c r="D82" s="132">
         <f t="shared" si="18"/>
@@ -6294,7 +6294,7 @@
         <v>73</v>
       </c>
       <c r="C84" s="56" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D84" s="132">
         <f t="shared" si="18"/>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="88" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B88" s="53" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C88" s="56" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D88" s="132">
         <f t="shared" si="18"/>
@@ -6394,7 +6394,7 @@
         <v>80</v>
       </c>
       <c r="C89" s="56" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D89" s="132">
         <f t="shared" si="18"/>
@@ -6501,6 +6501,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -6515,12 +6521,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -6571,7 +6571,7 @@
       <c r="E1" s="83"/>
       <c r="F1" s="83"/>
       <c r="G1" s="220" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H1" s="110"/>
       <c r="I1" s="110"/>
@@ -6583,7 +6583,7 @@
     </row>
     <row r="2" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G2" s="221" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H2" s="111"/>
       <c r="I2" s="111"/>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="C3" s="75">
         <f ca="1">IF($J$5&lt;&gt;"",$J$5,MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),9,1)),EOMONTH(DATE(YEAR(TODAY()),9,1),0),11)-MAX(0,$J$3-$J$4)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="76" t="s">
         <v>104</v>
@@ -6608,7 +6608,7 @@
         <v>30</v>
       </c>
       <c r="G3" s="221" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H3" s="111"/>
       <c r="I3" s="111"/>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="4" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G4" s="221" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H4" s="111"/>
       <c r="I4" s="111"/>
@@ -6628,7 +6628,7 @@
     </row>
     <row r="5" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G5" s="221" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H5" s="111"/>
       <c r="I5" s="111"/>
@@ -6652,7 +6652,7 @@
         <v>107</v>
       </c>
       <c r="O6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6690,10 +6690,10 @@
         <v>110</v>
       </c>
       <c r="E8" s="80" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F8" s="80" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G8" s="80" t="s">
         <v>111</v>
@@ -6748,7 +6748,7 @@
     </row>
     <row r="11" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="72" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C11" s="235">
         <v>5673423.4199980004</v>
@@ -6760,7 +6760,7 @@
         <v>294873875.35879999</v>
       </c>
       <c r="F11" s="235" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G11" s="235">
         <v>342865125.47879797</v>
@@ -6885,10 +6885,10 @@
         <v>331550587.10936803</v>
       </c>
       <c r="F16" s="235">
-        <v>1083995754.9499691</v>
+        <v>1085995754.9499691</v>
       </c>
       <c r="G16" s="235">
-        <v>1994124254.34692</v>
+        <v>1996124254.34692</v>
       </c>
       <c r="H16" s="111"/>
       <c r="I16" s="111"/>
@@ -6950,16 +6950,16 @@
     </row>
     <row r="19" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="235">
         <v>48019875.460000001</v>
       </c>
       <c r="D19" s="235" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E19" s="235" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F19" s="235">
         <v>9945945.6799999997</v>
@@ -6976,16 +6976,16 @@
     </row>
     <row r="20" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C20" s="235">
         <v>228406676.46000001</v>
       </c>
       <c r="D20" s="235" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E20" s="235" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F20" s="235">
         <v>13579549.18</v>
@@ -7001,7 +7001,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7031,12 +7031,12 @@
         <v>1048400865.610592</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="72" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C22" s="235">
         <v>203254368.21468899</v>
@@ -7105,7 +7105,7 @@
     </row>
     <row r="25" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="72" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C25" s="235">
         <v>350127609.35823399</v>
@@ -7196,7 +7196,7 @@
       <c r="B32" s="81" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="171">
+      <c r="C32" s="235">
         <v>473492851.69265503</v>
       </c>
       <c r="G32" s="111"/>
@@ -7260,15 +7260,15 @@
       <c r="H39" s="111"/>
       <c r="I39" s="111"/>
       <c r="S39" s="172" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="261" t="s">
-        <v>227</v>
-      </c>
-      <c r="C40" s="262"/>
-      <c r="D40" s="263"/>
+      <c r="B40" s="271" t="s">
+        <v>226</v>
+      </c>
+      <c r="C40" s="272"/>
+      <c r="D40" s="273"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -7277,19 +7277,19 @@
         <v>1</v>
       </c>
       <c r="G40" s="192" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H40" s="198">
         <v>0.95</v>
       </c>
       <c r="I40" s="201" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J40" s="199">
         <v>1</v>
       </c>
       <c r="K40" s="194" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L40" s="200">
         <v>1</v>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="H42" s="184">
         <f ca="1">IFERROR(G42/$C$3,0)</f>
-        <v>325374480.43365002</v>
+        <v>0</v>
       </c>
       <c r="I42" s="204">
         <f>D42*$J$40-E42</f>
@@ -7381,7 +7381,7 @@
       </c>
       <c r="J42" s="204">
         <f ca="1">IFERROR(I42/$C$3,0)</f>
-        <v>550963782.11861992</v>
+        <v>0</v>
       </c>
       <c r="K42" s="185">
         <f>D42*$L$40-E42</f>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="L42" s="185">
         <f ca="1">IFERROR(K42/$C$3,0)</f>
-        <v>550963782.11861992</v>
+        <v>0</v>
       </c>
       <c r="S42" s="173">
         <v>0.8</v>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="H43" s="184">
         <f ca="1">IFERROR(G43/$C$3,0)</f>
-        <v>230463071.32638597</v>
+        <v>0</v>
       </c>
       <c r="I43" s="204">
         <f>D43*$J$40-E43</f>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="J43" s="204">
         <f ca="1">IFERROR(I43/$C$3,0)</f>
-        <v>300531336.85215688</v>
+        <v>0</v>
       </c>
       <c r="K43" s="185">
         <f>D43*$L$40-E43</f>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="L43" s="185">
         <f ca="1">IFERROR(K43/$C$3,0)</f>
-        <v>300531336.85215688</v>
+        <v>0</v>
       </c>
       <c r="S43" s="173">
         <v>0.85</v>
@@ -7444,7 +7444,7 @@
     </row>
     <row r="44" spans="2:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="109" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C44" s="41" t="s">
         <v>143</v>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="H44" s="184">
         <f ca="1">IFERROR(G44/$C$3,0)</f>
-        <v>114069206.27038717</v>
+        <v>0</v>
       </c>
       <c r="I44" s="204">
         <f>IF(D44=0,0,D44*$J$40-E44)</f>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="J44" s="204">
         <f ca="1">IFERROR(I44/$C$3,0)</f>
-        <v>261309916.08682156</v>
+        <v>0</v>
       </c>
       <c r="K44" s="185">
         <f>IF(D44=0,0,D44*$L$40-E44)</f>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="L44" s="185">
         <f ca="1">IFERROR(K44/$C$3,0)</f>
-        <v>261309916.08682156</v>
+        <v>0</v>
       </c>
       <c r="S44" s="173">
         <v>0.9</v>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="H45" s="184">
         <f ca="1">IFERROR(G45/$C$3,0)</f>
-        <v>-149024634.17599225</v>
+        <v>0</v>
       </c>
       <c r="I45" s="204">
         <f>D45*$J$40-E45</f>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="J45" s="204">
         <f ca="1">IFERROR(I45/$C$3,0)</f>
-        <v>-62003357.580247402</v>
+        <v>0</v>
       </c>
       <c r="K45" s="185">
         <f>D45*$L$40-E45</f>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="L45" s="185">
         <f ca="1">IFERROR(K45/$C$3,0)</f>
-        <v>-62003357.580247402</v>
+        <v>0</v>
       </c>
       <c r="S45" s="173">
         <v>0.95</v>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="H46" s="181">
         <f ca="1">IFERROR(G46/$C$3,0)</f>
-        <v>520882123.85443091</v>
+        <v>0</v>
       </c>
       <c r="I46" s="186">
         <f>SUM(I42:I45)</f>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="J46" s="186">
         <f ca="1">IFERROR(I46/$C$3,0)</f>
-        <v>1050801677.477351</v>
+        <v>0</v>
       </c>
       <c r="K46" s="186">
         <f>SUM(K42:K45)</f>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="L46" s="186">
         <f ca="1">IFERROR(K46/$C$3,0)</f>
-        <v>1050801677.477351</v>
+        <v>0</v>
       </c>
       <c r="S46" s="173">
         <v>1</v>
@@ -7588,33 +7588,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="264" t="s">
-        <v>213</v>
-      </c>
-      <c r="C48" s="265"/>
-      <c r="D48" s="265"/>
-      <c r="E48" s="265"/>
-      <c r="F48" s="265"/>
-      <c r="G48" s="265"/>
-      <c r="H48" s="265"/>
-      <c r="I48" s="265"/>
-      <c r="J48" s="265"/>
-      <c r="K48" s="265"/>
-      <c r="L48" s="288"/>
-      <c r="M48" s="271" t="s">
-        <v>186</v>
-      </c>
-      <c r="N48" s="272"/>
-      <c r="O48" s="272"/>
-      <c r="P48" s="272"/>
-      <c r="Q48" s="272"/>
-      <c r="R48" s="273"/>
+      <c r="B48" s="274" t="s">
+        <v>212</v>
+      </c>
+      <c r="C48" s="275"/>
+      <c r="D48" s="275"/>
+      <c r="E48" s="275"/>
+      <c r="F48" s="275"/>
+      <c r="G48" s="275"/>
+      <c r="H48" s="275"/>
+      <c r="I48" s="275"/>
+      <c r="J48" s="275"/>
+      <c r="K48" s="275"/>
+      <c r="L48" s="285"/>
+      <c r="M48" s="262" t="s">
+        <v>185</v>
+      </c>
+      <c r="N48" s="263"/>
+      <c r="O48" s="263"/>
+      <c r="P48" s="263"/>
+      <c r="Q48" s="263"/>
+      <c r="R48" s="264"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="286" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="289" t="s">
+      <c r="C49" s="286" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="255" t="s">
@@ -7623,49 +7623,49 @@
       <c r="E49" s="256"/>
       <c r="F49" s="256"/>
       <c r="G49" s="257"/>
-      <c r="H49" s="290" t="s">
+      <c r="H49" s="287" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="291"/>
-      <c r="J49" s="291"/>
-      <c r="K49" s="292"/>
-      <c r="L49" s="293" t="s">
+      <c r="I49" s="288"/>
+      <c r="J49" s="288"/>
+      <c r="K49" s="289"/>
+      <c r="L49" s="290" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="274" t="str">
+      <c r="N49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="276" t="str">
+      <c r="O49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="276" t="str">
+      <c r="P49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="Q49" s="278" t="str">
+      <c r="Q49" s="269" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="278" t="str">
+      <c r="R49" s="269" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="270"/>
-      <c r="C50" s="270"/>
+      <c r="B50" s="261"/>
+      <c r="C50" s="261"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -7673,7 +7673,7 @@
         <v>150</v>
       </c>
       <c r="F50" s="70" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G50" s="70" t="s">
         <v>130</v>
@@ -7685,23 +7685,23 @@
         <v>150</v>
       </c>
       <c r="J50" s="113" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="294"/>
-      <c r="M50" s="275"/>
-      <c r="N50" s="275"/>
-      <c r="O50" s="277"/>
-      <c r="P50" s="277"/>
-      <c r="Q50" s="279"/>
-      <c r="R50" s="279"/>
+      <c r="L50" s="291"/>
+      <c r="M50" s="266"/>
+      <c r="N50" s="266"/>
+      <c r="O50" s="268"/>
+      <c r="P50" s="268"/>
+      <c r="Q50" s="270"/>
+      <c r="R50" s="270"/>
       <c r="T50" s="178" t="s">
+        <v>215</v>
+      </c>
+      <c r="U50" s="178" t="s">
         <v>216</v>
-      </c>
-      <c r="U50" s="178" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="51" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="N51" s="184">
         <f t="shared" ref="N51:N65" ca="1" si="7">IFERROR(M51/$C$3,0)</f>
-        <v>-17469463.741498113</v>
+        <v>0</v>
       </c>
       <c r="O51" s="180">
         <f t="shared" ref="O51:O64" si="8">G51*$J$40-K51</f>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="P51" s="180">
         <f t="shared" ref="P51:P65" ca="1" si="9">IFERROR(O51/$C$3,0)</f>
-        <v>8248912.2528426647</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="185">
         <f t="shared" ref="Q51:Q64" si="10">G51*$L$40-K51</f>
@@ -7769,13 +7769,13 @@
       </c>
       <c r="R51" s="185">
         <f t="shared" ref="R51:R65" ca="1" si="11">IFERROR(Q51/$C$3,0)</f>
-        <v>8248912.2528426647</v>
+        <v>0</v>
       </c>
       <c r="T51" t="s">
         <v>124</v>
       </c>
       <c r="U51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="52" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="N52" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>30053960.545837402</v>
+        <v>0</v>
       </c>
       <c r="O52" s="180">
         <f t="shared" si="8"/>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="P52" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>69330154.616844535</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="185">
         <f t="shared" si="10"/>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="R52" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>69330154.616844535</v>
+        <v>0</v>
       </c>
       <c r="T52" t="s">
         <v>70</v>
@@ -7854,10 +7854,10 @@
     </row>
     <row r="53" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="136" t="s">
+        <v>171</v>
+      </c>
+      <c r="C53" s="137" t="s">
         <v>172</v>
-      </c>
-      <c r="C53" s="137" t="s">
-        <v>173</v>
       </c>
       <c r="D53" s="138">
         <f>TARGETS!AB7</f>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="N53" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>201785574.34986019</v>
+        <v>0</v>
       </c>
       <c r="O53" s="180">
         <f t="shared" si="8"/>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="P53" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>214933229.60301074</v>
+        <v>0</v>
       </c>
       <c r="Q53" s="185">
         <f t="shared" si="10"/>
@@ -7917,13 +7917,13 @@
       </c>
       <c r="R53" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>214933229.60301074</v>
+        <v>0</v>
       </c>
       <c r="T53" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="U53" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="54" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="N54" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>-30940811.549464703</v>
+        <v>0</v>
       </c>
       <c r="O54" s="180">
         <f t="shared" si="8"/>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="P54" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>5392778.8898285627</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="185">
         <f t="shared" si="10"/>
@@ -7991,13 +7991,13 @@
       </c>
       <c r="R54" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>5392778.8898285627</v>
+        <v>0</v>
       </c>
       <c r="T54" t="s">
         <v>115</v>
       </c>
       <c r="U54" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="55" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8005,7 +8005,7 @@
         <v>73</v>
       </c>
       <c r="C55" s="55" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D55" s="118">
         <f>TARGETS!AB9</f>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="N55" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>167475824.11335337</v>
+        <v>0</v>
       </c>
       <c r="O55" s="180">
         <f t="shared" si="8"/>
@@ -8057,7 +8057,7 @@
       </c>
       <c r="P55" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>194335874.09188765</v>
+        <v>0</v>
       </c>
       <c r="Q55" s="185">
         <f t="shared" si="10"/>
@@ -8065,13 +8065,13 @@
       </c>
       <c r="R55" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>194335874.09188765</v>
+        <v>0</v>
       </c>
       <c r="T55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="U55" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8079,7 +8079,7 @@
         <v>75</v>
       </c>
       <c r="C56" s="56" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D56" s="119">
         <f>TARGETS!AB10</f>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="N56" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>114581506.16246545</v>
+        <v>0</v>
       </c>
       <c r="O56" s="180">
         <f t="shared" si="8"/>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="P56" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>143328805.58747637</v>
+        <v>0</v>
       </c>
       <c r="Q56" s="185">
         <f t="shared" si="10"/>
@@ -8139,13 +8139,13 @@
       </c>
       <c r="R56" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>143328805.58747637</v>
+        <v>0</v>
       </c>
       <c r="T56" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="U56" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="57" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="N57" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>143596362.85155833</v>
+        <v>0</v>
       </c>
       <c r="O57" s="180">
         <f t="shared" si="8"/>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="P57" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>199055566.1277957</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="185">
         <f t="shared" si="10"/>
@@ -8213,13 +8213,13 @@
       </c>
       <c r="R57" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>199055566.1277957</v>
+        <v>0</v>
       </c>
       <c r="T57" t="s">
         <v>120</v>
       </c>
       <c r="U57" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="N58" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>33380895.422910452</v>
+        <v>0</v>
       </c>
       <c r="O58" s="180">
         <f t="shared" si="8"/>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="P58" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>64109938.93176198</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="185">
         <f t="shared" si="10"/>
@@ -8287,21 +8287,21 @@
       </c>
       <c r="R58" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>64109938.93176198</v>
+        <v>0</v>
       </c>
       <c r="T58" t="s">
         <v>125</v>
       </c>
       <c r="U58" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="59" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="136" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C59" s="137" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D59" s="138">
         <f>TARGETS!AB13</f>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="N59" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>193247703.33759901</v>
+        <v>0</v>
       </c>
       <c r="O59" s="180">
         <f t="shared" si="8"/>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="P59" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>215440039.11642</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="185">
         <f t="shared" si="10"/>
@@ -8361,13 +8361,13 @@
       </c>
       <c r="R59" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>215440039.11642</v>
+        <v>0</v>
       </c>
       <c r="T59" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="U59" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="60" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8375,7 +8375,7 @@
         <v>80</v>
       </c>
       <c r="C60" s="56" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D60" s="119">
         <f>TARGETS!AB14</f>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="N60" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>5526049.1793714762</v>
+        <v>0</v>
       </c>
       <c r="O60" s="180">
         <f t="shared" si="8"/>
@@ -8427,7 +8427,7 @@
       </c>
       <c r="P60" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>34485359.589190722</v>
+        <v>0</v>
       </c>
       <c r="Q60" s="185">
         <f t="shared" si="10"/>
@@ -8435,13 +8435,13 @@
       </c>
       <c r="R60" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>34485359.589190722</v>
+        <v>0</v>
       </c>
       <c r="T60" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="U60" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="61" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="N61" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>-75171919.49645865</v>
+        <v>0</v>
       </c>
       <c r="O61" s="180">
         <f t="shared" si="8"/>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="P61" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>-39342279.41879952</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="185">
         <f t="shared" si="10"/>
@@ -8509,13 +8509,13 @@
       </c>
       <c r="R61" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>-39342279.41879952</v>
+        <v>0</v>
       </c>
       <c r="T61" t="s">
         <v>126</v>
       </c>
       <c r="U61" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="62" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="N62" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>62458503.55635345</v>
+        <v>0</v>
       </c>
       <c r="O62" s="180">
         <f t="shared" si="8"/>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P62" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>86309666.434393525</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="185">
         <f t="shared" si="10"/>
@@ -8583,13 +8583,13 @@
       </c>
       <c r="R62" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>86309666.434393525</v>
+        <v>0</v>
       </c>
       <c r="T62" t="s">
         <v>112</v>
       </c>
       <c r="U62" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="N63" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>-195327097.7814461</v>
+        <v>0</v>
       </c>
       <c r="O63" s="180">
         <f t="shared" si="8"/>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="P63" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>-146378397.91675568</v>
+        <v>0</v>
       </c>
       <c r="Q63" s="185">
         <f t="shared" si="10"/>
@@ -8657,13 +8657,13 @@
       </c>
       <c r="R63" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>-146378397.91675568</v>
+        <v>0</v>
       </c>
       <c r="T63" t="s">
         <v>127</v>
       </c>
       <c r="U63" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="64" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="N64" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>36709671.079981267</v>
+        <v>0</v>
       </c>
       <c r="O64" s="180">
         <f t="shared" si="8"/>
@@ -8723,7 +8723,7 @@
       </c>
       <c r="P64" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>63555387.151700854</v>
+        <v>0</v>
       </c>
       <c r="Q64" s="185">
         <f t="shared" si="10"/>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="R64" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>63555387.151700854</v>
+        <v>0</v>
       </c>
       <c r="T64" t="s">
         <v>122</v>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="N65" s="181">
         <f t="shared" ca="1" si="7"/>
-        <v>669906758.03042293</v>
+        <v>0</v>
       </c>
       <c r="O65" s="181">
         <f>SUM(O51:O64)</f>
@@ -8795,7 +8795,7 @@
       </c>
       <c r="P65" s="181">
         <f t="shared" ca="1" si="9"/>
-        <v>1112805035.0575981</v>
+        <v>0</v>
       </c>
       <c r="Q65" s="186">
         <f>SUM(Q51:Q64)</f>
@@ -8803,7 +8803,7 @@
       </c>
       <c r="R65" s="186">
         <f t="shared" ca="1" si="11"/>
-        <v>1112805035.0575981</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8812,21 +8812,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="285" t="s">
+      <c r="B67" s="292" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="286"/>
-      <c r="D67" s="286"/>
-      <c r="E67" s="286"/>
+      <c r="C67" s="293"/>
+      <c r="D67" s="293"/>
+      <c r="E67" s="293"/>
       <c r="F67" s="295"/>
-      <c r="G67" s="271" t="s">
-        <v>186</v>
-      </c>
-      <c r="H67" s="272"/>
-      <c r="I67" s="272"/>
-      <c r="J67" s="272"/>
-      <c r="K67" s="272"/>
-      <c r="L67" s="273"/>
+      <c r="G67" s="262" t="s">
+        <v>185</v>
+      </c>
+      <c r="H67" s="263"/>
+      <c r="I67" s="263"/>
+      <c r="J67" s="263"/>
+      <c r="K67" s="263"/>
+      <c r="L67" s="264"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="H69" s="184">
         <f t="shared" ref="H69:H74" ca="1" si="14">IFERROR(G69/$C$3,0)</f>
-        <v>-37090544.052177608</v>
+        <v>0</v>
       </c>
       <c r="I69" s="204">
         <f>D69*$J$40-E69</f>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="J69" s="204">
         <f t="shared" ref="J69:J74" ca="1" si="15">IFERROR(I69/$C$3,0)</f>
-        <v>-24277668.886929363</v>
+        <v>0</v>
       </c>
       <c r="K69" s="185">
         <f>D69*$L$40-E69</f>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="L69" s="185">
         <f t="shared" ref="L69:L74" ca="1" si="16">IFERROR(K69/$C$3,0)</f>
-        <v>-24277668.886929363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="H70" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>-93912360.002938688</v>
+        <v>0</v>
       </c>
       <c r="I70" s="204">
         <f>D70*$J$40-E70</f>
@@ -8952,7 +8952,7 @@
       </c>
       <c r="J70" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>-73934439.387690425</v>
+        <v>0</v>
       </c>
       <c r="K70" s="185">
         <f>D70*$L$40-E70</f>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="L70" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>-73934439.387690425</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.25">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="H71" s="184">
         <f t="shared" ca="1" si="14"/>
-        <v>-18021730.120875716</v>
+        <v>0</v>
       </c>
       <c r="I71" s="204">
         <f>D71*$J$40-E71</f>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="J71" s="204">
         <f t="shared" ca="1" si="15"/>
-        <v>36208750.694372535</v>
+        <v>0</v>
       </c>
       <c r="K71" s="185">
         <f>D71*$L$40-E71</f>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="L71" s="185">
         <f t="shared" ca="1" si="16"/>
-        <v>36208750.694372535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="2:21" hidden="1" x14ac:dyDescent="0.25">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="H74" s="181">
         <f t="shared" ca="1" si="14"/>
-        <v>-149024634.17599201</v>
+        <v>0</v>
       </c>
       <c r="I74" s="186">
         <f>SUM(I69:I73)</f>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="J74" s="186">
         <f t="shared" ca="1" si="15"/>
-        <v>-62003357.580247253</v>
+        <v>0</v>
       </c>
       <c r="K74" s="186">
         <f>SUM(K69:K73)</f>
@@ -9134,23 +9134,23 @@
       </c>
       <c r="L74" s="186">
         <f t="shared" ca="1" si="16"/>
-        <v>-62003357.580247253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="76" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="251" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C77" s="252"/>
       <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="270" t="s">
+      <c r="B78" s="261" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="270" t="s">
+      <c r="C78" s="261" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -9161,13 +9161,13 @@
       <c r="B79" s="260"/>
       <c r="C79" s="260"/>
       <c r="D79" s="70" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T79" s="178" t="s">
+        <v>215</v>
+      </c>
+      <c r="U79" s="178" t="s">
         <v>216</v>
-      </c>
-      <c r="U79" s="178" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="80" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -9212,10 +9212,10 @@
     </row>
     <row r="82" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="C82" s="56" t="s">
         <v>172</v>
-      </c>
-      <c r="C82" s="56" t="s">
-        <v>173</v>
       </c>
       <c r="D82" s="132">
         <f t="shared" si="17"/>
@@ -9255,7 +9255,7 @@
         <v>73</v>
       </c>
       <c r="C84" s="56" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D84" s="132">
         <f t="shared" si="17"/>
@@ -9275,7 +9275,7 @@
         <v>75</v>
       </c>
       <c r="C85" s="55" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D85" s="131">
         <f t="shared" si="17"/>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="D86" s="132">
         <f t="shared" si="17"/>
-        <v>1083995754.9499691</v>
+        <v>1085995754.9499691</v>
       </c>
       <c r="T86" t="str">
         <f t="shared" si="18"/>
@@ -9332,10 +9332,10 @@
     </row>
     <row r="88" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="53" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C88" s="56" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D88" s="132">
         <f t="shared" si="17"/>
@@ -9457,12 +9457,20 @@
       <c r="C94" s="58"/>
       <c r="D94" s="120">
         <f>SUM(D80:D93)</f>
-        <v>3598934224.7465181</v>
+        <v>3600934224.7465181</v>
       </c>
     </row>
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B48:L48"/>
+    <mergeCell ref="G67:L67"/>
     <mergeCell ref="M48:R48"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="C49:C50"/>
@@ -9475,14 +9483,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B48:L48"/>
-    <mergeCell ref="G67:L67"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -9525,7 +9525,7 @@
       <c r="E1" s="83"/>
       <c r="F1" s="83"/>
       <c r="G1" s="220" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H1" s="110"/>
       <c r="I1" s="110"/>
@@ -9537,7 +9537,7 @@
     </row>
     <row r="2" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G2" s="221" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H2" s="111"/>
       <c r="I2" s="111"/>
@@ -9562,7 +9562,7 @@
         <v>31</v>
       </c>
       <c r="G3" s="221" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H3" s="111"/>
       <c r="I3" s="111"/>
@@ -9572,7 +9572,7 @@
     </row>
     <row r="4" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G4" s="221" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H4" s="111"/>
       <c r="I4" s="111"/>
@@ -9582,7 +9582,7 @@
     </row>
     <row r="5" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G5" s="221" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H5" s="111"/>
       <c r="I5" s="111"/>
@@ -9607,7 +9607,7 @@
         <v>107</v>
       </c>
       <c r="O6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9646,10 +9646,10 @@
         <v>110</v>
       </c>
       <c r="E8" s="80" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F8" s="80" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G8" s="80" t="s">
         <v>111</v>
@@ -9683,13 +9683,20 @@
       <c r="B10" s="72" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15">
-        <f t="shared" ref="G10:G26" si="0">SUM(C10:F10)</f>
-        <v>0</v>
+      <c r="C10" s="235">
+        <v>5099399.1523909997</v>
+      </c>
+      <c r="D10" s="235">
+        <v>3553070.28</v>
+      </c>
+      <c r="E10" s="235">
+        <v>14595495.476</v>
+      </c>
+      <c r="F10" s="235">
+        <v>9891892.1299849991</v>
+      </c>
+      <c r="G10" s="235">
+        <v>33139857.038376</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="111"/>
@@ -9700,14 +9707,22 @@
     </row>
     <row r="11" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="72" t="s">
-        <v>220</v>
-      </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
+        <v>219</v>
+      </c>
+      <c r="C11" s="15">
+        <v>0</v>
+      </c>
+      <c r="D11" s="15">
+        <v>0</v>
+      </c>
+      <c r="E11" s="15">
+        <v>0</v>
+      </c>
+      <c r="F11" s="15">
+        <v>0</v>
+      </c>
       <c r="G11" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G10:G26" si="0">SUM(C11:F11)</f>
         <v>0</v>
       </c>
       <c r="H11" s="111"/>
@@ -9719,12 +9734,20 @@
     </row>
     <row r="12" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="72" t="s">
-        <v>182</v>
-      </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
+        <v>181</v>
+      </c>
+      <c r="C12" s="15">
+        <v>0</v>
+      </c>
+      <c r="D12" s="15">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15">
+        <v>0</v>
+      </c>
+      <c r="F12" s="15">
+        <v>0</v>
+      </c>
       <c r="G12" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9740,13 +9763,20 @@
       <c r="B13" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C13" s="235">
+        <v>9534933.6398440003</v>
+      </c>
+      <c r="D13" s="235">
+        <v>3657558.3389989999</v>
+      </c>
+      <c r="E13" s="235">
+        <v>4169594.6</v>
+      </c>
+      <c r="F13" s="235">
+        <v>1621621.7</v>
+      </c>
+      <c r="G13" s="235">
+        <v>18983708.278843001</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="111"/>
@@ -9759,13 +9789,20 @@
       <c r="B14" s="72" t="s">
         <v>114</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C14" s="235">
+        <v>0</v>
+      </c>
+      <c r="D14" s="235">
+        <v>0</v>
+      </c>
+      <c r="E14" s="235">
+        <v>5869369.3499999996</v>
+      </c>
+      <c r="F14" s="235">
+        <v>2756756.89</v>
+      </c>
+      <c r="G14" s="235">
+        <v>8626126.2400000002</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="111"/>
@@ -9778,13 +9815,20 @@
       <c r="B15" s="81" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C15" s="235">
+        <v>17804909.979979999</v>
+      </c>
+      <c r="D15" s="235">
+        <v>1535108.1499989999</v>
+      </c>
+      <c r="E15" s="235">
+        <v>5624603.5700000003</v>
+      </c>
+      <c r="F15" s="235">
+        <v>18467747.989999998</v>
+      </c>
+      <c r="G15" s="235">
+        <v>43432369.689979002</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="111"/>
@@ -9797,13 +9841,20 @@
       <c r="B16" s="72" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C16" s="235">
+        <v>21599788.68998</v>
+      </c>
+      <c r="D16" s="235">
+        <v>167891.88999900001</v>
+      </c>
+      <c r="E16" s="235">
+        <v>0</v>
+      </c>
+      <c r="F16" s="235">
+        <v>972973.02</v>
+      </c>
+      <c r="G16" s="235">
+        <v>22740653.599978998</v>
       </c>
       <c r="H16" s="111"/>
       <c r="I16" s="111"/>
@@ -9816,13 +9867,20 @@
       <c r="B17" s="72" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C17" s="235">
+        <v>24228400.236997999</v>
+      </c>
+      <c r="D17" s="235">
+        <v>2594594.52</v>
+      </c>
+      <c r="E17" s="235">
+        <v>36828739.059940003</v>
+      </c>
+      <c r="F17" s="235">
+        <v>142163962.83000001</v>
+      </c>
+      <c r="G17" s="235">
+        <v>205815696.646938</v>
       </c>
       <c r="H17" s="111"/>
       <c r="I17" s="111"/>
@@ -9835,13 +9893,20 @@
       <c r="B18" s="72" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C18" s="235">
+        <v>2741711.73</v>
+      </c>
+      <c r="D18" s="235">
+        <v>0</v>
+      </c>
+      <c r="E18" s="235">
+        <v>698198.49994999997</v>
+      </c>
+      <c r="F18" s="235">
+        <v>0</v>
+      </c>
+      <c r="G18" s="235">
+        <v>3439910.2299500001</v>
       </c>
       <c r="H18" s="111"/>
       <c r="I18" s="111"/>
@@ -9854,13 +9919,20 @@
       <c r="B19" s="72" t="s">
         <v>123</v>
       </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C19" s="235">
+        <v>2332400</v>
+      </c>
+      <c r="D19" s="235">
+        <v>2838292.3307739999</v>
+      </c>
+      <c r="E19" s="235">
+        <v>3712540.5</v>
+      </c>
+      <c r="F19" s="235">
+        <v>14486486.800000001</v>
+      </c>
+      <c r="G19" s="235">
+        <v>23369719.630773999</v>
       </c>
       <c r="H19" s="111"/>
       <c r="I19" s="111"/>
@@ -9871,12 +9943,20 @@
     </row>
     <row r="20" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>169</v>
-      </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
+        <v>168</v>
+      </c>
+      <c r="C20" s="15">
+        <v>0</v>
+      </c>
+      <c r="D20" s="15">
+        <v>0</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
+      </c>
+      <c r="F20" s="15">
+        <v>0</v>
+      </c>
       <c r="G20" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9889,17 +9969,25 @@
         <v>0</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="72" t="s">
-        <v>170</v>
-      </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
+        <v>169</v>
+      </c>
+      <c r="C21" s="15">
+        <v>0</v>
+      </c>
+      <c r="D21" s="15">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15">
+        <v>0</v>
+      </c>
+      <c r="F21" s="15">
+        <v>0</v>
+      </c>
       <c r="G21" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9909,23 +9997,30 @@
       <c r="J21" s="111"/>
       <c r="M21" s="14">
         <f>SUM(C33,C34)+M20</f>
-        <v>0</v>
+        <v>23778171.829761002</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="72" t="s">
         <v>124</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C22" s="235">
+        <v>12273347.239848999</v>
+      </c>
+      <c r="D22" s="235">
+        <v>3138986.5099889999</v>
+      </c>
+      <c r="E22" s="235">
+        <v>3614909.9</v>
+      </c>
+      <c r="F22" s="235">
+        <v>972973.02</v>
+      </c>
+      <c r="G22" s="235">
+        <v>20000216.669838</v>
       </c>
       <c r="H22" s="111"/>
       <c r="I22" s="111"/>
@@ -9935,13 +10030,20 @@
       <c r="B23" s="72" t="s">
         <v>125</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C23" s="235">
+        <v>7886135.4645919995</v>
+      </c>
+      <c r="D23" s="235">
+        <v>4799378.3999950001</v>
+      </c>
+      <c r="E23" s="235">
+        <v>9972973.1899980009</v>
+      </c>
+      <c r="F23" s="235">
+        <v>7967567.5999999996</v>
+      </c>
+      <c r="G23" s="235">
+        <v>30626054.654585</v>
       </c>
       <c r="H23" s="111"/>
       <c r="I23" s="111"/>
@@ -9951,13 +10053,20 @@
       <c r="B24" s="72" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C24" s="235">
+        <v>17326640.025509998</v>
+      </c>
+      <c r="D24" s="235">
+        <v>3598450.4599979999</v>
+      </c>
+      <c r="E24" s="235">
+        <v>9749459.7300000004</v>
+      </c>
+      <c r="F24" s="235">
+        <v>29344144.359993</v>
+      </c>
+      <c r="G24" s="235">
+        <v>60018694.575501002</v>
       </c>
       <c r="H24" s="111"/>
       <c r="I24" s="111"/>
@@ -9965,15 +10074,22 @@
     </row>
     <row r="25" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="72" t="s">
-        <v>225</v>
-      </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>224</v>
+      </c>
+      <c r="C25" s="235">
+        <v>9041895.5201660004</v>
+      </c>
+      <c r="D25" s="235">
+        <v>1793939.1151990001</v>
+      </c>
+      <c r="E25" s="235">
+        <v>6225856.0099980002</v>
+      </c>
+      <c r="F25" s="235">
+        <v>29513694.069988001</v>
+      </c>
+      <c r="G25" s="235">
+        <v>46575384.715351</v>
       </c>
       <c r="H25" s="111"/>
       <c r="I25" s="111"/>
@@ -9983,13 +10099,20 @@
       <c r="B26" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C26" s="235">
+        <v>26521190.528918002</v>
+      </c>
+      <c r="D26" s="235">
+        <v>297297.3</v>
+      </c>
+      <c r="E26" s="235">
+        <v>15905401.999435</v>
+      </c>
+      <c r="F26" s="235">
+        <v>0</v>
+      </c>
+      <c r="G26" s="235">
+        <v>42723889.828353003</v>
       </c>
       <c r="H26" s="111"/>
       <c r="I26" s="111"/>
@@ -10031,8 +10154,8 @@
       <c r="B31" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="C31" s="15">
-        <v>0</v>
+      <c r="C31" s="171">
+        <v>4400648.7999700001</v>
       </c>
       <c r="G31" s="111"/>
       <c r="H31" s="111"/>
@@ -10042,8 +10165,8 @@
       <c r="B32" s="81" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="15">
-        <v>0</v>
+      <c r="C32" s="235">
+        <v>9101351.5199759994</v>
       </c>
       <c r="G32" s="111"/>
       <c r="H32" s="111"/>
@@ -10053,8 +10176,8 @@
       <c r="B33" s="81" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="15">
-        <v>0</v>
+      <c r="C33" s="235">
+        <v>5173846.8699930003</v>
       </c>
       <c r="G33" s="111"/>
       <c r="H33" s="111"/>
@@ -10064,8 +10187,8 @@
       <c r="B34" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="15">
-        <v>0</v>
+      <c r="C34" s="235">
+        <v>18604324.959768001</v>
       </c>
       <c r="G34" s="111"/>
       <c r="H34" s="111"/>
@@ -10106,36 +10229,36 @@
       <c r="H39" s="111"/>
       <c r="I39" s="111"/>
       <c r="S39" s="172" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="261" t="s">
-        <v>163</v>
-      </c>
-      <c r="C40" s="262"/>
-      <c r="D40" s="263"/>
+      <c r="B40" s="271" t="s">
+        <v>227</v>
+      </c>
+      <c r="C40" s="272"/>
+      <c r="D40" s="273"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
       <c r="F40" s="174">
         <f ca="1">IF(MONTH(TODAY())=10,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;10,1,0))</f>
-        <v>0</v>
+        <v>3.2258064516129031E-2</v>
       </c>
       <c r="G40" s="192" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H40" s="198">
         <v>0.9</v>
       </c>
       <c r="I40" s="201" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J40" s="199">
         <v>0.95</v>
       </c>
       <c r="K40" s="194" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L40" s="200">
         <v>1</v>
@@ -10203,39 +10326,39 @@
       </c>
       <c r="D42" s="45">
         <f>SUM(TARGETS!AE5:AE18)</f>
-        <v>0</v>
+        <v>4464586688.6595287</v>
       </c>
       <c r="E42" s="46">
         <f>H65</f>
-        <v>0</v>
+        <v>134790963.51824799</v>
       </c>
       <c r="F42" s="176">
         <f>IFERROR(E42/D42,0)</f>
-        <v>0</v>
+        <v>3.0191140393942793E-2</v>
       </c>
       <c r="G42" s="184">
         <f>D42*$H$40-E42</f>
-        <v>0</v>
+        <v>3883337056.2753277</v>
       </c>
       <c r="H42" s="184">
         <f ca="1">IFERROR(G42/$C$3,0)</f>
-        <v>0</v>
+        <v>143827298.3805677</v>
       </c>
       <c r="I42" s="204">
         <f>D42*$J$40-E42</f>
-        <v>0</v>
+        <v>4106566390.7083039</v>
       </c>
       <c r="J42" s="204">
         <f ca="1">IFERROR(I42/$C$3,0)</f>
-        <v>0</v>
+        <v>152095051.50771496</v>
       </c>
       <c r="K42" s="185">
         <f>D42*$L$40-E42</f>
-        <v>0</v>
+        <v>4329795725.1412811</v>
       </c>
       <c r="L42" s="185">
         <f ca="1">IFERROR(K42/$C$3,0)</f>
-        <v>0</v>
+        <v>160362804.63486227</v>
       </c>
       <c r="S42" s="173">
         <v>0.8</v>
@@ -10250,39 +10373,39 @@
       </c>
       <c r="D43" s="45">
         <f>SUM(TARGETS!AF5:AF18)</f>
-        <v>0</v>
+        <v>1279908063.1092303</v>
       </c>
       <c r="E43" s="46">
         <f>I65</f>
-        <v>0</v>
+        <v>27806675.404953003</v>
       </c>
       <c r="F43" s="176">
         <f>IFERROR(E43/D43,0)</f>
-        <v>0</v>
+        <v>2.1725525611115647E-2</v>
       </c>
       <c r="G43" s="184">
         <f>D43*$H$40-E43</f>
-        <v>0</v>
+        <v>1124110581.3933542</v>
       </c>
       <c r="H43" s="184">
         <f ca="1">IFERROR(G43/$C$3,0)</f>
-        <v>0</v>
+        <v>41633725.236790895</v>
       </c>
       <c r="I43" s="204">
         <f>D43*$J$40-E43</f>
-        <v>0</v>
+        <v>1188105984.5488157</v>
       </c>
       <c r="J43" s="204">
         <f ca="1">IFERROR(I43/$C$3,0)</f>
-        <v>0</v>
+        <v>44003925.353659838</v>
       </c>
       <c r="K43" s="185">
         <f>D43*$L$40-E43</f>
-        <v>0</v>
+        <v>1252101387.7042773</v>
       </c>
       <c r="L43" s="185">
         <f ca="1">IFERROR(K43/$C$3,0)</f>
-        <v>0</v>
+        <v>46374125.470528789</v>
       </c>
       <c r="S43" s="173">
         <v>0.85</v>
@@ -10290,46 +10413,46 @@
     </row>
     <row r="44" spans="2:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="109" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C44" s="41" t="s">
         <v>143</v>
       </c>
       <c r="D44" s="45">
         <f>SUM(TARGETS!AG5:AG18)</f>
-        <v>0</v>
+        <v>2914007482.4702153</v>
       </c>
       <c r="E44" s="46">
         <f>J65</f>
-        <v>0</v>
+        <v>116967141.88532101</v>
       </c>
       <c r="F44" s="176">
         <f>IFERROR(E44/D44,0)</f>
-        <v>0</v>
+        <v>4.0139616177707102E-2</v>
       </c>
       <c r="G44" s="184">
         <f>IF(D44=0,0,D44*$H$40-E44)</f>
-        <v>0</v>
+        <v>2505639592.3378725</v>
       </c>
       <c r="H44" s="184">
         <f ca="1">IFERROR(G44/$C$3,0)</f>
-        <v>0</v>
+        <v>92801466.38288416</v>
       </c>
       <c r="I44" s="204">
         <f>IF(D44=0,0,D44*$J$40-E44)</f>
-        <v>0</v>
+        <v>2651339966.4613833</v>
       </c>
       <c r="J44" s="204">
         <f ca="1">IFERROR(I44/$C$3,0)</f>
-        <v>0</v>
+        <v>98197776.535606787</v>
       </c>
       <c r="K44" s="185">
         <f>IF(D44=0,0,D44*$L$40-E44)</f>
-        <v>0</v>
+        <v>2797040340.5848942</v>
       </c>
       <c r="L44" s="185">
         <f ca="1">IFERROR(K44/$C$3,0)</f>
-        <v>0</v>
+        <v>103594086.68832941</v>
       </c>
       <c r="S44" s="173">
         <v>0.9</v>
@@ -10344,39 +10467,39 @@
       </c>
       <c r="D45" s="45">
         <f>SUM(TARGETS!M22:M26)</f>
-        <v>0</v>
+        <v>1779787234.0425532</v>
       </c>
       <c r="E45" s="46">
         <f>E74</f>
-        <v>0</v>
+        <v>37280172.149707004</v>
       </c>
       <c r="F45" s="176">
         <f>IFERROR(E45/D45,0)</f>
-        <v>0</v>
+        <v>2.0946420693798318E-2</v>
       </c>
       <c r="G45" s="184">
         <f>D45*$H$40-E45</f>
-        <v>0</v>
+        <v>1564528338.4885907</v>
       </c>
       <c r="H45" s="184">
         <f ca="1">IFERROR(G45/$C$3,0)</f>
-        <v>0</v>
+        <v>57945494.018095955</v>
       </c>
       <c r="I45" s="204">
         <f>D45*$J$40-E45</f>
-        <v>0</v>
+        <v>1653517700.1907184</v>
       </c>
       <c r="J45" s="204">
         <f ca="1">IFERROR(I45/$C$3,0)</f>
-        <v>0</v>
+        <v>61241396.303359941</v>
       </c>
       <c r="K45" s="185">
         <f>D45*$L$40-E45</f>
-        <v>0</v>
+        <v>1742507061.8928461</v>
       </c>
       <c r="L45" s="185">
         <f ca="1">IFERROR(K45/$C$3,0)</f>
-        <v>0</v>
+        <v>64537298.588623933</v>
       </c>
       <c r="S45" s="173">
         <v>0.95</v>
@@ -10389,39 +10512,39 @@
       <c r="C46" s="259"/>
       <c r="D46" s="47">
         <f>SUM(D42:D45)</f>
-        <v>0</v>
+        <v>10438289468.281527</v>
       </c>
       <c r="E46" s="47">
         <f>SUM(E42:E45)</f>
-        <v>0</v>
+        <v>316844952.95822901</v>
       </c>
       <c r="F46" s="177">
         <f>IFERROR(E46/D46,0)</f>
-        <v>0</v>
+        <v>3.0354106764428686E-2</v>
       </c>
       <c r="G46" s="181">
         <f>SUM(G42:G45)</f>
-        <v>0</v>
+        <v>9077615568.4951458</v>
       </c>
       <c r="H46" s="181">
         <f ca="1">IFERROR(G46/$C$3,0)</f>
-        <v>0</v>
+        <v>336207984.01833874</v>
       </c>
       <c r="I46" s="186">
         <f>SUM(I42:I45)</f>
-        <v>0</v>
+        <v>9599530041.9092216</v>
       </c>
       <c r="J46" s="186">
         <f ca="1">IFERROR(I46/$C$3,0)</f>
-        <v>0</v>
+        <v>355538149.70034152</v>
       </c>
       <c r="K46" s="186">
         <f>SUM(K42:K45)</f>
-        <v>0</v>
+        <v>10121444515.323299</v>
       </c>
       <c r="L46" s="186">
         <f ca="1">IFERROR(K46/$C$3,0)</f>
-        <v>0</v>
+        <v>374868315.38234442</v>
       </c>
       <c r="S46" s="173">
         <v>1</v>
@@ -10434,33 +10557,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="264" t="s">
+      <c r="B48" s="274" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="265"/>
-      <c r="D48" s="265"/>
-      <c r="E48" s="265"/>
-      <c r="F48" s="265"/>
-      <c r="G48" s="265"/>
-      <c r="H48" s="265"/>
-      <c r="I48" s="265"/>
-      <c r="J48" s="265"/>
-      <c r="K48" s="265"/>
-      <c r="L48" s="288"/>
-      <c r="M48" s="271" t="s">
-        <v>186</v>
-      </c>
-      <c r="N48" s="272"/>
-      <c r="O48" s="272"/>
-      <c r="P48" s="272"/>
-      <c r="Q48" s="272"/>
-      <c r="R48" s="273"/>
+      <c r="C48" s="275"/>
+      <c r="D48" s="275"/>
+      <c r="E48" s="275"/>
+      <c r="F48" s="275"/>
+      <c r="G48" s="275"/>
+      <c r="H48" s="275"/>
+      <c r="I48" s="275"/>
+      <c r="J48" s="275"/>
+      <c r="K48" s="275"/>
+      <c r="L48" s="285"/>
+      <c r="M48" s="262" t="s">
+        <v>185</v>
+      </c>
+      <c r="N48" s="263"/>
+      <c r="O48" s="263"/>
+      <c r="P48" s="263"/>
+      <c r="Q48" s="263"/>
+      <c r="R48" s="264"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="286" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="289" t="s">
+      <c r="C49" s="286" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="255" t="s">
@@ -10469,49 +10592,49 @@
       <c r="E49" s="256"/>
       <c r="F49" s="256"/>
       <c r="G49" s="257"/>
-      <c r="H49" s="290" t="s">
+      <c r="H49" s="287" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="291"/>
-      <c r="J49" s="291"/>
-      <c r="K49" s="292"/>
-      <c r="L49" s="293" t="s">
+      <c r="I49" s="288"/>
+      <c r="J49" s="288"/>
+      <c r="K49" s="289"/>
+      <c r="L49" s="290" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="274" t="str">
+      <c r="N49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="276" t="str">
+      <c r="O49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="276" t="str">
+      <c r="P49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="278" t="str">
+      <c r="Q49" s="269" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="278" t="str">
+      <c r="R49" s="269" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="270"/>
-      <c r="C50" s="270"/>
+      <c r="B50" s="261"/>
+      <c r="C50" s="261"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -10519,7 +10642,7 @@
         <v>150</v>
       </c>
       <c r="F50" s="70" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G50" s="70" t="s">
         <v>130</v>
@@ -10531,23 +10654,23 @@
         <v>150</v>
       </c>
       <c r="J50" s="113" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="294"/>
-      <c r="M50" s="275"/>
-      <c r="N50" s="275"/>
-      <c r="O50" s="277"/>
-      <c r="P50" s="277"/>
-      <c r="Q50" s="279"/>
-      <c r="R50" s="279"/>
+      <c r="L50" s="291"/>
+      <c r="M50" s="266"/>
+      <c r="N50" s="266"/>
+      <c r="O50" s="268"/>
+      <c r="P50" s="268"/>
+      <c r="Q50" s="270"/>
+      <c r="R50" s="270"/>
       <c r="T50" s="178" t="s">
+        <v>215</v>
+      </c>
+      <c r="U50" s="178" t="s">
         <v>216</v>
-      </c>
-      <c r="U50" s="178" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="51" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10559,69 +10682,69 @@
       </c>
       <c r="D51" s="118">
         <f>TARGETS!AE5</f>
-        <v>0</v>
+        <v>264756949.64136907</v>
       </c>
       <c r="E51" s="118">
         <f>TARGETS!AF5</f>
-        <v>0</v>
+        <v>58508748.413354225</v>
       </c>
       <c r="F51" s="118">
         <f>TARGETS!AG5</f>
-        <v>0</v>
+        <v>172968793.98622558</v>
       </c>
       <c r="G51" s="118">
         <f t="shared" ref="G51:G64" si="1">SUM(D51:F51)</f>
-        <v>0</v>
+        <v>496234492.04094887</v>
       </c>
       <c r="H51" s="114">
         <f>SUMIF($B$10:$B$26,$T51,C$10:C$26)+SUMIF($B$10:$B$26,$U51,C$10:C$26)</f>
-        <v>0</v>
+        <v>12273347.239848999</v>
       </c>
       <c r="I51" s="114">
         <f t="shared" ref="I51:I64" si="2">SUMIF($B$10:$B$26,$T51,D$10:D$26)+SUMIF($B$10:$B$26,$U51,D$10:D$26)</f>
-        <v>0</v>
+        <v>3138986.5099889999</v>
       </c>
       <c r="J51" s="114">
         <f t="shared" ref="J51:J64" si="3">SUMIF($B$10:$B$26,$T51,E$10:E$26)+SUMIF($B$10:$B$26,$U51,E$10:E$26)</f>
-        <v>0</v>
+        <v>3614909.9</v>
       </c>
       <c r="K51" s="114">
         <f t="shared" ref="K51:K64" si="4">SUM(H51:J51)</f>
-        <v>0</v>
+        <v>19027243.649837997</v>
       </c>
       <c r="L51" s="187">
         <f t="shared" ref="L51:L65" si="5">IFERROR(K51/G51,0)</f>
-        <v>0</v>
+        <v>3.8343250932802719E-2</v>
       </c>
       <c r="M51" s="184">
         <f t="shared" ref="M51:M64" si="6">G51*$H$40-K51</f>
-        <v>0</v>
+        <v>427583799.18701601</v>
       </c>
       <c r="N51" s="184">
         <f t="shared" ref="N51:N65" ca="1" si="7">IFERROR(M51/$C$3,0)</f>
-        <v>0</v>
+        <v>15836437.00692652</v>
       </c>
       <c r="O51" s="180">
         <f t="shared" ref="O51:O64" si="8">G51*$J$40-K51</f>
-        <v>0</v>
+        <v>452395523.78906345</v>
       </c>
       <c r="P51" s="180">
         <f t="shared" ref="P51:P65" ca="1" si="9">IFERROR(O51/$C$3,0)</f>
-        <v>0</v>
+        <v>16755389.769965313</v>
       </c>
       <c r="Q51" s="185">
         <f t="shared" ref="Q51:Q64" si="10">G51*$L$40-K51</f>
-        <v>0</v>
+        <v>477207248.3911109</v>
       </c>
       <c r="R51" s="185">
         <f t="shared" ref="R51:R65" ca="1" si="11">IFERROR(Q51/$C$3,0)</f>
-        <v>0</v>
+        <v>17674342.533004109</v>
       </c>
       <c r="T51" t="s">
         <v>124</v>
       </c>
       <c r="U51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="52" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10633,63 +10756,63 @@
       </c>
       <c r="D52" s="119">
         <f>TARGETS!AE6</f>
-        <v>0</v>
+        <v>180052976.96171179</v>
       </c>
       <c r="E52" s="119">
         <f>TARGETS!AF6</f>
-        <v>0</v>
+        <v>163445127.22039506</v>
       </c>
       <c r="F52" s="119">
         <f>TARGETS!AG6</f>
-        <v>0</v>
+        <v>423892749.39216906</v>
       </c>
       <c r="G52" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>767390853.57427597</v>
       </c>
       <c r="H52" s="114">
         <f t="shared" ref="H52:H64" si="12">SUMIF($B$10:$B$26,$T52,C$10:C$26)+SUMIF($B$10:$B$26,$U52,C$10:C$26)</f>
-        <v>0</v>
+        <v>9534933.6398440003</v>
       </c>
       <c r="I52" s="114">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3657558.3389989999</v>
       </c>
       <c r="J52" s="114">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10038963.949999999</v>
       </c>
       <c r="K52" s="114">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>23231455.928842999</v>
       </c>
       <c r="L52" s="187">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.0273303129217475E-2</v>
       </c>
       <c r="M52" s="184">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>667420312.28800535</v>
       </c>
       <c r="N52" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>24719270.825481679</v>
       </c>
       <c r="O52" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>705789854.96671915</v>
       </c>
       <c r="P52" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>0</v>
+        <v>26140364.998767376</v>
       </c>
       <c r="Q52" s="185">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>744159397.64543295</v>
       </c>
       <c r="R52" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>0</v>
+        <v>27561459.172053073</v>
       </c>
       <c r="T52" t="s">
         <v>70</v>
@@ -10700,14 +10823,14 @@
     </row>
     <row r="53" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="136" t="s">
+        <v>171</v>
+      </c>
+      <c r="C53" s="137" t="s">
         <v>172</v>
-      </c>
-      <c r="C53" s="137" t="s">
-        <v>173</v>
       </c>
       <c r="D53" s="138">
         <f>TARGETS!AE7</f>
-        <v>0</v>
+        <v>262953105.06301075</v>
       </c>
       <c r="E53" s="138">
         <f>TARGETS!AF7</f>
@@ -10719,7 +10842,7 @@
       </c>
       <c r="G53" s="138">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>262953105.06301075</v>
       </c>
       <c r="H53" s="114">
         <f t="shared" si="12"/>
@@ -10743,33 +10866,33 @@
       </c>
       <c r="M53" s="184">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>236657794.55670968</v>
       </c>
       <c r="N53" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>8765103.5021003578</v>
       </c>
       <c r="O53" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>249805449.8098602</v>
       </c>
       <c r="P53" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>0</v>
+        <v>9252053.6966614891</v>
       </c>
       <c r="Q53" s="185">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>262953105.06301075</v>
       </c>
       <c r="R53" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>0</v>
+        <v>9739003.8912226204</v>
       </c>
       <c r="T53" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="U53" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="54" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10781,69 +10904,69 @@
       </c>
       <c r="D54" s="119">
         <f>TARGETS!AE8</f>
-        <v>0</v>
+        <v>590954252.3415246</v>
       </c>
       <c r="E54" s="119">
         <f>TARGETS!AF8</f>
-        <v>0</v>
+        <v>33662936.863966122</v>
       </c>
       <c r="F54" s="119">
         <f>TARGETS!AG8</f>
-        <v>0</v>
+        <v>83921591.734509259</v>
       </c>
       <c r="G54" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>708538780.93999994</v>
       </c>
       <c r="H54" s="114">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>17804909.979979999</v>
       </c>
       <c r="I54" s="114">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1535108.1499989999</v>
       </c>
       <c r="J54" s="114">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5624603.5700000003</v>
       </c>
       <c r="K54" s="114">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>24964621.699979</v>
       </c>
       <c r="L54" s="187">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.5233952426512331E-2</v>
       </c>
       <c r="M54" s="184">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>612720281.14602101</v>
       </c>
       <c r="N54" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>22693343.746148925</v>
       </c>
       <c r="O54" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>648147220.19302094</v>
       </c>
       <c r="P54" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>0</v>
+        <v>24005452.599741515</v>
       </c>
       <c r="Q54" s="185">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>683574159.24002099</v>
       </c>
       <c r="R54" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>0</v>
+        <v>25317561.453334112</v>
       </c>
       <c r="T54" t="s">
         <v>115</v>
       </c>
       <c r="U54" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="55" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10851,23 +10974,23 @@
         <v>73</v>
       </c>
       <c r="C55" s="55" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D55" s="118">
         <f>TARGETS!AE9</f>
-        <v>0</v>
+        <v>5575801.9517222047</v>
       </c>
       <c r="E55" s="118">
         <f>TARGETS!AF9</f>
-        <v>0</v>
+        <v>63507750.38497854</v>
       </c>
       <c r="F55" s="118">
         <f>TARGETS!AG9</f>
-        <v>0</v>
+        <v>468117447.23398483</v>
       </c>
       <c r="G55" s="118">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>537200999.57068563</v>
       </c>
       <c r="H55" s="114">
         <f t="shared" si="12"/>
@@ -10891,33 +11014,33 @@
       </c>
       <c r="M55" s="184">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>483480899.61361706</v>
       </c>
       <c r="N55" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>17906699.985689521</v>
       </c>
       <c r="O55" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>510340949.59215134</v>
       </c>
       <c r="P55" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>0</v>
+        <v>18901516.65156116</v>
       </c>
       <c r="Q55" s="185">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>537200999.57068563</v>
       </c>
       <c r="R55" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>0</v>
+        <v>19896333.317432802</v>
       </c>
       <c r="T55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="U55" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10925,73 +11048,73 @@
         <v>75</v>
       </c>
       <c r="C56" s="56" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D56" s="119">
         <f>TARGETS!AE10</f>
-        <v>0</v>
+        <v>267520870.86594501</v>
       </c>
       <c r="E56" s="119">
         <f>TARGETS!AF10</f>
-        <v>0</v>
+        <v>105132391.14913487</v>
       </c>
       <c r="F56" s="119">
         <f>TARGETS!AG10</f>
-        <v>0</v>
+        <v>184159698.63927278</v>
       </c>
       <c r="G56" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>556812960.65435266</v>
       </c>
       <c r="H56" s="114">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>9041895.5201660004</v>
       </c>
       <c r="I56" s="114">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1793939.1151990001</v>
       </c>
       <c r="J56" s="114">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6225856.0099980002</v>
       </c>
       <c r="K56" s="114">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>17061690.645362999</v>
       </c>
       <c r="L56" s="187">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.064169092851669E-2</v>
       </c>
       <c r="M56" s="184">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>484069973.94355446</v>
       </c>
       <c r="N56" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>17928517.553464979</v>
       </c>
       <c r="O56" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>511910621.97627205</v>
       </c>
       <c r="P56" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>0</v>
+        <v>18959652.665787853</v>
       </c>
       <c r="Q56" s="185">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>539751270.00898969</v>
       </c>
       <c r="R56" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>0</v>
+        <v>19990787.778110728</v>
       </c>
       <c r="T56" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="U56" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="57" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -11003,69 +11126,69 @@
       </c>
       <c r="D57" s="118">
         <f>TARGETS!AE11</f>
-        <v>0</v>
+        <v>664600150.5441153</v>
       </c>
       <c r="E57" s="118">
         <f>TARGETS!AF11</f>
-        <v>0</v>
+        <v>83317068.128031164</v>
       </c>
       <c r="F57" s="118">
         <f>TARGETS!AG11</f>
-        <v>0</v>
+        <v>343133819.00673455</v>
       </c>
       <c r="G57" s="118">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1091051037.6788809</v>
       </c>
       <c r="H57" s="114">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>24228400.236997999</v>
       </c>
       <c r="I57" s="114">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2594594.52</v>
       </c>
       <c r="J57" s="114">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>36828739.059940003</v>
       </c>
       <c r="K57" s="114">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>63651733.816937998</v>
       </c>
       <c r="L57" s="187">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5.8339831610766529E-2</v>
       </c>
       <c r="M57" s="184">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>918294200.09405482</v>
       </c>
       <c r="N57" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>34010896.29977981</v>
       </c>
       <c r="O57" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>972846751.97799873</v>
       </c>
       <c r="P57" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>0</v>
+        <v>36031361.184370324</v>
       </c>
       <c r="Q57" s="185">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1027399303.8619429</v>
       </c>
       <c r="R57" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>0</v>
+        <v>38051826.068960845</v>
       </c>
       <c r="T57" t="s">
         <v>120</v>
       </c>
       <c r="U57" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -11077,81 +11200,81 @@
       </c>
       <c r="D58" s="119">
         <f>TARGETS!AE12</f>
-        <v>0</v>
+        <v>259993077.39884707</v>
       </c>
       <c r="E58" s="119">
         <f>TARGETS!AF12</f>
-        <v>0</v>
+        <v>86845105.094943255</v>
       </c>
       <c r="F58" s="119">
         <f>TARGETS!AG12</f>
-        <v>0</v>
+        <v>249609659.83737293</v>
       </c>
       <c r="G58" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>596447842.33116329</v>
       </c>
       <c r="H58" s="114">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>7886135.4645919995</v>
       </c>
       <c r="I58" s="114">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4799378.3999950001</v>
       </c>
       <c r="J58" s="114">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9972973.1899980009</v>
       </c>
       <c r="K58" s="114">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>22658487.054585002</v>
       </c>
       <c r="L58" s="187">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.7989050251278175E-2</v>
       </c>
       <c r="M58" s="184">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>514144571.04346198</v>
       </c>
       <c r="N58" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>19042391.52012822</v>
       </c>
       <c r="O58" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>543966963.16002011</v>
       </c>
       <c r="P58" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>0</v>
+        <v>20146924.561482225</v>
       </c>
       <c r="Q58" s="185">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>573789355.27657831</v>
       </c>
       <c r="R58" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>0</v>
+        <v>21251457.602836233</v>
       </c>
       <c r="T58" t="s">
         <v>125</v>
       </c>
       <c r="U58" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="59" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="136" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C59" s="137" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D59" s="138">
         <f>TARGETS!AE13</f>
-        <v>0</v>
+        <v>443846715.57642001</v>
       </c>
       <c r="E59" s="138">
         <f>TARGETS!AF13</f>
@@ -11163,7 +11286,7 @@
       </c>
       <c r="G59" s="138">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>443846715.57642001</v>
       </c>
       <c r="H59" s="114">
         <f t="shared" si="12"/>
@@ -11187,33 +11310,33 @@
       </c>
       <c r="M59" s="184">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>399462044.01877803</v>
       </c>
       <c r="N59" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>14794890.519214001</v>
       </c>
       <c r="O59" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>421654379.79759902</v>
       </c>
       <c r="P59" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>0</v>
+        <v>15616828.881392555</v>
       </c>
       <c r="Q59" s="185">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>443846715.57642001</v>
       </c>
       <c r="R59" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>0</v>
+        <v>16438767.243571112</v>
       </c>
       <c r="T59" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="U59" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="60" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -11221,23 +11344,23 @@
         <v>80</v>
       </c>
       <c r="C60" s="56" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D60" s="119">
         <f>TARGETS!AE14</f>
-        <v>0</v>
+        <v>345737237.66667807</v>
       </c>
       <c r="E60" s="119">
         <f>TARGETS!AF14</f>
-        <v>0</v>
+        <v>99843502.42153886</v>
       </c>
       <c r="F60" s="119">
         <f>TARGETS!AG14</f>
-        <v>0</v>
+        <v>115472440.26230113</v>
       </c>
       <c r="G60" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>561053180.35051799</v>
       </c>
       <c r="H60" s="114">
         <f t="shared" si="12"/>
@@ -11261,33 +11384,33 @@
       </c>
       <c r="M60" s="184">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>504947862.31546623</v>
       </c>
       <c r="N60" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>18701772.678350601</v>
       </c>
       <c r="O60" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>533000521.33299208</v>
       </c>
       <c r="P60" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>0</v>
+        <v>19740760.049370077</v>
       </c>
       <c r="Q60" s="185">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>561053180.35051799</v>
       </c>
       <c r="R60" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>0</v>
+        <v>20779747.420389555</v>
       </c>
       <c r="T60" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="U60" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="61" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -11299,69 +11422,69 @@
       </c>
       <c r="D61" s="118">
         <f>TARGETS!AE15</f>
-        <v>0</v>
+        <v>476796144.98316145</v>
       </c>
       <c r="E61" s="118">
         <f>TARGETS!AF15</f>
-        <v>0</v>
+        <v>53126030.965583593</v>
       </c>
       <c r="F61" s="118">
         <f>TARGETS!AG15</f>
-        <v>0</v>
+        <v>168537597.75857076</v>
       </c>
       <c r="G61" s="118">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>698459773.7073158</v>
       </c>
       <c r="H61" s="114">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>17326640.025509998</v>
       </c>
       <c r="I61" s="114">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3598450.4599979999</v>
       </c>
       <c r="J61" s="114">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9749459.7300000004</v>
       </c>
       <c r="K61" s="114">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>30674550.215507999</v>
       </c>
       <c r="L61" s="187">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4.3917418540358105E-2</v>
       </c>
       <c r="M61" s="184">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>597939246.12107623</v>
       </c>
       <c r="N61" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>22145898.004484303</v>
       </c>
       <c r="O61" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>632862234.80644202</v>
       </c>
       <c r="P61" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>0</v>
+        <v>23439342.029868223</v>
       </c>
       <c r="Q61" s="185">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>667785223.49180782</v>
       </c>
       <c r="R61" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>0</v>
+        <v>24732786.055252142</v>
       </c>
       <c r="T61" t="s">
         <v>126</v>
       </c>
       <c r="U61" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="62" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -11373,69 +11496,69 @@
       </c>
       <c r="D62" s="119">
         <f>TARGETS!AE16</f>
-        <v>0</v>
+        <v>168507149.83198008</v>
       </c>
       <c r="E62" s="119">
         <f>TARGETS!AF16</f>
-        <v>0</v>
+        <v>30531298.995438561</v>
       </c>
       <c r="F62" s="119">
         <f>TARGETS!AG16</f>
-        <v>0</v>
+        <v>259851780.88751724</v>
       </c>
       <c r="G62" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>458890229.7149359</v>
       </c>
       <c r="H62" s="114">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>5099399.1523909997</v>
       </c>
       <c r="I62" s="114">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3553070.28</v>
       </c>
       <c r="J62" s="114">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>14595495.476</v>
       </c>
       <c r="K62" s="114">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>23247964.908390999</v>
       </c>
       <c r="L62" s="187">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5.0661276712804959E-2</v>
       </c>
       <c r="M62" s="184">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>389753241.8350513</v>
       </c>
       <c r="N62" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>14435305.253150048</v>
       </c>
       <c r="O62" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>412697753.3207981</v>
       </c>
       <c r="P62" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>0</v>
+        <v>15285101.974844374</v>
       </c>
       <c r="Q62" s="185">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>435642264.8065449</v>
       </c>
       <c r="R62" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>0</v>
+        <v>16134898.6965387</v>
       </c>
       <c r="T62" t="s">
         <v>112</v>
       </c>
       <c r="U62" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -11447,69 +11570,69 @@
       </c>
       <c r="D63" s="118">
         <f>TARGETS!AE17</f>
-        <v>0</v>
+        <v>409968842.36459517</v>
       </c>
       <c r="E63" s="118">
         <f>TARGETS!AF17</f>
-        <v>0</v>
+        <v>308297473.95300913</v>
       </c>
       <c r="F63" s="118">
         <f>TARGETS!AG17</f>
-        <v>0</v>
+        <v>242574653.13033652</v>
       </c>
       <c r="G63" s="118">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>960840969.44794083</v>
       </c>
       <c r="H63" s="114">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>26521190.528918002</v>
       </c>
       <c r="I63" s="114">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>297297.3</v>
       </c>
       <c r="J63" s="114">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>15905401.999435</v>
       </c>
       <c r="K63" s="114">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>42723889.828353003</v>
       </c>
       <c r="L63" s="187">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4.4465100039292008E-2</v>
       </c>
       <c r="M63" s="184">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>822032982.67479372</v>
       </c>
       <c r="N63" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>30445666.024992362</v>
       </c>
       <c r="O63" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>870075031.14719069</v>
       </c>
       <c r="P63" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>0</v>
+        <v>32225001.153599653</v>
       </c>
       <c r="Q63" s="185">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>918117079.61958778</v>
       </c>
       <c r="R63" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>0</v>
+        <v>34004336.282206953</v>
       </c>
       <c r="T63" t="s">
         <v>127</v>
       </c>
       <c r="U63" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="64" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -11521,63 +11644,63 @@
       </c>
       <c r="D64" s="119">
         <f>TARGETS!AE18</f>
-        <v>0</v>
+        <v>123323413.46844758</v>
       </c>
       <c r="E64" s="119">
         <f>TARGETS!AF18</f>
-        <v>0</v>
+        <v>193690629.51885673</v>
       </c>
       <c r="F64" s="119">
         <f>TARGETS!AG18</f>
-        <v>0</v>
+        <v>201767250.60122082</v>
       </c>
       <c r="G64" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>518781293.58852518</v>
       </c>
       <c r="H64" s="114">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>5074111.7300000004</v>
       </c>
       <c r="I64" s="114">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2838292.3307739999</v>
       </c>
       <c r="J64" s="114">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4410738.9999500001</v>
       </c>
       <c r="K64" s="114">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>12323143.060724001</v>
       </c>
       <c r="L64" s="187">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.3754023541369601E-2</v>
       </c>
       <c r="M64" s="184">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>454580021.16894865</v>
       </c>
       <c r="N64" s="184">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>16836297.08033143</v>
       </c>
       <c r="O64" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>480519085.8483749</v>
       </c>
       <c r="P64" s="180">
         <f t="shared" ca="1" si="9"/>
-        <v>0</v>
+        <v>17797003.179569442</v>
       </c>
       <c r="Q64" s="185">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>506458150.52780116</v>
       </c>
       <c r="R64" s="185">
         <f t="shared" ca="1" si="11"/>
-        <v>0</v>
+        <v>18757709.27880745</v>
       </c>
       <c r="T64" t="s">
         <v>122</v>
@@ -11593,63 +11716,63 @@
       <c r="C65" s="58"/>
       <c r="D65" s="134">
         <f t="shared" ref="D65:K65" si="13">SUM(D51:D64)</f>
-        <v>0</v>
+        <v>4464586688.6595287</v>
       </c>
       <c r="E65" s="134">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1279908063.1092303</v>
       </c>
       <c r="F65" s="134">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>2914007482.4702153</v>
       </c>
       <c r="G65" s="134">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>8658502234.2389736</v>
       </c>
       <c r="H65" s="135">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>134790963.51824799</v>
       </c>
       <c r="I65" s="135">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>27806675.404953003</v>
       </c>
       <c r="J65" s="135">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>116967141.88532101</v>
       </c>
       <c r="K65" s="135">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>279564780.80852205</v>
       </c>
       <c r="L65" s="189">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3.2287891513501928E-2</v>
       </c>
       <c r="M65" s="181">
         <f>SUM(M51:M64)</f>
-        <v>0</v>
+        <v>7513087230.0065556</v>
       </c>
       <c r="N65" s="181">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>278262490.00024277</v>
       </c>
       <c r="O65" s="181">
         <f>SUM(O51:O64)</f>
-        <v>0</v>
+        <v>7946012341.718504</v>
       </c>
       <c r="P65" s="181">
         <f t="shared" ca="1" si="9"/>
-        <v>0</v>
+        <v>294296753.39698166</v>
       </c>
       <c r="Q65" s="186">
         <f>SUM(Q51:Q64)</f>
-        <v>0</v>
+        <v>8378937453.4304523</v>
       </c>
       <c r="R65" s="186">
         <f t="shared" ca="1" si="11"/>
-        <v>0</v>
+        <v>310331016.79372048</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11658,21 +11781,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="285" t="s">
+      <c r="B67" s="292" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="286"/>
-      <c r="D67" s="286"/>
-      <c r="E67" s="286"/>
+      <c r="C67" s="293"/>
+      <c r="D67" s="293"/>
+      <c r="E67" s="293"/>
       <c r="F67" s="295"/>
-      <c r="G67" s="271" t="s">
-        <v>186</v>
-      </c>
-      <c r="H67" s="272"/>
-      <c r="I67" s="272"/>
-      <c r="J67" s="272"/>
-      <c r="K67" s="272"/>
-      <c r="L67" s="273"/>
+      <c r="G67" s="262" t="s">
+        <v>185</v>
+      </c>
+      <c r="H67" s="263"/>
+      <c r="I67" s="263"/>
+      <c r="J67" s="263"/>
+      <c r="K67" s="263"/>
+      <c r="L67" s="264"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -11730,39 +11853,39 @@
       </c>
       <c r="D69" s="116">
         <f>TARGETS!M22</f>
-        <v>0</v>
+        <v>269378070.68085116</v>
       </c>
       <c r="E69" s="114">
         <f>IFERROR($C$31,0)</f>
-        <v>0</v>
+        <v>4400648.7999700001</v>
       </c>
       <c r="F69" s="187">
         <f t="shared" ref="F69:F74" si="14">IFERROR(E69/D69,0)</f>
-        <v>0</v>
+        <v>1.6336329044333086E-2</v>
       </c>
       <c r="G69" s="184">
         <f>D69*$H$40-E69</f>
-        <v>0</v>
+        <v>238039614.81279606</v>
       </c>
       <c r="H69" s="184">
         <f t="shared" ref="H69:H74" ca="1" si="15">IFERROR(G69/$C$3,0)</f>
-        <v>0</v>
+        <v>8816282.0301035568</v>
       </c>
       <c r="I69" s="204">
         <f>D69*$J$40-E69</f>
-        <v>0</v>
+        <v>251508518.34683859</v>
       </c>
       <c r="J69" s="204">
         <f t="shared" ref="J69:J74" ca="1" si="16">IFERROR(I69/$C$3,0)</f>
-        <v>0</v>
+        <v>9315130.3091421705</v>
       </c>
       <c r="K69" s="185">
         <f>D69*$L$40-E69</f>
-        <v>0</v>
+        <v>264977421.88088116</v>
       </c>
       <c r="L69" s="185">
         <f t="shared" ref="L69:L74" ca="1" si="17">IFERROR(K69/$C$3,0)</f>
-        <v>0</v>
+        <v>9813978.5881807841</v>
       </c>
     </row>
     <row r="70" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -11774,39 +11897,39 @@
       </c>
       <c r="D70" s="117">
         <f>TARGETS!M23</f>
-        <v>0</v>
+        <v>412678979.6808511</v>
       </c>
       <c r="E70" s="114">
         <f>IFERROR($C$32,0)</f>
-        <v>0</v>
+        <v>9101351.5199759994</v>
       </c>
       <c r="F70" s="187">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2.2054313323675002E-2</v>
       </c>
       <c r="G70" s="184">
         <f>D70*$H$40-E70</f>
-        <v>0</v>
+        <v>362309730.19278997</v>
       </c>
       <c r="H70" s="184">
         <f t="shared" ca="1" si="15"/>
-        <v>0</v>
+        <v>13418878.896029258</v>
       </c>
       <c r="I70" s="204">
         <f>D70*$J$40-E70</f>
-        <v>0</v>
+        <v>382943679.1768325</v>
       </c>
       <c r="J70" s="204">
         <f t="shared" ca="1" si="16"/>
-        <v>0</v>
+        <v>14183099.228771575</v>
       </c>
       <c r="K70" s="185">
         <f>D70*$L$40-E70</f>
-        <v>0</v>
+        <v>403577628.16087508</v>
       </c>
       <c r="L70" s="185">
         <f t="shared" ca="1" si="17"/>
-        <v>0</v>
+        <v>14947319.561513891</v>
       </c>
     </row>
     <row r="71" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -11818,39 +11941,39 @@
       </c>
       <c r="D71" s="116">
         <f>TARGETS!M24</f>
-        <v>0</v>
+        <v>1097730183.680851</v>
       </c>
       <c r="E71" s="114">
         <f>M21</f>
-        <v>0</v>
+        <v>23778171.829761002</v>
       </c>
       <c r="F71" s="187">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2.1661217103486476E-2</v>
       </c>
       <c r="G71" s="184">
         <f>D71*$H$40-E71</f>
-        <v>0</v>
+        <v>964178993.48300493</v>
       </c>
       <c r="H71" s="184">
         <f t="shared" ca="1" si="15"/>
-        <v>0</v>
+        <v>35710333.091963142</v>
       </c>
       <c r="I71" s="204">
         <f>D71*$J$40-E71</f>
-        <v>0</v>
+        <v>1019065502.6670474</v>
       </c>
       <c r="J71" s="204">
         <f t="shared" ca="1" si="16"/>
-        <v>0</v>
+        <v>37743166.765446201</v>
       </c>
       <c r="K71" s="185">
         <f>D71*$L$40-E71</f>
-        <v>0</v>
+        <v>1073952011.85109</v>
       </c>
       <c r="L71" s="185">
         <f t="shared" ca="1" si="17"/>
-        <v>0</v>
+        <v>39776000.43892926</v>
       </c>
     </row>
     <row r="72" spans="2:21" hidden="1" x14ac:dyDescent="0.25">
@@ -11948,55 +12071,55 @@
       <c r="C74" s="58"/>
       <c r="D74" s="115">
         <f>SUM(D69:D73)</f>
-        <v>0</v>
+        <v>1779787234.0425532</v>
       </c>
       <c r="E74" s="115">
         <f>SUM(E69:E73)</f>
-        <v>0</v>
+        <v>37280172.149707004</v>
       </c>
       <c r="F74" s="177">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2.0946420693798318E-2</v>
       </c>
       <c r="G74" s="181">
         <f>SUM(G69:G73)</f>
-        <v>0</v>
+        <v>1564528338.488591</v>
       </c>
       <c r="H74" s="181">
         <f t="shared" ca="1" si="15"/>
-        <v>0</v>
+        <v>57945494.018095963</v>
       </c>
       <c r="I74" s="186">
         <f>SUM(I69:I73)</f>
-        <v>0</v>
+        <v>1653517700.1907187</v>
       </c>
       <c r="J74" s="186">
         <f t="shared" ca="1" si="16"/>
-        <v>0</v>
+        <v>61241396.303359948</v>
       </c>
       <c r="K74" s="186">
         <f>SUM(K69:K73)</f>
-        <v>0</v>
+        <v>1742507061.8928461</v>
       </c>
       <c r="L74" s="186">
         <f t="shared" ca="1" si="17"/>
-        <v>0</v>
+        <v>64537298.588623933</v>
       </c>
     </row>
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="76" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="251" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C77" s="252"/>
       <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="270" t="s">
+      <c r="B78" s="261" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="270" t="s">
+      <c r="C78" s="261" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -12007,13 +12130,13 @@
       <c r="B79" s="260"/>
       <c r="C79" s="260"/>
       <c r="D79" s="70" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T79" s="178" t="s">
+        <v>215</v>
+      </c>
+      <c r="U79" s="178" t="s">
         <v>216</v>
-      </c>
-      <c r="U79" s="178" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="80" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -12025,7 +12148,7 @@
       </c>
       <c r="D80" s="131">
         <f>SUMIF($B$10:$B$26,$T80,$F$10:$F$26)+SUMIF($B$10:$B$26,$U80,$F$10:$F$26)</f>
-        <v>0</v>
+        <v>972973.02</v>
       </c>
       <c r="T80" t="str">
         <f t="shared" ref="T80:U93" si="18">T51</f>
@@ -12045,7 +12168,7 @@
       </c>
       <c r="D81" s="132">
         <f t="shared" ref="D81:D93" si="19">SUMIF($B$10:$B$26,$T81,$F$10:$F$26)+SUMIF($B$10:$B$26,$U81,$F$10:$F$26)</f>
-        <v>0</v>
+        <v>4378378.59</v>
       </c>
       <c r="T81" t="str">
         <f t="shared" si="18"/>
@@ -12058,10 +12181,10 @@
     </row>
     <row r="82" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="C82" s="56" t="s">
         <v>172</v>
-      </c>
-      <c r="C82" s="56" t="s">
-        <v>173</v>
       </c>
       <c r="D82" s="132">
         <f t="shared" si="19"/>
@@ -12085,7 +12208,7 @@
       </c>
       <c r="D83" s="131">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>18467747.989999998</v>
       </c>
       <c r="T83" t="str">
         <f t="shared" si="18"/>
@@ -12101,7 +12224,7 @@
         <v>73</v>
       </c>
       <c r="C84" s="56" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D84" s="132">
         <f t="shared" si="19"/>
@@ -12121,11 +12244,11 @@
         <v>75</v>
       </c>
       <c r="C85" s="55" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D85" s="131">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>29513694.069988001</v>
       </c>
       <c r="T85" t="str">
         <f t="shared" si="18"/>
@@ -12145,7 +12268,7 @@
       </c>
       <c r="D86" s="132">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>142163962.83000001</v>
       </c>
       <c r="T86" t="str">
         <f t="shared" si="18"/>
@@ -12165,7 +12288,7 @@
       </c>
       <c r="D87" s="131">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>7967567.5999999996</v>
       </c>
       <c r="T87" t="str">
         <f t="shared" si="18"/>
@@ -12178,10 +12301,10 @@
     </row>
     <row r="88" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="53" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C88" s="56" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D88" s="132">
         <f t="shared" si="19"/>
@@ -12225,7 +12348,7 @@
       </c>
       <c r="D90" s="131">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>29344144.359993</v>
       </c>
       <c r="T90" t="str">
         <f t="shared" si="18"/>
@@ -12245,7 +12368,7 @@
       </c>
       <c r="D91" s="132">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>9891892.1299849991</v>
       </c>
       <c r="T91" t="str">
         <f t="shared" si="18"/>
@@ -12285,7 +12408,7 @@
       </c>
       <c r="D93" s="132">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>14486486.800000001</v>
       </c>
       <c r="T93" t="str">
         <f t="shared" si="18"/>
@@ -12303,12 +12426,18 @@
       <c r="C94" s="58"/>
       <c r="D94" s="120">
         <f>SUM(D80:D93)</f>
-        <v>0</v>
+        <v>257186847.38996604</v>
       </c>
     </row>
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -12323,12 +12452,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -12364,14 +12487,14 @@
   <sheetData>
     <row r="1" spans="2:15" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="83" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C1" s="83"/>
       <c r="D1" s="83"/>
       <c r="E1" s="83"/>
       <c r="F1" s="83"/>
       <c r="G1" s="220" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H1" s="110"/>
       <c r="I1" s="110"/>
@@ -12383,7 +12506,7 @@
     </row>
     <row r="2" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G2" s="221" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H2" s="111"/>
       <c r="I2" s="111"/>
@@ -12408,7 +12531,7 @@
         <v>30</v>
       </c>
       <c r="G3" s="221" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H3" s="111"/>
       <c r="I3" s="111"/>
@@ -12418,7 +12541,7 @@
     </row>
     <row r="4" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G4" s="221" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H4" s="111"/>
       <c r="I4" s="111"/>
@@ -12428,7 +12551,7 @@
     </row>
     <row r="5" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G5" s="221" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H5" s="111"/>
       <c r="I5" s="111"/>
@@ -12453,7 +12576,7 @@
         <v>107</v>
       </c>
       <c r="O6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12492,10 +12615,10 @@
         <v>110</v>
       </c>
       <c r="E8" s="80" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F8" s="80" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G8" s="80" t="s">
         <v>111</v>
@@ -12546,7 +12669,7 @@
     </row>
     <row r="11" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="72" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
@@ -12565,7 +12688,7 @@
     </row>
     <row r="12" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="72" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
@@ -12717,7 +12840,7 @@
     </row>
     <row r="20" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
@@ -12735,12 +12858,12 @@
         <v>0</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
@@ -12758,7 +12881,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12811,7 +12934,7 @@
     </row>
     <row r="25" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="72" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="15"/>
@@ -12952,15 +13075,15 @@
       <c r="H39" s="111"/>
       <c r="I39" s="111"/>
       <c r="S39" s="172" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="261" t="s">
-        <v>175</v>
-      </c>
-      <c r="C40" s="262"/>
-      <c r="D40" s="263"/>
+      <c r="B40" s="271" t="s">
+        <v>174</v>
+      </c>
+      <c r="C40" s="272"/>
+      <c r="D40" s="273"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -12969,19 +13092,19 @@
         <v>0</v>
       </c>
       <c r="G40" s="192" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H40" s="198">
         <v>0.9</v>
       </c>
       <c r="I40" s="201" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J40" s="199">
         <v>0.95</v>
       </c>
       <c r="K40" s="194" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L40" s="200">
         <v>1</v>
@@ -13136,7 +13259,7 @@
     </row>
     <row r="44" spans="2:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="109" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C44" s="41" t="s">
         <v>143</v>
@@ -13280,33 +13403,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="264" t="s">
+      <c r="B48" s="274" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="265"/>
-      <c r="D48" s="265"/>
-      <c r="E48" s="265"/>
-      <c r="F48" s="265"/>
-      <c r="G48" s="265"/>
-      <c r="H48" s="265"/>
-      <c r="I48" s="265"/>
-      <c r="J48" s="265"/>
-      <c r="K48" s="265"/>
-      <c r="L48" s="288"/>
-      <c r="M48" s="271" t="s">
-        <v>186</v>
-      </c>
-      <c r="N48" s="272"/>
-      <c r="O48" s="272"/>
-      <c r="P48" s="272"/>
-      <c r="Q48" s="272"/>
-      <c r="R48" s="273"/>
+      <c r="C48" s="275"/>
+      <c r="D48" s="275"/>
+      <c r="E48" s="275"/>
+      <c r="F48" s="275"/>
+      <c r="G48" s="275"/>
+      <c r="H48" s="275"/>
+      <c r="I48" s="275"/>
+      <c r="J48" s="275"/>
+      <c r="K48" s="275"/>
+      <c r="L48" s="285"/>
+      <c r="M48" s="262" t="s">
+        <v>185</v>
+      </c>
+      <c r="N48" s="263"/>
+      <c r="O48" s="263"/>
+      <c r="P48" s="263"/>
+      <c r="Q48" s="263"/>
+      <c r="R48" s="264"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="286" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="289" t="s">
+      <c r="C49" s="286" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="255" t="s">
@@ -13315,49 +13438,49 @@
       <c r="E49" s="256"/>
       <c r="F49" s="256"/>
       <c r="G49" s="257"/>
-      <c r="H49" s="290" t="s">
+      <c r="H49" s="287" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="291"/>
-      <c r="J49" s="291"/>
-      <c r="K49" s="292"/>
-      <c r="L49" s="293" t="s">
+      <c r="I49" s="288"/>
+      <c r="J49" s="288"/>
+      <c r="K49" s="289"/>
+      <c r="L49" s="290" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="274" t="str">
+      <c r="N49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="276" t="str">
+      <c r="O49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="276" t="str">
+      <c r="P49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="278" t="str">
+      <c r="Q49" s="269" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="278" t="str">
+      <c r="R49" s="269" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="270"/>
-      <c r="C50" s="270"/>
+      <c r="B50" s="261"/>
+      <c r="C50" s="261"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -13365,7 +13488,7 @@
         <v>150</v>
       </c>
       <c r="F50" s="70" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G50" s="70" t="s">
         <v>130</v>
@@ -13377,23 +13500,23 @@
         <v>150</v>
       </c>
       <c r="J50" s="113" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="294"/>
-      <c r="M50" s="275"/>
-      <c r="N50" s="275"/>
-      <c r="O50" s="277"/>
-      <c r="P50" s="277"/>
-      <c r="Q50" s="279"/>
-      <c r="R50" s="279"/>
+      <c r="L50" s="291"/>
+      <c r="M50" s="266"/>
+      <c r="N50" s="266"/>
+      <c r="O50" s="268"/>
+      <c r="P50" s="268"/>
+      <c r="Q50" s="270"/>
+      <c r="R50" s="270"/>
       <c r="T50" s="178" t="s">
+        <v>215</v>
+      </c>
+      <c r="U50" s="178" t="s">
         <v>216</v>
-      </c>
-      <c r="U50" s="178" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="51" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -13467,7 +13590,7 @@
         <v>124</v>
       </c>
       <c r="U51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="52" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -13546,10 +13669,10 @@
     </row>
     <row r="53" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="136" t="s">
+        <v>171</v>
+      </c>
+      <c r="C53" s="137" t="s">
         <v>172</v>
-      </c>
-      <c r="C53" s="137" t="s">
-        <v>173</v>
       </c>
       <c r="D53" s="138">
         <f>TARGETS!AH7</f>
@@ -13612,10 +13735,10 @@
         <v>0</v>
       </c>
       <c r="T53" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="U53" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="54" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -13689,7 +13812,7 @@
         <v>115</v>
       </c>
       <c r="U54" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="55" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -13697,7 +13820,7 @@
         <v>73</v>
       </c>
       <c r="C55" s="55" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D55" s="118">
         <f>TARGETS!AH9</f>
@@ -13760,10 +13883,10 @@
         <v>0</v>
       </c>
       <c r="T55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="U55" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -13834,10 +13957,10 @@
         <v>0</v>
       </c>
       <c r="T56" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="U56" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="57" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -13911,7 +14034,7 @@
         <v>120</v>
       </c>
       <c r="U57" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -13985,15 +14108,15 @@
         <v>125</v>
       </c>
       <c r="U58" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="59" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="136" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C59" s="137" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D59" s="138">
         <f>TARGETS!AH13</f>
@@ -14056,10 +14179,10 @@
         <v>0</v>
       </c>
       <c r="T59" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="U59" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="60" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14067,7 +14190,7 @@
         <v>80</v>
       </c>
       <c r="C60" s="56" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D60" s="119">
         <f>TARGETS!AH14</f>
@@ -14130,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="T60" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="U60" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="61" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14207,7 +14330,7 @@
         <v>126</v>
       </c>
       <c r="U61" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="62" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14281,7 +14404,7 @@
         <v>112</v>
       </c>
       <c r="U62" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14355,7 +14478,7 @@
         <v>127</v>
       </c>
       <c r="U63" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="64" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14504,21 +14627,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="285" t="s">
+      <c r="B67" s="292" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="286"/>
-      <c r="D67" s="286"/>
-      <c r="E67" s="286"/>
+      <c r="C67" s="293"/>
+      <c r="D67" s="293"/>
+      <c r="E67" s="293"/>
       <c r="F67" s="295"/>
-      <c r="G67" s="271" t="s">
-        <v>186</v>
-      </c>
-      <c r="H67" s="272"/>
-      <c r="I67" s="272"/>
-      <c r="J67" s="272"/>
-      <c r="K67" s="272"/>
-      <c r="L67" s="273"/>
+      <c r="G67" s="262" t="s">
+        <v>185</v>
+      </c>
+      <c r="H67" s="263"/>
+      <c r="I67" s="263"/>
+      <c r="J67" s="263"/>
+      <c r="K67" s="263"/>
+      <c r="L67" s="264"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -14833,16 +14956,16 @@
     <row r="76" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="251" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C77" s="252"/>
       <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="270" t="s">
+      <c r="B78" s="261" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="270" t="s">
+      <c r="C78" s="261" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -14853,13 +14976,13 @@
       <c r="B79" s="260"/>
       <c r="C79" s="260"/>
       <c r="D79" s="70" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T79" s="178" t="s">
+        <v>215</v>
+      </c>
+      <c r="U79" s="178" t="s">
         <v>216</v>
-      </c>
-      <c r="U79" s="178" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="80" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14904,10 +15027,10 @@
     </row>
     <row r="82" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="C82" s="56" t="s">
         <v>172</v>
-      </c>
-      <c r="C82" s="56" t="s">
-        <v>173</v>
       </c>
       <c r="D82" s="132">
         <f t="shared" si="19"/>
@@ -15024,10 +15147,10 @@
     </row>
     <row r="88" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="53" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C88" s="56" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D88" s="132">
         <f t="shared" si="19"/>
@@ -15155,6 +15278,12 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -15169,12 +15298,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -15210,14 +15333,14 @@
   <sheetData>
     <row r="1" spans="2:15" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="83" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C1" s="83"/>
       <c r="D1" s="83"/>
       <c r="E1" s="83"/>
       <c r="F1" s="83"/>
       <c r="G1" s="220" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H1" s="110"/>
       <c r="I1" s="110"/>
@@ -15229,7 +15352,7 @@
     </row>
     <row r="2" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G2" s="221" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H2" s="111"/>
       <c r="I2" s="111"/>
@@ -15254,7 +15377,7 @@
         <v>31</v>
       </c>
       <c r="G3" s="221" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H3" s="111"/>
       <c r="I3" s="111"/>
@@ -15264,7 +15387,7 @@
     </row>
     <row r="4" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G4" s="221" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H4" s="111"/>
       <c r="I4" s="111"/>
@@ -15274,7 +15397,7 @@
     </row>
     <row r="5" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G5" s="221" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H5" s="111"/>
       <c r="I5" s="111"/>
@@ -15299,7 +15422,7 @@
         <v>107</v>
       </c>
       <c r="O6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15338,10 +15461,10 @@
         <v>110</v>
       </c>
       <c r="E8" s="80" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F8" s="80" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G8" s="80" t="s">
         <v>111</v>
@@ -15392,7 +15515,7 @@
     </row>
     <row r="11" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="72" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
@@ -15411,7 +15534,7 @@
     </row>
     <row r="12" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="72" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
@@ -15563,7 +15686,7 @@
     </row>
     <row r="20" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
@@ -15581,12 +15704,12 @@
         <v>0</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
@@ -15604,7 +15727,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15657,7 +15780,7 @@
     </row>
     <row r="25" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="72" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="15"/>
@@ -15798,15 +15921,15 @@
       <c r="H39" s="111"/>
       <c r="I39" s="111"/>
       <c r="S39" s="172" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="261" t="s">
-        <v>177</v>
-      </c>
-      <c r="C40" s="262"/>
-      <c r="D40" s="263"/>
+      <c r="B40" s="271" t="s">
+        <v>176</v>
+      </c>
+      <c r="C40" s="272"/>
+      <c r="D40" s="273"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -15815,19 +15938,19 @@
         <v>0</v>
       </c>
       <c r="G40" s="192" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H40" s="198">
         <v>0.9</v>
       </c>
       <c r="I40" s="201" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J40" s="199">
         <v>0.95</v>
       </c>
       <c r="K40" s="194" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L40" s="200">
         <v>1</v>
@@ -15982,7 +16105,7 @@
     </row>
     <row r="44" spans="2:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="109" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C44" s="41" t="s">
         <v>143</v>
@@ -16126,33 +16249,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="264" t="s">
+      <c r="B48" s="274" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="265"/>
-      <c r="D48" s="265"/>
-      <c r="E48" s="265"/>
-      <c r="F48" s="265"/>
-      <c r="G48" s="265"/>
-      <c r="H48" s="265"/>
-      <c r="I48" s="265"/>
-      <c r="J48" s="265"/>
-      <c r="K48" s="265"/>
-      <c r="L48" s="288"/>
-      <c r="M48" s="271" t="s">
-        <v>186</v>
-      </c>
-      <c r="N48" s="272"/>
-      <c r="O48" s="272"/>
-      <c r="P48" s="272"/>
-      <c r="Q48" s="272"/>
-      <c r="R48" s="273"/>
+      <c r="C48" s="275"/>
+      <c r="D48" s="275"/>
+      <c r="E48" s="275"/>
+      <c r="F48" s="275"/>
+      <c r="G48" s="275"/>
+      <c r="H48" s="275"/>
+      <c r="I48" s="275"/>
+      <c r="J48" s="275"/>
+      <c r="K48" s="275"/>
+      <c r="L48" s="285"/>
+      <c r="M48" s="262" t="s">
+        <v>185</v>
+      </c>
+      <c r="N48" s="263"/>
+      <c r="O48" s="263"/>
+      <c r="P48" s="263"/>
+      <c r="Q48" s="263"/>
+      <c r="R48" s="264"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="286" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="289" t="s">
+      <c r="C49" s="286" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="255" t="s">
@@ -16161,49 +16284,49 @@
       <c r="E49" s="256"/>
       <c r="F49" s="256"/>
       <c r="G49" s="257"/>
-      <c r="H49" s="290" t="s">
+      <c r="H49" s="287" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="291"/>
-      <c r="J49" s="291"/>
-      <c r="K49" s="292"/>
-      <c r="L49" s="293" t="s">
+      <c r="I49" s="288"/>
+      <c r="J49" s="288"/>
+      <c r="K49" s="289"/>
+      <c r="L49" s="290" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="274" t="str">
+      <c r="M49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="274" t="str">
+      <c r="N49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="276" t="str">
+      <c r="O49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="276" t="str">
+      <c r="P49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="278" t="str">
+      <c r="Q49" s="269" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="278" t="str">
+      <c r="R49" s="269" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="270"/>
-      <c r="C50" s="270"/>
+      <c r="B50" s="261"/>
+      <c r="C50" s="261"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -16211,7 +16334,7 @@
         <v>150</v>
       </c>
       <c r="F50" s="70" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G50" s="70" t="s">
         <v>130</v>
@@ -16223,23 +16346,23 @@
         <v>150</v>
       </c>
       <c r="J50" s="113" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="294"/>
-      <c r="M50" s="275"/>
-      <c r="N50" s="275"/>
-      <c r="O50" s="277"/>
-      <c r="P50" s="277"/>
-      <c r="Q50" s="279"/>
-      <c r="R50" s="279"/>
+      <c r="L50" s="291"/>
+      <c r="M50" s="266"/>
+      <c r="N50" s="266"/>
+      <c r="O50" s="268"/>
+      <c r="P50" s="268"/>
+      <c r="Q50" s="270"/>
+      <c r="R50" s="270"/>
       <c r="T50" s="178" t="s">
+        <v>215</v>
+      </c>
+      <c r="U50" s="178" t="s">
         <v>216</v>
-      </c>
-      <c r="U50" s="178" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="51" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16312,7 +16435,7 @@
         <v>124</v>
       </c>
       <c r="U51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="52" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16390,10 +16513,10 @@
     </row>
     <row r="53" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="136" t="s">
+        <v>171</v>
+      </c>
+      <c r="C53" s="137" t="s">
         <v>172</v>
-      </c>
-      <c r="C53" s="137" t="s">
-        <v>173</v>
       </c>
       <c r="D53" s="138">
         <f>TARGETS!AK7</f>
@@ -16455,10 +16578,10 @@
         <v>0</v>
       </c>
       <c r="T53" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="U53" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="54" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16531,7 +16654,7 @@
         <v>115</v>
       </c>
       <c r="U54" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="55" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16539,7 +16662,7 @@
         <v>73</v>
       </c>
       <c r="C55" s="55" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D55" s="118">
         <f>TARGETS!AK9</f>
@@ -16601,10 +16724,10 @@
         <v>0</v>
       </c>
       <c r="T55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="U55" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16674,10 +16797,10 @@
         <v>0</v>
       </c>
       <c r="T56" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="U56" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="57" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16750,7 +16873,7 @@
         <v>120</v>
       </c>
       <c r="U57" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16823,15 +16946,15 @@
         <v>125</v>
       </c>
       <c r="U58" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="59" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="136" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C59" s="137" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D59" s="138">
         <f>TARGETS!AK13</f>
@@ -16893,10 +17016,10 @@
         <v>0</v>
       </c>
       <c r="T59" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="U59" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="60" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16904,7 +17027,7 @@
         <v>80</v>
       </c>
       <c r="C60" s="56" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D60" s="119">
         <f>TARGETS!AK14</f>
@@ -16966,10 +17089,10 @@
         <v>0</v>
       </c>
       <c r="T60" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="U60" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="61" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -17042,7 +17165,7 @@
         <v>126</v>
       </c>
       <c r="U61" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="62" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -17115,7 +17238,7 @@
         <v>112</v>
       </c>
       <c r="U62" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -17188,7 +17311,7 @@
         <v>127</v>
       </c>
       <c r="U63" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="64" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -17336,21 +17459,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="285" t="s">
+      <c r="B67" s="292" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="286"/>
-      <c r="D67" s="286"/>
-      <c r="E67" s="286"/>
+      <c r="C67" s="293"/>
+      <c r="D67" s="293"/>
+      <c r="E67" s="293"/>
       <c r="F67" s="295"/>
-      <c r="G67" s="271" t="s">
-        <v>186</v>
-      </c>
-      <c r="H67" s="272"/>
-      <c r="I67" s="272"/>
-      <c r="J67" s="272"/>
-      <c r="K67" s="272"/>
-      <c r="L67" s="273"/>
+      <c r="G67" s="262" t="s">
+        <v>185</v>
+      </c>
+      <c r="H67" s="263"/>
+      <c r="I67" s="263"/>
+      <c r="J67" s="263"/>
+      <c r="K67" s="263"/>
+      <c r="L67" s="264"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -17665,16 +17788,16 @@
     <row r="76" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="251" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C77" s="252"/>
       <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="270" t="s">
+      <c r="B78" s="261" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="270" t="s">
+      <c r="C78" s="261" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -17685,13 +17808,13 @@
       <c r="B79" s="260"/>
       <c r="C79" s="260"/>
       <c r="D79" s="70" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T79" s="178" t="s">
+        <v>215</v>
+      </c>
+      <c r="U79" s="178" t="s">
         <v>216</v>
-      </c>
-      <c r="U79" s="178" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="80" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -17736,10 +17859,10 @@
     </row>
     <row r="82" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="C82" s="56" t="s">
         <v>172</v>
-      </c>
-      <c r="C82" s="56" t="s">
-        <v>173</v>
       </c>
       <c r="D82" s="132">
         <f t="shared" si="19"/>
@@ -17856,10 +17979,10 @@
     </row>
     <row r="88" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="53" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C88" s="56" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D88" s="132">
         <f t="shared" si="19"/>
@@ -17987,6 +18110,12 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -18001,12 +18130,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -18040,22 +18163,21 @@
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="30" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.85546875" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" customWidth="1"/>
+    <col min="7" max="12" width="12.85546875" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.140625" customWidth="1"/>
+    <col min="15" max="15" width="8.28515625" customWidth="1"/>
+    <col min="16" max="17" width="11.140625" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" customWidth="1"/>
+    <col min="19" max="20" width="11.140625" customWidth="1"/>
+    <col min="21" max="21" width="8.28515625" customWidth="1"/>
+    <col min="22" max="22" width="12.85546875" customWidth="1"/>
+    <col min="23" max="23" width="11.140625" customWidth="1"/>
+    <col min="24" max="24" width="8.28515625" customWidth="1"/>
+    <col min="25" max="30" width="11.140625" customWidth="1"/>
+    <col min="31" max="33" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="5.7109375" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="8.28515625" bestFit="1" customWidth="1"/>
@@ -18185,7 +18307,7 @@
         <v>44</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>45</v>
@@ -18194,7 +18316,7 @@
         <v>46</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>47</v>
@@ -18203,7 +18325,7 @@
         <v>48</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>49</v>
@@ -18212,7 +18334,7 @@
         <v>50</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P4" s="4" t="s">
         <v>51</v>
@@ -18221,7 +18343,7 @@
         <v>52</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="S4" s="4" t="s">
         <v>53</v>
@@ -18230,7 +18352,7 @@
         <v>54</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="V4" s="4" t="s">
         <v>55</v>
@@ -18239,7 +18361,7 @@
         <v>56</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Y4" s="4" t="s">
         <v>57</v>
@@ -18248,7 +18370,7 @@
         <v>58</v>
       </c>
       <c r="AA4" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AB4" s="4" t="s">
         <v>59</v>
@@ -18257,7 +18379,7 @@
         <v>60</v>
       </c>
       <c r="AD4" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AE4" s="4" t="s">
         <v>61</v>
@@ -18266,7 +18388,7 @@
         <v>62</v>
       </c>
       <c r="AG4" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AH4" s="4" t="s">
         <v>63</v>
@@ -18275,7 +18397,7 @@
         <v>64</v>
       </c>
       <c r="AJ4" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AK4" s="4" t="s">
         <v>65</v>
@@ -18284,7 +18406,7 @@
         <v>66</v>
       </c>
       <c r="AM4" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="2:39" x14ac:dyDescent="0.25">
@@ -18376,13 +18498,13 @@
         <v>175769404.33699557</v>
       </c>
       <c r="AE5" s="7">
-        <v>0</v>
+        <v>264756949.64136907</v>
       </c>
       <c r="AF5" s="7">
-        <v>0</v>
+        <v>58508748.413354225</v>
       </c>
       <c r="AG5" s="7">
-        <v>0</v>
+        <v>172968793.98622558</v>
       </c>
       <c r="AH5" s="7">
         <v>0</v>
@@ -18492,13 +18614,13 @@
         <v>426693359.74293905</v>
       </c>
       <c r="AE6" s="7">
-        <v>0</v>
+        <v>180052976.96171179</v>
       </c>
       <c r="AF6" s="7">
-        <v>0</v>
+        <v>163445127.22039506</v>
       </c>
       <c r="AG6" s="7">
-        <v>0</v>
+        <v>423892749.39216906</v>
       </c>
       <c r="AH6" s="7">
         <v>0</v>
@@ -18521,10 +18643,10 @@
     </row>
     <row r="7" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B7" s="128" t="s">
+        <v>171</v>
+      </c>
+      <c r="C7" s="129" t="s">
         <v>172</v>
-      </c>
-      <c r="C7" s="129" t="s">
-        <v>173</v>
       </c>
       <c r="D7" s="130">
         <v>241473268</v>
@@ -18599,8 +18721,12 @@
       <c r="AD7" s="7">
         <v>0</v>
       </c>
-      <c r="AE7" s="7"/>
-      <c r="AF7" s="7"/>
+      <c r="AE7" s="7">
+        <v>262953105.06301075</v>
+      </c>
+      <c r="AF7" s="7">
+        <v>0</v>
+      </c>
       <c r="AG7" s="7">
         <v>0</v>
       </c>
@@ -18704,13 +18830,13 @@
         <v>86722202.085279256</v>
       </c>
       <c r="AE8" s="7">
-        <v>0</v>
+        <v>590954252.3415246</v>
       </c>
       <c r="AF8" s="7">
-        <v>0</v>
+        <v>33662936.863966122</v>
       </c>
       <c r="AG8" s="7">
-        <v>0</v>
+        <v>83921591.734509259</v>
       </c>
       <c r="AH8" s="7">
         <v>0</v>
@@ -18736,7 +18862,7 @@
         <v>73</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>181</v>
+        <v>221</v>
       </c>
       <c r="D9" s="7">
         <v>475292301</v>
@@ -18820,13 +18946,13 @@
         <v>468117447.23398483</v>
       </c>
       <c r="AE9" s="7">
-        <v>0</v>
+        <v>5575801.9517222047</v>
       </c>
       <c r="AF9" s="7">
-        <v>0</v>
+        <v>63507750.38497854</v>
       </c>
       <c r="AG9" s="7">
-        <v>0</v>
+        <v>468117447.23398483</v>
       </c>
       <c r="AH9" s="7">
         <v>0</v>
@@ -18852,7 +18978,7 @@
         <v>75</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D10" s="7">
         <v>519152974</v>
@@ -18936,13 +19062,13 @@
         <v>186960308.99004278</v>
       </c>
       <c r="AE10" s="7">
-        <v>0</v>
+        <v>267520870.86594501</v>
       </c>
       <c r="AF10" s="7">
-        <v>0</v>
+        <v>105132391.14913487</v>
       </c>
       <c r="AG10" s="7">
-        <v>0</v>
+        <v>184159698.63927278</v>
       </c>
       <c r="AH10" s="7">
         <v>0</v>
@@ -19052,13 +19178,13 @@
         <v>345934429.35750455</v>
       </c>
       <c r="AE11" s="7">
-        <v>0</v>
+        <v>664600150.5441153</v>
       </c>
       <c r="AF11" s="7">
-        <v>0</v>
+        <v>83317068.128031164</v>
       </c>
       <c r="AG11" s="7">
-        <v>0</v>
+        <v>343133819.00673455</v>
       </c>
       <c r="AH11" s="7">
         <v>0</v>
@@ -19168,13 +19294,13 @@
         <v>252410270.18814293</v>
       </c>
       <c r="AE12" s="7">
-        <v>0</v>
+        <v>259993077.39884707</v>
       </c>
       <c r="AF12" s="7">
-        <v>0</v>
+        <v>86845105.094943255</v>
       </c>
       <c r="AG12" s="7">
-        <v>0</v>
+        <v>249609659.83737293</v>
       </c>
       <c r="AH12" s="7">
         <v>0</v>
@@ -19197,10 +19323,10 @@
     </row>
     <row r="13" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B13" s="128" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C13" s="129" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D13" s="130">
         <v>404133664</v>
@@ -19275,8 +19401,12 @@
       <c r="AD13" s="7">
         <v>0</v>
       </c>
-      <c r="AE13" s="7"/>
-      <c r="AF13" s="7"/>
+      <c r="AE13" s="7">
+        <v>443846715.57642001</v>
+      </c>
+      <c r="AF13" s="7">
+        <v>0</v>
+      </c>
       <c r="AG13" s="7">
         <v>0</v>
       </c>
@@ -19296,7 +19426,7 @@
         <v>80</v>
       </c>
       <c r="C14" s="126" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D14" s="127">
         <v>479914486</v>
@@ -19380,13 +19510,13 @@
         <v>118273050.61307113</v>
       </c>
       <c r="AE14" s="7">
-        <v>0</v>
+        <v>345737237.66667807</v>
       </c>
       <c r="AF14" s="7">
-        <v>0</v>
+        <v>99843502.42153886</v>
       </c>
       <c r="AG14" s="7">
-        <v>0</v>
+        <v>115472440.26230113</v>
       </c>
       <c r="AH14" s="7">
         <v>0</v>
@@ -19496,13 +19626,13 @@
         <v>171338208.10934076</v>
       </c>
       <c r="AE15" s="7">
-        <v>0</v>
+        <v>476796144.98316145</v>
       </c>
       <c r="AF15" s="7">
-        <v>0</v>
+        <v>53126030.965583593</v>
       </c>
       <c r="AG15" s="7">
-        <v>0</v>
+        <v>168537597.75857076</v>
       </c>
       <c r="AH15" s="7">
         <v>0</v>
@@ -19612,13 +19742,13 @@
         <v>262652391.23828724</v>
       </c>
       <c r="AE16" s="7">
-        <v>0</v>
+        <v>168507149.83198008</v>
       </c>
       <c r="AF16" s="7">
-        <v>0</v>
+        <v>30531298.995438561</v>
       </c>
       <c r="AG16" s="7">
-        <v>0</v>
+        <v>259851780.88751724</v>
       </c>
       <c r="AH16" s="7">
         <v>0</v>
@@ -19728,13 +19858,13 @@
         <v>245375263.48110652</v>
       </c>
       <c r="AE17" s="7">
-        <v>0</v>
+        <v>409968842.36459517</v>
       </c>
       <c r="AF17" s="7">
-        <v>0</v>
+        <v>308297473.95300913</v>
       </c>
       <c r="AG17" s="7">
-        <v>0</v>
+        <v>242574653.13033652</v>
       </c>
       <c r="AH17" s="7">
         <v>0</v>
@@ -19844,13 +19974,13 @@
         <v>204567860.95199081</v>
       </c>
       <c r="AE18" s="7">
-        <v>0</v>
+        <v>123323413.46844758</v>
       </c>
       <c r="AF18" s="7">
-        <v>0</v>
+        <v>193690629.51885673</v>
       </c>
       <c r="AG18" s="7">
-        <v>0</v>
+        <v>201767250.60122082</v>
       </c>
       <c r="AH18" s="7">
         <v>0</v>
@@ -19968,7 +20098,7 @@
         <v>256257503.30496463</v>
       </c>
       <c r="M22" s="7">
-        <v>0</v>
+        <v>269378070.68085116</v>
       </c>
       <c r="N22" s="7">
         <v>0</v>
@@ -19982,7 +20112,7 @@
         <v>94</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D23" s="7">
         <v>439764978</v>
@@ -20012,7 +20142,7 @@
         <v>399558412.3049646</v>
       </c>
       <c r="M23" s="7">
-        <v>0</v>
+        <v>412678979.6808511</v>
       </c>
       <c r="N23" s="7">
         <v>0</v>
@@ -20056,7 +20186,7 @@
         <v>1084609616.3049645</v>
       </c>
       <c r="M24" s="7">
-        <v>0</v>
+        <v>1097730183.680851</v>
       </c>
       <c r="N24" s="7">
         <v>0</v>
@@ -20194,14 +20324,14 @@
   <sheetData>
     <row r="1" spans="2:17" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B1" s="83" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C1" s="83"/>
       <c r="D1" s="83"/>
       <c r="E1" s="83"/>
       <c r="F1" s="83"/>
       <c r="G1" s="215" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H1" s="83"/>
       <c r="I1" s="83"/>
@@ -20213,7 +20343,7 @@
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="G2" s="216" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J2" s="217">
         <f ca="1">E3</f>
@@ -20236,7 +20366,7 @@
         <v>31</v>
       </c>
       <c r="G3" s="216" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J3" s="218">
         <v>0</v>
@@ -20244,7 +20374,7 @@
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="G4" s="216" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J4" s="218">
         <v>0</v>
@@ -20252,7 +20382,7 @@
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="G5" s="216" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J5" s="218"/>
     </row>
@@ -21761,14 +21891,14 @@
   <sheetData>
     <row r="1" spans="2:17" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B1" s="83" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C1" s="83"/>
       <c r="D1" s="83"/>
       <c r="E1" s="83"/>
       <c r="F1" s="83"/>
       <c r="G1" s="215" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H1" s="83"/>
       <c r="I1" s="83"/>
@@ -21780,7 +21910,7 @@
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="G2" s="216" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J2" s="217">
         <f ca="1">E3</f>
@@ -21803,7 +21933,7 @@
         <v>28</v>
       </c>
       <c r="G3" s="216" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J3" s="218">
         <v>0</v>
@@ -21811,7 +21941,7 @@
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="G4" s="216" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J4" s="218">
         <v>0</v>
@@ -21819,7 +21949,7 @@
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="G5" s="216" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J5" s="218"/>
     </row>
@@ -23338,7 +23468,7 @@
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
       <c r="G1" s="219" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H1" s="21"/>
       <c r="I1" s="21"/>
@@ -23350,7 +23480,7 @@
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="G2" s="216" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J2" s="217">
         <f ca="1">E3</f>
@@ -23373,7 +23503,7 @@
         <v>31</v>
       </c>
       <c r="G3" s="216" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J3" s="218">
         <v>0</v>
@@ -23381,7 +23511,7 @@
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="G4" s="216" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J4" s="218">
         <v>0</v>
@@ -23389,7 +23519,7 @@
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="G5" s="216" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J5" s="218"/>
     </row>
@@ -23447,7 +23577,7 @@
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="72" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C9" s="15">
         <v>188107.92</v>
@@ -23585,7 +23715,7 @@
         <v>282161.88</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E15" s="15">
         <v>282161.88</v>
@@ -23801,7 +23931,7 @@
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B29" s="72" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C29" s="15">
         <v>3087270.2699850001</v>
@@ -25139,7 +25269,7 @@
       <c r="E1" s="83"/>
       <c r="F1" s="83"/>
       <c r="G1" s="220" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H1" s="110"/>
       <c r="I1" s="110"/>
@@ -25151,7 +25281,7 @@
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="G2" s="221" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J2" s="217">
         <f ca="1">E3</f>
@@ -25174,7 +25304,7 @@
         <v>30</v>
       </c>
       <c r="G3" s="221" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J3" s="218">
         <v>0</v>
@@ -25182,7 +25312,7 @@
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="G4" s="221" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J4" s="218">
         <v>0</v>
@@ -25190,7 +25320,7 @@
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="G5" s="221" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J5" s="218"/>
     </row>
@@ -25241,7 +25371,7 @@
         <v>110</v>
       </c>
       <c r="E8" s="80" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F8" s="80" t="s">
         <v>111</v>
@@ -25421,7 +25551,7 @@
       </c>
       <c r="C15" s="133"/>
       <c r="D15" s="133" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E15" s="133"/>
       <c r="F15" s="133"/>
@@ -25474,7 +25604,7 @@
         <v>44657675.509999998</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F17" s="15">
         <v>400283795.43999302</v>
@@ -25555,7 +25685,7 @@
         <v>16467727.799813</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F20" s="15">
         <v>121782785.42740899</v>
@@ -25581,7 +25711,7 @@
         <v>136240384.927111</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F21" s="15">
         <v>193600324.34711099</v>
@@ -25598,13 +25728,13 @@
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C22" s="15">
         <v>38884328.600000001</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E22" s="15">
         <v>12315315.119999999</v>
@@ -25619,13 +25749,13 @@
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C23" s="15">
         <v>120550492.72</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E23" s="15">
         <v>17151621.32</v>
@@ -25706,7 +25836,7 @@
         <v>200253231.98958299</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F27" s="15">
         <v>863813055.77967799</v>
@@ -25782,15 +25912,15 @@
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.25">
       <c r="S40" s="178" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="261" t="s">
-        <v>178</v>
-      </c>
-      <c r="C41" s="262"/>
-      <c r="D41" s="263"/>
+      <c r="B41" s="271" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="272"/>
+      <c r="D41" s="273"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -25798,19 +25928,19 @@
         <v>1</v>
       </c>
       <c r="G41" s="192" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H41" s="198">
         <v>0.9</v>
       </c>
       <c r="I41" s="201" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J41" s="199">
         <v>0.95</v>
       </c>
       <c r="K41" s="194" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L41" s="200">
         <v>1</v>
@@ -26061,59 +26191,59 @@
       </c>
     </row>
     <row r="48" spans="2:19" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="264" t="s">
+      <c r="B48" s="274" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="265"/>
-      <c r="D48" s="265"/>
-      <c r="E48" s="265"/>
-      <c r="F48" s="265"/>
-      <c r="G48" s="265"/>
-      <c r="H48" s="265"/>
-      <c r="I48" s="265"/>
-      <c r="J48" s="265"/>
-      <c r="K48" s="271" t="s">
-        <v>186</v>
-      </c>
-      <c r="L48" s="272"/>
-      <c r="M48" s="272"/>
-      <c r="N48" s="272"/>
-      <c r="O48" s="272"/>
-      <c r="P48" s="273"/>
+      <c r="C48" s="275"/>
+      <c r="D48" s="275"/>
+      <c r="E48" s="275"/>
+      <c r="F48" s="275"/>
+      <c r="G48" s="275"/>
+      <c r="H48" s="275"/>
+      <c r="I48" s="275"/>
+      <c r="J48" s="275"/>
+      <c r="K48" s="262" t="s">
+        <v>185</v>
+      </c>
+      <c r="L48" s="263"/>
+      <c r="M48" s="263"/>
+      <c r="N48" s="263"/>
+      <c r="O48" s="263"/>
+      <c r="P48" s="264"/>
       <c r="Q48"/>
       <c r="R48"/>
     </row>
     <row r="49" spans="2:18" s="139" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="269" t="s">
+      <c r="B49" s="279" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="269" t="s">
+      <c r="C49" s="279" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="266" t="s">
+      <c r="D49" s="276" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="267"/>
-      <c r="F49" s="268"/>
+      <c r="E49" s="277"/>
+      <c r="F49" s="278"/>
       <c r="G49" s="140" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="140"/>
       <c r="I49" s="140"/>
-      <c r="J49" s="266" t="s">
+      <c r="J49" s="276" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="274" t="str">
+      <c r="K49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="274" t="str">
+      <c r="L49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="276" t="str">
+      <c r="M49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
@@ -26128,7 +26258,7 @@
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="278" t="str">
+      <c r="P49" s="269" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -26137,8 +26267,8 @@
       <c r="R49"/>
     </row>
     <row r="50" spans="2:18" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="269"/>
-      <c r="C50" s="269"/>
+      <c r="B50" s="279"/>
+      <c r="C50" s="279"/>
       <c r="D50" s="141" t="s">
         <v>149</v>
       </c>
@@ -26157,13 +26287,13 @@
       <c r="I50" s="142" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="266"/>
-      <c r="K50" s="275"/>
-      <c r="L50" s="275"/>
-      <c r="M50" s="277"/>
+      <c r="J50" s="276"/>
+      <c r="K50" s="266"/>
+      <c r="L50" s="266"/>
+      <c r="M50" s="268"/>
       <c r="N50" s="188"/>
       <c r="O50" s="183"/>
-      <c r="P50" s="279"/>
+      <c r="P50" s="270"/>
       <c r="Q50"/>
       <c r="R50"/>
     </row>
@@ -26293,10 +26423,10 @@
     </row>
     <row r="53" spans="2:18" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="153" t="s">
+        <v>171</v>
+      </c>
+      <c r="C53" s="154" t="s">
         <v>172</v>
-      </c>
-      <c r="C53" s="154" t="s">
-        <v>173</v>
       </c>
       <c r="D53" s="146">
         <f>TARGETS!M7</f>
@@ -26665,10 +26795,10 @@
     </row>
     <row r="59" spans="2:18" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="153" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C59" s="154" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D59" s="146">
         <f>TARGETS!M13</f>
@@ -27495,7 +27625,7 @@
     </row>
     <row r="77" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="251" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C77" s="252"/>
       <c r="D77" s="253"/>
@@ -27504,10 +27634,10 @@
       <c r="I77"/>
     </row>
     <row r="78" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="270" t="s">
+      <c r="B78" s="261" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="270" t="s">
+      <c r="C78" s="261" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -27521,7 +27651,7 @@
       <c r="B79" s="260"/>
       <c r="C79" s="260"/>
       <c r="D79" s="70" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G79"/>
       <c r="H79"/>
@@ -27553,10 +27683,10 @@
     </row>
     <row r="82" spans="2:4" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="151" t="s">
+        <v>171</v>
+      </c>
+      <c r="C82" s="152" t="s">
         <v>172</v>
-      </c>
-      <c r="C82" s="152" t="s">
-        <v>173</v>
       </c>
       <c r="D82" s="158">
         <f>IF(E22="",0,E22)</f>
@@ -27624,10 +27754,10 @@
     </row>
     <row r="88" spans="2:4" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="151" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C88" s="152" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D88" s="158">
         <f>IF(E23="",0,E23)</f>
@@ -27706,6 +27836,13 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="J49:J50"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
     <mergeCell ref="K48:P48"/>
@@ -27715,13 +27852,6 @@
     <mergeCell ref="P49:P50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="J49:J50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="26" priority="8">
@@ -27767,7 +27897,7 @@
       <c r="E1" s="83"/>
       <c r="F1" s="83"/>
       <c r="G1" s="220" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H1" s="110"/>
       <c r="I1" s="110"/>
@@ -27779,7 +27909,7 @@
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="G2" s="221" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H2" s="111"/>
       <c r="I2" s="111"/>
@@ -27804,7 +27934,7 @@
         <v>31</v>
       </c>
       <c r="G3" s="221" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H3" s="111"/>
       <c r="I3" s="111"/>
@@ -27814,7 +27944,7 @@
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="G4" s="221" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H4" s="111"/>
       <c r="I4" s="111"/>
@@ -27824,7 +27954,7 @@
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="G5" s="221" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H5" s="111"/>
       <c r="I5" s="111"/>
@@ -27879,7 +28009,7 @@
         <v>110</v>
       </c>
       <c r="E8" s="80" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F8" s="80" t="s">
         <v>111</v>
@@ -28117,7 +28247,7 @@
         <v>42787524.299999997</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F17" s="15">
         <v>357138221.57999802</v>
@@ -28246,13 +28376,13 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C22" s="15">
         <v>197567845.80000001</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E22" s="15">
         <v>12832432.08</v>
@@ -28266,13 +28396,13 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C23" s="15">
         <v>300521523.82997501</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E23" s="15">
         <v>13813693.32</v>
@@ -28479,12 +28609,12 @@
       <c r="H40" s="111"/>
       <c r="I40" s="111"/>
       <c r="S40" s="178" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="280" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C41" s="281"/>
       <c r="D41" s="282"/>
@@ -28495,19 +28625,19 @@
         <v>0.97</v>
       </c>
       <c r="G41" s="192" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H41" s="198">
         <v>0.9</v>
       </c>
       <c r="I41" s="201" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J41" s="199">
         <v>0.95</v>
       </c>
       <c r="K41" s="194" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L41" s="200">
         <v>1</v>
@@ -28761,25 +28891,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="264" t="s">
+      <c r="B48" s="274" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="265"/>
-      <c r="D48" s="265"/>
-      <c r="E48" s="265"/>
-      <c r="F48" s="265"/>
-      <c r="G48" s="265"/>
-      <c r="H48" s="265"/>
-      <c r="I48" s="265"/>
-      <c r="J48" s="265"/>
-      <c r="K48" s="271" t="s">
-        <v>186</v>
-      </c>
-      <c r="L48" s="272"/>
-      <c r="M48" s="272"/>
-      <c r="N48" s="272"/>
-      <c r="O48" s="272"/>
-      <c r="P48" s="273"/>
+      <c r="C48" s="275"/>
+      <c r="D48" s="275"/>
+      <c r="E48" s="275"/>
+      <c r="F48" s="275"/>
+      <c r="G48" s="275"/>
+      <c r="H48" s="275"/>
+      <c r="I48" s="275"/>
+      <c r="J48" s="275"/>
+      <c r="K48" s="262" t="s">
+        <v>185</v>
+      </c>
+      <c r="L48" s="263"/>
+      <c r="M48" s="263"/>
+      <c r="N48" s="263"/>
+      <c r="O48" s="263"/>
+      <c r="P48" s="264"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="260" t="s">
@@ -28801,32 +28931,32 @@
       <c r="J49" s="255" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="274" t="str">
+      <c r="K49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="274" t="str">
+      <c r="L49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="276" t="str">
+      <c r="M49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="276" t="str">
+      <c r="N49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="278" t="str">
+      <c r="O49" s="269" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="278" t="str">
+      <c r="P49" s="269" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -28854,12 +28984,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="255"/>
-      <c r="K50" s="275"/>
-      <c r="L50" s="275"/>
-      <c r="M50" s="277"/>
-      <c r="N50" s="277"/>
-      <c r="O50" s="279"/>
-      <c r="P50" s="279"/>
+      <c r="K50" s="266"/>
+      <c r="L50" s="266"/>
+      <c r="M50" s="268"/>
+      <c r="N50" s="268"/>
+      <c r="O50" s="270"/>
+      <c r="P50" s="270"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="167" t="s">
@@ -28983,10 +29113,10 @@
     </row>
     <row r="53" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="136" t="s">
+        <v>171</v>
+      </c>
+      <c r="C53" s="137" t="s">
         <v>172</v>
-      </c>
-      <c r="C53" s="137" t="s">
-        <v>173</v>
       </c>
       <c r="D53" s="138">
         <f>TARGETS!P7</f>
@@ -29343,10 +29473,10 @@
     </row>
     <row r="59" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="136" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C59" s="137" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D59" s="138">
         <f>TARGETS!P13</f>
@@ -30090,16 +30220,16 @@
     </row>
     <row r="77" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="251" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C77" s="252"/>
       <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="270" t="s">
+      <c r="B78" s="261" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="270" t="s">
+      <c r="C78" s="261" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -30110,7 +30240,7 @@
       <c r="B79" s="260"/>
       <c r="C79" s="260"/>
       <c r="D79" s="70" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="80" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -30139,10 +30269,10 @@
     </row>
     <row r="82" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="167" t="s">
+        <v>171</v>
+      </c>
+      <c r="C82" s="168" t="s">
         <v>172</v>
-      </c>
-      <c r="C82" s="168" t="s">
-        <v>173</v>
       </c>
       <c r="D82" s="158">
         <f>IF(E22="",0,E22)</f>
@@ -30211,10 +30341,10 @@
     </row>
     <row r="88" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="167" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C88" s="168" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D88" s="158">
         <f>IF(E23="",0,E23)</f>
@@ -30293,6 +30423,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -30300,17 +30441,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -30356,7 +30486,7 @@
       <c r="E1" s="83"/>
       <c r="F1" s="83"/>
       <c r="G1" s="220" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H1" s="110"/>
       <c r="I1" s="110"/>
@@ -30368,7 +30498,7 @@
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="G2" s="221" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H2" s="111"/>
       <c r="I2" s="111"/>
@@ -30393,7 +30523,7 @@
         <v>30</v>
       </c>
       <c r="G3" s="221" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H3" s="111"/>
       <c r="I3" s="111"/>
@@ -30403,7 +30533,7 @@
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="G4" s="221" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H4" s="111"/>
       <c r="I4" s="111"/>
@@ -30413,7 +30543,7 @@
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="G5" s="221" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H5" s="111"/>
       <c r="I5" s="111"/>
@@ -30468,7 +30598,7 @@
         <v>110</v>
       </c>
       <c r="E8" s="80" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F8" s="80" t="s">
         <v>111</v>
@@ -30706,7 +30836,7 @@
         <v>50693884.710000001</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F17" s="15">
         <v>418857650.18890601</v>
@@ -30835,13 +30965,13 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C22" s="15">
         <v>167671841.09999999</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E22" s="15">
         <v>12540540.199999999</v>
@@ -30855,13 +30985,13 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C23" s="15">
         <v>388937679.18000001</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E23" s="15">
         <v>17519368.899999999</v>
@@ -31064,15 +31194,15 @@
       <c r="H40" s="111"/>
       <c r="I40" s="111"/>
       <c r="S40" s="178" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="261" t="s">
-        <v>180</v>
-      </c>
-      <c r="C41" s="262"/>
-      <c r="D41" s="263"/>
+      <c r="B41" s="271" t="s">
+        <v>179</v>
+      </c>
+      <c r="C41" s="272"/>
+      <c r="D41" s="273"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -31081,19 +31211,19 @@
         <v>1</v>
       </c>
       <c r="G41" s="192" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H41" s="198">
         <v>0.9</v>
       </c>
       <c r="I41" s="201" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J41" s="199">
         <v>0.95</v>
       </c>
       <c r="K41" s="194" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L41" s="200">
         <v>1</v>
@@ -31347,25 +31477,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="264" t="s">
+      <c r="B48" s="274" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="265"/>
-      <c r="D48" s="265"/>
-      <c r="E48" s="265"/>
-      <c r="F48" s="265"/>
-      <c r="G48" s="265"/>
-      <c r="H48" s="265"/>
-      <c r="I48" s="265"/>
-      <c r="J48" s="265"/>
-      <c r="K48" s="271" t="s">
-        <v>186</v>
-      </c>
-      <c r="L48" s="272"/>
-      <c r="M48" s="272"/>
-      <c r="N48" s="272"/>
-      <c r="O48" s="272"/>
-      <c r="P48" s="273"/>
+      <c r="C48" s="275"/>
+      <c r="D48" s="275"/>
+      <c r="E48" s="275"/>
+      <c r="F48" s="275"/>
+      <c r="G48" s="275"/>
+      <c r="H48" s="275"/>
+      <c r="I48" s="275"/>
+      <c r="J48" s="275"/>
+      <c r="K48" s="262" t="s">
+        <v>185</v>
+      </c>
+      <c r="L48" s="263"/>
+      <c r="M48" s="263"/>
+      <c r="N48" s="263"/>
+      <c r="O48" s="263"/>
+      <c r="P48" s="264"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="260" t="s">
@@ -31387,32 +31517,32 @@
       <c r="J49" s="255" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="274" t="str">
+      <c r="K49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="274" t="str">
+      <c r="L49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="276" t="str">
+      <c r="M49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="276" t="str">
+      <c r="N49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="278" t="str">
+      <c r="O49" s="269" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="278" t="str">
+      <c r="P49" s="269" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -31440,12 +31570,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="255"/>
-      <c r="K50" s="275"/>
-      <c r="L50" s="275"/>
-      <c r="M50" s="277"/>
-      <c r="N50" s="277"/>
-      <c r="O50" s="279"/>
-      <c r="P50" s="279"/>
+      <c r="K50" s="266"/>
+      <c r="L50" s="266"/>
+      <c r="M50" s="268"/>
+      <c r="N50" s="268"/>
+      <c r="O50" s="270"/>
+      <c r="P50" s="270"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -31569,10 +31699,10 @@
     </row>
     <row r="53" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="136" t="s">
+        <v>171</v>
+      </c>
+      <c r="C53" s="137" t="s">
         <v>172</v>
-      </c>
-      <c r="C53" s="137" t="s">
-        <v>173</v>
       </c>
       <c r="D53" s="138">
         <f>TARGETS!S7</f>
@@ -31929,10 +32059,10 @@
     </row>
     <row r="59" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="136" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C59" s="137" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D59" s="138">
         <f>TARGETS!S13</f>
@@ -32676,16 +32806,16 @@
     </row>
     <row r="77" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="251" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C77" s="252"/>
       <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="270" t="s">
+      <c r="B78" s="261" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="270" t="s">
+      <c r="C78" s="261" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -32696,7 +32826,7 @@
       <c r="B79" s="260"/>
       <c r="C79" s="260"/>
       <c r="D79" s="70" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="80" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -32723,10 +32853,10 @@
     </row>
     <row r="82" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="C82" s="56" t="s">
         <v>172</v>
-      </c>
-      <c r="C82" s="56" t="s">
-        <v>173</v>
       </c>
       <c r="D82" s="107">
         <v>12540540.199999999</v>
@@ -32790,10 +32920,10 @@
     </row>
     <row r="88" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="53" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C88" s="56" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D88" s="107">
         <v>17519368.899999999</v>
@@ -32866,6 +32996,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -32873,17 +33014,6 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -32942,7 +33072,7 @@
       <c r="E1" s="83"/>
       <c r="F1" s="83"/>
       <c r="G1" s="220" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H1" s="110"/>
       <c r="I1" s="110"/>
@@ -32954,7 +33084,7 @@
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="G2" s="221" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H2" s="111"/>
       <c r="I2" s="111"/>
@@ -32979,7 +33109,7 @@
         <v>31</v>
       </c>
       <c r="G3" s="221" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H3" s="111"/>
       <c r="I3" s="111"/>
@@ -32989,7 +33119,7 @@
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="G4" s="221" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H4" s="111"/>
       <c r="I4" s="111"/>
@@ -32999,7 +33129,7 @@
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="G5" s="221" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H5" s="111"/>
       <c r="I5" s="111"/>
@@ -33054,7 +33184,7 @@
         <v>110</v>
       </c>
       <c r="E8" s="80" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F8" s="80" t="s">
         <v>111</v>
@@ -33151,7 +33281,7 @@
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="72" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C12" s="15">
         <v>341819821.47863901</v>
@@ -33160,7 +33290,7 @@
         <v>43800016.100000001</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F12" s="15">
         <v>385619837.57863897</v>
@@ -33375,13 +33505,13 @@
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C20" s="15">
         <v>195476199.69999999</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E20" s="15">
         <v>11387387.08</v>
@@ -33402,13 +33532,13 @@
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C21" s="15">
         <v>288524887.39999998</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E21" s="15">
         <v>15855585.16</v>
@@ -33489,7 +33619,7 @@
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="72" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C25" s="15">
         <v>267316450.13510299</v>
@@ -33509,7 +33639,7 @@
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="72" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C26" s="15">
         <v>138084633.55645701</v>
@@ -33518,7 +33648,7 @@
         <v>103844000.433377</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F26" s="15">
         <v>241928633.98983401</v>
@@ -33658,15 +33788,15 @@
       <c r="H40" s="111"/>
       <c r="I40" s="111"/>
       <c r="S40" s="172" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41" spans="2:19" s="191" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="261" t="s">
-        <v>189</v>
-      </c>
-      <c r="C41" s="262"/>
-      <c r="D41" s="263"/>
+      <c r="B41" s="271" t="s">
+        <v>188</v>
+      </c>
+      <c r="C41" s="272"/>
+      <c r="D41" s="273"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -33675,19 +33805,19 @@
         <v>1</v>
       </c>
       <c r="G41" s="192" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H41" s="198">
         <v>0.9</v>
       </c>
       <c r="I41" s="193" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J41" s="199">
         <v>0.95</v>
       </c>
       <c r="K41" s="194" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L41" s="200">
         <v>1</v>
@@ -33941,25 +34071,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="264" t="s">
+      <c r="B48" s="274" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="265"/>
-      <c r="D48" s="265"/>
-      <c r="E48" s="265"/>
-      <c r="F48" s="265"/>
-      <c r="G48" s="265"/>
-      <c r="H48" s="265"/>
-      <c r="I48" s="265"/>
-      <c r="J48" s="265"/>
-      <c r="K48" s="271" t="s">
-        <v>186</v>
-      </c>
-      <c r="L48" s="272"/>
-      <c r="M48" s="272"/>
-      <c r="N48" s="272"/>
-      <c r="O48" s="272"/>
-      <c r="P48" s="273"/>
+      <c r="C48" s="275"/>
+      <c r="D48" s="275"/>
+      <c r="E48" s="275"/>
+      <c r="F48" s="275"/>
+      <c r="G48" s="275"/>
+      <c r="H48" s="275"/>
+      <c r="I48" s="275"/>
+      <c r="J48" s="275"/>
+      <c r="K48" s="262" t="s">
+        <v>185</v>
+      </c>
+      <c r="L48" s="263"/>
+      <c r="M48" s="263"/>
+      <c r="N48" s="263"/>
+      <c r="O48" s="263"/>
+      <c r="P48" s="264"/>
     </row>
     <row r="49" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="260" t="s">
@@ -33981,22 +34111,22 @@
       <c r="J49" s="255" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="274" t="str">
+      <c r="K49" s="265" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="274" t="str">
+      <c r="L49" s="265" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="276" t="str">
+      <c r="M49" s="267" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="276" t="str">
+      <c r="N49" s="267" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
@@ -34034,10 +34164,10 @@
         <v>130</v>
       </c>
       <c r="J50" s="255"/>
-      <c r="K50" s="275"/>
-      <c r="L50" s="275"/>
-      <c r="M50" s="277"/>
-      <c r="N50" s="277"/>
+      <c r="K50" s="266"/>
+      <c r="L50" s="266"/>
+      <c r="M50" s="268"/>
+      <c r="N50" s="268"/>
       <c r="O50" s="284"/>
       <c r="P50" s="284"/>
     </row>
@@ -34163,10 +34293,10 @@
     </row>
     <row r="53" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B53" s="136" t="s">
+        <v>171</v>
+      </c>
+      <c r="C53" s="137" t="s">
         <v>172</v>
-      </c>
-      <c r="C53" s="137" t="s">
-        <v>173</v>
       </c>
       <c r="D53" s="138">
         <f>TARGETS!V7</f>
@@ -34286,7 +34416,7 @@
         <v>73</v>
       </c>
       <c r="C55" s="55" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D55" s="118">
         <f>TARGETS!V9</f>
@@ -34523,10 +34653,10 @@
     </row>
     <row r="59" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B59" s="136" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C59" s="137" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D59" s="138">
         <f>TARGETS!V13</f>
@@ -35270,16 +35400,16 @@
     </row>
     <row r="77" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="251" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C77" s="252"/>
       <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="270" t="s">
+      <c r="B78" s="261" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="270" t="s">
+      <c r="C78" s="261" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -35290,7 +35420,7 @@
       <c r="B79" s="260"/>
       <c r="C79" s="260"/>
       <c r="D79" s="70" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="80" spans="2:16" x14ac:dyDescent="0.25">
@@ -35319,10 +35449,10 @@
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B82" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="C82" s="56" t="s">
         <v>172</v>
-      </c>
-      <c r="C82" s="56" t="s">
-        <v>173</v>
       </c>
       <c r="D82" s="131">
         <f>IF(E20="",0,E20)</f>
@@ -35346,7 +35476,7 @@
         <v>73</v>
       </c>
       <c r="C84" s="56" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D84" s="131">
         <f>0</f>
@@ -35391,10 +35521,10 @@
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B88" s="53" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C88" s="56" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D88" s="131">
         <f>IF(E21="",0,E21)</f>
@@ -35473,6 +35603,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
@@ -35486,11 +35621,6 @@
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2120" uniqueCount="228">
   <si>
     <t>📊  PANDUAN PENGGUNAAN — DATA PENCAPAIAN 2026</t>
   </si>
@@ -909,7 +909,7 @@
     <t>DATA PENCAPAIAN — GLOBAL —  30 SEPTEMBER 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL —  1 OKTOBER 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL —  2 OKTOBER 2026</t>
   </si>
 </sst>
 </file>
@@ -2562,6 +2562,33 @@
     <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2592,33 +2619,6 @@
     <xf numFmtId="0" fontId="48" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2632,6 +2632,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2653,15 +2662,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4305,11 +4305,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="271" t="s">
+      <c r="B40" s="261" t="s">
         <v>218</v>
       </c>
-      <c r="C40" s="272"/>
-      <c r="D40" s="273"/>
+      <c r="C40" s="262"/>
+      <c r="D40" s="263"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -4629,33 +4629,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="274" t="s">
+      <c r="B48" s="264" t="s">
         <v>212</v>
       </c>
-      <c r="C48" s="275"/>
-      <c r="D48" s="275"/>
-      <c r="E48" s="275"/>
-      <c r="F48" s="275"/>
-      <c r="G48" s="275"/>
-      <c r="H48" s="275"/>
-      <c r="I48" s="275"/>
-      <c r="J48" s="275"/>
-      <c r="K48" s="275"/>
-      <c r="L48" s="285"/>
-      <c r="M48" s="262" t="s">
+      <c r="C48" s="265"/>
+      <c r="D48" s="265"/>
+      <c r="E48" s="265"/>
+      <c r="F48" s="265"/>
+      <c r="G48" s="265"/>
+      <c r="H48" s="265"/>
+      <c r="I48" s="265"/>
+      <c r="J48" s="265"/>
+      <c r="K48" s="265"/>
+      <c r="L48" s="288"/>
+      <c r="M48" s="271" t="s">
         <v>185</v>
       </c>
-      <c r="N48" s="263"/>
-      <c r="O48" s="263"/>
-      <c r="P48" s="263"/>
-      <c r="Q48" s="263"/>
-      <c r="R48" s="264"/>
+      <c r="N48" s="272"/>
+      <c r="O48" s="272"/>
+      <c r="P48" s="272"/>
+      <c r="Q48" s="272"/>
+      <c r="R48" s="273"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="286" t="s">
+      <c r="B49" s="289" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="286" t="s">
+      <c r="C49" s="289" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="255" t="s">
@@ -4664,49 +4664,49 @@
       <c r="E49" s="256"/>
       <c r="F49" s="256"/>
       <c r="G49" s="257"/>
-      <c r="H49" s="287" t="s">
+      <c r="H49" s="290" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="288"/>
-      <c r="J49" s="288"/>
-      <c r="K49" s="289"/>
-      <c r="L49" s="290" t="s">
+      <c r="I49" s="291"/>
+      <c r="J49" s="291"/>
+      <c r="K49" s="292"/>
+      <c r="L49" s="293" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="265" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="267" t="str">
+      <c r="O49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="267" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="269" t="str">
+      <c r="Q49" s="278" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="269" t="str">
+      <c r="R49" s="278" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="261"/>
-      <c r="C50" s="261"/>
+      <c r="B50" s="270"/>
+      <c r="C50" s="270"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -4731,13 +4731,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="291"/>
-      <c r="M50" s="266"/>
-      <c r="N50" s="266"/>
-      <c r="O50" s="268"/>
-      <c r="P50" s="268"/>
-      <c r="Q50" s="270"/>
-      <c r="R50" s="270"/>
+      <c r="L50" s="294"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
+      <c r="O50" s="277"/>
+      <c r="P50" s="277"/>
+      <c r="Q50" s="279"/>
+      <c r="R50" s="279"/>
       <c r="T50" s="172" t="s">
         <v>215</v>
       </c>
@@ -5853,21 +5853,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="292" t="s">
+      <c r="B67" s="285" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="293"/>
-      <c r="D67" s="293"/>
-      <c r="E67" s="293"/>
-      <c r="F67" s="294"/>
-      <c r="G67" s="262" t="s">
+      <c r="C67" s="286"/>
+      <c r="D67" s="286"/>
+      <c r="E67" s="286"/>
+      <c r="F67" s="287"/>
+      <c r="G67" s="271" t="s">
         <v>185</v>
       </c>
-      <c r="H67" s="263"/>
-      <c r="I67" s="263"/>
-      <c r="J67" s="263"/>
-      <c r="K67" s="263"/>
-      <c r="L67" s="264"/>
+      <c r="H67" s="272"/>
+      <c r="I67" s="272"/>
+      <c r="J67" s="272"/>
+      <c r="K67" s="272"/>
+      <c r="L67" s="273"/>
     </row>
     <row r="68" spans="2:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -6186,10 +6186,10 @@
       <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="261" t="s">
+      <c r="B78" s="270" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="270" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -6501,12 +6501,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -6521,6 +6515,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -7264,11 +7264,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="271" t="s">
+      <c r="B40" s="261" t="s">
         <v>226</v>
       </c>
-      <c r="C40" s="272"/>
-      <c r="D40" s="273"/>
+      <c r="C40" s="262"/>
+      <c r="D40" s="263"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -7588,33 +7588,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="274" t="s">
+      <c r="B48" s="264" t="s">
         <v>212</v>
       </c>
-      <c r="C48" s="275"/>
-      <c r="D48" s="275"/>
-      <c r="E48" s="275"/>
-      <c r="F48" s="275"/>
-      <c r="G48" s="275"/>
-      <c r="H48" s="275"/>
-      <c r="I48" s="275"/>
-      <c r="J48" s="275"/>
-      <c r="K48" s="275"/>
-      <c r="L48" s="285"/>
-      <c r="M48" s="262" t="s">
+      <c r="C48" s="265"/>
+      <c r="D48" s="265"/>
+      <c r="E48" s="265"/>
+      <c r="F48" s="265"/>
+      <c r="G48" s="265"/>
+      <c r="H48" s="265"/>
+      <c r="I48" s="265"/>
+      <c r="J48" s="265"/>
+      <c r="K48" s="265"/>
+      <c r="L48" s="288"/>
+      <c r="M48" s="271" t="s">
         <v>185</v>
       </c>
-      <c r="N48" s="263"/>
-      <c r="O48" s="263"/>
-      <c r="P48" s="263"/>
-      <c r="Q48" s="263"/>
-      <c r="R48" s="264"/>
+      <c r="N48" s="272"/>
+      <c r="O48" s="272"/>
+      <c r="P48" s="272"/>
+      <c r="Q48" s="272"/>
+      <c r="R48" s="273"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="286" t="s">
+      <c r="B49" s="289" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="286" t="s">
+      <c r="C49" s="289" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="255" t="s">
@@ -7623,49 +7623,49 @@
       <c r="E49" s="256"/>
       <c r="F49" s="256"/>
       <c r="G49" s="257"/>
-      <c r="H49" s="287" t="s">
+      <c r="H49" s="290" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="288"/>
-      <c r="J49" s="288"/>
-      <c r="K49" s="289"/>
-      <c r="L49" s="290" t="s">
+      <c r="I49" s="291"/>
+      <c r="J49" s="291"/>
+      <c r="K49" s="292"/>
+      <c r="L49" s="293" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="265" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="267" t="str">
+      <c r="O49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="267" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
-      <c r="Q49" s="269" t="str">
+      <c r="Q49" s="278" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="269" t="str">
+      <c r="R49" s="278" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="261"/>
-      <c r="C50" s="261"/>
+      <c r="B50" s="270"/>
+      <c r="C50" s="270"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -7690,13 +7690,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="291"/>
-      <c r="M50" s="266"/>
-      <c r="N50" s="266"/>
-      <c r="O50" s="268"/>
-      <c r="P50" s="268"/>
-      <c r="Q50" s="270"/>
-      <c r="R50" s="270"/>
+      <c r="L50" s="294"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
+      <c r="O50" s="277"/>
+      <c r="P50" s="277"/>
+      <c r="Q50" s="279"/>
+      <c r="R50" s="279"/>
       <c r="T50" s="178" t="s">
         <v>215</v>
       </c>
@@ -8812,21 +8812,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="292" t="s">
+      <c r="B67" s="285" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="293"/>
-      <c r="D67" s="293"/>
-      <c r="E67" s="293"/>
+      <c r="C67" s="286"/>
+      <c r="D67" s="286"/>
+      <c r="E67" s="286"/>
       <c r="F67" s="295"/>
-      <c r="G67" s="262" t="s">
+      <c r="G67" s="271" t="s">
         <v>185</v>
       </c>
-      <c r="H67" s="263"/>
-      <c r="I67" s="263"/>
-      <c r="J67" s="263"/>
-      <c r="K67" s="263"/>
-      <c r="L67" s="264"/>
+      <c r="H67" s="272"/>
+      <c r="I67" s="272"/>
+      <c r="J67" s="272"/>
+      <c r="K67" s="272"/>
+      <c r="L67" s="273"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -9147,10 +9147,10 @@
       <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="261" t="s">
+      <c r="B78" s="270" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="270" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -9463,14 +9463,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B48:L48"/>
-    <mergeCell ref="G67:L67"/>
     <mergeCell ref="M48:R48"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="C49:C50"/>
@@ -9483,6 +9475,14 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B48:L48"/>
+    <mergeCell ref="G67:L67"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -9552,7 +9552,7 @@
       </c>
       <c r="C3" s="75">
         <f ca="1">IF($J$5&lt;&gt;"",$J$5,MAX(0,NETWORKDAYS.INTL(MAX(TODAY(),DATE(YEAR(TODAY()),10,1)),EOMONTH(DATE(YEAR(TODAY()),10,1),0),11)-MAX(0,$J$3-$J$4)))</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="76" t="s">
         <v>104</v>
@@ -9684,19 +9684,19 @@
         <v>112</v>
       </c>
       <c r="C10" s="235">
-        <v>5099399.1523909997</v>
+        <v>22829327.111478001</v>
       </c>
       <c r="D10" s="235">
-        <v>3553070.28</v>
+        <v>3694145.28</v>
       </c>
       <c r="E10" s="235">
-        <v>14595495.476</v>
+        <v>21813140.973623</v>
       </c>
       <c r="F10" s="235">
-        <v>9891892.1299849991</v>
+        <v>18115315.679985002</v>
       </c>
       <c r="G10" s="235">
-        <v>33139857.038376</v>
+        <v>66451929.045085996</v>
       </c>
       <c r="H10" s="111"/>
       <c r="I10" s="111"/>
@@ -9709,21 +9709,20 @@
       <c r="B11" s="72" t="s">
         <v>219</v>
       </c>
-      <c r="C11" s="15">
-        <v>0</v>
-      </c>
-      <c r="D11" s="15">
-        <v>0</v>
-      </c>
-      <c r="E11" s="15">
-        <v>0</v>
-      </c>
-      <c r="F11" s="15">
-        <v>0</v>
-      </c>
-      <c r="G11" s="15">
-        <f t="shared" ref="G10:G26" si="0">SUM(C11:F11)</f>
-        <v>0</v>
+      <c r="C11" s="235">
+        <v>21229693.035904001</v>
+      </c>
+      <c r="D11" s="235">
+        <v>19801023.489305001</v>
+      </c>
+      <c r="E11" s="235">
+        <v>11767765.855973</v>
+      </c>
+      <c r="F11" s="235">
+        <v>972973.02</v>
+      </c>
+      <c r="G11" s="235">
+        <v>53771455.401182003</v>
       </c>
       <c r="H11" s="111"/>
       <c r="I11" s="111"/>
@@ -9736,21 +9735,20 @@
       <c r="B12" s="72" t="s">
         <v>181</v>
       </c>
-      <c r="C12" s="15">
-        <v>0</v>
-      </c>
-      <c r="D12" s="15">
-        <v>0</v>
-      </c>
-      <c r="E12" s="15">
-        <v>0</v>
-      </c>
-      <c r="F12" s="15">
-        <v>0</v>
-      </c>
-      <c r="G12" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C12" s="235">
+        <v>0</v>
+      </c>
+      <c r="D12" s="235">
+        <v>0</v>
+      </c>
+      <c r="E12" s="235">
+        <v>1545045.04</v>
+      </c>
+      <c r="F12" s="235">
+        <v>0</v>
+      </c>
+      <c r="G12" s="235">
+        <v>1545045.04</v>
       </c>
       <c r="H12" s="111"/>
       <c r="I12" s="111"/>
@@ -9764,19 +9762,19 @@
         <v>70</v>
       </c>
       <c r="C13" s="235">
-        <v>9534933.6398440003</v>
+        <v>12831185.979831999</v>
       </c>
       <c r="D13" s="235">
-        <v>3657558.3389989999</v>
+        <v>4994459.2429989995</v>
       </c>
       <c r="E13" s="235">
-        <v>4169594.6</v>
+        <v>12284954.939983999</v>
       </c>
       <c r="F13" s="235">
-        <v>1621621.7</v>
+        <v>18887387.170000002</v>
       </c>
       <c r="G13" s="235">
-        <v>18983708.278843001</v>
+        <v>48997987.332814999</v>
       </c>
       <c r="H13" s="111"/>
       <c r="I13" s="111"/>
@@ -9790,19 +9788,19 @@
         <v>114</v>
       </c>
       <c r="C14" s="235">
-        <v>0</v>
+        <v>1140153.1599999999</v>
       </c>
       <c r="D14" s="235">
-        <v>0</v>
+        <v>5964126.2299880004</v>
       </c>
       <c r="E14" s="235">
-        <v>5869369.3499999996</v>
+        <v>24033648.909924999</v>
       </c>
       <c r="F14" s="235">
-        <v>2756756.89</v>
+        <v>6414414.54</v>
       </c>
       <c r="G14" s="235">
-        <v>8626126.2400000002</v>
+        <v>37552342.839913003</v>
       </c>
       <c r="H14" s="111"/>
       <c r="I14" s="111"/>
@@ -9816,19 +9814,19 @@
         <v>115</v>
       </c>
       <c r="C15" s="235">
-        <v>17804909.979979999</v>
+        <v>33281936.979975</v>
       </c>
       <c r="D15" s="235">
-        <v>1535108.1499989999</v>
+        <v>1906279.3299990001</v>
       </c>
       <c r="E15" s="235">
-        <v>5624603.5700000003</v>
+        <v>8236495.4799990002</v>
       </c>
       <c r="F15" s="235">
-        <v>18467747.989999998</v>
+        <v>24683964.210000001</v>
       </c>
       <c r="G15" s="235">
-        <v>43432369.689979002</v>
+        <v>68108675.999972999</v>
       </c>
       <c r="H15" s="111"/>
       <c r="I15" s="111"/>
@@ -9842,19 +9840,19 @@
         <v>118</v>
       </c>
       <c r="C16" s="235">
-        <v>21599788.68998</v>
+        <v>24092320.229979999</v>
       </c>
       <c r="D16" s="235">
-        <v>167891.88999900001</v>
+        <v>268972.96999900002</v>
       </c>
       <c r="E16" s="235">
         <v>0</v>
       </c>
       <c r="F16" s="235">
-        <v>972973.02</v>
+        <v>1091891.94</v>
       </c>
       <c r="G16" s="235">
-        <v>22740653.599978998</v>
+        <v>25453185.139979001</v>
       </c>
       <c r="H16" s="111"/>
       <c r="I16" s="111"/>
@@ -9868,19 +9866,19 @@
         <v>120</v>
       </c>
       <c r="C17" s="235">
-        <v>24228400.236997999</v>
+        <v>44226099.108975999</v>
       </c>
       <c r="D17" s="235">
-        <v>2594594.52</v>
+        <v>3479770.1999989999</v>
       </c>
       <c r="E17" s="235">
-        <v>36828739.059940003</v>
+        <v>59587297.579875</v>
       </c>
       <c r="F17" s="235">
-        <v>142163962.83000001</v>
+        <v>172490989.74000001</v>
       </c>
       <c r="G17" s="235">
-        <v>205815696.646938</v>
+        <v>279784156.62884998</v>
       </c>
       <c r="H17" s="111"/>
       <c r="I17" s="111"/>
@@ -9894,19 +9892,19 @@
         <v>122</v>
       </c>
       <c r="C18" s="235">
-        <v>2741711.73</v>
+        <v>15716027.090439999</v>
       </c>
       <c r="D18" s="235">
         <v>0</v>
       </c>
       <c r="E18" s="235">
-        <v>698198.49994999997</v>
-      </c>
-      <c r="F18" s="235">
-        <v>0</v>
+        <v>6981982.9994999999</v>
+      </c>
+      <c r="F18" s="235" t="s">
+        <v>164</v>
       </c>
       <c r="G18" s="235">
-        <v>3439910.2299500001</v>
+        <v>22698010.08994</v>
       </c>
       <c r="H18" s="111"/>
       <c r="I18" s="111"/>
@@ -9923,16 +9921,16 @@
         <v>2332400</v>
       </c>
       <c r="D19" s="235">
-        <v>2838292.3307739999</v>
+        <v>12045032.40667</v>
       </c>
       <c r="E19" s="235">
-        <v>3712540.5</v>
+        <v>4192540.5</v>
       </c>
       <c r="F19" s="235">
-        <v>14486486.800000001</v>
+        <v>16162162.5</v>
       </c>
       <c r="G19" s="235">
-        <v>23369719.630773999</v>
+        <v>34732135.406669997</v>
       </c>
       <c r="H19" s="111"/>
       <c r="I19" s="111"/>
@@ -9945,21 +9943,20 @@
       <c r="B20" s="72" t="s">
         <v>168</v>
       </c>
-      <c r="C20" s="15">
-        <v>0</v>
-      </c>
-      <c r="D20" s="15">
-        <v>0</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
-      </c>
-      <c r="F20" s="15">
-        <v>0</v>
-      </c>
-      <c r="G20" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C20" s="235">
+        <v>459459.48</v>
+      </c>
+      <c r="D20" s="235">
+        <v>0</v>
+      </c>
+      <c r="E20" s="235">
+        <v>0</v>
+      </c>
+      <c r="F20" s="235" t="s">
+        <v>164</v>
+      </c>
+      <c r="G20" s="235">
+        <v>459459.48</v>
       </c>
       <c r="H20" s="111"/>
       <c r="I20" s="111"/>
@@ -9976,28 +9973,27 @@
       <c r="B21" s="72" t="s">
         <v>169</v>
       </c>
-      <c r="C21" s="15">
-        <v>0</v>
-      </c>
-      <c r="D21" s="15">
-        <v>0</v>
-      </c>
-      <c r="E21" s="15">
-        <v>0</v>
-      </c>
-      <c r="F21" s="15">
-        <v>0</v>
-      </c>
-      <c r="G21" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C21" s="235">
+        <v>297297.3</v>
+      </c>
+      <c r="D21" s="235">
+        <v>0</v>
+      </c>
+      <c r="E21" s="235">
+        <v>0</v>
+      </c>
+      <c r="F21" s="235" t="s">
+        <v>164</v>
+      </c>
+      <c r="G21" s="235">
+        <v>297297.3</v>
       </c>
       <c r="H21" s="111"/>
       <c r="I21" s="111"/>
       <c r="J21" s="111"/>
       <c r="M21" s="14">
         <f>SUM(C33,C34)+M20</f>
-        <v>23778171.829761002</v>
+        <v>100984459.15882701</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>223</v>
@@ -10008,19 +10004,19 @@
         <v>124</v>
       </c>
       <c r="C22" s="235">
-        <v>12273347.239848999</v>
+        <v>24142386.242304999</v>
       </c>
       <c r="D22" s="235">
-        <v>3138986.5099889999</v>
+        <v>7628806.3299850002</v>
       </c>
       <c r="E22" s="235">
-        <v>3614909.9</v>
+        <v>9453918.8900000006</v>
       </c>
       <c r="F22" s="235">
-        <v>972973.02</v>
+        <v>74432433.089969993</v>
       </c>
       <c r="G22" s="235">
-        <v>20000216.669838</v>
+        <v>115657544.55226</v>
       </c>
       <c r="H22" s="111"/>
       <c r="I22" s="111"/>
@@ -10031,19 +10027,19 @@
         <v>125</v>
       </c>
       <c r="C23" s="235">
-        <v>7886135.4645919995</v>
+        <v>15124825.596582999</v>
       </c>
       <c r="D23" s="235">
-        <v>4799378.3999950001</v>
+        <v>8652653.2199789993</v>
       </c>
       <c r="E23" s="235">
-        <v>9972973.1899980009</v>
+        <v>18310631.499988001</v>
       </c>
       <c r="F23" s="235">
-        <v>7967567.5999999996</v>
+        <v>18955856.199965</v>
       </c>
       <c r="G23" s="235">
-        <v>30626054.654585</v>
+        <v>61043966.516515002</v>
       </c>
       <c r="H23" s="111"/>
       <c r="I23" s="111"/>
@@ -10054,19 +10050,19 @@
         <v>126</v>
       </c>
       <c r="C24" s="235">
-        <v>17326640.025509998</v>
+        <v>38217658.354423001</v>
       </c>
       <c r="D24" s="235">
-        <v>3598450.4599979999</v>
+        <v>6268450.4599980004</v>
       </c>
       <c r="E24" s="235">
-        <v>9749459.7300000004</v>
+        <v>22947162.569993999</v>
       </c>
       <c r="F24" s="235">
-        <v>29344144.359993</v>
+        <v>61440000.609972998</v>
       </c>
       <c r="G24" s="235">
-        <v>60018694.575501002</v>
+        <v>128873271.994388</v>
       </c>
       <c r="H24" s="111"/>
       <c r="I24" s="111"/>
@@ -10077,19 +10073,19 @@
         <v>224</v>
       </c>
       <c r="C25" s="235">
-        <v>9041895.5201660004</v>
+        <v>30572496.150494002</v>
       </c>
       <c r="D25" s="235">
-        <v>1793939.1151990001</v>
+        <v>1893038.215199</v>
       </c>
       <c r="E25" s="235">
-        <v>6225856.0099980002</v>
+        <v>12680153.279998001</v>
       </c>
       <c r="F25" s="235">
         <v>29513694.069988001</v>
       </c>
       <c r="G25" s="235">
-        <v>46575384.715351</v>
+        <v>74659381.715679005</v>
       </c>
       <c r="H25" s="111"/>
       <c r="I25" s="111"/>
@@ -10100,19 +10096,19 @@
         <v>127</v>
       </c>
       <c r="C26" s="235">
-        <v>26521190.528918002</v>
+        <v>68663137.828872994</v>
       </c>
       <c r="D26" s="235">
-        <v>297297.3</v>
+        <v>3715837.8599700001</v>
       </c>
       <c r="E26" s="235">
-        <v>15905401.999435</v>
+        <v>31963960.749435</v>
       </c>
       <c r="F26" s="235">
-        <v>0</v>
+        <v>3565405.4871999999</v>
       </c>
       <c r="G26" s="235">
-        <v>42723889.828353003</v>
+        <v>107908341.925478</v>
       </c>
       <c r="H26" s="111"/>
       <c r="I26" s="111"/>
@@ -10155,7 +10151,7 @@
         <v>131</v>
       </c>
       <c r="C31" s="171">
-        <v>4400648.7999700001</v>
+        <v>15509042.029937999</v>
       </c>
       <c r="G31" s="111"/>
       <c r="H31" s="111"/>
@@ -10166,7 +10162,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="235">
-        <v>9101351.5199759994</v>
+        <v>13028594.909956001</v>
       </c>
       <c r="G32" s="111"/>
       <c r="H32" s="111"/>
@@ -10177,7 +10173,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="235">
-        <v>5173846.8699930003</v>
+        <v>19529865.159830999</v>
       </c>
       <c r="G33" s="111"/>
       <c r="H33" s="111"/>
@@ -10188,7 +10184,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="235">
-        <v>18604324.959768001</v>
+        <v>81454593.998996004</v>
       </c>
       <c r="G34" s="111"/>
       <c r="H34" s="111"/>
@@ -10233,17 +10229,17 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="271" t="s">
+      <c r="B40" s="261" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="272"/>
-      <c r="D40" s="273"/>
+      <c r="C40" s="262"/>
+      <c r="D40" s="263"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
       <c r="F40" s="174">
         <f ca="1">IF(MONTH(TODAY())=10,DAY(TODAY())/DAY(EOMONTH(TODAY(),0)),IF(MONTH(TODAY())&gt;10,1,0))</f>
-        <v>3.2258064516129031E-2</v>
+        <v>6.4516129032258063E-2</v>
       </c>
       <c r="G40" s="192" t="s">
         <v>186</v>
@@ -10330,35 +10326,35 @@
       </c>
       <c r="E42" s="46">
         <f>H65</f>
-        <v>134790963.51824799</v>
+        <v>331064083.41928303</v>
       </c>
       <c r="F42" s="176">
         <f>IFERROR(E42/D42,0)</f>
-        <v>3.0191140393942793E-2</v>
+        <v>7.4153355395745149E-2</v>
       </c>
       <c r="G42" s="184">
         <f>D42*$H$40-E42</f>
-        <v>3883337056.2753277</v>
+        <v>3687063936.3742929</v>
       </c>
       <c r="H42" s="184">
         <f ca="1">IFERROR(G42/$C$3,0)</f>
-        <v>143827298.3805677</v>
+        <v>141810151.39901125</v>
       </c>
       <c r="I42" s="204">
         <f>D42*$J$40-E42</f>
-        <v>4106566390.7083039</v>
+        <v>3910293270.8072691</v>
       </c>
       <c r="J42" s="204">
         <f ca="1">IFERROR(I42/$C$3,0)</f>
-        <v>152095051.50771496</v>
+        <v>150395895.0310488</v>
       </c>
       <c r="K42" s="185">
         <f>D42*$L$40-E42</f>
-        <v>4329795725.1412811</v>
+        <v>4133522605.2402458</v>
       </c>
       <c r="L42" s="185">
         <f ca="1">IFERROR(K42/$C$3,0)</f>
-        <v>160362804.63486227</v>
+        <v>158981638.66308638</v>
       </c>
       <c r="S42" s="173">
         <v>0.8</v>
@@ -10377,35 +10373,35 @@
       </c>
       <c r="E43" s="46">
         <f>I65</f>
-        <v>27806675.404953003</v>
+        <v>80043622.264091015</v>
       </c>
       <c r="F43" s="176">
         <f>IFERROR(E43/D43,0)</f>
-        <v>2.1725525611115647E-2</v>
+        <v>6.2538571770259968E-2</v>
       </c>
       <c r="G43" s="184">
         <f>D43*$H$40-E43</f>
-        <v>1124110581.3933542</v>
+        <v>1071873634.5342162</v>
       </c>
       <c r="H43" s="184">
         <f ca="1">IFERROR(G43/$C$3,0)</f>
-        <v>41633725.236790895</v>
+        <v>41225909.020546779</v>
       </c>
       <c r="I43" s="204">
         <f>D43*$J$40-E43</f>
-        <v>1188105984.5488157</v>
+        <v>1135869037.6896777</v>
       </c>
       <c r="J43" s="204">
         <f ca="1">IFERROR(I43/$C$3,0)</f>
-        <v>44003925.353659838</v>
+        <v>43687270.680372223</v>
       </c>
       <c r="K43" s="185">
         <f>D43*$L$40-E43</f>
-        <v>1252101387.7042773</v>
+        <v>1199864440.8451393</v>
       </c>
       <c r="L43" s="185">
         <f ca="1">IFERROR(K43/$C$3,0)</f>
-        <v>46374125.470528789</v>
+        <v>46148632.340197667</v>
       </c>
       <c r="S43" s="173">
         <v>0.85</v>
@@ -10424,35 +10420,35 @@
       </c>
       <c r="E44" s="46">
         <f>J65</f>
-        <v>116967141.88532101</v>
+        <v>245798699.26829401</v>
       </c>
       <c r="F44" s="176">
         <f>IFERROR(E44/D44,0)</f>
-        <v>4.0139616177707102E-2</v>
+        <v>8.4350744034442052E-2</v>
       </c>
       <c r="G44" s="184">
         <f>IF(D44=0,0,D44*$H$40-E44)</f>
-        <v>2505639592.3378725</v>
+        <v>2376808034.9548998</v>
       </c>
       <c r="H44" s="184">
         <f ca="1">IFERROR(G44/$C$3,0)</f>
-        <v>92801466.38288416</v>
+        <v>91415693.65211153</v>
       </c>
       <c r="I44" s="204">
         <f>IF(D44=0,0,D44*$J$40-E44)</f>
-        <v>2651339966.4613833</v>
+        <v>2522508409.0784106</v>
       </c>
       <c r="J44" s="204">
         <f ca="1">IFERROR(I44/$C$3,0)</f>
-        <v>98197776.535606787</v>
+        <v>97019554.195323482</v>
       </c>
       <c r="K44" s="185">
         <f>IF(D44=0,0,D44*$L$40-E44)</f>
-        <v>2797040340.5848942</v>
+        <v>2668208783.2019215</v>
       </c>
       <c r="L44" s="185">
         <f ca="1">IFERROR(K44/$C$3,0)</f>
-        <v>103594086.68832941</v>
+        <v>102623414.73853543</v>
       </c>
       <c r="S44" s="173">
         <v>0.9</v>
@@ -10471,35 +10467,35 @@
       </c>
       <c r="E45" s="46">
         <f>E74</f>
-        <v>37280172.149707004</v>
+        <v>129522096.098721</v>
       </c>
       <c r="F45" s="176">
         <f>IFERROR(E45/D45,0)</f>
-        <v>2.0946420693798318E-2</v>
+        <v>7.2773921298743424E-2</v>
       </c>
       <c r="G45" s="184">
         <f>D45*$H$40-E45</f>
-        <v>1564528338.4885907</v>
+        <v>1472286414.5395768</v>
       </c>
       <c r="H45" s="184">
         <f ca="1">IFERROR(G45/$C$3,0)</f>
-        <v>57945494.018095955</v>
+        <v>56626400.559214488</v>
       </c>
       <c r="I45" s="204">
         <f>D45*$J$40-E45</f>
-        <v>1653517700.1907184</v>
+        <v>1561275776.2417045</v>
       </c>
       <c r="J45" s="204">
         <f ca="1">IFERROR(I45/$C$3,0)</f>
-        <v>61241396.303359941</v>
+        <v>60049068.316988632</v>
       </c>
       <c r="K45" s="185">
         <f>D45*$L$40-E45</f>
-        <v>1742507061.8928461</v>
+        <v>1650265137.9438322</v>
       </c>
       <c r="L45" s="185">
         <f ca="1">IFERROR(K45/$C$3,0)</f>
-        <v>64537298.588623933</v>
+        <v>63471736.074762776</v>
       </c>
       <c r="S45" s="173">
         <v>0.95</v>
@@ -10516,35 +10512,35 @@
       </c>
       <c r="E46" s="47">
         <f>SUM(E42:E45)</f>
-        <v>316844952.95822901</v>
+        <v>786428501.05038905</v>
       </c>
       <c r="F46" s="177">
         <f>IFERROR(E46/D46,0)</f>
-        <v>3.0354106764428686E-2</v>
+        <v>7.5340744615301436E-2</v>
       </c>
       <c r="G46" s="181">
         <f>SUM(G42:G45)</f>
-        <v>9077615568.4951458</v>
+        <v>8608032020.4029865</v>
       </c>
       <c r="H46" s="181">
         <f ca="1">IFERROR(G46/$C$3,0)</f>
-        <v>336207984.01833874</v>
+        <v>331078154.63088411</v>
       </c>
       <c r="I46" s="186">
         <f>SUM(I42:I45)</f>
-        <v>9599530041.9092216</v>
+        <v>9129946493.8170624</v>
       </c>
       <c r="J46" s="186">
         <f ca="1">IFERROR(I46/$C$3,0)</f>
-        <v>355538149.70034152</v>
+        <v>351151788.22373319</v>
       </c>
       <c r="K46" s="186">
         <f>SUM(K42:K45)</f>
-        <v>10121444515.323299</v>
+        <v>9651860967.2311382</v>
       </c>
       <c r="L46" s="186">
         <f ca="1">IFERROR(K46/$C$3,0)</f>
-        <v>374868315.38234442</v>
+        <v>371225421.81658226</v>
       </c>
       <c r="S46" s="173">
         <v>1</v>
@@ -10557,33 +10553,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="274" t="s">
+      <c r="B48" s="264" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="275"/>
-      <c r="D48" s="275"/>
-      <c r="E48" s="275"/>
-      <c r="F48" s="275"/>
-      <c r="G48" s="275"/>
-      <c r="H48" s="275"/>
-      <c r="I48" s="275"/>
-      <c r="J48" s="275"/>
-      <c r="K48" s="275"/>
-      <c r="L48" s="285"/>
-      <c r="M48" s="262" t="s">
+      <c r="C48" s="265"/>
+      <c r="D48" s="265"/>
+      <c r="E48" s="265"/>
+      <c r="F48" s="265"/>
+      <c r="G48" s="265"/>
+      <c r="H48" s="265"/>
+      <c r="I48" s="265"/>
+      <c r="J48" s="265"/>
+      <c r="K48" s="265"/>
+      <c r="L48" s="288"/>
+      <c r="M48" s="271" t="s">
         <v>185</v>
       </c>
-      <c r="N48" s="263"/>
-      <c r="O48" s="263"/>
-      <c r="P48" s="263"/>
-      <c r="Q48" s="263"/>
-      <c r="R48" s="264"/>
+      <c r="N48" s="272"/>
+      <c r="O48" s="272"/>
+      <c r="P48" s="272"/>
+      <c r="Q48" s="272"/>
+      <c r="R48" s="273"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="286" t="s">
+      <c r="B49" s="289" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="286" t="s">
+      <c r="C49" s="289" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="255" t="s">
@@ -10592,49 +10588,49 @@
       <c r="E49" s="256"/>
       <c r="F49" s="256"/>
       <c r="G49" s="257"/>
-      <c r="H49" s="287" t="s">
+      <c r="H49" s="290" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="288"/>
-      <c r="J49" s="288"/>
-      <c r="K49" s="289"/>
-      <c r="L49" s="290" t="s">
+      <c r="I49" s="291"/>
+      <c r="J49" s="291"/>
+      <c r="K49" s="292"/>
+      <c r="L49" s="293" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="265" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="267" t="str">
+      <c r="O49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="267" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="269" t="str">
+      <c r="Q49" s="278" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="269" t="str">
+      <c r="R49" s="278" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="261"/>
-      <c r="C50" s="261"/>
+      <c r="B50" s="270"/>
+      <c r="C50" s="270"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -10659,13 +10655,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="291"/>
-      <c r="M50" s="266"/>
-      <c r="N50" s="266"/>
-      <c r="O50" s="268"/>
-      <c r="P50" s="268"/>
-      <c r="Q50" s="270"/>
-      <c r="R50" s="270"/>
+      <c r="L50" s="294"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
+      <c r="O50" s="277"/>
+      <c r="P50" s="277"/>
+      <c r="Q50" s="279"/>
+      <c r="R50" s="279"/>
       <c r="T50" s="178" t="s">
         <v>215</v>
       </c>
@@ -10693,52 +10689,52 @@
         <v>172968793.98622558</v>
       </c>
       <c r="G51" s="118">
-        <f t="shared" ref="G51:G64" si="1">SUM(D51:F51)</f>
+        <f t="shared" ref="G51:G64" si="0">SUM(D51:F51)</f>
         <v>496234492.04094887</v>
       </c>
       <c r="H51" s="114">
         <f>SUMIF($B$10:$B$26,$T51,C$10:C$26)+SUMIF($B$10:$B$26,$U51,C$10:C$26)</f>
-        <v>12273347.239848999</v>
+        <v>24142386.242304999</v>
       </c>
       <c r="I51" s="114">
-        <f t="shared" ref="I51:I64" si="2">SUMIF($B$10:$B$26,$T51,D$10:D$26)+SUMIF($B$10:$B$26,$U51,D$10:D$26)</f>
-        <v>3138986.5099889999</v>
+        <f t="shared" ref="I51:I64" si="1">SUMIF($B$10:$B$26,$T51,D$10:D$26)+SUMIF($B$10:$B$26,$U51,D$10:D$26)</f>
+        <v>7628806.3299850002</v>
       </c>
       <c r="J51" s="114">
-        <f t="shared" ref="J51:J64" si="3">SUMIF($B$10:$B$26,$T51,E$10:E$26)+SUMIF($B$10:$B$26,$U51,E$10:E$26)</f>
-        <v>3614909.9</v>
+        <f t="shared" ref="J51:J64" si="2">SUMIF($B$10:$B$26,$T51,E$10:E$26)+SUMIF($B$10:$B$26,$U51,E$10:E$26)</f>
+        <v>9453918.8900000006</v>
       </c>
       <c r="K51" s="114">
-        <f t="shared" ref="K51:K64" si="4">SUM(H51:J51)</f>
-        <v>19027243.649837997</v>
+        <f t="shared" ref="K51:K64" si="3">SUM(H51:J51)</f>
+        <v>41225111.462290004</v>
       </c>
       <c r="L51" s="187">
-        <f t="shared" ref="L51:L65" si="5">IFERROR(K51/G51,0)</f>
-        <v>3.8343250932802719E-2</v>
+        <f t="shared" ref="L51:L65" si="4">IFERROR(K51/G51,0)</f>
+        <v>8.3075868613518594E-2</v>
       </c>
       <c r="M51" s="184">
-        <f t="shared" ref="M51:M64" si="6">G51*$H$40-K51</f>
-        <v>427583799.18701601</v>
+        <f t="shared" ref="M51:M64" si="5">G51*$H$40-K51</f>
+        <v>405385931.37456399</v>
       </c>
       <c r="N51" s="184">
-        <f t="shared" ref="N51:N65" ca="1" si="7">IFERROR(M51/$C$3,0)</f>
-        <v>15836437.00692652</v>
+        <f t="shared" ref="N51:N65" ca="1" si="6">IFERROR(M51/$C$3,0)</f>
+        <v>15591766.591329385</v>
       </c>
       <c r="O51" s="180">
-        <f t="shared" ref="O51:O64" si="8">G51*$J$40-K51</f>
-        <v>452395523.78906345</v>
+        <f t="shared" ref="O51:O64" si="7">G51*$J$40-K51</f>
+        <v>430197655.97661144</v>
       </c>
       <c r="P51" s="180">
-        <f t="shared" ref="P51:P65" ca="1" si="9">IFERROR(O51/$C$3,0)</f>
-        <v>16755389.769965313</v>
+        <f t="shared" ref="P51:P65" ca="1" si="8">IFERROR(O51/$C$3,0)</f>
+        <v>16546063.691408131</v>
       </c>
       <c r="Q51" s="185">
-        <f t="shared" ref="Q51:Q64" si="10">G51*$L$40-K51</f>
-        <v>477207248.3911109</v>
+        <f t="shared" ref="Q51:Q64" si="9">G51*$L$40-K51</f>
+        <v>455009380.57865888</v>
       </c>
       <c r="R51" s="185">
-        <f t="shared" ref="R51:R65" ca="1" si="11">IFERROR(Q51/$C$3,0)</f>
-        <v>17674342.533004109</v>
+        <f t="shared" ref="R51:R65" ca="1" si="10">IFERROR(Q51/$C$3,0)</f>
+        <v>17500360.791486882</v>
       </c>
       <c r="T51" t="s">
         <v>124</v>
@@ -10767,52 +10763,52 @@
         <v>423892749.39216906</v>
       </c>
       <c r="G52" s="119">
+        <f t="shared" si="0"/>
+        <v>767390853.57427597</v>
+      </c>
+      <c r="H52" s="114">
+        <f t="shared" ref="H52:H64" si="11">SUMIF($B$10:$B$26,$T52,C$10:C$26)+SUMIF($B$10:$B$26,$U52,C$10:C$26)</f>
+        <v>13971339.139831999</v>
+      </c>
+      <c r="I52" s="114">
         <f t="shared" si="1"/>
-        <v>767390853.57427597</v>
-      </c>
-      <c r="H52" s="114">
-        <f t="shared" ref="H52:H64" si="12">SUMIF($B$10:$B$26,$T52,C$10:C$26)+SUMIF($B$10:$B$26,$U52,C$10:C$26)</f>
-        <v>9534933.6398440003</v>
-      </c>
-      <c r="I52" s="114">
+        <v>10958585.472987</v>
+      </c>
+      <c r="J52" s="114">
         <f t="shared" si="2"/>
-        <v>3657558.3389989999</v>
-      </c>
-      <c r="J52" s="114">
+        <v>36318603.849909</v>
+      </c>
+      <c r="K52" s="114">
         <f t="shared" si="3"/>
-        <v>10038963.949999999</v>
-      </c>
-      <c r="K52" s="114">
+        <v>61248528.462728001</v>
+      </c>
+      <c r="L52" s="187">
         <f t="shared" si="4"/>
-        <v>23231455.928842999</v>
-      </c>
-      <c r="L52" s="187">
+        <v>7.9813993322243496E-2</v>
+      </c>
+      <c r="M52" s="184">
         <f t="shared" si="5"/>
-        <v>3.0273303129217475E-2</v>
-      </c>
-      <c r="M52" s="184">
-        <f t="shared" si="6"/>
-        <v>667420312.28800535</v>
+        <v>629403239.75412035</v>
       </c>
       <c r="N52" s="184">
-        <f t="shared" ca="1" si="7"/>
-        <v>24719270.825481679</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>24207816.913620014</v>
       </c>
       <c r="O52" s="180">
-        <f t="shared" si="8"/>
-        <v>705789854.96671915</v>
+        <f t="shared" si="7"/>
+        <v>667772782.43283415</v>
       </c>
       <c r="P52" s="180">
-        <f t="shared" ca="1" si="9"/>
-        <v>26140364.998767376</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>25683568.555109005</v>
       </c>
       <c r="Q52" s="185">
-        <f t="shared" si="10"/>
-        <v>744159397.64543295</v>
+        <f t="shared" si="9"/>
+        <v>706142325.11154795</v>
       </c>
       <c r="R52" s="185">
-        <f t="shared" ca="1" si="11"/>
-        <v>27561459.172053073</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>27159320.196597997</v>
       </c>
       <c r="T52" t="s">
         <v>70</v>
@@ -10841,52 +10837,52 @@
         <v>0</v>
       </c>
       <c r="G53" s="138">
+        <f t="shared" si="0"/>
+        <v>262953105.06301075</v>
+      </c>
+      <c r="H53" s="114">
+        <f t="shared" si="11"/>
+        <v>459459.48</v>
+      </c>
+      <c r="I53" s="114">
         <f t="shared" si="1"/>
-        <v>262953105.06301075</v>
-      </c>
-      <c r="H53" s="114">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I53" s="114">
+        <v>0</v>
+      </c>
+      <c r="J53" s="114">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J53" s="114">
+      <c r="K53" s="114">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K53" s="114">
+        <v>459459.48</v>
+      </c>
+      <c r="L53" s="187">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L53" s="187">
+        <v>1.7473057786859026E-3</v>
+      </c>
+      <c r="M53" s="184">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M53" s="184">
-        <f t="shared" si="6"/>
-        <v>236657794.55670968</v>
+        <v>236198335.07670969</v>
       </c>
       <c r="N53" s="184">
-        <f t="shared" ca="1" si="7"/>
-        <v>8765103.5021003578</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>9084551.3491042182</v>
       </c>
       <c r="O53" s="180">
-        <f t="shared" si="8"/>
-        <v>249805449.8098602</v>
+        <f t="shared" si="7"/>
+        <v>249345990.32986021</v>
       </c>
       <c r="P53" s="180">
-        <f t="shared" ca="1" si="9"/>
-        <v>9252053.6966614891</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>9590230.3973023165</v>
       </c>
       <c r="Q53" s="185">
-        <f t="shared" si="10"/>
-        <v>262953105.06301075</v>
+        <f t="shared" si="9"/>
+        <v>262493645.58301076</v>
       </c>
       <c r="R53" s="185">
-        <f t="shared" ca="1" si="11"/>
-        <v>9739003.8912226204</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>10095909.445500415</v>
       </c>
       <c r="T53" t="s">
         <v>168</v>
@@ -10915,52 +10911,52 @@
         <v>83921591.734509259</v>
       </c>
       <c r="G54" s="119">
+        <f t="shared" si="0"/>
+        <v>708538780.93999994</v>
+      </c>
+      <c r="H54" s="114">
+        <f t="shared" si="11"/>
+        <v>33281936.979975</v>
+      </c>
+      <c r="I54" s="114">
         <f t="shared" si="1"/>
-        <v>708538780.93999994</v>
-      </c>
-      <c r="H54" s="114">
-        <f t="shared" si="12"/>
-        <v>17804909.979979999</v>
-      </c>
-      <c r="I54" s="114">
+        <v>1906279.3299990001</v>
+      </c>
+      <c r="J54" s="114">
         <f t="shared" si="2"/>
-        <v>1535108.1499989999</v>
-      </c>
-      <c r="J54" s="114">
+        <v>8236495.4799990002</v>
+      </c>
+      <c r="K54" s="114">
         <f t="shared" si="3"/>
-        <v>5624603.5700000003</v>
-      </c>
-      <c r="K54" s="114">
+        <v>43424711.789972998</v>
+      </c>
+      <c r="L54" s="187">
         <f t="shared" si="4"/>
-        <v>24964621.699979</v>
-      </c>
-      <c r="L54" s="187">
+        <v>6.1287699358336556E-2</v>
+      </c>
+      <c r="M54" s="184">
         <f t="shared" si="5"/>
-        <v>3.5233952426512331E-2</v>
-      </c>
-      <c r="M54" s="184">
-        <f t="shared" si="6"/>
-        <v>612720281.14602101</v>
+        <v>594260191.05602694</v>
       </c>
       <c r="N54" s="184">
-        <f t="shared" ca="1" si="7"/>
-        <v>22693343.746148925</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>22856161.194462575</v>
       </c>
       <c r="O54" s="180">
-        <f t="shared" si="8"/>
-        <v>648147220.19302094</v>
+        <f t="shared" si="7"/>
+        <v>629687130.10302687</v>
       </c>
       <c r="P54" s="180">
-        <f t="shared" ca="1" si="9"/>
-        <v>24005452.599741515</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>24218735.773193341</v>
       </c>
       <c r="Q54" s="185">
-        <f t="shared" si="10"/>
-        <v>683574159.24002099</v>
+        <f t="shared" si="9"/>
+        <v>665114069.15002692</v>
       </c>
       <c r="R54" s="185">
-        <f t="shared" ca="1" si="11"/>
-        <v>25317561.453334112</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>25581310.351924114</v>
       </c>
       <c r="T54" t="s">
         <v>115</v>
@@ -10989,52 +10985,52 @@
         <v>468117447.23398483</v>
       </c>
       <c r="G55" s="118">
+        <f t="shared" si="0"/>
+        <v>537200999.57068563</v>
+      </c>
+      <c r="H55" s="114">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="114">
         <f t="shared" si="1"/>
-        <v>537200999.57068563</v>
-      </c>
-      <c r="H55" s="114">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I55" s="114">
+        <v>0</v>
+      </c>
+      <c r="J55" s="114">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J55" s="114">
+        <v>1545045.04</v>
+      </c>
+      <c r="K55" s="114">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K55" s="114">
+        <v>1545045.04</v>
+      </c>
+      <c r="L55" s="187">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L55" s="187">
+        <v>2.8761023178191258E-3</v>
+      </c>
+      <c r="M55" s="184">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M55" s="184">
-        <f t="shared" si="6"/>
-        <v>483480899.61361706</v>
+        <v>481935854.57361704</v>
       </c>
       <c r="N55" s="184">
-        <f t="shared" ca="1" si="7"/>
-        <v>17906699.985689521</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>18535994.406677578</v>
       </c>
       <c r="O55" s="180">
-        <f t="shared" si="8"/>
-        <v>510340949.59215134</v>
+        <f t="shared" si="7"/>
+        <v>508795904.55215132</v>
       </c>
       <c r="P55" s="180">
-        <f t="shared" ca="1" si="9"/>
-        <v>18901516.65156116</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>19569073.252005819</v>
       </c>
       <c r="Q55" s="185">
-        <f t="shared" si="10"/>
-        <v>537200999.57068563</v>
+        <f t="shared" si="9"/>
+        <v>535655954.5306856</v>
       </c>
       <c r="R55" s="185">
-        <f t="shared" ca="1" si="11"/>
-        <v>19896333.317432802</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>20602152.097334061</v>
       </c>
       <c r="T55" t="s">
         <v>181</v>
@@ -11063,52 +11059,52 @@
         <v>184159698.63927278</v>
       </c>
       <c r="G56" s="119">
+        <f t="shared" si="0"/>
+        <v>556812960.65435266</v>
+      </c>
+      <c r="H56" s="114">
+        <f t="shared" si="11"/>
+        <v>30572496.150494002</v>
+      </c>
+      <c r="I56" s="114">
         <f t="shared" si="1"/>
-        <v>556812960.65435266</v>
-      </c>
-      <c r="H56" s="114">
-        <f t="shared" si="12"/>
-        <v>9041895.5201660004</v>
-      </c>
-      <c r="I56" s="114">
+        <v>1893038.215199</v>
+      </c>
+      <c r="J56" s="114">
         <f t="shared" si="2"/>
-        <v>1793939.1151990001</v>
-      </c>
-      <c r="J56" s="114">
+        <v>12680153.279998001</v>
+      </c>
+      <c r="K56" s="114">
         <f t="shared" si="3"/>
-        <v>6225856.0099980002</v>
-      </c>
-      <c r="K56" s="114">
+        <v>45145687.645691007</v>
+      </c>
+      <c r="L56" s="187">
         <f t="shared" si="4"/>
-        <v>17061690.645362999</v>
-      </c>
-      <c r="L56" s="187">
+        <v>8.1078729907143196E-2</v>
+      </c>
+      <c r="M56" s="184">
         <f t="shared" si="5"/>
-        <v>3.064169092851669E-2</v>
-      </c>
-      <c r="M56" s="184">
-        <f t="shared" si="6"/>
-        <v>484069973.94355446</v>
+        <v>455985976.94322646</v>
       </c>
       <c r="N56" s="184">
-        <f t="shared" ca="1" si="7"/>
-        <v>17928517.553464979</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>17537922.190124094</v>
       </c>
       <c r="O56" s="180">
-        <f t="shared" si="8"/>
-        <v>511910621.97627205</v>
+        <f t="shared" si="7"/>
+        <v>483826624.97594404</v>
       </c>
       <c r="P56" s="180">
-        <f t="shared" ca="1" si="9"/>
-        <v>18959652.665787853</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>18608716.345228616</v>
       </c>
       <c r="Q56" s="185">
-        <f t="shared" si="10"/>
-        <v>539751270.00898969</v>
+        <f t="shared" si="9"/>
+        <v>511667273.00866163</v>
       </c>
       <c r="R56" s="185">
-        <f t="shared" ca="1" si="11"/>
-        <v>19990787.778110728</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>19679510.500333138</v>
       </c>
       <c r="T56" t="s">
         <v>224</v>
@@ -11137,52 +11133,52 @@
         <v>343133819.00673455</v>
       </c>
       <c r="G57" s="118">
+        <f t="shared" si="0"/>
+        <v>1091051037.6788809</v>
+      </c>
+      <c r="H57" s="114">
+        <f t="shared" si="11"/>
+        <v>44226099.108975999</v>
+      </c>
+      <c r="I57" s="114">
         <f t="shared" si="1"/>
-        <v>1091051037.6788809</v>
-      </c>
-      <c r="H57" s="114">
-        <f t="shared" si="12"/>
-        <v>24228400.236997999</v>
-      </c>
-      <c r="I57" s="114">
+        <v>3479770.1999989999</v>
+      </c>
+      <c r="J57" s="114">
         <f t="shared" si="2"/>
-        <v>2594594.52</v>
-      </c>
-      <c r="J57" s="114">
+        <v>59587297.579875</v>
+      </c>
+      <c r="K57" s="114">
         <f t="shared" si="3"/>
-        <v>36828739.059940003</v>
-      </c>
-      <c r="K57" s="114">
+        <v>107293166.88885</v>
+      </c>
+      <c r="L57" s="187">
         <f t="shared" si="4"/>
-        <v>63651733.816937998</v>
-      </c>
-      <c r="L57" s="187">
+        <v>9.8339273951021725E-2</v>
+      </c>
+      <c r="M57" s="184">
         <f t="shared" si="5"/>
-        <v>5.8339831610766529E-2</v>
-      </c>
-      <c r="M57" s="184">
-        <f t="shared" si="6"/>
-        <v>918294200.09405482</v>
+        <v>874652767.02214289</v>
       </c>
       <c r="N57" s="184">
-        <f t="shared" ca="1" si="7"/>
-        <v>34010896.29977981</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>33640491.03931319</v>
       </c>
       <c r="O57" s="180">
-        <f t="shared" si="8"/>
-        <v>972846751.97799873</v>
+        <f t="shared" si="7"/>
+        <v>929205318.9060868</v>
       </c>
       <c r="P57" s="180">
-        <f t="shared" ca="1" si="9"/>
-        <v>36031361.184370324</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>35738666.111772567</v>
       </c>
       <c r="Q57" s="185">
-        <f t="shared" si="10"/>
-        <v>1027399303.8619429</v>
+        <f t="shared" si="9"/>
+        <v>983757870.79003096</v>
       </c>
       <c r="R57" s="185">
-        <f t="shared" ca="1" si="11"/>
-        <v>38051826.068960845</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>37836841.184231959</v>
       </c>
       <c r="T57" t="s">
         <v>120</v>
@@ -11211,52 +11207,52 @@
         <v>249609659.83737293</v>
       </c>
       <c r="G58" s="119">
+        <f t="shared" si="0"/>
+        <v>596447842.33116329</v>
+      </c>
+      <c r="H58" s="114">
+        <f t="shared" si="11"/>
+        <v>15124825.596582999</v>
+      </c>
+      <c r="I58" s="114">
         <f t="shared" si="1"/>
-        <v>596447842.33116329</v>
-      </c>
-      <c r="H58" s="114">
-        <f t="shared" si="12"/>
-        <v>7886135.4645919995</v>
-      </c>
-      <c r="I58" s="114">
+        <v>8652653.2199789993</v>
+      </c>
+      <c r="J58" s="114">
         <f t="shared" si="2"/>
-        <v>4799378.3999950001</v>
-      </c>
-      <c r="J58" s="114">
+        <v>18310631.499988001</v>
+      </c>
+      <c r="K58" s="114">
         <f t="shared" si="3"/>
-        <v>9972973.1899980009</v>
-      </c>
-      <c r="K58" s="114">
+        <v>42088110.316550002</v>
+      </c>
+      <c r="L58" s="187">
         <f t="shared" si="4"/>
-        <v>22658487.054585002</v>
-      </c>
-      <c r="L58" s="187">
+        <v>7.0564611571151584E-2</v>
+      </c>
+      <c r="M58" s="184">
         <f t="shared" si="5"/>
-        <v>3.7989050251278175E-2</v>
-      </c>
-      <c r="M58" s="184">
-        <f t="shared" si="6"/>
-        <v>514144571.04346198</v>
+        <v>494714947.78149694</v>
       </c>
       <c r="N58" s="184">
-        <f t="shared" ca="1" si="7"/>
-        <v>19042391.52012822</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>19027497.991596036</v>
       </c>
       <c r="O58" s="180">
-        <f t="shared" si="8"/>
-        <v>543966963.16002011</v>
+        <f t="shared" si="7"/>
+        <v>524537339.89805508</v>
       </c>
       <c r="P58" s="180">
-        <f t="shared" ca="1" si="9"/>
-        <v>20146924.561482225</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>20174513.073002119</v>
       </c>
       <c r="Q58" s="185">
-        <f t="shared" si="10"/>
-        <v>573789355.27657831</v>
+        <f t="shared" si="9"/>
+        <v>554359732.01461327</v>
       </c>
       <c r="R58" s="185">
-        <f t="shared" ca="1" si="11"/>
-        <v>21251457.602836233</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>21321528.154408202</v>
       </c>
       <c r="T58" t="s">
         <v>125</v>
@@ -11285,52 +11281,52 @@
         <v>0</v>
       </c>
       <c r="G59" s="138">
+        <f t="shared" si="0"/>
+        <v>443846715.57642001</v>
+      </c>
+      <c r="H59" s="114">
+        <f t="shared" si="11"/>
+        <v>297297.3</v>
+      </c>
+      <c r="I59" s="114">
         <f t="shared" si="1"/>
-        <v>443846715.57642001</v>
-      </c>
-      <c r="H59" s="114">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I59" s="114">
+        <v>0</v>
+      </c>
+      <c r="J59" s="114">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J59" s="114">
+      <c r="K59" s="114">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K59" s="114">
+        <v>297297.3</v>
+      </c>
+      <c r="L59" s="187">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L59" s="187">
+        <v>6.6981975886405394E-4</v>
+      </c>
+      <c r="M59" s="184">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M59" s="184">
-        <f t="shared" si="6"/>
-        <v>399462044.01877803</v>
+        <v>399164746.71877801</v>
       </c>
       <c r="N59" s="184">
-        <f t="shared" ca="1" si="7"/>
-        <v>14794890.519214001</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>15352490.258414539</v>
       </c>
       <c r="O59" s="180">
-        <f t="shared" si="8"/>
-        <v>421654379.79759902</v>
+        <f t="shared" si="7"/>
+        <v>421357082.49759901</v>
       </c>
       <c r="P59" s="180">
-        <f t="shared" ca="1" si="9"/>
-        <v>15616828.881392555</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>16206041.634523038</v>
       </c>
       <c r="Q59" s="185">
-        <f t="shared" si="10"/>
-        <v>443846715.57642001</v>
+        <f t="shared" si="9"/>
+        <v>443549418.27642</v>
       </c>
       <c r="R59" s="185">
-        <f t="shared" ca="1" si="11"/>
-        <v>16438767.243571112</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>17059593.010631539</v>
       </c>
       <c r="T59" t="s">
         <v>169</v>
@@ -11359,52 +11355,52 @@
         <v>115472440.26230113</v>
       </c>
       <c r="G60" s="119">
+        <f t="shared" si="0"/>
+        <v>561053180.35051799</v>
+      </c>
+      <c r="H60" s="114">
+        <f t="shared" si="11"/>
+        <v>21229693.035904001</v>
+      </c>
+      <c r="I60" s="114">
         <f t="shared" si="1"/>
-        <v>561053180.35051799</v>
-      </c>
-      <c r="H60" s="114">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I60" s="114">
+        <v>19801023.489305001</v>
+      </c>
+      <c r="J60" s="114">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J60" s="114">
+        <v>11767765.855973</v>
+      </c>
+      <c r="K60" s="114">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K60" s="114">
+        <v>52798482.381182</v>
+      </c>
+      <c r="L60" s="187">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L60" s="187">
+        <v>9.4106021016040126E-2</v>
+      </c>
+      <c r="M60" s="184">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M60" s="184">
-        <f t="shared" si="6"/>
-        <v>504947862.31546623</v>
+        <v>452149379.93428421</v>
       </c>
       <c r="N60" s="184">
-        <f t="shared" ca="1" si="7"/>
-        <v>18701772.678350601</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>17390360.766703241</v>
       </c>
       <c r="O60" s="180">
-        <f t="shared" si="8"/>
-        <v>533000521.33299208</v>
+        <f t="shared" si="7"/>
+        <v>480202038.95181006</v>
       </c>
       <c r="P60" s="180">
-        <f t="shared" ca="1" si="9"/>
-        <v>19740760.049370077</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>18469309.190454233</v>
       </c>
       <c r="Q60" s="185">
-        <f t="shared" si="10"/>
-        <v>561053180.35051799</v>
+        <f t="shared" si="9"/>
+        <v>508254697.96933597</v>
       </c>
       <c r="R60" s="185">
-        <f t="shared" ca="1" si="11"/>
-        <v>20779747.420389555</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>19548257.61420523</v>
       </c>
       <c r="T60" t="s">
         <v>219</v>
@@ -11433,52 +11429,52 @@
         <v>168537597.75857076</v>
       </c>
       <c r="G61" s="118">
+        <f t="shared" si="0"/>
+        <v>698459773.7073158</v>
+      </c>
+      <c r="H61" s="114">
+        <f t="shared" si="11"/>
+        <v>38217658.354423001</v>
+      </c>
+      <c r="I61" s="114">
         <f t="shared" si="1"/>
-        <v>698459773.7073158</v>
-      </c>
-      <c r="H61" s="114">
-        <f t="shared" si="12"/>
-        <v>17326640.025509998</v>
-      </c>
-      <c r="I61" s="114">
+        <v>6268450.4599980004</v>
+      </c>
+      <c r="J61" s="114">
         <f t="shared" si="2"/>
-        <v>3598450.4599979999</v>
-      </c>
-      <c r="J61" s="114">
+        <v>22947162.569993999</v>
+      </c>
+      <c r="K61" s="114">
         <f t="shared" si="3"/>
-        <v>9749459.7300000004</v>
-      </c>
-      <c r="K61" s="114">
+        <v>67433271.384415001</v>
+      </c>
+      <c r="L61" s="187">
         <f t="shared" si="4"/>
-        <v>30674550.215507999</v>
-      </c>
-      <c r="L61" s="187">
+        <v>9.6545676534082539E-2</v>
+      </c>
+      <c r="M61" s="184">
         <f t="shared" si="5"/>
-        <v>4.3917418540358105E-2</v>
-      </c>
-      <c r="M61" s="184">
-        <f t="shared" si="6"/>
-        <v>597939246.12107623</v>
+        <v>561180524.95216918</v>
       </c>
       <c r="N61" s="184">
-        <f t="shared" ca="1" si="7"/>
-        <v>22145898.004484303</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>21583866.344314199</v>
       </c>
       <c r="O61" s="180">
-        <f t="shared" si="8"/>
-        <v>632862234.80644202</v>
+        <f t="shared" si="7"/>
+        <v>596103513.63753498</v>
       </c>
       <c r="P61" s="180">
-        <f t="shared" ca="1" si="9"/>
-        <v>23439342.029868223</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>22927058.216828268</v>
       </c>
       <c r="Q61" s="185">
-        <f t="shared" si="10"/>
-        <v>667785223.49180782</v>
+        <f t="shared" si="9"/>
+        <v>631026502.32290077</v>
       </c>
       <c r="R61" s="185">
-        <f t="shared" ca="1" si="11"/>
-        <v>24732786.055252142</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>24270250.089342337</v>
       </c>
       <c r="T61" t="s">
         <v>126</v>
@@ -11507,52 +11503,52 @@
         <v>259851780.88751724</v>
       </c>
       <c r="G62" s="119">
+        <f t="shared" si="0"/>
+        <v>458890229.7149359</v>
+      </c>
+      <c r="H62" s="114">
+        <f t="shared" si="11"/>
+        <v>22829327.111478001</v>
+      </c>
+      <c r="I62" s="114">
         <f t="shared" si="1"/>
-        <v>458890229.7149359</v>
-      </c>
-      <c r="H62" s="114">
-        <f t="shared" si="12"/>
-        <v>5099399.1523909997</v>
-      </c>
-      <c r="I62" s="114">
+        <v>3694145.28</v>
+      </c>
+      <c r="J62" s="114">
         <f t="shared" si="2"/>
-        <v>3553070.28</v>
-      </c>
-      <c r="J62" s="114">
+        <v>21813140.973623</v>
+      </c>
+      <c r="K62" s="114">
         <f t="shared" si="3"/>
-        <v>14595495.476</v>
-      </c>
-      <c r="K62" s="114">
+        <v>48336613.365101002</v>
+      </c>
+      <c r="L62" s="187">
         <f t="shared" si="4"/>
-        <v>23247964.908390999</v>
-      </c>
-      <c r="L62" s="187">
+        <v>0.10533371650803693</v>
+      </c>
+      <c r="M62" s="184">
         <f t="shared" si="5"/>
-        <v>5.0661276712804959E-2</v>
-      </c>
-      <c r="M62" s="184">
-        <f t="shared" si="6"/>
-        <v>389753241.8350513</v>
+        <v>364664593.37834132</v>
       </c>
       <c r="N62" s="184">
-        <f t="shared" ca="1" si="7"/>
-        <v>14435305.253150048</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>14025561.283782359</v>
       </c>
       <c r="O62" s="180">
-        <f t="shared" si="8"/>
-        <v>412697753.3207981</v>
+        <f t="shared" si="7"/>
+        <v>387609104.86408812</v>
       </c>
       <c r="P62" s="180">
-        <f t="shared" ca="1" si="9"/>
-        <v>15285101.974844374</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>14908042.49477262</v>
       </c>
       <c r="Q62" s="185">
-        <f t="shared" si="10"/>
-        <v>435642264.8065449</v>
+        <f t="shared" si="9"/>
+        <v>410553616.34983492</v>
       </c>
       <c r="R62" s="185">
-        <f t="shared" ca="1" si="11"/>
-        <v>16134898.6965387</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>15790523.705762882</v>
       </c>
       <c r="T62" t="s">
         <v>112</v>
@@ -11581,52 +11577,52 @@
         <v>242574653.13033652</v>
       </c>
       <c r="G63" s="118">
+        <f t="shared" si="0"/>
+        <v>960840969.44794083</v>
+      </c>
+      <c r="H63" s="114">
+        <f t="shared" si="11"/>
+        <v>68663137.828872994</v>
+      </c>
+      <c r="I63" s="114">
         <f t="shared" si="1"/>
-        <v>960840969.44794083</v>
-      </c>
-      <c r="H63" s="114">
-        <f t="shared" si="12"/>
-        <v>26521190.528918002</v>
-      </c>
-      <c r="I63" s="114">
+        <v>3715837.8599700001</v>
+      </c>
+      <c r="J63" s="114">
         <f t="shared" si="2"/>
-        <v>297297.3</v>
-      </c>
-      <c r="J63" s="114">
+        <v>31963960.749435</v>
+      </c>
+      <c r="K63" s="114">
         <f t="shared" si="3"/>
-        <v>15905401.999435</v>
-      </c>
-      <c r="K63" s="114">
+        <v>104342936.43827799</v>
+      </c>
+      <c r="L63" s="187">
         <f t="shared" si="4"/>
-        <v>42723889.828353003</v>
-      </c>
-      <c r="L63" s="187">
+        <v>0.10859542812608115</v>
+      </c>
+      <c r="M63" s="184">
         <f t="shared" si="5"/>
-        <v>4.4465100039292008E-2</v>
-      </c>
-      <c r="M63" s="184">
-        <f t="shared" si="6"/>
-        <v>822032982.67479372</v>
+        <v>760413936.06486881</v>
       </c>
       <c r="N63" s="184">
-        <f t="shared" ca="1" si="7"/>
-        <v>30445666.024992362</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>29246689.848648801</v>
       </c>
       <c r="O63" s="180">
-        <f t="shared" si="8"/>
-        <v>870075031.14719069</v>
+        <f t="shared" si="7"/>
+        <v>808455984.53726578</v>
       </c>
       <c r="P63" s="180">
-        <f t="shared" ca="1" si="9"/>
-        <v>32225001.153599653</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>31094460.94374099</v>
       </c>
       <c r="Q63" s="185">
-        <f t="shared" si="10"/>
-        <v>918117079.61958778</v>
+        <f t="shared" si="9"/>
+        <v>856498033.00966287</v>
       </c>
       <c r="R63" s="185">
-        <f t="shared" ca="1" si="11"/>
-        <v>34004336.282206953</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>32942232.038833186</v>
       </c>
       <c r="T63" t="s">
         <v>127</v>
@@ -11655,52 +11651,52 @@
         <v>201767250.60122082</v>
       </c>
       <c r="G64" s="119">
+        <f t="shared" si="0"/>
+        <v>518781293.58852518</v>
+      </c>
+      <c r="H64" s="114">
+        <f t="shared" si="11"/>
+        <v>18048427.090439998</v>
+      </c>
+      <c r="I64" s="114">
         <f t="shared" si="1"/>
-        <v>518781293.58852518</v>
-      </c>
-      <c r="H64" s="114">
-        <f t="shared" si="12"/>
-        <v>5074111.7300000004</v>
-      </c>
-      <c r="I64" s="114">
+        <v>12045032.40667</v>
+      </c>
+      <c r="J64" s="114">
         <f t="shared" si="2"/>
-        <v>2838292.3307739999</v>
-      </c>
-      <c r="J64" s="114">
+        <v>11174523.499499999</v>
+      </c>
+      <c r="K64" s="114">
         <f t="shared" si="3"/>
-        <v>4410738.9999500001</v>
-      </c>
-      <c r="K64" s="114">
+        <v>41267982.996610001</v>
+      </c>
+      <c r="L64" s="187">
         <f t="shared" si="4"/>
-        <v>12323143.060724001</v>
-      </c>
-      <c r="L64" s="187">
+        <v>7.9547939578064233E-2</v>
+      </c>
+      <c r="M64" s="184">
         <f t="shared" si="5"/>
-        <v>2.3754023541369601E-2</v>
-      </c>
-      <c r="M64" s="184">
-        <f t="shared" si="6"/>
-        <v>454580021.16894865</v>
+        <v>425635181.23306268</v>
       </c>
       <c r="N64" s="184">
-        <f t="shared" ca="1" si="7"/>
-        <v>16836297.08033143</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>16370583.893579334</v>
       </c>
       <c r="O64" s="180">
-        <f t="shared" si="8"/>
-        <v>480519085.8483749</v>
+        <f t="shared" si="7"/>
+        <v>451574245.91248894</v>
       </c>
       <c r="P64" s="180">
-        <f t="shared" ca="1" si="9"/>
-        <v>17797003.179569442</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>17368240.227403421</v>
       </c>
       <c r="Q64" s="185">
-        <f t="shared" si="10"/>
-        <v>506458150.52780116</v>
+        <f t="shared" si="9"/>
+        <v>477513310.59191519</v>
       </c>
       <c r="R64" s="185">
-        <f t="shared" ca="1" si="11"/>
-        <v>18757709.27880745</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>18365896.561227508</v>
       </c>
       <c r="T64" t="s">
         <v>122</v>
@@ -11715,64 +11711,64 @@
       </c>
       <c r="C65" s="58"/>
       <c r="D65" s="134">
-        <f t="shared" ref="D65:K65" si="13">SUM(D51:D64)</f>
+        <f t="shared" ref="D65:K65" si="12">SUM(D51:D64)</f>
         <v>4464586688.6595287</v>
       </c>
       <c r="E65" s="134">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1279908063.1092303</v>
       </c>
       <c r="F65" s="134">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>2914007482.4702153</v>
       </c>
       <c r="G65" s="134">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>8658502234.2389736</v>
       </c>
       <c r="H65" s="135">
-        <f t="shared" si="13"/>
-        <v>134790963.51824799</v>
+        <f t="shared" si="12"/>
+        <v>331064083.41928303</v>
       </c>
       <c r="I65" s="135">
-        <f t="shared" si="13"/>
-        <v>27806675.404953003</v>
+        <f t="shared" si="12"/>
+        <v>80043622.264091015</v>
       </c>
       <c r="J65" s="135">
-        <f t="shared" si="13"/>
-        <v>116967141.88532101</v>
+        <f t="shared" si="12"/>
+        <v>245798699.26829401</v>
       </c>
       <c r="K65" s="135">
-        <f t="shared" si="13"/>
-        <v>279564780.80852205</v>
+        <f t="shared" si="12"/>
+        <v>656906404.95166802</v>
       </c>
       <c r="L65" s="189">
-        <f t="shared" si="5"/>
-        <v>3.2287891513501928E-2</v>
+        <f t="shared" si="4"/>
+        <v>7.586836466404237E-2</v>
       </c>
       <c r="M65" s="181">
         <f>SUM(M51:M64)</f>
-        <v>7513087230.0065556</v>
+        <v>7135745605.863409</v>
       </c>
       <c r="N65" s="181">
-        <f t="shared" ca="1" si="7"/>
-        <v>278262490.00024277</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>274451754.07166958</v>
       </c>
       <c r="O65" s="181">
         <f>SUM(O51:O64)</f>
-        <v>7946012341.718504</v>
+        <v>7568670717.5753565</v>
       </c>
       <c r="P65" s="181">
-        <f t="shared" ca="1" si="9"/>
-        <v>294296753.39698166</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>291102719.90674448</v>
       </c>
       <c r="Q65" s="186">
         <f>SUM(Q51:Q64)</f>
-        <v>8378937453.4304523</v>
+        <v>8001595829.2873039</v>
       </c>
       <c r="R65" s="186">
-        <f t="shared" ca="1" si="11"/>
-        <v>310331016.79372048</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>307753685.74181938</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11781,21 +11777,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="292" t="s">
+      <c r="B67" s="285" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="293"/>
-      <c r="D67" s="293"/>
-      <c r="E67" s="293"/>
+      <c r="C67" s="286"/>
+      <c r="D67" s="286"/>
+      <c r="E67" s="286"/>
       <c r="F67" s="295"/>
-      <c r="G67" s="262" t="s">
+      <c r="G67" s="271" t="s">
         <v>185</v>
       </c>
-      <c r="H67" s="263"/>
-      <c r="I67" s="263"/>
-      <c r="J67" s="263"/>
-      <c r="K67" s="263"/>
-      <c r="L67" s="264"/>
+      <c r="H67" s="272"/>
+      <c r="I67" s="272"/>
+      <c r="J67" s="272"/>
+      <c r="K67" s="272"/>
+      <c r="L67" s="273"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -11857,35 +11853,35 @@
       </c>
       <c r="E69" s="114">
         <f>IFERROR($C$31,0)</f>
-        <v>4400648.7999700001</v>
+        <v>15509042.029937999</v>
       </c>
       <c r="F69" s="187">
-        <f t="shared" ref="F69:F74" si="14">IFERROR(E69/D69,0)</f>
-        <v>1.6336329044333086E-2</v>
+        <f t="shared" ref="F69:F74" si="13">IFERROR(E69/D69,0)</f>
+        <v>5.7573513652165544E-2</v>
       </c>
       <c r="G69" s="184">
         <f>D69*$H$40-E69</f>
-        <v>238039614.81279606</v>
+        <v>226931221.58282804</v>
       </c>
       <c r="H69" s="184">
-        <f t="shared" ref="H69:H74" ca="1" si="15">IFERROR(G69/$C$3,0)</f>
-        <v>8816282.0301035568</v>
+        <f t="shared" ref="H69:H74" ca="1" si="14">IFERROR(G69/$C$3,0)</f>
+        <v>8728123.9070318472</v>
       </c>
       <c r="I69" s="204">
         <f>D69*$J$40-E69</f>
-        <v>251508518.34683859</v>
+        <v>240400125.11687058</v>
       </c>
       <c r="J69" s="204">
-        <f t="shared" ref="J69:J74" ca="1" si="16">IFERROR(I69/$C$3,0)</f>
-        <v>9315130.3091421705</v>
+        <f t="shared" ref="J69:J74" ca="1" si="15">IFERROR(I69/$C$3,0)</f>
+        <v>9246158.6583411768</v>
       </c>
       <c r="K69" s="185">
         <f>D69*$L$40-E69</f>
-        <v>264977421.88088116</v>
+        <v>253869028.65091315</v>
       </c>
       <c r="L69" s="185">
-        <f t="shared" ref="L69:L74" ca="1" si="17">IFERROR(K69/$C$3,0)</f>
-        <v>9813978.5881807841</v>
+        <f t="shared" ref="L69:L74" ca="1" si="16">IFERROR(K69/$C$3,0)</f>
+        <v>9764193.4096505065</v>
       </c>
     </row>
     <row r="70" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -11901,35 +11897,35 @@
       </c>
       <c r="E70" s="114">
         <f>IFERROR($C$32,0)</f>
-        <v>9101351.5199759994</v>
+        <v>13028594.909956001</v>
       </c>
       <c r="F70" s="187">
-        <f t="shared" si="14"/>
-        <v>2.2054313323675002E-2</v>
+        <f t="shared" si="13"/>
+        <v>3.1570774261465359E-2</v>
       </c>
       <c r="G70" s="184">
         <f>D70*$H$40-E70</f>
-        <v>362309730.19278997</v>
+        <v>358382486.80281001</v>
       </c>
       <c r="H70" s="184">
-        <f t="shared" ca="1" si="15"/>
-        <v>13418878.896029258</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>13783941.800108077</v>
       </c>
       <c r="I70" s="204">
         <f>D70*$J$40-E70</f>
-        <v>382943679.1768325</v>
+        <v>379016435.78685254</v>
       </c>
       <c r="J70" s="204">
-        <f t="shared" ca="1" si="16"/>
-        <v>14183099.228771575</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>14577555.222571252</v>
       </c>
       <c r="K70" s="185">
         <f>D70*$L$40-E70</f>
-        <v>403577628.16087508</v>
+        <v>399650384.77089512</v>
       </c>
       <c r="L70" s="185">
-        <f t="shared" ca="1" si="17"/>
-        <v>14947319.561513891</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>15371168.645034429</v>
       </c>
     </row>
     <row r="71" spans="2:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -11945,35 +11941,35 @@
       </c>
       <c r="E71" s="114">
         <f>M21</f>
-        <v>23778171.829761002</v>
+        <v>100984459.15882701</v>
       </c>
       <c r="F71" s="187">
-        <f t="shared" si="14"/>
-        <v>2.1661217103486476E-2</v>
+        <f t="shared" si="13"/>
+        <v>9.1993880336068784E-2</v>
       </c>
       <c r="G71" s="184">
         <f>D71*$H$40-E71</f>
-        <v>964178993.48300493</v>
+        <v>886972706.15393901</v>
       </c>
       <c r="H71" s="184">
-        <f t="shared" ca="1" si="15"/>
-        <v>35710333.091963142</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>34114334.852074578</v>
       </c>
       <c r="I71" s="204">
         <f>D71*$J$40-E71</f>
-        <v>1019065502.6670474</v>
+        <v>941859215.33798146</v>
       </c>
       <c r="J71" s="204">
-        <f t="shared" ca="1" si="16"/>
-        <v>37743166.765446201</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>36225354.436076209</v>
       </c>
       <c r="K71" s="185">
         <f>D71*$L$40-E71</f>
-        <v>1073952011.85109</v>
+        <v>996745724.52202392</v>
       </c>
       <c r="L71" s="185">
-        <f t="shared" ca="1" si="17"/>
-        <v>39776000.43892926</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>38336374.020077839</v>
       </c>
     </row>
     <row r="72" spans="2:21" hidden="1" x14ac:dyDescent="0.25">
@@ -11992,7 +11988,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="187">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G72" s="184">
@@ -12000,7 +11996,7 @@
         <v>0</v>
       </c>
       <c r="H72" s="184">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v>0</v>
       </c>
       <c r="I72" s="204">
@@ -12008,7 +12004,7 @@
         <v>0</v>
       </c>
       <c r="J72" s="204">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" ca="1" si="15"/>
         <v>0</v>
       </c>
       <c r="K72" s="185">
@@ -12016,7 +12012,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="185">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -12036,7 +12032,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="187">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G73" s="184">
@@ -12044,7 +12040,7 @@
         <v>0</v>
       </c>
       <c r="H73" s="184">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="14"/>
         <v>0</v>
       </c>
       <c r="I73" s="204">
@@ -12052,7 +12048,7 @@
         <v>0</v>
       </c>
       <c r="J73" s="204">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" ca="1" si="15"/>
         <v>0</v>
       </c>
       <c r="K73" s="185">
@@ -12060,7 +12056,7 @@
         <v>0</v>
       </c>
       <c r="L73" s="185">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -12075,35 +12071,35 @@
       </c>
       <c r="E74" s="115">
         <f>SUM(E69:E73)</f>
-        <v>37280172.149707004</v>
+        <v>129522096.098721</v>
       </c>
       <c r="F74" s="177">
-        <f t="shared" si="14"/>
-        <v>2.0946420693798318E-2</v>
+        <f t="shared" si="13"/>
+        <v>7.2773921298743424E-2</v>
       </c>
       <c r="G74" s="181">
         <f>SUM(G69:G73)</f>
-        <v>1564528338.488591</v>
+        <v>1472286414.539577</v>
       </c>
       <c r="H74" s="181">
-        <f t="shared" ca="1" si="15"/>
-        <v>57945494.018095963</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>56626400.559214503</v>
       </c>
       <c r="I74" s="186">
         <f>SUM(I69:I73)</f>
-        <v>1653517700.1907187</v>
+        <v>1561275776.2417045</v>
       </c>
       <c r="J74" s="186">
-        <f t="shared" ca="1" si="16"/>
-        <v>61241396.303359948</v>
+        <f t="shared" ca="1" si="15"/>
+        <v>60049068.316988632</v>
       </c>
       <c r="K74" s="186">
         <f>SUM(K69:K73)</f>
-        <v>1742507061.8928461</v>
+        <v>1650265137.9438322</v>
       </c>
       <c r="L74" s="186">
-        <f t="shared" ca="1" si="17"/>
-        <v>64537298.588623933</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>63471736.074762776</v>
       </c>
     </row>
     <row r="75" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -12116,10 +12112,10 @@
       <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="261" t="s">
+      <c r="B78" s="270" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="270" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -12148,14 +12144,14 @@
       </c>
       <c r="D80" s="131">
         <f>SUMIF($B$10:$B$26,$T80,$F$10:$F$26)+SUMIF($B$10:$B$26,$U80,$F$10:$F$26)</f>
-        <v>972973.02</v>
+        <v>74432433.089969993</v>
       </c>
       <c r="T80" t="str">
-        <f t="shared" ref="T80:U93" si="18">T51</f>
+        <f t="shared" ref="T80:U93" si="17">T51</f>
         <v>Picrom Stalyon</v>
       </c>
       <c r="U80" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>n/a</v>
       </c>
     </row>
@@ -12167,15 +12163,15 @@
         <v>70</v>
       </c>
       <c r="D81" s="132">
-        <f t="shared" ref="D81:D93" si="19">SUMIF($B$10:$B$26,$T81,$F$10:$F$26)+SUMIF($B$10:$B$26,$U81,$F$10:$F$26)</f>
-        <v>4378378.59</v>
+        <f t="shared" ref="D81:D93" si="18">SUMIF($B$10:$B$26,$T81,$F$10:$F$26)+SUMIF($B$10:$B$26,$U81,$F$10:$F$26)</f>
+        <v>25301801.710000001</v>
       </c>
       <c r="T81" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>I MADE LUIH</v>
       </c>
       <c r="U81" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>I Made Luih (Sanur)</v>
       </c>
     </row>
@@ -12187,15 +12183,15 @@
         <v>172</v>
       </c>
       <c r="D82" s="132">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T82" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NN Made Luih</v>
       </c>
       <c r="U82" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>n/a</v>
       </c>
     </row>
@@ -12207,15 +12203,15 @@
         <v>72</v>
       </c>
       <c r="D83" s="131">
-        <f t="shared" si="19"/>
-        <v>18467747.989999998</v>
+        <f t="shared" si="18"/>
+        <v>24683964.210000001</v>
       </c>
       <c r="T83" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>Juni</v>
       </c>
       <c r="U83" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>n/a</v>
       </c>
     </row>
@@ -12227,15 +12223,15 @@
         <v>221</v>
       </c>
       <c r="D84" s="132">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T84" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>FIB</v>
       </c>
       <c r="U84" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>n/a</v>
       </c>
     </row>
@@ -12247,15 +12243,15 @@
         <v>225</v>
       </c>
       <c r="D85" s="131">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>29513694.069988001</v>
       </c>
       <c r="T85" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>Ronald</v>
       </c>
       <c r="U85" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>n/a</v>
       </c>
     </row>
@@ -12267,15 +12263,15 @@
         <v>77</v>
       </c>
       <c r="D86" s="132">
-        <f t="shared" si="19"/>
-        <v>142163962.83000001</v>
+        <f t="shared" si="18"/>
+        <v>172490989.74000001</v>
       </c>
       <c r="T86" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>Monica</v>
       </c>
       <c r="U86" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>n/a</v>
       </c>
     </row>
@@ -12287,15 +12283,15 @@
         <v>79</v>
       </c>
       <c r="D87" s="131">
-        <f t="shared" si="19"/>
-        <v>7967567.5999999996</v>
+        <f t="shared" si="18"/>
+        <v>18955856.199965</v>
       </c>
       <c r="T87" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>Sujana</v>
       </c>
       <c r="U87" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>n/a</v>
       </c>
     </row>
@@ -12307,15 +12303,15 @@
         <v>173</v>
       </c>
       <c r="D88" s="132">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T88" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NN Sujana</v>
       </c>
       <c r="U88" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>n/a</v>
       </c>
     </row>
@@ -12327,15 +12323,15 @@
         <v>81</v>
       </c>
       <c r="D89" s="132">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f t="shared" si="18"/>
+        <v>972973.02</v>
       </c>
       <c r="T89" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>Wahyu</v>
       </c>
       <c r="U89" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>n/a</v>
       </c>
     </row>
@@ -12347,15 +12343,15 @@
         <v>83</v>
       </c>
       <c r="D90" s="131">
-        <f t="shared" si="19"/>
-        <v>29344144.359993</v>
+        <f t="shared" si="18"/>
+        <v>61440000.609972998</v>
       </c>
       <c r="T90" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>Taufik</v>
       </c>
       <c r="U90" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>n/a</v>
       </c>
     </row>
@@ -12367,15 +12363,15 @@
         <v>85</v>
       </c>
       <c r="D91" s="132">
-        <f t="shared" si="19"/>
-        <v>9891892.1299849991</v>
+        <f t="shared" si="18"/>
+        <v>18115315.679985002</v>
       </c>
       <c r="T91" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>Dewi Kristiani</v>
       </c>
       <c r="U91" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>n/a</v>
       </c>
     </row>
@@ -12387,15 +12383,15 @@
         <v>87</v>
       </c>
       <c r="D92" s="131">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f t="shared" si="18"/>
+        <v>3565405.4871999999</v>
       </c>
       <c r="T92" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>Wira</v>
       </c>
       <c r="U92" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>n/a</v>
       </c>
     </row>
@@ -12407,15 +12403,15 @@
         <v>89</v>
       </c>
       <c r="D93" s="132">
-        <f t="shared" si="19"/>
-        <v>14486486.800000001</v>
+        <f t="shared" si="18"/>
+        <v>16162162.5</v>
       </c>
       <c r="T93" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>Ni Ketut Sriasih (GT)</v>
       </c>
       <c r="U93" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>Ni Ketut Sriasih (MT)</v>
       </c>
     </row>
@@ -12426,18 +12422,12 @@
       <c r="C94" s="58"/>
       <c r="D94" s="120">
         <f>SUM(D80:D93)</f>
-        <v>257186847.38996604</v>
+        <v>445634596.31708103</v>
       </c>
     </row>
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -12452,6 +12442,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -13079,11 +13075,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="271" t="s">
+      <c r="B40" s="261" t="s">
         <v>174</v>
       </c>
-      <c r="C40" s="272"/>
-      <c r="D40" s="273"/>
+      <c r="C40" s="262"/>
+      <c r="D40" s="263"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -13403,33 +13399,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="274" t="s">
+      <c r="B48" s="264" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="275"/>
-      <c r="D48" s="275"/>
-      <c r="E48" s="275"/>
-      <c r="F48" s="275"/>
-      <c r="G48" s="275"/>
-      <c r="H48" s="275"/>
-      <c r="I48" s="275"/>
-      <c r="J48" s="275"/>
-      <c r="K48" s="275"/>
-      <c r="L48" s="285"/>
-      <c r="M48" s="262" t="s">
+      <c r="C48" s="265"/>
+      <c r="D48" s="265"/>
+      <c r="E48" s="265"/>
+      <c r="F48" s="265"/>
+      <c r="G48" s="265"/>
+      <c r="H48" s="265"/>
+      <c r="I48" s="265"/>
+      <c r="J48" s="265"/>
+      <c r="K48" s="265"/>
+      <c r="L48" s="288"/>
+      <c r="M48" s="271" t="s">
         <v>185</v>
       </c>
-      <c r="N48" s="263"/>
-      <c r="O48" s="263"/>
-      <c r="P48" s="263"/>
-      <c r="Q48" s="263"/>
-      <c r="R48" s="264"/>
+      <c r="N48" s="272"/>
+      <c r="O48" s="272"/>
+      <c r="P48" s="272"/>
+      <c r="Q48" s="272"/>
+      <c r="R48" s="273"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="286" t="s">
+      <c r="B49" s="289" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="286" t="s">
+      <c r="C49" s="289" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="255" t="s">
@@ -13438,49 +13434,49 @@
       <c r="E49" s="256"/>
       <c r="F49" s="256"/>
       <c r="G49" s="257"/>
-      <c r="H49" s="287" t="s">
+      <c r="H49" s="290" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="288"/>
-      <c r="J49" s="288"/>
-      <c r="K49" s="289"/>
-      <c r="L49" s="290" t="s">
+      <c r="I49" s="291"/>
+      <c r="J49" s="291"/>
+      <c r="K49" s="292"/>
+      <c r="L49" s="293" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="265" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="267" t="str">
+      <c r="O49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="267" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="269" t="str">
+      <c r="Q49" s="278" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="269" t="str">
+      <c r="R49" s="278" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="261"/>
-      <c r="C50" s="261"/>
+      <c r="B50" s="270"/>
+      <c r="C50" s="270"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -13505,13 +13501,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="291"/>
-      <c r="M50" s="266"/>
-      <c r="N50" s="266"/>
-      <c r="O50" s="268"/>
-      <c r="P50" s="268"/>
-      <c r="Q50" s="270"/>
-      <c r="R50" s="270"/>
+      <c r="L50" s="294"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
+      <c r="O50" s="277"/>
+      <c r="P50" s="277"/>
+      <c r="Q50" s="279"/>
+      <c r="R50" s="279"/>
       <c r="T50" s="178" t="s">
         <v>215</v>
       </c>
@@ -14627,21 +14623,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="292" t="s">
+      <c r="B67" s="285" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="293"/>
-      <c r="D67" s="293"/>
-      <c r="E67" s="293"/>
+      <c r="C67" s="286"/>
+      <c r="D67" s="286"/>
+      <c r="E67" s="286"/>
       <c r="F67" s="295"/>
-      <c r="G67" s="262" t="s">
+      <c r="G67" s="271" t="s">
         <v>185</v>
       </c>
-      <c r="H67" s="263"/>
-      <c r="I67" s="263"/>
-      <c r="J67" s="263"/>
-      <c r="K67" s="263"/>
-      <c r="L67" s="264"/>
+      <c r="H67" s="272"/>
+      <c r="I67" s="272"/>
+      <c r="J67" s="272"/>
+      <c r="K67" s="272"/>
+      <c r="L67" s="273"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -14962,10 +14958,10 @@
       <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="261" t="s">
+      <c r="B78" s="270" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="270" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -15278,12 +15274,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -15298,6 +15288,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -15925,11 +15921,11 @@
       </c>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="271" t="s">
+      <c r="B40" s="261" t="s">
         <v>176</v>
       </c>
-      <c r="C40" s="272"/>
-      <c r="D40" s="273"/>
+      <c r="C40" s="262"/>
+      <c r="D40" s="263"/>
       <c r="E40" s="66" t="s">
         <v>137</v>
       </c>
@@ -16249,33 +16245,33 @@
       <c r="S47" s="173"/>
     </row>
     <row r="48" spans="2:19" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="274" t="s">
+      <c r="B48" s="264" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="275"/>
-      <c r="D48" s="275"/>
-      <c r="E48" s="275"/>
-      <c r="F48" s="275"/>
-      <c r="G48" s="275"/>
-      <c r="H48" s="275"/>
-      <c r="I48" s="275"/>
-      <c r="J48" s="275"/>
-      <c r="K48" s="275"/>
-      <c r="L48" s="285"/>
-      <c r="M48" s="262" t="s">
+      <c r="C48" s="265"/>
+      <c r="D48" s="265"/>
+      <c r="E48" s="265"/>
+      <c r="F48" s="265"/>
+      <c r="G48" s="265"/>
+      <c r="H48" s="265"/>
+      <c r="I48" s="265"/>
+      <c r="J48" s="265"/>
+      <c r="K48" s="265"/>
+      <c r="L48" s="288"/>
+      <c r="M48" s="271" t="s">
         <v>185</v>
       </c>
-      <c r="N48" s="263"/>
-      <c r="O48" s="263"/>
-      <c r="P48" s="263"/>
-      <c r="Q48" s="263"/>
-      <c r="R48" s="264"/>
+      <c r="N48" s="272"/>
+      <c r="O48" s="272"/>
+      <c r="P48" s="272"/>
+      <c r="Q48" s="272"/>
+      <c r="R48" s="273"/>
     </row>
     <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="286" t="s">
+      <c r="B49" s="289" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="286" t="s">
+      <c r="C49" s="289" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="255" t="s">
@@ -16284,49 +16280,49 @@
       <c r="E49" s="256"/>
       <c r="F49" s="256"/>
       <c r="G49" s="257"/>
-      <c r="H49" s="287" t="s">
+      <c r="H49" s="290" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="288"/>
-      <c r="J49" s="288"/>
-      <c r="K49" s="289"/>
-      <c r="L49" s="290" t="s">
+      <c r="I49" s="291"/>
+      <c r="J49" s="291"/>
+      <c r="K49" s="292"/>
+      <c r="L49" s="293" t="s">
         <v>139</v>
       </c>
-      <c r="M49" s="265" t="str">
+      <c r="M49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="N49" s="265" t="str">
+      <c r="N49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$40,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="O49" s="267" t="str">
+      <c r="O49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="P49" s="267" t="str">
+      <c r="P49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$40,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="Q49" s="269" t="str">
+      <c r="Q49" s="278" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="R49" s="269" t="str">
+      <c r="R49" s="278" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$40,"0%")</f>
         <v>PER HARI
 100%</v>
       </c>
     </row>
     <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="261"/>
-      <c r="C50" s="261"/>
+      <c r="B50" s="270"/>
+      <c r="C50" s="270"/>
       <c r="D50" s="70" t="s">
         <v>149</v>
       </c>
@@ -16351,13 +16347,13 @@
       <c r="K50" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="L50" s="291"/>
-      <c r="M50" s="266"/>
-      <c r="N50" s="266"/>
-      <c r="O50" s="268"/>
-      <c r="P50" s="268"/>
-      <c r="Q50" s="270"/>
-      <c r="R50" s="270"/>
+      <c r="L50" s="294"/>
+      <c r="M50" s="275"/>
+      <c r="N50" s="275"/>
+      <c r="O50" s="277"/>
+      <c r="P50" s="277"/>
+      <c r="Q50" s="279"/>
+      <c r="R50" s="279"/>
       <c r="T50" s="178" t="s">
         <v>215</v>
       </c>
@@ -17459,21 +17455,21 @@
       <c r="I66" s="111"/>
     </row>
     <row r="67" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="292" t="s">
+      <c r="B67" s="285" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="293"/>
-      <c r="D67" s="293"/>
-      <c r="E67" s="293"/>
+      <c r="C67" s="286"/>
+      <c r="D67" s="286"/>
+      <c r="E67" s="286"/>
       <c r="F67" s="295"/>
-      <c r="G67" s="262" t="s">
+      <c r="G67" s="271" t="s">
         <v>185</v>
       </c>
-      <c r="H67" s="263"/>
-      <c r="I67" s="263"/>
-      <c r="J67" s="263"/>
-      <c r="K67" s="263"/>
-      <c r="L67" s="264"/>
+      <c r="H67" s="272"/>
+      <c r="I67" s="272"/>
+      <c r="J67" s="272"/>
+      <c r="K67" s="272"/>
+      <c r="L67" s="273"/>
     </row>
     <row r="68" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
@@ -17794,10 +17790,10 @@
       <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="261" t="s">
+      <c r="B78" s="270" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="270" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -18110,12 +18106,6 @@
     <row r="95" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="G67:L67"/>
     <mergeCell ref="B48:L48"/>
     <mergeCell ref="M48:R48"/>
@@ -18130,6 +18120,12 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <conditionalFormatting sqref="L51:L64">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -25916,11 +25912,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="271" t="s">
+      <c r="B41" s="261" t="s">
         <v>177</v>
       </c>
-      <c r="C41" s="272"/>
-      <c r="D41" s="273"/>
+      <c r="C41" s="262"/>
+      <c r="D41" s="263"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -26191,59 +26187,59 @@
       </c>
     </row>
     <row r="48" spans="2:19" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="274" t="s">
+      <c r="B48" s="264" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="275"/>
-      <c r="D48" s="275"/>
-      <c r="E48" s="275"/>
-      <c r="F48" s="275"/>
-      <c r="G48" s="275"/>
-      <c r="H48" s="275"/>
-      <c r="I48" s="275"/>
-      <c r="J48" s="275"/>
-      <c r="K48" s="262" t="s">
+      <c r="C48" s="265"/>
+      <c r="D48" s="265"/>
+      <c r="E48" s="265"/>
+      <c r="F48" s="265"/>
+      <c r="G48" s="265"/>
+      <c r="H48" s="265"/>
+      <c r="I48" s="265"/>
+      <c r="J48" s="265"/>
+      <c r="K48" s="271" t="s">
         <v>185</v>
       </c>
-      <c r="L48" s="263"/>
-      <c r="M48" s="263"/>
-      <c r="N48" s="263"/>
-      <c r="O48" s="263"/>
-      <c r="P48" s="264"/>
+      <c r="L48" s="272"/>
+      <c r="M48" s="272"/>
+      <c r="N48" s="272"/>
+      <c r="O48" s="272"/>
+      <c r="P48" s="273"/>
       <c r="Q48"/>
       <c r="R48"/>
     </row>
     <row r="49" spans="2:18" s="139" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="279" t="s">
+      <c r="B49" s="269" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="279" t="s">
+      <c r="C49" s="269" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="276" t="s">
+      <c r="D49" s="266" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="277"/>
-      <c r="F49" s="278"/>
+      <c r="E49" s="267"/>
+      <c r="F49" s="268"/>
       <c r="G49" s="140" t="s">
         <v>138</v>
       </c>
       <c r="H49" s="140"/>
       <c r="I49" s="140"/>
-      <c r="J49" s="276" t="s">
+      <c r="J49" s="266" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="265" t="str">
+      <c r="K49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="265" t="str">
+      <c r="L49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="267" t="str">
+      <c r="M49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
@@ -26258,7 +26254,7 @@
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="269" t="str">
+      <c r="P49" s="278" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -26267,8 +26263,8 @@
       <c r="R49"/>
     </row>
     <row r="50" spans="2:18" s="139" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="279"/>
-      <c r="C50" s="279"/>
+      <c r="B50" s="269"/>
+      <c r="C50" s="269"/>
       <c r="D50" s="141" t="s">
         <v>149</v>
       </c>
@@ -26287,13 +26283,13 @@
       <c r="I50" s="142" t="s">
         <v>130</v>
       </c>
-      <c r="J50" s="276"/>
-      <c r="K50" s="266"/>
-      <c r="L50" s="266"/>
-      <c r="M50" s="268"/>
+      <c r="J50" s="266"/>
+      <c r="K50" s="275"/>
+      <c r="L50" s="275"/>
+      <c r="M50" s="277"/>
       <c r="N50" s="188"/>
       <c r="O50" s="183"/>
-      <c r="P50" s="270"/>
+      <c r="P50" s="279"/>
       <c r="Q50"/>
       <c r="R50"/>
     </row>
@@ -27634,10 +27630,10 @@
       <c r="I77"/>
     </row>
     <row r="78" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="261" t="s">
+      <c r="B78" s="270" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="270" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -27836,13 +27832,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="J49:J50"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
     <mergeCell ref="K48:P48"/>
@@ -27852,6 +27841,13 @@
     <mergeCell ref="P49:P50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="J49:J50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="26" priority="8">
@@ -28891,25 +28887,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="274" t="s">
+      <c r="B48" s="264" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="275"/>
-      <c r="D48" s="275"/>
-      <c r="E48" s="275"/>
-      <c r="F48" s="275"/>
-      <c r="G48" s="275"/>
-      <c r="H48" s="275"/>
-      <c r="I48" s="275"/>
-      <c r="J48" s="275"/>
-      <c r="K48" s="262" t="s">
+      <c r="C48" s="265"/>
+      <c r="D48" s="265"/>
+      <c r="E48" s="265"/>
+      <c r="F48" s="265"/>
+      <c r="G48" s="265"/>
+      <c r="H48" s="265"/>
+      <c r="I48" s="265"/>
+      <c r="J48" s="265"/>
+      <c r="K48" s="271" t="s">
         <v>185</v>
       </c>
-      <c r="L48" s="263"/>
-      <c r="M48" s="263"/>
-      <c r="N48" s="263"/>
-      <c r="O48" s="263"/>
-      <c r="P48" s="264"/>
+      <c r="L48" s="272"/>
+      <c r="M48" s="272"/>
+      <c r="N48" s="272"/>
+      <c r="O48" s="272"/>
+      <c r="P48" s="273"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="260" t="s">
@@ -28931,32 +28927,32 @@
       <c r="J49" s="255" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="265" t="str">
+      <c r="K49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="265" t="str">
+      <c r="L49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="267" t="str">
+      <c r="M49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="267" t="str">
+      <c r="N49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="269" t="str">
+      <c r="O49" s="278" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="269" t="str">
+      <c r="P49" s="278" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -28984,12 +28980,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="255"/>
-      <c r="K50" s="266"/>
-      <c r="L50" s="266"/>
-      <c r="M50" s="268"/>
-      <c r="N50" s="268"/>
-      <c r="O50" s="270"/>
-      <c r="P50" s="270"/>
+      <c r="K50" s="275"/>
+      <c r="L50" s="275"/>
+      <c r="M50" s="277"/>
+      <c r="N50" s="277"/>
+      <c r="O50" s="279"/>
+      <c r="P50" s="279"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="167" t="s">
@@ -30226,10 +30222,10 @@
       <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="261" t="s">
+      <c r="B78" s="270" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="270" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -30423,17 +30419,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -30441,6 +30426,17 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="23" priority="1">
@@ -31198,11 +31194,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="271" t="s">
+      <c r="B41" s="261" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="272"/>
-      <c r="D41" s="273"/>
+      <c r="C41" s="262"/>
+      <c r="D41" s="263"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -31477,25 +31473,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="274" t="s">
+      <c r="B48" s="264" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="275"/>
-      <c r="D48" s="275"/>
-      <c r="E48" s="275"/>
-      <c r="F48" s="275"/>
-      <c r="G48" s="275"/>
-      <c r="H48" s="275"/>
-      <c r="I48" s="275"/>
-      <c r="J48" s="275"/>
-      <c r="K48" s="262" t="s">
+      <c r="C48" s="265"/>
+      <c r="D48" s="265"/>
+      <c r="E48" s="265"/>
+      <c r="F48" s="265"/>
+      <c r="G48" s="265"/>
+      <c r="H48" s="265"/>
+      <c r="I48" s="265"/>
+      <c r="J48" s="265"/>
+      <c r="K48" s="271" t="s">
         <v>185</v>
       </c>
-      <c r="L48" s="263"/>
-      <c r="M48" s="263"/>
-      <c r="N48" s="263"/>
-      <c r="O48" s="263"/>
-      <c r="P48" s="264"/>
+      <c r="L48" s="272"/>
+      <c r="M48" s="272"/>
+      <c r="N48" s="272"/>
+      <c r="O48" s="272"/>
+      <c r="P48" s="273"/>
     </row>
     <row r="49" spans="2:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="260" t="s">
@@ -31517,32 +31513,32 @@
       <c r="J49" s="255" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="265" t="str">
+      <c r="K49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="265" t="str">
+      <c r="L49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="267" t="str">
+      <c r="M49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="267" t="str">
+      <c r="N49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
       </c>
-      <c r="O49" s="269" t="str">
+      <c r="O49" s="278" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>SELISIH
 100%</v>
       </c>
-      <c r="P49" s="269" t="str">
+      <c r="P49" s="278" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($L$41,"0%")</f>
         <v>PER HARI
 100%</v>
@@ -31570,12 +31566,12 @@
         <v>130</v>
       </c>
       <c r="J50" s="255"/>
-      <c r="K50" s="266"/>
-      <c r="L50" s="266"/>
-      <c r="M50" s="268"/>
-      <c r="N50" s="268"/>
-      <c r="O50" s="270"/>
-      <c r="P50" s="270"/>
+      <c r="K50" s="275"/>
+      <c r="L50" s="275"/>
+      <c r="M50" s="277"/>
+      <c r="N50" s="277"/>
+      <c r="O50" s="279"/>
+      <c r="P50" s="279"/>
     </row>
     <row r="51" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
@@ -32812,10 +32808,10 @@
       <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="261" t="s">
+      <c r="B78" s="270" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="270" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -32996,17 +32992,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B77:D77"/>
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="K49:K50"/>
@@ -33014,6 +32999,17 @@
     <mergeCell ref="M49:M50"/>
     <mergeCell ref="O49:O50"/>
     <mergeCell ref="P49:P50"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -33792,11 +33788,11 @@
       </c>
     </row>
     <row r="41" spans="2:19" s="191" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="271" t="s">
+      <c r="B41" s="261" t="s">
         <v>188</v>
       </c>
-      <c r="C41" s="272"/>
-      <c r="D41" s="273"/>
+      <c r="C41" s="262"/>
+      <c r="D41" s="263"/>
       <c r="E41" s="66" t="s">
         <v>137</v>
       </c>
@@ -34071,25 +34067,25 @@
       </c>
     </row>
     <row r="48" spans="2:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="274" t="s">
+      <c r="B48" s="264" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="275"/>
-      <c r="D48" s="275"/>
-      <c r="E48" s="275"/>
-      <c r="F48" s="275"/>
-      <c r="G48" s="275"/>
-      <c r="H48" s="275"/>
-      <c r="I48" s="275"/>
-      <c r="J48" s="275"/>
-      <c r="K48" s="262" t="s">
+      <c r="C48" s="265"/>
+      <c r="D48" s="265"/>
+      <c r="E48" s="265"/>
+      <c r="F48" s="265"/>
+      <c r="G48" s="265"/>
+      <c r="H48" s="265"/>
+      <c r="I48" s="265"/>
+      <c r="J48" s="265"/>
+      <c r="K48" s="271" t="s">
         <v>185</v>
       </c>
-      <c r="L48" s="263"/>
-      <c r="M48" s="263"/>
-      <c r="N48" s="263"/>
-      <c r="O48" s="263"/>
-      <c r="P48" s="264"/>
+      <c r="L48" s="272"/>
+      <c r="M48" s="272"/>
+      <c r="N48" s="272"/>
+      <c r="O48" s="272"/>
+      <c r="P48" s="273"/>
     </row>
     <row r="49" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="260" t="s">
@@ -34111,22 +34107,22 @@
       <c r="J49" s="255" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="265" t="str">
+      <c r="K49" s="274" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>SELISIH
 90%</v>
       </c>
-      <c r="L49" s="265" t="str">
+      <c r="L49" s="274" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($H$41,"0%")</f>
         <v>PER HARI
 90%</v>
       </c>
-      <c r="M49" s="267" t="str">
+      <c r="M49" s="276" t="str">
         <f>"SELISIH"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>SELISIH
 95%</v>
       </c>
-      <c r="N49" s="267" t="str">
+      <c r="N49" s="276" t="str">
         <f>"PER HARI"&amp;CHAR(10)&amp;TEXT($J$41,"0%")</f>
         <v>PER HARI
 95%</v>
@@ -34164,10 +34160,10 @@
         <v>130</v>
       </c>
       <c r="J50" s="255"/>
-      <c r="K50" s="266"/>
-      <c r="L50" s="266"/>
-      <c r="M50" s="268"/>
-      <c r="N50" s="268"/>
+      <c r="K50" s="275"/>
+      <c r="L50" s="275"/>
+      <c r="M50" s="277"/>
+      <c r="N50" s="277"/>
       <c r="O50" s="284"/>
       <c r="P50" s="284"/>
     </row>
@@ -35406,10 +35402,10 @@
       <c r="D77" s="253"/>
     </row>
     <row r="78" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="261" t="s">
+      <c r="B78" s="270" t="s">
         <v>41</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="270" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="231" t="s">
@@ -35603,11 +35599,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
     <mergeCell ref="K48:P48"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
@@ -35621,6 +35612,11 @@
     <mergeCell ref="N49:N50"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:J48"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <conditionalFormatting sqref="J51:J64">
     <cfRule type="expression" dxfId="17" priority="1">

--- a/uploads/DATA PENCAPAIAN 2026.xlsx
+++ b/uploads/DATA PENCAPAIAN 2026.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA PENCAPAIAN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YULI\TALITHA\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03BEA8A-2C3C-4C2D-A956-D4906EBA5629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" tabRatio="500" firstSheet="4" activeTab="11"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="4" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HOW TO USE" sheetId="1" r:id="rId1"/>
@@ -27,29 +28,17 @@
     <sheet name="NOV" sheetId="13" r:id="rId13"/>
     <sheet name="DES" sheetId="14" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Microsoft Office User</author>
   </authors>
   <commentList>
-    <comment ref="H41" authorId="0" shapeId="0">
+    <comment ref="H41" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000001000000}">
       <text>
         <r>
           <rPr>
@@ -63,7 +52,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J41" authorId="0" shapeId="0">
+    <comment ref="J41" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000002000000}">
       <text>
         <r>
           <rPr>
@@ -101,12 +90,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Microsoft Office User</author>
   </authors>
   <commentList>
-    <comment ref="C3" authorId="0" shapeId="0">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000001000000}">
       <text>
         <r>
           <rPr>
@@ -130,7 +119,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0" shapeId="0">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000002000000}">
       <text>
         <r>
           <rPr>
@@ -163,7 +152,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J4" authorId="0" shapeId="0">
+    <comment ref="J4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000003000000}">
       <text>
         <r>
           <rPr>
@@ -187,7 +176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J5" authorId="0" shapeId="0">
+    <comment ref="J5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000004000000}">
       <text>
         <r>
           <rPr>
@@ -225,7 +214,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2120" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="228">
   <si>
     <t>📊  PANDUAN PENGGUNAAN — DATA PENCAPAIAN 2026</t>
   </si>
@@ -909,16 +898,18 @@
     <t>DATA PENCAPAIAN — GLOBAL —  30 SEPTEMBER 2026</t>
   </si>
   <si>
-    <t>DATA PENCAPAIAN — GLOBAL —  2 OKTOBER 2026</t>
+    <t>DATA PENCAPAIAN — GLOBAL —  3 OKTOBER 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="2">
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="#,##0.#0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="#,##0.#0"/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="58" x14ac:knownFonts="1">
     <font>
@@ -1802,11 +1793,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="296">
+  <cellXfs count="297">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1844,7 +1836,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2116,7 +2108,7 @@
     <xf numFmtId="9" fontId="21" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2125,35 +2117,35 @@
     <xf numFmtId="0" fontId="26" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="41" fontId="29" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="29" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="29" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="10" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2186,19 +2178,19 @@
     <xf numFmtId="3" fontId="10" fillId="26" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="22" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="22" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2207,35 +2199,35 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="26" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="41" fontId="36" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="36" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="36" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="36" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="38" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="38" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="38" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="38" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="38" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="38" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="38" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="38" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="33" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="33" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="33" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="33" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2262,25 +2254,25 @@
     <xf numFmtId="0" fontId="40" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="41" fontId="38" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="38" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="38" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="38" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="33" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="33" fillId="16" borderId="1" xfId="0" app